--- a/src/xlsx/cleaned_data.xlsx
+++ b/src/xlsx/cleaned_data.xlsx
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,34 +539,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>77314</v>
+        <v>76721</v>
       </c>
       <c r="F2" t="n">
-        <v>1552722866590</v>
+        <v>1540822738759</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>28639817629</v>
+        <v>15423566617</v>
       </c>
       <c r="I2" t="n">
-        <v>79607</v>
+        <v>77479</v>
       </c>
       <c r="J2" t="n">
-        <v>76952</v>
+        <v>76516</v>
       </c>
       <c r="K2" t="n">
-        <v>-262.4575759976724</v>
+        <v>-567.5499394721992</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.40435</v>
+        <v>-0.73433</v>
       </c>
       <c r="M2" t="n">
-        <v>20083262</v>
+        <v>20083712</v>
       </c>
       <c r="N2" t="n">
-        <v>20083312</v>
+        <v>20083803</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -575,7 +575,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -587,7 +587,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,34 +606,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2534.68</v>
+        <v>2475.01</v>
       </c>
       <c r="F3" t="n">
-        <v>309335837072</v>
+        <v>302065765195</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>21125178458</v>
+        <v>8681587348</v>
       </c>
       <c r="I3" t="n">
-        <v>2647.68</v>
+        <v>2543.69</v>
       </c>
       <c r="J3" t="n">
-        <v>2492.31</v>
+        <v>2470.18</v>
       </c>
       <c r="K3" t="n">
-        <v>40.13</v>
+        <v>-63.41930568684711</v>
       </c>
       <c r="L3" t="n">
-        <v>1.54763</v>
+        <v>-2.49837</v>
       </c>
       <c r="M3" t="n">
-        <v>122041373.1030534</v>
+        <v>122044301.968694</v>
       </c>
       <c r="N3" t="n">
-        <v>122041373.1030533</v>
+        <v>122044301.968694</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -642,19 +642,19 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.19893376061168</v>
+        <v>0.1957521731289227</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,28 +673,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.99981</v>
+        <v>0.9997549999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>183482230974</v>
+        <v>183471976747</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>59719219122</v>
+        <v>31189029121</v>
       </c>
       <c r="I4" t="n">
-        <v>0.99993</v>
+        <v>0.9999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999562</v>
+        <v>0.999673</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00025862</v>
+        <v>-2.4432368397109e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02306</v>
+        <v>-0.00244</v>
       </c>
       <c r="M4" t="n">
         <v>183517171052.1943</v>
@@ -709,19 +709,19 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1178511430863342</v>
+        <v>0.1187566052530865</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,34 +740,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>736.4299999999999</v>
+        <v>715.63</v>
       </c>
       <c r="F5" t="n">
-        <v>98062399038</v>
+        <v>95291988111</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1194854270</v>
+        <v>729267845</v>
       </c>
       <c r="I5" t="n">
-        <v>740.12</v>
+        <v>736.9</v>
       </c>
       <c r="J5" t="n">
-        <v>717.4400000000001</v>
+        <v>714.33</v>
       </c>
       <c r="K5" t="n">
-        <v>14.67</v>
+        <v>-20.34689269518844</v>
       </c>
       <c r="L5" t="n">
-        <v>1.99022</v>
+        <v>-2.76462</v>
       </c>
       <c r="M5" t="n">
-        <v>133161036.91</v>
+        <v>133160976.96</v>
       </c>
       <c r="N5" t="n">
-        <v>133161033.96</v>
+        <v>133160976.96</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -776,19 +776,19 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06281844456712928</v>
+        <v>0.06150682523370059</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -807,28 +807,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="F6" t="n">
-        <v>86186130739</v>
+        <v>84099500734</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2258448691</v>
+        <v>926219439</v>
       </c>
       <c r="I6" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="J6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0121198</v>
+        <v>-0.02964740290489787</v>
       </c>
       <c r="L6" t="n">
-        <v>0.73402</v>
+        <v>-2.16849</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -843,19 +843,19 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05516702360294676</v>
+        <v>0.05424023958184662</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,34 +874,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999865</v>
+        <v>0.999803</v>
       </c>
       <c r="F7" t="n">
-        <v>74337600627</v>
+        <v>74215368644</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>15757949678</v>
+        <v>6204149731</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999952</v>
+        <v>0.999961</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999771</v>
+        <v>0.999717</v>
       </c>
       <c r="K7" t="n">
-        <v>7.379e-05</v>
+        <v>-2.497102552268e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00401</v>
+        <v>-0.0025</v>
       </c>
       <c r="M7" t="n">
-        <v>74347671861.2077</v>
+        <v>74230204758.1429</v>
       </c>
       <c r="N7" t="n">
-        <v>74349866797.12619</v>
+        <v>74232084708.50609</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -910,19 +910,19 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04753347328130759</v>
+        <v>0.04782308761133666</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -941,34 +941,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102.26</v>
+        <v>99.78</v>
       </c>
       <c r="F8" t="n">
-        <v>59986196956</v>
+        <v>58544716598</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4038038163</v>
+        <v>1835705498</v>
       </c>
       <c r="I8" t="n">
-        <v>105.42</v>
+        <v>102.3</v>
       </c>
       <c r="J8" t="n">
-        <v>100.64</v>
+        <v>99.45</v>
       </c>
       <c r="K8" t="n">
-        <v>1.29</v>
+        <v>-2.106818682073197</v>
       </c>
       <c r="L8" t="n">
-        <v>1.16766</v>
+        <v>-2.06771</v>
       </c>
       <c r="M8" t="n">
-        <v>586632914.9787524</v>
+        <v>586731099.4701495</v>
       </c>
       <c r="N8" t="n">
-        <v>633924207.4848769</v>
+        <v>634018355.2162156</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -977,19 +977,19 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03828741819488104</v>
+        <v>0.03764910827349428</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1008,34 +1008,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.341025</v>
+        <v>0.340537</v>
       </c>
       <c r="F9" t="n">
-        <v>32378541531</v>
+        <v>32326642058</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>521177154</v>
+        <v>340530028</v>
       </c>
       <c r="I9" t="n">
-        <v>0.344079</v>
+        <v>0.341069</v>
       </c>
       <c r="J9" t="n">
-        <v>0.335532</v>
+        <v>0.339263</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00460594</v>
+        <v>0.00014634</v>
       </c>
       <c r="L9" t="n">
-        <v>1.36849</v>
+        <v>0.04299</v>
       </c>
       <c r="M9" t="n">
         <v>94944652948.92628</v>
       </c>
       <c r="N9" t="n">
-        <v>94946361438.41998</v>
+        <v>94948611026.79419</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1044,19 +1044,19 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0205008721037525</v>
+        <v>0.02062734377607768</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1075,34 +1075,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.016</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>22870501626</v>
+        <v>22551817529</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>60215308</v>
+        <v>50043</v>
       </c>
       <c r="I10" t="n">
-        <v>1.036</v>
+        <v>1.044</v>
       </c>
       <c r="J10" t="n">
-        <v>1.016</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0185665039219145</v>
+        <v>-0.01618492385492987</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.79099</v>
+        <v>-1.59239</v>
       </c>
       <c r="M10" t="n">
-        <v>22502232981.668</v>
+        <v>22547102017.768</v>
       </c>
       <c r="N10" t="n">
-        <v>22502232981.668</v>
+        <v>22552850918.668</v>
       </c>
       <c r="O10" t="n">
         <v>1.061</v>
@@ -1111,19 +1111,19 @@
         <v>46237.59675925926</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.05567129629</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01437520922499061</v>
+        <v>0.01428115840375518</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1142,34 +1142,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1158.26</v>
+        <v>1087.03</v>
       </c>
       <c r="F11" t="n">
-        <v>19604336005</v>
+        <v>18394302590</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>1665786195</v>
+        <v>1165436311</v>
       </c>
       <c r="I11" t="n">
-        <v>1215.61</v>
+        <v>1154.85</v>
       </c>
       <c r="J11" t="n">
-        <v>1121.91</v>
+        <v>1075.39</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.629609895717067</v>
+        <v>-67.91789754973047</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1411</v>
+        <v>-5.88059</v>
       </c>
       <c r="M11" t="n">
         <v>16925695.4780448</v>
       </c>
       <c r="N11" t="n">
-        <v>16928367.3530448</v>
+        <v>16930195.4780448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1178,19 +1178,19 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01227094486552713</v>
+        <v>0.01158194263647293</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1209,28 +1209,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>80.31999999999999</v>
+        <v>77.36</v>
       </c>
       <c r="F12" t="n">
-        <v>17867396242</v>
+        <v>17208887027</v>
       </c>
       <c r="G12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>1071366521</v>
+        <v>575492758</v>
       </c>
       <c r="I12" t="n">
-        <v>83.63</v>
+        <v>80.77</v>
       </c>
       <c r="J12" t="n">
-        <v>78.41</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.044752684165488</v>
+        <v>-2.878903719731241</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.36165</v>
+        <v>-3.58773</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1245,19 +1245,19 @@
         <v>46271.5199074074</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01115190166259954</v>
+        <v>0.01081232606855243</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1276,34 +1276,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.085033</v>
+        <v>0.08321099999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>13255413715</v>
+        <v>12972524811</v>
       </c>
       <c r="G13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H13" t="n">
-        <v>651168802</v>
+        <v>331894085</v>
       </c>
       <c r="I13" t="n">
-        <v>0.087898</v>
+        <v>0.085325</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08368</v>
+        <v>0.08315699999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00046809</v>
+        <v>-0.001738211689757158</v>
       </c>
       <c r="L13" t="n">
-        <v>0.50806</v>
+        <v>-2.04618</v>
       </c>
       <c r="M13" t="n">
-        <v>155884756383.7052</v>
+        <v>155898206383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>155884476383.7052</v>
+        <v>171610343126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1312,19 +1312,19 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.00818057945051188</v>
+        <v>0.008061919670230172</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1343,31 +1343,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01512165</v>
+        <v>0.01525428</v>
       </c>
       <c r="F14" t="n">
-        <v>10724534145</v>
+        <v>10818364725</v>
       </c>
       <c r="G14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H14" t="n">
-        <v>38289961</v>
+        <v>34695409</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01626765</v>
+        <v>0.01589978</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01509086</v>
+        <v>0.01503352</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000651524093373202</v>
+        <v>0.00017217</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.09935</v>
+        <v>1.14158</v>
       </c>
       <c r="M14" t="n">
-        <v>709217602168.6873</v>
+        <v>709218381891.3804</v>
       </c>
       <c r="N14" t="n">
         <v>1142408526965.963</v>
@@ -1379,19 +1379,19 @@
         <v>46259.82847222222</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.00655003149452222</v>
+        <v>0.006663357559283231</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1410,34 +1410,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>529.46</v>
+        <v>529.33</v>
       </c>
       <c r="F15" t="n">
-        <v>9955702220</v>
+        <v>9952232995</v>
       </c>
       <c r="G15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H15" t="n">
-        <v>123793672</v>
+        <v>97785882</v>
       </c>
       <c r="I15" t="n">
-        <v>546.62</v>
+        <v>543.63</v>
       </c>
       <c r="J15" t="n">
-        <v>509.38</v>
+        <v>524.34</v>
       </c>
       <c r="K15" t="n">
-        <v>16.48</v>
+        <v>-1.876506267517925</v>
       </c>
       <c r="L15" t="n">
-        <v>3.27851</v>
+        <v>-0.35326</v>
       </c>
       <c r="M15" t="n">
-        <v>18803665.4396461</v>
+        <v>18804107.03109685</v>
       </c>
       <c r="N15" t="n">
-        <v>18803679.83773144</v>
+        <v>18804122.63109685</v>
       </c>
       <c r="O15" t="n">
         <v>797.73</v>
@@ -1446,19 +1446,19 @@
         <v>46036.48202546296</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.006054702780083096</v>
+        <v>0.006101032118133577</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1477,34 +1477,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.999871</v>
+        <v>0.999763</v>
       </c>
       <c r="F16" t="n">
-        <v>9804836648</v>
+        <v>9846306603</v>
       </c>
       <c r="G16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H16" t="n">
-        <v>169068394</v>
+        <v>69915065</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0.999937</v>
       </c>
       <c r="J16" t="n">
         <v>0.999626</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00020096</v>
+        <v>1.663e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.00217</v>
+        <v>0.00166</v>
       </c>
       <c r="M16" t="n">
-        <v>9806099950.497782</v>
+        <v>9849589553.751617</v>
       </c>
       <c r="N16" t="n">
-        <v>9806099950.497782</v>
+        <v>9848763608.199549</v>
       </c>
       <c r="O16" t="n">
         <v>1.057</v>
@@ -1513,19 +1513,19 @@
         <v>45593.90336805556</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.005957505918972154</v>
+        <v>0.006032260702599832</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1544,28 +1544,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>80.37</v>
+        <v>79.53</v>
       </c>
       <c r="F17" t="n">
-        <v>9474296952</v>
+        <v>9375103870</v>
       </c>
       <c r="G17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H17" t="n">
-        <v>120604559</v>
+        <v>29764166</v>
       </c>
       <c r="I17" t="n">
-        <v>83.22</v>
+        <v>80.62</v>
       </c>
       <c r="J17" t="n">
-        <v>80</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.054638</v>
+        <v>-0.8357182138967261</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.18838</v>
+        <v>-1.03986</v>
       </c>
       <c r="M17" t="n">
         <v>117882016</v>
@@ -1580,19 +1580,19 @@
         <v>46276.58553240741</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005744551959378476</v>
+        <v>0.005726338086527162</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1611,28 +1611,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.57</v>
+        <v>11.24</v>
       </c>
       <c r="F18" t="n">
-        <v>8653159423</v>
+        <v>8409875424</v>
       </c>
       <c r="G18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H18" t="n">
-        <v>449714905</v>
+        <v>217162086</v>
       </c>
       <c r="I18" t="n">
-        <v>12.17</v>
+        <v>11.62</v>
       </c>
       <c r="J18" t="n">
-        <v>11.46</v>
+        <v>11.24</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02458788</v>
+        <v>-0.3109450215767513</v>
       </c>
       <c r="L18" t="n">
-        <v>0.05704</v>
+        <v>-2.69148</v>
       </c>
       <c r="M18" t="n">
         <v>748099970.424884</v>
@@ -1647,19 +1647,19 @@
         <v>44325.67635416667</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005215524764498022</v>
+        <v>0.005099675313524787</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1678,28 +1678,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.109999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="F19" t="n">
-        <v>8383078709</v>
+        <v>8329317905</v>
       </c>
       <c r="G19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H19" t="n">
-        <v>119813</v>
+        <v>253370</v>
       </c>
       <c r="I19" t="n">
-        <v>9.16</v>
+        <v>9.15</v>
       </c>
       <c r="J19" t="n">
-        <v>9.1</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.03313417990051093</v>
+        <v>-0.06044450122227296</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.36101</v>
+        <v>-0.6631</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1714,19 +1714,19 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.00504152219188058</v>
+        <v>0.005047374328766271</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1745,28 +1745,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.208994</v>
+        <v>0.20505</v>
       </c>
       <c r="F20" t="n">
-        <v>7840773190</v>
+        <v>7692716004</v>
       </c>
       <c r="G20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H20" t="n">
-        <v>484036030</v>
+        <v>203748626</v>
       </c>
       <c r="I20" t="n">
-        <v>0.215743</v>
+        <v>0.209134</v>
       </c>
       <c r="J20" t="n">
-        <v>0.203215</v>
+        <v>0.203378</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00173125</v>
+        <v>-0.003357533117483491</v>
       </c>
       <c r="L20" t="n">
-        <v>0.54303</v>
+        <v>-1.61104</v>
       </c>
       <c r="M20" t="n">
         <v>37516725700.17653</v>
@@ -1781,19 +1781,19 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004692135691626298</v>
+        <v>0.004634068324128231</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1812,31 +1812,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.181899</v>
+        <v>0.178693</v>
       </c>
       <c r="F21" t="n">
-        <v>6336215728</v>
+        <v>6224230152</v>
       </c>
       <c r="G21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H21" t="n">
-        <v>152590419</v>
+        <v>77381146</v>
       </c>
       <c r="I21" t="n">
-        <v>0.184869</v>
+        <v>0.182593</v>
       </c>
       <c r="J21" t="n">
-        <v>0.177114</v>
+        <v>0.177194</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00402238</v>
+        <v>-0.002332784981005254</v>
       </c>
       <c r="L21" t="n">
-        <v>2.13215</v>
+        <v>-1.28865</v>
       </c>
       <c r="M21" t="n">
-        <v>34833772973.98598</v>
+        <v>34833765117.35425</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70248</v>
@@ -1848,220 +1848,220 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R21" t="b">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.003722807429857964</v>
+        <v>0.003680671830331697</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>bitcoin-cash</t>
+          <t>ethena-usde</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>bch</t>
+          <t>usde</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bitcoin Cash</t>
+          <t>Ethena USDe</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>231.06</v>
+        <v>0.999617</v>
       </c>
       <c r="F22" t="n">
-        <v>4641577287</v>
+        <v>4600512204</v>
       </c>
       <c r="G22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H22" t="n">
-        <v>183606425</v>
+        <v>20823617</v>
       </c>
       <c r="I22" t="n">
-        <v>237.75</v>
+        <v>0.999852</v>
       </c>
       <c r="J22" t="n">
-        <v>225.57</v>
+        <v>0.999548</v>
       </c>
       <c r="K22" t="n">
-        <v>3.84</v>
+        <v>-0.000129444137486834</v>
       </c>
       <c r="L22" t="n">
-        <v>1.55399</v>
+        <v>-0.01295</v>
       </c>
       <c r="M22" t="n">
-        <v>20088074.89665078</v>
+        <v>4602286942.433918</v>
       </c>
       <c r="N22" t="n">
-        <v>20088099.89665078</v>
+        <v>4600286942.433918</v>
       </c>
       <c r="O22" t="n">
-        <v>3785.82</v>
+        <v>1.034</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>46000.38208333333</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R22" t="b">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.002631017334877644</v>
+        <v>0.002626492795219208</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ethena-usde</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>usde</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ethena USDe</t>
+          <t>Dai</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9997549999999999</v>
+        <v>0.999888</v>
       </c>
       <c r="F23" t="n">
-        <v>4599690699</v>
+        <v>4572090305</v>
       </c>
       <c r="G23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H23" t="n">
-        <v>57253693</v>
+        <v>88873493</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9999440000000001</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0.999438</v>
+        <v>0.999689</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0003092</v>
+        <v>0.00014913</v>
       </c>
       <c r="L23" t="n">
-        <v>0.02766</v>
+        <v>0.01492</v>
       </c>
       <c r="M23" t="n">
-        <v>4600819094.053699</v>
+        <v>4573046928.984426</v>
       </c>
       <c r="N23" t="n">
-        <v>4600819094.053699</v>
+        <v>4571846995.287507</v>
       </c>
       <c r="O23" t="n">
-        <v>1.034</v>
+        <v>1.22</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>46000.38208333333</v>
+        <v>43902.79363425926</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R23" t="b">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.002604031424028167</v>
+        <v>0.002608040224622948</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>bitcoin-cash</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>bch</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Dai</t>
+          <t>Bitcoin Cash</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.99977</v>
+        <v>224.01</v>
       </c>
       <c r="F24" t="n">
-        <v>4575781871</v>
+        <v>4499652482</v>
       </c>
       <c r="G24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H24" t="n">
-        <v>212008770</v>
+        <v>131335669</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>230.98</v>
       </c>
       <c r="J24" t="n">
-        <v>0.999699</v>
+        <v>221.91</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.000199777112947164</v>
+        <v>-6.427621685092504</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.0039</v>
+        <v>-2.78932</v>
       </c>
       <c r="M24" t="n">
-        <v>4576834066.613646</v>
+        <v>20088571.77165077</v>
       </c>
       <c r="N24" t="n">
-        <v>4575568673.433953</v>
+        <v>20088881.14665077</v>
       </c>
       <c r="O24" t="n">
-        <v>1.22</v>
+        <v>3785.82</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>43902.79363425926</v>
+        <v>43088.66666666666</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002588627889585986</v>
+        <v>0.002561010853265781</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2080,34 +2080,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.999718</v>
+        <v>0.999573</v>
       </c>
       <c r="F25" t="n">
-        <v>4301404459</v>
+        <v>4307249899</v>
       </c>
       <c r="G25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H25" t="n">
-        <v>1112443789</v>
+        <v>571994025</v>
       </c>
       <c r="I25" t="n">
-        <v>0.999893</v>
+        <v>0.999912</v>
       </c>
       <c r="J25" t="n">
-        <v>0.999515</v>
+        <v>0.9993840000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.00016961</v>
+        <v>-0.000160970613908407</v>
       </c>
       <c r="L25" t="n">
-        <v>0.01252</v>
+        <v>-0.0161</v>
       </c>
       <c r="M25" t="n">
-        <v>4302618142.639469</v>
+        <v>4309116026.3293</v>
       </c>
       <c r="N25" t="n">
-        <v>4302618142.639469</v>
+        <v>4309116026.3293</v>
       </c>
       <c r="O25" t="n">
         <v>1.048</v>
@@ -2116,19 +2116,19 @@
         <v>46212.42696759259</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002411857120399867</v>
+        <v>0.002436095827506584</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2147,34 +2147,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53.98</v>
+        <v>53.47</v>
       </c>
       <c r="F26" t="n">
-        <v>4188496530</v>
+        <v>4149149491</v>
       </c>
       <c r="G26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H26" t="n">
-        <v>221042595</v>
+        <v>174765883</v>
       </c>
       <c r="I26" t="n">
-        <v>54.24</v>
+        <v>54.53</v>
       </c>
       <c r="J26" t="n">
-        <v>52.9</v>
+        <v>53.4</v>
       </c>
       <c r="K26" t="n">
-        <v>0.958371</v>
+        <v>-0.4001230123206057</v>
       </c>
       <c r="L26" t="n">
-        <v>1.68775</v>
+        <v>-0.74282</v>
       </c>
       <c r="M26" t="n">
-        <v>77599073.1147867</v>
+        <v>77602941.87435494</v>
       </c>
       <c r="N26" t="n">
-        <v>77601641.87155811</v>
+        <v>77602929.37429333</v>
       </c>
       <c r="O26" t="n">
         <v>410.26</v>
@@ -2183,19 +2183,19 @@
         <v>44325.80077546297</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002339114902623786</v>
+        <v>0.002333451069676802</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2214,28 +2214,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6.45</v>
+        <v>6.23</v>
       </c>
       <c r="F27" t="n">
-        <v>4020690137</v>
+        <v>3883037390</v>
       </c>
       <c r="G27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H27" t="n">
-        <v>653762748</v>
+        <v>394857591</v>
       </c>
       <c r="I27" t="n">
-        <v>6.51</v>
+        <v>6.55</v>
       </c>
       <c r="J27" t="n">
-        <v>5.94</v>
+        <v>6.17</v>
       </c>
       <c r="K27" t="n">
-        <v>0.340794</v>
+        <v>-0.1737016955206609</v>
       </c>
       <c r="L27" t="n">
-        <v>5.28911</v>
+        <v>-2.71232</v>
       </c>
       <c r="M27" t="n">
         <v>623212423.7271129</v>
@@ -2250,19 +2250,19 @@
         <v>44318.89240740741</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002231003724853227</v>
+        <v>0.002160681040122422</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2281,34 +2281,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.098431</v>
+        <v>0.094912</v>
       </c>
       <c r="F28" t="n">
-        <v>3895610450</v>
+        <v>3756999297</v>
       </c>
       <c r="G28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H28" t="n">
-        <v>8865517</v>
+        <v>6502123</v>
       </c>
       <c r="I28" t="n">
-        <v>0.101898</v>
+        <v>0.098969</v>
       </c>
       <c r="J28" t="n">
-        <v>0.096594</v>
+        <v>0.094314</v>
       </c>
       <c r="K28" t="n">
-        <v>0.00051503</v>
+        <v>-0.003071083278145426</v>
       </c>
       <c r="L28" t="n">
-        <v>0.46758</v>
+        <v>-3.13429</v>
       </c>
       <c r="M28" t="n">
-        <v>39576931489.55997</v>
+        <v>39583136301.85078</v>
       </c>
       <c r="N28" t="n">
-        <v>39576931489.55997</v>
+        <v>39583136301.85078</v>
       </c>
       <c r="O28" t="n">
         <v>0.194152</v>
@@ -2317,19 +2317,19 @@
         <v>46056.00148148148</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0021504197135114</v>
+        <v>0.002078852348489238</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2348,34 +2348,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="F29" t="n">
-        <v>3839636947</v>
+        <v>3752328394</v>
       </c>
       <c r="G29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H29" t="n">
-        <v>27386361</v>
+        <v>22159128</v>
       </c>
       <c r="I29" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="J29" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="K29" t="n">
-        <v>0.01469045</v>
+        <v>-0.02511075836948562</v>
       </c>
       <c r="L29" t="n">
-        <v>0.9879</v>
+        <v>-1.83118</v>
       </c>
       <c r="M29" t="n">
-        <v>2787175826.164195</v>
+        <v>2787775226.971808</v>
       </c>
       <c r="N29" t="n">
-        <v>5247793479.85942</v>
+        <v>5248392812.065145</v>
       </c>
       <c r="O29" t="n">
         <v>8.25</v>
@@ -2384,220 +2384,220 @@
         <v>45457.69225694444</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002114358147410793</v>
+        <v>0.002075819821797204</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>global-dollar</t>
+          <t>hedera-hashgraph</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>usdg</t>
+          <t>hbar</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Global Dollar</t>
+          <t>Hedera</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0.07571799999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>3306050702</v>
+        <v>3318798395</v>
       </c>
       <c r="G30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H30" t="n">
-        <v>1707855037</v>
+        <v>38129440</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0.075777</v>
       </c>
       <c r="J30" t="n">
-        <v>0.999818</v>
+        <v>0.07427499999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.000103654832734001</v>
+        <v>0.00114562</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.00161</v>
+        <v>1.53626</v>
       </c>
       <c r="M30" t="n">
-        <v>3306051192.175045</v>
+        <v>43831559672.50867</v>
       </c>
       <c r="N30" t="n">
-        <v>3306126794.725507</v>
+        <v>50000000000</v>
       </c>
       <c r="O30" t="n">
-        <v>1.65</v>
+        <v>0.569229</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>45686.67436342593</v>
+        <v>44454.11143518519</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.001770589138627437</v>
+        <v>0.001794355767894821</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>avalanche-2</t>
+          <t>global-dollar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>avax</t>
+          <t>usdg</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Global Dollar</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>7.45</v>
+        <v>0.999936</v>
       </c>
       <c r="F31" t="n">
-        <v>3298662556</v>
+        <v>3299867937</v>
       </c>
       <c r="G31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H31" t="n">
-        <v>279708963</v>
+        <v>735176292</v>
       </c>
       <c r="I31" t="n">
-        <v>7.81</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>7.41</v>
+        <v>0.999711</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.09093661311304313</v>
+        <v>-2.533269023941e-05</v>
       </c>
       <c r="L31" t="n">
-        <v>-1.3548</v>
+        <v>-0.00253</v>
       </c>
       <c r="M31" t="n">
-        <v>442494917.9713389</v>
+        <v>3300126794.724858</v>
       </c>
       <c r="N31" t="n">
-        <v>469163526.3103041</v>
+        <v>3300126794.724858</v>
       </c>
       <c r="O31" t="n">
-        <v>144.96</v>
+        <v>1.65</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>44521.26314814815</v>
+        <v>45686.67436342593</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.001765829241514334</v>
+        <v>0.001782065399377766</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>hedera-hashgraph</t>
+          <t>avalanche-2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>hbar</t>
+          <t>avax</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Hedera</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.07473399999999999</v>
+        <v>7.33</v>
       </c>
       <c r="F32" t="n">
-        <v>3275725089</v>
+        <v>3244317382</v>
       </c>
       <c r="G32" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H32" t="n">
-        <v>52016055</v>
+        <v>154038480</v>
       </c>
       <c r="I32" t="n">
-        <v>0.07695299999999999</v>
+        <v>7.46</v>
       </c>
       <c r="J32" t="n">
-        <v>0.073904</v>
+        <v>7.28</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.00031668373285558</v>
+        <v>-0.1091593768955574</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.60851</v>
+        <v>-1.46725</v>
       </c>
       <c r="M32" t="n">
-        <v>43831559674.09415</v>
+        <v>442498936.567694</v>
       </c>
       <c r="N32" t="n">
-        <v>50000000000</v>
+        <v>469167636.567694</v>
       </c>
       <c r="O32" t="n">
-        <v>0.569229</v>
+        <v>144.96</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>44454.11143518519</v>
+        <v>44521.26314814815</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.00175105151744727</v>
+        <v>0.001745999880398934</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2616,28 +2616,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5.35e-06</v>
+        <v>5.18e-06</v>
       </c>
       <c r="F33" t="n">
-        <v>3155339989</v>
+        <v>3055112871</v>
       </c>
       <c r="G33" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H33" t="n">
-        <v>86440248</v>
+        <v>52713505</v>
       </c>
       <c r="I33" t="n">
-        <v>5.39e-06</v>
+        <v>5.31e-06</v>
       </c>
       <c r="J33" t="n">
-        <v>5.11e-06</v>
+        <v>5.18e-06</v>
       </c>
       <c r="K33" t="n">
-        <v>2.234e-07</v>
+        <v>-1.19790131833e-07</v>
       </c>
       <c r="L33" t="n">
-        <v>4.11151</v>
+        <v>-2.25831</v>
       </c>
       <c r="M33" t="n">
         <v>589239233105565.5</v>
@@ -2652,19 +2652,19 @@
         <v>44496.82980324074</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R33" t="b">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001673492047189027</v>
+        <v>0.001623161163803735</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2683,34 +2683,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="F34" t="n">
-        <v>3098020615</v>
+        <v>3000244069</v>
       </c>
       <c r="G34" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H34" t="n">
-        <v>508937832</v>
+        <v>242432037</v>
       </c>
       <c r="I34" t="n">
-        <v>2.72</v>
+        <v>2.42</v>
       </c>
       <c r="J34" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.1722313415777665</v>
+        <v>-0.07010848625083321</v>
       </c>
       <c r="L34" t="n">
-        <v>-6.9323</v>
+        <v>-2.96103</v>
       </c>
       <c r="M34" t="n">
-        <v>1306106318</v>
+        <v>1306215857</v>
       </c>
       <c r="N34" t="n">
-        <v>1306106333</v>
+        <v>1306215884</v>
       </c>
       <c r="O34" t="n">
         <v>20.44</v>
@@ -2719,19 +2719,19 @@
         <v>44577.59010416667</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.00163656338838512</v>
+        <v>0.001587538264628799</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.729106</v>
+        <v>0.709546</v>
       </c>
       <c r="F35" t="n">
-        <v>2986810464</v>
+        <v>2906515077</v>
       </c>
       <c r="G35" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H35" t="n">
-        <v>499464398</v>
+        <v>269646665</v>
       </c>
       <c r="I35" t="n">
-        <v>0.763093</v>
+        <v>0.730719</v>
       </c>
       <c r="J35" t="n">
-        <v>0.719113</v>
+        <v>0.706657</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.00523676014790786</v>
+        <v>-0.01642906225733354</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.8893799999999999</v>
+        <v>-2.26303</v>
       </c>
       <c r="M35" t="n">
         <v>4096537146.540959</v>
@@ -2786,19 +2786,19 @@
         <v>45661.62243055556</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001564914983400623</v>
+        <v>0.001526685861986868</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2817,34 +2817,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.058225</v>
+        <v>0.058267</v>
       </c>
       <c r="F36" t="n">
-        <v>2826808968</v>
+        <v>2828956293</v>
       </c>
       <c r="G36" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H36" t="n">
-        <v>5783379</v>
+        <v>6834493</v>
       </c>
       <c r="I36" t="n">
-        <v>0.058403</v>
+        <v>0.060711</v>
       </c>
       <c r="J36" t="n">
-        <v>0.055969</v>
+        <v>0.058001</v>
       </c>
       <c r="K36" t="n">
-        <v>0.00145309</v>
+        <v>-1.7873520683317e-05</v>
       </c>
       <c r="L36" t="n">
-        <v>2.68879</v>
+        <v>-0.03067</v>
       </c>
       <c r="M36" t="n">
-        <v>48550035909.05608</v>
+        <v>48552181317.88692</v>
       </c>
       <c r="N36" t="n">
-        <v>98916656597.64023</v>
+        <v>98918860079.80734</v>
       </c>
       <c r="O36" t="n">
         <v>0.891544</v>
@@ -2853,19 +2853,19 @@
         <v>44523.66666666666</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.00146183219931616</v>
+        <v>0.001476331769281096</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2884,34 +2884,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.999861</v>
+        <v>0.999763</v>
       </c>
       <c r="F37" t="n">
-        <v>2792156571</v>
+        <v>2785072340</v>
       </c>
       <c r="G37" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H37" t="n">
-        <v>144383699</v>
+        <v>27670088</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>0.999739</v>
+        <v>0.999674</v>
       </c>
       <c r="K37" t="n">
-        <v>0.00015109</v>
+        <v>-3.113755925066e-05</v>
       </c>
       <c r="L37" t="n">
-        <v>0.00487</v>
+        <v>-0.00311</v>
       </c>
       <c r="M37" t="n">
-        <v>2792543783.480257</v>
+        <v>2785819367.950104</v>
       </c>
       <c r="N37" t="n">
-        <v>2792543783.480256</v>
+        <v>2785819367.950103</v>
       </c>
       <c r="O37" t="n">
         <v>1.021</v>
@@ -2920,19 +2920,19 @@
         <v>45222.61454861111</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001439506998319539</v>
+        <v>0.001447840649079189</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2957,7 +2957,7 @@
         <v>2750834099</v>
       </c>
       <c r="G38" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2969,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1.11e-16</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -2987,220 +2987,220 @@
         <v>45699.87511574074</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R38" t="b">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001412884525620832</v>
+        <v>0.001425611889517969</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>memecore</t>
+          <t>tether-gold</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>xaut</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MemeCore</t>
+          <t>Tether Gold</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1.18</v>
+        <v>4346.32</v>
       </c>
       <c r="F39" t="n">
-        <v>2671365632</v>
+        <v>2663435399</v>
       </c>
       <c r="G39" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H39" t="n">
-        <v>1356005</v>
+        <v>70881608</v>
       </c>
       <c r="I39" t="n">
-        <v>1.21</v>
+        <v>4352.55</v>
       </c>
       <c r="J39" t="n">
-        <v>1.17</v>
+        <v>4343.6</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.01885958591067305</v>
+        <v>-1.693088852525761</v>
       </c>
       <c r="L39" t="n">
-        <v>-1.64046</v>
+        <v>-0.03894</v>
       </c>
       <c r="M39" t="n">
-        <v>2271935475.487713</v>
+        <v>612823.6595320001</v>
       </c>
       <c r="N39" t="n">
-        <v>5413309902.267487</v>
+        <v>707747.089</v>
       </c>
       <c r="O39" t="n">
-        <v>5.64</v>
+        <v>5504.62</v>
       </c>
       <c r="P39" s="1" t="n">
-        <v>46205.17638888889</v>
+        <v>46050.66666666666</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001361686061668444</v>
+        <v>0.001368869351597777</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>tether-gold</t>
+          <t>hashnote-usyc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>xaut</t>
+          <t>usyc</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tether Gold</t>
+          <t>Circle USYC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4347.44</v>
+        <v>1.14</v>
       </c>
       <c r="F40" t="n">
-        <v>2664214314</v>
+        <v>2605383630</v>
       </c>
       <c r="G40" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H40" t="n">
-        <v>130346848</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>4397.49</v>
+        <v>1.14</v>
       </c>
       <c r="J40" t="n">
-        <v>4341.97</v>
+        <v>1.14</v>
       </c>
       <c r="K40" t="n">
-        <v>-9.31237544006126</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.31546</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>612823.6595320001</v>
+        <v>2291144643.386653</v>
       </c>
       <c r="N40" t="n">
-        <v>707747.089</v>
+        <v>2291144643.386653</v>
       </c>
       <c r="O40" t="n">
-        <v>5504.62</v>
+        <v>1.14</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>46050.66666666666</v>
+        <v>46276.53819444445</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001357078743688658</v>
+        <v>0.001331179949995503</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>hashnote-usyc</t>
+          <t>memecore</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>usyc</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Circle USYC</t>
+          <t>MemeCore</t>
         </is>
       </c>
       <c r="E41" t="n">
         <v>1.14</v>
       </c>
       <c r="F41" t="n">
-        <v>2605383630</v>
+        <v>2597946723</v>
       </c>
       <c r="G41" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1076531</v>
       </c>
       <c r="I41" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>1.14</v>
       </c>
       <c r="K41" t="n">
-        <v>0.00031524</v>
+        <v>-0.02934800996583409</v>
       </c>
       <c r="L41" t="n">
-        <v>0.02773</v>
+        <v>-2.50279</v>
       </c>
       <c r="M41" t="n">
-        <v>2291144643.386653</v>
+        <v>2272321208.767787</v>
       </c>
       <c r="N41" t="n">
-        <v>2291144643.386653</v>
+        <v>5413711055.275012</v>
       </c>
       <c r="O41" t="n">
-        <v>1.14</v>
+        <v>5.64</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>46276.53819444445</v>
+        <v>46205.17638888889</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001319176406223556</v>
+        <v>0.001326351629008389</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3219,34 +3219,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.999974</v>
+        <v>0.999949</v>
       </c>
       <c r="F42" t="n">
-        <v>2422784833</v>
+        <v>2422692219</v>
       </c>
       <c r="G42" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H42" t="n">
-        <v>149871915</v>
+        <v>64123176</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>0.999803</v>
+        <v>0.999815</v>
       </c>
       <c r="K42" t="n">
-        <v>4.397e-05</v>
+        <v>2.006e-05</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.00181</v>
+        <v>0.00201</v>
       </c>
       <c r="M42" t="n">
         <v>2422848190.107193</v>
       </c>
       <c r="N42" t="n">
-        <v>2422848190.107191</v>
+        <v>2422848190.107193</v>
       </c>
       <c r="O42" t="n">
         <v>1.073</v>
@@ -3255,19 +3255,19 @@
         <v>45652.11518518518</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.00120153505388749</v>
+        <v>0.00121256978398204</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3286,28 +3286,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>114.27</v>
+        <v>112.5</v>
       </c>
       <c r="F43" t="n">
-        <v>2399752529</v>
+        <v>2362420688</v>
       </c>
       <c r="G43" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H43" t="n">
-        <v>22842507</v>
+        <v>14950178</v>
       </c>
       <c r="I43" t="n">
-        <v>115.9</v>
+        <v>114.72</v>
       </c>
       <c r="J43" t="n">
-        <v>112.58</v>
+        <v>112.66</v>
       </c>
       <c r="K43" t="n">
-        <v>0.404237</v>
+        <v>-1.404209937858923</v>
       </c>
       <c r="L43" t="n">
-        <v>0.35947</v>
+        <v>-1.23285</v>
       </c>
       <c r="M43" t="n">
         <v>21000000</v>
@@ -3322,19 +3322,19 @@
         <v>45934.66666666666</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001186696230004245</v>
+        <v>0.001173439229027841</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3353,28 +3353,28 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>236.86</v>
+        <v>233.9</v>
       </c>
       <c r="F44" t="n">
-        <v>2273295351</v>
+        <v>2244685454</v>
       </c>
       <c r="G44" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H44" t="n">
-        <v>183659571</v>
+        <v>107860464</v>
       </c>
       <c r="I44" t="n">
-        <v>246.82</v>
+        <v>239.13</v>
       </c>
       <c r="J44" t="n">
-        <v>232.66</v>
+        <v>231.12</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.262096608194696</v>
+        <v>-0.7518508925017215</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.33097</v>
+        <v>-0.32041</v>
       </c>
       <c r="M44" t="n">
         <v>9597491</v>
@@ -3389,19 +3389,19 @@
         <v>45358.44833333333</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001105224754414389</v>
+        <v>0.001097001067135414</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3420,16 +3420,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="F45" t="n">
-        <v>2226911540</v>
+        <v>2225069373</v>
       </c>
       <c r="G45" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H45" t="n">
-        <v>1344243</v>
+        <v>801724</v>
       </c>
       <c r="I45" t="n">
         <v>1.15</v>
@@ -3438,16 +3438,16 @@
         <v>1.14</v>
       </c>
       <c r="K45" t="n">
-        <v>0.00019397</v>
+        <v>-0.000379577747015247</v>
       </c>
       <c r="L45" t="n">
-        <v>0.01413</v>
+        <v>-0.03315</v>
       </c>
       <c r="M45" t="n">
-        <v>1944367993.570987</v>
+        <v>1944368850.693475</v>
       </c>
       <c r="N45" t="n">
-        <v>1944367993.574475</v>
+        <v>1944368850.693474</v>
       </c>
       <c r="O45" t="n">
         <v>1.26</v>
@@ -3456,19 +3456,19 @@
         <v>45377.89175925926</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.001075341456483678</v>
+        <v>0.001084265566264257</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3487,31 +3487,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>127.44</v>
+        <v>126.33</v>
       </c>
       <c r="F46" t="n">
-        <v>1966054567</v>
+        <v>1949033898</v>
       </c>
       <c r="G46" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H46" t="n">
-        <v>210362355</v>
+        <v>174977167</v>
       </c>
       <c r="I46" t="n">
-        <v>129.92</v>
+        <v>128.03</v>
       </c>
       <c r="J46" t="n">
-        <v>123.42</v>
+        <v>123.73</v>
       </c>
       <c r="K46" t="n">
-        <v>2.87</v>
+        <v>0.131101</v>
       </c>
       <c r="L46" t="n">
-        <v>1.51048</v>
+        <v>0.10388</v>
       </c>
       <c r="M46" t="n">
-        <v>15427574.57809611</v>
+        <v>15427580.14666632</v>
       </c>
       <c r="N46" t="n">
         <v>16000000</v>
@@ -3523,220 +3523,220 @@
         <v>44334.55554398148</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0009072813839410718</v>
+        <v>0.0009050529074088546</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>mantle</t>
+          <t>pax-gold</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>mnt</t>
+          <t>paxg</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mantle</t>
+          <t>PAX Gold</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.5740690000000001</v>
+        <v>4350.54</v>
       </c>
       <c r="F47" t="n">
-        <v>1895745258</v>
+        <v>1883372570</v>
       </c>
       <c r="G47" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H47" t="n">
-        <v>26568682</v>
+        <v>38849396</v>
       </c>
       <c r="I47" t="n">
-        <v>0.606896</v>
+        <v>4358.06</v>
       </c>
       <c r="J47" t="n">
-        <v>0.57258</v>
+        <v>4349.36</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.009221854130325946</v>
+        <v>-3.154654329549885</v>
       </c>
       <c r="L47" t="n">
-        <v>-1.61632</v>
+        <v>-0.07246</v>
       </c>
       <c r="M47" t="n">
-        <v>3302294382.53684</v>
+        <v>432906.598539</v>
       </c>
       <c r="N47" t="n">
-        <v>6219316794.889999</v>
+        <v>432906.598539</v>
       </c>
       <c r="O47" t="n">
-        <v>2.86</v>
+        <v>5619.09</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>45938.71164351852</v>
+        <v>46050.93814814815</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0008619838117310296</v>
+        <v>0.0008624230926183583</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>pax-gold</t>
+          <t>aster-2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>paxg</t>
+          <t>aster</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>PAX Gold</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4352.79</v>
+        <v>0.694321</v>
       </c>
       <c r="F48" t="n">
-        <v>1884351020</v>
+        <v>1877224626</v>
       </c>
       <c r="G48" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H48" t="n">
-        <v>100832663</v>
+        <v>90143110</v>
       </c>
       <c r="I48" t="n">
-        <v>4401.08</v>
+        <v>0.698188</v>
       </c>
       <c r="J48" t="n">
-        <v>4348.7</v>
+        <v>0.683132</v>
       </c>
       <c r="K48" t="n">
-        <v>-8.094537499183389</v>
+        <v>0.00968485</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.25164</v>
+        <v>1.4146</v>
       </c>
       <c r="M48" t="n">
-        <v>432906.598539</v>
+        <v>2704071066.799731</v>
       </c>
       <c r="N48" t="n">
-        <v>432906.598539</v>
+        <v>7803968119.651995</v>
       </c>
       <c r="O48" t="n">
-        <v>5619.09</v>
+        <v>2.41</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>46050.93814814815</v>
+        <v>45924.13766203704</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0008546429442708842</v>
+        <v>0.0008584316151072372</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>aster-2</t>
+          <t>mantle</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>aster</t>
+          <t>mnt</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Mantle</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.686569</v>
+        <v>0.564358</v>
       </c>
       <c r="F49" t="n">
-        <v>1856531466</v>
+        <v>1863602194</v>
       </c>
       <c r="G49" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H49" t="n">
-        <v>115220006</v>
+        <v>23688481</v>
       </c>
       <c r="I49" t="n">
-        <v>0.716822</v>
+        <v>0.574505</v>
       </c>
       <c r="J49" t="n">
-        <v>0.672749</v>
+        <v>0.550594</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.0118206512966319</v>
+        <v>-0.009028353259263433</v>
       </c>
       <c r="L49" t="n">
-        <v>-1.76831</v>
+        <v>-1.57457</v>
       </c>
       <c r="M49" t="n">
-        <v>2704071066.799731</v>
+        <v>3302294382.53684</v>
       </c>
       <c r="N49" t="n">
-        <v>7803968119.651995</v>
+        <v>6219316794.889999</v>
       </c>
       <c r="O49" t="n">
-        <v>2.41</v>
+        <v>2.86</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>45924.13766203704</v>
+        <v>45938.71164351852</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R49" t="b">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0008367198801121088</v>
+        <v>0.0008495874176040108</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3755,31 +3755,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.057204</v>
+        <v>0.0574</v>
       </c>
       <c r="F50" t="n">
-        <v>1817776264</v>
+        <v>1823894559</v>
       </c>
       <c r="G50" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H50" t="n">
-        <v>61693163</v>
+        <v>68574804</v>
       </c>
       <c r="I50" t="n">
-        <v>0.05773</v>
+        <v>0.06113</v>
       </c>
       <c r="J50" t="n">
-        <v>0.052011</v>
+        <v>0.056678</v>
       </c>
       <c r="K50" t="n">
-        <v>0.0046668</v>
+        <v>0.00049218</v>
       </c>
       <c r="L50" t="n">
-        <v>8.911820000000001</v>
+        <v>0.86486</v>
       </c>
       <c r="M50" t="n">
-        <v>31777210091</v>
+        <v>31777223322</v>
       </c>
       <c r="N50" t="n">
         <v>100000000000</v>
@@ -3791,354 +3791,354 @@
         <v>45901.18065972222</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0008117514003179216</v>
+        <v>0.0008238077208269577</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>polkadot</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>dot</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1.046</v>
+        <v>0.667876</v>
       </c>
       <c r="F51" t="n">
-        <v>1780719543</v>
+        <v>1807336147</v>
       </c>
       <c r="G51" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H51" t="n">
-        <v>156543168</v>
+        <v>30527053</v>
       </c>
       <c r="I51" t="n">
-        <v>1.11</v>
+        <v>0.728917</v>
       </c>
       <c r="J51" t="n">
-        <v>1.031</v>
+        <v>0.504794</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.04921686161834615</v>
+        <v>0.119042</v>
       </c>
       <c r="L51" t="n">
-        <v>-4.73488</v>
+        <v>21.69009</v>
       </c>
       <c r="M51" t="n">
-        <v>1702414888.957769</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N51" t="n">
-        <v>1702422593.621313</v>
+        <v>10000000000</v>
       </c>
       <c r="O51" t="n">
-        <v>54.98</v>
+        <v>0.745279</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>44504.25704861111</v>
+        <v>46253.4</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R51" t="b">
         <v>1</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0007878771862310659</v>
+        <v>0.0008130573741878411</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ondo-finance</t>
+          <t>polkadot</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ondo</t>
+          <t>dot</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Ondo</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.352305</v>
+        <v>1.006</v>
       </c>
       <c r="F52" t="n">
-        <v>1715488264</v>
+        <v>1713254528</v>
       </c>
       <c r="G52" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H52" t="n">
-        <v>76577445</v>
+        <v>103954483</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3679</v>
+        <v>1.043</v>
       </c>
       <c r="J52" t="n">
-        <v>0.34678</v>
+        <v>0.996648</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.002580851204815326</v>
+        <v>-0.03214671140746428</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.94938</v>
+        <v>-3.0955</v>
       </c>
       <c r="M52" t="n">
-        <v>4869330647</v>
+        <v>1702555180.263461</v>
       </c>
       <c r="N52" t="n">
-        <v>10000000000</v>
+        <v>1702581303.296338</v>
       </c>
       <c r="O52" t="n">
-        <v>2.14</v>
+        <v>54.98</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>45641.69166666667</v>
+        <v>44504.25704861111</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R52" t="b">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0007458511926196666</v>
+        <v>0.0007519760327754342</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>ondo-finance</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>ondo</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Morpho</t>
+          <t>Ondo</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2.29</v>
+        <v>0.343808</v>
       </c>
       <c r="F53" t="n">
-        <v>1579756865</v>
+        <v>1674061222</v>
       </c>
       <c r="G53" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H53" t="n">
-        <v>20563790</v>
+        <v>53093523</v>
       </c>
       <c r="I53" t="n">
-        <v>2.46</v>
+        <v>0.353277</v>
       </c>
       <c r="J53" t="n">
-        <v>2.27</v>
+        <v>0.341176</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.07578842279781606</v>
+        <v>-0.006722452036544091</v>
       </c>
       <c r="L53" t="n">
-        <v>-3.29573</v>
+        <v>-1.91779</v>
       </c>
       <c r="M53" t="n">
-        <v>688986833.9200211</v>
+        <v>4869330647</v>
       </c>
       <c r="N53" t="n">
-        <v>1000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O53" t="n">
-        <v>4.17</v>
+        <v>2.14</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>45674.19883101852</v>
+        <v>45641.69166666667</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R53" t="b">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0006584046946406787</v>
+        <v>0.0007265302578162794</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>internet-computer</t>
+          <t>htx-dao</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>icp</t>
+          <t>htx</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Internet Computer</t>
+          <t>HTX DAO</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2.75</v>
+        <v>1.7e-06</v>
       </c>
       <c r="F54" t="n">
-        <v>1532378165</v>
+        <v>1529057947</v>
       </c>
       <c r="G54" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H54" t="n">
-        <v>35111368</v>
+        <v>43518659</v>
       </c>
       <c r="I54" t="n">
-        <v>2.87</v>
+        <v>1.71e-06</v>
       </c>
       <c r="J54" t="n">
-        <v>2.72</v>
+        <v>1.69e-06</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.05095835614630051</v>
+        <v>-1.813195854e-09</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.94273</v>
+        <v>-0.1064</v>
       </c>
       <c r="M54" t="n">
-        <v>556276725.9312513</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="N54" t="n">
-        <v>556276747.3933151</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="O54" t="n">
-        <v>700.65</v>
+        <v>3.75e-06</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>44326.33741898148</v>
+        <v>45629.67800925926</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R54" t="b">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0006278804281531795</v>
+        <v>0.000632388653533384</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>htx-dao</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>htx</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>HTX DAO</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1.71e-06</v>
+        <v>0.00368693</v>
       </c>
       <c r="F55" t="n">
-        <v>1531747172</v>
+        <v>1529168745</v>
       </c>
       <c r="G55" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H55" t="n">
-        <v>58584790</v>
+        <v>188688626</v>
       </c>
       <c r="I55" t="n">
-        <v>1.71e-06</v>
+        <v>0.00395184</v>
       </c>
       <c r="J55" t="n">
-        <v>1.66e-06</v>
+        <v>0.0035918</v>
       </c>
       <c r="K55" t="n">
-        <v>2.483e-08</v>
+        <v>8.375e-05</v>
       </c>
       <c r="L55" t="n">
-        <v>1.41494</v>
+        <v>2.32424</v>
       </c>
       <c r="M55" t="n">
-        <v>898232728634017.2</v>
+        <v>414815762056.5878</v>
       </c>
       <c r="N55" t="n">
-        <v>898232728634017.2</v>
+        <v>834327582311.8589</v>
       </c>
       <c r="O55" t="n">
-        <v>3.75e-06</v>
+        <v>0.00881908</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>45629.67800925926</v>
+        <v>45914.36296296296</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R55" t="b">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0006274739037343216</v>
+        <v>0.0006324605877808783</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4157,34 +4157,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.997449</v>
+        <v>0.998907</v>
       </c>
       <c r="F56" t="n">
-        <v>1508480377</v>
+        <v>1524004223</v>
       </c>
       <c r="G56" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H56" t="n">
-        <v>2306401</v>
+        <v>2090791</v>
       </c>
       <c r="I56" t="n">
-        <v>0.999555</v>
+        <v>0.999628</v>
       </c>
       <c r="J56" t="n">
-        <v>0.9954499999999999</v>
+        <v>0.9961680000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.001296324483550215</v>
+        <v>0.00162806</v>
       </c>
       <c r="L56" t="n">
-        <v>-0.10334</v>
+        <v>0.16325</v>
       </c>
       <c r="M56" t="n">
-        <v>1512337957</v>
+        <v>1525524624</v>
       </c>
       <c r="N56" t="n">
-        <v>1514499799</v>
+        <v>1525486098</v>
       </c>
       <c r="O56" t="n">
         <v>1.24</v>
@@ -4193,153 +4193,153 @@
         <v>46212.39942129629</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R56" t="b">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0006124840063565967</v>
+        <v>0.00062910758498536</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>Morpho</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.0036227</v>
+        <v>2.17</v>
       </c>
       <c r="F57" t="n">
-        <v>1501077364</v>
+        <v>1494721401</v>
       </c>
       <c r="G57" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H57" t="n">
-        <v>174508980</v>
+        <v>15885684</v>
       </c>
       <c r="I57" t="n">
-        <v>0.00387035</v>
+        <v>2.29</v>
       </c>
       <c r="J57" t="n">
-        <v>0.00351746</v>
+        <v>2.16</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.000112795186921209</v>
+        <v>-0.1172328898001407</v>
       </c>
       <c r="L57" t="n">
-        <v>-3.1487</v>
+        <v>-5.12678</v>
       </c>
       <c r="M57" t="n">
-        <v>414353436173.9454</v>
+        <v>689038406.6772338</v>
       </c>
       <c r="N57" t="n">
-        <v>834490255313.1332</v>
+        <v>1000000000</v>
       </c>
       <c r="O57" t="n">
-        <v>0.00881908</v>
+        <v>4.17</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>45914.36296296296</v>
+        <v>45674.19883101852</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S57" t="n">
-        <v>0.000607714531009607</v>
+        <v>0.0006100960706522495</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>internet-computer</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>icp</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>Internet Computer</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.551997</v>
+        <v>2.67</v>
       </c>
       <c r="F58" t="n">
-        <v>1494887005</v>
+        <v>1486990925</v>
       </c>
       <c r="G58" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H58" t="n">
-        <v>11630739</v>
+        <v>25432475</v>
       </c>
       <c r="I58" t="n">
-        <v>0.569699</v>
+        <v>2.77</v>
       </c>
       <c r="J58" t="n">
-        <v>0.495642</v>
+        <v>2.64</v>
       </c>
       <c r="K58" t="n">
-        <v>0.04655557</v>
+        <v>-0.09486369083001422</v>
       </c>
       <c r="L58" t="n">
-        <v>9.010249999999999</v>
+        <v>-3.42728</v>
       </c>
       <c r="M58" t="n">
-        <v>2708142280.000001</v>
+        <v>556288332.0867959</v>
       </c>
       <c r="N58" t="n">
-        <v>10000000000</v>
+        <v>556288442.1779287</v>
       </c>
       <c r="O58" t="n">
-        <v>0.745279</v>
+        <v>700.65</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>46253.4</v>
+        <v>44326.33741898148</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0006037263217980987</v>
+        <v>0.0006050771535794425</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4358,34 +4358,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.06364</v>
+        <v>0.061816</v>
       </c>
       <c r="F59" t="n">
-        <v>1490714308</v>
+        <v>1448383094</v>
       </c>
       <c r="G59" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H59" t="n">
-        <v>22718656</v>
+        <v>7181124</v>
       </c>
       <c r="I59" t="n">
-        <v>0.06393699999999999</v>
+        <v>0.06422600000000001</v>
       </c>
       <c r="J59" t="n">
-        <v>0.057814</v>
+        <v>0.061655</v>
       </c>
       <c r="K59" t="n">
-        <v>0.00425821</v>
+        <v>-0.00182546775971467</v>
       </c>
       <c r="L59" t="n">
-        <v>7.12569</v>
+        <v>-2.86835</v>
       </c>
       <c r="M59" t="n">
-        <v>23424161538.38614</v>
+        <v>23429540152.7714</v>
       </c>
       <c r="N59" t="n">
-        <v>23462665147.36596</v>
+        <v>23459804203.60596</v>
       </c>
       <c r="O59" t="n">
         <v>0.100535</v>
@@ -4394,86 +4394,86 @@
         <v>45630.09302083333</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0006010380142843935</v>
+        <v>0.0005800114911092473</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>worldcoin-wld</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>wld</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Worldcoin</t>
+          <t>Pepe</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.401719</v>
+        <v>3.4e-06</v>
       </c>
       <c r="F60" t="n">
-        <v>1467776366</v>
+        <v>1429580510</v>
       </c>
       <c r="G60" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H60" t="n">
-        <v>145431349</v>
+        <v>140594078</v>
       </c>
       <c r="I60" t="n">
-        <v>0.427578</v>
+        <v>3.48e-06</v>
       </c>
       <c r="J60" t="n">
-        <v>0.395299</v>
+        <v>3.38e-06</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.005559293841472135</v>
+        <v>1.2851e-08</v>
       </c>
       <c r="L60" t="n">
-        <v>-1.43875</v>
+        <v>0.37951</v>
       </c>
       <c r="M60" t="n">
-        <v>3653737094.945146</v>
+        <v>420690000000000</v>
       </c>
       <c r="N60" t="n">
-        <v>10000000000</v>
+        <v>420690000000000</v>
       </c>
       <c r="O60" t="n">
-        <v>11.74</v>
+        <v>2.803e-05</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>45360.67409722223</v>
+        <v>45635.35457175926</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0005862599841931752</v>
+        <v>0.0005678041432240088</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4492,28 +4492,28 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.141868</v>
+        <v>0.139191</v>
       </c>
       <c r="F61" t="n">
-        <v>1432198996</v>
+        <v>1405006118</v>
       </c>
       <c r="G61" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H61" t="n">
-        <v>377246978</v>
+        <v>144723881</v>
       </c>
       <c r="I61" t="n">
-        <v>0.157211</v>
+        <v>0.143815</v>
       </c>
       <c r="J61" t="n">
-        <v>0.138292</v>
+        <v>0.138364</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.005293080626809415</v>
+        <v>-0.002546763812056457</v>
       </c>
       <c r="L61" t="n">
-        <v>-3.8544</v>
+        <v>-1.79681</v>
       </c>
       <c r="M61" t="n">
         <v>10095312500</v>
@@ -4528,86 +4528,86 @@
         <v>45393.21892361111</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0005633388588181785</v>
+        <v>0.0005518495195290837</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>worldcoin-wld</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>wld</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Pepe</t>
+          <t>Worldcoin</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3.4e-06</v>
+        <v>0.389604</v>
       </c>
       <c r="F62" t="n">
-        <v>1428671176</v>
+        <v>1399169269</v>
       </c>
       <c r="G62" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H62" t="n">
-        <v>243786948</v>
+        <v>97023558</v>
       </c>
       <c r="I62" t="n">
-        <v>3.55e-06</v>
+        <v>0.411451</v>
       </c>
       <c r="J62" t="n">
-        <v>3.25e-06</v>
+        <v>0.387357</v>
       </c>
       <c r="K62" t="n">
-        <v>5.7378e-08</v>
+        <v>-0.01096885046806378</v>
       </c>
       <c r="L62" t="n">
-        <v>1.73265</v>
+        <v>-2.73829</v>
       </c>
       <c r="M62" t="n">
-        <v>420690000000000</v>
+        <v>3591409311.083124</v>
       </c>
       <c r="N62" t="n">
-        <v>420690000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O62" t="n">
-        <v>2.803e-05</v>
+        <v>11.74</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>45635.35457175926</v>
+        <v>45360.67409722223</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005610660206482851</v>
+        <v>0.0005480600166449797</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4629,13 +4629,13 @@
         <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>1383105673</v>
+        <v>1383088021</v>
       </c>
       <c r="G63" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H63" t="n">
-        <v>20105463</v>
+        <v>7212222</v>
       </c>
       <c r="I63" t="n">
         <v>1</v>
@@ -4644,10 +4644,10 @@
         <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>3.754e-05</v>
+        <v>-7.38700859193e-06</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.00259</v>
+        <v>-0.00074</v>
       </c>
       <c r="M63" t="n">
         <v>1382792045.16</v>
@@ -4662,19 +4662,19 @@
         <v>46092.00303240741</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0005317099269562053</v>
+        <v>0.000537619462901686</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4693,28 +4693,28 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="F64" t="n">
-        <v>1365892496</v>
+        <v>1341575645</v>
       </c>
       <c r="G64" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H64" t="n">
-        <v>12523335</v>
+        <v>7205523</v>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="J64" t="n">
         <v>1.92</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.005742599409946703</v>
+        <v>-0.02997327612354672</v>
       </c>
       <c r="L64" t="n">
-        <v>-0.2626</v>
+        <v>-1.53991</v>
       </c>
       <c r="M64" t="n">
         <v>699992029.6481038</v>
@@ -4729,19 +4729,19 @@
         <v>45653.15375</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R64" t="b">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0005206201418450796</v>
+        <v>0.0005106680600851995</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4760,34 +4760,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.996233</v>
+        <v>0.996407</v>
       </c>
       <c r="F65" t="n">
-        <v>1339425000</v>
+        <v>1339686255</v>
       </c>
       <c r="G65" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H65" t="n">
-        <v>481917</v>
+        <v>490682</v>
       </c>
       <c r="I65" t="n">
-        <v>0.997675</v>
+        <v>0.99773</v>
       </c>
       <c r="J65" t="n">
-        <v>0.977391</v>
+        <v>0.9963689999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>6.295999999999999e-05</v>
+        <v>0.00012986</v>
       </c>
       <c r="L65" t="n">
-        <v>-6e-05</v>
+        <v>0.01303</v>
       </c>
       <c r="M65" t="n">
-        <v>1344489118.116781</v>
+        <v>1344517433.482414</v>
       </c>
       <c r="N65" t="n">
-        <v>1344489118.116781</v>
+        <v>1344517433.482414</v>
       </c>
       <c r="O65" t="n">
         <v>1.075</v>
@@ -4796,19 +4796,19 @@
         <v>45785.55951388889</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0005035681564347408</v>
+        <v>0.0005094413967169683</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="F66" t="n">
-        <v>1334376241</v>
+        <v>1335525954</v>
       </c>
       <c r="G66" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -4845,10 +4845,10 @@
         <v>1.17</v>
       </c>
       <c r="K66" t="n">
-        <v>0.00180267</v>
+        <v>0.00101211</v>
       </c>
       <c r="L66" t="n">
-        <v>0.1537</v>
+        <v>0.08616</v>
       </c>
       <c r="M66" t="n">
         <v>1135960146.90006</v>
@@ -4863,19 +4863,19 @@
         <v>46255.48263888889</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.000500315436010855</v>
+        <v>0.0005067403721336288</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4894,28 +4894,28 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.999646</v>
+        <v>0.999269</v>
       </c>
       <c r="F67" t="n">
-        <v>1319533294</v>
+        <v>1319035606</v>
       </c>
       <c r="G67" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H67" t="n">
-        <v>1059898</v>
+        <v>2360558</v>
       </c>
       <c r="I67" t="n">
-        <v>0.999877</v>
+        <v>0.999847</v>
       </c>
       <c r="J67" t="n">
-        <v>0.999486</v>
+        <v>0.9992220000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>0.00017403</v>
+        <v>-0.000348682830913716</v>
       </c>
       <c r="L67" t="n">
-        <v>0.01437</v>
+        <v>-0.03488</v>
       </c>
       <c r="M67" t="n">
         <v>1320000000</v>
@@ -4930,19 +4930,19 @@
         <v>45940.56990740741</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0004907526985425871</v>
+        <v>0.0004960342152147369</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4961,28 +4961,28 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.999305</v>
+        <v>0.999343</v>
       </c>
       <c r="F68" t="n">
-        <v>1285106288</v>
+        <v>1285134272</v>
       </c>
       <c r="G68" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H68" t="n">
-        <v>171246171</v>
+        <v>84854418</v>
       </c>
       <c r="I68" t="n">
-        <v>0.999557</v>
+        <v>0.999593</v>
       </c>
       <c r="J68" t="n">
-        <v>0.99905</v>
+        <v>0.999094</v>
       </c>
       <c r="K68" t="n">
-        <v>0.0002578</v>
+        <v>6.834999999999999e-05</v>
       </c>
       <c r="L68" t="n">
-        <v>0.02343</v>
+        <v>0.00684</v>
       </c>
       <c r="M68" t="n">
         <v>1286000007.8</v>
@@ -4997,19 +4997,19 @@
         <v>46058.54591435185</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.000468572708261918</v>
+        <v>0.0004740241884060992</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5028,34 +5028,34 @@
         </is>
       </c>
       <c r="E69" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1189953494</v>
+      </c>
+      <c r="G69" t="n">
+        <v>67</v>
+      </c>
+      <c r="H69" t="n">
+        <v>40949275</v>
+      </c>
+      <c r="I69" t="n">
         <v>7.78</v>
       </c>
-      <c r="F69" t="n">
-        <v>1229960904</v>
-      </c>
-      <c r="G69" t="n">
-        <v>68</v>
-      </c>
-      <c r="H69" t="n">
-        <v>50428712</v>
-      </c>
-      <c r="I69" t="n">
-        <v>8.039999999999999</v>
-      </c>
       <c r="J69" t="n">
-        <v>7.56</v>
+        <v>7.48</v>
       </c>
       <c r="K69" t="n">
-        <v>0.148372</v>
+        <v>-0.2376247766535613</v>
       </c>
       <c r="L69" t="n">
-        <v>1.65537</v>
+        <v>-3.06131</v>
       </c>
       <c r="M69" t="n">
-        <v>158147055.6165969</v>
+        <v>158156878.9004274</v>
       </c>
       <c r="N69" t="n">
-        <v>158147807.8469969</v>
+        <v>158157253.7868274</v>
       </c>
       <c r="O69" t="n">
         <v>167.09</v>
@@ -5064,287 +5064,287 @@
         <v>44322.44053240741</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0004330446672483092</v>
+        <v>0.0004122292314452022</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>venice-token</t>
+          <t>pi-network</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>vvv</t>
+          <t>pi</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Venice Token</t>
+          <t>Pi Network</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>23.26</v>
+        <v>0.09778199999999999</v>
       </c>
       <c r="F70" t="n">
-        <v>1115260871</v>
+        <v>1094472076</v>
       </c>
       <c r="G70" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H70" t="n">
-        <v>64886551</v>
+        <v>5940870</v>
       </c>
       <c r="I70" t="n">
-        <v>26.96</v>
+        <v>0.098353</v>
       </c>
       <c r="J70" t="n">
-        <v>22.9</v>
+        <v>0.095195</v>
       </c>
       <c r="K70" t="n">
-        <v>-2.111842464813492</v>
+        <v>0.00233842</v>
       </c>
       <c r="L70" t="n">
-        <v>-8.392390000000001</v>
+        <v>2.45006</v>
       </c>
       <c r="M70" t="n">
-        <v>47938677.12722591</v>
+        <v>11193060990.054</v>
       </c>
       <c r="N70" t="n">
-        <v>80993152.67908402</v>
+        <v>17220093830.8523</v>
       </c>
       <c r="O70" t="n">
-        <v>29.19</v>
+        <v>2.99</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>46274.32083333333</v>
+        <v>45714.36184027778</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0003591478660820267</v>
+        <v>0.0003502390876382728</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>lighter</t>
+          <t>venice-token</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>lit</t>
+          <t>vvv</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Lighter</t>
+          <t>Venice Token</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4.38</v>
+        <v>21.99</v>
       </c>
       <c r="F71" t="n">
-        <v>1094810297</v>
+        <v>1051744869</v>
       </c>
       <c r="G71" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H71" t="n">
-        <v>75118887</v>
+        <v>31662360</v>
       </c>
       <c r="I71" t="n">
-        <v>4.89</v>
+        <v>24.64</v>
       </c>
       <c r="J71" t="n">
-        <v>4.29</v>
+        <v>22.11</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.2442743405838863</v>
+        <v>-1.071007754172321</v>
       </c>
       <c r="L71" t="n">
-        <v>-5.57308</v>
+        <v>-4.64441</v>
       </c>
       <c r="M71" t="n">
-        <v>250000000</v>
+        <v>47949972.85733457</v>
       </c>
       <c r="N71" t="n">
-        <v>1000000000</v>
+        <v>81000288.01647621</v>
       </c>
       <c r="O71" t="n">
-        <v>7.86</v>
+        <v>29.19</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>46021.04538194444</v>
+        <v>46274.32083333333</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R71" t="b">
         <v>1</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0003459723511228083</v>
+        <v>0.0003224989706408646</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>pi-network</t>
+          <t>polygon-ecosystem-token</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>pi</t>
+          <t>pol</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Pi Network</t>
+          <t>POL (ex-MATIC)</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.09500699999999999</v>
+        <v>0.096285</v>
       </c>
       <c r="F72" t="n">
-        <v>1061823224</v>
+        <v>1031576270</v>
       </c>
       <c r="G72" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H72" t="n">
-        <v>4189239</v>
+        <v>42931958</v>
       </c>
       <c r="I72" t="n">
-        <v>0.096189</v>
+        <v>0.097431</v>
       </c>
       <c r="J72" t="n">
-        <v>0.09408999999999999</v>
+        <v>0.09479</v>
       </c>
       <c r="K72" t="n">
-        <v>0.00025705</v>
+        <v>-0.000352092608966403</v>
       </c>
       <c r="L72" t="n">
-        <v>0.2691</v>
+        <v>-0.36434</v>
       </c>
       <c r="M72" t="n">
-        <v>11176267335.13786</v>
+        <v>10713522708.58917</v>
       </c>
       <c r="N72" t="n">
-        <v>17193106891.0133</v>
+        <v>10713522708.58917</v>
       </c>
       <c r="O72" t="n">
-        <v>2.99</v>
+        <v>1.29</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>45714.36184027778</v>
+        <v>45364.45493055556</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0003247200540590521</v>
+        <v>0.0003094047542102467</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>polygon-ecosystem-token</t>
+          <t>lighter</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>pol</t>
+          <t>lit</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>POL (ex-MATIC)</t>
+          <t>Lighter</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.09667100000000001</v>
+        <v>4.06</v>
       </c>
       <c r="F73" t="n">
-        <v>1035629322</v>
+        <v>1015247730</v>
       </c>
       <c r="G73" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H73" t="n">
-        <v>76591456</v>
+        <v>48556691</v>
       </c>
       <c r="I73" t="n">
-        <v>0.098053</v>
+        <v>4.36</v>
       </c>
       <c r="J73" t="n">
-        <v>0.09514599999999999</v>
+        <v>4.07</v>
       </c>
       <c r="K73" t="n">
-        <v>0.00135837</v>
+        <v>-0.2888899709572943</v>
       </c>
       <c r="L73" t="n">
-        <v>1.30768</v>
+        <v>-6.63943</v>
       </c>
       <c r="M73" t="n">
-        <v>10712941475.32286</v>
+        <v>250000000</v>
       </c>
       <c r="N73" t="n">
-        <v>10712941475.32286</v>
+        <v>1000000000</v>
       </c>
       <c r="O73" t="n">
-        <v>1.29</v>
+        <v>7.86</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>45364.45493055556</v>
+        <v>46021.04538194444</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003078443346958058</v>
+        <v>0.000298803649157982</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5363,34 +5363,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>9.43</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F74" t="n">
-        <v>1005188774</v>
+        <v>980902454</v>
       </c>
       <c r="G74" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H74" t="n">
-        <v>3280701</v>
+        <v>1924570</v>
       </c>
       <c r="I74" t="n">
-        <v>9.5</v>
+        <v>9.44</v>
       </c>
       <c r="J74" t="n">
-        <v>9.17</v>
+        <v>9.07</v>
       </c>
       <c r="K74" t="n">
-        <v>0.343488</v>
+        <v>-0.2252325919768072</v>
       </c>
       <c r="L74" t="n">
-        <v>3.68606</v>
+        <v>-2.39019</v>
       </c>
       <c r="M74" t="n">
-        <v>106625412.8293429</v>
+        <v>106626638.5617626</v>
       </c>
       <c r="N74" t="n">
-        <v>118876736.8495598</v>
+        <v>118877870.6688078</v>
       </c>
       <c r="O74" t="n">
         <v>25.38</v>
@@ -5399,220 +5399,220 @@
         <v>45682.66666666666</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R74" t="b">
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0002882326653343098</v>
+        <v>0.0002765053984310324</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>kaspa</t>
+          <t>blockchain-capital</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>kas</t>
+          <t>bcap</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Kaspa</t>
+          <t>Blockchain Capital</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.03560476</v>
+        <v>106.49</v>
       </c>
       <c r="F75" t="n">
-        <v>986010979</v>
+        <v>970348700</v>
       </c>
       <c r="G75" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H75" t="n">
-        <v>11878093</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0.03674793</v>
+        <v>106.49</v>
       </c>
       <c r="J75" t="n">
-        <v>0.0352174</v>
+        <v>106.49</v>
       </c>
       <c r="K75" t="n">
-        <v>0.00048354</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>1.14891</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>27693237714.84791</v>
+        <v>9112111</v>
       </c>
       <c r="N75" t="n">
-        <v>27696019387.569</v>
+        <v>9112111</v>
       </c>
       <c r="O75" t="n">
-        <v>0.207411</v>
+        <v>106.49</v>
       </c>
       <c r="P75" s="1" t="n">
-        <v>45504.69498842592</v>
+        <v>46273.93067129629</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R75" t="b">
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0002758771527258459</v>
+        <v>0.0002696535026185617</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>blockchain-capital</t>
+          <t>kaspa</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>bcap</t>
+          <t>kas</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Blockchain Capital</t>
+          <t>Kaspa</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106.49</v>
+        <v>0.03434143</v>
       </c>
       <c r="F76" t="n">
-        <v>970348700</v>
+        <v>951162173</v>
       </c>
       <c r="G76" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>5171603</v>
       </c>
       <c r="I76" t="n">
-        <v>106.49</v>
+        <v>0.03558984</v>
       </c>
       <c r="J76" t="n">
-        <v>106.49</v>
+        <v>0.03415747</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>-0.000979915992404469</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>-2.77429</v>
       </c>
       <c r="M76" t="n">
-        <v>9112111</v>
+        <v>27697431694.91903</v>
       </c>
       <c r="N76" t="n">
-        <v>9112111</v>
+        <v>27697985160.55182</v>
       </c>
       <c r="O76" t="n">
-        <v>106.49</v>
+        <v>0.207411</v>
       </c>
       <c r="P76" s="1" t="n">
-        <v>46273.93067129629</v>
+        <v>45504.69498842592</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R76" t="b">
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0002657865512952967</v>
+        <v>0.0002571968844325443</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>quant-network</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>arb</t>
+          <t>qnt</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Arbitrum</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.144492</v>
+        <v>64.09</v>
       </c>
       <c r="F77" t="n">
-        <v>964925627</v>
+        <v>933028720</v>
       </c>
       <c r="G77" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H77" t="n">
-        <v>176225601</v>
+        <v>4413297</v>
       </c>
       <c r="I77" t="n">
-        <v>0.151528</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>0.137756</v>
+        <v>63.45</v>
       </c>
       <c r="K77" t="n">
-        <v>0.00125256</v>
+        <v>-0.3508712021686478</v>
       </c>
       <c r="L77" t="n">
-        <v>0.5424600000000001</v>
+        <v>-0.54451</v>
       </c>
       <c r="M77" t="n">
-        <v>6678075931</v>
+        <v>14544176.16408117</v>
       </c>
       <c r="N77" t="n">
-        <v>10000000000</v>
+        <v>14612493</v>
       </c>
       <c r="O77" t="n">
-        <v>2.39</v>
+        <v>427.42</v>
       </c>
       <c r="P77" s="1" t="n">
-        <v>45303.18748842592</v>
+        <v>44450.05208333334</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R77" t="b">
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002622926748184588</v>
+        <v>0.0002454239616719482</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5631,28 +5631,28 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="F78" t="n">
-        <v>946493499</v>
+        <v>932317322</v>
       </c>
       <c r="G78" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H78" t="n">
-        <v>2806743</v>
+        <v>1750241</v>
       </c>
       <c r="I78" t="n">
-        <v>7.2</v>
+        <v>6.92</v>
       </c>
       <c r="J78" t="n">
-        <v>6.88</v>
+        <v>6.8</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.06895540986525894</v>
+        <v>-0.1079685940489261</v>
       </c>
       <c r="L78" t="n">
-        <v>-0.99277</v>
+        <v>-1.56362</v>
       </c>
       <c r="M78" t="n">
         <v>137155021.2773955</v>
@@ -5667,86 +5667,86 @@
         <v>44531.29832175926</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R78" t="b">
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002504175666579627</v>
+        <v>0.0002449620952140792</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>quant-network</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>qnt</t>
+          <t>arb</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Arbitrum</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>64.47</v>
+        <v>0.136972</v>
       </c>
       <c r="F79" t="n">
-        <v>937680591</v>
+        <v>914447252</v>
       </c>
       <c r="G79" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H79" t="n">
-        <v>10154754</v>
+        <v>116956324</v>
       </c>
       <c r="I79" t="n">
-        <v>65.94</v>
+        <v>0.144581</v>
       </c>
       <c r="J79" t="n">
-        <v>62.82</v>
+        <v>0.13437</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.4152476391461448</v>
+        <v>-0.006598295908196022</v>
       </c>
       <c r="L79" t="n">
-        <v>-0.56288</v>
+        <v>-4.59585</v>
       </c>
       <c r="M79" t="n">
-        <v>14544176.16408117</v>
+        <v>6678075931</v>
       </c>
       <c r="N79" t="n">
-        <v>14612493</v>
+        <v>10000000000</v>
       </c>
       <c r="O79" t="n">
-        <v>427.42</v>
+        <v>2.39</v>
       </c>
       <c r="P79" s="1" t="n">
-        <v>44450.05208333334</v>
+        <v>45303.18748842592</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002447397504172931</v>
+        <v>0.0002333601706475642</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5765,28 +5765,28 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.108937</v>
+        <v>0.111673</v>
       </c>
       <c r="F80" t="n">
-        <v>892054189</v>
+        <v>914218317</v>
       </c>
       <c r="G80" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H80" t="n">
-        <v>31577160</v>
+        <v>20649316</v>
       </c>
       <c r="I80" t="n">
-        <v>0.108792</v>
+        <v>0.112641</v>
       </c>
       <c r="J80" t="n">
-        <v>0.102155</v>
+        <v>0.108534</v>
       </c>
       <c r="K80" t="n">
-        <v>0.00589916</v>
+        <v>0.00279723</v>
       </c>
       <c r="L80" t="n">
-        <v>5.79298</v>
+        <v>2.56919</v>
       </c>
       <c r="M80" t="n">
         <v>8188743036.341737</v>
@@ -5801,19 +5801,19 @@
         <v>44290.85721064815</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002153444218516346</v>
+        <v>0.0002332115373965117</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5835,10 +5835,10 @@
         <v>1.23</v>
       </c>
       <c r="F81" t="n">
-        <v>880446339</v>
+        <v>881204940</v>
       </c>
       <c r="G81" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -5850,10 +5850,10 @@
         <v>1.23</v>
       </c>
       <c r="K81" t="n">
-        <v>0.00178684</v>
+        <v>0.0010583</v>
       </c>
       <c r="L81" t="n">
-        <v>0.14569</v>
+        <v>0.08616</v>
       </c>
       <c r="M81" t="n">
         <v>716808406.83022</v>
@@ -5868,19 +5868,19 @@
         <v>46049.54175925926</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R81" t="b">
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.000207865932430293</v>
+        <v>0.0002117780058188557</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5899,34 +5899,34 @@
         </is>
       </c>
       <c r="E82" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="F82" t="n">
+        <v>844751116</v>
+      </c>
+      <c r="G82" t="n">
+        <v>80</v>
+      </c>
+      <c r="H82" t="n">
+        <v>36926557</v>
+      </c>
+      <c r="I82" t="n">
         <v>1.64</v>
       </c>
-      <c r="F82" t="n">
-        <v>870384550</v>
-      </c>
-      <c r="G82" t="n">
-        <v>81</v>
-      </c>
-      <c r="H82" t="n">
-        <v>48583957</v>
-      </c>
-      <c r="I82" t="n">
-        <v>1.76</v>
-      </c>
       <c r="J82" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.09507162704493877</v>
+        <v>-0.04581604925677163</v>
       </c>
       <c r="L82" t="n">
-        <v>-5.56627</v>
+        <v>-2.79669</v>
       </c>
       <c r="M82" t="n">
-        <v>530269185.354314</v>
+        <v>530462111.92831</v>
       </c>
       <c r="N82" t="n">
-        <v>530292014.176179</v>
+        <v>530478342.369727</v>
       </c>
       <c r="O82" t="n">
         <v>43.84</v>
@@ -5935,19 +5935,19 @@
         <v>44458.66666666666</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0002013835103972489</v>
+        <v>0.0001881108060703927</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5966,34 +5966,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.09302299999999999</v>
+        <v>0.093178</v>
       </c>
       <c r="F83" t="n">
-        <v>840932378</v>
+        <v>842206075</v>
       </c>
       <c r="G83" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H83" t="n">
-        <v>41412012</v>
+        <v>29529404</v>
       </c>
       <c r="I83" t="n">
-        <v>0.094961</v>
+        <v>0.09484099999999999</v>
       </c>
       <c r="J83" t="n">
-        <v>0.090361</v>
+        <v>0.091696</v>
       </c>
       <c r="K83" t="n">
-        <v>0.00234688</v>
+        <v>0.00045171</v>
       </c>
       <c r="L83" t="n">
-        <v>2.41763</v>
+        <v>0.48715</v>
       </c>
       <c r="M83" t="n">
         <v>9040075710.158276</v>
       </c>
       <c r="N83" t="n">
-        <v>9040413275.136045</v>
+        <v>9040640286.975349</v>
       </c>
       <c r="O83" t="n">
         <v>3.56</v>
@@ -6002,19 +6002,19 @@
         <v>43636.28563657407</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0001824086135181944</v>
+        <v>0.0001864584693027869</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6033,28 +6033,28 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.834313</v>
+        <v>0.82647</v>
       </c>
       <c r="F84" t="n">
-        <v>834313461</v>
+        <v>826200915</v>
       </c>
       <c r="G84" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H84" t="n">
-        <v>3488275</v>
+        <v>3377653</v>
       </c>
       <c r="I84" t="n">
-        <v>0.846082</v>
+        <v>0.836029</v>
       </c>
       <c r="J84" t="n">
-        <v>0.825558</v>
+        <v>0.821452</v>
       </c>
       <c r="K84" t="n">
-        <v>0.007850930000000001</v>
+        <v>-0.004186455123449062</v>
       </c>
       <c r="L84" t="n">
-        <v>0.8590100000000001</v>
+        <v>-0.50399</v>
       </c>
       <c r="M84" t="n">
         <v>1000000000</v>
@@ -6069,287 +6069,287 @@
         <v>44328.27623842593</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R84" t="b">
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001781443009396171</v>
+        <v>0.0001760673147636607</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jupiter-exchange-solana</t>
+          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>jup</t>
+          <t>ustb</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Invesco Short Duration US Government Securities Fund</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.247551</v>
+        <v>11.21</v>
       </c>
       <c r="F85" t="n">
-        <v>821702438</v>
+        <v>805323062</v>
       </c>
       <c r="G85" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H85" t="n">
-        <v>103867053</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0.256569</v>
+        <v>11.21</v>
       </c>
       <c r="J85" t="n">
-        <v>0.23951</v>
+        <v>11.21</v>
       </c>
       <c r="K85" t="n">
-        <v>0.008722809999999999</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>2.85164</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3319369204.37</v>
+        <v>71851495.88542999</v>
       </c>
       <c r="N85" t="n">
-        <v>6861487227.770792</v>
+        <v>71851495.88542999</v>
       </c>
       <c r="O85" t="n">
-        <v>2</v>
+        <v>11.21</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>45322.29359953704</v>
+        <v>46276.59027777778</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R85" t="b">
         <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001700195059002433</v>
+        <v>0.0001625126238409731</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
+          <t>jupiter-exchange-solana</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ustb</t>
+          <t>jup</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Invesco Short Duration US Government Securities Fund</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>11.21</v>
+        <v>0.233377</v>
       </c>
       <c r="F86" t="n">
-        <v>805069396</v>
+        <v>774708889</v>
       </c>
       <c r="G86" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>53816588</v>
       </c>
       <c r="I86" t="n">
-        <v>11.21</v>
+        <v>0.248026</v>
       </c>
       <c r="J86" t="n">
-        <v>11.21</v>
+        <v>0.23225</v>
       </c>
       <c r="K86" t="n">
-        <v>0.001097</v>
+        <v>-0.01130721160412404</v>
       </c>
       <c r="L86" t="n">
-        <v>0.00979</v>
+        <v>-4.62114</v>
       </c>
       <c r="M86" t="n">
-        <v>71828863.654614</v>
+        <v>3319369204.37</v>
       </c>
       <c r="N86" t="n">
-        <v>71828863.654614</v>
+        <v>6861487156.891288</v>
       </c>
       <c r="O86" t="n">
-        <v>11.21</v>
+        <v>2</v>
       </c>
       <c r="P86" s="1" t="n">
-        <v>46276.59027777778</v>
+        <v>45322.29359953704</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001593034793628802</v>
+        <v>0.0001426367461408722</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ether-fi</t>
+          <t>stable-2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ethfi</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Ether.fi</t>
+          <t>​​Stable</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.7649010000000001</v>
+        <v>0.0283106</v>
       </c>
       <c r="F87" t="n">
-        <v>738397322</v>
+        <v>744262459</v>
       </c>
       <c r="G87" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H87" t="n">
-        <v>154766747</v>
+        <v>7582550</v>
       </c>
       <c r="I87" t="n">
-        <v>0.774993</v>
+        <v>0.02831921</v>
       </c>
       <c r="J87" t="n">
-        <v>0.63907</v>
+        <v>0.02753636</v>
       </c>
       <c r="K87" t="n">
-        <v>0.127353</v>
+        <v>0.0005849199999999999</v>
       </c>
       <c r="L87" t="n">
-        <v>19.69859</v>
+        <v>2.10966</v>
       </c>
       <c r="M87" t="n">
-        <v>965350000</v>
+        <v>26283132716</v>
       </c>
       <c r="N87" t="n">
-        <v>965350000</v>
+        <v>100000000000</v>
       </c>
       <c r="O87" t="n">
-        <v>8.529999999999999</v>
+        <v>0.04323745</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>45378.63525462963</v>
+        <v>46156.97986111111</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001163492371812613</v>
+        <v>0.0001228697735336199</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>stable-2</t>
+          <t>janus-henderson-anemoy-treasury-fund</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>jtrsy</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>​​Stable</t>
+          <t>Janus Henderson Anemoy Treasury Fund</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.02772471</v>
+        <v>1.12</v>
       </c>
       <c r="F88" t="n">
-        <v>727843516</v>
+        <v>725070974</v>
       </c>
       <c r="G88" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H88" t="n">
-        <v>9957228</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0291463</v>
+        <v>1.12</v>
       </c>
       <c r="J88" t="n">
-        <v>0.02702663</v>
+        <v>1.12</v>
       </c>
       <c r="K88" t="n">
-        <v>0.0007886</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>2.55751</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>26252515775</v>
+        <v>649898513.025921</v>
       </c>
       <c r="N88" t="n">
-        <v>100000000000</v>
+        <v>649898513.025921</v>
       </c>
       <c r="O88" t="n">
-        <v>0.04323745</v>
+        <v>1.12</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>46156.97986111111</v>
+        <v>46276.55543981482</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R88" t="b">
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001095498275984453</v>
+        <v>0.0001104099364266916</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6368,28 +6368,28 @@
         </is>
       </c>
       <c r="E89" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F89" t="n">
+        <v>714694281</v>
+      </c>
+      <c r="G89" t="n">
+        <v>87</v>
+      </c>
+      <c r="H89" t="n">
+        <v>26269304</v>
+      </c>
+      <c r="I89" t="n">
         <v>1.4</v>
       </c>
-      <c r="F89" t="n">
-        <v>727013232</v>
-      </c>
-      <c r="G89" t="n">
-        <v>88</v>
-      </c>
-      <c r="H89" t="n">
-        <v>38956531</v>
-      </c>
-      <c r="I89" t="n">
-        <v>1.46</v>
-      </c>
       <c r="J89" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="K89" t="n">
-        <v>0.00484286</v>
+        <v>-0.01491997644989529</v>
       </c>
       <c r="L89" t="n">
-        <v>0.28892</v>
+        <v>-1.07055</v>
       </c>
       <c r="M89" t="n">
         <v>518776241.2826915</v>
@@ -6404,354 +6404,354 @@
         <v>45368.35444444444</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R89" t="b">
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001090149076855666</v>
+        <v>0.0001036729953046991</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-treasury-fund</t>
+          <t>janus-henderson-anemoy-aaa-clo-fund</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>jtrsy</t>
+          <t>jaaa</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund</t>
+          <t>Janus Henderson Anemoy AAA CLO Fund</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1.12</v>
+        <v>1.049</v>
       </c>
       <c r="F90" t="n">
-        <v>725070974</v>
+        <v>713695634</v>
       </c>
       <c r="G90" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>1.12</v>
+        <v>1.049</v>
       </c>
       <c r="J90" t="n">
-        <v>1.12</v>
+        <v>1.049</v>
       </c>
       <c r="K90" t="n">
-        <v>3.1e-05</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>0.00278</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>649898513.025921</v>
+        <v>680267946.936126</v>
       </c>
       <c r="N90" t="n">
-        <v>649898513.025921</v>
+        <v>680267946.936126</v>
       </c>
       <c r="O90" t="n">
-        <v>1.12</v>
+        <v>1.049</v>
       </c>
       <c r="P90" s="1" t="n">
-        <v>46276.55543981482</v>
+        <v>46276.84375</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>0.000107763585872611</v>
+        <v>0.0001030246359439033</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>pancakeswap-token</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Dash</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>56.46</v>
+        <v>2.18</v>
       </c>
       <c r="F91" t="n">
-        <v>724189441</v>
+        <v>698387350</v>
       </c>
       <c r="G91" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H91" t="n">
-        <v>117062460</v>
+        <v>49232076</v>
       </c>
       <c r="I91" t="n">
-        <v>59.25</v>
+        <v>2.23</v>
       </c>
       <c r="J91" t="n">
-        <v>55.31</v>
+        <v>2.17</v>
       </c>
       <c r="K91" t="n">
-        <v>-0.2610257403269927</v>
+        <v>-0.04925185431566437</v>
       </c>
       <c r="L91" t="n">
-        <v>-0.49723</v>
+        <v>-2.20761</v>
       </c>
       <c r="M91" t="n">
-        <v>12825646.1579011</v>
+        <v>320190976.0630089</v>
       </c>
       <c r="N91" t="n">
-        <v>12825952.24479751</v>
+        <v>331857365.0100838</v>
       </c>
       <c r="O91" t="n">
-        <v>1493.59</v>
+        <v>43.96</v>
       </c>
       <c r="P91" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>44316.08914351852</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R91" t="b">
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>0.0001071956482084386</v>
+        <v>9.308591963161186e-05</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>pancakeswap-token</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>GHO</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2.24</v>
+        <v>0.998686</v>
       </c>
       <c r="F92" t="n">
-        <v>718311097</v>
+        <v>698081387</v>
       </c>
       <c r="G92" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H92" t="n">
-        <v>68699327</v>
+        <v>1756918</v>
       </c>
       <c r="I92" t="n">
-        <v>2.27</v>
+        <v>0.998964</v>
       </c>
       <c r="J92" t="n">
-        <v>2.16</v>
+        <v>0.998574</v>
       </c>
       <c r="K92" t="n">
-        <v>0.07718800000000001</v>
+        <v>-0.00012704836909827</v>
       </c>
       <c r="L92" t="n">
-        <v>3.40602</v>
+        <v>-0.01272</v>
       </c>
       <c r="M92" t="n">
-        <v>320188615.5306796</v>
+        <v>699000000</v>
       </c>
       <c r="N92" t="n">
-        <v>331857365.0223532</v>
+        <v>699000000</v>
       </c>
       <c r="O92" t="n">
-        <v>43.96</v>
+        <v>1.03</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>44316.08914351852</v>
+        <v>45350.38608796296</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R92" t="b">
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>0.0001034084582103764</v>
+        <v>9.28872768928792e-05</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-aaa-clo-fund</t>
+          <t>filecoin</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>jaaa</t>
+          <t>fil</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy AAA CLO Fund</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1.049</v>
+        <v>0.841786</v>
       </c>
       <c r="F93" t="n">
-        <v>713695634</v>
+        <v>696662345</v>
       </c>
       <c r="G93" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>58328314</v>
       </c>
       <c r="I93" t="n">
-        <v>1.049</v>
+        <v>0.83914</v>
       </c>
       <c r="J93" t="n">
-        <v>1.049</v>
+        <v>0.7973209999999999</v>
       </c>
       <c r="K93" t="n">
-        <v>0.000158</v>
+        <v>0.03396596</v>
       </c>
       <c r="L93" t="n">
-        <v>0.01506</v>
+        <v>4.20465</v>
       </c>
       <c r="M93" t="n">
-        <v>680267946.936126</v>
+        <v>827747763</v>
       </c>
       <c r="N93" t="n">
-        <v>680267946.936126</v>
+        <v>1957056557</v>
       </c>
       <c r="O93" t="n">
-        <v>1.049</v>
+        <v>236.84</v>
       </c>
       <c r="P93" s="1" t="n">
-        <v>46276.84375</v>
+        <v>44287.22894675926</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R93" t="b">
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>0.0001004348936639622</v>
+        <v>9.196598121576564e-05</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>GHO</t>
+          <t>Dash</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.998669</v>
+        <v>53.66</v>
       </c>
       <c r="F94" t="n">
-        <v>698069272</v>
+        <v>688404472</v>
       </c>
       <c r="G94" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H94" t="n">
-        <v>7357160</v>
+        <v>80144094</v>
       </c>
       <c r="I94" t="n">
-        <v>0.998995</v>
+        <v>56.52</v>
       </c>
       <c r="J94" t="n">
-        <v>0.998175</v>
+        <v>53.69</v>
       </c>
       <c r="K94" t="n">
-        <v>7.726e-05</v>
+        <v>-2.621952386134858</v>
       </c>
       <c r="L94" t="n">
-        <v>0.00617</v>
+        <v>-4.65825</v>
       </c>
       <c r="M94" t="n">
-        <v>699000000</v>
+        <v>12826804.35764862</v>
       </c>
       <c r="N94" t="n">
-        <v>699000000</v>
+        <v>12827522.60472958</v>
       </c>
       <c r="O94" t="n">
-        <v>1.03</v>
+        <v>1493.59</v>
       </c>
       <c r="P94" s="1" t="n">
-        <v>45350.38608796296</v>
+        <v>43088.66666666666</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S94" t="n">
-        <v>9.036743216927938e-05</v>
+        <v>8.660465808575767e-05</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6770,28 +6770,28 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.00785427</v>
+        <v>0.00768983</v>
       </c>
       <c r="F95" t="n">
-        <v>675349478</v>
+        <v>661185178</v>
       </c>
       <c r="G95" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H95" t="n">
-        <v>13302986</v>
+        <v>13964290</v>
       </c>
       <c r="I95" t="n">
-        <v>0.007819039999999999</v>
+        <v>0.0079963</v>
       </c>
       <c r="J95" t="n">
-        <v>0.00723474</v>
+        <v>0.00749197</v>
       </c>
       <c r="K95" t="n">
-        <v>0.00046606</v>
+        <v>-9.4151996024112e-05</v>
       </c>
       <c r="L95" t="n">
-        <v>6.25405</v>
+        <v>-1.20956</v>
       </c>
       <c r="M95" t="n">
         <v>85985041177</v>
@@ -6806,86 +6806,86 @@
         <v>44304.71413194444</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>7.572994640886207e-05</v>
+        <v>6.893286408932697e-05</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>filecoin</t>
+          <t>ether-fi</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>ethfi</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>Ether.fi</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.813648</v>
+        <v>0.6500050000000001</v>
       </c>
       <c r="F96" t="n">
-        <v>673437387</v>
+        <v>626888647</v>
       </c>
       <c r="G96" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H96" t="n">
-        <v>76557335</v>
+        <v>66604793</v>
       </c>
       <c r="I96" t="n">
-        <v>0.825543</v>
+        <v>0.773031</v>
       </c>
       <c r="J96" t="n">
-        <v>0.775082</v>
+        <v>0.651512</v>
       </c>
       <c r="K96" t="n">
-        <v>0.01862285</v>
+        <v>-0.1070226092627694</v>
       </c>
       <c r="L96" t="n">
-        <v>2.18164</v>
+        <v>-14.13721</v>
       </c>
       <c r="M96" t="n">
-        <v>827677063</v>
+        <v>965350000</v>
       </c>
       <c r="N96" t="n">
-        <v>1957060739</v>
+        <v>965350000</v>
       </c>
       <c r="O96" t="n">
-        <v>236.84</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="P96" s="1" t="n">
-        <v>44287.22894675926</v>
+        <v>45378.63525462963</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S96" t="n">
-        <v>7.449806002885693e-05</v>
+        <v>4.666626045793964e-05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6904,34 +6904,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.076846</v>
+        <v>0.076042</v>
       </c>
       <c r="F97" t="n">
-        <v>604829349</v>
+        <v>598617819</v>
       </c>
       <c r="G97" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H97" t="n">
-        <v>11285459</v>
+        <v>11123884</v>
       </c>
       <c r="I97" t="n">
-        <v>0.07735300000000001</v>
+        <v>0.07681300000000001</v>
       </c>
       <c r="J97" t="n">
-        <v>0.076713</v>
+        <v>0.075978</v>
       </c>
       <c r="K97" t="n">
-        <v>-0.000132520480209841</v>
+        <v>-0.0006413350189097971</v>
       </c>
       <c r="L97" t="n">
-        <v>-0.19458</v>
+        <v>-0.83634</v>
       </c>
       <c r="M97" t="n">
-        <v>7870620289.70434</v>
+        <v>7870655757.768536</v>
       </c>
       <c r="N97" t="n">
-        <v>9939560336.1777</v>
+        <v>9939595838.896603</v>
       </c>
       <c r="O97" t="n">
         <v>0.450785</v>
@@ -6940,19 +6940,19 @@
         <v>43450.66666666666</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>3.029655101538742e-05</v>
+        <v>2.83117708622681e-05</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6971,28 +6971,28 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5.95</v>
+        <v>5.97</v>
       </c>
       <c r="F98" t="n">
-        <v>595309141</v>
+        <v>597001466</v>
       </c>
       <c r="G98" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H98" t="n">
-        <v>85558506</v>
+        <v>63175325</v>
       </c>
       <c r="I98" t="n">
-        <v>6.12</v>
+        <v>6.18</v>
       </c>
       <c r="J98" t="n">
-        <v>5.7</v>
+        <v>5.77</v>
       </c>
       <c r="K98" t="n">
-        <v>0.04170575</v>
+        <v>0.04376152</v>
       </c>
       <c r="L98" t="n">
-        <v>0.50802</v>
+        <v>0.73812</v>
       </c>
       <c r="M98" t="n">
         <v>100000000</v>
@@ -7007,86 +7007,86 @@
         <v>45365.29608796296</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R98" t="b">
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>2.416304870298921e-05</v>
+        <v>2.726237342964135e-05</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>aerodrome-finance</t>
+          <t>flare-networks</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>aero</t>
+          <t>flr</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Aerodrome Finance</t>
+          <t>Flare</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.578739</v>
+        <v>0.00642494</v>
       </c>
       <c r="F99" t="n">
-        <v>572272862</v>
+        <v>558487137</v>
       </c>
       <c r="G99" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H99" t="n">
-        <v>60416766</v>
+        <v>1975430</v>
       </c>
       <c r="I99" t="n">
-        <v>0.615443</v>
+        <v>0.00653376</v>
       </c>
       <c r="J99" t="n">
-        <v>0.564084</v>
+        <v>0.00640673</v>
       </c>
       <c r="K99" t="n">
-        <v>0.01491191</v>
+        <v>7.93e-06</v>
       </c>
       <c r="L99" t="n">
-        <v>2.46761</v>
+        <v>0.12362</v>
       </c>
       <c r="M99" t="n">
-        <v>988827052.1381764</v>
+        <v>86938088551.2818</v>
       </c>
       <c r="N99" t="n">
-        <v>1978450301.483024</v>
+        <v>106539016188.1805</v>
       </c>
       <c r="O99" t="n">
-        <v>2.32</v>
+        <v>0.150073</v>
       </c>
       <c r="P99" s="1" t="n">
-        <v>45633.25043981482</v>
+        <v>44935.80144675926</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R99" t="b">
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>9.321663880772048e-06</v>
+        <v>2.257415990305974e-06</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7105,28 +7105,28 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.02802343</v>
+        <v>0.02784597</v>
       </c>
       <c r="F100" t="n">
-        <v>558974589</v>
+        <v>555295579</v>
       </c>
       <c r="G100" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H100" t="n">
-        <v>6328854</v>
+        <v>3799999</v>
       </c>
       <c r="I100" t="n">
-        <v>0.02852745</v>
+        <v>0.02803692</v>
       </c>
       <c r="J100" t="n">
-        <v>0.02781623</v>
+        <v>0.02763857</v>
       </c>
       <c r="K100" t="n">
-        <v>0.0002222</v>
+        <v>-0.000140795085449043</v>
       </c>
       <c r="L100" t="n">
-        <v>0.53825</v>
+        <v>-0.50308</v>
       </c>
       <c r="M100" t="n">
         <v>19946688440</v>
@@ -7141,74 +7141,74 @@
         <v>44428.86097222222</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R100" t="b">
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>7.541002102721244e-07</v>
+        <v>1.853359612038094e-07</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>flare-networks</t>
+          <t>aerodrome-finance</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>flr</t>
+          <t>aero</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Flare</t>
+          <t>Aerodrome Finance</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.00641703</v>
+        <v>0.561319</v>
       </c>
       <c r="F101" t="n">
-        <v>557804101</v>
+        <v>555010112</v>
       </c>
       <c r="G101" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H101" t="n">
-        <v>1789194</v>
+        <v>14976935</v>
       </c>
       <c r="I101" t="n">
-        <v>0.00645471</v>
+        <v>0.5745209999999999</v>
       </c>
       <c r="J101" t="n">
-        <v>0.00628271</v>
+        <v>0.55507</v>
       </c>
       <c r="K101" t="n">
-        <v>9.946999999999999e-05</v>
+        <v>-0.01302517765560196</v>
       </c>
       <c r="L101" t="n">
-        <v>1.54403</v>
+        <v>-2.26783</v>
       </c>
       <c r="M101" t="n">
-        <v>86925636898.98215</v>
+        <v>988772768.1180431</v>
       </c>
       <c r="N101" t="n">
-        <v>106531758480.7972</v>
+        <v>1978450301.483024</v>
       </c>
       <c r="O101" t="n">
-        <v>0.150073</v>
+        <v>2.32</v>
       </c>
       <c r="P101" s="1" t="n">
-        <v>44935.80144675926</v>
+        <v>45633.25043981482</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46277.53078703704</v>
+        <v>46278.57106481482</v>
       </c>
       <c r="R101" t="b">
         <v>0</v>

--- a/src/xlsx/cleaned_data.xlsx
+++ b/src/xlsx/cleaned_data.xlsx
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,34 +539,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>76721</v>
+        <v>78362</v>
       </c>
       <c r="F2" t="n">
-        <v>1540822738759</v>
+        <v>1573986553774</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>15423566617</v>
+        <v>25984289979</v>
       </c>
       <c r="I2" t="n">
-        <v>77479</v>
+        <v>78630</v>
       </c>
       <c r="J2" t="n">
-        <v>76516</v>
+        <v>76439</v>
       </c>
       <c r="K2" t="n">
-        <v>-567.5499394721992</v>
+        <v>1231.1</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.73433</v>
+        <v>1.60581</v>
       </c>
       <c r="M2" t="n">
-        <v>20083712</v>
+        <v>20084256</v>
       </c>
       <c r="N2" t="n">
-        <v>20083803</v>
+        <v>20084296</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -575,7 +575,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -587,7 +587,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,34 +606,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2475.01</v>
+        <v>2504.03</v>
       </c>
       <c r="F3" t="n">
-        <v>302065765195</v>
+        <v>305633502308</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>8681587348</v>
+        <v>12681366507</v>
       </c>
       <c r="I3" t="n">
-        <v>2543.69</v>
+        <v>2531.64</v>
       </c>
       <c r="J3" t="n">
-        <v>2470.18</v>
+        <v>2467.86</v>
       </c>
       <c r="K3" t="n">
-        <v>-63.41930568684711</v>
+        <v>14.1</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.49837</v>
+        <v>0.55974</v>
       </c>
       <c r="M3" t="n">
-        <v>122044301.968694</v>
+        <v>122047243.4940371</v>
       </c>
       <c r="N3" t="n">
-        <v>122044301.968694</v>
+        <v>122047243.4940371</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -642,19 +642,19 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1957521731289227</v>
+        <v>0.1938930412502688</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,34 +673,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9997549999999999</v>
+        <v>0.999729</v>
       </c>
       <c r="F4" t="n">
-        <v>183471976747</v>
+        <v>183381380503</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>31189029121</v>
+        <v>47887967714</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9999</v>
+        <v>0.999795</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999673</v>
+        <v>0.999546</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.4432368397109e-05</v>
+        <v>-3.1522703644593e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00244</v>
+        <v>-0.00331</v>
       </c>
       <c r="M4" t="n">
-        <v>183517171052.1943</v>
+        <v>183430992297.9018</v>
       </c>
       <c r="N4" t="n">
-        <v>188984116915.3062</v>
+        <v>188897938202.3062</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -709,19 +709,19 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1187566052530865</v>
+        <v>0.116195206254701</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,34 +740,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>715.63</v>
+        <v>721.51</v>
       </c>
       <c r="F5" t="n">
-        <v>95291988111</v>
+        <v>96081461908</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>729267845</v>
+        <v>887352635</v>
       </c>
       <c r="I5" t="n">
-        <v>736.9</v>
+        <v>727.36</v>
       </c>
       <c r="J5" t="n">
-        <v>714.33</v>
+        <v>714.28</v>
       </c>
       <c r="K5" t="n">
-        <v>-20.34689269518844</v>
+        <v>2.66</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.76462</v>
+        <v>0.3615</v>
       </c>
       <c r="M5" t="n">
-        <v>133160976.96</v>
+        <v>133160863.85</v>
       </c>
       <c r="N5" t="n">
-        <v>133160976.96</v>
+        <v>133160863.85</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -776,19 +776,19 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06150682523370059</v>
+        <v>0.06071138666962943</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -807,28 +807,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="F6" t="n">
-        <v>84099500734</v>
+        <v>88060370043</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>926219439</v>
+        <v>2415726593</v>
       </c>
       <c r="I6" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="J6" t="n">
         <v>1.34</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.02964740290489787</v>
+        <v>0.056142</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.16849</v>
+        <v>4.18102</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -843,19 +843,19 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05424023958184662</v>
+        <v>0.05561354899606218</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,34 +874,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999803</v>
+        <v>0.999841</v>
       </c>
       <c r="F7" t="n">
-        <v>74215368644</v>
+        <v>74142138897</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>6204149731</v>
+        <v>13799048631</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999961</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999717</v>
+        <v>0.999711</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.497102552268e-05</v>
+        <v>-2.1127436362067e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0025</v>
+        <v>-0.00261</v>
       </c>
       <c r="M7" t="n">
-        <v>74230204758.1429</v>
+        <v>74153956598.56355</v>
       </c>
       <c r="N7" t="n">
-        <v>74232084708.50609</v>
+        <v>74236759977.72971</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -910,19 +910,19 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04782308761133666</v>
+        <v>0.04676776038278142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -941,34 +941,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>99.78</v>
+        <v>101.84</v>
       </c>
       <c r="F8" t="n">
-        <v>58544716598</v>
+        <v>59767609118</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>1835705498</v>
+        <v>2729178439</v>
       </c>
       <c r="I8" t="n">
-        <v>102.3</v>
+        <v>102.21</v>
       </c>
       <c r="J8" t="n">
-        <v>99.45</v>
+        <v>99.03</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.106818682073197</v>
+        <v>1.51</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.06771</v>
+        <v>1.50505</v>
       </c>
       <c r="M8" t="n">
-        <v>586731099.4701495</v>
+        <v>586892648.6679221</v>
       </c>
       <c r="N8" t="n">
-        <v>634018355.2162156</v>
+        <v>634017381.8979012</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -977,19 +977,19 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03764910827349428</v>
+        <v>0.03763196931087597</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1008,34 +1008,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.340537</v>
+        <v>0.340552</v>
       </c>
       <c r="F9" t="n">
-        <v>32326642058</v>
+        <v>32338144917</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>340530028</v>
+        <v>363419765</v>
       </c>
       <c r="I9" t="n">
-        <v>0.341069</v>
+        <v>0.341529</v>
       </c>
       <c r="J9" t="n">
-        <v>0.339263</v>
+        <v>0.337711</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00014634</v>
+        <v>-0.000581742705109523</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04299</v>
+        <v>-0.15732</v>
       </c>
       <c r="M9" t="n">
-        <v>94944652948.92628</v>
+        <v>94950123551.61649</v>
       </c>
       <c r="N9" t="n">
-        <v>94948611026.79419</v>
+        <v>94950129154.07608</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1044,19 +1044,19 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02062734377607768</v>
+        <v>0.02019906138224671</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1075,34 +1075,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>1.046</v>
       </c>
       <c r="F10" t="n">
-        <v>22551817529</v>
+        <v>23593992468</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>50043</v>
+        <v>958374</v>
       </c>
       <c r="I10" t="n">
-        <v>1.044</v>
+        <v>1.042</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>1.006</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.01618492385492987</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.59239</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>22547102017.768</v>
+        <v>22558008629.268</v>
       </c>
       <c r="N10" t="n">
-        <v>22552850918.668</v>
+        <v>22558008629.268</v>
       </c>
       <c r="O10" t="n">
         <v>1.061</v>
@@ -1111,19 +1111,19 @@
         <v>46237.59675925926</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46278.05567129629</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01428115840375518</v>
+        <v>0.01464167960328518</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1142,34 +1142,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1087.03</v>
+        <v>1135.01</v>
       </c>
       <c r="F11" t="n">
-        <v>18394302590</v>
+        <v>19206090756</v>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1165436311</v>
+        <v>1142157231</v>
       </c>
       <c r="I11" t="n">
-        <v>1154.85</v>
+        <v>1155.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1075.39</v>
+        <v>1048.58</v>
       </c>
       <c r="K11" t="n">
-        <v>-67.91789754973047</v>
+        <v>46.32</v>
       </c>
       <c r="L11" t="n">
-        <v>-5.88059</v>
+        <v>4.11852</v>
       </c>
       <c r="M11" t="n">
-        <v>16925695.4780448</v>
+        <v>16930431.4155448</v>
       </c>
       <c r="N11" t="n">
-        <v>16930195.4780448</v>
+        <v>16932228.2905448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1178,19 +1178,19 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01158194263647293</v>
+        <v>0.01185293076063072</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1209,28 +1209,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>77.36</v>
+        <v>79.87</v>
       </c>
       <c r="F12" t="n">
-        <v>17208887027</v>
+        <v>17767318483</v>
       </c>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>575492758</v>
+        <v>722094725</v>
       </c>
       <c r="I12" t="n">
-        <v>80.77</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>77.09999999999999</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.878903719731241</v>
+        <v>1.74</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.58773</v>
+        <v>2.18041</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1245,19 +1245,19 @@
         <v>46271.5199074074</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01081232606855243</v>
+        <v>0.01093851317005456</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1276,34 +1276,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.08321099999999999</v>
+        <v>0.08391800000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>12972524811</v>
+        <v>13084729747</v>
       </c>
       <c r="G13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>331894085</v>
+        <v>582797744</v>
       </c>
       <c r="I13" t="n">
-        <v>0.085325</v>
+        <v>0.084753</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08315699999999999</v>
+        <v>0.08204</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.001738211689757158</v>
+        <v>0.00034659</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.04618</v>
+        <v>0.35787</v>
       </c>
       <c r="M13" t="n">
-        <v>155898206383.7052</v>
+        <v>155910866383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171610343126.579</v>
+        <v>155913316383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1312,19 +1312,19 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.008061919670230172</v>
+        <v>0.007962474786506826</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1343,31 +1343,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01525428</v>
+        <v>0.01437241</v>
       </c>
       <c r="F14" t="n">
-        <v>10818364725</v>
+        <v>10194077797</v>
       </c>
       <c r="G14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>34695409</v>
+        <v>23950993</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01589978</v>
+        <v>0.01539524</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01503352</v>
+        <v>0.01471193</v>
       </c>
       <c r="K14" t="n">
-        <v>0.00017217</v>
+        <v>-0.000917734779514243</v>
       </c>
       <c r="L14" t="n">
-        <v>1.14158</v>
+        <v>-5.95737</v>
       </c>
       <c r="M14" t="n">
-        <v>709218381891.3804</v>
+        <v>709219646352.0608</v>
       </c>
       <c r="N14" t="n">
         <v>1142408526965.963</v>
@@ -1379,153 +1379,153 @@
         <v>46259.82847222222</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.006663357559283231</v>
+        <v>0.006125309141243313</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>529.33</v>
+        <v>0.999728</v>
       </c>
       <c r="F15" t="n">
-        <v>9952232995</v>
+        <v>9822164283</v>
       </c>
       <c r="G15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>97785882</v>
+        <v>103418986</v>
       </c>
       <c r="I15" t="n">
-        <v>543.63</v>
+        <v>0.999883</v>
       </c>
       <c r="J15" t="n">
-        <v>524.34</v>
+        <v>0.99953</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.876506267517925</v>
+        <v>-5.1109509834446e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.35326</v>
+        <v>-0.00638</v>
       </c>
       <c r="M15" t="n">
-        <v>18804107.03109685</v>
+        <v>9825388957.758593</v>
       </c>
       <c r="N15" t="n">
-        <v>18804122.63109685</v>
+        <v>9825388957.758593</v>
       </c>
       <c r="O15" t="n">
-        <v>797.73</v>
+        <v>1.057</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>46036.48202546296</v>
+        <v>45593.90336805556</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.006101032118133577</v>
+        <v>0.005888937989424073</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.999763</v>
+        <v>513.16</v>
       </c>
       <c r="F16" t="n">
-        <v>9846306603</v>
+        <v>9650985830</v>
       </c>
       <c r="G16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>69915065</v>
+        <v>120076787</v>
       </c>
       <c r="I16" t="n">
-        <v>0.999937</v>
+        <v>537.77</v>
       </c>
       <c r="J16" t="n">
-        <v>0.999626</v>
+        <v>502.91</v>
       </c>
       <c r="K16" t="n">
-        <v>1.663e-05</v>
+        <v>-22.04391946356634</v>
       </c>
       <c r="L16" t="n">
-        <v>0.00166</v>
+        <v>-4.24549</v>
       </c>
       <c r="M16" t="n">
-        <v>9849589553.751617</v>
+        <v>18804596.02384349</v>
       </c>
       <c r="N16" t="n">
-        <v>9848763608.199549</v>
+        <v>18804629.02373879</v>
       </c>
       <c r="O16" t="n">
-        <v>1.057</v>
+        <v>797.73</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>45593.90336805556</v>
+        <v>46036.48202546296</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>0.006032260702599832</v>
+        <v>0.005780144824940554</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1544,28 +1544,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>79.53</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>9375103870</v>
+        <v>9541965154</v>
       </c>
       <c r="G17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>29764166</v>
+        <v>103097807</v>
       </c>
       <c r="I17" t="n">
-        <v>80.62</v>
+        <v>81.25</v>
       </c>
       <c r="J17" t="n">
-        <v>79.31999999999999</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.8357182138967261</v>
+        <v>1.063</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.03986</v>
+        <v>1.3493</v>
       </c>
       <c r="M17" t="n">
         <v>117882016</v>
@@ -1580,19 +1580,19 @@
         <v>46276.58553240741</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005726338086527162</v>
+        <v>0.005710856289331622</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1611,28 +1611,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.24</v>
+        <v>11.43</v>
       </c>
       <c r="F18" t="n">
-        <v>8409875424</v>
+        <v>8547956810</v>
       </c>
       <c r="G18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>217162086</v>
+        <v>351732452</v>
       </c>
       <c r="I18" t="n">
-        <v>11.62</v>
+        <v>11.49</v>
       </c>
       <c r="J18" t="n">
-        <v>11.24</v>
+        <v>11.14</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3109450215767513</v>
+        <v>0.167787</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.69148</v>
+        <v>1.4751</v>
       </c>
       <c r="M18" t="n">
         <v>748099970.424884</v>
@@ -1647,19 +1647,19 @@
         <v>44325.67635416667</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005099675313524787</v>
+        <v>0.005079110229173091</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1678,28 +1678,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.06</v>
+        <v>8.99</v>
       </c>
       <c r="F19" t="n">
-        <v>8329317905</v>
+        <v>8265020156</v>
       </c>
       <c r="G19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>253370</v>
+        <v>146114</v>
       </c>
       <c r="I19" t="n">
-        <v>9.15</v>
+        <v>9.08</v>
       </c>
       <c r="J19" t="n">
-        <v>9.050000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.06044450122227296</v>
+        <v>-0.06750082080595554</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6631</v>
+        <v>-0.7448900000000001</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1714,19 +1714,19 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.005047374328766271</v>
+        <v>0.004899288683893449</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1745,28 +1745,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.20505</v>
+        <v>0.208339</v>
       </c>
       <c r="F20" t="n">
-        <v>7692716004</v>
+        <v>7816066705</v>
       </c>
       <c r="G20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>203748626</v>
+        <v>352248691</v>
       </c>
       <c r="I20" t="n">
-        <v>0.209134</v>
+        <v>0.212356</v>
       </c>
       <c r="J20" t="n">
-        <v>0.203378</v>
+        <v>0.202412</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.003357533117483491</v>
+        <v>0.00229722</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.61104</v>
+        <v>1.0824</v>
       </c>
       <c r="M20" t="n">
         <v>37516725700.17653</v>
@@ -1781,19 +1781,19 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004634068324128231</v>
+        <v>0.004613954485668825</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1812,31 +1812,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.178693</v>
+        <v>0.192245</v>
       </c>
       <c r="F21" t="n">
-        <v>6224230152</v>
+        <v>6698510243</v>
       </c>
       <c r="G21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>77381146</v>
+        <v>232181544</v>
       </c>
       <c r="I21" t="n">
-        <v>0.182593</v>
+        <v>0.193471</v>
       </c>
       <c r="J21" t="n">
-        <v>0.177194</v>
+        <v>0.176496</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.002332784981005254</v>
+        <v>0.01369287</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.28865</v>
+        <v>7.59998</v>
       </c>
       <c r="M21" t="n">
-        <v>34833765117.35425</v>
+        <v>34833755724.17101</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70248</v>
@@ -1848,19 +1848,19 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.003680671830331697</v>
+        <v>0.003903686914843275</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1879,34 +1879,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.999617</v>
+        <v>0.999681</v>
       </c>
       <c r="F22" t="n">
-        <v>4600512204</v>
+        <v>4614179179</v>
       </c>
       <c r="G22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>20823617</v>
+        <v>32050801</v>
       </c>
       <c r="I22" t="n">
-        <v>0.999852</v>
+        <v>0.9996969999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>0.999548</v>
+        <v>0.9994150000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.000129444137486834</v>
+        <v>7.073e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.01295</v>
+        <v>0.00777</v>
       </c>
       <c r="M22" t="n">
-        <v>4602286942.433918</v>
+        <v>4615650751.612019</v>
       </c>
       <c r="N22" t="n">
-        <v>4600286942.433918</v>
+        <v>4620286189.396619</v>
       </c>
       <c r="O22" t="n">
         <v>1.034</v>
@@ -1915,19 +1915,19 @@
         <v>46000.38208333333</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R22" t="b">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.002626492795219208</v>
+        <v>0.00257898179974412</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1946,16 +1946,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.999888</v>
+        <v>0.999906</v>
       </c>
       <c r="F23" t="n">
-        <v>4572090305</v>
+        <v>4559719507</v>
       </c>
       <c r="G23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>88873493</v>
+        <v>200977036</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -1964,16 +1964,16 @@
         <v>0.999689</v>
       </c>
       <c r="K23" t="n">
-        <v>0.00014913</v>
+        <v>0.00013305</v>
       </c>
       <c r="L23" t="n">
-        <v>0.01492</v>
+        <v>0.00223</v>
       </c>
       <c r="M23" t="n">
-        <v>4573046928.984426</v>
+        <v>4560681562.981492</v>
       </c>
       <c r="N23" t="n">
-        <v>4571846995.287507</v>
+        <v>4560681562.981492</v>
       </c>
       <c r="O23" t="n">
         <v>1.22</v>
@@ -1982,19 +1982,19 @@
         <v>43902.79363425926</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R23" t="b">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.002608040224622948</v>
+        <v>0.002544369732922752</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2013,34 +2013,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>224.01</v>
+        <v>222.92</v>
       </c>
       <c r="F24" t="n">
-        <v>4499652482</v>
+        <v>4478998809</v>
       </c>
       <c r="G24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>131335669</v>
+        <v>154256060</v>
       </c>
       <c r="I24" t="n">
-        <v>230.98</v>
+        <v>225.71</v>
       </c>
       <c r="J24" t="n">
-        <v>221.91</v>
+        <v>219.99</v>
       </c>
       <c r="K24" t="n">
-        <v>-6.427621685092504</v>
+        <v>-0.8566991381841831</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.78932</v>
+        <v>-0.39865</v>
       </c>
       <c r="M24" t="n">
-        <v>20088571.77165077</v>
+        <v>20089046.77165077</v>
       </c>
       <c r="N24" t="n">
-        <v>20088881.14665077</v>
+        <v>20089328.02165077</v>
       </c>
       <c r="O24" t="n">
         <v>3785.82</v>
@@ -2049,19 +2049,19 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002561010853265781</v>
+        <v>0.002493067363840479</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2080,34 +2080,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.999573</v>
+        <v>0.9996</v>
       </c>
       <c r="F25" t="n">
-        <v>4307249899</v>
+        <v>4325414452</v>
       </c>
       <c r="G25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>571994025</v>
+        <v>1030935992</v>
       </c>
       <c r="I25" t="n">
-        <v>0.999912</v>
+        <v>0.999718</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9993840000000001</v>
+        <v>0.999383</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.000160970613908407</v>
+        <v>8.182999999999999e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.0161</v>
+        <v>0.00484</v>
       </c>
       <c r="M25" t="n">
-        <v>4309116026.3293</v>
+        <v>4327109501.780501</v>
       </c>
       <c r="N25" t="n">
-        <v>4309116026.3293</v>
+        <v>4327109501.780501</v>
       </c>
       <c r="O25" t="n">
         <v>1.048</v>
@@ -2116,19 +2116,19 @@
         <v>46212.42696759259</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002436095827506584</v>
+        <v>0.002395456198881555</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2147,34 +2147,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53.47</v>
+        <v>53.77</v>
       </c>
       <c r="F26" t="n">
-        <v>4149149491</v>
+        <v>4173096340</v>
       </c>
       <c r="G26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>174765883</v>
+        <v>218860200</v>
       </c>
       <c r="I26" t="n">
-        <v>54.53</v>
+        <v>55.19</v>
       </c>
       <c r="J26" t="n">
-        <v>53.4</v>
+        <v>53.41</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.4001230123206057</v>
+        <v>-0.5798134796304737</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.74282</v>
+        <v>-1.07178</v>
       </c>
       <c r="M26" t="n">
-        <v>77602941.87435494</v>
+        <v>77606448.13410389</v>
       </c>
       <c r="N26" t="n">
-        <v>77602929.37429333</v>
+        <v>77609316.89202861</v>
       </c>
       <c r="O26" t="n">
         <v>410.26</v>
@@ -2183,19 +2183,19 @@
         <v>44325.80077546297</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002333451069676802</v>
+        <v>0.002298649801100667</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2214,28 +2214,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6.23</v>
+        <v>6.36</v>
       </c>
       <c r="F27" t="n">
-        <v>3883037390</v>
+        <v>3962142069</v>
       </c>
       <c r="G27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>394857591</v>
+        <v>365274151</v>
       </c>
       <c r="I27" t="n">
-        <v>6.55</v>
+        <v>6.46</v>
       </c>
       <c r="J27" t="n">
-        <v>6.17</v>
+        <v>6.1</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.1737016955206609</v>
+        <v>0.106608</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.71232</v>
+        <v>1.65018</v>
       </c>
       <c r="M27" t="n">
         <v>623212423.7271129</v>
@@ -2250,19 +2250,19 @@
         <v>44318.89240740741</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002160681040122422</v>
+        <v>0.002164576953138874</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2281,34 +2281,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.094912</v>
+        <v>0.095821</v>
       </c>
       <c r="F28" t="n">
-        <v>3756999297</v>
+        <v>3794641050</v>
       </c>
       <c r="G28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>6502123</v>
+        <v>7684439</v>
       </c>
       <c r="I28" t="n">
-        <v>0.098969</v>
+        <v>0.097021</v>
       </c>
       <c r="J28" t="n">
-        <v>0.094314</v>
+        <v>0.094268</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.003071083278145426</v>
+        <v>0.00091269</v>
       </c>
       <c r="L28" t="n">
-        <v>-3.13429</v>
+        <v>0.9368</v>
       </c>
       <c r="M28" t="n">
-        <v>39583136301.85078</v>
+        <v>39589485630.91892</v>
       </c>
       <c r="N28" t="n">
-        <v>39583136301.85078</v>
+        <v>39589485630.91892</v>
       </c>
       <c r="O28" t="n">
         <v>0.194152</v>
@@ -2317,19 +2317,19 @@
         <v>46056.00148148148</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002078852348489238</v>
+        <v>0.002058120996843814</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2351,31 +2351,31 @@
         <v>1.35</v>
       </c>
       <c r="F29" t="n">
-        <v>3752328394</v>
+        <v>3763625970</v>
       </c>
       <c r="G29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>22159128</v>
+        <v>20347988</v>
       </c>
       <c r="I29" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="J29" t="n">
         <v>1.34</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.02511075836948562</v>
+        <v>-0.006013759062806434</v>
       </c>
       <c r="L29" t="n">
-        <v>-1.83118</v>
+        <v>-0.56774</v>
       </c>
       <c r="M29" t="n">
-        <v>2787775226.971808</v>
+        <v>2788394271.526778</v>
       </c>
       <c r="N29" t="n">
-        <v>5248392812.065145</v>
+        <v>5248995037.316007</v>
       </c>
       <c r="O29" t="n">
         <v>8.25</v>
@@ -2384,19 +2384,19 @@
         <v>45457.69225694444</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002075819821797204</v>
+        <v>0.002038409236159135</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2415,31 +2415,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.07571799999999999</v>
+        <v>0.07660699999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>3318798395</v>
+        <v>3357654046</v>
       </c>
       <c r="G30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>38129440</v>
+        <v>50267819</v>
       </c>
       <c r="I30" t="n">
-        <v>0.075777</v>
+        <v>0.077444</v>
       </c>
       <c r="J30" t="n">
-        <v>0.07427499999999999</v>
+        <v>0.074799</v>
       </c>
       <c r="K30" t="n">
-        <v>0.00114562</v>
+        <v>0.0009911</v>
       </c>
       <c r="L30" t="n">
-        <v>1.53626</v>
+        <v>1.31124</v>
       </c>
       <c r="M30" t="n">
-        <v>43831559672.50867</v>
+        <v>43831559671.84134</v>
       </c>
       <c r="N30" t="n">
         <v>50000000000</v>
@@ -2451,287 +2451,287 @@
         <v>44454.11143518519</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.001794355767894821</v>
+        <v>0.001780392122852108</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>global-dollar</t>
+          <t>avalanche-2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>usdg</t>
+          <t>avax</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Global Dollar</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.999936</v>
+        <v>7.46</v>
       </c>
       <c r="F31" t="n">
-        <v>3299867937</v>
+        <v>3298802999</v>
       </c>
       <c r="G31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>735176292</v>
+        <v>210126645</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>7.54</v>
       </c>
       <c r="J31" t="n">
-        <v>0.999711</v>
+        <v>7.27</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.533269023941e-05</v>
+        <v>0.08415</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.00253</v>
+        <v>1.08225</v>
       </c>
       <c r="M31" t="n">
-        <v>3300126794.724858</v>
+        <v>442507221.2454377</v>
       </c>
       <c r="N31" t="n">
-        <v>3300126794.724858</v>
+        <v>469175921.2454377</v>
       </c>
       <c r="O31" t="n">
-        <v>1.65</v>
+        <v>144.96</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>45686.67436342593</v>
+        <v>44521.26314814815</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.001782065399377766</v>
+        <v>0.00174298909972572</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>avalanche-2</t>
+          <t>global-dollar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>avax</t>
+          <t>usdg</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Global Dollar</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>7.33</v>
+        <v>0.999893</v>
       </c>
       <c r="F32" t="n">
-        <v>3244317382</v>
+        <v>3295066818</v>
       </c>
       <c r="G32" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>154038480</v>
+        <v>1120940203</v>
       </c>
       <c r="I32" t="n">
-        <v>7.46</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>7.28</v>
+        <v>0.999695</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.1091593768955574</v>
+        <v>-7.908955085512e-06</v>
       </c>
       <c r="L32" t="n">
-        <v>-1.46725</v>
+        <v>-0.00122</v>
       </c>
       <c r="M32" t="n">
-        <v>442498936.567694</v>
+        <v>3295411793.224418</v>
       </c>
       <c r="N32" t="n">
-        <v>469167636.567694</v>
+        <v>3295411793.224418</v>
       </c>
       <c r="O32" t="n">
-        <v>144.96</v>
+        <v>1.65</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>44521.26314814815</v>
+        <v>45686.67436342593</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001745999880398934</v>
+        <v>0.00174061455464163</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>shiba-inu</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>shib</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Shiba Inu</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5.18e-06</v>
+        <v>2.4</v>
       </c>
       <c r="F33" t="n">
-        <v>3055112871</v>
+        <v>3133561597</v>
       </c>
       <c r="G33" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>52713505</v>
+        <v>258953884</v>
       </c>
       <c r="I33" t="n">
-        <v>5.31e-06</v>
+        <v>2.45</v>
       </c>
       <c r="J33" t="n">
-        <v>5.18e-06</v>
+        <v>2.28</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.19790131833e-07</v>
+        <v>0.107905</v>
       </c>
       <c r="L33" t="n">
-        <v>-2.25831</v>
+        <v>4.63364</v>
       </c>
       <c r="M33" t="n">
-        <v>589239233105565.5</v>
+        <v>1306297396</v>
       </c>
       <c r="N33" t="n">
-        <v>589496238721205.9</v>
+        <v>1306297390</v>
       </c>
       <c r="O33" t="n">
-        <v>8.616e-05</v>
+        <v>20.44</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>44496.82980324074</v>
+        <v>44577.59010416667</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R33" t="b">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001623161163803735</v>
+        <v>0.001637969252237828</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>shiba-inu</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>shib</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Shiba Inu</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2.3</v>
+        <v>5.25e-06</v>
       </c>
       <c r="F34" t="n">
-        <v>3000244069</v>
+        <v>3091601517</v>
       </c>
       <c r="G34" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>242432037</v>
+        <v>64690922</v>
       </c>
       <c r="I34" t="n">
-        <v>2.42</v>
+        <v>5.28e-06</v>
       </c>
       <c r="J34" t="n">
-        <v>2.28</v>
+        <v>5.12e-06</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.07010848625083321</v>
+        <v>3.9627e-08</v>
       </c>
       <c r="L34" t="n">
-        <v>-2.96103</v>
+        <v>0.72497</v>
       </c>
       <c r="M34" t="n">
-        <v>1306215857</v>
+        <v>589239233105565.5</v>
       </c>
       <c r="N34" t="n">
-        <v>1306215884</v>
+        <v>589496238721205.9</v>
       </c>
       <c r="O34" t="n">
-        <v>20.44</v>
+        <v>8.616e-05</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>44577.59010416667</v>
+        <v>44496.82980324074</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R34" t="b">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001587538264628799</v>
+        <v>0.001611301352130204</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.709546</v>
+        <v>0.723262</v>
       </c>
       <c r="F35" t="n">
-        <v>2906515077</v>
+        <v>2962996213</v>
       </c>
       <c r="G35" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>269646665</v>
+        <v>410097418</v>
       </c>
       <c r="I35" t="n">
-        <v>0.730719</v>
+        <v>0.729503</v>
       </c>
       <c r="J35" t="n">
-        <v>0.706657</v>
+        <v>0.694705</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.01642906225733354</v>
+        <v>0.01047564</v>
       </c>
       <c r="L35" t="n">
-        <v>-2.26303</v>
+        <v>1.42339</v>
       </c>
       <c r="M35" t="n">
         <v>4096537146.540959</v>
@@ -2786,19 +2786,19 @@
         <v>45661.62243055556</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001526685861986868</v>
+        <v>0.001529565726259552</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2817,34 +2817,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.058267</v>
+        <v>0.058793</v>
       </c>
       <c r="F36" t="n">
-        <v>2828956293</v>
+        <v>2854726058</v>
       </c>
       <c r="G36" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>6834493</v>
+        <v>6464607</v>
       </c>
       <c r="I36" t="n">
-        <v>0.060711</v>
+        <v>0.060149</v>
       </c>
       <c r="J36" t="n">
-        <v>0.058001</v>
+        <v>0.057043</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.7873520683317e-05</v>
+        <v>0.0010674</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.03067</v>
+        <v>1.82224</v>
       </c>
       <c r="M36" t="n">
-        <v>48552181317.88692</v>
+        <v>48554394464.2072</v>
       </c>
       <c r="N36" t="n">
-        <v>98918860079.80734</v>
+        <v>98921008561.1628</v>
       </c>
       <c r="O36" t="n">
         <v>0.891544</v>
@@ -2853,19 +2853,19 @@
         <v>44523.66666666666</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001476331769281096</v>
+        <v>0.001460754187335485</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2884,34 +2884,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.999763</v>
+        <v>0.999815</v>
       </c>
       <c r="F37" t="n">
-        <v>2785072340</v>
+        <v>2769193648</v>
       </c>
       <c r="G37" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>27670088</v>
+        <v>45935786</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0.999867</v>
       </c>
       <c r="J37" t="n">
-        <v>0.999674</v>
+        <v>0.999611</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.113755925066e-05</v>
+        <v>3.682e-05</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.00311</v>
+        <v>0.00343</v>
       </c>
       <c r="M37" t="n">
-        <v>2785819367.950104</v>
+        <v>2769773922.446399</v>
       </c>
       <c r="N37" t="n">
-        <v>2785819367.950103</v>
+        <v>2769776124.406399</v>
       </c>
       <c r="O37" t="n">
         <v>1.021</v>
@@ -2920,19 +2920,19 @@
         <v>45222.61454861111</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001447840649079189</v>
+        <v>0.001406393715052202</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2957,7 +2957,7 @@
         <v>2750834099</v>
       </c>
       <c r="G38" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2969,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>1.11e-16</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -2987,19 +2987,19 @@
         <v>45699.87511574074</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R38" t="b">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001425611889517969</v>
+        <v>0.001394725228749196</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3018,31 +3018,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4346.32</v>
+        <v>4294.27</v>
       </c>
       <c r="F39" t="n">
-        <v>2663435399</v>
+        <v>2674779549</v>
       </c>
       <c r="G39" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>70881608</v>
+        <v>224100656</v>
       </c>
       <c r="I39" t="n">
-        <v>4352.55</v>
+        <v>4353.59</v>
       </c>
       <c r="J39" t="n">
-        <v>4343.6</v>
+        <v>4259.22</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.693088852525761</v>
+        <v>-51.30744412156491</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.03894</v>
+        <v>-1.19023</v>
       </c>
       <c r="M39" t="n">
-        <v>612823.6595320001</v>
+        <v>622823.6595320001</v>
       </c>
       <c r="N39" t="n">
         <v>707747.089</v>
@@ -3054,220 +3054,220 @@
         <v>46050.66666666666</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001368869351597777</v>
+        <v>0.001346388449073602</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>hashnote-usyc</t>
+          <t>bittensor</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>usyc</t>
+          <t>tao</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Circle USYC</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1.14</v>
+        <v>233.18</v>
       </c>
       <c r="F40" t="n">
-        <v>2605383630</v>
+        <v>2644200474</v>
       </c>
       <c r="G40" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>156673045</v>
       </c>
       <c r="I40" t="n">
-        <v>1.14</v>
+        <v>238.03</v>
       </c>
       <c r="J40" t="n">
-        <v>1.14</v>
+        <v>229.94</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>-0.7483804272891348</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>-0.3765</v>
       </c>
       <c r="M40" t="n">
-        <v>2291144643.386653</v>
+        <v>11339645.9251</v>
       </c>
       <c r="N40" t="n">
-        <v>2291144643.386653</v>
+        <v>21000000</v>
       </c>
       <c r="O40" t="n">
-        <v>1.14</v>
+        <v>757.6</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>46276.53819444445</v>
+        <v>45358.44833333333</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001331179949995503</v>
+        <v>0.001326953793146265</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>memecore</t>
+          <t>hashnote-usyc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>usyc</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MemeCore</t>
+          <t>Circle USYC</t>
         </is>
       </c>
       <c r="E41" t="n">
         <v>1.14</v>
       </c>
       <c r="F41" t="n">
-        <v>2597946723</v>
+        <v>2605584295</v>
       </c>
       <c r="G41" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H41" t="n">
-        <v>1076531</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="J41" t="n">
         <v>1.14</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.02934800996583409</v>
+        <v>7.625e-05</v>
       </c>
       <c r="L41" t="n">
-        <v>-2.50279</v>
+        <v>0.00671</v>
       </c>
       <c r="M41" t="n">
-        <v>2272321208.767787</v>
+        <v>2291167466.910423</v>
       </c>
       <c r="N41" t="n">
-        <v>5413711055.275012</v>
+        <v>2291167466.910423</v>
       </c>
       <c r="O41" t="n">
-        <v>5.64</v>
+        <v>1.14</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>46205.17638888889</v>
+        <v>46279.50347222222</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001326351629008389</v>
+        <v>0.001302411122967606</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ripple-usd</t>
+          <t>memecore</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>rlusd</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ripple USD</t>
+          <t>MemeCore</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.999949</v>
+        <v>1.093</v>
       </c>
       <c r="F42" t="n">
-        <v>2422692219</v>
+        <v>2479136714</v>
       </c>
       <c r="G42" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H42" t="n">
-        <v>64123176</v>
+        <v>2141286</v>
       </c>
       <c r="I42" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-0.04632907166194666</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-4.04612</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2272737750.694923</v>
+      </c>
+      <c r="N42" t="n">
+        <v>5414112177.517013</v>
+      </c>
+      <c r="O42" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="P42" s="1" t="n">
+        <v>46205.17638888889</v>
+      </c>
+      <c r="Q42" s="1" t="n">
+        <v>46279.65787037037</v>
+      </c>
+      <c r="R42" t="b">
         <v>1</v>
       </c>
-      <c r="J42" t="n">
-        <v>0.999815</v>
-      </c>
-      <c r="K42" t="n">
-        <v>2.006e-05</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.00201</v>
-      </c>
-      <c r="M42" t="n">
-        <v>2422848190.107193</v>
-      </c>
-      <c r="N42" t="n">
-        <v>2422848190.107193</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1.073</v>
-      </c>
-      <c r="P42" s="1" t="n">
-        <v>45652.11518518518</v>
-      </c>
-      <c r="Q42" s="1" t="n">
-        <v>46278.57106481482</v>
-      </c>
-      <c r="R42" t="b">
-        <v>0</v>
-      </c>
       <c r="S42" t="n">
-        <v>0.00121256978398204</v>
+        <v>0.001222046846756533</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3286,28 +3286,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>112.5</v>
+        <v>113.8</v>
       </c>
       <c r="F43" t="n">
-        <v>2362420688</v>
+        <v>2389910882</v>
       </c>
       <c r="G43" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>14950178</v>
+        <v>14273148</v>
       </c>
       <c r="I43" t="n">
-        <v>114.72</v>
+        <v>114.32</v>
       </c>
       <c r="J43" t="n">
-        <v>112.66</v>
+        <v>111.76</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.404209937858923</v>
+        <v>0.9231470000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>-1.23285</v>
+        <v>0.82967</v>
       </c>
       <c r="M43" t="n">
         <v>21000000</v>
@@ -3322,86 +3322,86 @@
         <v>45934.66666666666</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001173439229027841</v>
+        <v>0.001165339005046135</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>bittensor</t>
+          <t>ripple-usd</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>tao</t>
+          <t>rlusd</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>Ripple USD</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>233.9</v>
+        <v>0.999982</v>
       </c>
       <c r="F44" t="n">
-        <v>2244685454</v>
+        <v>2382381916</v>
       </c>
       <c r="G44" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>107860464</v>
+        <v>158954239</v>
       </c>
       <c r="I44" t="n">
-        <v>239.13</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>231.12</v>
+        <v>0.999817</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.7518508925017215</v>
+        <v>4.732e-05</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.32041</v>
+        <v>0.00722</v>
       </c>
       <c r="M44" t="n">
-        <v>9597491</v>
+        <v>2382406353.107468</v>
       </c>
       <c r="N44" t="n">
-        <v>21000000</v>
+        <v>2382406353.107467</v>
       </c>
       <c r="O44" t="n">
-        <v>757.6</v>
+        <v>1.073</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>45358.44833333333</v>
+        <v>45652.11518518518</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001097001067135414</v>
+        <v>0.001160553939974722</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3420,16 +3420,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="F45" t="n">
-        <v>2225069373</v>
+        <v>2231380367</v>
       </c>
       <c r="G45" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H45" t="n">
-        <v>801724</v>
+        <v>726746</v>
       </c>
       <c r="I45" t="n">
         <v>1.15</v>
@@ -3438,16 +3438,16 @@
         <v>1.14</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.000379577747015247</v>
+        <v>0.00141936</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.03315</v>
+        <v>0.21073</v>
       </c>
       <c r="M45" t="n">
-        <v>1944368850.693475</v>
+        <v>1947116570.988323</v>
       </c>
       <c r="N45" t="n">
-        <v>1944368850.693474</v>
+        <v>1947116570.988323</v>
       </c>
       <c r="O45" t="n">
         <v>1.26</v>
@@ -3456,19 +3456,19 @@
         <v>45377.89175925926</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.001084265566264257</v>
+        <v>0.001064584289182148</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3487,31 +3487,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>126.33</v>
+        <v>126.12</v>
       </c>
       <c r="F46" t="n">
-        <v>1949033898</v>
+        <v>1945834087</v>
       </c>
       <c r="G46" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>174977167</v>
+        <v>185533365</v>
       </c>
       <c r="I46" t="n">
-        <v>128.03</v>
+        <v>127.47</v>
       </c>
       <c r="J46" t="n">
-        <v>123.73</v>
+        <v>123.98</v>
       </c>
       <c r="K46" t="n">
-        <v>0.131101</v>
+        <v>0.234178</v>
       </c>
       <c r="L46" t="n">
-        <v>0.10388</v>
+        <v>0.18402</v>
       </c>
       <c r="M46" t="n">
-        <v>15427580.14666632</v>
+        <v>15427704.87209198</v>
       </c>
       <c r="N46" t="n">
         <v>16000000</v>
@@ -3523,86 +3523,86 @@
         <v>44334.55554398148</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0009050529074088546</v>
+        <v>0.0008831041854467962</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>pax-gold</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>paxg</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>PAX Gold</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4350.54</v>
+        <v>0.715265</v>
       </c>
       <c r="F47" t="n">
-        <v>1883372570</v>
+        <v>1936792837</v>
       </c>
       <c r="G47" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>38849396</v>
+        <v>38053504</v>
       </c>
       <c r="I47" t="n">
-        <v>4358.06</v>
+        <v>0.782873</v>
       </c>
       <c r="J47" t="n">
-        <v>4349.36</v>
+        <v>0.550861</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.154654329549885</v>
+        <v>0.02832656</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.07246</v>
+        <v>4.56831</v>
       </c>
       <c r="M47" t="n">
-        <v>432906.598539</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N47" t="n">
-        <v>432906.598539</v>
+        <v>10000000000</v>
       </c>
       <c r="O47" t="n">
-        <v>5619.09</v>
+        <v>0.782873</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>46050.93814814815</v>
+        <v>46279.42037037037</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0008624230926183583</v>
+        <v>0.0008773579821066677</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3621,28 +3621,28 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.694321</v>
+        <v>0.697187</v>
       </c>
       <c r="F48" t="n">
-        <v>1877224626</v>
+        <v>1884268718</v>
       </c>
       <c r="G48" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>90143110</v>
+        <v>82042332</v>
       </c>
       <c r="I48" t="n">
-        <v>0.698188</v>
+        <v>0.704145</v>
       </c>
       <c r="J48" t="n">
-        <v>0.683132</v>
+        <v>0.681949</v>
       </c>
       <c r="K48" t="n">
-        <v>0.00968485</v>
+        <v>-8.60094681809e-07</v>
       </c>
       <c r="L48" t="n">
-        <v>1.4146</v>
+        <v>-0.01662</v>
       </c>
       <c r="M48" t="n">
         <v>2704071066.799731</v>
@@ -3657,19 +3657,19 @@
         <v>45924.13766203704</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0008584316151072372</v>
+        <v>0.0008439760638945729</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3688,28 +3688,28 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.564358</v>
+        <v>0.567269</v>
       </c>
       <c r="F49" t="n">
-        <v>1863602194</v>
+        <v>1873306634</v>
       </c>
       <c r="G49" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>23688481</v>
+        <v>24085849</v>
       </c>
       <c r="I49" t="n">
-        <v>0.574505</v>
+        <v>0.572306</v>
       </c>
       <c r="J49" t="n">
-        <v>0.550594</v>
+        <v>0.555812</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.009028353259263433</v>
+        <v>0.00040073</v>
       </c>
       <c r="L49" t="n">
-        <v>-1.57457</v>
+        <v>0.02702</v>
       </c>
       <c r="M49" t="n">
         <v>3302294382.53684</v>
@@ -3724,153 +3724,153 @@
         <v>45938.71164351852</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R49" t="b">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0008495874176040108</v>
+        <v>0.0008370090666656977</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>world-liberty-financial</t>
+          <t>pax-gold</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>wlfi</t>
+          <t>paxg</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>World Liberty Financial</t>
+          <t>PAX Gold</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.0574</v>
+        <v>4299.21</v>
       </c>
       <c r="F50" t="n">
-        <v>1823894559</v>
+        <v>1861295293</v>
       </c>
       <c r="G50" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>68574804</v>
+        <v>121881672</v>
       </c>
       <c r="I50" t="n">
-        <v>0.06113</v>
+        <v>4357.16</v>
       </c>
       <c r="J50" t="n">
-        <v>0.056678</v>
+        <v>4266.85</v>
       </c>
       <c r="K50" t="n">
-        <v>0.00049218</v>
+        <v>-48.52037737387218</v>
       </c>
       <c r="L50" t="n">
-        <v>0.86486</v>
+        <v>-1.09767</v>
       </c>
       <c r="M50" t="n">
-        <v>31777223322</v>
+        <v>432905.428702</v>
       </c>
       <c r="N50" t="n">
-        <v>100000000000</v>
+        <v>432906.598539</v>
       </c>
       <c r="O50" t="n">
-        <v>0.331336</v>
+        <v>5619.09</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>45901.18065972222</v>
+        <v>46050.93814814815</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R50" t="b">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0008238077208269577</v>
+        <v>0.000829375209867841</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>world-liberty-financial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>wlfi</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.667876</v>
+        <v>0.05717</v>
       </c>
       <c r="F51" t="n">
-        <v>1807336147</v>
+        <v>1816457741</v>
       </c>
       <c r="G51" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>30527053</v>
+        <v>32945175</v>
       </c>
       <c r="I51" t="n">
-        <v>0.728917</v>
+        <v>0.058201</v>
       </c>
       <c r="J51" t="n">
-        <v>0.504794</v>
+        <v>0.056363</v>
       </c>
       <c r="K51" t="n">
-        <v>0.119042</v>
+        <v>0.00019241</v>
       </c>
       <c r="L51" t="n">
-        <v>21.69009</v>
+        <v>0.32666</v>
       </c>
       <c r="M51" t="n">
-        <v>2708142280.000001</v>
+        <v>31777274001</v>
       </c>
       <c r="N51" t="n">
-        <v>10000000000</v>
+        <v>100000000000</v>
       </c>
       <c r="O51" t="n">
-        <v>0.745279</v>
+        <v>0.331336</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>46253.4</v>
+        <v>45901.18065972222</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0008130573741878411</v>
+        <v>0.000800878520685971</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3889,34 +3889,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1.006</v>
+        <v>1.011</v>
       </c>
       <c r="F52" t="n">
-        <v>1713254528</v>
+        <v>1720896263</v>
       </c>
       <c r="G52" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>103954483</v>
+        <v>125697957</v>
       </c>
       <c r="I52" t="n">
-        <v>1.043</v>
+        <v>1.027</v>
       </c>
       <c r="J52" t="n">
-        <v>0.996648</v>
+        <v>0.997945</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.03214671140746428</v>
+        <v>-0.008389516963648314</v>
       </c>
       <c r="L52" t="n">
-        <v>-3.0955</v>
+        <v>-0.88369</v>
       </c>
       <c r="M52" t="n">
-        <v>1702555180.263461</v>
+        <v>1702723763.976507</v>
       </c>
       <c r="N52" t="n">
-        <v>1702581303.296338</v>
+        <v>1702742182.32487</v>
       </c>
       <c r="O52" t="n">
         <v>54.98</v>
@@ -3925,19 +3925,19 @@
         <v>44504.25704861111</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R52" t="b">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0007519760327754342</v>
+        <v>0.0007401440333007966</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3956,28 +3956,28 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.343808</v>
+        <v>0.351009</v>
       </c>
       <c r="F53" t="n">
-        <v>1674061222</v>
+        <v>1709601855</v>
       </c>
       <c r="G53" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>53093523</v>
+        <v>82945240</v>
       </c>
       <c r="I53" t="n">
-        <v>0.353277</v>
+        <v>0.358278</v>
       </c>
       <c r="J53" t="n">
-        <v>0.341176</v>
+        <v>0.339718</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.006722452036544091</v>
+        <v>0.00591865</v>
       </c>
       <c r="L53" t="n">
-        <v>-1.91779</v>
+        <v>1.65097</v>
       </c>
       <c r="M53" t="n">
         <v>4869330647</v>
@@ -3992,354 +3992,354 @@
         <v>45641.69166666667</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R53" t="b">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0007265302578162794</v>
+        <v>0.0007329658261973127</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>htx-dao</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>htx</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>HTX DAO</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1.7e-06</v>
+        <v>0.00361277</v>
       </c>
       <c r="F54" t="n">
-        <v>1529057947</v>
+        <v>1693432142</v>
       </c>
       <c r="G54" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>43518659</v>
+        <v>103892831</v>
       </c>
       <c r="I54" t="n">
-        <v>1.71e-06</v>
+        <v>0.0036761</v>
       </c>
       <c r="J54" t="n">
-        <v>1.69e-06</v>
+        <v>0.00346727</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.813195854e-09</v>
+        <v>-4.0926702022416e-05</v>
       </c>
       <c r="L54" t="n">
-        <v>-0.1064</v>
+        <v>-1.17425</v>
       </c>
       <c r="M54" t="n">
-        <v>898232728634017.2</v>
+        <v>468637942893.683</v>
       </c>
       <c r="N54" t="n">
-        <v>898232728634017.2</v>
+        <v>834149763148.9541</v>
       </c>
       <c r="O54" t="n">
-        <v>3.75e-06</v>
+        <v>0.00881908</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>45629.67800925926</v>
+        <v>45914.36296296296</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R54" t="b">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.000632388653533384</v>
+        <v>0.0007226890991021081</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>USDD</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.00368693</v>
+        <v>0.999225</v>
       </c>
       <c r="F55" t="n">
-        <v>1529168745</v>
+        <v>1529381392</v>
       </c>
       <c r="G55" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>188688626</v>
+        <v>2853415</v>
       </c>
       <c r="I55" t="n">
-        <v>0.00395184</v>
+        <v>0.99962</v>
       </c>
       <c r="J55" t="n">
-        <v>0.0035918</v>
+        <v>0.998611</v>
       </c>
       <c r="K55" t="n">
-        <v>8.375e-05</v>
+        <v>-0.00014378888773503</v>
       </c>
       <c r="L55" t="n">
-        <v>2.32424</v>
+        <v>0.02166</v>
       </c>
       <c r="M55" t="n">
-        <v>414815762056.5878</v>
+        <v>1530867781</v>
       </c>
       <c r="N55" t="n">
-        <v>834327582311.8589</v>
+        <v>1532088633</v>
       </c>
       <c r="O55" t="n">
-        <v>0.00881908</v>
+        <v>1.24</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>45914.36296296296</v>
+        <v>46212.39942129629</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R55" t="b">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0006324605877808783</v>
+        <v>0.0006184259753525633</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>htx-dao</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>htx</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>USDD</t>
+          <t>HTX DAO</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.998907</v>
+        <v>1.7e-06</v>
       </c>
       <c r="F56" t="n">
-        <v>1524004223</v>
+        <v>1525555129</v>
       </c>
       <c r="G56" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>2090791</v>
+        <v>105375559</v>
       </c>
       <c r="I56" t="n">
-        <v>0.999628</v>
+        <v>1.71e-06</v>
       </c>
       <c r="J56" t="n">
-        <v>0.9961680000000001</v>
+        <v>1.69e-06</v>
       </c>
       <c r="K56" t="n">
-        <v>0.00162806</v>
+        <v>-3.019953681e-09</v>
       </c>
       <c r="L56" t="n">
-        <v>0.16325</v>
+        <v>-0.1775</v>
       </c>
       <c r="M56" t="n">
-        <v>1525524624</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="N56" t="n">
-        <v>1525486098</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="O56" t="n">
-        <v>1.24</v>
+        <v>3.75e-06</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>46212.39942129629</v>
+        <v>45629.67800925926</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R56" t="b">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.00062910758498536</v>
+        <v>0.0006159941782856965</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>internet-computer</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>icp</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Morpho</t>
+          <t>Internet Computer</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2.17</v>
+        <v>2.73</v>
       </c>
       <c r="F57" t="n">
-        <v>1494721401</v>
+        <v>1522846678</v>
       </c>
       <c r="G57" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>15885684</v>
+        <v>46433404</v>
       </c>
       <c r="I57" t="n">
-        <v>2.29</v>
+        <v>2.85</v>
       </c>
       <c r="J57" t="n">
-        <v>2.16</v>
+        <v>2.71</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.1172328898001407</v>
+        <v>-0.04371069852076781</v>
       </c>
       <c r="L57" t="n">
-        <v>-5.12678</v>
+        <v>-1.63721</v>
       </c>
       <c r="M57" t="n">
-        <v>689038406.6772338</v>
+        <v>556821653.0008103</v>
       </c>
       <c r="N57" t="n">
-        <v>1000000000</v>
+        <v>556821653.0008103</v>
       </c>
       <c r="O57" t="n">
-        <v>4.17</v>
+        <v>700.65</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>45674.19883101852</v>
+        <v>44326.33741898148</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0006100960706522495</v>
+        <v>0.0006142728111978741</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>internet-computer</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>icp</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Internet Computer</t>
+          <t>Morpho</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2.67</v>
+        <v>2.18</v>
       </c>
       <c r="F58" t="n">
-        <v>1486990925</v>
+        <v>1504308793</v>
       </c>
       <c r="G58" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>25432475</v>
+        <v>15460300</v>
       </c>
       <c r="I58" t="n">
-        <v>2.77</v>
+        <v>2.24</v>
       </c>
       <c r="J58" t="n">
-        <v>2.64</v>
+        <v>2.14</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.09486369083001422</v>
+        <v>0.007838299999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>-3.42728</v>
+        <v>0.37484</v>
       </c>
       <c r="M58" t="n">
-        <v>556288332.0867959</v>
+        <v>689112006.7947352</v>
       </c>
       <c r="N58" t="n">
-        <v>556288442.1779287</v>
+        <v>1000000000</v>
       </c>
       <c r="O58" t="n">
-        <v>700.65</v>
+        <v>4.17</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>44326.33741898148</v>
+        <v>45674.19883101852</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0006050771535794425</v>
+        <v>0.0006024909827221747</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4358,31 +4358,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.061816</v>
+        <v>0.064161</v>
       </c>
       <c r="F59" t="n">
-        <v>1448383094</v>
+        <v>1503637857</v>
       </c>
       <c r="G59" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>7181124</v>
+        <v>11248975</v>
       </c>
       <c r="I59" t="n">
-        <v>0.06422600000000001</v>
+        <v>0.06504799999999999</v>
       </c>
       <c r="J59" t="n">
-        <v>0.061655</v>
+        <v>0.061748</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.00182546775971467</v>
+        <v>0.0015437</v>
       </c>
       <c r="L59" t="n">
-        <v>-2.86835</v>
+        <v>2.47851</v>
       </c>
       <c r="M59" t="n">
-        <v>23429540152.7714</v>
+        <v>23427652317.1642</v>
       </c>
       <c r="N59" t="n">
         <v>23459804203.60596</v>
@@ -4394,19 +4394,19 @@
         <v>45630.09302083333</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R59" t="b">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0005800114911092473</v>
+        <v>0.0006020645666088925</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4425,28 +4425,28 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3.4e-06</v>
+        <v>3.45e-06</v>
       </c>
       <c r="F60" t="n">
-        <v>1429580510</v>
+        <v>1451129135</v>
       </c>
       <c r="G60" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>140594078</v>
+        <v>170040252</v>
       </c>
       <c r="I60" t="n">
-        <v>3.48e-06</v>
+        <v>3.47e-06</v>
       </c>
       <c r="J60" t="n">
-        <v>3.38e-06</v>
+        <v>3.34e-06</v>
       </c>
       <c r="K60" t="n">
-        <v>1.2851e-08</v>
+        <v>4.1828e-08</v>
       </c>
       <c r="L60" t="n">
-        <v>0.37951</v>
+        <v>1.21699</v>
       </c>
       <c r="M60" t="n">
         <v>420690000000000</v>
@@ -4461,19 +4461,19 @@
         <v>45635.35457175926</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0005678041432240088</v>
+        <v>0.0005686924340229918</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4492,28 +4492,28 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.139191</v>
+        <v>0.141382</v>
       </c>
       <c r="F61" t="n">
-        <v>1405006118</v>
+        <v>1426794520</v>
       </c>
       <c r="G61" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>144723881</v>
+        <v>224795572</v>
       </c>
       <c r="I61" t="n">
-        <v>0.143815</v>
+        <v>0.143203</v>
       </c>
       <c r="J61" t="n">
-        <v>0.138364</v>
+        <v>0.135179</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.002546763812056457</v>
+        <v>0.00257779</v>
       </c>
       <c r="L61" t="n">
-        <v>-1.79681</v>
+        <v>1.79652</v>
       </c>
       <c r="M61" t="n">
         <v>10095312500</v>
@@ -4528,153 +4528,153 @@
         <v>45393.21892361111</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0005518495195290837</v>
+        <v>0.0005532264701359475</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>worldcoin-wld</t>
+          <t>usdgo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>wld</t>
+          <t>usdgo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Worldcoin</t>
+          <t>USDGO</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.389604</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>1399169269</v>
+        <v>1392029194</v>
       </c>
       <c r="G62" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>97023558</v>
+        <v>25560451</v>
       </c>
       <c r="I62" t="n">
-        <v>0.411451</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
-        <v>0.387357</v>
+        <v>0.999966</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.01096885046806378</v>
+        <v>7.287e-05</v>
       </c>
       <c r="L62" t="n">
-        <v>-2.73829</v>
+        <v>0.0092</v>
       </c>
       <c r="M62" t="n">
-        <v>3591409311.083124</v>
+        <v>1391792045.16</v>
       </c>
       <c r="N62" t="n">
-        <v>10000000000</v>
+        <v>1391792045.16</v>
       </c>
       <c r="O62" t="n">
-        <v>11.74</v>
+        <v>1.002</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>45360.67409722223</v>
+        <v>46092.00303240741</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005480600166449797</v>
+        <v>0.000531131225299022</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>usdgo</t>
+          <t>worldcoin-wld</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>usdgo</t>
+          <t>wld</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>USDGO</t>
+          <t>Worldcoin</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>0.383134</v>
       </c>
       <c r="F63" t="n">
-        <v>1383088021</v>
+        <v>1376538249</v>
       </c>
       <c r="G63" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>7212222</v>
+        <v>126323707</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0.396461</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>0.375987</v>
       </c>
       <c r="K63" t="n">
-        <v>-7.38700859193e-06</v>
+        <v>-0.009776990171701305</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.00074</v>
+        <v>-2.56148</v>
       </c>
       <c r="M63" t="n">
-        <v>1382792045.16</v>
+        <v>3592836116.582616</v>
       </c>
       <c r="N63" t="n">
-        <v>1382792045.16</v>
+        <v>10000000000</v>
       </c>
       <c r="O63" t="n">
-        <v>1.002</v>
+        <v>11.74</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>46092.00303240741</v>
+        <v>45360.67409722223</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.000537619462901686</v>
+        <v>0.0005212858919766666</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4693,28 +4693,28 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="F64" t="n">
-        <v>1341575645</v>
+        <v>1358673919</v>
       </c>
       <c r="G64" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>7205523</v>
+        <v>10471507</v>
       </c>
       <c r="I64" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="J64" t="n">
         <v>1.92</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.02997327612354672</v>
+        <v>-0.0009659930391829891</v>
       </c>
       <c r="L64" t="n">
-        <v>-1.53991</v>
+        <v>-0.09539</v>
       </c>
       <c r="M64" t="n">
         <v>699992029.6481038</v>
@@ -4729,19 +4729,19 @@
         <v>45653.15375</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R64" t="b">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0005106680600851995</v>
+        <v>0.0005099321441303891</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4760,28 +4760,28 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.996407</v>
+        <v>0.996299</v>
       </c>
       <c r="F65" t="n">
-        <v>1339686255</v>
+        <v>1339540722</v>
       </c>
       <c r="G65" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>490682</v>
+        <v>608010</v>
       </c>
       <c r="I65" t="n">
-        <v>0.99773</v>
+        <v>0.997239</v>
       </c>
       <c r="J65" t="n">
-        <v>0.9963689999999999</v>
+        <v>0.996238</v>
       </c>
       <c r="K65" t="n">
-        <v>0.00012986</v>
+        <v>-0.000211135080925851</v>
       </c>
       <c r="L65" t="n">
-        <v>0.01303</v>
+        <v>-0.0215</v>
       </c>
       <c r="M65" t="n">
         <v>1344517433.482414</v>
@@ -4796,19 +4796,19 @@
         <v>45785.55951388889</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0005094413967169683</v>
+        <v>0.0004977719626832733</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="F66" t="n">
-        <v>1335525954</v>
+        <v>1328135582</v>
       </c>
       <c r="G66" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -4845,10 +4845,10 @@
         <v>1.17</v>
       </c>
       <c r="K66" t="n">
-        <v>0.00101211</v>
+        <v>-0.006505837321536312</v>
       </c>
       <c r="L66" t="n">
-        <v>0.08616</v>
+        <v>-0.55337</v>
       </c>
       <c r="M66" t="n">
         <v>1135960146.90006</v>
@@ -4863,19 +4863,19 @@
         <v>46255.48263888889</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0005067403721336288</v>
+        <v>0.0004905233794052275</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4894,28 +4894,28 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.999269</v>
+        <v>0.999593</v>
       </c>
       <c r="F67" t="n">
-        <v>1319035606</v>
+        <v>1319462832</v>
       </c>
       <c r="G67" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H67" t="n">
-        <v>2360558</v>
+        <v>4321338</v>
       </c>
       <c r="I67" t="n">
-        <v>0.999847</v>
+        <v>0.999707</v>
       </c>
       <c r="J67" t="n">
-        <v>0.9992220000000001</v>
+        <v>0.999053</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.000348682830913716</v>
+        <v>0.00041378</v>
       </c>
       <c r="L67" t="n">
-        <v>-0.03488</v>
+        <v>0.04109</v>
       </c>
       <c r="M67" t="n">
         <v>1320000000</v>
@@ -4930,19 +4930,19 @@
         <v>45940.56990740741</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0004960342152147369</v>
+        <v>0.000485011377744163</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4961,34 +4961,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.999343</v>
+        <v>0.999765</v>
       </c>
       <c r="F68" t="n">
-        <v>1285134272</v>
+        <v>1314958390</v>
       </c>
       <c r="G68" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>84854418</v>
+        <v>174732986</v>
       </c>
       <c r="I68" t="n">
-        <v>0.999593</v>
+        <v>0.999831</v>
       </c>
       <c r="J68" t="n">
-        <v>0.999094</v>
+        <v>0.999084</v>
       </c>
       <c r="K68" t="n">
-        <v>6.834999999999999e-05</v>
+        <v>0.0004305</v>
       </c>
       <c r="L68" t="n">
-        <v>0.00684</v>
+        <v>0.04722</v>
       </c>
       <c r="M68" t="n">
-        <v>1286000007.8</v>
+        <v>1315244007.8</v>
       </c>
       <c r="N68" t="n">
-        <v>1286000007.8</v>
+        <v>1315244007.8</v>
       </c>
       <c r="O68" t="n">
         <v>1.008</v>
@@ -4997,19 +4997,19 @@
         <v>46058.54591435185</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0004740241884060992</v>
+        <v>0.0004821485612458011</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5028,34 +5028,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>7.52</v>
+        <v>7.61</v>
       </c>
       <c r="F69" t="n">
-        <v>1189953494</v>
+        <v>1203865987</v>
       </c>
       <c r="G69" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>40949275</v>
+        <v>49212991</v>
       </c>
       <c r="I69" t="n">
-        <v>7.78</v>
+        <v>7.69</v>
       </c>
       <c r="J69" t="n">
-        <v>7.48</v>
+        <v>7.4</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.2376247766535613</v>
+        <v>0.02530351</v>
       </c>
       <c r="L69" t="n">
-        <v>-3.06131</v>
+        <v>0.27311</v>
       </c>
       <c r="M69" t="n">
-        <v>158156878.9004274</v>
+        <v>158165250.3413957</v>
       </c>
       <c r="N69" t="n">
-        <v>158157253.7868274</v>
+        <v>158165720.1525957</v>
       </c>
       <c r="O69" t="n">
         <v>167.09</v>
@@ -5064,287 +5064,287 @@
         <v>44322.44053240741</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0004122292314452022</v>
+        <v>0.0004115433310860895</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>pi-network</t>
+          <t>lighter</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>pi</t>
+          <t>lit</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Pi Network</t>
+          <t>Lighter</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.09778199999999999</v>
+        <v>4.39</v>
       </c>
       <c r="F70" t="n">
-        <v>1094472076</v>
+        <v>1097273231</v>
       </c>
       <c r="G70" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>5940870</v>
+        <v>94634914</v>
       </c>
       <c r="I70" t="n">
-        <v>0.098353</v>
+        <v>4.69</v>
       </c>
       <c r="J70" t="n">
-        <v>0.095195</v>
+        <v>4.09</v>
       </c>
       <c r="K70" t="n">
-        <v>0.00233842</v>
+        <v>0.304136</v>
       </c>
       <c r="L70" t="n">
-        <v>2.45006</v>
+        <v>7.4937</v>
       </c>
       <c r="M70" t="n">
-        <v>11193060990.054</v>
+        <v>250000000</v>
       </c>
       <c r="N70" t="n">
-        <v>17220093830.8523</v>
+        <v>1000000000</v>
       </c>
       <c r="O70" t="n">
-        <v>2.99</v>
+        <v>7.86</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>45714.36184027778</v>
+        <v>46021.04538194444</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0003502390876382728</v>
+        <v>0.0003437978699429186</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>venice-token</t>
+          <t>pi-network</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>vvv</t>
+          <t>pi</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Venice Token</t>
+          <t>Pi Network</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>21.99</v>
+        <v>0.097383</v>
       </c>
       <c r="F71" t="n">
-        <v>1051744869</v>
+        <v>1089901574</v>
       </c>
       <c r="G71" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>31662360</v>
+        <v>4589866</v>
       </c>
       <c r="I71" t="n">
-        <v>24.64</v>
+        <v>0.098366</v>
       </c>
       <c r="J71" t="n">
-        <v>22.11</v>
+        <v>0.09639</v>
       </c>
       <c r="K71" t="n">
-        <v>-1.071007754172321</v>
+        <v>-7.499999479311499e-05</v>
       </c>
       <c r="L71" t="n">
-        <v>-4.64441</v>
+        <v>-0.05854</v>
       </c>
       <c r="M71" t="n">
-        <v>47949972.85733457</v>
+        <v>11193062149.394</v>
       </c>
       <c r="N71" t="n">
-        <v>81000288.01647621</v>
+        <v>17220095483.28307</v>
       </c>
       <c r="O71" t="n">
-        <v>29.19</v>
+        <v>2.99</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>46274.32083333333</v>
+        <v>45714.36184027778</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0003224989706408646</v>
+        <v>0.0003391127832485255</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>polygon-ecosystem-token</t>
+          <t>venice-token</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>pol</t>
+          <t>vvv</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>POL (ex-MATIC)</t>
+          <t>Venice Token</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.096285</v>
+        <v>22.14</v>
       </c>
       <c r="F72" t="n">
-        <v>1031576270</v>
+        <v>1062019823</v>
       </c>
       <c r="G72" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>42931958</v>
+        <v>34807612</v>
       </c>
       <c r="I72" t="n">
-        <v>0.097431</v>
+        <v>23.28</v>
       </c>
       <c r="J72" t="n">
-        <v>0.09479</v>
+        <v>21.22</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.000352092608966403</v>
+        <v>0.580173</v>
       </c>
       <c r="L72" t="n">
-        <v>-0.36434</v>
+        <v>2.65269</v>
       </c>
       <c r="M72" t="n">
-        <v>10713522708.58917</v>
+        <v>47963017.79499942</v>
       </c>
       <c r="N72" t="n">
-        <v>10713522708.58917</v>
+        <v>81007441.11135192</v>
       </c>
       <c r="O72" t="n">
-        <v>1.29</v>
+        <v>29.19</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>45364.45493055556</v>
+        <v>46274.32083333333</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0003094047542102467</v>
+        <v>0.0003213924225987449</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>lighter</t>
+          <t>polygon-ecosystem-token</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>lit</t>
+          <t>pol</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Lighter</t>
+          <t>POL (ex-MATIC)</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4.06</v>
+        <v>0.097994</v>
       </c>
       <c r="F73" t="n">
-        <v>1015247730</v>
+        <v>1049927178</v>
       </c>
       <c r="G73" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>48556691</v>
+        <v>59452758</v>
       </c>
       <c r="I73" t="n">
-        <v>4.36</v>
+        <v>0.09861499999999999</v>
       </c>
       <c r="J73" t="n">
-        <v>4.07</v>
+        <v>0.095473</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.2888899709572943</v>
+        <v>0.00083642</v>
       </c>
       <c r="L73" t="n">
-        <v>-6.63943</v>
+        <v>0.8908199999999999</v>
       </c>
       <c r="M73" t="n">
-        <v>250000000</v>
+        <v>10714103973.39043</v>
       </c>
       <c r="N73" t="n">
-        <v>1000000000</v>
+        <v>10714103973.39043</v>
       </c>
       <c r="O73" t="n">
-        <v>7.86</v>
+        <v>1.29</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>46021.04538194444</v>
+        <v>45364.45493055556</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.000298803649157982</v>
+        <v>0.0003137068927118391</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5363,34 +5363,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F74" t="n">
-        <v>980902454</v>
+        <v>992009996</v>
       </c>
       <c r="G74" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>1924570</v>
+        <v>3232039</v>
       </c>
       <c r="I74" t="n">
-        <v>9.44</v>
+        <v>9.32</v>
       </c>
       <c r="J74" t="n">
-        <v>9.07</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.2252325919768072</v>
+        <v>0.104809</v>
       </c>
       <c r="L74" t="n">
-        <v>-2.39019</v>
+        <v>1.12118</v>
       </c>
       <c r="M74" t="n">
-        <v>106626638.5617626</v>
+        <v>106627878.3326154</v>
       </c>
       <c r="N74" t="n">
-        <v>118877870.6688078</v>
+        <v>118879110.4396606</v>
       </c>
       <c r="O74" t="n">
         <v>25.38</v>
@@ -5399,19 +5399,19 @@
         <v>45682.66666666666</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R74" t="b">
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0002765053984310324</v>
+        <v>0.0002768973912978503</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5436,7 +5436,7 @@
         <v>970348700</v>
       </c>
       <c r="G75" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -5466,86 +5466,86 @@
         <v>46273.93067129629</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R75" t="b">
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0002696535026185617</v>
+        <v>0.0002631304662126342</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>kaspa</t>
+          <t>kucoin-shares</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>kas</t>
+          <t>kcs</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Kaspa</t>
+          <t>KuCoin</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.03434143</v>
+        <v>6.97</v>
       </c>
       <c r="F76" t="n">
-        <v>951162173</v>
+        <v>956628458</v>
       </c>
       <c r="G76" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>5171603</v>
+        <v>6421517</v>
       </c>
       <c r="I76" t="n">
-        <v>0.03558984</v>
+        <v>7.02</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03415747</v>
+        <v>6.76</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.000979915992404469</v>
+        <v>0.205323</v>
       </c>
       <c r="L76" t="n">
-        <v>-2.77429</v>
+        <v>2.99787</v>
       </c>
       <c r="M76" t="n">
-        <v>27697431694.91903</v>
+        <v>137155021.2773955</v>
       </c>
       <c r="N76" t="n">
-        <v>27697985160.55182</v>
+        <v>142155021.2773955</v>
       </c>
       <c r="O76" t="n">
-        <v>0.207411</v>
+        <v>28.83</v>
       </c>
       <c r="P76" s="1" t="n">
-        <v>45504.69498842592</v>
+        <v>44531.29832175926</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R76" t="b">
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0002571968844325443</v>
+        <v>0.0002544105104092032</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5564,28 +5564,28 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>64.09</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="F77" t="n">
-        <v>933028720</v>
+        <v>939384952</v>
       </c>
       <c r="G77" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>4413297</v>
+        <v>6565185</v>
       </c>
       <c r="I77" t="n">
-        <v>64.48999999999999</v>
+        <v>65.56</v>
       </c>
       <c r="J77" t="n">
-        <v>63.45</v>
+        <v>62.27</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.3508712021686478</v>
+        <v>0.534498</v>
       </c>
       <c r="L77" t="n">
-        <v>-0.54451</v>
+        <v>0.68503</v>
       </c>
       <c r="M77" t="n">
         <v>14544176.16408117</v>
@@ -5600,1091 +5600,1091 @@
         <v>44450.05208333334</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R77" t="b">
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002454239616719482</v>
+        <v>0.0002434513297900715</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>kucoin-shares</t>
+          <t>just</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>kcs</t>
+          <t>jst</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>KuCoin</t>
+          <t>JUST</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6.8</v>
+        <v>0.113516</v>
       </c>
       <c r="F78" t="n">
-        <v>932317322</v>
+        <v>930049450</v>
       </c>
       <c r="G78" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>1750241</v>
+        <v>20636631</v>
       </c>
       <c r="I78" t="n">
-        <v>6.92</v>
+        <v>0.114356</v>
       </c>
       <c r="J78" t="n">
-        <v>6.8</v>
+        <v>0.112356</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.1079685940489261</v>
+        <v>0.00127463</v>
       </c>
       <c r="L78" t="n">
-        <v>-1.56362</v>
+        <v>1.1539</v>
       </c>
       <c r="M78" t="n">
-        <v>137155021.2773955</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="N78" t="n">
-        <v>142155021.2773955</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="O78" t="n">
-        <v>28.83</v>
+        <v>0.193254</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>44531.29832175926</v>
+        <v>44290.85721064815</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R78" t="b">
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002449620952140792</v>
+        <v>0.0002375181133903286</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>kaspa</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>arb</t>
+          <t>kas</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Arbitrum</t>
+          <t>Kaspa</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.136972</v>
+        <v>0.03346518</v>
       </c>
       <c r="F79" t="n">
-        <v>914447252</v>
+        <v>927160821</v>
       </c>
       <c r="G79" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>116956324</v>
+        <v>8749848</v>
       </c>
       <c r="I79" t="n">
-        <v>0.144581</v>
+        <v>0.03483587</v>
       </c>
       <c r="J79" t="n">
-        <v>0.13437</v>
+        <v>0.0330794</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.006598295908196022</v>
+        <v>-0.001137926064620966</v>
       </c>
       <c r="L79" t="n">
-        <v>-4.59585</v>
+        <v>-3.30486</v>
       </c>
       <c r="M79" t="n">
-        <v>6678075931</v>
+        <v>27698781826.54268</v>
       </c>
       <c r="N79" t="n">
-        <v>10000000000</v>
+        <v>27700079092.35108</v>
       </c>
       <c r="O79" t="n">
-        <v>2.39</v>
+        <v>0.207411</v>
       </c>
       <c r="P79" s="1" t="n">
-        <v>45303.18748842592</v>
+        <v>45504.69498842592</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002333601706475642</v>
+        <v>0.0002356822334391944</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>just</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>jst</t>
+          <t>arb</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>JUST</t>
+          <t>Arbitrum</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.111673</v>
+        <v>0.134902</v>
       </c>
       <c r="F80" t="n">
-        <v>914218317</v>
+        <v>900787139</v>
       </c>
       <c r="G80" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>20649316</v>
+        <v>125791092</v>
       </c>
       <c r="I80" t="n">
-        <v>0.112641</v>
+        <v>0.140932</v>
       </c>
       <c r="J80" t="n">
-        <v>0.108534</v>
+        <v>0.132467</v>
       </c>
       <c r="K80" t="n">
-        <v>0.00279723</v>
+        <v>-0.003846886341674016</v>
       </c>
       <c r="L80" t="n">
-        <v>2.56919</v>
+        <v>-2.8211</v>
       </c>
       <c r="M80" t="n">
-        <v>8188743036.341737</v>
+        <v>6678075931</v>
       </c>
       <c r="N80" t="n">
-        <v>8188743036.341737</v>
+        <v>10000000000</v>
       </c>
       <c r="O80" t="n">
-        <v>0.193254</v>
+        <v>2.39</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>44290.85721064815</v>
+        <v>45303.18748842592</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R80" t="b">
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002332115373965117</v>
+        <v>0.0002189203321976753</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>algorand</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>algo</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Spiko EU T-Bills Money Market Fund</t>
+          <t>Algorand</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1.23</v>
+        <v>0.095542</v>
       </c>
       <c r="F81" t="n">
-        <v>881204940</v>
+        <v>864028446</v>
       </c>
       <c r="G81" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>44342304</v>
       </c>
       <c r="I81" t="n">
-        <v>1.23</v>
+        <v>0.100768</v>
       </c>
       <c r="J81" t="n">
-        <v>1.23</v>
+        <v>0.093289</v>
       </c>
       <c r="K81" t="n">
-        <v>0.0010583</v>
+        <v>0.00188462</v>
       </c>
       <c r="L81" t="n">
-        <v>0.08616</v>
+        <v>2.01466</v>
       </c>
       <c r="M81" t="n">
-        <v>716808406.83022</v>
+        <v>9040751604.212919</v>
       </c>
       <c r="N81" t="n">
-        <v>716808406.83022</v>
+        <v>9041261887.915733</v>
       </c>
       <c r="O81" t="n">
-        <v>1.26</v>
+        <v>3.56</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>46049.54175925926</v>
+        <v>43636.28563657407</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R81" t="b">
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0002117780058188557</v>
+        <v>0.0001955581948278033</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>cosmos</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Cosmos Hub</t>
+          <t>Spiko EU T-Bills Money Market Fund</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1.59</v>
+        <v>1.22</v>
       </c>
       <c r="F82" t="n">
-        <v>844751116</v>
+        <v>830399404</v>
       </c>
       <c r="G82" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H82" t="n">
-        <v>36926557</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>1.64</v>
+        <v>1.23</v>
       </c>
       <c r="J82" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.04581604925677163</v>
+        <v>-0.006725431564868378</v>
       </c>
       <c r="L82" t="n">
-        <v>-2.79669</v>
+        <v>-0.5470699999999999</v>
       </c>
       <c r="M82" t="n">
-        <v>530462111.92831</v>
+        <v>679196801.73762</v>
       </c>
       <c r="N82" t="n">
-        <v>530478342.369727</v>
+        <v>679196801.73762</v>
       </c>
       <c r="O82" t="n">
-        <v>43.84</v>
+        <v>1.26</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>44458.66666666666</v>
+        <v>46049.54175925926</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R82" t="b">
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0001881108060703927</v>
+        <v>0.0001741851199249172</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>algorand</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>algo</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Algorand</t>
+          <t>NEXO</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.093178</v>
+        <v>0.824062</v>
       </c>
       <c r="F83" t="n">
-        <v>842206075</v>
+        <v>825837569</v>
       </c>
       <c r="G83" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>29529404</v>
+        <v>3324768</v>
       </c>
       <c r="I83" t="n">
-        <v>0.09484099999999999</v>
+        <v>0.83821</v>
       </c>
       <c r="J83" t="n">
-        <v>0.091696</v>
+        <v>0.820778</v>
       </c>
       <c r="K83" t="n">
-        <v>0.00045171</v>
+        <v>-0.002100593183993915</v>
       </c>
       <c r="L83" t="n">
-        <v>0.48715</v>
+        <v>-0.27099</v>
       </c>
       <c r="M83" t="n">
-        <v>9040075710.158276</v>
+        <v>1000000000</v>
       </c>
       <c r="N83" t="n">
-        <v>9040640286.975349</v>
+        <v>1000000000</v>
       </c>
       <c r="O83" t="n">
-        <v>3.56</v>
+        <v>4.07</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>43636.28563657407</v>
+        <v>44328.27623842593</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0001864584693027869</v>
+        <v>0.0001712858270711509</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>cosmos</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NEXO</t>
+          <t>Cosmos Hub</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.82647</v>
+        <v>1.55</v>
       </c>
       <c r="F84" t="n">
-        <v>826200915</v>
+        <v>820417685</v>
       </c>
       <c r="G84" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>3377653</v>
+        <v>40281610</v>
       </c>
       <c r="I84" t="n">
-        <v>0.836029</v>
+        <v>1.62</v>
       </c>
       <c r="J84" t="n">
-        <v>0.821452</v>
+        <v>1.53</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.004186455123449062</v>
+        <v>-0.05224919617736412</v>
       </c>
       <c r="L84" t="n">
-        <v>-0.50399</v>
+        <v>-3.27084</v>
       </c>
       <c r="M84" t="n">
-        <v>1000000000</v>
+        <v>530649765.65786</v>
       </c>
       <c r="N84" t="n">
-        <v>1000000000</v>
+        <v>530679280.827608</v>
       </c>
       <c r="O84" t="n">
-        <v>4.07</v>
+        <v>43.84</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>44328.27623842593</v>
+        <v>44458.66666666666</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R84" t="b">
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001760673147636607</v>
+        <v>0.0001678411976732348</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
+          <t>filecoin</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ustb</t>
+          <t>fil</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Invesco Short Duration US Government Securities Fund</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>11.21</v>
+        <v>0.983266</v>
       </c>
       <c r="F85" t="n">
-        <v>805323062</v>
+        <v>813568021</v>
       </c>
       <c r="G85" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>403575969</v>
       </c>
       <c r="I85" t="n">
-        <v>11.21</v>
+        <v>1.033</v>
       </c>
       <c r="J85" t="n">
-        <v>11.21</v>
+        <v>0.937837</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>0.02855161</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.2453</v>
       </c>
       <c r="M85" t="n">
-        <v>71851495.88542999</v>
+        <v>827813309</v>
       </c>
       <c r="N85" t="n">
-        <v>71851495.88542999</v>
+        <v>1957054313</v>
       </c>
       <c r="O85" t="n">
-        <v>11.21</v>
+        <v>236.84</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>46276.59027777778</v>
+        <v>44287.22894675926</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R85" t="b">
         <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001625126238409731</v>
+        <v>0.0001634878657605504</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jupiter-exchange-solana</t>
+          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>jup</t>
+          <t>ustb</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Invesco Short Duration US Government Securities Fund</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.233377</v>
+        <v>11.21</v>
       </c>
       <c r="F86" t="n">
-        <v>774708889</v>
+        <v>804620334</v>
       </c>
       <c r="G86" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H86" t="n">
-        <v>53816588</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0.248026</v>
+        <v>11.21</v>
       </c>
       <c r="J86" t="n">
-        <v>0.23225</v>
+        <v>11.21</v>
       </c>
       <c r="K86" t="n">
-        <v>-0.01130721160412404</v>
+        <v>0.001089</v>
       </c>
       <c r="L86" t="n">
-        <v>-4.62114</v>
+        <v>0.009719999999999999</v>
       </c>
       <c r="M86" t="n">
-        <v>3319369204.37</v>
+        <v>71781823.530606</v>
       </c>
       <c r="N86" t="n">
-        <v>6861487156.891288</v>
+        <v>67143413.755615</v>
       </c>
       <c r="O86" t="n">
-        <v>2</v>
+        <v>11.21</v>
       </c>
       <c r="P86" s="1" t="n">
-        <v>45322.29359953704</v>
+        <v>46279.58333333334</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001426367461408722</v>
+        <v>0.0001578011267669573</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>stable-2</t>
+          <t>jupiter-exchange-solana</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>jup</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>​​Stable</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.0283106</v>
+        <v>0.237187</v>
       </c>
       <c r="F87" t="n">
-        <v>744262459</v>
+        <v>788051591</v>
       </c>
       <c r="G87" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>7582550</v>
+        <v>54045582</v>
       </c>
       <c r="I87" t="n">
-        <v>0.02831921</v>
+        <v>0.239422</v>
       </c>
       <c r="J87" t="n">
-        <v>0.02753636</v>
+        <v>0.228991</v>
       </c>
       <c r="K87" t="n">
-        <v>0.0005849199999999999</v>
+        <v>0.00210852</v>
       </c>
       <c r="L87" t="n">
-        <v>2.10966</v>
+        <v>0.83004</v>
       </c>
       <c r="M87" t="n">
-        <v>26283132716</v>
+        <v>3319369204.37</v>
       </c>
       <c r="N87" t="n">
-        <v>100000000000</v>
+        <v>6861487132.729219</v>
       </c>
       <c r="O87" t="n">
-        <v>0.04323745</v>
+        <v>2</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>46156.97986111111</v>
+        <v>45322.29359953704</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R87" t="b">
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001228697735336199</v>
+        <v>0.000147270794526578</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-treasury-fund</t>
+          <t>pancakeswap-token</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>jtrsy</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1.12</v>
+        <v>2.37</v>
       </c>
       <c r="F88" t="n">
-        <v>725070974</v>
+        <v>757435880</v>
       </c>
       <c r="G88" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>92491504</v>
       </c>
       <c r="I88" t="n">
-        <v>1.12</v>
+        <v>2.39</v>
       </c>
       <c r="J88" t="n">
-        <v>1.12</v>
+        <v>2.19</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>0.174328</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>8.01408</v>
       </c>
       <c r="M88" t="n">
-        <v>649898513.025921</v>
+        <v>319427134.4515297</v>
       </c>
       <c r="N88" t="n">
-        <v>649898513.025921</v>
+        <v>331093394.0100838</v>
       </c>
       <c r="O88" t="n">
-        <v>1.12</v>
+        <v>43.96</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>46276.55543981482</v>
+        <v>44316.08914351852</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001104099364266916</v>
+        <v>0.0001278128544399079</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>render-token</t>
+          <t>stable-2</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>render</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>​​Stable</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1.38</v>
+        <v>0.02830765</v>
       </c>
       <c r="F89" t="n">
-        <v>714694281</v>
+        <v>745103332</v>
       </c>
       <c r="G89" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>26269304</v>
+        <v>8555253</v>
       </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>0.02947948</v>
       </c>
       <c r="J89" t="n">
-        <v>1.36</v>
+        <v>0.02766103</v>
       </c>
       <c r="K89" t="n">
-        <v>-0.01491997644989529</v>
+        <v>-6.0716447863509e-05</v>
       </c>
       <c r="L89" t="n">
-        <v>-1.07055</v>
+        <v>-0.12741</v>
       </c>
       <c r="M89" t="n">
-        <v>518776241.2826915</v>
+        <v>26315479766</v>
       </c>
       <c r="N89" t="n">
-        <v>533536414.5626915</v>
+        <v>100000000000</v>
       </c>
       <c r="O89" t="n">
-        <v>13.53</v>
+        <v>0.04323745</v>
       </c>
       <c r="P89" s="1" t="n">
-        <v>45368.35444444444</v>
+        <v>46156.97986111111</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R89" t="b">
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001036729953046991</v>
+        <v>0.0001199748532221676</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-aaa-clo-fund</t>
+          <t>janus-henderson-anemoy-treasury-fund</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>jaaa</t>
+          <t>jtrsy</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy AAA CLO Fund</t>
+          <t>Janus Henderson Anemoy Treasury Fund</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1.049</v>
+        <v>1.12</v>
       </c>
       <c r="F90" t="n">
-        <v>713695634</v>
+        <v>725211452</v>
       </c>
       <c r="G90" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>1.049</v>
+        <v>1.12</v>
       </c>
       <c r="J90" t="n">
-        <v>1.049</v>
+        <v>1.12</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>0.000216</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>0.01936</v>
       </c>
       <c r="M90" t="n">
-        <v>680267946.936126</v>
+        <v>649898602.6408989</v>
       </c>
       <c r="N90" t="n">
-        <v>680267946.936126</v>
+        <v>649898652.640859</v>
       </c>
       <c r="O90" t="n">
-        <v>1.049</v>
+        <v>1.12</v>
       </c>
       <c r="P90" s="1" t="n">
-        <v>46276.84375</v>
+        <v>46279.33680555555</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>0.0001030246359439033</v>
+        <v>0.0001073324876977729</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>pancakeswap-token</t>
+          <t>render-token</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>render</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2.18</v>
+        <v>1.38</v>
       </c>
       <c r="F91" t="n">
-        <v>698387350</v>
+        <v>716563534</v>
       </c>
       <c r="G91" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>49232076</v>
+        <v>34216975</v>
       </c>
       <c r="I91" t="n">
-        <v>2.23</v>
+        <v>1.41</v>
       </c>
       <c r="J91" t="n">
-        <v>2.17</v>
+        <v>1.36</v>
       </c>
       <c r="K91" t="n">
-        <v>-0.04925185431566437</v>
+        <v>-0.00029432628659487</v>
       </c>
       <c r="L91" t="n">
-        <v>-2.20761</v>
+        <v>-0.01348</v>
       </c>
       <c r="M91" t="n">
-        <v>320190976.0630089</v>
+        <v>518776241.2826915</v>
       </c>
       <c r="N91" t="n">
-        <v>331857365.0100838</v>
+        <v>533536414.5626915</v>
       </c>
       <c r="O91" t="n">
-        <v>43.96</v>
+        <v>13.53</v>
       </c>
       <c r="P91" s="1" t="n">
-        <v>44316.08914351852</v>
+        <v>45368.35444444444</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R91" t="b">
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>9.308591963161186e-05</v>
+        <v>0.0001018362681156624</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>janus-henderson-anemoy-aaa-clo-fund</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>jaaa</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>GHO</t>
+          <t>Janus Henderson Anemoy AAA CLO Fund</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.998686</v>
+        <v>1.05</v>
       </c>
       <c r="F92" t="n">
-        <v>698081387</v>
+        <v>713986788</v>
       </c>
       <c r="G92" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H92" t="n">
-        <v>1756918</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>0.998964</v>
+        <v>1.05</v>
       </c>
       <c r="J92" t="n">
-        <v>0.998574</v>
+        <v>1.049</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.00012704836909827</v>
+        <v>0.000428</v>
       </c>
       <c r="L92" t="n">
-        <v>-0.01272</v>
+        <v>0.0408</v>
       </c>
       <c r="M92" t="n">
-        <v>699000000</v>
+        <v>680267946.936126</v>
       </c>
       <c r="N92" t="n">
-        <v>699000000</v>
+        <v>680267946.936126</v>
       </c>
       <c r="O92" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>45350.38608796296</v>
+        <v>46279.33680555555</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R92" t="b">
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>9.28872768928792e-05</v>
+        <v>0.0001001986066781551</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>filecoin</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>GHO</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.841786</v>
+        <v>0.998708</v>
       </c>
       <c r="F93" t="n">
-        <v>696662345</v>
+        <v>698095861</v>
       </c>
       <c r="G93" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H93" t="n">
-        <v>58328314</v>
+        <v>4559188</v>
       </c>
       <c r="I93" t="n">
-        <v>0.83914</v>
+        <v>0.998929</v>
       </c>
       <c r="J93" t="n">
-        <v>0.7973209999999999</v>
+        <v>0.998309</v>
       </c>
       <c r="K93" t="n">
-        <v>0.03396596</v>
+        <v>4.271e-05</v>
       </c>
       <c r="L93" t="n">
-        <v>4.20465</v>
+        <v>0.00465</v>
       </c>
       <c r="M93" t="n">
-        <v>827747763</v>
+        <v>699000000</v>
       </c>
       <c r="N93" t="n">
-        <v>1957056557</v>
+        <v>699000000</v>
       </c>
       <c r="O93" t="n">
-        <v>236.84</v>
+        <v>1.03</v>
       </c>
       <c r="P93" s="1" t="n">
-        <v>44287.22894675926</v>
+        <v>45350.38608796296</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R93" t="b">
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>9.196598121576564e-05</v>
+        <v>9.009906316313929e-05</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6703,34 +6703,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>53.66</v>
+        <v>53.9</v>
       </c>
       <c r="F94" t="n">
-        <v>688404472</v>
+        <v>691341172</v>
       </c>
       <c r="G94" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H94" t="n">
-        <v>80144094</v>
+        <v>83860594</v>
       </c>
       <c r="I94" t="n">
-        <v>56.52</v>
+        <v>55.07</v>
       </c>
       <c r="J94" t="n">
-        <v>53.69</v>
+        <v>52.65</v>
       </c>
       <c r="K94" t="n">
-        <v>-2.621952386134858</v>
+        <v>0.404915</v>
       </c>
       <c r="L94" t="n">
-        <v>-4.65825</v>
+        <v>0.72858</v>
       </c>
       <c r="M94" t="n">
-        <v>12826804.35764862</v>
+        <v>12827825.55374544</v>
       </c>
       <c r="N94" t="n">
-        <v>12827522.60472958</v>
+        <v>12828534.51612917</v>
       </c>
       <c r="O94" t="n">
         <v>1493.59</v>
@@ -6739,19 +6739,19 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>8.660465808575767e-05</v>
+        <v>8.580609299935344e-05</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6770,28 +6770,28 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.00768983</v>
+        <v>0.00771809</v>
       </c>
       <c r="F95" t="n">
-        <v>661185178</v>
+        <v>663403604</v>
       </c>
       <c r="G95" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>13964290</v>
+        <v>11855889</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0079963</v>
+        <v>0.008113840000000001</v>
       </c>
       <c r="J95" t="n">
-        <v>0.00749197</v>
+        <v>0.0076483</v>
       </c>
       <c r="K95" t="n">
-        <v>-9.4151996024112e-05</v>
+        <v>-6.0082351379e-07</v>
       </c>
       <c r="L95" t="n">
-        <v>-1.20956</v>
+        <v>-0.05431</v>
       </c>
       <c r="M95" t="n">
         <v>85985041177</v>
@@ -6806,19 +6806,19 @@
         <v>44304.71413194444</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R95" t="b">
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>6.893286408932697e-05</v>
+        <v>6.805025762740101e-05</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6837,28 +6837,28 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.6500050000000001</v>
+        <v>0.643865</v>
       </c>
       <c r="F96" t="n">
-        <v>626888647</v>
+        <v>621648285</v>
       </c>
       <c r="G96" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>66604793</v>
+        <v>58218057</v>
       </c>
       <c r="I96" t="n">
-        <v>0.773031</v>
+        <v>0.667844</v>
       </c>
       <c r="J96" t="n">
-        <v>0.651512</v>
+        <v>0.619474</v>
       </c>
       <c r="K96" t="n">
-        <v>-0.1070226092627694</v>
+        <v>0.00547454</v>
       </c>
       <c r="L96" t="n">
-        <v>-14.13721</v>
+        <v>0.89502</v>
       </c>
       <c r="M96" t="n">
         <v>965350000</v>
@@ -6873,153 +6873,153 @@
         <v>45378.63525462963</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>4.666626045793964e-05</v>
+        <v>4.151249420907636e-05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>beldex</t>
+          <t>injective-protocol</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>bdx</t>
+          <t>inj</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Beldex</t>
+          <t>Injective</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.076042</v>
+        <v>6.2</v>
       </c>
       <c r="F97" t="n">
-        <v>598617819</v>
+        <v>619644975</v>
       </c>
       <c r="G97" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>11123884</v>
+        <v>93091125</v>
       </c>
       <c r="I97" t="n">
-        <v>0.07681300000000001</v>
+        <v>6.27</v>
       </c>
       <c r="J97" t="n">
-        <v>0.075978</v>
+        <v>5.85</v>
       </c>
       <c r="K97" t="n">
-        <v>-0.0006413350189097971</v>
+        <v>0.07942</v>
       </c>
       <c r="L97" t="n">
-        <v>-0.83634</v>
+        <v>1.2766</v>
       </c>
       <c r="M97" t="n">
-        <v>7870655757.768536</v>
+        <v>100000000</v>
       </c>
       <c r="N97" t="n">
-        <v>9939595838.896603</v>
+        <v>100000000</v>
       </c>
       <c r="O97" t="n">
-        <v>0.450785</v>
+        <v>52.62</v>
       </c>
       <c r="P97" s="1" t="n">
-        <v>43450.66666666666</v>
+        <v>45365.29608796296</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>2.83117708622681e-05</v>
+        <v>4.023928236189675e-05</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>injective-protocol</t>
+          <t>beldex</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>inj</t>
+          <t>bdx</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Injective</t>
+          <t>Beldex</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5.97</v>
+        <v>0.076239</v>
       </c>
       <c r="F98" t="n">
-        <v>597001466</v>
+        <v>599934863</v>
       </c>
       <c r="G98" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>63175325</v>
+        <v>10276372</v>
       </c>
       <c r="I98" t="n">
-        <v>6.18</v>
+        <v>0.076415</v>
       </c>
       <c r="J98" t="n">
-        <v>5.77</v>
+        <v>0.075914</v>
       </c>
       <c r="K98" t="n">
-        <v>0.04376152</v>
+        <v>0.00015292</v>
       </c>
       <c r="L98" t="n">
-        <v>0.73812</v>
+        <v>0.20802</v>
       </c>
       <c r="M98" t="n">
-        <v>100000000</v>
+        <v>7870667509.557123</v>
       </c>
       <c r="N98" t="n">
-        <v>100000000</v>
+        <v>9939607085.763391</v>
       </c>
       <c r="O98" t="n">
-        <v>52.62</v>
+        <v>0.450785</v>
       </c>
       <c r="P98" s="1" t="n">
-        <v>45365.29608796296</v>
+        <v>43450.66666666666</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R98" t="b">
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>2.726237342964135e-05</v>
+        <v>2.771244023180353e-05</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7038,34 +7038,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.00642494</v>
+        <v>0.00664088</v>
       </c>
       <c r="F99" t="n">
-        <v>558487137</v>
+        <v>577235836</v>
       </c>
       <c r="G99" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>1975430</v>
+        <v>2212140</v>
       </c>
       <c r="I99" t="n">
-        <v>0.00653376</v>
+        <v>0.00660261</v>
       </c>
       <c r="J99" t="n">
-        <v>0.00640673</v>
+        <v>0.00639912</v>
       </c>
       <c r="K99" t="n">
-        <v>7.93e-06</v>
+        <v>0.00018282</v>
       </c>
       <c r="L99" t="n">
-        <v>0.12362</v>
+        <v>3.16072</v>
       </c>
       <c r="M99" t="n">
-        <v>86938088551.2818</v>
+        <v>86942314077.73903</v>
       </c>
       <c r="N99" t="n">
-        <v>106539016188.1805</v>
+        <v>106545584672.7701</v>
       </c>
       <c r="O99" t="n">
         <v>0.150073</v>
@@ -7074,141 +7074,141 @@
         <v>44935.80144675926</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R99" t="b">
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>2.257415990305974e-06</v>
+        <v>1.328598097395033e-05</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>xdce-crowd-sale</t>
+          <t>aerodrome-finance</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>xdc</t>
+          <t>aero</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>XDC Network</t>
+          <t>Aerodrome Finance</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.02784597</v>
+        <v>0.573146</v>
       </c>
       <c r="F100" t="n">
-        <v>555295579</v>
+        <v>566879138</v>
       </c>
       <c r="G100" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>3799999</v>
+        <v>24995379</v>
       </c>
       <c r="I100" t="n">
-        <v>0.02803692</v>
+        <v>0.584179</v>
       </c>
       <c r="J100" t="n">
-        <v>0.02763857</v>
+        <v>0.5548070000000001</v>
       </c>
       <c r="K100" t="n">
-        <v>-0.000140795085449043</v>
+        <v>0.01146812</v>
       </c>
       <c r="L100" t="n">
-        <v>-0.50308</v>
+        <v>2.01643</v>
       </c>
       <c r="M100" t="n">
-        <v>19946688440</v>
+        <v>988792626.4788798</v>
       </c>
       <c r="N100" t="n">
-        <v>38065686425.1</v>
+        <v>1978450301.483024</v>
       </c>
       <c r="O100" t="n">
-        <v>0.192754</v>
+        <v>2.32</v>
       </c>
       <c r="P100" s="1" t="n">
-        <v>44428.86097222222</v>
+        <v>45633.25043981482</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R100" t="b">
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>1.853359612038094e-07</v>
+        <v>6.703739288309363e-06</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>aerodrome-finance</t>
+          <t>xdce-crowd-sale</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>aero</t>
+          <t>xdc</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Aerodrome Finance</t>
+          <t>XDC Network</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.561319</v>
+        <v>0.02789734</v>
       </c>
       <c r="F101" t="n">
-        <v>555010112</v>
+        <v>556331272</v>
       </c>
       <c r="G101" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>14976935</v>
+        <v>6122903</v>
       </c>
       <c r="I101" t="n">
-        <v>0.5745209999999999</v>
+        <v>0.02799834</v>
       </c>
       <c r="J101" t="n">
-        <v>0.55507</v>
+        <v>0.02759105</v>
       </c>
       <c r="K101" t="n">
-        <v>-0.01302517765560196</v>
+        <v>-8.1389842287991e-05</v>
       </c>
       <c r="L101" t="n">
-        <v>-2.26783</v>
+        <v>-0.31486</v>
       </c>
       <c r="M101" t="n">
-        <v>988772768.1180431</v>
+        <v>19946688440</v>
       </c>
       <c r="N101" t="n">
-        <v>1978450301.483024</v>
+        <v>38065686425.1</v>
       </c>
       <c r="O101" t="n">
-        <v>2.32</v>
+        <v>0.192754</v>
       </c>
       <c r="P101" s="1" t="n">
-        <v>45633.25043981482</v>
+        <v>44428.86097222222</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46278.57106481482</v>
+        <v>46279.65787037037</v>
       </c>
       <c r="R101" t="b">
         <v>0</v>

--- a/src/xlsx/cleaned_data.xlsx
+++ b/src/xlsx/cleaned_data.xlsx
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,34 +539,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>78362</v>
+        <v>77928</v>
       </c>
       <c r="F2" t="n">
-        <v>1573986553774</v>
+        <v>1565278264656</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>25984289979</v>
+        <v>32481754899</v>
       </c>
       <c r="I2" t="n">
-        <v>78630</v>
+        <v>79530</v>
       </c>
       <c r="J2" t="n">
-        <v>76439</v>
+        <v>77010</v>
       </c>
       <c r="K2" t="n">
-        <v>1231.1</v>
+        <v>1192.34</v>
       </c>
       <c r="L2" t="n">
-        <v>1.60581</v>
+        <v>1.55383</v>
       </c>
       <c r="M2" t="n">
-        <v>20084256</v>
+        <v>20084421</v>
       </c>
       <c r="N2" t="n">
-        <v>20084296</v>
+        <v>20084481</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -575,7 +575,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -587,7 +587,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,28 +606,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2504.03</v>
+        <v>2512.93</v>
       </c>
       <c r="F3" t="n">
-        <v>305633502308</v>
+        <v>306704123966</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>12681366507</v>
+        <v>16310732511</v>
       </c>
       <c r="I3" t="n">
-        <v>2531.64</v>
+        <v>2607.56</v>
       </c>
       <c r="J3" t="n">
-        <v>2467.86</v>
+        <v>2489.59</v>
       </c>
       <c r="K3" t="n">
-        <v>14.1</v>
+        <v>33.64</v>
       </c>
       <c r="L3" t="n">
-        <v>0.55974</v>
+        <v>1.35678</v>
       </c>
       <c r="M3" t="n">
         <v>122047243.4940371</v>
@@ -642,19 +642,19 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1938930412502688</v>
+        <v>0.1956558152727918</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,34 +673,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999729</v>
+        <v>0.9998359999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>183381380503</v>
+        <v>183404017289</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>47887967714</v>
+        <v>58316519980</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999795</v>
+        <v>0.999954</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999546</v>
+        <v>0.999563</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.1522703644593e-05</v>
+        <v>0.00017816</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00331</v>
+        <v>0.01782</v>
       </c>
       <c r="M4" t="n">
-        <v>183430992297.9018</v>
+        <v>183431197333.8773</v>
       </c>
       <c r="N4" t="n">
-        <v>188897938202.3062</v>
+        <v>188898143247.2662</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -709,19 +709,19 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.116195206254701</v>
+        <v>0.1168557505205339</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,34 +740,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>721.51</v>
+        <v>719.73</v>
       </c>
       <c r="F5" t="n">
-        <v>96081461908</v>
+        <v>95843853248</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>887352635</v>
+        <v>1013896622</v>
       </c>
       <c r="I5" t="n">
-        <v>727.36</v>
+        <v>732.8</v>
       </c>
       <c r="J5" t="n">
-        <v>714.28</v>
+        <v>717.26</v>
       </c>
       <c r="K5" t="n">
-        <v>2.66</v>
+        <v>3.33</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3615</v>
+        <v>0.46471</v>
       </c>
       <c r="M5" t="n">
-        <v>133160863.85</v>
+        <v>133160833.09</v>
       </c>
       <c r="N5" t="n">
-        <v>133160863.85</v>
+        <v>133160833.09</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -776,19 +776,19 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06071138666962943</v>
+        <v>0.0608967835569134</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -807,28 +807,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="F6" t="n">
-        <v>88060370043</v>
+        <v>89328302982</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2415726593</v>
+        <v>3988480517</v>
       </c>
       <c r="I6" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="J6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="K6" t="n">
-        <v>0.056142</v>
+        <v>0.07849299999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>4.18102</v>
+        <v>5.84888</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -843,19 +843,19 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05561354899606218</v>
+        <v>0.05673274999121362</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,16 +874,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999841</v>
+        <v>0.999866</v>
       </c>
       <c r="F7" t="n">
-        <v>74142138897</v>
+        <v>74355972434</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>13799048631</v>
+        <v>18147169260</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -892,16 +892,16 @@
         <v>0.999711</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.1127436362067e-05</v>
+        <v>3.435e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00261</v>
+        <v>0.00344</v>
       </c>
       <c r="M7" t="n">
-        <v>74153956598.56355</v>
+        <v>74364752733.23085</v>
       </c>
       <c r="N7" t="n">
-        <v>74236759977.72971</v>
+        <v>74371126949.03763</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -910,19 +910,19 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04676776038278142</v>
+        <v>0.04716405902677434</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -941,34 +941,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101.84</v>
+        <v>102.33</v>
       </c>
       <c r="F8" t="n">
-        <v>59767609118</v>
+        <v>60071914459</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2729178439</v>
+        <v>3391879841</v>
       </c>
       <c r="I8" t="n">
-        <v>102.21</v>
+        <v>104.76</v>
       </c>
       <c r="J8" t="n">
-        <v>99.03</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>1.51</v>
+        <v>2.95</v>
       </c>
       <c r="L8" t="n">
-        <v>1.50505</v>
+        <v>2.96946</v>
       </c>
       <c r="M8" t="n">
-        <v>586892648.6679221</v>
+        <v>587028564.7667522</v>
       </c>
       <c r="N8" t="n">
-        <v>634017381.8979012</v>
+        <v>634017029.7664536</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -977,19 +977,19 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03763196931087597</v>
+        <v>0.03803523729506558</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1008,34 +1008,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.340552</v>
+        <v>0.337933</v>
       </c>
       <c r="F9" t="n">
-        <v>32338144917</v>
+        <v>32085906398</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>363419765</v>
+        <v>459700901</v>
       </c>
       <c r="I9" t="n">
-        <v>0.341529</v>
+        <v>0.342048</v>
       </c>
       <c r="J9" t="n">
-        <v>0.337711</v>
+        <v>0.33736</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.000581742705109523</v>
+        <v>-0.000482044361519829</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.15732</v>
+        <v>-0.14244</v>
       </c>
       <c r="M9" t="n">
-        <v>94950123551.61649</v>
+        <v>94950365063.49529</v>
       </c>
       <c r="N9" t="n">
-        <v>94950129154.07608</v>
+        <v>94950919109.75899</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1044,19 +1044,19 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02019906138224671</v>
+        <v>0.02014961410464071</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1075,19 +1075,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.046</v>
+        <v>1.028</v>
       </c>
       <c r="F10" t="n">
-        <v>23593992468</v>
+        <v>23190254032</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>958374</v>
+        <v>26456887</v>
       </c>
       <c r="I10" t="n">
-        <v>1.042</v>
+        <v>1.048</v>
       </c>
       <c r="J10" t="n">
         <v>1.006</v>
@@ -1111,19 +1111,19 @@
         <v>46237.59675925926</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01464167960328518</v>
+        <v>0.01446447723537038</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1142,34 +1142,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1135.01</v>
+        <v>1156.87</v>
       </c>
       <c r="F11" t="n">
-        <v>19206090756</v>
+        <v>19585748329</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1142157231</v>
+        <v>1339721891</v>
       </c>
       <c r="I11" t="n">
-        <v>1155.3</v>
+        <v>1222.73</v>
       </c>
       <c r="J11" t="n">
-        <v>1048.58</v>
+        <v>1072.1</v>
       </c>
       <c r="K11" t="n">
-        <v>46.32</v>
+        <v>95.72</v>
       </c>
       <c r="L11" t="n">
-        <v>4.11852</v>
+        <v>9.020440000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>16930431.4155448</v>
+        <v>16932570.4780448</v>
       </c>
       <c r="N11" t="n">
-        <v>16932228.2905448</v>
+        <v>16932909.5405448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1178,19 +1178,19 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01185293076063072</v>
+        <v>0.01216086785131406</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1209,28 +1209,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>79.87</v>
+        <v>80.2</v>
       </c>
       <c r="F12" t="n">
-        <v>17767318483</v>
+        <v>17841668216</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>722094725</v>
+        <v>820683271</v>
       </c>
       <c r="I12" t="n">
-        <v>80.98999999999999</v>
+        <v>82.38</v>
       </c>
       <c r="J12" t="n">
-        <v>77.01000000000001</v>
+        <v>78.05</v>
       </c>
       <c r="K12" t="n">
-        <v>1.74</v>
+        <v>2.51</v>
       </c>
       <c r="L12" t="n">
-        <v>2.18041</v>
+        <v>3.22502</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1245,19 +1245,19 @@
         <v>46271.5199074074</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01093851317005456</v>
+        <v>0.01104624086889344</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1276,34 +1276,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.08391800000000001</v>
+        <v>0.083762</v>
       </c>
       <c r="F13" t="n">
-        <v>13084729747</v>
+        <v>13061146331</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>582797744</v>
+        <v>623849039</v>
       </c>
       <c r="I13" t="n">
-        <v>0.084753</v>
+        <v>0.086033</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08204</v>
+        <v>0.083028</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00034659</v>
+        <v>0.00124728</v>
       </c>
       <c r="L13" t="n">
-        <v>0.35787</v>
+        <v>1.51158</v>
       </c>
       <c r="M13" t="n">
-        <v>155910866383.7052</v>
+        <v>155919246383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>155913316383.7052</v>
+        <v>171630873126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1312,19 +1312,19 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.007962474786506826</v>
+        <v>0.007991049399559087</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1343,31 +1343,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01437241</v>
+        <v>0.01423283</v>
       </c>
       <c r="F14" t="n">
-        <v>10194077797</v>
+        <v>10097241960</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>23950993</v>
+        <v>27250626</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01539524</v>
+        <v>0.01529975</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01471193</v>
+        <v>0.01423111</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000917734779514243</v>
+        <v>-0.000917806640155248</v>
       </c>
       <c r="L14" t="n">
-        <v>-5.95737</v>
+        <v>-6.05787</v>
       </c>
       <c r="M14" t="n">
-        <v>709219646352.0608</v>
+        <v>709219950838.6726</v>
       </c>
       <c r="N14" t="n">
         <v>1142408526965.963</v>
@@ -1379,19 +1379,19 @@
         <v>46259.82847222222</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R14" t="b">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.006125309141243313</v>
+        <v>0.006096842957660955</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1410,34 +1410,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.999728</v>
+        <v>0.999815</v>
       </c>
       <c r="F15" t="n">
-        <v>9822164283</v>
+        <v>9841412373</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>103418986</v>
+        <v>128014911</v>
       </c>
       <c r="I15" t="n">
-        <v>0.999883</v>
+        <v>0.999922</v>
       </c>
       <c r="J15" t="n">
         <v>0.99953</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.1109509834446e-05</v>
+        <v>4.974e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.00638</v>
+        <v>0.00497</v>
       </c>
       <c r="M15" t="n">
-        <v>9825388957.758593</v>
+        <v>9843079519.306154</v>
       </c>
       <c r="N15" t="n">
-        <v>9825388957.758593</v>
+        <v>9859445986.033854</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1446,19 +1446,19 @@
         <v>45593.90336805556</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005888937989424073</v>
+        <v>0.005933344412814166</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1477,34 +1477,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>513.16</v>
+        <v>517.35</v>
       </c>
       <c r="F16" t="n">
-        <v>9650985830</v>
+        <v>9729591804</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>120076787</v>
+        <v>144582594</v>
       </c>
       <c r="I16" t="n">
-        <v>537.77</v>
+        <v>526.9</v>
       </c>
       <c r="J16" t="n">
         <v>502.91</v>
       </c>
       <c r="K16" t="n">
-        <v>-22.04391946356634</v>
+        <v>4.44</v>
       </c>
       <c r="L16" t="n">
-        <v>-4.24549</v>
+        <v>0.86522</v>
       </c>
       <c r="M16" t="n">
-        <v>18804596.02384349</v>
+        <v>18804748.99981384</v>
       </c>
       <c r="N16" t="n">
-        <v>18804629.02373879</v>
+        <v>18804784.39672368</v>
       </c>
       <c r="O16" t="n">
         <v>797.73</v>
@@ -1513,19 +1513,19 @@
         <v>46036.48202546296</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.005780144824940554</v>
+        <v>0.005861880824376915</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1544,28 +1544,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>80.93000000000001</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>9541965154</v>
+        <v>9508070993</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>103097807</v>
+        <v>124952764</v>
       </c>
       <c r="I17" t="n">
-        <v>81.25</v>
+        <v>82.67</v>
       </c>
       <c r="J17" t="n">
-        <v>79.23999999999999</v>
+        <v>79.78</v>
       </c>
       <c r="K17" t="n">
-        <v>1.063</v>
+        <v>1.11</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3493</v>
+        <v>1.40009</v>
       </c>
       <c r="M17" t="n">
         <v>117882016</v>
@@ -1580,19 +1580,19 @@
         <v>46276.58553240741</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005710856289331622</v>
+        <v>0.005720308730716846</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1611,28 +1611,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.43</v>
+        <v>11.57</v>
       </c>
       <c r="F18" t="n">
-        <v>8547956810</v>
+        <v>8656632447</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>351732452</v>
+        <v>378630111</v>
       </c>
       <c r="I18" t="n">
-        <v>11.49</v>
+        <v>11.95</v>
       </c>
       <c r="J18" t="n">
-        <v>11.14</v>
+        <v>11.25</v>
       </c>
       <c r="K18" t="n">
-        <v>0.167787</v>
+        <v>0.331506</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4751</v>
+        <v>2.94987</v>
       </c>
       <c r="M18" t="n">
         <v>748099970.424884</v>
@@ -1647,19 +1647,19 @@
         <v>44325.67635416667</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005079110229173091</v>
+        <v>0.005176161492198002</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1678,28 +1678,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.99</v>
+        <v>8.98</v>
       </c>
       <c r="F19" t="n">
-        <v>8265020156</v>
+        <v>8262550568</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>146114</v>
+        <v>119220</v>
       </c>
       <c r="I19" t="n">
-        <v>9.08</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="J19" t="n">
         <v>8.949999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.06750082080595554</v>
+        <v>-0.05097400490951998</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7448900000000001</v>
+        <v>-0.56428</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1714,19 +1714,19 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004899288683893449</v>
+        <v>0.004924307066278969</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1745,28 +1745,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.208339</v>
+        <v>0.207943</v>
       </c>
       <c r="F20" t="n">
-        <v>7816066705</v>
+        <v>7803954887</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>352248691</v>
+        <v>399285548</v>
       </c>
       <c r="I20" t="n">
-        <v>0.212356</v>
+        <v>0.215603</v>
       </c>
       <c r="J20" t="n">
-        <v>0.202412</v>
+        <v>0.204682</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00229722</v>
+        <v>0.00435576</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0824</v>
+        <v>2.1395</v>
       </c>
       <c r="M20" t="n">
         <v>37516725700.17653</v>
@@ -1781,19 +1781,19 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004613954485668825</v>
+        <v>0.004631222410216406</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1812,31 +1812,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.192245</v>
+        <v>0.192906</v>
       </c>
       <c r="F21" t="n">
-        <v>6698510243</v>
+        <v>6720183097</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>232181544</v>
+        <v>352873849</v>
       </c>
       <c r="I21" t="n">
-        <v>0.193471</v>
+        <v>0.196711</v>
       </c>
       <c r="J21" t="n">
-        <v>0.176496</v>
+        <v>0.178695</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01369287</v>
+        <v>0.01534281</v>
       </c>
       <c r="L21" t="n">
-        <v>7.59998</v>
+        <v>8.640750000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>34833755724.17101</v>
+        <v>34835002057.12234</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70248</v>
@@ -1848,19 +1848,19 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R21" t="b">
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.003903686914843275</v>
+        <v>0.003938592942730301</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1879,34 +1879,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.999681</v>
+        <v>0.999786</v>
       </c>
       <c r="F22" t="n">
-        <v>4614179179</v>
+        <v>4666338082</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>32050801</v>
+        <v>48169800</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9996969999999999</v>
+        <v>0.999955</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9994150000000001</v>
+        <v>0.999457</v>
       </c>
       <c r="K22" t="n">
-        <v>7.073e-05</v>
+        <v>0.00024197</v>
       </c>
       <c r="L22" t="n">
-        <v>0.00777</v>
+        <v>0.02421</v>
       </c>
       <c r="M22" t="n">
-        <v>4615650751.612019</v>
+        <v>4667235430.751101</v>
       </c>
       <c r="N22" t="n">
-        <v>4620286189.396619</v>
+        <v>4667235430.751101</v>
       </c>
       <c r="O22" t="n">
         <v>1.034</v>
@@ -1915,19 +1915,19 @@
         <v>46000.38208333333</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R22" t="b">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.00257898179974412</v>
+        <v>0.002625997807698744</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1946,34 +1946,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.999906</v>
+        <v>0.9999</v>
       </c>
       <c r="F23" t="n">
-        <v>4559719507</v>
+        <v>4587613885</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>200977036</v>
+        <v>272052157</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0.999689</v>
+        <v>0.999684</v>
       </c>
       <c r="K23" t="n">
-        <v>0.00013305</v>
+        <v>-9.104097099410499e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.00223</v>
+        <v>-0.0091</v>
       </c>
       <c r="M23" t="n">
-        <v>4560681562.981492</v>
+        <v>4587994881.149207</v>
       </c>
       <c r="N23" t="n">
-        <v>4560681562.981492</v>
+        <v>4587994881.149207</v>
       </c>
       <c r="O23" t="n">
         <v>1.22</v>
@@ -1982,19 +1982,19 @@
         <v>43902.79363425926</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R23" t="b">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.002544369732922752</v>
+        <v>0.002575685833213432</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2013,34 +2013,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222.92</v>
+        <v>223.01</v>
       </c>
       <c r="F24" t="n">
-        <v>4478998809</v>
+        <v>4480527872</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>154256060</v>
+        <v>144998419</v>
       </c>
       <c r="I24" t="n">
-        <v>225.71</v>
+        <v>230.06</v>
       </c>
       <c r="J24" t="n">
-        <v>219.99</v>
+        <v>220.2</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8566991381841831</v>
+        <v>1.33</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.39865</v>
+        <v>0.59892</v>
       </c>
       <c r="M24" t="n">
-        <v>20089046.77165077</v>
+        <v>20089143.64665077</v>
       </c>
       <c r="N24" t="n">
-        <v>20089328.02165077</v>
+        <v>20089490.52165077</v>
       </c>
       <c r="O24" t="n">
         <v>3785.82</v>
@@ -2049,19 +2049,19 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002493067363840479</v>
+        <v>0.002507248059833669</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2080,34 +2080,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9996</v>
+        <v>0.999652</v>
       </c>
       <c r="F25" t="n">
-        <v>4325414452</v>
+        <v>4340634644</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>1030935992</v>
+        <v>1166862007</v>
       </c>
       <c r="I25" t="n">
-        <v>0.999718</v>
+        <v>0.9998939999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>0.999383</v>
+        <v>0.9994189999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>8.182999999999999e-05</v>
+        <v>8.205e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>0.00484</v>
+        <v>0.00821</v>
       </c>
       <c r="M25" t="n">
-        <v>4327109501.780501</v>
+        <v>4342109207.801132</v>
       </c>
       <c r="N25" t="n">
-        <v>4327109501.780501</v>
+        <v>4342109207.801132</v>
       </c>
       <c r="O25" t="n">
         <v>1.048</v>
@@ -2116,153 +2116,153 @@
         <v>46212.42696759259</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002395456198881555</v>
+        <v>0.002417843470317132</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>litecoin</t>
+          <t>uniswap</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ltc</t>
+          <t>uni</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53.77</v>
+        <v>6.7</v>
       </c>
       <c r="F26" t="n">
-        <v>4173096340</v>
+        <v>4172914708</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>218860200</v>
+        <v>546287575</v>
       </c>
       <c r="I26" t="n">
-        <v>55.19</v>
+        <v>6.79</v>
       </c>
       <c r="J26" t="n">
-        <v>53.41</v>
+        <v>6.22</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.5798134796304737</v>
+        <v>0.5339469999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.07178</v>
+        <v>8.66582</v>
       </c>
       <c r="M26" t="n">
-        <v>77606448.13410389</v>
+        <v>623212423.7271129</v>
       </c>
       <c r="N26" t="n">
-        <v>77609316.89202861</v>
+        <v>890460420.0329479</v>
       </c>
       <c r="O26" t="n">
-        <v>410.26</v>
+        <v>44.92</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>44325.80077546297</v>
+        <v>44318.89240740741</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002298649801100667</v>
+        <v>0.002310655064944002</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>uniswap</t>
+          <t>litecoin</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>uni</t>
+          <t>ltc</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6.36</v>
+        <v>52.89</v>
       </c>
       <c r="F27" t="n">
-        <v>3962142069</v>
+        <v>4104723979</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>365274151</v>
+        <v>215062599</v>
       </c>
       <c r="I27" t="n">
-        <v>6.46</v>
+        <v>54.54</v>
       </c>
       <c r="J27" t="n">
-        <v>6.1</v>
+        <v>52.61</v>
       </c>
       <c r="K27" t="n">
-        <v>0.106608</v>
+        <v>-1.067596865327559</v>
       </c>
       <c r="L27" t="n">
-        <v>1.65018</v>
+        <v>-1.97876</v>
       </c>
       <c r="M27" t="n">
-        <v>623212423.7271129</v>
+        <v>77607591.88778906</v>
       </c>
       <c r="N27" t="n">
-        <v>890460420.0329479</v>
+        <v>77610835.64571653</v>
       </c>
       <c r="O27" t="n">
-        <v>44.92</v>
+        <v>410.26</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>44318.89240740741</v>
+        <v>44325.80077546297</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002164576953138874</v>
+        <v>0.002267074941572494</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2281,34 +2281,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.095821</v>
+        <v>0.095952</v>
       </c>
       <c r="F28" t="n">
-        <v>3794641050</v>
+        <v>3799143043</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>7684439</v>
+        <v>8810925</v>
       </c>
       <c r="I28" t="n">
-        <v>0.097021</v>
+        <v>0.09957199999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>0.094268</v>
+        <v>0.094793</v>
       </c>
       <c r="K28" t="n">
-        <v>0.00091269</v>
+        <v>0.00060352</v>
       </c>
       <c r="L28" t="n">
-        <v>0.9368</v>
+        <v>0.63296</v>
       </c>
       <c r="M28" t="n">
-        <v>39589485630.91892</v>
+        <v>39591792568.75395</v>
       </c>
       <c r="N28" t="n">
-        <v>39589485630.91892</v>
+        <v>39592719231.5488</v>
       </c>
       <c r="O28" t="n">
         <v>0.194152</v>
@@ -2317,19 +2317,19 @@
         <v>46056.00148148148</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002058120996843814</v>
+        <v>0.002071780726564752</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2351,13 +2351,13 @@
         <v>1.35</v>
       </c>
       <c r="F29" t="n">
-        <v>3763625970</v>
+        <v>3758347414</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>20347988</v>
+        <v>22644492</v>
       </c>
       <c r="I29" t="n">
         <v>1.37</v>
@@ -2366,16 +2366,16 @@
         <v>1.34</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.006013759062806434</v>
+        <v>0.00194014</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.56774</v>
+        <v>0.14417</v>
       </c>
       <c r="M29" t="n">
-        <v>2788394271.526778</v>
+        <v>2788626129.896895</v>
       </c>
       <c r="N29" t="n">
-        <v>5248995037.316007</v>
+        <v>5249250485.565387</v>
       </c>
       <c r="O29" t="n">
         <v>8.25</v>
@@ -2384,19 +2384,19 @@
         <v>45457.69225694444</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002038409236159135</v>
+        <v>0.002045708581994509</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2415,31 +2415,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.07660699999999999</v>
+        <v>0.07807600000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>3357654046</v>
+        <v>3423512744</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>50267819</v>
+        <v>62181970</v>
       </c>
       <c r="I30" t="n">
-        <v>0.077444</v>
+        <v>0.0793</v>
       </c>
       <c r="J30" t="n">
-        <v>0.074799</v>
+        <v>0.075722</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0009911</v>
+        <v>0.00274329</v>
       </c>
       <c r="L30" t="n">
-        <v>1.31124</v>
+        <v>3.64156</v>
       </c>
       <c r="M30" t="n">
-        <v>43831559671.84134</v>
+        <v>43831559670.36193</v>
       </c>
       <c r="N30" t="n">
         <v>50000000000</v>
@@ -2451,19 +2451,19 @@
         <v>44454.11143518519</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.001780392122852108</v>
+        <v>0.00183171855077402</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2482,34 +2482,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>7.46</v>
+        <v>7.55</v>
       </c>
       <c r="F31" t="n">
-        <v>3298802999</v>
+        <v>3340140954</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>210126645</v>
+        <v>260534190</v>
       </c>
       <c r="I31" t="n">
-        <v>7.54</v>
+        <v>7.79</v>
       </c>
       <c r="J31" t="n">
-        <v>7.27</v>
+        <v>7.34</v>
       </c>
       <c r="K31" t="n">
-        <v>0.08415</v>
+        <v>0.230515</v>
       </c>
       <c r="L31" t="n">
-        <v>1.08225</v>
+        <v>3.15048</v>
       </c>
       <c r="M31" t="n">
-        <v>442507221.2454377</v>
+        <v>442511274.1977351</v>
       </c>
       <c r="N31" t="n">
-        <v>469175921.2454377</v>
+        <v>469180009.5183742</v>
       </c>
       <c r="O31" t="n">
         <v>144.96</v>
@@ -2518,19 +2518,19 @@
         <v>44521.26314814815</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.00174298909972572</v>
+        <v>0.001778436338555649</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2549,34 +2549,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.999893</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>3295066818</v>
+        <v>3320460979</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>1120940203</v>
+        <v>1355481705</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>0.999695</v>
+        <v>0.999787</v>
       </c>
       <c r="K32" t="n">
-        <v>-7.908955085512e-06</v>
+        <v>9.195e-05</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.00122</v>
+        <v>0.0092</v>
       </c>
       <c r="M32" t="n">
-        <v>3295411793.224418</v>
+        <v>3320411793.153075</v>
       </c>
       <c r="N32" t="n">
-        <v>3295411793.224418</v>
+        <v>3320406787.932336</v>
       </c>
       <c r="O32" t="n">
         <v>1.65</v>
@@ -2585,19 +2585,19 @@
         <v>45686.67436342593</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.00174061455464163</v>
+        <v>0.001765859031478493</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2616,34 +2616,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="F33" t="n">
-        <v>3133561597</v>
+        <v>3186108462</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>258953884</v>
+        <v>367243361</v>
       </c>
       <c r="I33" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="J33" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="K33" t="n">
-        <v>0.107905</v>
+        <v>0.140426</v>
       </c>
       <c r="L33" t="n">
-        <v>4.63364</v>
+        <v>6.11029</v>
       </c>
       <c r="M33" t="n">
-        <v>1306297396</v>
+        <v>1306324632</v>
       </c>
       <c r="N33" t="n">
-        <v>1306297390</v>
+        <v>1306324630</v>
       </c>
       <c r="O33" t="n">
         <v>20.44</v>
@@ -2652,19 +2652,19 @@
         <v>44577.59010416667</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001637969252237828</v>
+        <v>0.001679995463923253</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2683,31 +2683,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5.25e-06</v>
+        <v>5.21e-06</v>
       </c>
       <c r="F34" t="n">
-        <v>3091601517</v>
+        <v>3070281412</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>64690922</v>
+        <v>70179974</v>
       </c>
       <c r="I34" t="n">
-        <v>5.28e-06</v>
+        <v>5.39e-06</v>
       </c>
       <c r="J34" t="n">
-        <v>5.12e-06</v>
+        <v>5.19e-06</v>
       </c>
       <c r="K34" t="n">
-        <v>3.9627e-08</v>
+        <v>5.8736e-08</v>
       </c>
       <c r="L34" t="n">
-        <v>0.72497</v>
+        <v>1.1407</v>
       </c>
       <c r="M34" t="n">
-        <v>589239233105565.5</v>
+        <v>589239232074943.9</v>
       </c>
       <c r="N34" t="n">
         <v>589496238721205.9</v>
@@ -2719,19 +2719,19 @@
         <v>44496.82980324074</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R34" t="b">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001611301352130204</v>
+        <v>0.00160597136705874</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.723262</v>
+        <v>0.719072</v>
       </c>
       <c r="F35" t="n">
-        <v>2962996213</v>
+        <v>2945764651</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>410097418</v>
+        <v>491009920</v>
       </c>
       <c r="I35" t="n">
-        <v>0.729503</v>
+        <v>0.7470830000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>0.694705</v>
+        <v>0.706761</v>
       </c>
       <c r="K35" t="n">
-        <v>0.01047564</v>
+        <v>0.01781222</v>
       </c>
       <c r="L35" t="n">
-        <v>1.42339</v>
+        <v>2.54003</v>
       </c>
       <c r="M35" t="n">
         <v>4096537146.540959</v>
@@ -2786,153 +2786,153 @@
         <v>45661.62243055556</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001529565726259552</v>
+        <v>0.001526393748725895</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>crypto-com-chain</t>
+          <t>paypal-usd</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>cro</t>
+          <t>pyusd</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cronos</t>
+          <t>PayPal USD</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.058793</v>
+        <v>0.999903</v>
       </c>
       <c r="F36" t="n">
-        <v>2854726058</v>
+        <v>2872990937</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>6464607</v>
+        <v>91650449</v>
       </c>
       <c r="I36" t="n">
-        <v>0.060149</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0.057043</v>
+        <v>0.999634</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0010674</v>
+        <v>0.00019089</v>
       </c>
       <c r="L36" t="n">
-        <v>1.82224</v>
+        <v>0.01909</v>
       </c>
       <c r="M36" t="n">
-        <v>48554394464.2072</v>
+        <v>2873226914.536399</v>
       </c>
       <c r="N36" t="n">
-        <v>98921008561.1628</v>
+        <v>2873226914.536399</v>
       </c>
       <c r="O36" t="n">
-        <v>0.891544</v>
+        <v>1.021</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>44523.66666666666</v>
+        <v>45222.61454861111</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001460754187335485</v>
+        <v>0.001479884678052625</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>paypal-usd</t>
+          <t>crypto-com-chain</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>pyusd</t>
+          <t>cro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PayPal USD</t>
+          <t>Cronos</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.999815</v>
+        <v>0.059086</v>
       </c>
       <c r="F37" t="n">
-        <v>2769193648</v>
+        <v>2868915956</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>45935786</v>
+        <v>7181516</v>
       </c>
       <c r="I37" t="n">
-        <v>0.999867</v>
+        <v>0.060149</v>
       </c>
       <c r="J37" t="n">
-        <v>0.999611</v>
+        <v>0.057738</v>
       </c>
       <c r="K37" t="n">
-        <v>3.682e-05</v>
+        <v>0.00173643</v>
       </c>
       <c r="L37" t="n">
-        <v>0.00343</v>
+        <v>3.0278</v>
       </c>
       <c r="M37" t="n">
-        <v>2769773922.446399</v>
+        <v>48555221292.30435</v>
       </c>
       <c r="N37" t="n">
-        <v>2769776124.406399</v>
+        <v>98921836999.88431</v>
       </c>
       <c r="O37" t="n">
-        <v>1.021</v>
+        <v>0.891544</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>45222.61454861111</v>
+        <v>44523.66666666666</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001406393715052202</v>
+        <v>0.001477280391849488</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2954,7 +2954,7 @@
         <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>2750834099</v>
+        <v>2726116192</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
@@ -2975,10 +2975,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>2750834099.470449</v>
+        <v>2726116192.030449</v>
       </c>
       <c r="N38" t="n">
-        <v>2750834099.470449</v>
+        <v>2726116192.030449</v>
       </c>
       <c r="O38" t="n">
         <v>1</v>
@@ -2987,19 +2987,19 @@
         <v>45699.87511574074</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R38" t="b">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001394725228749196</v>
+        <v>0.001386018259536133</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3018,16 +3018,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4294.27</v>
+        <v>4298.39</v>
       </c>
       <c r="F39" t="n">
-        <v>2674779549</v>
+        <v>2677383681</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>224100656</v>
+        <v>224742458</v>
       </c>
       <c r="I39" t="n">
         <v>4353.59</v>
@@ -3036,10 +3036,10 @@
         <v>4259.22</v>
       </c>
       <c r="K39" t="n">
-        <v>-51.30744412156491</v>
+        <v>-41.33995619151119</v>
       </c>
       <c r="L39" t="n">
-        <v>-1.19023</v>
+        <v>-0.95259</v>
       </c>
       <c r="M39" t="n">
         <v>622823.6595320001</v>
@@ -3054,19 +3054,19 @@
         <v>46050.66666666666</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001346388449073602</v>
+        <v>0.001354873720201712</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3085,28 +3085,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>233.18</v>
+        <v>232.45</v>
       </c>
       <c r="F40" t="n">
-        <v>2644200474</v>
+        <v>2636345004</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>156673045</v>
+        <v>167213088</v>
       </c>
       <c r="I40" t="n">
-        <v>238.03</v>
+        <v>241.79</v>
       </c>
       <c r="J40" t="n">
-        <v>229.94</v>
+        <v>230.68</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.7483804272891348</v>
+        <v>-0.258092428543506</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.3765</v>
+        <v>-0.11091</v>
       </c>
       <c r="M40" t="n">
         <v>11339645.9251</v>
@@ -3121,19 +3121,19 @@
         <v>45358.44833333333</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001326953793146265</v>
+        <v>0.001328646245691747</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3188,19 +3188,19 @@
         <v>46279.50347222222</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001302411122967606</v>
+        <v>0.00130898733438703</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3219,34 +3219,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1.093</v>
+        <v>1.099</v>
       </c>
       <c r="F42" t="n">
-        <v>2479136714</v>
+        <v>2497076821</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
       </c>
       <c r="H42" t="n">
-        <v>2141286</v>
+        <v>2469543</v>
       </c>
       <c r="I42" t="n">
         <v>1.17</v>
       </c>
       <c r="J42" t="n">
-        <v>1.09</v>
+        <v>1.073</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.04632907166194666</v>
+        <v>-0.03170530368788538</v>
       </c>
       <c r="L42" t="n">
-        <v>-4.04612</v>
+        <v>-2.80488</v>
       </c>
       <c r="M42" t="n">
-        <v>2272737750.694923</v>
+        <v>2272876618.22503</v>
       </c>
       <c r="N42" t="n">
-        <v>5414112177.517013</v>
+        <v>5414281884.44665</v>
       </c>
       <c r="O42" t="n">
         <v>5.64</v>
@@ -3255,153 +3255,153 @@
         <v>46205.17638888889</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001222046846756533</v>
+        <v>0.001239641117195971</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>okb</t>
+          <t>ripple-usd</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>okb</t>
+          <t>rlusd</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>OKB</t>
+          <t>Ripple USD</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>113.8</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>2389910882</v>
+        <v>2382483240</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>14273148</v>
+        <v>277638174</v>
       </c>
       <c r="I43" t="n">
-        <v>114.32</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>111.76</v>
+        <v>0.999817</v>
       </c>
       <c r="K43" t="n">
-        <v>0.9231470000000001</v>
+        <v>-1.1304607067109e-05</v>
       </c>
       <c r="L43" t="n">
-        <v>0.82967</v>
+        <v>-0.00113</v>
       </c>
       <c r="M43" t="n">
-        <v>21000000</v>
+        <v>2382406353.107469</v>
       </c>
       <c r="N43" t="n">
-        <v>21000000</v>
+        <v>2382406353.107468</v>
       </c>
       <c r="O43" t="n">
-        <v>228.74</v>
+        <v>1.073</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>45934.66666666666</v>
+        <v>45652.11518518518</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001165339005046135</v>
+        <v>0.001166405320031186</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ripple-usd</t>
+          <t>okb</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>rlusd</t>
+          <t>okb</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ripple USD</t>
+          <t>OKB</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.999982</v>
+        <v>112.52</v>
       </c>
       <c r="F44" t="n">
-        <v>2382381916</v>
+        <v>2363000637</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>158954239</v>
+        <v>15641178</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>114.57</v>
       </c>
       <c r="J44" t="n">
-        <v>0.999817</v>
+        <v>112.9</v>
       </c>
       <c r="K44" t="n">
-        <v>4.732e-05</v>
+        <v>-1.207969078914175</v>
       </c>
       <c r="L44" t="n">
-        <v>0.00722</v>
+        <v>-1.06215</v>
       </c>
       <c r="M44" t="n">
-        <v>2382406353.107468</v>
+        <v>21000000</v>
       </c>
       <c r="N44" t="n">
-        <v>2382406353.107467</v>
+        <v>21000000</v>
       </c>
       <c r="O44" t="n">
-        <v>1.073</v>
+        <v>228.74</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>45652.11518518518</v>
+        <v>45934.66666666666</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001160553939974722</v>
+        <v>0.00115395415174498</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3423,13 +3423,13 @@
         <v>1.15</v>
       </c>
       <c r="F45" t="n">
-        <v>2231380367</v>
+        <v>2230402772</v>
       </c>
       <c r="G45" t="n">
         <v>44</v>
       </c>
       <c r="H45" t="n">
-        <v>726746</v>
+        <v>2204246</v>
       </c>
       <c r="I45" t="n">
         <v>1.15</v>
@@ -3438,16 +3438,16 @@
         <v>1.14</v>
       </c>
       <c r="K45" t="n">
-        <v>0.00141936</v>
+        <v>0.00021521</v>
       </c>
       <c r="L45" t="n">
-        <v>0.21073</v>
+        <v>0.01879</v>
       </c>
       <c r="M45" t="n">
-        <v>1947116570.988323</v>
+        <v>1947118142.176293</v>
       </c>
       <c r="N45" t="n">
-        <v>1947116570.988323</v>
+        <v>1948863759.674766</v>
       </c>
       <c r="O45" t="n">
         <v>1.26</v>
@@ -3456,19 +3456,19 @@
         <v>45377.89175925926</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.001064584289182148</v>
+        <v>0.001069211967576535</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3487,31 +3487,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>126.12</v>
+        <v>128.27</v>
       </c>
       <c r="F46" t="n">
-        <v>1945834087</v>
+        <v>1979215256</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>185533365</v>
+        <v>228704407</v>
       </c>
       <c r="I46" t="n">
-        <v>127.47</v>
+        <v>133.48</v>
       </c>
       <c r="J46" t="n">
-        <v>123.98</v>
+        <v>124.84</v>
       </c>
       <c r="K46" t="n">
-        <v>0.234178</v>
+        <v>3.74</v>
       </c>
       <c r="L46" t="n">
-        <v>0.18402</v>
+        <v>3.00696</v>
       </c>
       <c r="M46" t="n">
-        <v>15427704.87209198</v>
+        <v>15427712.70066378</v>
       </c>
       <c r="N46" t="n">
         <v>16000000</v>
@@ -3523,86 +3523,86 @@
         <v>44334.55554398148</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0008831041854467962</v>
+        <v>0.0009086801313988863</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>mantle</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>mnt</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>Mantle</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.715265</v>
+        <v>0.573255</v>
       </c>
       <c r="F47" t="n">
-        <v>1936792837</v>
+        <v>1893106394</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>38053504</v>
+        <v>25943886</v>
       </c>
       <c r="I47" t="n">
-        <v>0.782873</v>
+        <v>0.576697</v>
       </c>
       <c r="J47" t="n">
-        <v>0.550861</v>
+        <v>0.556098</v>
       </c>
       <c r="K47" t="n">
-        <v>0.02832656</v>
+        <v>0.01612117</v>
       </c>
       <c r="L47" t="n">
-        <v>4.56831</v>
+        <v>2.89359</v>
       </c>
       <c r="M47" t="n">
-        <v>2708142280.000001</v>
+        <v>3302294382.53684</v>
       </c>
       <c r="N47" t="n">
-        <v>10000000000</v>
+        <v>6219316794.889999</v>
       </c>
       <c r="O47" t="n">
-        <v>0.782873</v>
+        <v>2.86</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>46279.42037037037</v>
+        <v>45938.71164351852</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0008773579821066677</v>
+        <v>0.0008536486794057554</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3621,28 +3621,28 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.697187</v>
+        <v>0.697497</v>
       </c>
       <c r="F48" t="n">
-        <v>1884268718</v>
+        <v>1885521352</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>82042332</v>
+        <v>86647040</v>
       </c>
       <c r="I48" t="n">
-        <v>0.704145</v>
+        <v>0.7098100000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>0.681949</v>
+        <v>0.689983</v>
       </c>
       <c r="K48" t="n">
-        <v>-8.60094681809e-07</v>
+        <v>0.00743343</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.01662</v>
+        <v>1.07721</v>
       </c>
       <c r="M48" t="n">
         <v>2704071066.799731</v>
@@ -3657,555 +3657,555 @@
         <v>45924.13766203704</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0008439760638945729</v>
+        <v>0.0008488011426366726</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>mantle</t>
+          <t>pax-gold</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>mnt</t>
+          <t>paxg</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mantle</t>
+          <t>PAX Gold</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.567269</v>
+        <v>4302.53</v>
       </c>
       <c r="F49" t="n">
-        <v>1873306634</v>
+        <v>1862712407</v>
       </c>
       <c r="G49" t="n">
         <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>24085849</v>
+        <v>139692866</v>
       </c>
       <c r="I49" t="n">
-        <v>0.572306</v>
+        <v>4357.16</v>
       </c>
       <c r="J49" t="n">
-        <v>0.555812</v>
+        <v>4266.85</v>
       </c>
       <c r="K49" t="n">
-        <v>0.00040073</v>
+        <v>-39.15537911431238</v>
       </c>
       <c r="L49" t="n">
-        <v>0.02702</v>
+        <v>-0.90185</v>
       </c>
       <c r="M49" t="n">
-        <v>3302294382.53684</v>
+        <v>432906.598539</v>
       </c>
       <c r="N49" t="n">
-        <v>6219316794.889999</v>
+        <v>432906.598539</v>
       </c>
       <c r="O49" t="n">
-        <v>2.86</v>
+        <v>5619.09</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>45938.71164351852</v>
+        <v>46050.93814814815</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R49" t="b">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0008370090666656977</v>
+        <v>0.0008342241370576014</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>pax-gold</t>
+          <t>world-liberty-financial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>paxg</t>
+          <t>wlfi</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>PAX Gold</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4299.21</v>
+        <v>0.057452</v>
       </c>
       <c r="F50" t="n">
-        <v>1861295293</v>
+        <v>1826519621</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>121881672</v>
+        <v>35019422</v>
       </c>
       <c r="I50" t="n">
-        <v>4357.16</v>
+        <v>0.058603</v>
       </c>
       <c r="J50" t="n">
-        <v>4266.85</v>
+        <v>0.056864</v>
       </c>
       <c r="K50" t="n">
-        <v>-48.52037737387218</v>
+        <v>0.00054135</v>
       </c>
       <c r="L50" t="n">
-        <v>-1.09767</v>
+        <v>0.95124</v>
       </c>
       <c r="M50" t="n">
-        <v>432905.428702</v>
+        <v>31777350471</v>
       </c>
       <c r="N50" t="n">
-        <v>432906.598539</v>
+        <v>100000000000</v>
       </c>
       <c r="O50" t="n">
-        <v>5619.09</v>
+        <v>0.331336</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>46050.93814814815</v>
+        <v>45901.18065972222</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R50" t="b">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.000829375209867841</v>
+        <v>0.0008110936308704838</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>world-liberty-financial</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>wlfi</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>World Liberty Financial</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.05717</v>
+        <v>0.00368359</v>
       </c>
       <c r="F51" t="n">
-        <v>1816457741</v>
+        <v>1726347329</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>32945175</v>
+        <v>114464800</v>
       </c>
       <c r="I51" t="n">
-        <v>0.058201</v>
+        <v>0.00380079</v>
       </c>
       <c r="J51" t="n">
-        <v>0.056363</v>
+        <v>0.00354774</v>
       </c>
       <c r="K51" t="n">
-        <v>0.00019241</v>
+        <v>0.00018135</v>
       </c>
       <c r="L51" t="n">
-        <v>0.32666</v>
+        <v>5.17824</v>
       </c>
       <c r="M51" t="n">
-        <v>31777274001</v>
+        <v>468546701392.5829</v>
       </c>
       <c r="N51" t="n">
-        <v>100000000000</v>
+        <v>834058521647.854</v>
       </c>
       <c r="O51" t="n">
-        <v>0.331336</v>
+        <v>0.00881908</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>45901.18065972222</v>
+        <v>45914.36296296296</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S51" t="n">
-        <v>0.000800878520685971</v>
+        <v>0.0007470743586352999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>polkadot</t>
+          <t>ondo-finance</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>dot</t>
+          <t>ondo</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Ondo</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1.011</v>
+        <v>0.353999</v>
       </c>
       <c r="F52" t="n">
-        <v>1720896263</v>
+        <v>1723853332</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>125697957</v>
+        <v>107834998</v>
       </c>
       <c r="I52" t="n">
-        <v>1.027</v>
+        <v>0.365023</v>
       </c>
       <c r="J52" t="n">
-        <v>0.997945</v>
+        <v>0.344342</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.008389516963648314</v>
+        <v>0.01173941</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.88369</v>
+        <v>3.42997</v>
       </c>
       <c r="M52" t="n">
-        <v>1702723763.976507</v>
+        <v>4869330647</v>
       </c>
       <c r="N52" t="n">
-        <v>1702742182.32487</v>
+        <v>10000000000</v>
       </c>
       <c r="O52" t="n">
-        <v>54.98</v>
+        <v>2.14</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>44504.25704861111</v>
+        <v>45641.69166666667</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R52" t="b">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0007401440333007966</v>
+        <v>0.0007454804660557357</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ondo-finance</t>
+          <t>polkadot</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ondo</t>
+          <t>dot</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ondo</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.351009</v>
+        <v>0.992134</v>
       </c>
       <c r="F53" t="n">
-        <v>1709601855</v>
+        <v>1689505775</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>82945240</v>
+        <v>136435235</v>
       </c>
       <c r="I53" t="n">
-        <v>0.358278</v>
+        <v>1.036</v>
       </c>
       <c r="J53" t="n">
-        <v>0.339718</v>
+        <v>0.9884849999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>0.00591865</v>
+        <v>-0.01550569575868166</v>
       </c>
       <c r="L53" t="n">
-        <v>1.65097</v>
+        <v>-1.53881</v>
       </c>
       <c r="M53" t="n">
-        <v>4869330647</v>
+        <v>1702798500.775251</v>
       </c>
       <c r="N53" t="n">
-        <v>10000000000</v>
+        <v>1702806667.802638</v>
       </c>
       <c r="O53" t="n">
-        <v>2.14</v>
+        <v>54.98</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>45641.69166666667</v>
+        <v>44504.25704861111</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R53" t="b">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0007329658261973127</v>
+        <v>0.0007235292302569531</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.00361277</v>
+        <v>0.621812</v>
       </c>
       <c r="F54" t="n">
-        <v>1693432142</v>
+        <v>1678535453</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>103892831</v>
+        <v>32002995</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0036761</v>
+        <v>0.782873</v>
       </c>
       <c r="J54" t="n">
-        <v>0.00346727</v>
+        <v>0.550861</v>
       </c>
       <c r="K54" t="n">
-        <v>-4.0926702022416e-05</v>
+        <v>-0.05165533995442673</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.17425</v>
+        <v>-7.67006</v>
       </c>
       <c r="M54" t="n">
-        <v>468637942893.683</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N54" t="n">
-        <v>834149763148.9541</v>
+        <v>10000000000</v>
       </c>
       <c r="O54" t="n">
-        <v>0.00881908</v>
+        <v>0.782873</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>45914.36296296296</v>
+        <v>46279.42037037037</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0007226890991021081</v>
+        <v>0.0007165181894131875</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>htx-dao</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>htx</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>USDD</t>
+          <t>HTX DAO</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.999225</v>
+        <v>1.7e-06</v>
       </c>
       <c r="F55" t="n">
-        <v>1529381392</v>
+        <v>1526676591</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>2853415</v>
+        <v>85564279</v>
       </c>
       <c r="I55" t="n">
-        <v>0.99962</v>
+        <v>1.71e-06</v>
       </c>
       <c r="J55" t="n">
-        <v>0.998611</v>
+        <v>1.69e-06</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.00014378888773503</v>
+        <v>7.322e-09</v>
       </c>
       <c r="L55" t="n">
-        <v>0.02166</v>
+        <v>0.43269</v>
       </c>
       <c r="M55" t="n">
-        <v>1530867781</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="N55" t="n">
-        <v>1532088633</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="O55" t="n">
-        <v>1.24</v>
+        <v>3.75e-06</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>46212.39942129629</v>
+        <v>45629.67800925926</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R55" t="b">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0006184259753525633</v>
+        <v>0.0006194664634957727</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>htx-dao</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>htx</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>HTX DAO</t>
+          <t>USDD</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1.7e-06</v>
+        <v>0.999385</v>
       </c>
       <c r="F56" t="n">
-        <v>1525555129</v>
+        <v>1521785559</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>105375559</v>
+        <v>3081524</v>
       </c>
       <c r="I56" t="n">
-        <v>1.71e-06</v>
+        <v>0.999766</v>
       </c>
       <c r="J56" t="n">
-        <v>1.69e-06</v>
+        <v>0.998611</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.019953681e-09</v>
+        <v>0.00042834</v>
       </c>
       <c r="L56" t="n">
-        <v>-0.1775</v>
+        <v>0.04288</v>
       </c>
       <c r="M56" t="n">
-        <v>898232728634017.2</v>
+        <v>1522697852</v>
       </c>
       <c r="N56" t="n">
-        <v>898232728634017.2</v>
+        <v>1527853807</v>
       </c>
       <c r="O56" t="n">
-        <v>3.75e-06</v>
+        <v>1.24</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>45629.67800925926</v>
+        <v>46212.39942129629</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R56" t="b">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0006159941782856965</v>
+        <v>0.0006163406459381691</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4227,13 +4227,13 @@
         <v>2.73</v>
       </c>
       <c r="F57" t="n">
-        <v>1522846678</v>
+        <v>1519711785</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>46433404</v>
+        <v>39738610</v>
       </c>
       <c r="I57" t="n">
         <v>2.85</v>
@@ -4242,16 +4242,16 @@
         <v>2.71</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.04371069852076781</v>
+        <v>-0.03372515551564437</v>
       </c>
       <c r="L57" t="n">
-        <v>-1.63721</v>
+        <v>-1.2212</v>
       </c>
       <c r="M57" t="n">
-        <v>556821653.0008103</v>
+        <v>556822465.3739831</v>
       </c>
       <c r="N57" t="n">
-        <v>556821653.0008103</v>
+        <v>556822835.1342702</v>
       </c>
       <c r="O57" t="n">
         <v>700.65</v>
@@ -4260,19 +4260,19 @@
         <v>44326.33741898148</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R57" t="b">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0006142728111978741</v>
+        <v>0.0006150153143558565</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4294,28 +4294,28 @@
         <v>2.18</v>
       </c>
       <c r="F58" t="n">
-        <v>1504308793</v>
+        <v>1500123106</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>15460300</v>
+        <v>17752244</v>
       </c>
       <c r="I58" t="n">
         <v>2.24</v>
       </c>
       <c r="J58" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="K58" t="n">
-        <v>0.007838299999999999</v>
+        <v>0.02762086</v>
       </c>
       <c r="L58" t="n">
-        <v>0.37484</v>
+        <v>1.28534</v>
       </c>
       <c r="M58" t="n">
-        <v>689112006.7947352</v>
+        <v>689113485.2462531</v>
       </c>
       <c r="N58" t="n">
         <v>1000000000</v>
@@ -4327,19 +4327,19 @@
         <v>45674.19883101852</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0006024909827221747</v>
+        <v>0.0006024963537871132</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4358,31 +4358,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.064161</v>
+        <v>0.063151</v>
       </c>
       <c r="F59" t="n">
-        <v>1503637857</v>
+        <v>1479524760</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>11248975</v>
+        <v>11887885</v>
       </c>
       <c r="I59" t="n">
-        <v>0.06504799999999999</v>
+        <v>0.065204</v>
       </c>
       <c r="J59" t="n">
-        <v>0.061748</v>
+        <v>0.062163</v>
       </c>
       <c r="K59" t="n">
-        <v>0.0015437</v>
+        <v>0.00123391</v>
       </c>
       <c r="L59" t="n">
-        <v>2.47851</v>
+        <v>1.99282</v>
       </c>
       <c r="M59" t="n">
-        <v>23427652317.1642</v>
+        <v>23427036695.42831</v>
       </c>
       <c r="N59" t="n">
         <v>23459804203.60596</v>
@@ -4394,19 +4394,19 @@
         <v>45630.09302083333</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R59" t="b">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0006020645666088925</v>
+        <v>0.0005893321235010726</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4428,25 +4428,25 @@
         <v>3.45e-06</v>
       </c>
       <c r="F60" t="n">
-        <v>1451129135</v>
+        <v>1452076193</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>170040252</v>
+        <v>202273322</v>
       </c>
       <c r="I60" t="n">
-        <v>3.47e-06</v>
+        <v>3.58e-06</v>
       </c>
       <c r="J60" t="n">
-        <v>3.34e-06</v>
+        <v>3.39e-06</v>
       </c>
       <c r="K60" t="n">
-        <v>4.1828e-08</v>
+        <v>9.014e-08</v>
       </c>
       <c r="L60" t="n">
-        <v>1.21699</v>
+        <v>2.68021</v>
       </c>
       <c r="M60" t="n">
         <v>420690000000000</v>
@@ -4461,19 +4461,19 @@
         <v>45635.35457175926</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0005686924340229918</v>
+        <v>0.0005717899743882351</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4492,28 +4492,28 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.141382</v>
+        <v>0.143689</v>
       </c>
       <c r="F61" t="n">
-        <v>1426794520</v>
+        <v>1451421164</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>224795572</v>
+        <v>325876097</v>
       </c>
       <c r="I61" t="n">
-        <v>0.143203</v>
+        <v>0.148653</v>
       </c>
       <c r="J61" t="n">
-        <v>0.135179</v>
+        <v>0.137803</v>
       </c>
       <c r="K61" t="n">
-        <v>0.00257779</v>
+        <v>0.00704747</v>
       </c>
       <c r="L61" t="n">
-        <v>1.79652</v>
+        <v>5.15763</v>
       </c>
       <c r="M61" t="n">
         <v>10095312500</v>
@@ -4528,19 +4528,19 @@
         <v>45393.21892361111</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0005532264701359475</v>
+        <v>0.000571371350844382</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4559,28 +4559,28 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>0.999956</v>
       </c>
       <c r="F62" t="n">
-        <v>1392029194</v>
+        <v>1391737243</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>25560451</v>
+        <v>41760343</v>
       </c>
       <c r="I62" t="n">
         <v>1</v>
       </c>
       <c r="J62" t="n">
-        <v>0.999966</v>
+        <v>0.999939</v>
       </c>
       <c r="K62" t="n">
-        <v>7.287e-05</v>
+        <v>-0.000256610788944456</v>
       </c>
       <c r="L62" t="n">
-        <v>0.0092</v>
+        <v>-0.02566</v>
       </c>
       <c r="M62" t="n">
         <v>1391792045.16</v>
@@ -4595,19 +4595,19 @@
         <v>46092.00303240741</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.000531131225299022</v>
+        <v>0.0005332278571668866</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4626,31 +4626,31 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.383134</v>
+        <v>0.383451</v>
       </c>
       <c r="F63" t="n">
-        <v>1376538249</v>
+        <v>1378123513</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>126323707</v>
+        <v>153034511</v>
       </c>
       <c r="I63" t="n">
-        <v>0.396461</v>
+        <v>0.399039</v>
       </c>
       <c r="J63" t="n">
-        <v>0.375987</v>
+        <v>0.379332</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.009776990171701305</v>
+        <v>0.0036273</v>
       </c>
       <c r="L63" t="n">
-        <v>-2.56148</v>
+        <v>0.955</v>
       </c>
       <c r="M63" t="n">
-        <v>3592836116.582616</v>
+        <v>3594239151.909092</v>
       </c>
       <c r="N63" t="n">
         <v>10000000000</v>
@@ -4662,220 +4662,220 @@
         <v>45360.67409722223</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0005212858919766666</v>
+        <v>0.000524527436425727</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>bitget-token</t>
+          <t>spiko-amundi-overnight-swap-fund-eur</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>bgb</t>
+          <t>eursafo</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Bitget Token</t>
+          <t>Spiko Amundi Overnight Swap Fund (EUR)</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1.94</v>
+        <v>1.17</v>
       </c>
       <c r="F64" t="n">
-        <v>1358673919</v>
+        <v>1375639431</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>10471507</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>1.95</v>
+        <v>1.17</v>
       </c>
       <c r="J64" t="n">
-        <v>1.92</v>
+        <v>1.17</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.0009659930391829891</v>
+        <v>-0.004895468671041181</v>
       </c>
       <c r="L64" t="n">
-        <v>-0.09539</v>
+        <v>-0.41727</v>
       </c>
       <c r="M64" t="n">
-        <v>699992029.6481038</v>
+        <v>1177453283.40974</v>
       </c>
       <c r="N64" t="n">
-        <v>910920874.6481038</v>
+        <v>1177453283.40974</v>
       </c>
       <c r="O64" t="n">
-        <v>8.449999999999999</v>
+        <v>1.18</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>45653.15375</v>
+        <v>46255.48263888889</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R64" t="b">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0005099321441303891</v>
+        <v>0.0005229398804395616</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>falcon-finance</t>
+          <t>bitget-token</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>usdf</t>
+          <t>bgb</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Falcon USD</t>
+          <t>Bitget Token</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.996299</v>
+        <v>1.94</v>
       </c>
       <c r="F65" t="n">
-        <v>1339540722</v>
+        <v>1358577952</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>608010</v>
+        <v>11750541</v>
       </c>
       <c r="I65" t="n">
-        <v>0.997239</v>
+        <v>1.96</v>
       </c>
       <c r="J65" t="n">
-        <v>0.996238</v>
+        <v>1.93</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.000211135080925851</v>
+        <v>0.01663887</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.0215</v>
+        <v>0.86469</v>
       </c>
       <c r="M65" t="n">
-        <v>1344517433.482414</v>
+        <v>699992029.6481038</v>
       </c>
       <c r="N65" t="n">
-        <v>1344517433.482414</v>
+        <v>910920874.6481038</v>
       </c>
       <c r="O65" t="n">
-        <v>1.075</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>45785.55951388889</v>
+        <v>45653.15375</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0004977719626832733</v>
+        <v>0.0005120360322093955</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>spiko-amundi-overnight-swap-fund-eur</t>
+          <t>falcon-finance</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>eursafo</t>
+          <t>usdf</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Spiko Amundi Overnight Swap Fund (EUR)</t>
+          <t>Falcon USD</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1.17</v>
+        <v>0.996285</v>
       </c>
       <c r="F66" t="n">
-        <v>1328135582</v>
+        <v>1339542714</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>610664</v>
       </c>
       <c r="I66" t="n">
-        <v>1.18</v>
+        <v>0.997106</v>
       </c>
       <c r="J66" t="n">
-        <v>1.17</v>
+        <v>0.996221</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.006505837321536312</v>
+        <v>-0.00024087761769287</v>
       </c>
       <c r="L66" t="n">
-        <v>-0.55337</v>
+        <v>-0.02417</v>
       </c>
       <c r="M66" t="n">
-        <v>1135960146.90006</v>
+        <v>1344517433.482414</v>
       </c>
       <c r="N66" t="n">
-        <v>1135960146.90006</v>
+        <v>1344517433.482414</v>
       </c>
       <c r="O66" t="n">
-        <v>1.18</v>
+        <v>1.075</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>46255.48263888889</v>
+        <v>45785.55951388889</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0004905233794052275</v>
+        <v>0.0004998707711451532</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4894,28 +4894,28 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.999593</v>
+        <v>0.999714</v>
       </c>
       <c r="F67" t="n">
-        <v>1319462832</v>
+        <v>1319775637</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
       </c>
       <c r="H67" t="n">
-        <v>4321338</v>
+        <v>4661439</v>
       </c>
       <c r="I67" t="n">
-        <v>0.999707</v>
+        <v>0.999887</v>
       </c>
       <c r="J67" t="n">
         <v>0.999053</v>
       </c>
       <c r="K67" t="n">
-        <v>0.00041378</v>
+        <v>0.00059451</v>
       </c>
       <c r="L67" t="n">
-        <v>0.04109</v>
+        <v>0.0595</v>
       </c>
       <c r="M67" t="n">
         <v>1320000000</v>
@@ -4930,19 +4930,19 @@
         <v>45940.56990740741</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.000485011377744163</v>
+        <v>0.0004872377979098313</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4961,28 +4961,28 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.999765</v>
+        <v>0.999865</v>
       </c>
       <c r="F68" t="n">
-        <v>1314958390</v>
+        <v>1315117304</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>174732986</v>
+        <v>210457416</v>
       </c>
       <c r="I68" t="n">
-        <v>0.999831</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
-        <v>0.999084</v>
+        <v>0.999121</v>
       </c>
       <c r="K68" t="n">
-        <v>0.0004305</v>
+        <v>0.00050696</v>
       </c>
       <c r="L68" t="n">
-        <v>0.04722</v>
+        <v>0.05073</v>
       </c>
       <c r="M68" t="n">
         <v>1315244007.8</v>
@@ -4997,19 +4997,19 @@
         <v>46058.54591435185</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0004821485612458011</v>
+        <v>0.000484260696332789</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5028,34 +5028,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>7.61</v>
+        <v>7.54</v>
       </c>
       <c r="F69" t="n">
-        <v>1203865987</v>
+        <v>1192445170</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>49212991</v>
+        <v>45235742</v>
       </c>
       <c r="I69" t="n">
-        <v>7.69</v>
+        <v>7.76</v>
       </c>
       <c r="J69" t="n">
-        <v>7.4</v>
+        <v>7.53</v>
       </c>
       <c r="K69" t="n">
-        <v>0.02530351</v>
+        <v>0.03071381</v>
       </c>
       <c r="L69" t="n">
-        <v>0.27311</v>
+        <v>0.40915</v>
       </c>
       <c r="M69" t="n">
-        <v>158165250.3413957</v>
+        <v>158170028.1227235</v>
       </c>
       <c r="N69" t="n">
-        <v>158165720.1525957</v>
+        <v>158170028.1227235</v>
       </c>
       <c r="O69" t="n">
         <v>167.09</v>
@@ -5064,153 +5064,153 @@
         <v>44322.44053240741</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0004115433310860895</v>
+        <v>0.0004058619636551243</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>lighter</t>
+          <t>pi-network</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>lit</t>
+          <t>pi</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Lighter</t>
+          <t>Pi Network</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4.39</v>
+        <v>0.09816800000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>1097273231</v>
+        <v>1098844648</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>94634914</v>
+        <v>5260698</v>
       </c>
       <c r="I70" t="n">
-        <v>4.69</v>
+        <v>0.09867099999999999</v>
       </c>
       <c r="J70" t="n">
-        <v>4.09</v>
+        <v>0.096938</v>
       </c>
       <c r="K70" t="n">
-        <v>0.304136</v>
+        <v>0.00097241</v>
       </c>
       <c r="L70" t="n">
-        <v>7.4937</v>
+        <v>1.00046</v>
       </c>
       <c r="M70" t="n">
-        <v>250000000</v>
+        <v>11193100322.87027</v>
       </c>
       <c r="N70" t="n">
-        <v>1000000000</v>
+        <v>17220154342.87733</v>
       </c>
       <c r="O70" t="n">
-        <v>7.86</v>
+        <v>2.99</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>46021.04538194444</v>
+        <v>45714.36184027778</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0003437978699429186</v>
+        <v>0.0003460426545464406</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>pi-network</t>
+          <t>lighter</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>pi</t>
+          <t>lit</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Pi Network</t>
+          <t>Lighter</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.097383</v>
+        <v>4.37</v>
       </c>
       <c r="F71" t="n">
-        <v>1089901574</v>
+        <v>1091394927</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>4589866</v>
+        <v>117268467</v>
       </c>
       <c r="I71" t="n">
-        <v>0.098366</v>
+        <v>4.69</v>
       </c>
       <c r="J71" t="n">
-        <v>0.09639</v>
+        <v>4.21</v>
       </c>
       <c r="K71" t="n">
-        <v>-7.499999479311499e-05</v>
+        <v>0.178989</v>
       </c>
       <c r="L71" t="n">
-        <v>-0.05854</v>
+        <v>4.2755</v>
       </c>
       <c r="M71" t="n">
-        <v>11193062149.394</v>
+        <v>250000000</v>
       </c>
       <c r="N71" t="n">
-        <v>17220095483.28307</v>
+        <v>1000000000</v>
       </c>
       <c r="O71" t="n">
-        <v>2.99</v>
+        <v>7.86</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>45714.36184027778</v>
+        <v>46021.04538194444</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R71" t="b">
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0003391127832485255</v>
+        <v>0.0003412816002942811</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5229,34 +5229,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>22.14</v>
+        <v>22.71</v>
       </c>
       <c r="F72" t="n">
-        <v>1062019823</v>
+        <v>1090563974</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>34807612</v>
+        <v>45172293</v>
       </c>
       <c r="I72" t="n">
         <v>23.28</v>
       </c>
       <c r="J72" t="n">
-        <v>21.22</v>
+        <v>21.47</v>
       </c>
       <c r="K72" t="n">
-        <v>0.580173</v>
+        <v>1.49</v>
       </c>
       <c r="L72" t="n">
-        <v>2.65269</v>
+        <v>6.99935</v>
       </c>
       <c r="M72" t="n">
-        <v>47963017.79499942</v>
+        <v>47972447.24318358</v>
       </c>
       <c r="N72" t="n">
-        <v>81007441.11135192</v>
+        <v>81010558.97664872</v>
       </c>
       <c r="O72" t="n">
         <v>29.19</v>
@@ -5265,19 +5265,19 @@
         <v>46274.32083333333</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0003213924225987449</v>
+        <v>0.0003407505451965137</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5296,34 +5296,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.097994</v>
+        <v>0.096807</v>
       </c>
       <c r="F73" t="n">
-        <v>1049927178</v>
+        <v>1037331940</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>59452758</v>
+        <v>59166159</v>
       </c>
       <c r="I73" t="n">
         <v>0.09861499999999999</v>
       </c>
       <c r="J73" t="n">
-        <v>0.095473</v>
+        <v>0.09566</v>
       </c>
       <c r="K73" t="n">
-        <v>0.00083642</v>
+        <v>0.0008951</v>
       </c>
       <c r="L73" t="n">
-        <v>0.8908199999999999</v>
+        <v>0.93325</v>
       </c>
       <c r="M73" t="n">
-        <v>10714103973.39043</v>
+        <v>10714685269.72835</v>
       </c>
       <c r="N73" t="n">
-        <v>10714103973.39043</v>
+        <v>10714685269.72835</v>
       </c>
       <c r="O73" t="n">
         <v>1.29</v>
@@ -5332,19 +5332,19 @@
         <v>45364.45493055556</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R73" t="b">
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003137068927118391</v>
+        <v>0.0003067303984250036</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5363,34 +5363,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>9.300000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="F74" t="n">
-        <v>992009996</v>
+        <v>995839693</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>3232039</v>
+        <v>3290086</v>
       </c>
       <c r="I74" t="n">
-        <v>9.32</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="J74" t="n">
-        <v>9.050000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="K74" t="n">
-        <v>0.104809</v>
+        <v>0.233148</v>
       </c>
       <c r="L74" t="n">
-        <v>1.12118</v>
+        <v>2.56047</v>
       </c>
       <c r="M74" t="n">
-        <v>106627878.3326154</v>
+        <v>106628362.8519531</v>
       </c>
       <c r="N74" t="n">
-        <v>118879110.4396606</v>
+        <v>118879637.7543574</v>
       </c>
       <c r="O74" t="n">
         <v>25.38</v>
@@ -5399,19 +5399,19 @@
         <v>45682.66666666666</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R74" t="b">
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0002768973912978503</v>
+        <v>0.0002802130511295808</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5466,287 +5466,287 @@
         <v>46273.93067129629</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R75" t="b">
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0002631304662126342</v>
+        <v>0.0002639219711529725</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>kucoin-shares</t>
+          <t>kaspa</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>kcs</t>
+          <t>kas</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>KuCoin</t>
+          <t>Kaspa</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6.97</v>
+        <v>0.03491874</v>
       </c>
       <c r="F76" t="n">
-        <v>956628458</v>
+        <v>967415813</v>
       </c>
       <c r="G76" t="n">
         <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>6421517</v>
+        <v>10871350</v>
       </c>
       <c r="I76" t="n">
-        <v>7.02</v>
+        <v>0.03532002</v>
       </c>
       <c r="J76" t="n">
-        <v>6.76</v>
+        <v>0.03324669</v>
       </c>
       <c r="K76" t="n">
-        <v>0.205323</v>
+        <v>0.0011685</v>
       </c>
       <c r="L76" t="n">
-        <v>2.99787</v>
+        <v>3.4622</v>
       </c>
       <c r="M76" t="n">
-        <v>137155021.2773955</v>
+        <v>27700473315.66705</v>
       </c>
       <c r="N76" t="n">
-        <v>142155021.2773955</v>
+        <v>27700811506.09942</v>
       </c>
       <c r="O76" t="n">
-        <v>28.83</v>
+        <v>0.207411</v>
       </c>
       <c r="P76" s="1" t="n">
-        <v>44531.29832175926</v>
+        <v>45504.69498842592</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R76" t="b">
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0002544105104092032</v>
+        <v>0.0002620475876529121</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>quant-network</t>
+          <t>kucoin-shares</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>qnt</t>
+          <t>kcs</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>KuCoin</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>64.56999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="F77" t="n">
-        <v>939384952</v>
+        <v>947096614</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>6565185</v>
+        <v>6128464</v>
       </c>
       <c r="I77" t="n">
-        <v>65.56</v>
+        <v>7.13</v>
       </c>
       <c r="J77" t="n">
-        <v>62.27</v>
+        <v>6.86</v>
       </c>
       <c r="K77" t="n">
-        <v>0.534498</v>
+        <v>0.058742</v>
       </c>
       <c r="L77" t="n">
-        <v>0.68503</v>
+        <v>0.85832</v>
       </c>
       <c r="M77" t="n">
-        <v>14544176.16408117</v>
+        <v>137155021.2773955</v>
       </c>
       <c r="N77" t="n">
-        <v>14612493</v>
+        <v>142155021.2773955</v>
       </c>
       <c r="O77" t="n">
-        <v>427.42</v>
+        <v>28.83</v>
       </c>
       <c r="P77" s="1" t="n">
-        <v>44450.05208333334</v>
+        <v>44531.29832175926</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R77" t="b">
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002434513297900715</v>
+        <v>0.0002490617578749343</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>just</t>
+          <t>quant-network</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>jst</t>
+          <t>qnt</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>JUST</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.113516</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="F78" t="n">
-        <v>930049450</v>
+        <v>938743755</v>
       </c>
       <c r="G78" t="n">
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>20636631</v>
+        <v>7167107</v>
       </c>
       <c r="I78" t="n">
-        <v>0.114356</v>
+        <v>64.78</v>
       </c>
       <c r="J78" t="n">
-        <v>0.112356</v>
+        <v>62.75</v>
       </c>
       <c r="K78" t="n">
-        <v>0.00127463</v>
+        <v>1.77</v>
       </c>
       <c r="L78" t="n">
-        <v>1.1539</v>
+        <v>2.81932</v>
       </c>
       <c r="M78" t="n">
-        <v>8188743036.341737</v>
+        <v>14544176.16408117</v>
       </c>
       <c r="N78" t="n">
-        <v>8188743036.341737</v>
+        <v>14612493</v>
       </c>
       <c r="O78" t="n">
-        <v>0.193254</v>
+        <v>427.42</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>44290.85721064815</v>
+        <v>44450.05208333334</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R78" t="b">
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002375181133903286</v>
+        <v>0.0002437235156965173</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>kaspa</t>
+          <t>just</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>kas</t>
+          <t>jst</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Kaspa</t>
+          <t>JUST</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.03346518</v>
+        <v>0.114497</v>
       </c>
       <c r="F79" t="n">
-        <v>927160821</v>
+        <v>937681089</v>
       </c>
       <c r="G79" t="n">
         <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>8749848</v>
+        <v>21798469</v>
       </c>
       <c r="I79" t="n">
-        <v>0.03483587</v>
+        <v>0.114591</v>
       </c>
       <c r="J79" t="n">
-        <v>0.0330794</v>
+        <v>0.112465</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.001137926064620966</v>
+        <v>0.00064492</v>
       </c>
       <c r="L79" t="n">
-        <v>-3.30486</v>
+        <v>0.56645</v>
       </c>
       <c r="M79" t="n">
-        <v>27698781826.54268</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="N79" t="n">
-        <v>27700079092.35108</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="O79" t="n">
-        <v>0.207411</v>
+        <v>0.193254</v>
       </c>
       <c r="P79" s="1" t="n">
-        <v>45504.69498842592</v>
+        <v>44290.85721064815</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R79" t="b">
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002356822334391944</v>
+        <v>0.0002430443747625246</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5765,28 +5765,28 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.134902</v>
+        <v>0.134013</v>
       </c>
       <c r="F80" t="n">
-        <v>900787139</v>
+        <v>895591340</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>125791092</v>
+        <v>154359503</v>
       </c>
       <c r="I80" t="n">
-        <v>0.140932</v>
+        <v>0.142061</v>
       </c>
       <c r="J80" t="n">
-        <v>0.132467</v>
+        <v>0.132131</v>
       </c>
       <c r="K80" t="n">
-        <v>-0.003846886341674016</v>
+        <v>-7.935190169344701e-05</v>
       </c>
       <c r="L80" t="n">
-        <v>-2.8211</v>
+        <v>-0.05918</v>
       </c>
       <c r="M80" t="n">
         <v>6678075931</v>
@@ -5801,19 +5801,19 @@
         <v>45303.18748842592</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R80" t="b">
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002189203321976753</v>
+        <v>0.000216145168946793</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5832,34 +5832,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.095542</v>
+        <v>0.09596499999999999</v>
       </c>
       <c r="F81" t="n">
-        <v>864028446</v>
+        <v>867575949</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>44342304</v>
+        <v>37884247</v>
       </c>
       <c r="I81" t="n">
-        <v>0.100768</v>
+        <v>0.098883</v>
       </c>
       <c r="J81" t="n">
-        <v>0.093289</v>
+        <v>0.093946</v>
       </c>
       <c r="K81" t="n">
-        <v>0.00188462</v>
+        <v>-0.001014014016988418</v>
       </c>
       <c r="L81" t="n">
-        <v>2.01466</v>
+        <v>-1.0456</v>
       </c>
       <c r="M81" t="n">
-        <v>9040751604.212919</v>
+        <v>9041305867.480665</v>
       </c>
       <c r="N81" t="n">
-        <v>9041261887.915733</v>
+        <v>9041339786.614456</v>
       </c>
       <c r="O81" t="n">
         <v>3.56</v>
@@ -5868,287 +5868,287 @@
         <v>43636.28563657407</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R81" t="b">
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0001955581948278033</v>
+        <v>0.0001982407673663228</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>cosmos</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Spiko EU T-Bills Money Market Fund</t>
+          <t>Cosmos Hub</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1.22</v>
+        <v>1.59</v>
       </c>
       <c r="F82" t="n">
-        <v>830399404</v>
+        <v>842792755</v>
       </c>
       <c r="G82" t="n">
         <v>81</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>48731093</v>
       </c>
       <c r="I82" t="n">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="J82" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.006725431564868378</v>
+        <v>0.00198646</v>
       </c>
       <c r="L82" t="n">
-        <v>-0.5470699999999999</v>
+        <v>0.12521</v>
       </c>
       <c r="M82" t="n">
-        <v>679196801.73762</v>
+        <v>530724739.158381</v>
       </c>
       <c r="N82" t="n">
-        <v>679196801.73762</v>
+        <v>530755609.732035</v>
       </c>
       <c r="O82" t="n">
-        <v>1.26</v>
+        <v>43.84</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>46049.54175925926</v>
+        <v>44458.66666666666</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R82" t="b">
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0001741851199249172</v>
+        <v>0.0001824020357982822</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NEXO</t>
+          <t>Spiko EU T-Bills Money Market Fund</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.824062</v>
+        <v>1.22</v>
       </c>
       <c r="F83" t="n">
-        <v>825837569</v>
+        <v>829733487</v>
       </c>
       <c r="G83" t="n">
         <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>3324768</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>0.83821</v>
+        <v>1.23</v>
       </c>
       <c r="J83" t="n">
-        <v>0.820778</v>
+        <v>1.22</v>
       </c>
       <c r="K83" t="n">
-        <v>-0.002100593183993915</v>
+        <v>-0.005126074567904038</v>
       </c>
       <c r="L83" t="n">
-        <v>-0.27099</v>
+        <v>-0.41785</v>
       </c>
       <c r="M83" t="n">
-        <v>1000000000</v>
+        <v>679196801.73762</v>
       </c>
       <c r="N83" t="n">
-        <v>1000000000</v>
+        <v>679196801.73762</v>
       </c>
       <c r="O83" t="n">
-        <v>4.07</v>
+        <v>1.26</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>44328.27623842593</v>
+        <v>46049.54175925926</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0001712858270711509</v>
+        <v>0.0001740559670741661</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>cosmos</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Cosmos Hub</t>
+          <t>NEXO</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1.55</v>
+        <v>0.81163</v>
       </c>
       <c r="F84" t="n">
-        <v>820417685</v>
+        <v>813181332</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>40281610</v>
+        <v>3513857</v>
       </c>
       <c r="I84" t="n">
-        <v>1.62</v>
+        <v>0.838348</v>
       </c>
       <c r="J84" t="n">
-        <v>1.53</v>
+        <v>0.813947</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.05224919617736412</v>
+        <v>-0.0110379836898139</v>
       </c>
       <c r="L84" t="n">
-        <v>-3.27084</v>
+        <v>-1.34173</v>
       </c>
       <c r="M84" t="n">
-        <v>530649765.65786</v>
+        <v>1000000000</v>
       </c>
       <c r="N84" t="n">
-        <v>530679280.827608</v>
+        <v>1000000000</v>
       </c>
       <c r="O84" t="n">
-        <v>43.84</v>
+        <v>4.07</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>44458.66666666666</v>
+        <v>44328.27623842593</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R84" t="b">
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001678411976732348</v>
+        <v>0.0001634776235435622</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>filecoin</t>
+          <t>jupiter-exchange-solana</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>jup</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.983266</v>
+        <v>0.238904</v>
       </c>
       <c r="F85" t="n">
-        <v>813568021</v>
+        <v>792971070</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>403575969</v>
+        <v>61238503</v>
       </c>
       <c r="I85" t="n">
-        <v>1.033</v>
+        <v>0.246898</v>
       </c>
       <c r="J85" t="n">
-        <v>0.937837</v>
+        <v>0.233096</v>
       </c>
       <c r="K85" t="n">
-        <v>0.02855161</v>
+        <v>0.00749233</v>
       </c>
       <c r="L85" t="n">
-        <v>2.2453</v>
+        <v>3.23766</v>
       </c>
       <c r="M85" t="n">
-        <v>827813309</v>
+        <v>3319369204.37</v>
       </c>
       <c r="N85" t="n">
-        <v>1957054313</v>
+        <v>6861487117.895551</v>
       </c>
       <c r="O85" t="n">
-        <v>236.84</v>
+        <v>2</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>44287.22894675926</v>
+        <v>45322.29359953704</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R85" t="b">
         <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001634878657605504</v>
+        <v>0.0001505614144892422</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6170,7 +6170,7 @@
         <v>11.21</v>
       </c>
       <c r="F86" t="n">
-        <v>804620334</v>
+        <v>754918574</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
@@ -6191,10 +6191,10 @@
         <v>0.009719999999999999</v>
       </c>
       <c r="M86" t="n">
-        <v>71781823.530606</v>
+        <v>67347827.99992301</v>
       </c>
       <c r="N86" t="n">
-        <v>67143413.755615</v>
+        <v>67347827.99992301</v>
       </c>
       <c r="O86" t="n">
         <v>11.21</v>
@@ -6203,86 +6203,86 @@
         <v>46279.58333333334</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R86" t="b">
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001578011267669573</v>
+        <v>0.0001262423832280602</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jupiter-exchange-solana</t>
+          <t>filecoin</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>jup</t>
+          <t>fil</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.237187</v>
+        <v>0.910478</v>
       </c>
       <c r="F87" t="n">
-        <v>788051591</v>
+        <v>753570066</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>54045582</v>
+        <v>278415645</v>
       </c>
       <c r="I87" t="n">
-        <v>0.239422</v>
+        <v>1.033</v>
       </c>
       <c r="J87" t="n">
-        <v>0.228991</v>
+        <v>0.9061439999999999</v>
       </c>
       <c r="K87" t="n">
-        <v>0.00210852</v>
+        <v>-0.06665711956897025</v>
       </c>
       <c r="L87" t="n">
-        <v>0.83004</v>
+        <v>-6.82169</v>
       </c>
       <c r="M87" t="n">
-        <v>3319369204.37</v>
+        <v>827813309</v>
       </c>
       <c r="N87" t="n">
-        <v>6861487132.729219</v>
+        <v>1957052463</v>
       </c>
       <c r="O87" t="n">
-        <v>2</v>
+        <v>236.84</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>45322.29359953704</v>
+        <v>44287.22894675926</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S87" t="n">
-        <v>0.000147270794526578</v>
+        <v>0.0001253805630676178</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6301,31 +6301,31 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="F88" t="n">
-        <v>757435880</v>
+        <v>746280358</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>92491504</v>
+        <v>85972002</v>
       </c>
       <c r="I88" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="J88" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="K88" t="n">
-        <v>0.174328</v>
+        <v>0.078164</v>
       </c>
       <c r="L88" t="n">
-        <v>8.01408</v>
+        <v>3.46156</v>
       </c>
       <c r="M88" t="n">
-        <v>319427134.4515297</v>
+        <v>319428613.3953888</v>
       </c>
       <c r="N88" t="n">
         <v>331093394.0100838</v>
@@ -6337,19 +6337,19 @@
         <v>44316.08914351852</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001278128544399079</v>
+        <v>0.0001207217717826285</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6368,31 +6368,31 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.02830765</v>
+        <v>0.02791111</v>
       </c>
       <c r="F89" t="n">
-        <v>745103332</v>
+        <v>734698091</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>8555253</v>
+        <v>9414573</v>
       </c>
       <c r="I89" t="n">
         <v>0.02947948</v>
       </c>
       <c r="J89" t="n">
-        <v>0.02766103</v>
+        <v>0.02776311</v>
       </c>
       <c r="K89" t="n">
-        <v>-6.0716447863509e-05</v>
+        <v>-4.3763375709591e-05</v>
       </c>
       <c r="L89" t="n">
-        <v>-0.12741</v>
+        <v>-0.15655</v>
       </c>
       <c r="M89" t="n">
-        <v>26315479766</v>
+        <v>26327578875</v>
       </c>
       <c r="N89" t="n">
         <v>100000000000</v>
@@ -6404,175 +6404,175 @@
         <v>46156.97986111111</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R89" t="b">
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001199748532221676</v>
+        <v>0.0001133196420183062</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-treasury-fund</t>
+          <t>render-token</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>jtrsy</t>
+          <t>render</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="F90" t="n">
-        <v>725211452</v>
+        <v>716935713</v>
       </c>
       <c r="G90" t="n">
         <v>89</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>36085963</v>
       </c>
       <c r="I90" t="n">
-        <v>1.12</v>
+        <v>1.41</v>
       </c>
       <c r="J90" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="K90" t="n">
-        <v>0.000216</v>
+        <v>0.0113678</v>
       </c>
       <c r="L90" t="n">
-        <v>0.01936</v>
+        <v>0.82941</v>
       </c>
       <c r="M90" t="n">
-        <v>649898602.6408989</v>
+        <v>518776241.2826915</v>
       </c>
       <c r="N90" t="n">
-        <v>649898652.640859</v>
+        <v>533536414.5626915</v>
       </c>
       <c r="O90" t="n">
-        <v>1.12</v>
+        <v>13.53</v>
       </c>
       <c r="P90" s="1" t="n">
-        <v>46279.33680555555</v>
+        <v>45368.35444444444</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>0.0001073324876977729</v>
+        <v>0.0001019678551117408</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>render-token</t>
+          <t>janus-henderson-anemoy-aaa-clo-fund</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>render</t>
+          <t>jaaa</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>Janus Henderson Anemoy AAA CLO Fund</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1.38</v>
+        <v>1.05</v>
       </c>
       <c r="F91" t="n">
-        <v>716563534</v>
+        <v>714986808</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>34216975</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>1.41</v>
+        <v>1.05</v>
       </c>
       <c r="J91" t="n">
-        <v>1.36</v>
+        <v>1.049</v>
       </c>
       <c r="K91" t="n">
-        <v>-0.00029432628659487</v>
+        <v>0.000428</v>
       </c>
       <c r="L91" t="n">
-        <v>-0.01348</v>
+        <v>0.0408</v>
       </c>
       <c r="M91" t="n">
-        <v>518776241.2826915</v>
+        <v>681220739.278982</v>
       </c>
       <c r="N91" t="n">
-        <v>533536414.5626915</v>
+        <v>681220739.278982</v>
       </c>
       <c r="O91" t="n">
-        <v>13.53</v>
+        <v>1.05</v>
       </c>
       <c r="P91" s="1" t="n">
-        <v>45368.35444444444</v>
+        <v>46279.33680555555</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R91" t="b">
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>0.0001018362681156624</v>
+        <v>0.0001007223262607537</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-aaa-clo-fund</t>
+          <t>janus-henderson-anemoy-treasury-fund</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>jaaa</t>
+          <t>jtrsy</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy AAA CLO Fund</t>
+          <t>Janus Henderson Anemoy Treasury Fund</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="F92" t="n">
-        <v>713986788</v>
+        <v>700205978</v>
       </c>
       <c r="G92" t="n">
         <v>91</v>
@@ -6581,43 +6581,43 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="J92" t="n">
-        <v>1.049</v>
+        <v>1.12</v>
       </c>
       <c r="K92" t="n">
-        <v>0.000428</v>
+        <v>0.000216</v>
       </c>
       <c r="L92" t="n">
-        <v>0.0408</v>
+        <v>0.01936</v>
       </c>
       <c r="M92" t="n">
-        <v>680267946.936126</v>
+        <v>627489934.721184</v>
       </c>
       <c r="N92" t="n">
-        <v>680267946.936126</v>
+        <v>627489934.721184</v>
       </c>
       <c r="O92" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="P92" s="1" t="n">
         <v>46279.33680555555</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R92" t="b">
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>0.0001001986066781551</v>
+        <v>9.127602169150238e-05</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6636,28 +6636,28 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.998708</v>
+        <v>0.998983</v>
       </c>
       <c r="F93" t="n">
-        <v>698095861</v>
+        <v>698277498</v>
       </c>
       <c r="G93" t="n">
         <v>92</v>
       </c>
       <c r="H93" t="n">
-        <v>4559188</v>
+        <v>6391973</v>
       </c>
       <c r="I93" t="n">
-        <v>0.998929</v>
+        <v>0.999081</v>
       </c>
       <c r="J93" t="n">
         <v>0.998309</v>
       </c>
       <c r="K93" t="n">
-        <v>4.271e-05</v>
+        <v>0.00045765</v>
       </c>
       <c r="L93" t="n">
-        <v>0.00465</v>
+        <v>0.04583</v>
       </c>
       <c r="M93" t="n">
         <v>699000000</v>
@@ -6672,19 +6672,19 @@
         <v>45350.38608796296</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R93" t="b">
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>9.009906316313929e-05</v>
+        <v>9.004354628682553e-05</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6703,34 +6703,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>53.9</v>
+        <v>53.98</v>
       </c>
       <c r="F94" t="n">
-        <v>691341172</v>
+        <v>692431241</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
       </c>
       <c r="H94" t="n">
-        <v>83860594</v>
+        <v>94534295</v>
       </c>
       <c r="I94" t="n">
-        <v>55.07</v>
+        <v>56.34</v>
       </c>
       <c r="J94" t="n">
-        <v>52.65</v>
+        <v>52.96</v>
       </c>
       <c r="K94" t="n">
-        <v>0.404915</v>
+        <v>1.15</v>
       </c>
       <c r="L94" t="n">
-        <v>0.72858</v>
+        <v>2.18371</v>
       </c>
       <c r="M94" t="n">
-        <v>12827825.55374544</v>
+        <v>12828706.97240898</v>
       </c>
       <c r="N94" t="n">
-        <v>12828534.51612917</v>
+        <v>12828738.87202284</v>
       </c>
       <c r="O94" t="n">
         <v>1493.59</v>
@@ -6739,19 +6739,19 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R94" t="b">
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>8.580609299935344e-05</v>
+        <v>8.630725243782535e-05</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6770,28 +6770,28 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.00771809</v>
+        <v>0.00762882</v>
       </c>
       <c r="F95" t="n">
-        <v>663403604</v>
+        <v>656071782</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>11855889</v>
+        <v>12299600</v>
       </c>
       <c r="I95" t="n">
         <v>0.008113840000000001</v>
       </c>
       <c r="J95" t="n">
-        <v>0.0076483</v>
+        <v>0.00760228</v>
       </c>
       <c r="K95" t="n">
-        <v>-6.0082351379e-07</v>
+        <v>-0.000102793897326767</v>
       </c>
       <c r="L95" t="n">
-        <v>-0.05431</v>
+        <v>-1.32953</v>
       </c>
       <c r="M95" t="n">
         <v>85985041177</v>
@@ -6806,153 +6806,153 @@
         <v>44304.71413194444</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R95" t="b">
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>6.805025762740101e-05</v>
+        <v>6.307022693335742e-05</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ether-fi</t>
+          <t>injective-protocol</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ethfi</t>
+          <t>inj</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Ether.fi</t>
+          <t>Injective</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.643865</v>
+        <v>6.21</v>
       </c>
       <c r="F96" t="n">
-        <v>621648285</v>
+        <v>621016732</v>
       </c>
       <c r="G96" t="n">
         <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>58218057</v>
+        <v>97222782</v>
       </c>
       <c r="I96" t="n">
-        <v>0.667844</v>
+        <v>6.43</v>
       </c>
       <c r="J96" t="n">
-        <v>0.619474</v>
+        <v>5.94</v>
       </c>
       <c r="K96" t="n">
-        <v>0.00547454</v>
+        <v>0.243003</v>
       </c>
       <c r="L96" t="n">
-        <v>0.89502</v>
+        <v>4.07246</v>
       </c>
       <c r="M96" t="n">
-        <v>965350000</v>
+        <v>100000000</v>
       </c>
       <c r="N96" t="n">
-        <v>965350000</v>
+        <v>100000000</v>
       </c>
       <c r="O96" t="n">
-        <v>8.529999999999999</v>
+        <v>52.62</v>
       </c>
       <c r="P96" s="1" t="n">
-        <v>45378.63525462963</v>
+        <v>45365.29608796296</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R96" t="b">
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>4.151249420907636e-05</v>
+        <v>4.066683828804234e-05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>injective-protocol</t>
+          <t>ether-fi</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>inj</t>
+          <t>ethfi</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Injective</t>
+          <t>Ether.fi</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6.2</v>
+        <v>0.632925</v>
       </c>
       <c r="F97" t="n">
-        <v>619644975</v>
+        <v>611105341</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>93091125</v>
+        <v>52488946</v>
       </c>
       <c r="I97" t="n">
-        <v>6.27</v>
+        <v>0.667844</v>
       </c>
       <c r="J97" t="n">
-        <v>5.85</v>
+        <v>0.624448</v>
       </c>
       <c r="K97" t="n">
-        <v>0.07942</v>
+        <v>-0.006288105739961969</v>
       </c>
       <c r="L97" t="n">
-        <v>1.2766</v>
+        <v>-0.98373</v>
       </c>
       <c r="M97" t="n">
-        <v>100000000</v>
+        <v>965350000</v>
       </c>
       <c r="N97" t="n">
-        <v>100000000</v>
+        <v>965350000</v>
       </c>
       <c r="O97" t="n">
-        <v>52.62</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="P97" s="1" t="n">
-        <v>45365.29608796296</v>
+        <v>45378.63525462963</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>4.023928236189675e-05</v>
+        <v>3.43325513710738e-05</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6971,34 +6971,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.076239</v>
+        <v>0.075492</v>
       </c>
       <c r="F98" t="n">
-        <v>599934863</v>
+        <v>594174861</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>10276372</v>
+        <v>10090722</v>
       </c>
       <c r="I98" t="n">
         <v>0.076415</v>
       </c>
       <c r="J98" t="n">
-        <v>0.075914</v>
+        <v>0.07459200000000001</v>
       </c>
       <c r="K98" t="n">
-        <v>0.00015292</v>
+        <v>-0.00046679286666719</v>
       </c>
       <c r="L98" t="n">
-        <v>0.20802</v>
+        <v>-0.61453</v>
       </c>
       <c r="M98" t="n">
-        <v>7870667509.557123</v>
+        <v>7870693688.976309</v>
       </c>
       <c r="N98" t="n">
-        <v>9939607085.763391</v>
+        <v>9939633963.163563</v>
       </c>
       <c r="O98" t="n">
         <v>0.450785</v>
@@ -7007,19 +7007,19 @@
         <v>43450.66666666666</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R98" t="b">
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>2.771244023180353e-05</v>
+        <v>2.351242350385541e-05</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7038,34 +7038,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.00664088</v>
+        <v>0.00665837</v>
       </c>
       <c r="F99" t="n">
-        <v>577235836</v>
+        <v>578963467</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>2212140</v>
+        <v>4298793</v>
       </c>
       <c r="I99" t="n">
-        <v>0.00660261</v>
+        <v>0.00683709</v>
       </c>
       <c r="J99" t="n">
-        <v>0.00639912</v>
+        <v>0.00643178</v>
       </c>
       <c r="K99" t="n">
-        <v>0.00018282</v>
+        <v>0.00024516</v>
       </c>
       <c r="L99" t="n">
-        <v>3.16072</v>
+        <v>3.82277</v>
       </c>
       <c r="M99" t="n">
-        <v>86942314077.73903</v>
+        <v>86948958161.74995</v>
       </c>
       <c r="N99" t="n">
-        <v>106545584672.7701</v>
+        <v>106552794056.9216</v>
       </c>
       <c r="O99" t="n">
         <v>0.150073</v>
@@ -7074,141 +7074,141 @@
         <v>44935.80144675926</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R99" t="b">
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>1.328598097395033e-05</v>
+        <v>1.37909490909245e-05</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>aerodrome-finance</t>
+          <t>xdce-crowd-sale</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>aero</t>
+          <t>xdc</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Aerodrome Finance</t>
+          <t>XDC Network</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.573146</v>
+        <v>0.0283792</v>
       </c>
       <c r="F100" t="n">
-        <v>566879138</v>
+        <v>566117297</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>24995379</v>
+        <v>6969744</v>
       </c>
       <c r="I100" t="n">
-        <v>0.584179</v>
+        <v>0.02838163</v>
       </c>
       <c r="J100" t="n">
-        <v>0.5548070000000001</v>
+        <v>0.02759105</v>
       </c>
       <c r="K100" t="n">
-        <v>0.01146812</v>
+        <v>0.00069195</v>
       </c>
       <c r="L100" t="n">
-        <v>2.01643</v>
+        <v>2.49916</v>
       </c>
       <c r="M100" t="n">
-        <v>988792626.4788798</v>
+        <v>19946688440</v>
       </c>
       <c r="N100" t="n">
-        <v>1978450301.483024</v>
+        <v>38065686425.1</v>
       </c>
       <c r="O100" t="n">
-        <v>2.32</v>
+        <v>0.192754</v>
       </c>
       <c r="P100" s="1" t="n">
-        <v>45633.25043981482</v>
+        <v>44428.86097222222</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R100" t="b">
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>6.703739288309363e-06</v>
+        <v>5.581069512553136e-06</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>xdce-crowd-sale</t>
+          <t>aerodrome-finance</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>xdc</t>
+          <t>aero</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>XDC Network</t>
+          <t>Aerodrome Finance</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.02789734</v>
+        <v>0.563694</v>
       </c>
       <c r="F101" t="n">
-        <v>556331272</v>
+        <v>557384481</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>6122903</v>
+        <v>27643511</v>
       </c>
       <c r="I101" t="n">
-        <v>0.02799834</v>
+        <v>0.585051</v>
       </c>
       <c r="J101" t="n">
-        <v>0.02759105</v>
+        <v>0.564971</v>
       </c>
       <c r="K101" t="n">
-        <v>-8.1389842287991e-05</v>
+        <v>0.00492885</v>
       </c>
       <c r="L101" t="n">
-        <v>-0.31486</v>
+        <v>0.8821</v>
       </c>
       <c r="M101" t="n">
-        <v>19946688440</v>
+        <v>988735867.9762976</v>
       </c>
       <c r="N101" t="n">
-        <v>38065686425.1</v>
+        <v>1978450301.483024</v>
       </c>
       <c r="O101" t="n">
-        <v>0.192754</v>
+        <v>2.32</v>
       </c>
       <c r="P101" s="1" t="n">
-        <v>44428.86097222222</v>
+        <v>45633.25043981482</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46279.65787037037</v>
+        <v>46280.06759259259</v>
       </c>
       <c r="R101" t="b">
         <v>0</v>

--- a/src/xlsx/cleaned_data.xlsx
+++ b/src/xlsx/cleaned_data.xlsx
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,34 +539,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>77928</v>
+        <v>76381</v>
       </c>
       <c r="F2" t="n">
-        <v>1565278264656</v>
+        <v>1534205559019</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>32481754899</v>
+        <v>32859344708</v>
       </c>
       <c r="I2" t="n">
         <v>79530</v>
       </c>
       <c r="J2" t="n">
-        <v>77010</v>
+        <v>76142</v>
       </c>
       <c r="K2" t="n">
-        <v>1192.34</v>
+        <v>-2095.025691471383</v>
       </c>
       <c r="L2" t="n">
-        <v>1.55383</v>
+        <v>-2.67474</v>
       </c>
       <c r="M2" t="n">
-        <v>20084421</v>
+        <v>20084731</v>
       </c>
       <c r="N2" t="n">
-        <v>20084481</v>
+        <v>20084753</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -575,7 +575,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -587,7 +587,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,34 +606,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2512.93</v>
+        <v>2447.41</v>
       </c>
       <c r="F3" t="n">
-        <v>306704123966</v>
+        <v>298739245343</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>16310732511</v>
+        <v>16736514590</v>
       </c>
       <c r="I3" t="n">
         <v>2607.56</v>
       </c>
       <c r="J3" t="n">
-        <v>2489.59</v>
+        <v>2440.21</v>
       </c>
       <c r="K3" t="n">
-        <v>33.64</v>
+        <v>-65.88360726961491</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35678</v>
+        <v>-2.62877</v>
       </c>
       <c r="M3" t="n">
-        <v>122047243.4940371</v>
+        <v>122050160.8356428</v>
       </c>
       <c r="N3" t="n">
-        <v>122047243.4940371</v>
+        <v>122050160.8356428</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -642,19 +642,19 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1956558152727918</v>
+        <v>0.1944146707650489</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,28 +673,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9998359999999999</v>
+        <v>0.999597</v>
       </c>
       <c r="F4" t="n">
-        <v>183404017289</v>
+        <v>183354416193</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>58316519980</v>
+        <v>58445617168</v>
       </c>
       <c r="I4" t="n">
         <v>0.999954</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999563</v>
+        <v>0.999574</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00017816</v>
+        <v>-6.3166689663885e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01782</v>
+        <v>-0.00637</v>
       </c>
       <c r="M4" t="n">
         <v>183431197333.8773</v>
@@ -709,19 +709,19 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1168557505205339</v>
+        <v>0.1191780378025916</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,34 +740,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>719.73</v>
+        <v>719.6900000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>95843853248</v>
+        <v>95838645444</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1013896622</v>
+        <v>918308118</v>
       </c>
       <c r="I5" t="n">
         <v>732.8</v>
       </c>
       <c r="J5" t="n">
-        <v>717.26</v>
+        <v>714.1900000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>3.33</v>
+        <v>-2.763283885708461</v>
       </c>
       <c r="L5" t="n">
-        <v>0.46471</v>
+        <v>-0.38611</v>
       </c>
       <c r="M5" t="n">
-        <v>133160833.09</v>
+        <v>133160762.8</v>
       </c>
       <c r="N5" t="n">
-        <v>133160833.09</v>
+        <v>133160756.43</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -776,19 +776,19 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0608967835569134</v>
+        <v>0.06211341352941806</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -807,28 +807,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="F6" t="n">
-        <v>89328302982</v>
+        <v>88748268343</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>3988480517</v>
+        <v>4262068843</v>
       </c>
       <c r="I6" t="n">
         <v>1.49</v>
       </c>
       <c r="J6" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="K6" t="n">
-        <v>0.07849299999999999</v>
+        <v>0.009628629999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>5.84888</v>
+        <v>0.71812</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -843,19 +843,19 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05673274999121362</v>
+        <v>0.05749013589887395</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,34 +874,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999866</v>
+        <v>0.999758</v>
       </c>
       <c r="F7" t="n">
-        <v>74355972434</v>
+        <v>74113425015</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>18147169260</v>
+        <v>17704315342</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.9999980000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999711</v>
+        <v>0.999376</v>
       </c>
       <c r="K7" t="n">
-        <v>3.435e-05</v>
+        <v>-3.6659991143884e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00344</v>
+        <v>-0.00376</v>
       </c>
       <c r="M7" t="n">
-        <v>74364752733.23085</v>
+        <v>74132157601.51918</v>
       </c>
       <c r="N7" t="n">
-        <v>74371126949.03763</v>
+        <v>74178971119.97899</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -910,19 +910,19 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04716405902677434</v>
+        <v>0.0479474919998185</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -941,34 +941,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102.33</v>
+        <v>100.3</v>
       </c>
       <c r="F8" t="n">
-        <v>60071914459</v>
+        <v>58889059739</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3391879841</v>
+        <v>3215127218</v>
       </c>
       <c r="I8" t="n">
         <v>104.76</v>
       </c>
       <c r="J8" t="n">
-        <v>99.95999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>2.95</v>
+        <v>-1.508608506609704</v>
       </c>
       <c r="L8" t="n">
-        <v>2.96946</v>
+        <v>-1.50767</v>
       </c>
       <c r="M8" t="n">
-        <v>587028564.7667522</v>
+        <v>587027977.1330632</v>
       </c>
       <c r="N8" t="n">
-        <v>634017029.7664536</v>
+        <v>634111537.8744141</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -977,19 +977,19 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03803523729506558</v>
+        <v>0.03802045054389421</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1008,16 +1008,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.337933</v>
+        <v>0.337441</v>
       </c>
       <c r="F9" t="n">
-        <v>32085906398</v>
+        <v>32042437914</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>459700901</v>
+        <v>439649621</v>
       </c>
       <c r="I9" t="n">
         <v>0.342048</v>
@@ -1026,16 +1026,16 @@
         <v>0.33736</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.000482044361519829</v>
+        <v>-0.003462706707822782</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.14244</v>
+        <v>-1.02556</v>
       </c>
       <c r="M9" t="n">
-        <v>94950365063.49529</v>
+        <v>94951106760.14119</v>
       </c>
       <c r="N9" t="n">
-        <v>94950919109.75899</v>
+        <v>94951113668.88469</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1044,19 +1044,19 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02014961410464071</v>
+        <v>0.02051512122626251</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1075,34 +1075,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.028</v>
+        <v>1.029</v>
       </c>
       <c r="F10" t="n">
-        <v>23190254032</v>
+        <v>23203168550</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>26456887</v>
+        <v>26481105</v>
       </c>
       <c r="I10" t="n">
         <v>1.048</v>
       </c>
       <c r="J10" t="n">
-        <v>1.006</v>
+        <v>1.008</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.01315564104259104</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-1.26266</v>
       </c>
       <c r="M10" t="n">
         <v>22558008629.268</v>
       </c>
       <c r="N10" t="n">
-        <v>22558008629.268</v>
+        <v>22624876494.218</v>
       </c>
       <c r="O10" t="n">
         <v>1.061</v>
@@ -1111,19 +1111,19 @@
         <v>46237.59675925926</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01446447723537038</v>
+        <v>0.01475147907594988</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1142,34 +1142,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1156.87</v>
+        <v>1131</v>
       </c>
       <c r="F11" t="n">
-        <v>19585748329</v>
+        <v>19189557969</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1339721891</v>
+        <v>911698850</v>
       </c>
       <c r="I11" t="n">
         <v>1222.73</v>
       </c>
       <c r="J11" t="n">
-        <v>1072.1</v>
+        <v>1121.6</v>
       </c>
       <c r="K11" t="n">
-        <v>95.72</v>
+        <v>-21.47479087819488</v>
       </c>
       <c r="L11" t="n">
-        <v>9.020440000000001</v>
+        <v>-1.9864</v>
       </c>
       <c r="M11" t="n">
-        <v>16932570.4780448</v>
+        <v>16933759.5405448</v>
       </c>
       <c r="N11" t="n">
-        <v>16932909.5405448</v>
+        <v>16933876.7280448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1178,19 +1178,19 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01216086785131406</v>
+        <v>0.01213440585790688</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1209,28 +1209,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>80.2</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>17841668216</v>
+        <v>17472789844</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>820683271</v>
+        <v>701147955</v>
       </c>
       <c r="I12" t="n">
         <v>82.38</v>
       </c>
       <c r="J12" t="n">
-        <v>78.05</v>
+        <v>78.53</v>
       </c>
       <c r="K12" t="n">
-        <v>2.51</v>
+        <v>-2.33141737096723</v>
       </c>
       <c r="L12" t="n">
-        <v>3.22502</v>
+        <v>-2.94723</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1245,19 +1245,19 @@
         <v>46271.5199074074</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01104624086889344</v>
+        <v>0.01101498786982495</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1276,34 +1276,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.083762</v>
+        <v>0.08265599999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>13061146331</v>
+        <v>12888618761</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>623849039</v>
+        <v>577108242</v>
       </c>
       <c r="I13" t="n">
         <v>0.086033</v>
       </c>
       <c r="J13" t="n">
-        <v>0.083028</v>
+        <v>0.08219799999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00124728</v>
+        <v>-0.001444614891101273</v>
       </c>
       <c r="L13" t="n">
-        <v>1.51158</v>
+        <v>-1.74714</v>
       </c>
       <c r="M13" t="n">
-        <v>155919246383.7052</v>
+        <v>155926276383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171630873126.579</v>
+        <v>171638413126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1312,287 +1312,287 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.007991049399559087</v>
+        <v>0.008025880898401385</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01423283</v>
+        <v>0.999568</v>
       </c>
       <c r="F14" t="n">
-        <v>10097241960</v>
+        <v>9854320658</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>27250626</v>
+        <v>147515323</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01529975</v>
+        <v>0.999922</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01423111</v>
+        <v>0.999566</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000917806640155248</v>
+        <v>-8.5224967625419e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>-6.05787</v>
+        <v>-0.00975</v>
       </c>
       <c r="M14" t="n">
-        <v>709219950838.6726</v>
+        <v>9858747591.389191</v>
       </c>
       <c r="N14" t="n">
-        <v>1142408526965.963</v>
+        <v>9841353158.538542</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01946402</v>
+        <v>1.057</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>46259.82847222222</v>
+        <v>45593.90336805556</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.006096842957660955</v>
+        <v>0.006047368000684871</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.999815</v>
+        <v>518.12</v>
       </c>
       <c r="F15" t="n">
-        <v>9841412373</v>
+        <v>9747395293</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>128014911</v>
+        <v>120378755</v>
       </c>
       <c r="I15" t="n">
-        <v>0.999922</v>
+        <v>519.62</v>
       </c>
       <c r="J15" t="n">
-        <v>0.99953</v>
+        <v>509.39</v>
       </c>
       <c r="K15" t="n">
-        <v>4.974e-05</v>
+        <v>5.25</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00497</v>
+        <v>1.05346</v>
       </c>
       <c r="M15" t="n">
-        <v>9843079519.306154</v>
+        <v>18804964.99452248</v>
       </c>
       <c r="N15" t="n">
-        <v>9859445986.033854</v>
+        <v>18804999.79259193</v>
       </c>
       <c r="O15" t="n">
-        <v>1.057</v>
+        <v>797.73</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>45593.90336805556</v>
+        <v>46036.48202546296</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005933344412814166</v>
+        <v>0.005977647358030682</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>517.35</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>9729591804</v>
+        <v>9307310396</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>144582594</v>
+        <v>111976919</v>
       </c>
       <c r="I16" t="n">
-        <v>526.9</v>
+        <v>82.67</v>
       </c>
       <c r="J16" t="n">
-        <v>502.91</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>4.44</v>
+        <v>-2.1789629554996</v>
       </c>
       <c r="L16" t="n">
-        <v>0.86522</v>
+        <v>-2.71408</v>
       </c>
       <c r="M16" t="n">
-        <v>18804748.99981384</v>
+        <v>117882016</v>
       </c>
       <c r="N16" t="n">
-        <v>18804784.39672368</v>
+        <v>293532015</v>
       </c>
       <c r="O16" t="n">
-        <v>797.73</v>
+        <v>83.22</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>46036.48202546296</v>
+        <v>46276.58553240741</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.005861880824376915</v>
+        <v>0.005690690172135245</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>80.65000000000001</v>
+        <v>0.01303906</v>
       </c>
       <c r="F17" t="n">
-        <v>9508070993</v>
+        <v>9248658690</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>124952764</v>
+        <v>22655688</v>
       </c>
       <c r="I17" t="n">
-        <v>82.67</v>
+        <v>0.01474682</v>
       </c>
       <c r="J17" t="n">
-        <v>79.78</v>
+        <v>0.01303694</v>
       </c>
       <c r="K17" t="n">
-        <v>1.11</v>
+        <v>-0.001979134494756592</v>
       </c>
       <c r="L17" t="n">
-        <v>1.40009</v>
+        <v>-13.1993</v>
       </c>
       <c r="M17" t="n">
-        <v>117882016</v>
+        <v>709230388026.6638</v>
       </c>
       <c r="N17" t="n">
-        <v>293532015</v>
+        <v>1142408526965.963</v>
       </c>
       <c r="O17" t="n">
-        <v>83.22</v>
+        <v>0.01946402</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>46276.58553240741</v>
+        <v>46259.82847222222</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005720308730716846</v>
+        <v>0.005652446350053511</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1611,28 +1611,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.57</v>
+        <v>11.33</v>
       </c>
       <c r="F18" t="n">
-        <v>8656632447</v>
+        <v>8476405612</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>378630111</v>
+        <v>354920743</v>
       </c>
       <c r="I18" t="n">
         <v>11.95</v>
       </c>
       <c r="J18" t="n">
-        <v>11.25</v>
+        <v>11.3</v>
       </c>
       <c r="K18" t="n">
-        <v>0.331506</v>
+        <v>-0.09682141799737742</v>
       </c>
       <c r="L18" t="n">
-        <v>2.94987</v>
+        <v>-0.88814</v>
       </c>
       <c r="M18" t="n">
         <v>748099970.424884</v>
@@ -1647,19 +1647,19 @@
         <v>44325.67635416667</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005176161492198002</v>
+        <v>0.005148899030950739</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1678,28 +1678,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.98</v>
+        <v>8.76</v>
       </c>
       <c r="F19" t="n">
-        <v>8262550568</v>
+        <v>8058856074</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>119220</v>
+        <v>310469</v>
       </c>
       <c r="I19" t="n">
-        <v>9.050000000000001</v>
+        <v>9.02</v>
       </c>
       <c r="J19" t="n">
-        <v>8.949999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.05097400490951998</v>
+        <v>-0.2049368320736651</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.56428</v>
+        <v>-2.28863</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1714,19 +1714,19 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004924307066278969</v>
+        <v>0.004876636017124977</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1745,28 +1745,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.207943</v>
+        <v>0.20469</v>
       </c>
       <c r="F20" t="n">
-        <v>7803954887</v>
+        <v>7681523043</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>399285548</v>
+        <v>364530117</v>
       </c>
       <c r="I20" t="n">
         <v>0.215603</v>
       </c>
       <c r="J20" t="n">
-        <v>0.204682</v>
+        <v>0.203227</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00435576</v>
+        <v>-0.005640167035805999</v>
       </c>
       <c r="L20" t="n">
-        <v>2.1395</v>
+        <v>-2.66892</v>
       </c>
       <c r="M20" t="n">
         <v>37516725700.17653</v>
@@ -1781,19 +1781,19 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004631222410216406</v>
+        <v>0.004630596161044309</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1812,31 +1812,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.192906</v>
+        <v>0.196107</v>
       </c>
       <c r="F21" t="n">
-        <v>6720183097</v>
+        <v>6829435123</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>352873849</v>
+        <v>381135110</v>
       </c>
       <c r="I21" t="n">
-        <v>0.196711</v>
+        <v>0.198377</v>
       </c>
       <c r="J21" t="n">
-        <v>0.178695</v>
+        <v>0.189175</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01534281</v>
+        <v>0.00446452</v>
       </c>
       <c r="L21" t="n">
-        <v>8.640750000000001</v>
+        <v>2.34329</v>
       </c>
       <c r="M21" t="n">
-        <v>34835002057.12234</v>
+        <v>34840249441.93312</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70248</v>
@@ -1848,19 +1848,19 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.003938592942730301</v>
+        <v>0.00407499256427126</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1879,34 +1879,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.999786</v>
+        <v>0.999451</v>
       </c>
       <c r="F22" t="n">
-        <v>4666338082</v>
+        <v>4689264034</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>48169800</v>
+        <v>51680215</v>
       </c>
       <c r="I22" t="n">
         <v>0.999955</v>
       </c>
       <c r="J22" t="n">
-        <v>0.999457</v>
+        <v>0.999484</v>
       </c>
       <c r="K22" t="n">
-        <v>0.00024197</v>
+        <v>-0.000111107568562585</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02421</v>
+        <v>-0.01282</v>
       </c>
       <c r="M22" t="n">
-        <v>4667235430.751101</v>
+        <v>4691925488.305101</v>
       </c>
       <c r="N22" t="n">
-        <v>4667235430.751101</v>
+        <v>4691925488.305101</v>
       </c>
       <c r="O22" t="n">
         <v>1.034</v>
@@ -1915,19 +1915,19 @@
         <v>46000.38208333333</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R22" t="b">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.002625997807698744</v>
+        <v>0.00267949483821725</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1946,16 +1946,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9999</v>
+        <v>0.99983</v>
       </c>
       <c r="F23" t="n">
-        <v>4587613885</v>
+        <v>4601958030</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>272052157</v>
+        <v>298574661</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -1964,16 +1964,16 @@
         <v>0.999684</v>
       </c>
       <c r="K23" t="n">
-        <v>-9.104097099410499e-05</v>
+        <v>-0.000171526442148129</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0091</v>
+        <v>0.01416</v>
       </c>
       <c r="M23" t="n">
-        <v>4587994881.149207</v>
+        <v>4602712385.445437</v>
       </c>
       <c r="N23" t="n">
-        <v>4587994881.149207</v>
+        <v>4606604755.4429</v>
       </c>
       <c r="O23" t="n">
         <v>1.22</v>
@@ -1982,19 +1982,19 @@
         <v>43902.79363425926</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R23" t="b">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.002575685833213432</v>
+        <v>0.002622566992271162</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2013,34 +2013,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>223.01</v>
+        <v>223.53</v>
       </c>
       <c r="F24" t="n">
-        <v>4480527872</v>
+        <v>4491666529</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>144998419</v>
+        <v>120014932</v>
       </c>
       <c r="I24" t="n">
         <v>230.06</v>
       </c>
       <c r="J24" t="n">
-        <v>220.2</v>
+        <v>220.11</v>
       </c>
       <c r="K24" t="n">
-        <v>1.33</v>
+        <v>-0.6298749753331379</v>
       </c>
       <c r="L24" t="n">
-        <v>0.59892</v>
+        <v>-0.2963</v>
       </c>
       <c r="M24" t="n">
-        <v>20089143.64665077</v>
+        <v>20089446.77165077</v>
       </c>
       <c r="N24" t="n">
-        <v>20089490.52165077</v>
+        <v>20089746.77165077</v>
       </c>
       <c r="O24" t="n">
         <v>3785.82</v>
@@ -2049,19 +2049,19 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002507248059833669</v>
+        <v>0.002550651461947603</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2080,34 +2080,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.999652</v>
+        <v>0.99942</v>
       </c>
       <c r="F25" t="n">
-        <v>4340634644</v>
+        <v>4343951640</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>1166862007</v>
+        <v>1038808054</v>
       </c>
       <c r="I25" t="n">
         <v>0.9998939999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9994189999999999</v>
+        <v>0.999368</v>
       </c>
       <c r="K25" t="n">
-        <v>8.205e-05</v>
+        <v>-0.000119357677266674</v>
       </c>
       <c r="L25" t="n">
-        <v>0.00821</v>
+        <v>-0.01591</v>
       </c>
       <c r="M25" t="n">
-        <v>4342109207.801132</v>
+        <v>4346607627.726874</v>
       </c>
       <c r="N25" t="n">
-        <v>4342109207.801132</v>
+        <v>4346607627.726874</v>
       </c>
       <c r="O25" t="n">
         <v>1.048</v>
@@ -2116,287 +2116,287 @@
         <v>46212.42696759259</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002417843470317132</v>
+        <v>0.002454334026036375</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>uniswap</t>
+          <t>litecoin</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>uni</t>
+          <t>ltc</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6.7</v>
+        <v>52.26</v>
       </c>
       <c r="F26" t="n">
-        <v>4172914708</v>
+        <v>4056708774</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>546287575</v>
+        <v>201051632</v>
       </c>
       <c r="I26" t="n">
-        <v>6.79</v>
+        <v>54.41</v>
       </c>
       <c r="J26" t="n">
-        <v>6.22</v>
+        <v>52.21</v>
       </c>
       <c r="K26" t="n">
-        <v>0.5339469999999999</v>
+        <v>-1.580792074926798</v>
       </c>
       <c r="L26" t="n">
-        <v>8.66582</v>
+        <v>-2.97</v>
       </c>
       <c r="M26" t="n">
-        <v>623212423.7271129</v>
+        <v>77609673.14233896</v>
       </c>
       <c r="N26" t="n">
-        <v>890460420.0329479</v>
+        <v>77612785.65080889</v>
       </c>
       <c r="O26" t="n">
-        <v>44.92</v>
+        <v>410.26</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>44318.89240740741</v>
+        <v>44325.80077546297</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002310655064944002</v>
+        <v>0.002267037426998803</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>litecoin</t>
+          <t>uniswap</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ltc</t>
+          <t>uni</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>52.89</v>
+        <v>6.4</v>
       </c>
       <c r="F27" t="n">
-        <v>4104723979</v>
+        <v>3990125658</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>215062599</v>
+        <v>655992252</v>
       </c>
       <c r="I27" t="n">
-        <v>54.54</v>
+        <v>6.82</v>
       </c>
       <c r="J27" t="n">
-        <v>52.61</v>
+        <v>6.32</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.067596865327559</v>
+        <v>0.01557894</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.97876</v>
+        <v>0.14958</v>
       </c>
       <c r="M27" t="n">
-        <v>77607591.88778906</v>
+        <v>623212423.7271129</v>
       </c>
       <c r="N27" t="n">
-        <v>77610835.64571653</v>
+        <v>890460420.0329479</v>
       </c>
       <c r="O27" t="n">
-        <v>410.26</v>
+        <v>44.92</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>44325.80077546297</v>
+        <v>44318.89240740741</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002267074941572494</v>
+        <v>0.002223621932111894</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>canton-network</t>
+          <t>the-open-network</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>gram</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Gram (prev. Toncoin)</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.095952</v>
+        <v>1.34</v>
       </c>
       <c r="F28" t="n">
-        <v>3799143043</v>
+        <v>3734431422</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>8810925</v>
+        <v>23256474</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09957199999999999</v>
+        <v>1.37</v>
       </c>
       <c r="J28" t="n">
-        <v>0.094793</v>
+        <v>1.33</v>
       </c>
       <c r="K28" t="n">
-        <v>0.00060352</v>
+        <v>-0.01560654388762583</v>
       </c>
       <c r="L28" t="n">
-        <v>0.63296</v>
+        <v>-1.17175</v>
       </c>
       <c r="M28" t="n">
-        <v>39591792568.75395</v>
+        <v>2789630325.698153</v>
       </c>
       <c r="N28" t="n">
-        <v>39592719231.5488</v>
+        <v>5249545239.296951</v>
       </c>
       <c r="O28" t="n">
-        <v>0.194152</v>
+        <v>8.25</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>46056.00148148148</v>
+        <v>45457.69225694444</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002071780726564752</v>
+        <v>0.002056896604993377</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>the-open-network</t>
+          <t>canton-network</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>gram</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Gram (prev. Toncoin)</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.35</v>
+        <v>0.09410399999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>3758347414</v>
+        <v>3725190679</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>22644492</v>
+        <v>8411442</v>
       </c>
       <c r="I29" t="n">
-        <v>1.37</v>
+        <v>0.09957199999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>1.34</v>
+        <v>0.09396599999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.00194014</v>
+        <v>-0.002110394020577555</v>
       </c>
       <c r="L29" t="n">
-        <v>0.14417</v>
+        <v>-2.19196</v>
       </c>
       <c r="M29" t="n">
-        <v>2788626129.896895</v>
+        <v>39595289848.56115</v>
       </c>
       <c r="N29" t="n">
-        <v>5249250485.565387</v>
+        <v>39595289848.56115</v>
       </c>
       <c r="O29" t="n">
-        <v>8.25</v>
+        <v>0.194152</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>45457.69225694444</v>
+        <v>46056.00148148148</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002045708581994509</v>
+        <v>0.002050871182114884</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2415,31 +2415,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.07807600000000001</v>
+        <v>0.07849299999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>3423512744</v>
+        <v>3441847762</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>62181970</v>
+        <v>79904973</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0793</v>
+        <v>0.079821</v>
       </c>
       <c r="J30" t="n">
-        <v>0.075722</v>
+        <v>0.076289</v>
       </c>
       <c r="K30" t="n">
-        <v>0.00274329</v>
+        <v>0.00167729</v>
       </c>
       <c r="L30" t="n">
-        <v>3.64156</v>
+        <v>2.18686</v>
       </c>
       <c r="M30" t="n">
-        <v>43831559670.36193</v>
+        <v>43831559670.90491</v>
       </c>
       <c r="N30" t="n">
         <v>50000000000</v>
@@ -2451,19 +2451,19 @@
         <v>44454.11143518519</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.00183171855077402</v>
+        <v>0.001866117543305678</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2482,34 +2482,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>7.55</v>
+        <v>7.52</v>
       </c>
       <c r="F31" t="n">
-        <v>3340140954</v>
+        <v>3330626737</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>260534190</v>
+        <v>256933798</v>
       </c>
       <c r="I31" t="n">
         <v>7.79</v>
       </c>
       <c r="J31" t="n">
-        <v>7.34</v>
+        <v>7.43</v>
       </c>
       <c r="K31" t="n">
-        <v>0.230515</v>
+        <v>0.03078822</v>
       </c>
       <c r="L31" t="n">
-        <v>3.15048</v>
+        <v>0.36221</v>
       </c>
       <c r="M31" t="n">
-        <v>442511274.1977351</v>
+        <v>442517742.512899</v>
       </c>
       <c r="N31" t="n">
-        <v>469180009.5183742</v>
+        <v>469186419.7681523</v>
       </c>
       <c r="O31" t="n">
         <v>144.96</v>
@@ -2518,19 +2518,19 @@
         <v>44521.26314814815</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.001778436338555649</v>
+        <v>0.001793595917219505</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2549,34 +2549,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0.999933</v>
       </c>
       <c r="F32" t="n">
-        <v>3320460979</v>
+        <v>3314144494</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>1355481705</v>
+        <v>1286433563</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>0.999787</v>
+        <v>0.999816</v>
       </c>
       <c r="K32" t="n">
-        <v>9.195e-05</v>
+        <v>3.92e-06</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0092</v>
+        <v>0.00018</v>
       </c>
       <c r="M32" t="n">
-        <v>3320411793.153075</v>
+        <v>3314421155.993802</v>
       </c>
       <c r="N32" t="n">
-        <v>3320406787.932336</v>
+        <v>3320411793.117109</v>
       </c>
       <c r="O32" t="n">
         <v>1.65</v>
@@ -2585,19 +2585,19 @@
         <v>45686.67436342593</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001765859031478493</v>
+        <v>0.001782848677082962</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2616,34 +2616,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="F33" t="n">
-        <v>3186108462</v>
+        <v>3096910012</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>367243361</v>
+        <v>384207681</v>
       </c>
       <c r="I33" t="n">
         <v>2.59</v>
       </c>
       <c r="J33" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="K33" t="n">
-        <v>0.140426</v>
+        <v>-0.05920351575864702</v>
       </c>
       <c r="L33" t="n">
-        <v>6.11029</v>
+        <v>-2.54883</v>
       </c>
       <c r="M33" t="n">
-        <v>1306324632</v>
+        <v>1306379194</v>
       </c>
       <c r="N33" t="n">
-        <v>1306324630</v>
+        <v>1306379203</v>
       </c>
       <c r="O33" t="n">
         <v>20.44</v>
@@ -2652,19 +2652,19 @@
         <v>44577.59010416667</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001679995463923253</v>
+        <v>0.001641201017599267</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2683,28 +2683,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5.21e-06</v>
+        <v>5.16e-06</v>
       </c>
       <c r="F34" t="n">
-        <v>3070281412</v>
+        <v>3042104770</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>70179974</v>
+        <v>67610639</v>
       </c>
       <c r="I34" t="n">
         <v>5.39e-06</v>
       </c>
       <c r="J34" t="n">
-        <v>5.19e-06</v>
+        <v>5.13e-06</v>
       </c>
       <c r="K34" t="n">
-        <v>5.8736e-08</v>
+        <v>-9.922755486000001e-08</v>
       </c>
       <c r="L34" t="n">
-        <v>1.1407</v>
+        <v>-1.91446</v>
       </c>
       <c r="M34" t="n">
         <v>589239232074943.9</v>
@@ -2719,19 +2719,19 @@
         <v>44496.82980324074</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R34" t="b">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.00160597136705874</v>
+        <v>0.001605465280872455</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.719072</v>
+        <v>0.709537</v>
       </c>
       <c r="F35" t="n">
-        <v>2945764651</v>
+        <v>2907090081</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>491009920</v>
+        <v>446416765</v>
       </c>
       <c r="I35" t="n">
         <v>0.7470830000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>0.706761</v>
+        <v>0.702775</v>
       </c>
       <c r="K35" t="n">
-        <v>0.01781222</v>
+        <v>-0.01632837389630148</v>
       </c>
       <c r="L35" t="n">
-        <v>2.54003</v>
+        <v>-2.26866</v>
       </c>
       <c r="M35" t="n">
         <v>4096537146.540959</v>
@@ -2786,19 +2786,19 @@
         <v>45661.62243055556</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001526393748725895</v>
+        <v>0.001517429005430838</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2817,34 +2817,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.999903</v>
+        <v>0.999596</v>
       </c>
       <c r="F36" t="n">
-        <v>2872990937</v>
+        <v>2847196672</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>91650449</v>
+        <v>113170639</v>
       </c>
       <c r="I36" t="n">
         <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0.999634</v>
+        <v>0.999588</v>
       </c>
       <c r="K36" t="n">
-        <v>0.00019089</v>
+        <v>-0.000129970499106125</v>
       </c>
       <c r="L36" t="n">
-        <v>0.01909</v>
+        <v>-0.01317</v>
       </c>
       <c r="M36" t="n">
-        <v>2873226914.536399</v>
+        <v>2848397238.831206</v>
       </c>
       <c r="N36" t="n">
-        <v>2873226914.536399</v>
+        <v>2849124073.776223</v>
       </c>
       <c r="O36" t="n">
         <v>1.021</v>
@@ -2853,19 +2853,19 @@
         <v>45222.61454861111</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001479884678052625</v>
+        <v>0.001478375531390976</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2884,34 +2884,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.059086</v>
+        <v>0.057053</v>
       </c>
       <c r="F37" t="n">
-        <v>2868915956</v>
+        <v>2770362369</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>7181516</v>
+        <v>8558565</v>
       </c>
       <c r="I37" t="n">
-        <v>0.060149</v>
+        <v>0.060066</v>
       </c>
       <c r="J37" t="n">
-        <v>0.057738</v>
+        <v>0.056826</v>
       </c>
       <c r="K37" t="n">
-        <v>0.00173643</v>
+        <v>-0.002513645447222712</v>
       </c>
       <c r="L37" t="n">
-        <v>3.0278</v>
+        <v>-4.22884</v>
       </c>
       <c r="M37" t="n">
-        <v>48555221292.30435</v>
+        <v>48556300890.85578</v>
       </c>
       <c r="N37" t="n">
-        <v>98921836999.88431</v>
+        <v>98922960112.48987</v>
       </c>
       <c r="O37" t="n">
         <v>0.891544</v>
@@ -2920,19 +2920,19 @@
         <v>44523.66666666666</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001477280391849488</v>
+        <v>0.001428275754008438</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2987,19 +2987,19 @@
         <v>45699.87511574074</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R38" t="b">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001386018259536133</v>
+        <v>0.00139942505150739</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3018,28 +3018,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4298.39</v>
+        <v>4295.67</v>
       </c>
       <c r="F39" t="n">
-        <v>2677383681</v>
+        <v>2675286730</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>224742458</v>
+        <v>170538665</v>
       </c>
       <c r="I39" t="n">
-        <v>4353.59</v>
+        <v>4318.64</v>
       </c>
       <c r="J39" t="n">
-        <v>4259.22</v>
+        <v>4264.56</v>
       </c>
       <c r="K39" t="n">
-        <v>-41.33995619151119</v>
+        <v>11.57</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.95259</v>
+        <v>0.25337</v>
       </c>
       <c r="M39" t="n">
         <v>622823.6595320001</v>
@@ -3054,153 +3054,153 @@
         <v>46050.66666666666</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001354873720201712</v>
+        <v>0.001366281720582995</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>bittensor</t>
+          <t>hashnote-usyc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>tao</t>
+          <t>usyc</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>Circle USYC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>232.45</v>
+        <v>1.14</v>
       </c>
       <c r="F40" t="n">
-        <v>2636345004</v>
+        <v>2605808911</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>167213088</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>241.79</v>
+        <v>1.14</v>
       </c>
       <c r="J40" t="n">
-        <v>230.68</v>
+        <v>1.14</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.258092428543506</v>
+        <v>9.804e-05</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.11091</v>
+        <v>0.008619999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>11339645.9251</v>
+        <v>2291167466.910423</v>
       </c>
       <c r="N40" t="n">
-        <v>21000000</v>
+        <v>2291321221.608375</v>
       </c>
       <c r="O40" t="n">
-        <v>757.6</v>
+        <v>1.14</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>45358.44833333333</v>
+        <v>46280.54201388889</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001328646245691747</v>
+        <v>0.001320978735730978</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>hashnote-usyc</t>
+          <t>bittensor</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>usyc</t>
+          <t>tao</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Circle USYC</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1.14</v>
+        <v>225.33</v>
       </c>
       <c r="F41" t="n">
-        <v>2605584295</v>
+        <v>2555400017</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>148329497</v>
       </c>
       <c r="I41" t="n">
-        <v>1.14</v>
+        <v>241.79</v>
       </c>
       <c r="J41" t="n">
-        <v>1.14</v>
+        <v>223.09</v>
       </c>
       <c r="K41" t="n">
-        <v>7.625e-05</v>
+        <v>-9.283924826997833</v>
       </c>
       <c r="L41" t="n">
-        <v>0.00671</v>
+        <v>-3.97822</v>
       </c>
       <c r="M41" t="n">
-        <v>2291167466.910423</v>
+        <v>11339645.9251</v>
       </c>
       <c r="N41" t="n">
-        <v>2291167466.910423</v>
+        <v>21000000</v>
       </c>
       <c r="O41" t="n">
-        <v>1.14</v>
+        <v>757.6</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>46279.50347222222</v>
+        <v>45358.44833333333</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>0.00130898733438703</v>
+        <v>0.001288109636007382</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3219,34 +3219,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1.099</v>
+        <v>1.1</v>
       </c>
       <c r="F42" t="n">
-        <v>2497076821</v>
+        <v>2508232270</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
       </c>
       <c r="H42" t="n">
-        <v>2469543</v>
+        <v>2451075</v>
       </c>
       <c r="I42" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="J42" t="n">
         <v>1.073</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.03170530368788538</v>
+        <v>0.0007872000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>-2.80488</v>
+        <v>0.03687</v>
       </c>
       <c r="M42" t="n">
-        <v>2272876618.22503</v>
+        <v>2273077194.610963</v>
       </c>
       <c r="N42" t="n">
-        <v>5414281884.44665</v>
+        <v>5414467041.118188</v>
       </c>
       <c r="O42" t="n">
         <v>5.64</v>
@@ -3255,19 +3255,19 @@
         <v>46205.17638888889</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001239641117195971</v>
+        <v>0.001257353924924328</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3286,34 +3286,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0.999871</v>
       </c>
       <c r="F43" t="n">
-        <v>2382483240</v>
+        <v>2363114871</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>277638174</v>
+        <v>302885988</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>1.001</v>
       </c>
       <c r="J43" t="n">
-        <v>0.999817</v>
+        <v>0.999754</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.1304607067109e-05</v>
+        <v>-0.000114811151807337</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.00113</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>2382406353.107469</v>
+        <v>2363406353.107541</v>
       </c>
       <c r="N43" t="n">
-        <v>2382406353.107468</v>
+        <v>2359976357.487542</v>
       </c>
       <c r="O43" t="n">
         <v>1.073</v>
@@ -3322,19 +3322,19 @@
         <v>45652.11518518518</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001166405320031186</v>
+        <v>0.001162730181357174</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3353,28 +3353,28 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>112.52</v>
+        <v>112.23</v>
       </c>
       <c r="F44" t="n">
-        <v>2363000637</v>
+        <v>2356599579</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>15641178</v>
+        <v>17719113</v>
       </c>
       <c r="I44" t="n">
         <v>114.57</v>
       </c>
       <c r="J44" t="n">
-        <v>112.9</v>
+        <v>111.88</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.207969078914175</v>
+        <v>-1.700078909527733</v>
       </c>
       <c r="L44" t="n">
-        <v>-1.06215</v>
+        <v>-1.51226</v>
       </c>
       <c r="M44" t="n">
         <v>21000000</v>
@@ -3389,19 +3389,19 @@
         <v>45934.66666666666</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.00115395415174498</v>
+        <v>0.001158481887743028</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3423,13 +3423,13 @@
         <v>1.15</v>
       </c>
       <c r="F45" t="n">
-        <v>2230402772</v>
+        <v>2232069303</v>
       </c>
       <c r="G45" t="n">
         <v>44</v>
       </c>
       <c r="H45" t="n">
-        <v>2204246</v>
+        <v>4126024</v>
       </c>
       <c r="I45" t="n">
         <v>1.15</v>
@@ -3438,16 +3438,16 @@
         <v>1.14</v>
       </c>
       <c r="K45" t="n">
-        <v>0.00021521</v>
+        <v>-0.000421448190936813</v>
       </c>
       <c r="L45" t="n">
-        <v>0.01879</v>
+        <v>-0.03646</v>
       </c>
       <c r="M45" t="n">
-        <v>1947118142.176293</v>
+        <v>1950284546.742239</v>
       </c>
       <c r="N45" t="n">
-        <v>1948863759.674766</v>
+        <v>1950284571.383834</v>
       </c>
       <c r="O45" t="n">
         <v>1.26</v>
@@ -3456,19 +3456,19 @@
         <v>45377.89175925926</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.001069211967576535</v>
+        <v>0.001077281969719615</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3487,31 +3487,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>128.27</v>
+        <v>127.1</v>
       </c>
       <c r="F46" t="n">
-        <v>1979215256</v>
+        <v>1960871266</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>228704407</v>
+        <v>232309710</v>
       </c>
       <c r="I46" t="n">
         <v>133.48</v>
       </c>
       <c r="J46" t="n">
-        <v>124.84</v>
+        <v>125.41</v>
       </c>
       <c r="K46" t="n">
-        <v>3.74</v>
+        <v>0.676671</v>
       </c>
       <c r="L46" t="n">
-        <v>3.00696</v>
+        <v>0.51344</v>
       </c>
       <c r="M46" t="n">
-        <v>15427712.70066378</v>
+        <v>15427725.26623425</v>
       </c>
       <c r="N46" t="n">
         <v>16000000</v>
@@ -3523,86 +3523,86 @@
         <v>44334.55554398148</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0009086801313988863</v>
+        <v>0.0009004473951900405</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>mantle</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>mnt</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mantle</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.573255</v>
+        <v>0.70362</v>
       </c>
       <c r="F47" t="n">
-        <v>1893106394</v>
+        <v>1903820068</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>25943886</v>
+        <v>32634718</v>
       </c>
       <c r="I47" t="n">
-        <v>0.576697</v>
+        <v>0.7355120000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>0.556098</v>
+        <v>0.553432</v>
       </c>
       <c r="K47" t="n">
-        <v>0.01612117</v>
+        <v>0.00815778</v>
       </c>
       <c r="L47" t="n">
-        <v>2.89359</v>
+        <v>1.40638</v>
       </c>
       <c r="M47" t="n">
-        <v>3302294382.53684</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N47" t="n">
-        <v>6219316794.889999</v>
+        <v>10000000000</v>
       </c>
       <c r="O47" t="n">
-        <v>2.86</v>
+        <v>0.782873</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>45938.71164351852</v>
+        <v>46279.42037037037</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0008536486794057554</v>
+        <v>0.0008632471837271068</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3621,28 +3621,28 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.697497</v>
+        <v>0.69319</v>
       </c>
       <c r="F48" t="n">
-        <v>1885521352</v>
+        <v>1874917814</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>86647040</v>
+        <v>83983574</v>
       </c>
       <c r="I48" t="n">
         <v>0.7098100000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>0.689983</v>
+        <v>0.683408</v>
       </c>
       <c r="K48" t="n">
-        <v>0.00743343</v>
+        <v>-0.003530075159953072</v>
       </c>
       <c r="L48" t="n">
-        <v>1.07721</v>
+        <v>-0.53695</v>
       </c>
       <c r="M48" t="n">
         <v>2704071066.799731</v>
@@ -3657,19 +3657,19 @@
         <v>45924.13766203704</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0008488011426366726</v>
+        <v>0.0008444014802494091</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3688,28 +3688,28 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4302.53</v>
+        <v>4297.19</v>
       </c>
       <c r="F49" t="n">
-        <v>1862712407</v>
+        <v>1860248516</v>
       </c>
       <c r="G49" t="n">
         <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>139692866</v>
+        <v>142796805</v>
       </c>
       <c r="I49" t="n">
-        <v>4357.16</v>
+        <v>4322.66</v>
       </c>
       <c r="J49" t="n">
-        <v>4266.85</v>
+        <v>4266.02</v>
       </c>
       <c r="K49" t="n">
-        <v>-39.15537911431238</v>
+        <v>10.41</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.90185</v>
+        <v>0.22468</v>
       </c>
       <c r="M49" t="n">
         <v>432906.598539</v>
@@ -3724,153 +3724,153 @@
         <v>46050.93814814815</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R49" t="b">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0008342241370576014</v>
+        <v>0.0008348363701948789</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>world-liberty-financial</t>
+          <t>mantle</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>wlfi</t>
+          <t>mnt</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>World Liberty Financial</t>
+          <t>Mantle</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.057452</v>
+        <v>0.55154</v>
       </c>
       <c r="F50" t="n">
-        <v>1826519621</v>
+        <v>1821320244</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>35019422</v>
+        <v>22814959</v>
       </c>
       <c r="I50" t="n">
-        <v>0.058603</v>
+        <v>0.581183</v>
       </c>
       <c r="J50" t="n">
-        <v>0.056864</v>
+        <v>0.551291</v>
       </c>
       <c r="K50" t="n">
-        <v>0.00054135</v>
+        <v>-0.01576741668789894</v>
       </c>
       <c r="L50" t="n">
-        <v>0.95124</v>
+        <v>-2.78762</v>
       </c>
       <c r="M50" t="n">
-        <v>31777350471</v>
+        <v>3302294382.53684</v>
       </c>
       <c r="N50" t="n">
-        <v>100000000000</v>
+        <v>6219316794.889999</v>
       </c>
       <c r="O50" t="n">
-        <v>0.331336</v>
+        <v>2.86</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>45901.18065972222</v>
+        <v>45938.71164351852</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R50" t="b">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0008110936308704838</v>
+        <v>0.000809453205580411</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>world-liberty-financial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>wlfi</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.00368359</v>
+        <v>0.057155</v>
       </c>
       <c r="F51" t="n">
-        <v>1726347329</v>
+        <v>1816498792</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>114464800</v>
+        <v>29696092</v>
       </c>
       <c r="I51" t="n">
-        <v>0.00380079</v>
+        <v>0.058603</v>
       </c>
       <c r="J51" t="n">
-        <v>0.00354774</v>
+        <v>0.056788</v>
       </c>
       <c r="K51" t="n">
-        <v>0.00018135</v>
+        <v>-0.000289076965196013</v>
       </c>
       <c r="L51" t="n">
-        <v>5.17824</v>
+        <v>-0.46882</v>
       </c>
       <c r="M51" t="n">
-        <v>468546701392.5829</v>
+        <v>31777354724</v>
       </c>
       <c r="N51" t="n">
-        <v>834058521647.854</v>
+        <v>100000000000</v>
       </c>
       <c r="O51" t="n">
-        <v>0.00881908</v>
+        <v>0.331336</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>45914.36296296296</v>
+        <v>45901.18065972222</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0007470743586352999</v>
+        <v>0.0008063093796793601</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3889,28 +3889,28 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.353999</v>
+        <v>0.346558</v>
       </c>
       <c r="F52" t="n">
-        <v>1723853332</v>
+        <v>1687473441</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>107834998</v>
+        <v>74904800</v>
       </c>
       <c r="I52" t="n">
         <v>0.365023</v>
       </c>
       <c r="J52" t="n">
-        <v>0.344342</v>
+        <v>0.344965</v>
       </c>
       <c r="K52" t="n">
-        <v>0.01173941</v>
+        <v>-0.008247247960141424</v>
       </c>
       <c r="L52" t="n">
-        <v>3.42997</v>
+        <v>-2.37679</v>
       </c>
       <c r="M52" t="n">
         <v>4869330647</v>
@@ -3925,19 +3925,19 @@
         <v>45641.69166666667</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R52" t="b">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0007454804660557357</v>
+        <v>0.0007221784497507853</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3956,34 +3956,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.992134</v>
+        <v>0.987437</v>
       </c>
       <c r="F53" t="n">
-        <v>1689505775</v>
+        <v>1681496989</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>136435235</v>
+        <v>137018341</v>
       </c>
       <c r="I53" t="n">
         <v>1.036</v>
       </c>
       <c r="J53" t="n">
-        <v>0.9884849999999999</v>
+        <v>0.9796049999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.01550569575868166</v>
+        <v>-0.02848518674979184</v>
       </c>
       <c r="L53" t="n">
-        <v>-1.53881</v>
+        <v>-2.8598</v>
       </c>
       <c r="M53" t="n">
-        <v>1702798500.775251</v>
+        <v>1702874768.910783</v>
       </c>
       <c r="N53" t="n">
-        <v>1702806667.802638</v>
+        <v>1702890257.762186</v>
       </c>
       <c r="O53" t="n">
         <v>54.98</v>
@@ -3992,86 +3992,86 @@
         <v>44504.25704861111</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R53" t="b">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0007235292302569531</v>
+        <v>0.0007182815065490303</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.621812</v>
+        <v>0.00358044</v>
       </c>
       <c r="F54" t="n">
-        <v>1678535453</v>
+        <v>1677536262</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>32002995</v>
+        <v>115713157</v>
       </c>
       <c r="I54" t="n">
-        <v>0.782873</v>
+        <v>0.00380079</v>
       </c>
       <c r="J54" t="n">
-        <v>0.550861</v>
+        <v>0.00356134</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.05165533995442673</v>
+        <v>-6.6514859277032e-05</v>
       </c>
       <c r="L54" t="n">
-        <v>-7.67006</v>
+        <v>-1.86686</v>
       </c>
       <c r="M54" t="n">
-        <v>2708142280.000001</v>
+        <v>468474629168.2731</v>
       </c>
       <c r="N54" t="n">
-        <v>10000000000</v>
+        <v>833978841344.554</v>
       </c>
       <c r="O54" t="n">
-        <v>0.782873</v>
+        <v>0.00881908</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>46279.42037037037</v>
+        <v>45914.36296296296</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0007165181894131875</v>
+        <v>0.0007156989160494066</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4090,28 +4090,28 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1.7e-06</v>
+        <v>1.69e-06</v>
       </c>
       <c r="F55" t="n">
-        <v>1526676591</v>
+        <v>1515518580</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>85564279</v>
+        <v>24186473</v>
       </c>
       <c r="I55" t="n">
         <v>1.71e-06</v>
       </c>
       <c r="J55" t="n">
-        <v>1.69e-06</v>
+        <v>1.68e-06</v>
       </c>
       <c r="K55" t="n">
-        <v>7.322e-09</v>
+        <v>-1.0232432597e-08</v>
       </c>
       <c r="L55" t="n">
-        <v>0.43269</v>
+        <v>-0.53354</v>
       </c>
       <c r="M55" t="n">
         <v>898232728634017.2</v>
@@ -4126,19 +4126,19 @@
         <v>45629.67800925926</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R55" t="b">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0006194664634957727</v>
+        <v>0.0006100553495263278</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4157,34 +4157,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.999385</v>
+        <v>0.998906</v>
       </c>
       <c r="F56" t="n">
-        <v>1521785559</v>
+        <v>1499951843</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>3081524</v>
+        <v>7702046</v>
       </c>
       <c r="I56" t="n">
         <v>0.999766</v>
       </c>
       <c r="J56" t="n">
-        <v>0.998611</v>
+        <v>0.9987279999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>0.00042834</v>
+        <v>-0.000103033010561582</v>
       </c>
       <c r="L56" t="n">
-        <v>0.04288</v>
+        <v>0.01199</v>
       </c>
       <c r="M56" t="n">
-        <v>1522697852</v>
+        <v>1501621157</v>
       </c>
       <c r="N56" t="n">
-        <v>1527853807</v>
+        <v>1500853803</v>
       </c>
       <c r="O56" t="n">
         <v>1.24</v>
@@ -4193,354 +4193,354 @@
         <v>46212.39942129629</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R56" t="b">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0006163406459381691</v>
+        <v>0.0005999050647209522</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>internet-computer</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>icp</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Internet Computer</t>
+          <t>Morpho</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2.73</v>
+        <v>2.13</v>
       </c>
       <c r="F57" t="n">
-        <v>1519711785</v>
+        <v>1468888515</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>39738610</v>
+        <v>16440903</v>
       </c>
       <c r="I57" t="n">
-        <v>2.85</v>
+        <v>2.23</v>
       </c>
       <c r="J57" t="n">
-        <v>2.71</v>
+        <v>2.12</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.03372515551564437</v>
+        <v>-0.07791215298827892</v>
       </c>
       <c r="L57" t="n">
-        <v>-1.2212</v>
+        <v>-3.52363</v>
       </c>
       <c r="M57" t="n">
-        <v>556822465.3739831</v>
+        <v>689139191.0768665</v>
       </c>
       <c r="N57" t="n">
-        <v>556822835.1342702</v>
+        <v>1000000000</v>
       </c>
       <c r="O57" t="n">
-        <v>700.65</v>
+        <v>4.17</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>44326.33741898148</v>
+        <v>45674.19883101852</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R57" t="b">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0006150153143558565</v>
+        <v>0.0005796502337822141</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>ethena</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>ena</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Morpho</t>
+          <t>Ethena</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2.18</v>
+        <v>0.143826</v>
       </c>
       <c r="F58" t="n">
-        <v>1500123106</v>
+        <v>1450610285</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>17752244</v>
+        <v>297301548</v>
       </c>
       <c r="I58" t="n">
-        <v>2.24</v>
+        <v>0.148653</v>
       </c>
       <c r="J58" t="n">
-        <v>2.16</v>
+        <v>0.139581</v>
       </c>
       <c r="K58" t="n">
-        <v>0.02762086</v>
+        <v>0.00269862</v>
       </c>
       <c r="L58" t="n">
-        <v>1.28534</v>
+        <v>1.82936</v>
       </c>
       <c r="M58" t="n">
-        <v>689113485.2462531</v>
+        <v>10095312500</v>
       </c>
       <c r="N58" t="n">
-        <v>1000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="O58" t="n">
-        <v>4.17</v>
+        <v>1.52</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>45674.19883101852</v>
+        <v>45393.21892361111</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0006024963537871132</v>
+        <v>0.0005677319210209617</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sky</t>
+          <t>Pepe</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.063151</v>
+        <v>3.45e-06</v>
       </c>
       <c r="F59" t="n">
-        <v>1479524760</v>
+        <v>1449365068</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>11887885</v>
+        <v>199905591</v>
       </c>
       <c r="I59" t="n">
-        <v>0.065204</v>
+        <v>3.58e-06</v>
       </c>
       <c r="J59" t="n">
-        <v>0.062163</v>
+        <v>3.39e-06</v>
       </c>
       <c r="K59" t="n">
-        <v>0.00123391</v>
+        <v>3.59802e-10</v>
       </c>
       <c r="L59" t="n">
-        <v>1.99282</v>
+        <v>-0.09737</v>
       </c>
       <c r="M59" t="n">
-        <v>23427036695.42831</v>
+        <v>420690000000000</v>
       </c>
       <c r="N59" t="n">
-        <v>23459804203.60596</v>
+        <v>420690000000000</v>
       </c>
       <c r="O59" t="n">
-        <v>0.100535</v>
+        <v>2.803e-05</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>45630.09302083333</v>
+        <v>45635.35457175926</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R59" t="b">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0005893321235010726</v>
+        <v>0.0005669199777605022</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Pepe</t>
+          <t>Sky</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3.45e-06</v>
+        <v>0.061537</v>
       </c>
       <c r="F60" t="n">
-        <v>1452076193</v>
+        <v>1441504397</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>202273322</v>
+        <v>12430056</v>
       </c>
       <c r="I60" t="n">
-        <v>3.58e-06</v>
+        <v>0.065204</v>
       </c>
       <c r="J60" t="n">
-        <v>3.39e-06</v>
+        <v>0.061287</v>
       </c>
       <c r="K60" t="n">
-        <v>9.014e-08</v>
+        <v>-0.001827857813673638</v>
       </c>
       <c r="L60" t="n">
-        <v>2.68021</v>
+        <v>-2.90173</v>
       </c>
       <c r="M60" t="n">
-        <v>420690000000000</v>
+        <v>23426097368.71168</v>
       </c>
       <c r="N60" t="n">
-        <v>420690000000000</v>
+        <v>23459804203.60596</v>
       </c>
       <c r="O60" t="n">
-        <v>2.803e-05</v>
+        <v>0.100535</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>45635.35457175926</v>
+        <v>45630.09302083333</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0005717899743882351</v>
+        <v>0.0005617944302927602</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ethena</t>
+          <t>internet-computer</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ena</t>
+          <t>icp</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ethena</t>
+          <t>Internet Computer</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.143689</v>
+        <v>2.56</v>
       </c>
       <c r="F61" t="n">
-        <v>1451421164</v>
+        <v>1425439616</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>325876097</v>
+        <v>42887004</v>
       </c>
       <c r="I61" t="n">
-        <v>0.148653</v>
+        <v>2.81</v>
       </c>
       <c r="J61" t="n">
-        <v>0.137803</v>
+        <v>2.55</v>
       </c>
       <c r="K61" t="n">
-        <v>0.00704747</v>
+        <v>-0.1819481903047433</v>
       </c>
       <c r="L61" t="n">
-        <v>5.15763</v>
+        <v>-6.70116</v>
       </c>
       <c r="M61" t="n">
-        <v>10095312500</v>
+        <v>556836861.785925</v>
       </c>
       <c r="N61" t="n">
-        <v>15000000000</v>
+        <v>556837055.0446609</v>
       </c>
       <c r="O61" t="n">
-        <v>1.52</v>
+        <v>700.65</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>45393.21892361111</v>
+        <v>44326.33741898148</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R61" t="b">
         <v>1</v>
       </c>
       <c r="S61" t="n">
-        <v>0.000571371350844382</v>
+        <v>0.0005513193960909241</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4559,34 +4559,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.999956</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>1391737243</v>
+        <v>1377093904</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>41760343</v>
+        <v>31562399</v>
       </c>
       <c r="I62" t="n">
         <v>1</v>
       </c>
       <c r="J62" t="n">
-        <v>0.999939</v>
+        <v>0.999933</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.000256610788944456</v>
+        <v>-4.5947677081992e-05</v>
       </c>
       <c r="L62" t="n">
-        <v>-0.02566</v>
+        <v>-0.01203</v>
       </c>
       <c r="M62" t="n">
-        <v>1391792045.16</v>
+        <v>1376792098.16</v>
       </c>
       <c r="N62" t="n">
-        <v>1391792045.16</v>
+        <v>1376792098.16</v>
       </c>
       <c r="O62" t="n">
         <v>1.002</v>
@@ -4595,421 +4595,421 @@
         <v>46092.00303240741</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005332278571668866</v>
+        <v>0.0005197955933878487</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>worldcoin-wld</t>
+          <t>spiko-amundi-overnight-swap-fund-eur</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>wld</t>
+          <t>eursafo</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Worldcoin</t>
+          <t>Spiko Amundi Overnight Swap Fund (EUR)</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.383451</v>
+        <v>1.17</v>
       </c>
       <c r="F63" t="n">
-        <v>1378123513</v>
+        <v>1376544776</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>153034511</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0.399039</v>
+        <v>1.17</v>
       </c>
       <c r="J63" t="n">
-        <v>0.379332</v>
+        <v>1.17</v>
       </c>
       <c r="K63" t="n">
-        <v>0.0036273</v>
+        <v>0.00164308</v>
       </c>
       <c r="L63" t="n">
-        <v>0.955</v>
+        <v>0.14074</v>
       </c>
       <c r="M63" t="n">
-        <v>3594239151.909092</v>
+        <v>1177453283.40974</v>
       </c>
       <c r="N63" t="n">
-        <v>10000000000</v>
+        <v>1177453283.40974</v>
       </c>
       <c r="O63" t="n">
-        <v>11.74</v>
+        <v>1.18</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>45360.67409722223</v>
+        <v>46255.48263888889</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.000524527436425727</v>
+        <v>0.0005194375346890599</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>spiko-amundi-overnight-swap-fund-eur</t>
+          <t>united-stables</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>eursafo</t>
+          <t>u</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Spiko Amundi Overnight Swap Fund (EUR)</t>
+          <t>United Stables</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1.17</v>
+        <v>0.999803</v>
       </c>
       <c r="F64" t="n">
-        <v>1375639431</v>
+        <v>1373827468</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>216485336</v>
       </c>
       <c r="I64" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
-        <v>1.17</v>
+        <v>0.999583</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.004895468671041181</v>
+        <v>0.00021758</v>
       </c>
       <c r="L64" t="n">
-        <v>-0.41727</v>
+        <v>0.01423</v>
       </c>
       <c r="M64" t="n">
-        <v>1177453283.40974</v>
+        <v>1374129107.8</v>
       </c>
       <c r="N64" t="n">
-        <v>1177453283.40974</v>
+        <v>1375129007.8</v>
       </c>
       <c r="O64" t="n">
-        <v>1.18</v>
+        <v>1.008</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>46255.48263888889</v>
+        <v>46058.54591435185</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R64" t="b">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0005229398804395616</v>
+        <v>0.0005176657150646952</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>bitget-token</t>
+          <t>worldcoin-wld</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>bgb</t>
+          <t>wld</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Bitget Token</t>
+          <t>Worldcoin</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1.94</v>
+        <v>0.375954</v>
       </c>
       <c r="F65" t="n">
-        <v>1358577952</v>
+        <v>1351513415</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>11750541</v>
+        <v>142263721</v>
       </c>
       <c r="I65" t="n">
-        <v>1.96</v>
+        <v>0.399039</v>
       </c>
       <c r="J65" t="n">
-        <v>1.93</v>
+        <v>0.37093</v>
       </c>
       <c r="K65" t="n">
-        <v>0.01663887</v>
+        <v>-0.009506752743714764</v>
       </c>
       <c r="L65" t="n">
-        <v>0.86469</v>
+        <v>-2.53456</v>
       </c>
       <c r="M65" t="n">
-        <v>699992029.6481038</v>
+        <v>3594283025.842473</v>
       </c>
       <c r="N65" t="n">
-        <v>910920874.6481038</v>
+        <v>10000000000</v>
       </c>
       <c r="O65" t="n">
-        <v>8.449999999999999</v>
+        <v>11.74</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>45653.15375</v>
+        <v>45360.67409722223</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0005120360322093955</v>
+        <v>0.0005031158454862314</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>falcon-finance</t>
+          <t>bitget-token</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>usdf</t>
+          <t>bgb</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Falcon USD</t>
+          <t>Bitget Token</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.996285</v>
+        <v>1.92</v>
       </c>
       <c r="F66" t="n">
-        <v>1339542714</v>
+        <v>1347341975</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
       </c>
       <c r="H66" t="n">
-        <v>610664</v>
+        <v>10542804</v>
       </c>
       <c r="I66" t="n">
-        <v>0.997106</v>
+        <v>1.96</v>
       </c>
       <c r="J66" t="n">
-        <v>0.996221</v>
+        <v>1.92</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.00024087761769287</v>
+        <v>-0.01668685705277295</v>
       </c>
       <c r="L66" t="n">
-        <v>-0.02417</v>
+        <v>-0.8549600000000001</v>
       </c>
       <c r="M66" t="n">
-        <v>1344517433.482414</v>
+        <v>699992029.6481038</v>
       </c>
       <c r="N66" t="n">
-        <v>1344517433.482414</v>
+        <v>910920874.6481038</v>
       </c>
       <c r="O66" t="n">
-        <v>1.075</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>45785.55951388889</v>
+        <v>45653.15375</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0004998707711451532</v>
+        <v>0.0005003958596569253</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>falcon-finance</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>usdf</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>BFUSD</t>
+          <t>Falcon USD</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.999714</v>
+        <v>0.996205</v>
       </c>
       <c r="F67" t="n">
-        <v>1319775637</v>
+        <v>1339405916</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
       </c>
       <c r="H67" t="n">
-        <v>4661439</v>
+        <v>818460</v>
       </c>
       <c r="I67" t="n">
-        <v>0.999887</v>
+        <v>0.9967240000000001</v>
       </c>
       <c r="J67" t="n">
-        <v>0.999053</v>
+        <v>0.996085</v>
       </c>
       <c r="K67" t="n">
-        <v>0.00059451</v>
+        <v>-8.8844266114108e-05</v>
       </c>
       <c r="L67" t="n">
-        <v>0.0595</v>
+        <v>-0.01422</v>
       </c>
       <c r="M67" t="n">
-        <v>1320000000</v>
+        <v>1344553697.303609</v>
       </c>
       <c r="N67" t="n">
-        <v>1320000000</v>
+        <v>1344553697.303609</v>
       </c>
       <c r="O67" t="n">
-        <v>1.007</v>
+        <v>1.075</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>45940.56990740741</v>
+        <v>45785.55951388889</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0004872377979098313</v>
+        <v>0.0004952211554731092</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>united-stables</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>United Stables</t>
+          <t>BFUSD</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.999865</v>
+        <v>0.999567</v>
       </c>
       <c r="F68" t="n">
-        <v>1315117304</v>
+        <v>1319406092</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>210457416</v>
+        <v>2266914</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0.999887</v>
       </c>
       <c r="J68" t="n">
-        <v>0.999121</v>
+        <v>0.999465</v>
       </c>
       <c r="K68" t="n">
-        <v>0.00050696</v>
+        <v>3.971e-05</v>
       </c>
       <c r="L68" t="n">
-        <v>0.05073</v>
+        <v>0.00378</v>
       </c>
       <c r="M68" t="n">
-        <v>1315244007.8</v>
+        <v>1320000000</v>
       </c>
       <c r="N68" t="n">
-        <v>1315244007.8</v>
+        <v>1320000000</v>
       </c>
       <c r="O68" t="n">
-        <v>1.008</v>
+        <v>1.007</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>46058.54591435185</v>
+        <v>45940.56990740741</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.000484260696332789</v>
+        <v>0.0004821802780138584</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5028,34 +5028,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>7.54</v>
+        <v>7.38</v>
       </c>
       <c r="F69" t="n">
-        <v>1192445170</v>
+        <v>1167799278</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>45235742</v>
+        <v>44519262</v>
       </c>
       <c r="I69" t="n">
         <v>7.76</v>
       </c>
       <c r="J69" t="n">
-        <v>7.53</v>
+        <v>7.36</v>
       </c>
       <c r="K69" t="n">
-        <v>0.03071381</v>
+        <v>-0.2463582866913399</v>
       </c>
       <c r="L69" t="n">
-        <v>0.40915</v>
+        <v>-3.23381</v>
       </c>
       <c r="M69" t="n">
-        <v>158170028.1227235</v>
+        <v>158175159.0847009</v>
       </c>
       <c r="N69" t="n">
-        <v>158170028.1227235</v>
+        <v>158175567.4156298</v>
       </c>
       <c r="O69" t="n">
         <v>167.09</v>
@@ -5064,153 +5064,153 @@
         <v>44322.44053240741</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0004058619636551243</v>
+        <v>0.0003833251139203426</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>pi-network</t>
+          <t>lighter</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>pi</t>
+          <t>lit</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Pi Network</t>
+          <t>Lighter</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.09816800000000001</v>
+        <v>4.29</v>
       </c>
       <c r="F70" t="n">
-        <v>1098844648</v>
+        <v>1072773446</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>5260698</v>
+        <v>80010700</v>
       </c>
       <c r="I70" t="n">
-        <v>0.09867099999999999</v>
+        <v>4.63</v>
       </c>
       <c r="J70" t="n">
-        <v>0.096938</v>
+        <v>4.31</v>
       </c>
       <c r="K70" t="n">
-        <v>0.00097241</v>
+        <v>-0.1893094868186722</v>
       </c>
       <c r="L70" t="n">
-        <v>1.00046</v>
+        <v>-4.19031</v>
       </c>
       <c r="M70" t="n">
-        <v>11193100322.87027</v>
+        <v>250000000</v>
       </c>
       <c r="N70" t="n">
-        <v>17220154342.87733</v>
+        <v>1000000000</v>
       </c>
       <c r="O70" t="n">
-        <v>2.99</v>
+        <v>7.86</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>45714.36184027778</v>
+        <v>46021.04538194444</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0003460426545464406</v>
+        <v>0.000321363557129875</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>lighter</t>
+          <t>pi-network</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>lit</t>
+          <t>pi</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Lighter</t>
+          <t>Pi Network</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4.37</v>
+        <v>0.095679</v>
       </c>
       <c r="F71" t="n">
-        <v>1091394927</v>
+        <v>1071248945</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>117268467</v>
+        <v>6883895</v>
       </c>
       <c r="I71" t="n">
-        <v>4.69</v>
+        <v>0.09867099999999999</v>
       </c>
       <c r="J71" t="n">
-        <v>4.21</v>
+        <v>0.09478</v>
       </c>
       <c r="K71" t="n">
-        <v>0.178989</v>
+        <v>-0.001542167443357528</v>
       </c>
       <c r="L71" t="n">
-        <v>4.2755</v>
+        <v>-1.62195</v>
       </c>
       <c r="M71" t="n">
-        <v>250000000</v>
+        <v>11193100867.75027</v>
       </c>
       <c r="N71" t="n">
-        <v>1000000000</v>
+        <v>17220155181.15426</v>
       </c>
       <c r="O71" t="n">
-        <v>7.86</v>
+        <v>2.99</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>46021.04538194444</v>
+        <v>45714.36184027778</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R71" t="b">
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0003412816002942811</v>
+        <v>0.0003203695068458573</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5229,34 +5229,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>22.71</v>
+        <v>22.27</v>
       </c>
       <c r="F72" t="n">
-        <v>1090563974</v>
+        <v>1068292746</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>45172293</v>
+        <v>35619335</v>
       </c>
       <c r="I72" t="n">
-        <v>23.28</v>
+        <v>23.27</v>
       </c>
       <c r="J72" t="n">
-        <v>21.47</v>
+        <v>21.56</v>
       </c>
       <c r="K72" t="n">
-        <v>1.49</v>
+        <v>-0.2217232803884315</v>
       </c>
       <c r="L72" t="n">
-        <v>6.99935</v>
+        <v>-0.85206</v>
       </c>
       <c r="M72" t="n">
-        <v>47972447.24318358</v>
+        <v>47975693.6029577</v>
       </c>
       <c r="N72" t="n">
-        <v>81010558.97664872</v>
+        <v>81014279.80364013</v>
       </c>
       <c r="O72" t="n">
         <v>29.19</v>
@@ -5265,19 +5265,19 @@
         <v>46274.32083333333</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0003407505451965137</v>
+        <v>0.0003184419184378713</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5296,28 +5296,28 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.096807</v>
+        <v>0.096828</v>
       </c>
       <c r="F73" t="n">
-        <v>1037331940</v>
+        <v>1038280082</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>59166159</v>
+        <v>60782906</v>
       </c>
       <c r="I73" t="n">
-        <v>0.09861499999999999</v>
+        <v>0.098589</v>
       </c>
       <c r="J73" t="n">
-        <v>0.09566</v>
+        <v>0.095649</v>
       </c>
       <c r="K73" t="n">
-        <v>0.0008951</v>
+        <v>-0.0009225235350158319</v>
       </c>
       <c r="L73" t="n">
-        <v>0.93325</v>
+        <v>-0.95701</v>
       </c>
       <c r="M73" t="n">
         <v>10714685269.72835</v>
@@ -5332,19 +5332,19 @@
         <v>45364.45493055556</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R73" t="b">
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003067303984250036</v>
+        <v>0.000298872172551624</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5363,34 +5363,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>9.34</v>
+        <v>9.17</v>
       </c>
       <c r="F74" t="n">
-        <v>995839693</v>
+        <v>977340269</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>3290086</v>
+        <v>3739451</v>
       </c>
       <c r="I74" t="n">
-        <v>9.369999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="J74" t="n">
-        <v>9.1</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>0.233148</v>
+        <v>-0.1388848429960898</v>
       </c>
       <c r="L74" t="n">
-        <v>2.56047</v>
+        <v>-1.49455</v>
       </c>
       <c r="M74" t="n">
-        <v>106628362.8519531</v>
+        <v>106628927.3474872</v>
       </c>
       <c r="N74" t="n">
-        <v>118879637.7543574</v>
+        <v>118880214.648508</v>
       </c>
       <c r="O74" t="n">
         <v>25.38</v>
@@ -5399,19 +5399,19 @@
         <v>45682.66666666666</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R74" t="b">
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0002802130511295808</v>
+        <v>0.0002591363911906149</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106.49</v>
+        <v>106.54</v>
       </c>
       <c r="F75" t="n">
-        <v>970348700</v>
+        <v>970804306</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
@@ -5442,16 +5442,16 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>106.49</v>
+        <v>106.54</v>
       </c>
       <c r="J75" t="n">
         <v>106.49</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>0.04695</v>
       </c>
       <c r="M75" t="n">
         <v>9112111</v>
@@ -5460,92 +5460,92 @@
         <v>9112111</v>
       </c>
       <c r="O75" t="n">
-        <v>106.49</v>
+        <v>106.54</v>
       </c>
       <c r="P75" s="1" t="n">
-        <v>46273.93067129629</v>
+        <v>46280.14583333334</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R75" t="b">
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0002639219711529725</v>
+        <v>0.0002548746190589603</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>kaspa</t>
+          <t>just</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>kas</t>
+          <t>jst</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Kaspa</t>
+          <t>JUST</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.03491874</v>
+        <v>0.115767</v>
       </c>
       <c r="F76" t="n">
-        <v>967415813</v>
+        <v>947997627</v>
       </c>
       <c r="G76" t="n">
         <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>10871350</v>
+        <v>24339509</v>
       </c>
       <c r="I76" t="n">
-        <v>0.03532002</v>
+        <v>0.116079</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03324669</v>
+        <v>0.112465</v>
       </c>
       <c r="K76" t="n">
-        <v>0.0011685</v>
+        <v>0.00243642</v>
       </c>
       <c r="L76" t="n">
-        <v>3.4622</v>
+        <v>2.15246</v>
       </c>
       <c r="M76" t="n">
-        <v>27700473315.66705</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="N76" t="n">
-        <v>27700811506.09942</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="O76" t="n">
-        <v>0.207411</v>
+        <v>0.193254</v>
       </c>
       <c r="P76" s="1" t="n">
-        <v>45504.69498842592</v>
+        <v>44290.85721064815</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R76" t="b">
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0002620475876529121</v>
+        <v>0.0002400035328888285</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5564,28 +5564,28 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6.9</v>
+        <v>6.88</v>
       </c>
       <c r="F77" t="n">
-        <v>947096614</v>
+        <v>943479766</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>6128464</v>
+        <v>3877147</v>
       </c>
       <c r="I77" t="n">
         <v>7.13</v>
       </c>
       <c r="J77" t="n">
-        <v>6.86</v>
+        <v>6.88</v>
       </c>
       <c r="K77" t="n">
-        <v>0.058742</v>
+        <v>-0.1194161402508094</v>
       </c>
       <c r="L77" t="n">
-        <v>0.85832</v>
+        <v>-1.73771</v>
       </c>
       <c r="M77" t="n">
         <v>137155021.2773955</v>
@@ -5600,220 +5600,220 @@
         <v>44531.29832175926</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R77" t="b">
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002490617578749343</v>
+        <v>0.0002370576633812304</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>quant-network</t>
+          <t>kaspa</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>qnt</t>
+          <t>kas</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Kaspa</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>64.51000000000001</v>
+        <v>0.03388516</v>
       </c>
       <c r="F78" t="n">
-        <v>938743755</v>
+        <v>939990647</v>
       </c>
       <c r="G78" t="n">
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>7167107</v>
+        <v>11621395</v>
       </c>
       <c r="I78" t="n">
-        <v>64.78</v>
+        <v>0.03532002</v>
       </c>
       <c r="J78" t="n">
-        <v>62.75</v>
+        <v>0.03340135</v>
       </c>
       <c r="K78" t="n">
-        <v>1.77</v>
+        <v>0.00035058</v>
       </c>
       <c r="L78" t="n">
-        <v>2.81932</v>
+        <v>1.06347</v>
       </c>
       <c r="M78" t="n">
-        <v>14544176.16408117</v>
+        <v>27701726137.01383</v>
       </c>
       <c r="N78" t="n">
-        <v>14612493</v>
+        <v>27701821229.68735</v>
       </c>
       <c r="O78" t="n">
-        <v>427.42</v>
+        <v>0.207411</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>44450.05208333334</v>
+        <v>45504.69498842592</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R78" t="b">
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002437235156965173</v>
+        <v>0.0002347825846945508</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>just</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>jst</t>
+          <t>arb</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>JUST</t>
+          <t>Arbitrum</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.114497</v>
+        <v>0.140071</v>
       </c>
       <c r="F79" t="n">
-        <v>937681089</v>
+        <v>935413458</v>
       </c>
       <c r="G79" t="n">
         <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>21798469</v>
+        <v>203934843</v>
       </c>
       <c r="I79" t="n">
-        <v>0.114591</v>
+        <v>0.143736</v>
       </c>
       <c r="J79" t="n">
-        <v>0.112465</v>
+        <v>0.131607</v>
       </c>
       <c r="K79" t="n">
-        <v>0.00064492</v>
+        <v>0.00446819</v>
       </c>
       <c r="L79" t="n">
-        <v>0.56645</v>
+        <v>3.13831</v>
       </c>
       <c r="M79" t="n">
-        <v>8188743036.341737</v>
+        <v>6678075931</v>
       </c>
       <c r="N79" t="n">
-        <v>8188743036.341737</v>
+        <v>10000000000</v>
       </c>
       <c r="O79" t="n">
-        <v>0.193254</v>
+        <v>2.39</v>
       </c>
       <c r="P79" s="1" t="n">
-        <v>44290.85721064815</v>
+        <v>45303.18748842592</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R79" t="b">
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002430443747625246</v>
+        <v>0.0002317980303876314</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>quant-network</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>arb</t>
+          <t>qnt</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Arbitrum</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.134013</v>
+        <v>62.44</v>
       </c>
       <c r="F80" t="n">
-        <v>895591340</v>
+        <v>908830203</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>154359503</v>
+        <v>7799171</v>
       </c>
       <c r="I80" t="n">
-        <v>0.142061</v>
+        <v>65.02</v>
       </c>
       <c r="J80" t="n">
-        <v>0.132131</v>
+        <v>62.38</v>
       </c>
       <c r="K80" t="n">
-        <v>-7.935190169344701e-05</v>
+        <v>-1.883624011551255</v>
       </c>
       <c r="L80" t="n">
-        <v>-0.05918</v>
+        <v>-2.8827</v>
       </c>
       <c r="M80" t="n">
-        <v>6678075931</v>
+        <v>14544176.16408117</v>
       </c>
       <c r="N80" t="n">
-        <v>10000000000</v>
+        <v>14612493</v>
       </c>
       <c r="O80" t="n">
-        <v>2.39</v>
+        <v>427.42</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>45303.18748842592</v>
+        <v>44450.05208333334</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R80" t="b">
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.000216145168946793</v>
+        <v>0.000214464429305791</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5832,34 +5832,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.09596499999999999</v>
+        <v>0.095805</v>
       </c>
       <c r="F81" t="n">
-        <v>867575949</v>
+        <v>867128014</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>37884247</v>
+        <v>38797892</v>
       </c>
       <c r="I81" t="n">
-        <v>0.098883</v>
+        <v>0.098229</v>
       </c>
       <c r="J81" t="n">
-        <v>0.093946</v>
+        <v>0.09395299999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.001014014016988418</v>
+        <v>0.00082591</v>
       </c>
       <c r="L81" t="n">
-        <v>-1.0456</v>
+        <v>0.85286</v>
       </c>
       <c r="M81" t="n">
-        <v>9041305867.480665</v>
+        <v>9041440361.74052</v>
       </c>
       <c r="N81" t="n">
-        <v>9041339786.614456</v>
+        <v>9041449215.81741</v>
       </c>
       <c r="O81" t="n">
         <v>3.56</v>
@@ -5868,19 +5868,19 @@
         <v>43636.28563657407</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R81" t="b">
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0001982407673663228</v>
+        <v>0.0001872725331905293</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5899,34 +5899,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="F82" t="n">
-        <v>842792755</v>
+        <v>828847171</v>
       </c>
       <c r="G82" t="n">
         <v>81</v>
       </c>
       <c r="H82" t="n">
-        <v>48731093</v>
+        <v>50034794</v>
       </c>
       <c r="I82" t="n">
         <v>1.62</v>
       </c>
       <c r="J82" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="K82" t="n">
-        <v>0.00198646</v>
+        <v>0.01176572</v>
       </c>
       <c r="L82" t="n">
-        <v>0.12521</v>
+        <v>0.75398</v>
       </c>
       <c r="M82" t="n">
-        <v>530724739.158381</v>
+        <v>530840914.851673</v>
       </c>
       <c r="N82" t="n">
-        <v>530755609.732035</v>
+        <v>530857108.180759</v>
       </c>
       <c r="O82" t="n">
         <v>43.84</v>
@@ -5935,153 +5935,153 @@
         <v>44458.66666666666</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R82" t="b">
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0001824020357982822</v>
+        <v>0.0001623115244036609</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Spiko EU T-Bills Money Market Fund</t>
+          <t>NEXO</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1.22</v>
+        <v>0.803162</v>
       </c>
       <c r="F83" t="n">
-        <v>829733487</v>
+        <v>803120563</v>
       </c>
       <c r="G83" t="n">
         <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>4922595</v>
       </c>
       <c r="I83" t="n">
-        <v>1.23</v>
+        <v>0.838348</v>
       </c>
       <c r="J83" t="n">
-        <v>1.22</v>
+        <v>0.800049</v>
       </c>
       <c r="K83" t="n">
-        <v>-0.005126074567904038</v>
+        <v>-0.03110939307527849</v>
       </c>
       <c r="L83" t="n">
-        <v>-0.41785</v>
+        <v>-3.69456</v>
       </c>
       <c r="M83" t="n">
-        <v>679196801.73762</v>
+        <v>1000000000</v>
       </c>
       <c r="N83" t="n">
-        <v>679196801.73762</v>
+        <v>1000000000</v>
       </c>
       <c r="O83" t="n">
-        <v>1.26</v>
+        <v>4.07</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>46049.54175925926</v>
+        <v>44328.27623842593</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0001740559670741661</v>
+        <v>0.0001455364996649341</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NEXO</t>
+          <t>Spiko EU T-Bills Money Market Fund</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.81163</v>
+        <v>1.22</v>
       </c>
       <c r="F84" t="n">
-        <v>813181332</v>
+        <v>801792779</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>3513857</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>0.838348</v>
+        <v>1.22</v>
       </c>
       <c r="J84" t="n">
-        <v>0.813947</v>
+        <v>1.22</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.0110379836898139</v>
+        <v>0.00220774</v>
       </c>
       <c r="L84" t="n">
-        <v>-1.34173</v>
+        <v>0.18093</v>
       </c>
       <c r="M84" t="n">
-        <v>1000000000</v>
+        <v>655893653.31917</v>
       </c>
       <c r="N84" t="n">
-        <v>1000000000</v>
+        <v>655893653.31917</v>
       </c>
       <c r="O84" t="n">
-        <v>4.07</v>
+        <v>1.26</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>44328.27623842593</v>
+        <v>46049.54175925926</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R84" t="b">
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001634776235435622</v>
+        <v>0.0001446707186242432</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6100,34 +6100,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.238904</v>
+        <v>0.230018</v>
       </c>
       <c r="F85" t="n">
-        <v>792971070</v>
+        <v>763485841</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>61238503</v>
+        <v>60014202</v>
       </c>
       <c r="I85" t="n">
         <v>0.246898</v>
       </c>
       <c r="J85" t="n">
-        <v>0.233096</v>
+        <v>0.228675</v>
       </c>
       <c r="K85" t="n">
-        <v>0.00749233</v>
+        <v>-0.007376134673183238</v>
       </c>
       <c r="L85" t="n">
-        <v>3.23766</v>
+        <v>-3.11634</v>
       </c>
       <c r="M85" t="n">
         <v>3319369204.37</v>
       </c>
       <c r="N85" t="n">
-        <v>6861487117.895551</v>
+        <v>6861487098.486876</v>
       </c>
       <c r="O85" t="n">
         <v>2</v>
@@ -6136,19 +6136,19 @@
         <v>45322.29359953704</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R85" t="b">
         <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001505614144892422</v>
+        <v>0.0001196926946027759</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6170,7 +6170,7 @@
         <v>11.21</v>
       </c>
       <c r="F86" t="n">
-        <v>754918574</v>
+        <v>751978768</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
@@ -6185,372 +6185,372 @@
         <v>11.21</v>
       </c>
       <c r="K86" t="n">
-        <v>0.001089</v>
+        <v>0.003239</v>
       </c>
       <c r="L86" t="n">
-        <v>0.009719999999999999</v>
+        <v>0.0289</v>
       </c>
       <c r="M86" t="n">
-        <v>67347827.99992301</v>
+        <v>67066182.610332</v>
       </c>
       <c r="N86" t="n">
-        <v>67347827.99992301</v>
+        <v>65222093.392313</v>
       </c>
       <c r="O86" t="n">
         <v>11.21</v>
       </c>
       <c r="P86" s="1" t="n">
-        <v>46279.58333333334</v>
+        <v>46280.55555555555</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R86" t="b">
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001262423832280602</v>
+        <v>0.0001121895121293874</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>filecoin</t>
+          <t>pancakeswap-token</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.910478</v>
+        <v>2.29</v>
       </c>
       <c r="F87" t="n">
-        <v>753570066</v>
+        <v>732574091</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>278415645</v>
+        <v>74051260</v>
       </c>
       <c r="I87" t="n">
-        <v>1.033</v>
+        <v>2.4</v>
       </c>
       <c r="J87" t="n">
-        <v>0.9061439999999999</v>
+        <v>2.27</v>
       </c>
       <c r="K87" t="n">
-        <v>-0.06665711956897025</v>
+        <v>-0.06867599323406859</v>
       </c>
       <c r="L87" t="n">
-        <v>-6.82169</v>
+        <v>-2.92392</v>
       </c>
       <c r="M87" t="n">
-        <v>827813309</v>
+        <v>319429131.5073305</v>
       </c>
       <c r="N87" t="n">
-        <v>1957052463</v>
+        <v>331093394.0100838</v>
       </c>
       <c r="O87" t="n">
-        <v>236.84</v>
+        <v>43.96</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>44287.22894675926</v>
+        <v>44316.08914351852</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001253805630676178</v>
+        <v>9.953670003997387e-05</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>pancakeswap-token</t>
+          <t>stable-2</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>​​Stable</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2.34</v>
+        <v>0.0276833</v>
       </c>
       <c r="F88" t="n">
-        <v>746280358</v>
+        <v>729228574</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>85972002</v>
+        <v>9345608</v>
       </c>
       <c r="I88" t="n">
-        <v>2.4</v>
+        <v>0.02859739</v>
       </c>
       <c r="J88" t="n">
-        <v>2.27</v>
+        <v>0.02752428</v>
       </c>
       <c r="K88" t="n">
-        <v>0.078164</v>
+        <v>-0.001107858424843254</v>
       </c>
       <c r="L88" t="n">
-        <v>3.46156</v>
+        <v>-3.90902</v>
       </c>
       <c r="M88" t="n">
-        <v>319428613.3953888</v>
+        <v>26343010631</v>
       </c>
       <c r="N88" t="n">
-        <v>331093394.0100838</v>
+        <v>100000000000</v>
       </c>
       <c r="O88" t="n">
-        <v>43.96</v>
+        <v>0.04323745</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>44316.08914351852</v>
+        <v>46156.97986111111</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001207217717826285</v>
+        <v>9.735525698153293e-05</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>stable-2</t>
+          <t>filecoin</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>fil</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>​​Stable</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.02791111</v>
+        <v>0.877628</v>
       </c>
       <c r="F89" t="n">
-        <v>734698091</v>
+        <v>726414795</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>9414573</v>
+        <v>182542096</v>
       </c>
       <c r="I89" t="n">
-        <v>0.02947948</v>
+        <v>0.997536</v>
       </c>
       <c r="J89" t="n">
-        <v>0.02776311</v>
+        <v>0.869956</v>
       </c>
       <c r="K89" t="n">
-        <v>-4.3763375709591e-05</v>
+        <v>-0.1430934825638447</v>
       </c>
       <c r="L89" t="n">
-        <v>-0.15655</v>
+        <v>-13.77457</v>
       </c>
       <c r="M89" t="n">
-        <v>26327578875</v>
+        <v>827813309</v>
       </c>
       <c r="N89" t="n">
-        <v>100000000000</v>
+        <v>1957050532</v>
       </c>
       <c r="O89" t="n">
-        <v>0.04323745</v>
+        <v>236.84</v>
       </c>
       <c r="P89" s="1" t="n">
-        <v>46156.97986111111</v>
+        <v>44287.22894675926</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001133196420183062</v>
+        <v>9.552053347914544e-05</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>render-token</t>
+          <t>janus-henderson-anemoy-aaa-clo-fund</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>render</t>
+          <t>jaaa</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>Janus Henderson Anemoy AAA CLO Fund</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1.38</v>
+        <v>1.05</v>
       </c>
       <c r="F90" t="n">
-        <v>716935713</v>
+        <v>715044711</v>
       </c>
       <c r="G90" t="n">
         <v>89</v>
       </c>
       <c r="H90" t="n">
-        <v>36085963</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>1.41</v>
+        <v>1.05</v>
       </c>
       <c r="J90" t="n">
-        <v>1.37</v>
+        <v>1.05</v>
       </c>
       <c r="K90" t="n">
-        <v>0.0113678</v>
+        <v>8.500000000000001e-05</v>
       </c>
       <c r="L90" t="n">
-        <v>0.82941</v>
+        <v>0.0081</v>
       </c>
       <c r="M90" t="n">
-        <v>518776241.2826915</v>
+        <v>681220739.278982</v>
       </c>
       <c r="N90" t="n">
-        <v>533536414.5626915</v>
+        <v>681220786.91379</v>
       </c>
       <c r="O90" t="n">
-        <v>13.53</v>
+        <v>1.05</v>
       </c>
       <c r="P90" s="1" t="n">
-        <v>45368.35444444444</v>
+        <v>46280.48611111111</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>0.0001019678551117408</v>
+        <v>8.810667462991815e-05</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-aaa-clo-fund</t>
+          <t>render-token</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>jaaa</t>
+          <t>render</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy AAA CLO Fund</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="F91" t="n">
-        <v>714986808</v>
+        <v>704219729</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>36902335</v>
       </c>
       <c r="I91" t="n">
-        <v>1.05</v>
+        <v>1.41</v>
       </c>
       <c r="J91" t="n">
-        <v>1.049</v>
+        <v>1.35</v>
       </c>
       <c r="K91" t="n">
-        <v>0.000428</v>
+        <v>-0.02604220787391576</v>
       </c>
       <c r="L91" t="n">
-        <v>0.0408</v>
+        <v>-1.90472</v>
       </c>
       <c r="M91" t="n">
-        <v>681220739.278982</v>
+        <v>518776241.2826915</v>
       </c>
       <c r="N91" t="n">
-        <v>681220739.278982</v>
+        <v>533536414.5626915</v>
       </c>
       <c r="O91" t="n">
-        <v>1.05</v>
+        <v>13.53</v>
       </c>
       <c r="P91" s="1" t="n">
-        <v>46279.33680555555</v>
+        <v>45368.35444444444</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R91" t="b">
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>0.0001007223262607537</v>
+        <v>8.104824932774568e-05</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6572,7 +6572,7 @@
         <v>1.12</v>
       </c>
       <c r="F92" t="n">
-        <v>700205978</v>
+        <v>700262452</v>
       </c>
       <c r="G92" t="n">
         <v>91</v>
@@ -6587,10 +6587,10 @@
         <v>1.12</v>
       </c>
       <c r="K92" t="n">
-        <v>0.000216</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="L92" t="n">
-        <v>0.01936</v>
+        <v>0.008070000000000001</v>
       </c>
       <c r="M92" t="n">
         <v>627489934.721184</v>
@@ -6602,22 +6602,22 @@
         <v>1.12</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>46279.33680555555</v>
+        <v>46280.48958333334</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R92" t="b">
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>9.127602169150238e-05</v>
+        <v>7.846790839927992e-05</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6636,28 +6636,28 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.998983</v>
+        <v>0.9987549999999999</v>
       </c>
       <c r="F93" t="n">
-        <v>698277498</v>
+        <v>698117719</v>
       </c>
       <c r="G93" t="n">
         <v>92</v>
       </c>
       <c r="H93" t="n">
-        <v>6391973</v>
+        <v>7700537</v>
       </c>
       <c r="I93" t="n">
         <v>0.999081</v>
       </c>
       <c r="J93" t="n">
-        <v>0.998309</v>
+        <v>0.998621</v>
       </c>
       <c r="K93" t="n">
-        <v>0.00045765</v>
+        <v>0.00015295</v>
       </c>
       <c r="L93" t="n">
-        <v>0.04583</v>
+        <v>0.01535</v>
       </c>
       <c r="M93" t="n">
         <v>699000000</v>
@@ -6672,19 +6672,19 @@
         <v>45350.38608796296</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R93" t="b">
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>9.004354628682553e-05</v>
+        <v>7.706943608093294e-05</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6703,34 +6703,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>53.98</v>
+        <v>52.5</v>
       </c>
       <c r="F94" t="n">
-        <v>692431241</v>
+        <v>673584844</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
       </c>
       <c r="H94" t="n">
-        <v>94534295</v>
+        <v>91099510</v>
       </c>
       <c r="I94" t="n">
         <v>56.34</v>
       </c>
       <c r="J94" t="n">
-        <v>52.96</v>
+        <v>52.44</v>
       </c>
       <c r="K94" t="n">
-        <v>1.15</v>
+        <v>-1.576147428098317</v>
       </c>
       <c r="L94" t="n">
-        <v>2.18371</v>
+        <v>-3.00894</v>
       </c>
       <c r="M94" t="n">
-        <v>12828706.97240898</v>
+        <v>12829630.22789848</v>
       </c>
       <c r="N94" t="n">
-        <v>12828738.87202284</v>
+        <v>12829743.16411079</v>
       </c>
       <c r="O94" t="n">
         <v>1493.59</v>
@@ -6739,19 +6739,19 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R94" t="b">
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>8.630725243782535e-05</v>
+        <v>6.107278448049294e-05</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6770,28 +6770,28 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.00762882</v>
+        <v>0.00737211</v>
       </c>
       <c r="F95" t="n">
-        <v>656071782</v>
+        <v>634078632</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>12299600</v>
+        <v>11823521</v>
       </c>
       <c r="I95" t="n">
-        <v>0.008113840000000001</v>
+        <v>0.007920190000000001</v>
       </c>
       <c r="J95" t="n">
-        <v>0.00760228</v>
+        <v>0.00730566</v>
       </c>
       <c r="K95" t="n">
-        <v>-0.000102793897326767</v>
+        <v>-0.000340490086909007</v>
       </c>
       <c r="L95" t="n">
-        <v>-1.32953</v>
+        <v>-4.44513</v>
       </c>
       <c r="M95" t="n">
         <v>85985041177</v>
@@ -6806,287 +6806,287 @@
         <v>44304.71413194444</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S95" t="n">
-        <v>6.307022693335742e-05</v>
+        <v>3.531277431384421e-05</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>injective-protocol</t>
+          <t>akedo</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>inj</t>
+          <t>ake</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Injective</t>
+          <t>Akedo</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6.21</v>
+        <v>0.02610193</v>
       </c>
       <c r="F96" t="n">
-        <v>621016732</v>
+        <v>597035420</v>
       </c>
       <c r="G96" t="n">
         <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>97222782</v>
+        <v>61721944</v>
       </c>
       <c r="I96" t="n">
-        <v>6.43</v>
+        <v>0.02741537</v>
       </c>
       <c r="J96" t="n">
-        <v>5.94</v>
+        <v>0.01516416</v>
       </c>
       <c r="K96" t="n">
-        <v>0.243003</v>
+        <v>0.01068846</v>
       </c>
       <c r="L96" t="n">
-        <v>4.07246</v>
+        <v>69.84222</v>
       </c>
       <c r="M96" t="n">
-        <v>100000000</v>
+        <v>22796250000</v>
       </c>
       <c r="N96" t="n">
-        <v>100000000</v>
+        <v>100000000000</v>
       </c>
       <c r="O96" t="n">
-        <v>52.62</v>
+        <v>0.0363756</v>
       </c>
       <c r="P96" s="1" t="n">
-        <v>45365.29608796296</v>
+        <v>46267.90648148148</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S96" t="n">
-        <v>4.066683828804234e-05</v>
+        <v>1.115876233908633e-05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ether-fi</t>
+          <t>beldex</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ethfi</t>
+          <t>bdx</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Ether.fi</t>
+          <t>Beldex</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.632925</v>
+        <v>0.075861</v>
       </c>
       <c r="F97" t="n">
-        <v>611105341</v>
+        <v>596871431</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>52488946</v>
+        <v>10114343</v>
       </c>
       <c r="I97" t="n">
-        <v>0.667844</v>
+        <v>0.076349</v>
       </c>
       <c r="J97" t="n">
-        <v>0.624448</v>
+        <v>0.07459200000000001</v>
       </c>
       <c r="K97" t="n">
-        <v>-0.006288105739961969</v>
+        <v>-0.00050519058263214</v>
       </c>
       <c r="L97" t="n">
-        <v>-0.98373</v>
+        <v>-0.68989</v>
       </c>
       <c r="M97" t="n">
-        <v>965350000</v>
+        <v>7870696881.257065</v>
       </c>
       <c r="N97" t="n">
-        <v>965350000</v>
+        <v>9939636626.049881</v>
       </c>
       <c r="O97" t="n">
-        <v>8.529999999999999</v>
+        <v>0.450785</v>
       </c>
       <c r="P97" s="1" t="n">
-        <v>45378.63525462963</v>
+        <v>43450.66666666666</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>3.43325513710738e-05</v>
+        <v>1.105183337542819e-05</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>beldex</t>
+          <t>ether-fi</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>bdx</t>
+          <t>ethfi</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Beldex</t>
+          <t>Ether.fi</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.075492</v>
+        <v>0.611225</v>
       </c>
       <c r="F98" t="n">
-        <v>594174861</v>
+        <v>590090078</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>10090722</v>
+        <v>38896642</v>
       </c>
       <c r="I98" t="n">
-        <v>0.076415</v>
+        <v>0.662154</v>
       </c>
       <c r="J98" t="n">
-        <v>0.07459200000000001</v>
+        <v>0.607681</v>
       </c>
       <c r="K98" t="n">
-        <v>-0.00046679286666719</v>
+        <v>-0.03185111082065628</v>
       </c>
       <c r="L98" t="n">
-        <v>-0.61453</v>
+        <v>-4.98443</v>
       </c>
       <c r="M98" t="n">
-        <v>7870693688.976309</v>
+        <v>965350000</v>
       </c>
       <c r="N98" t="n">
-        <v>9939633963.163563</v>
+        <v>965350000</v>
       </c>
       <c r="O98" t="n">
-        <v>0.450785</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="P98" s="1" t="n">
-        <v>43450.66666666666</v>
+        <v>45378.63525462963</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S98" t="n">
-        <v>2.351242350385541e-05</v>
+        <v>6.630054789730483e-06</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>flare-networks</t>
+          <t>injective-protocol</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>flr</t>
+          <t>inj</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Flare</t>
+          <t>Injective</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.00665837</v>
+        <v>5.89</v>
       </c>
       <c r="F99" t="n">
-        <v>578963467</v>
+        <v>589329459</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>4298793</v>
+        <v>88259966</v>
       </c>
       <c r="I99" t="n">
-        <v>0.00683709</v>
+        <v>6.43</v>
       </c>
       <c r="J99" t="n">
-        <v>0.00643178</v>
+        <v>5.84</v>
       </c>
       <c r="K99" t="n">
-        <v>0.00024516</v>
+        <v>-0.3017526046568832</v>
       </c>
       <c r="L99" t="n">
-        <v>3.82277</v>
+        <v>-4.91081</v>
       </c>
       <c r="M99" t="n">
-        <v>86948958161.74995</v>
+        <v>100000000</v>
       </c>
       <c r="N99" t="n">
-        <v>106552794056.9216</v>
+        <v>100000000</v>
       </c>
       <c r="O99" t="n">
-        <v>0.150073</v>
+        <v>52.62</v>
       </c>
       <c r="P99" s="1" t="n">
-        <v>44935.80144675926</v>
+        <v>45365.29608796296</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S99" t="n">
-        <v>1.37909490909245e-05</v>
+        <v>6.134093466661944e-06</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7105,28 +7105,28 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.0283792</v>
+        <v>0.02914224</v>
       </c>
       <c r="F100" t="n">
-        <v>566117297</v>
+        <v>581431899</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>6969744</v>
+        <v>10513944</v>
       </c>
       <c r="I100" t="n">
-        <v>0.02838163</v>
+        <v>0.02919974</v>
       </c>
       <c r="J100" t="n">
-        <v>0.02759105</v>
+        <v>0.02784208</v>
       </c>
       <c r="K100" t="n">
-        <v>0.00069195</v>
+        <v>0.00139765</v>
       </c>
       <c r="L100" t="n">
-        <v>2.49916</v>
+        <v>5.02064</v>
       </c>
       <c r="M100" t="n">
         <v>19946688440</v>
@@ -7141,74 +7141,74 @@
         <v>44428.86097222222</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S100" t="n">
-        <v>5.581069512553136e-06</v>
+        <v>9.844925408197425e-07</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>aerodrome-finance</t>
+          <t>flare-networks</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>aero</t>
+          <t>flr</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Aerodrome Finance</t>
+          <t>Flare</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.563694</v>
+        <v>0.00666919</v>
       </c>
       <c r="F101" t="n">
-        <v>557384481</v>
+        <v>579922056</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>27643511</v>
+        <v>5808817</v>
       </c>
       <c r="I101" t="n">
-        <v>0.585051</v>
+        <v>0.00683709</v>
       </c>
       <c r="J101" t="n">
-        <v>0.564971</v>
+        <v>0.00649789</v>
       </c>
       <c r="K101" t="n">
-        <v>0.00492885</v>
+        <v>9.24e-05</v>
       </c>
       <c r="L101" t="n">
-        <v>0.8821</v>
+        <v>1.39992</v>
       </c>
       <c r="M101" t="n">
-        <v>988735867.9762976</v>
+        <v>86956577959.42989</v>
       </c>
       <c r="N101" t="n">
-        <v>1978450301.483024</v>
+        <v>106552783687.1503</v>
       </c>
       <c r="O101" t="n">
-        <v>2.32</v>
+        <v>0.150073</v>
       </c>
       <c r="P101" s="1" t="n">
-        <v>45633.25043981482</v>
+        <v>44935.80144675926</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46280.06759259259</v>
+        <v>46280.59259259259</v>
       </c>
       <c r="R101" t="b">
         <v>0</v>

--- a/src/xlsx/cleaned_data.xlsx
+++ b/src/xlsx/cleaned_data.xlsx
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,34 +539,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>76381</v>
+        <v>75575</v>
       </c>
       <c r="F2" t="n">
-        <v>1534205559019</v>
+        <v>1516961178908</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>32859344708</v>
+        <v>36368251316</v>
       </c>
       <c r="I2" t="n">
-        <v>79530</v>
+        <v>77146</v>
       </c>
       <c r="J2" t="n">
-        <v>76142</v>
+        <v>75038</v>
       </c>
       <c r="K2" t="n">
-        <v>-2095.025691471383</v>
+        <v>-769.8386863019696</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.67474</v>
+        <v>-0.95843</v>
       </c>
       <c r="M2" t="n">
-        <v>20084731</v>
+        <v>20085225</v>
       </c>
       <c r="N2" t="n">
-        <v>20084753</v>
+        <v>20085256</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -575,7 +575,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -587,7 +587,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,34 +606,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2447.41</v>
+        <v>2391.27</v>
       </c>
       <c r="F3" t="n">
-        <v>298739245343</v>
+        <v>291683286516</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>16736514590</v>
+        <v>17993150906</v>
       </c>
       <c r="I3" t="n">
-        <v>2607.56</v>
+        <v>2445.14</v>
       </c>
       <c r="J3" t="n">
-        <v>2440.21</v>
+        <v>2361.16</v>
       </c>
       <c r="K3" t="n">
-        <v>-65.88360726961491</v>
+        <v>-56.62823994185237</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.62877</v>
+        <v>-2.27435</v>
       </c>
       <c r="M3" t="n">
-        <v>122050160.8356428</v>
+        <v>122053082.6997495</v>
       </c>
       <c r="N3" t="n">
-        <v>122050160.8356428</v>
+        <v>122053082.6997494</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -642,19 +642,19 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1944146707650489</v>
+        <v>0.1919918599889429</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,34 +673,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999597</v>
+        <v>0.999375</v>
       </c>
       <c r="F4" t="n">
-        <v>183354416193</v>
+        <v>183321762724</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>58445617168</v>
+        <v>64865798573</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999954</v>
+        <v>0.999575</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999574</v>
+        <v>0.999246</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.3166689663885e-05</v>
+        <v>-0.000230253735472474</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00637</v>
+        <v>-0.02245</v>
       </c>
       <c r="M4" t="n">
-        <v>183431197333.8773</v>
+        <v>183442587855.5799</v>
       </c>
       <c r="N4" t="n">
-        <v>188898143247.2662</v>
+        <v>188909533773.7262</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -709,19 +709,19 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1191780378025916</v>
+        <v>0.1205329739422779</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,34 +740,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>719.6900000000001</v>
+        <v>709.98</v>
       </c>
       <c r="F5" t="n">
-        <v>95838645444</v>
+        <v>94483713743</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>918308118</v>
+        <v>962279454</v>
       </c>
       <c r="I5" t="n">
-        <v>732.8</v>
+        <v>723.8200000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>714.1900000000001</v>
+        <v>704.22</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.763283885708461</v>
+        <v>-9.017519857691013</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.38611</v>
+        <v>-1.23775</v>
       </c>
       <c r="M5" t="n">
-        <v>133160762.8</v>
+        <v>133160634.98</v>
       </c>
       <c r="N5" t="n">
-        <v>133160756.43</v>
+        <v>133160630.47</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -776,19 +776,19 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06211341352941806</v>
+        <v>0.0619488215919766</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -807,28 +807,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="F6" t="n">
-        <v>88748268343</v>
+        <v>79971731012</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>4262068843</v>
+        <v>5372201415</v>
       </c>
       <c r="I6" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="J6" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="K6" t="n">
-        <v>0.009628629999999999</v>
+        <v>-0.135845277811097</v>
       </c>
       <c r="L6" t="n">
-        <v>0.71812</v>
+        <v>-9.61839</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -843,19 +843,19 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05749013589887395</v>
+        <v>0.05237891076019242</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,34 +874,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999758</v>
+        <v>0.999722</v>
       </c>
       <c r="F7" t="n">
-        <v>74113425015</v>
+        <v>73642078830</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>17704315342</v>
+        <v>19054647817</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9999980000000001</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999376</v>
+        <v>0.999605</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.6659991143884e-05</v>
+        <v>-4.6245719710569e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00376</v>
+        <v>-0.0043</v>
       </c>
       <c r="M7" t="n">
-        <v>74132157601.51918</v>
+        <v>73664812907.1277</v>
       </c>
       <c r="N7" t="n">
-        <v>74178971119.97899</v>
+        <v>73653551003.2375</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -910,19 +910,19 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0479474919998185</v>
+        <v>0.04820482868603507</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -941,34 +941,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100.3</v>
+        <v>97</v>
       </c>
       <c r="F8" t="n">
-        <v>58889059739</v>
+        <v>56905505779</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3215127218</v>
+        <v>3795321892</v>
       </c>
       <c r="I8" t="n">
-        <v>104.76</v>
+        <v>100.54</v>
       </c>
       <c r="J8" t="n">
-        <v>99.90000000000001</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.508608506609704</v>
+        <v>-3.282241035908527</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.50767</v>
+        <v>-3.20872</v>
       </c>
       <c r="M8" t="n">
-        <v>587027977.1330632</v>
+        <v>587064549.8169115</v>
       </c>
       <c r="N8" t="n">
-        <v>634111537.8744141</v>
+        <v>634110600.7933525</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -977,19 +977,19 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03802045054389421</v>
+        <v>0.03716791424803979</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1008,34 +1008,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.337441</v>
+        <v>0.334519</v>
       </c>
       <c r="F9" t="n">
-        <v>32042437914</v>
+        <v>31757981216</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>439649621</v>
+        <v>506942384</v>
       </c>
       <c r="I9" t="n">
-        <v>0.342048</v>
+        <v>0.336594</v>
       </c>
       <c r="J9" t="n">
-        <v>0.33736</v>
+        <v>0.331863</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.003462706707822782</v>
+        <v>-0.002960896167564342</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.02556</v>
+        <v>-0.8641</v>
       </c>
       <c r="M9" t="n">
-        <v>94951106760.14119</v>
+        <v>94952171628.92049</v>
       </c>
       <c r="N9" t="n">
-        <v>94951113668.88469</v>
+        <v>94952166580.72699</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1044,19 +1044,19 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02051512122626251</v>
+        <v>0.02058440721326888</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1075,34 +1075,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.029</v>
+        <v>1.003</v>
       </c>
       <c r="F10" t="n">
-        <v>23203168550</v>
+        <v>22696694484</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>26481105</v>
+        <v>786631020</v>
       </c>
       <c r="I10" t="n">
-        <v>1.048</v>
+        <v>1.047</v>
       </c>
       <c r="J10" t="n">
-        <v>1.008</v>
+        <v>1.003</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.01315564104259104</v>
+        <v>-0.02554960894943803</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.26266</v>
+        <v>-2.48407</v>
       </c>
       <c r="M10" t="n">
-        <v>22558008629.268</v>
+        <v>22624876494.218</v>
       </c>
       <c r="N10" t="n">
-        <v>22624876494.218</v>
+        <v>22598468218.548</v>
       </c>
       <c r="O10" t="n">
         <v>1.061</v>
@@ -1111,19 +1111,19 @@
         <v>46237.59675925926</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01475147907594988</v>
+        <v>0.01460895178075724</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1142,34 +1142,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1131</v>
+        <v>1247.89</v>
       </c>
       <c r="F11" t="n">
-        <v>19189557969</v>
+        <v>21100710958</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>911698850</v>
+        <v>1521322408</v>
       </c>
       <c r="I11" t="n">
-        <v>1222.73</v>
+        <v>1268.97</v>
       </c>
       <c r="J11" t="n">
-        <v>1121.6</v>
+        <v>1088.87</v>
       </c>
       <c r="K11" t="n">
-        <v>-21.47479087819488</v>
+        <v>114.82</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9864</v>
+        <v>10.09064</v>
       </c>
       <c r="M11" t="n">
         <v>16933759.5405448</v>
       </c>
       <c r="N11" t="n">
-        <v>16933876.7280448</v>
+        <v>16935675.1655448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1178,19 +1178,19 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01213440585790688</v>
+        <v>0.01355648222398262</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1209,28 +1209,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>78.54000000000001</v>
+        <v>78.44</v>
       </c>
       <c r="F12" t="n">
-        <v>17472789844</v>
+        <v>17440527363</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>701147955</v>
+        <v>931340877</v>
       </c>
       <c r="I12" t="n">
-        <v>82.38</v>
+        <v>79.58</v>
       </c>
       <c r="J12" t="n">
-        <v>78.53</v>
+        <v>75.27</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.33141737096723</v>
+        <v>-0.3175158379041818</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.94723</v>
+        <v>-0.40749</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1245,19 +1245,19 @@
         <v>46271.5199074074</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01101498786982495</v>
+        <v>0.01114277823319131</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1276,34 +1276,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.08265599999999999</v>
+        <v>0.07914300000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>12888618761</v>
+        <v>12328095249</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>577108242</v>
+        <v>845852778</v>
       </c>
       <c r="I13" t="n">
-        <v>0.086033</v>
+        <v>0.082368</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08219799999999999</v>
+        <v>0.078671</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.001444614891101273</v>
+        <v>-0.003420279153313957</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.74714</v>
+        <v>-4.14377</v>
       </c>
       <c r="M13" t="n">
-        <v>155926276383.7052</v>
+        <v>155939426383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171638413126.579</v>
+        <v>171651883126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1312,19 +1312,19 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>0.008025880898401385</v>
+        <v>0.007771390575733804</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1343,34 +1343,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.999568</v>
+        <v>0.999362</v>
       </c>
       <c r="F14" t="n">
-        <v>9854320658</v>
+        <v>9577947441</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>147515323</v>
+        <v>218091969</v>
       </c>
       <c r="I14" t="n">
-        <v>0.999922</v>
+        <v>0.999655</v>
       </c>
       <c r="J14" t="n">
-        <v>0.999566</v>
+        <v>0.999215</v>
       </c>
       <c r="K14" t="n">
-        <v>-8.5224967625419e-05</v>
+        <v>-0.000261162282703786</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.00975</v>
+        <v>-0.02601</v>
       </c>
       <c r="M14" t="n">
-        <v>9858747591.389191</v>
+        <v>9583931558.104593</v>
       </c>
       <c r="N14" t="n">
-        <v>9841353158.538542</v>
+        <v>9577504586.820999</v>
       </c>
       <c r="O14" t="n">
         <v>1.057</v>
@@ -1379,354 +1379,354 @@
         <v>45593.90336805556</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R14" t="b">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.006047368000684871</v>
+        <v>0.005957808670032822</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>518.12</v>
+        <v>0.01321058</v>
       </c>
       <c r="F15" t="n">
-        <v>9747395293</v>
+        <v>9373518968</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>120378755</v>
+        <v>26286505</v>
       </c>
       <c r="I15" t="n">
-        <v>519.62</v>
+        <v>0.01451168</v>
       </c>
       <c r="J15" t="n">
-        <v>509.39</v>
+        <v>0.01254013</v>
       </c>
       <c r="K15" t="n">
-        <v>5.25</v>
+        <v>0.00014604</v>
       </c>
       <c r="L15" t="n">
-        <v>1.05346</v>
+        <v>1.13872</v>
       </c>
       <c r="M15" t="n">
-        <v>18804964.99452248</v>
+        <v>709233397159.627</v>
       </c>
       <c r="N15" t="n">
-        <v>18804999.79259193</v>
+        <v>1142408526965.963</v>
       </c>
       <c r="O15" t="n">
-        <v>797.73</v>
+        <v>0.01946402</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>46036.48202546296</v>
+        <v>46259.82847222222</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005977647358030682</v>
+        <v>0.005822998541441042</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>78.95999999999999</v>
+        <v>494.91</v>
       </c>
       <c r="F16" t="n">
-        <v>9307310396</v>
+        <v>9317262109</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>111976919</v>
+        <v>110227395</v>
       </c>
       <c r="I16" t="n">
-        <v>82.67</v>
+        <v>517.62</v>
       </c>
       <c r="J16" t="n">
-        <v>78.73999999999999</v>
+        <v>494.65</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.1789629554996</v>
+        <v>-21.99978176566327</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.71408</v>
+        <v>-4.26237</v>
       </c>
       <c r="M16" t="n">
-        <v>117882016</v>
+        <v>18805370.55291757</v>
       </c>
       <c r="N16" t="n">
-        <v>293532015</v>
+        <v>18805423.95177342</v>
       </c>
       <c r="O16" t="n">
-        <v>83.22</v>
+        <v>797.73</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>46276.58553240741</v>
+        <v>46036.48202546296</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>0.005690690172135245</v>
+        <v>0.005785900018497227</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.01303906</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>9248658690</v>
+        <v>9153123057</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>22655688</v>
+        <v>163351294</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01474682</v>
+        <v>79.44</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01303694</v>
+        <v>77.27</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.001979134494756592</v>
+        <v>-1.220355107256495</v>
       </c>
       <c r="L17" t="n">
-        <v>-13.1993</v>
+        <v>-1.53926</v>
       </c>
       <c r="M17" t="n">
-        <v>709230388026.6638</v>
+        <v>117882016</v>
       </c>
       <c r="N17" t="n">
-        <v>1142408526965.963</v>
+        <v>293532015</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01946402</v>
+        <v>83.22</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>46259.82847222222</v>
+        <v>46276.58553240741</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005652446350053511</v>
+        <v>0.0056776587036631</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>leo-token</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>LEO Token</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.33</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>8476405612</v>
+        <v>8163877232</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>354920743</v>
+        <v>319807</v>
       </c>
       <c r="I18" t="n">
-        <v>11.95</v>
+        <v>8.91</v>
       </c>
       <c r="J18" t="n">
-        <v>11.3</v>
+        <v>8.73</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.09682141799737742</v>
+        <v>0.11644</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.88814</v>
+        <v>1.32755</v>
       </c>
       <c r="M18" t="n">
-        <v>748099970.424884</v>
+        <v>919857851.9</v>
       </c>
       <c r="N18" t="n">
-        <v>1000000000</v>
+        <v>985239504</v>
       </c>
       <c r="O18" t="n">
-        <v>52.7</v>
+        <v>10.61</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>44325.67635416667</v>
+        <v>46146.39930555555</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005148899030950739</v>
+        <v>0.005025301647329115</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>leo-token</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LEO Token</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.76</v>
+        <v>10.69</v>
       </c>
       <c r="F19" t="n">
-        <v>8058856074</v>
+        <v>7986538864</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>310469</v>
+        <v>450558976</v>
       </c>
       <c r="I19" t="n">
-        <v>9.02</v>
+        <v>11.38</v>
       </c>
       <c r="J19" t="n">
-        <v>8.92</v>
+        <v>10.68</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2049368320736651</v>
+        <v>-0.6460806364119609</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.28863</v>
+        <v>-5.68476</v>
       </c>
       <c r="M19" t="n">
-        <v>919857851.9</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N19" t="n">
-        <v>985239504</v>
+        <v>1000000000</v>
       </c>
       <c r="O19" t="n">
-        <v>10.61</v>
+        <v>52.7</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>46146.39930555555</v>
+        <v>44325.67635416667</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004876636017124977</v>
+        <v>0.004908356058275401</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1745,28 +1745,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.20469</v>
+        <v>0.191834</v>
       </c>
       <c r="F20" t="n">
-        <v>7681523043</v>
+        <v>7189370215</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>364530117</v>
+        <v>466275840</v>
       </c>
       <c r="I20" t="n">
-        <v>0.215603</v>
+        <v>0.204209</v>
       </c>
       <c r="J20" t="n">
-        <v>0.203227</v>
+        <v>0.191485</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.005640167035805999</v>
+        <v>-0.01285599910683713</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.66892</v>
+        <v>-6.26884</v>
       </c>
       <c r="M20" t="n">
         <v>37516725700.17653</v>
@@ -1781,19 +1781,19 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004630596161044309</v>
+        <v>0.004382664081497658</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1812,34 +1812,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.196107</v>
+        <v>0.174197</v>
       </c>
       <c r="F21" t="n">
-        <v>6829435123</v>
+        <v>6061365830</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>381135110</v>
+        <v>350153192</v>
       </c>
       <c r="I21" t="n">
-        <v>0.198377</v>
+        <v>0.193982</v>
       </c>
       <c r="J21" t="n">
-        <v>0.189175</v>
+        <v>0.173614</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00446452</v>
+        <v>-0.02132487491538929</v>
       </c>
       <c r="L21" t="n">
-        <v>2.34329</v>
+        <v>-10.8698</v>
       </c>
       <c r="M21" t="n">
-        <v>34840249441.93312</v>
+        <v>34842263125.93008</v>
       </c>
       <c r="N21" t="n">
-        <v>50001786839.70248</v>
+        <v>50001786839.70148</v>
       </c>
       <c r="O21" t="n">
         <v>0.875563</v>
@@ -1848,19 +1848,19 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.00407499256427126</v>
+        <v>0.003638802847480899</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1879,34 +1879,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.999451</v>
+        <v>0.999165</v>
       </c>
       <c r="F22" t="n">
-        <v>4689264034</v>
+        <v>4727220083</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>51680215</v>
+        <v>93356081</v>
       </c>
       <c r="I22" t="n">
-        <v>0.999955</v>
+        <v>0.99937</v>
       </c>
       <c r="J22" t="n">
-        <v>0.999484</v>
+        <v>0.998924</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.000111107568562585</v>
+        <v>-0.000318845787347533</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.01282</v>
+        <v>-0.02983</v>
       </c>
       <c r="M22" t="n">
-        <v>4691925488.305101</v>
+        <v>4731366617.901646</v>
       </c>
       <c r="N22" t="n">
-        <v>4691925488.305101</v>
+        <v>4730392672.461645</v>
       </c>
       <c r="O22" t="n">
         <v>1.034</v>
@@ -1915,19 +1915,19 @@
         <v>46000.38208333333</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R22" t="b">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.00267949483821725</v>
+        <v>0.002759001922131101</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1946,34 +1946,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.99983</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>4601958030</v>
+        <v>4582463387</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>298574661</v>
+        <v>315605485</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0.999684</v>
+        <v>0.999623</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.000171526442148129</v>
+        <v>0.00011636</v>
       </c>
       <c r="L23" t="n">
-        <v>0.01416</v>
+        <v>0.00776</v>
       </c>
       <c r="M23" t="n">
-        <v>4602712385.445437</v>
+        <v>4582364613.50938</v>
       </c>
       <c r="N23" t="n">
-        <v>4606604755.4429</v>
+        <v>4538186664.507218</v>
       </c>
       <c r="O23" t="n">
         <v>1.22</v>
@@ -1982,19 +1982,19 @@
         <v>43902.79363425926</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R23" t="b">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.002622566992271162</v>
+        <v>0.002663542280350764</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2013,34 +2013,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>223.53</v>
+        <v>217.59</v>
       </c>
       <c r="F24" t="n">
-        <v>4491666529</v>
+        <v>4368271459</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>120014932</v>
+        <v>138736543</v>
       </c>
       <c r="I24" t="n">
-        <v>230.06</v>
+        <v>223.76</v>
       </c>
       <c r="J24" t="n">
-        <v>220.11</v>
+        <v>213.37</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6298749753331379</v>
+        <v>-6.059388942349528</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.2963</v>
+        <v>-2.658</v>
       </c>
       <c r="M24" t="n">
-        <v>20089446.77165077</v>
+        <v>20089853.02165077</v>
       </c>
       <c r="N24" t="n">
-        <v>20089746.77165077</v>
+        <v>20089940.52165077</v>
       </c>
       <c r="O24" t="n">
         <v>3785.82</v>
@@ -2049,19 +2049,19 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002550651461947603</v>
+        <v>0.002522293652245025</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2080,28 +2080,28 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.99942</v>
+        <v>0.999203</v>
       </c>
       <c r="F25" t="n">
-        <v>4343951640</v>
+        <v>4342992938</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>1038808054</v>
+        <v>1107595320</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9998939999999999</v>
+        <v>0.99947</v>
       </c>
       <c r="J25" t="n">
-        <v>0.999368</v>
+        <v>0.999034</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.000119357677266674</v>
+        <v>-0.000215952711094203</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.01591</v>
+        <v>-0.02075</v>
       </c>
       <c r="M25" t="n">
         <v>4346607627.726874</v>
@@ -2116,19 +2116,19 @@
         <v>46212.42696759259</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002454334026036375</v>
+        <v>0.002505623759755929</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2147,34 +2147,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>52.26</v>
+        <v>50.37</v>
       </c>
       <c r="F26" t="n">
-        <v>4056708774</v>
+        <v>3911524891</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>201051632</v>
+        <v>253209054</v>
       </c>
       <c r="I26" t="n">
-        <v>54.41</v>
+        <v>52.18</v>
       </c>
       <c r="J26" t="n">
-        <v>52.21</v>
+        <v>50.37</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.580792074926798</v>
+        <v>-1.916235601012829</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.97</v>
+        <v>-3.76849</v>
       </c>
       <c r="M26" t="n">
-        <v>77609673.14233896</v>
+        <v>77612279.40124893</v>
       </c>
       <c r="N26" t="n">
-        <v>77612785.65080889</v>
+        <v>77616385.66292557</v>
       </c>
       <c r="O26" t="n">
         <v>410.26</v>
@@ -2183,19 +2183,19 @@
         <v>44325.80077546297</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002267037426998803</v>
+        <v>0.002221092637228226</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2214,28 +2214,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="F27" t="n">
-        <v>3990125658</v>
+        <v>3856869904</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>655992252</v>
+        <v>623546845</v>
       </c>
       <c r="I27" t="n">
-        <v>6.82</v>
+        <v>6.56</v>
       </c>
       <c r="J27" t="n">
-        <v>6.32</v>
+        <v>6.21</v>
       </c>
       <c r="K27" t="n">
-        <v>0.01557894</v>
+        <v>-0.1916856986930116</v>
       </c>
       <c r="L27" t="n">
-        <v>0.14958</v>
+        <v>-2.88367</v>
       </c>
       <c r="M27" t="n">
         <v>623212423.7271129</v>
@@ -2250,19 +2250,19 @@
         <v>44318.89240740741</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002223621932111894</v>
+        <v>0.002185050466988799</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2281,34 +2281,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="F28" t="n">
-        <v>3734431422</v>
+        <v>3653450637</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>23256474</v>
+        <v>27111515</v>
       </c>
       <c r="I28" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="J28" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.01560654388762583</v>
+        <v>-0.03105510902163489</v>
       </c>
       <c r="L28" t="n">
-        <v>-1.17175</v>
+        <v>-2.27751</v>
       </c>
       <c r="M28" t="n">
-        <v>2789630325.698153</v>
+        <v>2794750881.605409</v>
       </c>
       <c r="N28" t="n">
-        <v>5249545239.296951</v>
+        <v>5250123209.163897</v>
       </c>
       <c r="O28" t="n">
         <v>8.25</v>
@@ -2317,19 +2317,19 @@
         <v>45457.69225694444</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002056896604993377</v>
+        <v>0.002050905858168502</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2348,34 +2348,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.09410399999999999</v>
+        <v>0.091306</v>
       </c>
       <c r="F29" t="n">
-        <v>3725190679</v>
+        <v>3617437521</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>8411442</v>
+        <v>8729948</v>
       </c>
       <c r="I29" t="n">
-        <v>0.09957199999999999</v>
+        <v>0.094012</v>
       </c>
       <c r="J29" t="n">
-        <v>0.09396599999999999</v>
+        <v>0.09014800000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.002110394020577555</v>
+        <v>-0.002752256873662845</v>
       </c>
       <c r="L29" t="n">
-        <v>-2.19196</v>
+        <v>-2.90075</v>
       </c>
       <c r="M29" t="n">
-        <v>39595289848.56115</v>
+        <v>39601011841.82496</v>
       </c>
       <c r="N29" t="n">
-        <v>39595289848.56115</v>
+        <v>39601011841.82496</v>
       </c>
       <c r="O29" t="n">
         <v>0.194152</v>
@@ -2384,287 +2384,287 @@
         <v>46056.00148148148</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002050871182114884</v>
+        <v>0.002027157048975222</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>hedera-hashgraph</t>
+          <t>global-dollar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>hbar</t>
+          <t>usdg</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Hedera</t>
+          <t>Global Dollar</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.07849299999999999</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>3441847762</v>
+        <v>3282838433</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>79904973</v>
+        <v>1103839469</v>
       </c>
       <c r="I30" t="n">
-        <v>0.079821</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>0.076289</v>
+        <v>0.9998089999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.00167729</v>
+        <v>5.409e-05</v>
       </c>
       <c r="L30" t="n">
-        <v>2.18686</v>
+        <v>0.01099</v>
       </c>
       <c r="M30" t="n">
-        <v>43831559670.90491</v>
+        <v>3282758930.547109</v>
       </c>
       <c r="N30" t="n">
-        <v>50000000000</v>
+        <v>3282758930.547109</v>
       </c>
       <c r="O30" t="n">
-        <v>0.569229</v>
+        <v>1.65</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>44454.11143518519</v>
+        <v>45686.67436342593</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.001866117543305678</v>
+        <v>0.001806506053455766</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>avalanche-2</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>avax</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>7.52</v>
+        <v>2.46</v>
       </c>
       <c r="F31" t="n">
-        <v>3330626737</v>
+        <v>3213737490</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>256933798</v>
+        <v>399257593</v>
       </c>
       <c r="I31" t="n">
-        <v>7.79</v>
+        <v>2.5</v>
       </c>
       <c r="J31" t="n">
-        <v>7.43</v>
+        <v>2.3</v>
       </c>
       <c r="K31" t="n">
-        <v>0.03078822</v>
+        <v>0.088107</v>
       </c>
       <c r="L31" t="n">
-        <v>0.36221</v>
+        <v>3.82432</v>
       </c>
       <c r="M31" t="n">
-        <v>442517742.512899</v>
+        <v>1306460821</v>
       </c>
       <c r="N31" t="n">
-        <v>469186419.7681523</v>
+        <v>1306488202</v>
       </c>
       <c r="O31" t="n">
-        <v>144.96</v>
+        <v>20.44</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>44521.26314814815</v>
+        <v>44577.59010416667</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.001793595917219505</v>
+        <v>0.001760937513638696</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>global-dollar</t>
+          <t>avalanche-2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>usdg</t>
+          <t>avax</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Global Dollar</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.999933</v>
+        <v>7.26</v>
       </c>
       <c r="F32" t="n">
-        <v>3314144494</v>
+        <v>3212309286</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>1286433563</v>
+        <v>276887586</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>7.53</v>
       </c>
       <c r="J32" t="n">
-        <v>0.999816</v>
+        <v>7.19</v>
       </c>
       <c r="K32" t="n">
-        <v>3.92e-06</v>
+        <v>-0.2650792157821398</v>
       </c>
       <c r="L32" t="n">
-        <v>0.00018</v>
+        <v>-3.60054</v>
       </c>
       <c r="M32" t="n">
-        <v>3314421155.993802</v>
+        <v>442839467.2032731</v>
       </c>
       <c r="N32" t="n">
-        <v>3320411793.117109</v>
+        <v>469508157.910476</v>
       </c>
       <c r="O32" t="n">
-        <v>1.65</v>
+        <v>144.96</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>45686.67436342593</v>
+        <v>44521.26314814815</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001782848677082962</v>
+        <v>0.001759995686103276</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>hedera-hashgraph</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>hbar</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Hedera</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2.37</v>
+        <v>0.072974</v>
       </c>
       <c r="F33" t="n">
-        <v>3096910012</v>
+        <v>3196842944</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>384207681</v>
+        <v>90080835</v>
       </c>
       <c r="I33" t="n">
-        <v>2.59</v>
+        <v>0.078586</v>
       </c>
       <c r="J33" t="n">
-        <v>2.34</v>
+        <v>0.073006</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.05920351575864702</v>
+        <v>-0.005635858701912577</v>
       </c>
       <c r="L33" t="n">
-        <v>-2.54883</v>
+        <v>-7.24699</v>
       </c>
       <c r="M33" t="n">
-        <v>1306379194</v>
+        <v>43831556056.62752</v>
       </c>
       <c r="N33" t="n">
-        <v>1306379203</v>
+        <v>50000000000</v>
       </c>
       <c r="O33" t="n">
-        <v>20.44</v>
+        <v>0.569229</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>44577.59010416667</v>
+        <v>44454.11143518519</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001641201017599267</v>
+        <v>0.001749796424115615</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2683,31 +2683,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5.16e-06</v>
+        <v>4.78e-06</v>
       </c>
       <c r="F34" t="n">
-        <v>3042104770</v>
+        <v>2819044705</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>67610639</v>
+        <v>89914815</v>
       </c>
       <c r="I34" t="n">
-        <v>5.39e-06</v>
+        <v>5.16e-06</v>
       </c>
       <c r="J34" t="n">
-        <v>5.13e-06</v>
+        <v>4.79e-06</v>
       </c>
       <c r="K34" t="n">
-        <v>-9.922755486000001e-08</v>
+        <v>-3.72696589079e-07</v>
       </c>
       <c r="L34" t="n">
-        <v>-1.91446</v>
+        <v>-7.17479</v>
       </c>
       <c r="M34" t="n">
-        <v>589239232074943.9</v>
+        <v>589239215066517.9</v>
       </c>
       <c r="N34" t="n">
         <v>589496238721205.9</v>
@@ -2719,19 +2719,19 @@
         <v>44496.82980324074</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001605465280872455</v>
+        <v>0.001500657796634217</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.709537</v>
+        <v>0.688042</v>
       </c>
       <c r="F35" t="n">
-        <v>2907090081</v>
+        <v>2815990283</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>446416765</v>
+        <v>516267580</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7470830000000001</v>
+        <v>0.71071</v>
       </c>
       <c r="J35" t="n">
-        <v>0.702775</v>
+        <v>0.675641</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.01632837389630148</v>
+        <v>-0.02100642298407862</v>
       </c>
       <c r="L35" t="n">
-        <v>-2.26866</v>
+        <v>-2.96068</v>
       </c>
       <c r="M35" t="n">
         <v>4096537146.540959</v>
@@ -2786,19 +2786,19 @@
         <v>45661.62243055556</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001517429005430838</v>
+        <v>0.001498643561451853</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2817,34 +2817,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.999596</v>
+        <v>0.999512</v>
       </c>
       <c r="F36" t="n">
-        <v>2847196672</v>
+        <v>2804921432</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>113170639</v>
+        <v>100030070</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0.999706</v>
       </c>
       <c r="J36" t="n">
-        <v>0.999588</v>
+        <v>0.999375</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.000129970499106125</v>
+        <v>-0.000122881507387151</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.01317</v>
+        <v>-0.01195</v>
       </c>
       <c r="M36" t="n">
-        <v>2848397238.831206</v>
+        <v>2806316064.287177</v>
       </c>
       <c r="N36" t="n">
-        <v>2849124073.776223</v>
+        <v>2806266063.289376</v>
       </c>
       <c r="O36" t="n">
         <v>1.021</v>
@@ -2853,153 +2853,153 @@
         <v>45222.61454861111</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001478375531390976</v>
+        <v>0.001491344220001148</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>crypto-com-chain</t>
+          <t>blackrock-usd-institutional-digital-liquidity-fund</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>cro</t>
+          <t>buidl</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cronos</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.057053</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>2770362369</v>
+        <v>2701488574</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>8558565</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0.060066</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>0.056826</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.002513645447222712</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>-4.22884</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>48556300890.85578</v>
+        <v>2701488573.550449</v>
       </c>
       <c r="N37" t="n">
-        <v>98922960112.48987</v>
+        <v>2701488573.550449</v>
       </c>
       <c r="O37" t="n">
-        <v>0.891544</v>
+        <v>1</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>44523.66666666666</v>
+        <v>45699.87511574074</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001428275754008438</v>
+        <v>0.001423135537115788</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>blackrock-usd-institutional-digital-liquidity-fund</t>
+          <t>crypto-com-chain</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>buidl</t>
+          <t>cro</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund</t>
+          <t>Cronos</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0.055498</v>
       </c>
       <c r="F38" t="n">
-        <v>2726116192</v>
+        <v>2694112592</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>8206200</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0.057362</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0.05466</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>-0.001550860462855075</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>-2.65792</v>
       </c>
       <c r="M38" t="n">
-        <v>2726116192.030449</v>
+        <v>48558313167.31941</v>
       </c>
       <c r="N38" t="n">
-        <v>2726116192.030449</v>
+        <v>98924974447.10681</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>0.891544</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>45699.87511574074</v>
+        <v>44523.66666666666</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R38" t="b">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.00139942505150739</v>
+        <v>0.001418271454009759</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3018,28 +3018,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4295.67</v>
+        <v>4323.31</v>
       </c>
       <c r="F39" t="n">
-        <v>2675286730</v>
+        <v>2693520445</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>170538665</v>
+        <v>167835192</v>
       </c>
       <c r="I39" t="n">
-        <v>4318.64</v>
+        <v>4354.07</v>
       </c>
       <c r="J39" t="n">
-        <v>4264.56</v>
+        <v>4274.94</v>
       </c>
       <c r="K39" t="n">
-        <v>11.57</v>
+        <v>26.07</v>
       </c>
       <c r="L39" t="n">
-        <v>0.25337</v>
+        <v>0.53286</v>
       </c>
       <c r="M39" t="n">
         <v>622823.6595320001</v>
@@ -3054,19 +3054,19 @@
         <v>46050.66666666666</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001366281720582995</v>
+        <v>0.001417880963330825</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3088,7 +3088,7 @@
         <v>1.14</v>
       </c>
       <c r="F40" t="n">
-        <v>2605808911</v>
+        <v>2606216681</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
@@ -3103,171 +3103,171 @@
         <v>1.14</v>
       </c>
       <c r="K40" t="n">
-        <v>9.804e-05</v>
+        <v>0.00010164</v>
       </c>
       <c r="L40" t="n">
-        <v>0.008619999999999999</v>
+        <v>0.00894</v>
       </c>
       <c r="M40" t="n">
-        <v>2291167466.910423</v>
+        <v>2291321221.608375</v>
       </c>
       <c r="N40" t="n">
-        <v>2291321221.608375</v>
+        <v>2246343166.601824</v>
       </c>
       <c r="O40" t="n">
         <v>1.14</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>46280.54201388889</v>
+        <v>46281.53125</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001320978735730978</v>
+        <v>0.001360308593500589</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>bittensor</t>
+          <t>memecore</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>tao</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>MemeCore</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>225.33</v>
+        <v>1.11</v>
       </c>
       <c r="F41" t="n">
-        <v>2555400017</v>
+        <v>2531426802</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
       </c>
       <c r="H41" t="n">
-        <v>148329497</v>
+        <v>627998</v>
       </c>
       <c r="I41" t="n">
-        <v>241.79</v>
+        <v>1.15</v>
       </c>
       <c r="J41" t="n">
-        <v>223.09</v>
+        <v>1.091</v>
       </c>
       <c r="K41" t="n">
-        <v>-9.283924826997833</v>
+        <v>0.01102276</v>
       </c>
       <c r="L41" t="n">
-        <v>-3.97822</v>
+        <v>1.04359</v>
       </c>
       <c r="M41" t="n">
-        <v>11339645.9251</v>
+        <v>2273447446.030578</v>
       </c>
       <c r="N41" t="n">
-        <v>21000000</v>
+        <v>5414837292.537803</v>
       </c>
       <c r="O41" t="n">
-        <v>757.6</v>
+        <v>5.64</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>45358.44833333333</v>
+        <v>46205.17638888889</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001288109636007382</v>
+        <v>0.001310988491181214</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>memecore</t>
+          <t>bittensor</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>tao</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>MemeCore</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1.1</v>
+        <v>216</v>
       </c>
       <c r="F42" t="n">
-        <v>2508232270</v>
+        <v>2447094677</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
       </c>
       <c r="H42" t="n">
-        <v>2451075</v>
+        <v>183067847</v>
       </c>
       <c r="I42" t="n">
-        <v>1.14</v>
+        <v>226.84</v>
       </c>
       <c r="J42" t="n">
-        <v>1.073</v>
+        <v>213.51</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0007872000000000001</v>
+        <v>-9.15093076012684</v>
       </c>
       <c r="L42" t="n">
-        <v>0.03687</v>
+        <v>-4.07487</v>
       </c>
       <c r="M42" t="n">
-        <v>2273077194.610963</v>
+        <v>11339645.9251</v>
       </c>
       <c r="N42" t="n">
-        <v>5414467041.118188</v>
+        <v>21000000</v>
       </c>
       <c r="O42" t="n">
-        <v>5.64</v>
+        <v>757.6</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>46205.17638888889</v>
+        <v>45358.44833333333</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001257353924924328</v>
+        <v>0.001255375765376291</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3286,34 +3286,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.999871</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>2363114871</v>
+        <v>2347586666</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>302885988</v>
+        <v>334483072</v>
       </c>
       <c r="I43" t="n">
         <v>1.001</v>
       </c>
       <c r="J43" t="n">
-        <v>0.999754</v>
+        <v>0.9996429999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.000114811151807337</v>
+        <v>0.00027881</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.0092</v>
       </c>
       <c r="M43" t="n">
-        <v>2363406353.107541</v>
+        <v>2347466285.367542</v>
       </c>
       <c r="N43" t="n">
-        <v>2359976357.487542</v>
+        <v>2347467285.367542</v>
       </c>
       <c r="O43" t="n">
         <v>1.073</v>
@@ -3322,19 +3322,19 @@
         <v>45652.11518518518</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001162730181357174</v>
+        <v>0.001189755318469063</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3353,28 +3353,28 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>112.23</v>
+        <v>109.54</v>
       </c>
       <c r="F44" t="n">
-        <v>2356599579</v>
+        <v>2299970668</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>17719113</v>
+        <v>20138692</v>
       </c>
       <c r="I44" t="n">
-        <v>114.57</v>
+        <v>111.78</v>
       </c>
       <c r="J44" t="n">
-        <v>111.88</v>
+        <v>108.53</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.700078909527733</v>
+        <v>-2.603623464937826</v>
       </c>
       <c r="L44" t="n">
-        <v>-1.51226</v>
+        <v>-2.30475</v>
       </c>
       <c r="M44" t="n">
         <v>21000000</v>
@@ -3389,19 +3389,19 @@
         <v>45934.66666666666</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001158481887743028</v>
+        <v>0.001158355001677546</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3420,16 +3420,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="F45" t="n">
-        <v>2232069303</v>
+        <v>2234039229</v>
       </c>
       <c r="G45" t="n">
         <v>44</v>
       </c>
       <c r="H45" t="n">
-        <v>4126024</v>
+        <v>4117977</v>
       </c>
       <c r="I45" t="n">
         <v>1.15</v>
@@ -3438,16 +3438,16 @@
         <v>1.14</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.000421448190936813</v>
+        <v>-0.001008384954372055</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.03646</v>
+        <v>0.15997</v>
       </c>
       <c r="M45" t="n">
-        <v>1950284546.742239</v>
+        <v>1954712699.278615</v>
       </c>
       <c r="N45" t="n">
-        <v>1950284571.383834</v>
+        <v>1954713137.876704</v>
       </c>
       <c r="O45" t="n">
         <v>1.26</v>
@@ -3456,153 +3456,153 @@
         <v>45377.89175925926</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.001077281969719615</v>
+        <v>0.00111487658773943</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Aave</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>127.1</v>
+        <v>0.765609</v>
       </c>
       <c r="F46" t="n">
-        <v>1960871266</v>
+        <v>2074964727</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>232309710</v>
+        <v>15877531</v>
       </c>
       <c r="I46" t="n">
-        <v>133.48</v>
+        <v>0.789172</v>
       </c>
       <c r="J46" t="n">
-        <v>125.41</v>
+        <v>0.679488</v>
       </c>
       <c r="K46" t="n">
-        <v>0.676671</v>
+        <v>0.061745</v>
       </c>
       <c r="L46" t="n">
-        <v>0.51344</v>
+        <v>8.760260000000001</v>
       </c>
       <c r="M46" t="n">
-        <v>15427725.26623425</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N46" t="n">
-        <v>16000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O46" t="n">
-        <v>661.6900000000001</v>
+        <v>0.789172</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>44334.55554398148</v>
+        <v>46281.50775462963</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0009004473951900405</v>
+        <v>0.001009975084756069</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>pax-gold</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>paxg</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>PAX Gold</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.70362</v>
+        <v>4331.13</v>
       </c>
       <c r="F47" t="n">
-        <v>1903820068</v>
+        <v>1882287997</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>32634718</v>
+        <v>167216327</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7355120000000001</v>
+        <v>4358.82</v>
       </c>
       <c r="J47" t="n">
-        <v>0.553432</v>
+        <v>4278.77</v>
       </c>
       <c r="K47" t="n">
-        <v>0.00815778</v>
+        <v>32.52</v>
       </c>
       <c r="L47" t="n">
-        <v>1.40638</v>
+        <v>0.68909</v>
       </c>
       <c r="M47" t="n">
-        <v>2708142280.000001</v>
+        <v>434499.367539</v>
       </c>
       <c r="N47" t="n">
-        <v>10000000000</v>
+        <v>434499.367539</v>
       </c>
       <c r="O47" t="n">
-        <v>0.782873</v>
+        <v>5619.09</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>46279.42037037037</v>
+        <v>46050.93814814815</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0008632471837271068</v>
+        <v>0.0008829146299830021</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3621,28 +3621,28 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.69319</v>
+        <v>0.679137</v>
       </c>
       <c r="F48" t="n">
-        <v>1874917814</v>
+        <v>1833968107</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>83983574</v>
+        <v>94782264</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7098100000000001</v>
+        <v>0.695809</v>
       </c>
       <c r="J48" t="n">
-        <v>0.683408</v>
+        <v>0.6623250000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.003530075159953072</v>
+        <v>-0.01434930831923498</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.53695</v>
+        <v>-2.07165</v>
       </c>
       <c r="M48" t="n">
         <v>2704071066.799731</v>
@@ -3657,287 +3657,287 @@
         <v>45924.13766203704</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0008444014802494091</v>
+        <v>0.0008510501323968921</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>pax-gold</t>
+          <t>world-liberty-financial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>paxg</t>
+          <t>wlfi</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>PAX Gold</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4297.19</v>
+        <v>0.056921</v>
       </c>
       <c r="F49" t="n">
-        <v>1860248516</v>
+        <v>1807603208</v>
       </c>
       <c r="G49" t="n">
         <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>142796805</v>
+        <v>32654435</v>
       </c>
       <c r="I49" t="n">
-        <v>4322.66</v>
+        <v>0.057554</v>
       </c>
       <c r="J49" t="n">
-        <v>4266.02</v>
+        <v>0.056071</v>
       </c>
       <c r="K49" t="n">
-        <v>10.41</v>
+        <v>-0.000205578363537087</v>
       </c>
       <c r="L49" t="n">
-        <v>0.22468</v>
+        <v>-0.30227</v>
       </c>
       <c r="M49" t="n">
-        <v>432906.598539</v>
+        <v>31777370298</v>
       </c>
       <c r="N49" t="n">
-        <v>432906.598539</v>
+        <v>100000000000</v>
       </c>
       <c r="O49" t="n">
-        <v>5619.09</v>
+        <v>0.331336</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>46050.93814814815</v>
+        <v>45901.18065972222</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R49" t="b">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0008348363701948789</v>
+        <v>0.0008336638291469564</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>mantle</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>mnt</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mantle</t>
+          <t>Aave</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.55154</v>
+        <v>117.04</v>
       </c>
       <c r="F50" t="n">
-        <v>1821320244</v>
+        <v>1803872610</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>22814959</v>
+        <v>258050196</v>
       </c>
       <c r="I50" t="n">
-        <v>0.581183</v>
+        <v>127.12</v>
       </c>
       <c r="J50" t="n">
-        <v>0.551291</v>
+        <v>116.96</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.01576741668789894</v>
+        <v>-10.12713674677889</v>
       </c>
       <c r="L50" t="n">
-        <v>-2.78762</v>
+        <v>-7.94872</v>
       </c>
       <c r="M50" t="n">
-        <v>3302294382.53684</v>
+        <v>15427760.79998905</v>
       </c>
       <c r="N50" t="n">
-        <v>6219316794.889999</v>
+        <v>16000000</v>
       </c>
       <c r="O50" t="n">
-        <v>2.86</v>
+        <v>661.6900000000001</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>45938.71164351852</v>
+        <v>44334.55554398148</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" t="n">
-        <v>0.000809453205580411</v>
+        <v>0.0008312036904552965</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>world-liberty-financial</t>
+          <t>mantle</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>wlfi</t>
+          <t>mnt</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>World Liberty Financial</t>
+          <t>Mantle</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.057155</v>
+        <v>0.545925</v>
       </c>
       <c r="F51" t="n">
-        <v>1816498792</v>
+        <v>1802664518</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>29696092</v>
+        <v>22538349</v>
       </c>
       <c r="I51" t="n">
-        <v>0.058603</v>
+        <v>0.552142</v>
       </c>
       <c r="J51" t="n">
-        <v>0.056788</v>
+        <v>0.537594</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.000289076965196013</v>
+        <v>-0.006649308129468623</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.46882</v>
+        <v>-1.13588</v>
       </c>
       <c r="M51" t="n">
-        <v>31777354724</v>
+        <v>3302294382.53684</v>
       </c>
       <c r="N51" t="n">
-        <v>100000000000</v>
+        <v>6219316794.889999</v>
       </c>
       <c r="O51" t="n">
-        <v>0.331336</v>
+        <v>2.86</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>45901.18065972222</v>
+        <v>45938.71164351852</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R51" t="b">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0008063093796793601</v>
+        <v>0.0008304070155328619</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ondo-finance</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ondo</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Ondo</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.346558</v>
+        <v>0.0036242</v>
       </c>
       <c r="F52" t="n">
-        <v>1687473441</v>
+        <v>1693844208</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>74904800</v>
+        <v>149774810</v>
       </c>
       <c r="I52" t="n">
-        <v>0.365023</v>
+        <v>0.00367103</v>
       </c>
       <c r="J52" t="n">
-        <v>0.344965</v>
+        <v>0.0034046</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.008247247960141424</v>
+        <v>3.511e-05</v>
       </c>
       <c r="L52" t="n">
-        <v>-2.37679</v>
+        <v>1.04017</v>
       </c>
       <c r="M52" t="n">
-        <v>4869330647</v>
+        <v>468254258147.3779</v>
       </c>
       <c r="N52" t="n">
-        <v>10000000000</v>
+        <v>833746661504.1492</v>
       </c>
       <c r="O52" t="n">
-        <v>2.14</v>
+        <v>0.00881908</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>45641.69166666667</v>
+        <v>45914.36296296296</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R52" t="b">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0007221784497507853</v>
+        <v>0.0007586455834328562</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3956,34 +3956,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.987437</v>
+        <v>0.974857</v>
       </c>
       <c r="F53" t="n">
-        <v>1681496989</v>
+        <v>1658632157</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>137018341</v>
+        <v>172781669</v>
       </c>
       <c r="I53" t="n">
-        <v>1.036</v>
+        <v>0.991195</v>
       </c>
       <c r="J53" t="n">
-        <v>0.9796049999999999</v>
+        <v>0.937387</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.02848518674979184</v>
+        <v>-0.01264061151858564</v>
       </c>
       <c r="L53" t="n">
-        <v>-2.8598</v>
+        <v>-1.3444</v>
       </c>
       <c r="M53" t="n">
-        <v>1702874768.910783</v>
+        <v>1703027693.562892</v>
       </c>
       <c r="N53" t="n">
-        <v>1702890257.762186</v>
+        <v>1703041183.197886</v>
       </c>
       <c r="O53" t="n">
         <v>54.98</v>
@@ -3992,354 +3992,354 @@
         <v>44504.25704861111</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R53" t="b">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0007182815065490303</v>
+        <v>0.0007354250356606762</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>ondo-finance</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>ondo</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>Ondo</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.00358044</v>
+        <v>0.328726</v>
       </c>
       <c r="F54" t="n">
-        <v>1677536262</v>
+        <v>1600661449</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>115713157</v>
+        <v>134573756</v>
       </c>
       <c r="I54" t="n">
-        <v>0.00380079</v>
+        <v>0.346461</v>
       </c>
       <c r="J54" t="n">
-        <v>0.00356134</v>
+        <v>0.323088</v>
       </c>
       <c r="K54" t="n">
-        <v>-6.6514859277032e-05</v>
+        <v>-0.01760857147179312</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.86686</v>
+        <v>-5.04144</v>
       </c>
       <c r="M54" t="n">
-        <v>468474629168.2731</v>
+        <v>4869330647</v>
       </c>
       <c r="N54" t="n">
-        <v>833978841344.554</v>
+        <v>10000000000</v>
       </c>
       <c r="O54" t="n">
-        <v>0.00881908</v>
+        <v>2.14</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>45914.36296296296</v>
+        <v>45641.69166666667</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0007156989160494066</v>
+        <v>0.0006971963169046713</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>htx-dao</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>htx</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>HTX DAO</t>
+          <t>USDD</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1.69e-06</v>
+        <v>0.998667</v>
       </c>
       <c r="F55" t="n">
-        <v>1515518580</v>
+        <v>1510476486</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>24186473</v>
+        <v>3599737</v>
       </c>
       <c r="I55" t="n">
-        <v>1.71e-06</v>
+        <v>0.999115</v>
       </c>
       <c r="J55" t="n">
-        <v>1.68e-06</v>
+        <v>0.998204</v>
       </c>
       <c r="K55" t="n">
-        <v>-1.0232432597e-08</v>
+        <v>-0.000243772364906358</v>
       </c>
       <c r="L55" t="n">
-        <v>-0.53354</v>
+        <v>-0.07045</v>
       </c>
       <c r="M55" t="n">
-        <v>898232728634017.2</v>
+        <v>1512683787</v>
       </c>
       <c r="N55" t="n">
-        <v>898232728634017.2</v>
+        <v>1514683059</v>
       </c>
       <c r="O55" t="n">
-        <v>3.75e-06</v>
+        <v>1.24</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>45629.67800925926</v>
+        <v>46212.39942129629</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R55" t="b">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0006100553495263278</v>
+        <v>0.0006377239436062859</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>htx-dao</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>htx</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>USDD</t>
+          <t>HTX DAO</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.998906</v>
+        <v>1.66e-06</v>
       </c>
       <c r="F56" t="n">
-        <v>1499951843</v>
+        <v>1491562831</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>7702046</v>
+        <v>13864357</v>
       </c>
       <c r="I56" t="n">
-        <v>0.999766</v>
+        <v>1.69e-06</v>
       </c>
       <c r="J56" t="n">
-        <v>0.9987279999999999</v>
+        <v>1.65e-06</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.000103033010561582</v>
+        <v>-2.7396874213e-08</v>
       </c>
       <c r="L56" t="n">
-        <v>0.01199</v>
+        <v>-1.65791</v>
       </c>
       <c r="M56" t="n">
-        <v>1501621157</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="N56" t="n">
-        <v>1500853803</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="O56" t="n">
-        <v>1.24</v>
+        <v>3.75e-06</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>46212.39942129629</v>
+        <v>45629.67800925926</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R56" t="b">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0005999050647209522</v>
+        <v>0.0006252513549043658</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>ethena</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>ena</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Morpho</t>
+          <t>Ethena</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2.13</v>
+        <v>0.145504</v>
       </c>
       <c r="F57" t="n">
-        <v>1468888515</v>
+        <v>1464719993</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>16440903</v>
+        <v>357939471</v>
       </c>
       <c r="I57" t="n">
-        <v>2.23</v>
+        <v>0.147265</v>
       </c>
       <c r="J57" t="n">
-        <v>2.12</v>
+        <v>0.135956</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.07791215298827892</v>
+        <v>0.00228853</v>
       </c>
       <c r="L57" t="n">
-        <v>-3.52363</v>
+        <v>1.4782</v>
       </c>
       <c r="M57" t="n">
-        <v>689139191.0768665</v>
+        <v>10095312500</v>
       </c>
       <c r="N57" t="n">
-        <v>1000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="O57" t="n">
-        <v>4.17</v>
+        <v>1.52</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>45674.19883101852</v>
+        <v>45393.21892361111</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R57" t="b">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0005796502337822141</v>
+        <v>0.0006075498753137595</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ethena</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ena</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ethena</t>
+          <t>Morpho</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.143826</v>
+        <v>2.1</v>
       </c>
       <c r="F58" t="n">
-        <v>1450610285</v>
+        <v>1444714709</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>297301548</v>
+        <v>20211623</v>
       </c>
       <c r="I58" t="n">
-        <v>0.148653</v>
+        <v>2.16</v>
       </c>
       <c r="J58" t="n">
-        <v>0.139581</v>
+        <v>2.06</v>
       </c>
       <c r="K58" t="n">
-        <v>0.00269862</v>
+        <v>-0.0329807614339539</v>
       </c>
       <c r="L58" t="n">
-        <v>1.82936</v>
+        <v>-1.55208</v>
       </c>
       <c r="M58" t="n">
-        <v>10095312500</v>
+        <v>689193692.0482025</v>
       </c>
       <c r="N58" t="n">
-        <v>15000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="O58" t="n">
-        <v>1.52</v>
+        <v>4.17</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>45393.21892361111</v>
+        <v>45674.19883101852</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0005677319210209617</v>
+        <v>0.0005943574130849042</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4358,28 +4358,28 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3.45e-06</v>
+        <v>3.34e-06</v>
       </c>
       <c r="F59" t="n">
-        <v>1449365068</v>
+        <v>1403578214</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>199905591</v>
+        <v>227287742</v>
       </c>
       <c r="I59" t="n">
-        <v>3.58e-06</v>
+        <v>3.45e-06</v>
       </c>
       <c r="J59" t="n">
-        <v>3.39e-06</v>
+        <v>3.28e-06</v>
       </c>
       <c r="K59" t="n">
-        <v>3.59802e-10</v>
+        <v>-1.02294976604e-07</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.09737</v>
+        <v>-2.91505</v>
       </c>
       <c r="M59" t="n">
         <v>420690000000000</v>
@@ -4394,153 +4394,153 @@
         <v>45635.35457175926</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R59" t="b">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0005669199777605022</v>
+        <v>0.0005672299973223988</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>internet-computer</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>icp</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sky</t>
+          <t>Internet Computer</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.061537</v>
+        <v>2.48</v>
       </c>
       <c r="F60" t="n">
-        <v>1441504397</v>
+        <v>1382482369</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>12430056</v>
+        <v>46496852</v>
       </c>
       <c r="I60" t="n">
-        <v>0.065204</v>
+        <v>2.56</v>
       </c>
       <c r="J60" t="n">
-        <v>0.061287</v>
+        <v>2.45</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.001827857813673638</v>
+        <v>-0.07423048861210324</v>
       </c>
       <c r="L60" t="n">
-        <v>-2.90173</v>
+        <v>-2.8557</v>
       </c>
       <c r="M60" t="n">
-        <v>23426097368.71168</v>
+        <v>556864813.9605618</v>
       </c>
       <c r="N60" t="n">
-        <v>23459804203.60596</v>
+        <v>556870388.8185315</v>
       </c>
       <c r="O60" t="n">
-        <v>0.100535</v>
+        <v>700.65</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>45630.09302083333</v>
+        <v>44326.33741898148</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0005617944302927602</v>
+        <v>0.0005533183658580173</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>internet-computer</t>
+          <t>united-stables</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>icp</t>
+          <t>u</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Internet Computer</t>
+          <t>United Stables</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2.56</v>
+        <v>0.99959</v>
       </c>
       <c r="F61" t="n">
-        <v>1425439616</v>
+        <v>1377510242</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>42887004</v>
+        <v>225841873</v>
       </c>
       <c r="I61" t="n">
-        <v>2.81</v>
+        <v>0.999798</v>
       </c>
       <c r="J61" t="n">
-        <v>2.55</v>
+        <v>0.999166</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.1819481903047433</v>
+        <v>-0.000154769200326643</v>
       </c>
       <c r="L61" t="n">
-        <v>-6.70116</v>
+        <v>-0.01442</v>
       </c>
       <c r="M61" t="n">
-        <v>556836861.785925</v>
+        <v>1378129007.8</v>
       </c>
       <c r="N61" t="n">
-        <v>556837055.0446609</v>
+        <v>1378129007.8</v>
       </c>
       <c r="O61" t="n">
-        <v>700.65</v>
+        <v>1.008</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>44326.33741898148</v>
+        <v>46058.54591435185</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0005513193960909241</v>
+        <v>0.0005500395022515535</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4562,25 +4562,25 @@
         <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>1377093904</v>
+        <v>1376853385</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>31562399</v>
+        <v>29199129</v>
       </c>
       <c r="I62" t="n">
         <v>1</v>
       </c>
       <c r="J62" t="n">
-        <v>0.999933</v>
+        <v>0.99992</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.5947677081992e-05</v>
+        <v>-8.0981112964729e-05</v>
       </c>
       <c r="L62" t="n">
-        <v>-0.01203</v>
+        <v>0.009379999999999999</v>
       </c>
       <c r="M62" t="n">
         <v>1376792098.16</v>
@@ -4595,19 +4595,19 @@
         <v>46092.00303240741</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005197955933878487</v>
+        <v>0.0005496063386352679</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4629,7 +4629,7 @@
         <v>1.17</v>
       </c>
       <c r="F63" t="n">
-        <v>1376544776</v>
+        <v>1376168930</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
@@ -4644,16 +4644,16 @@
         <v>1.17</v>
       </c>
       <c r="K63" t="n">
-        <v>0.00164308</v>
+        <v>-0.001659150911115903</v>
       </c>
       <c r="L63" t="n">
-        <v>0.14074</v>
+        <v>-0.14188</v>
       </c>
       <c r="M63" t="n">
-        <v>1177453283.40974</v>
+        <v>1178470806.74904</v>
       </c>
       <c r="N63" t="n">
-        <v>1177453283.40974</v>
+        <v>1178470806.74904</v>
       </c>
       <c r="O63" t="n">
         <v>1.18</v>
@@ -4662,153 +4662,153 @@
         <v>46255.48263888889</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0005194375346890599</v>
+        <v>0.000549154975548653</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>united-stables</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>United Stables</t>
+          <t>Sky</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.999803</v>
+        <v>0.057334</v>
       </c>
       <c r="F64" t="n">
-        <v>1373827468</v>
+        <v>1342806546</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>216485336</v>
+        <v>10993284</v>
       </c>
       <c r="I64" t="n">
+        <v>0.06300699999999999</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.057434</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-0.004148728338795607</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-6.78372</v>
+      </c>
+      <c r="M64" t="n">
+        <v>23424420947.147</v>
+      </c>
+      <c r="N64" t="n">
+        <v>23459804203.60596</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.100535</v>
+      </c>
+      <c r="P64" s="1" t="n">
+        <v>45630.09302083333</v>
+      </c>
+      <c r="Q64" s="1" t="n">
+        <v>46281.58692129629</v>
+      </c>
+      <c r="R64" t="b">
         <v>1</v>
       </c>
-      <c r="J64" t="n">
-        <v>0.999583</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0.00021758</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0.01423</v>
-      </c>
-      <c r="M64" t="n">
-        <v>1374129107.8</v>
-      </c>
-      <c r="N64" t="n">
-        <v>1375129007.8</v>
-      </c>
-      <c r="O64" t="n">
-        <v>1.008</v>
-      </c>
-      <c r="P64" s="1" t="n">
-        <v>46058.54591435185</v>
-      </c>
-      <c r="Q64" s="1" t="n">
-        <v>46280.59259259259</v>
-      </c>
-      <c r="R64" t="b">
-        <v>0</v>
-      </c>
       <c r="S64" t="n">
-        <v>0.0005176657150646952</v>
+        <v>0.0005271541886173318</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>worldcoin-wld</t>
+          <t>falcon-finance</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>wld</t>
+          <t>usdf</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Worldcoin</t>
+          <t>Falcon USD</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.375954</v>
+        <v>0.9957589999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>1351513415</v>
+        <v>1339091149</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>142263721</v>
+        <v>460881</v>
       </c>
       <c r="I65" t="n">
-        <v>0.399039</v>
+        <v>0.996406</v>
       </c>
       <c r="J65" t="n">
-        <v>0.37093</v>
+        <v>0.995601</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.009506752743714764</v>
+        <v>-0.000431174357211184</v>
       </c>
       <c r="L65" t="n">
-        <v>-2.53456</v>
+        <v>-0.0372</v>
       </c>
       <c r="M65" t="n">
-        <v>3594283025.842473</v>
+        <v>1344884513.993609</v>
       </c>
       <c r="N65" t="n">
-        <v>10000000000</v>
+        <v>1344884513.993609</v>
       </c>
       <c r="O65" t="n">
-        <v>11.74</v>
+        <v>1.075</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>45360.67409722223</v>
+        <v>45785.55951388889</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0005031158454862314</v>
+        <v>0.0005247040742081735</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4827,28 +4827,28 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="F66" t="n">
-        <v>1347341975</v>
+        <v>1332577327</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
       </c>
       <c r="H66" t="n">
-        <v>10542804</v>
+        <v>13392614</v>
       </c>
       <c r="I66" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="J66" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.01668685705277295</v>
+        <v>-0.02025327828207968</v>
       </c>
       <c r="L66" t="n">
-        <v>-0.8549600000000001</v>
+        <v>-0.97004</v>
       </c>
       <c r="M66" t="n">
         <v>699992029.6481038</v>
@@ -4863,153 +4863,153 @@
         <v>45653.15375</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0005003958596569253</v>
+        <v>0.0005204085415528767</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>falcon-finance</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>usdf</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Falcon USD</t>
+          <t>BFUSD</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.996205</v>
+        <v>0.9993570000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>1339405916</v>
+        <v>1318973778</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
       </c>
       <c r="H67" t="n">
-        <v>818460</v>
+        <v>1518246</v>
       </c>
       <c r="I67" t="n">
-        <v>0.9967240000000001</v>
+        <v>0.999513</v>
       </c>
       <c r="J67" t="n">
-        <v>0.996085</v>
+        <v>0.999119</v>
       </c>
       <c r="K67" t="n">
-        <v>-8.8844266114108e-05</v>
+        <v>-0.000116076332385417</v>
       </c>
       <c r="L67" t="n">
-        <v>-0.01422</v>
+        <v>-0.01124</v>
       </c>
       <c r="M67" t="n">
-        <v>1344553697.303609</v>
+        <v>1320000000</v>
       </c>
       <c r="N67" t="n">
-        <v>1344553697.303609</v>
+        <v>1320000000</v>
       </c>
       <c r="O67" t="n">
-        <v>1.075</v>
+        <v>1.007</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>45785.55951388889</v>
+        <v>45940.56990740741</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0004952211554731092</v>
+        <v>0.0005114376963321398</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>worldcoin-wld</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>wld</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>BFUSD</t>
+          <t>Worldcoin</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.999567</v>
+        <v>0.365299</v>
       </c>
       <c r="F68" t="n">
-        <v>1319406092</v>
+        <v>1311688082</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>2266914</v>
+        <v>153619759</v>
       </c>
       <c r="I68" t="n">
-        <v>0.999887</v>
+        <v>0.376268</v>
       </c>
       <c r="J68" t="n">
-        <v>0.999465</v>
+        <v>0.356093</v>
       </c>
       <c r="K68" t="n">
-        <v>3.971e-05</v>
+        <v>-0.01090622315875917</v>
       </c>
       <c r="L68" t="n">
-        <v>0.00378</v>
+        <v>-2.86525</v>
       </c>
       <c r="M68" t="n">
-        <v>1320000000</v>
+        <v>3595707955.148494</v>
       </c>
       <c r="N68" t="n">
-        <v>1320000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O68" t="n">
-        <v>1.007</v>
+        <v>11.74</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>45940.56990740741</v>
+        <v>45360.67409722223</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0004821802780138584</v>
+        <v>0.000506633152228146</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5028,34 +5028,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>7.38</v>
+        <v>7.18</v>
       </c>
       <c r="F69" t="n">
-        <v>1167799278</v>
+        <v>1133907018</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>44519262</v>
+        <v>46650779</v>
       </c>
       <c r="I69" t="n">
-        <v>7.76</v>
+        <v>7.45</v>
       </c>
       <c r="J69" t="n">
-        <v>7.36</v>
+        <v>7.11</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.2463582866913399</v>
+        <v>-0.20766814353341</v>
       </c>
       <c r="L69" t="n">
-        <v>-3.23381</v>
+        <v>-2.87563</v>
       </c>
       <c r="M69" t="n">
-        <v>158175159.0847009</v>
+        <v>158185641.5337251</v>
       </c>
       <c r="N69" t="n">
-        <v>158175567.4156298</v>
+        <v>158186024.4073251</v>
       </c>
       <c r="O69" t="n">
         <v>167.09</v>
@@ -5064,220 +5064,220 @@
         <v>44322.44053240741</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0003833251139203426</v>
+        <v>0.0003893956277908165</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>lighter</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>lit</t>
+          <t>arb</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Lighter</t>
+          <t>Arbitrum</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4.29</v>
+        <v>0.165277</v>
       </c>
       <c r="F70" t="n">
-        <v>1072773446</v>
+        <v>1102969954</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>80010700</v>
+        <v>650336297</v>
       </c>
       <c r="I70" t="n">
-        <v>4.63</v>
+        <v>0.172852</v>
       </c>
       <c r="J70" t="n">
-        <v>4.31</v>
+        <v>0.137254</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.1893094868186722</v>
+        <v>0.02526612</v>
       </c>
       <c r="L70" t="n">
-        <v>-4.19031</v>
+        <v>18.2524</v>
       </c>
       <c r="M70" t="n">
-        <v>250000000</v>
+        <v>6678075931</v>
       </c>
       <c r="N70" t="n">
-        <v>1000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O70" t="n">
-        <v>7.86</v>
+        <v>2.39</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>46021.04538194444</v>
+        <v>45303.18748842592</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R70" t="b">
         <v>1</v>
       </c>
       <c r="S70" t="n">
-        <v>0.000321363557129875</v>
+        <v>0.0003689942154293784</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>pi-network</t>
+          <t>venice-token</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>pi</t>
+          <t>vvv</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Pi Network</t>
+          <t>Venice Token</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.095679</v>
+        <v>22.61</v>
       </c>
       <c r="F71" t="n">
-        <v>1071248945</v>
+        <v>1083491058</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>6883895</v>
+        <v>43193731</v>
       </c>
       <c r="I71" t="n">
-        <v>0.09867099999999999</v>
+        <v>23.14</v>
       </c>
       <c r="J71" t="n">
-        <v>0.09478</v>
+        <v>21.2</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.001542167443357528</v>
+        <v>0.357533</v>
       </c>
       <c r="L71" t="n">
-        <v>-1.62195</v>
+        <v>1.59864</v>
       </c>
       <c r="M71" t="n">
-        <v>11193100867.75027</v>
+        <v>48003455.9200405</v>
       </c>
       <c r="N71" t="n">
-        <v>17220155181.15426</v>
+        <v>81021132.76533473</v>
       </c>
       <c r="O71" t="n">
-        <v>2.99</v>
+        <v>29.19</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>45714.36184027778</v>
+        <v>46274.32083333333</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R71" t="b">
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0003203695068458573</v>
+        <v>0.0003561488791802253</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>venice-token</t>
+          <t>lighter</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>vvv</t>
+          <t>lit</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Venice Token</t>
+          <t>Lighter</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>22.27</v>
+        <v>4.23</v>
       </c>
       <c r="F72" t="n">
-        <v>1068292746</v>
+        <v>1055579082</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>35619335</v>
+        <v>96637961</v>
       </c>
       <c r="I72" t="n">
-        <v>23.27</v>
+        <v>4.34</v>
       </c>
       <c r="J72" t="n">
-        <v>21.56</v>
+        <v>4.01</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.2217232803884315</v>
+        <v>-0.07017384741305221</v>
       </c>
       <c r="L72" t="n">
-        <v>-0.85206</v>
+        <v>-1.61376</v>
       </c>
       <c r="M72" t="n">
-        <v>47975693.6029577</v>
+        <v>250000000</v>
       </c>
       <c r="N72" t="n">
-        <v>81014279.80364013</v>
+        <v>1000000000</v>
       </c>
       <c r="O72" t="n">
-        <v>29.19</v>
+        <v>7.86</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>46274.32083333333</v>
+        <v>46021.04538194444</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0003184419184378713</v>
+        <v>0.0003377423577275572</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5296,34 +5296,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.096828</v>
+        <v>0.09250899999999999</v>
       </c>
       <c r="F73" t="n">
-        <v>1038280082</v>
+        <v>991192671</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>60782906</v>
+        <v>107112474</v>
       </c>
       <c r="I73" t="n">
-        <v>0.098589</v>
+        <v>0.09823900000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>0.095649</v>
+        <v>0.090587</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.0009225235350158319</v>
+        <v>-0.004415757777720158</v>
       </c>
       <c r="L73" t="n">
-        <v>-0.95701</v>
+        <v>-4.61361</v>
       </c>
       <c r="M73" t="n">
-        <v>10714685269.72835</v>
+        <v>10715266597.60465</v>
       </c>
       <c r="N73" t="n">
-        <v>10714685269.72835</v>
+        <v>10715266597.60465</v>
       </c>
       <c r="O73" t="n">
         <v>1.29</v>
@@ -5332,153 +5332,153 @@
         <v>45364.45493055556</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S73" t="n">
-        <v>0.000298872172551624</v>
+        <v>0.0002952828107814076</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>gatechain-token</t>
+          <t>blockchain-capital</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>gt</t>
+          <t>bcap</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Blockchain Capital</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>9.17</v>
+        <v>106.54</v>
       </c>
       <c r="F74" t="n">
-        <v>977340269</v>
+        <v>970804306</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>3739451</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>9.42</v>
+        <v>106.54</v>
       </c>
       <c r="J74" t="n">
-        <v>9.130000000000001</v>
+        <v>106.54</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.1388848429960898</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>-1.49455</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>106628927.3474872</v>
+        <v>9112111</v>
       </c>
       <c r="N74" t="n">
-        <v>118880214.648508</v>
+        <v>9112111</v>
       </c>
       <c r="O74" t="n">
-        <v>25.38</v>
+        <v>106.54</v>
       </c>
       <c r="P74" s="1" t="n">
-        <v>45682.66666666666</v>
+        <v>46280.14583333334</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R74" t="b">
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0002591363911906149</v>
+        <v>0.0002818377262142194</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>blockchain-capital</t>
+          <t>gatechain-token</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>bcap</t>
+          <t>gt</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Blockchain Capital</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106.54</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="F75" t="n">
-        <v>970804306</v>
+        <v>964005510</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>3857894</v>
       </c>
       <c r="I75" t="n">
-        <v>106.54</v>
+        <v>9.17</v>
       </c>
       <c r="J75" t="n">
-        <v>106.49</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>0.05</v>
+        <v>-0.1091559648858578</v>
       </c>
       <c r="L75" t="n">
-        <v>0.04695</v>
+        <v>-1.13057</v>
       </c>
       <c r="M75" t="n">
-        <v>9112111</v>
+        <v>106630069.9300583</v>
       </c>
       <c r="N75" t="n">
-        <v>9112111</v>
+        <v>118881346.4290974</v>
       </c>
       <c r="O75" t="n">
-        <v>106.54</v>
+        <v>25.38</v>
       </c>
       <c r="P75" s="1" t="n">
-        <v>46280.14583333334</v>
+        <v>45682.66666666666</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R75" t="b">
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0002548746190589603</v>
+        <v>0.0002773542677723551</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5497,28 +5497,28 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.115767</v>
+        <v>0.115864</v>
       </c>
       <c r="F76" t="n">
-        <v>947997627</v>
+        <v>947734118</v>
       </c>
       <c r="G76" t="n">
         <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>24339509</v>
+        <v>17124734</v>
       </c>
       <c r="I76" t="n">
-        <v>0.116079</v>
+        <v>0.116574</v>
       </c>
       <c r="J76" t="n">
-        <v>0.112465</v>
+        <v>0.113158</v>
       </c>
       <c r="K76" t="n">
-        <v>0.00243642</v>
+        <v>0.00020579</v>
       </c>
       <c r="L76" t="n">
-        <v>2.15246</v>
+        <v>0.19438</v>
       </c>
       <c r="M76" t="n">
         <v>8188743036.341737</v>
@@ -5533,19 +5533,19 @@
         <v>44290.85721064815</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R76" t="b">
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0002400035328888285</v>
+        <v>0.0002666241164597869</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5564,28 +5564,28 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6.88</v>
+        <v>6.78</v>
       </c>
       <c r="F77" t="n">
-        <v>943479766</v>
+        <v>929627401</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>3877147</v>
+        <v>4671099</v>
       </c>
       <c r="I77" t="n">
-        <v>7.13</v>
+        <v>6.84</v>
       </c>
       <c r="J77" t="n">
-        <v>6.88</v>
+        <v>6.76</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.1194161402508094</v>
+        <v>-0.1033133770776775</v>
       </c>
       <c r="L77" t="n">
-        <v>-1.73771</v>
+        <v>-1.48355</v>
       </c>
       <c r="M77" t="n">
         <v>137155021.2773955</v>
@@ -5600,153 +5600,153 @@
         <v>44531.29832175926</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R77" t="b">
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002370576633812304</v>
+        <v>0.0002546836621222692</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>kaspa</t>
+          <t>pi-network</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>kas</t>
+          <t>pi</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Kaspa</t>
+          <t>Pi Network</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.03388516</v>
+        <v>0.082159</v>
       </c>
       <c r="F78" t="n">
-        <v>939990647</v>
+        <v>919967696</v>
       </c>
       <c r="G78" t="n">
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>11621395</v>
+        <v>15567692</v>
       </c>
       <c r="I78" t="n">
-        <v>0.03532002</v>
+        <v>0.09499</v>
       </c>
       <c r="J78" t="n">
-        <v>0.03340135</v>
+        <v>0.081188</v>
       </c>
       <c r="K78" t="n">
-        <v>0.00035058</v>
+        <v>-0.0134566338486979</v>
       </c>
       <c r="L78" t="n">
-        <v>1.06347</v>
+        <v>-14.04266</v>
       </c>
       <c r="M78" t="n">
-        <v>27701726137.01383</v>
+        <v>11202518627.78052</v>
       </c>
       <c r="N78" t="n">
-        <v>27701821229.68735</v>
+        <v>17234644042.73926</v>
       </c>
       <c r="O78" t="n">
-        <v>0.207411</v>
+        <v>2.99</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>45504.69498842592</v>
+        <v>45714.36184027778</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002347825846945508</v>
+        <v>0.000248313580430133</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>kaspa</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>arb</t>
+          <t>kas</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Arbitrum</t>
+          <t>Kaspa</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.140071</v>
+        <v>0.03209132</v>
       </c>
       <c r="F79" t="n">
-        <v>935413458</v>
+        <v>888927046</v>
       </c>
       <c r="G79" t="n">
         <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>203934843</v>
+        <v>11894660</v>
       </c>
       <c r="I79" t="n">
-        <v>0.143736</v>
+        <v>0.03407844</v>
       </c>
       <c r="J79" t="n">
-        <v>0.131607</v>
+        <v>0.03173331</v>
       </c>
       <c r="K79" t="n">
-        <v>0.00446819</v>
+        <v>-0.00185140908267041</v>
       </c>
       <c r="L79" t="n">
-        <v>3.13831</v>
+        <v>-5.43137</v>
       </c>
       <c r="M79" t="n">
-        <v>6678075931</v>
+        <v>27701989210.63944</v>
       </c>
       <c r="N79" t="n">
-        <v>10000000000</v>
+        <v>27703725584.33658</v>
       </c>
       <c r="O79" t="n">
-        <v>2.39</v>
+        <v>0.207411</v>
       </c>
       <c r="P79" s="1" t="n">
-        <v>45303.18748842592</v>
+        <v>45504.69498842592</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002317980303876314</v>
+        <v>0.0002278438583964883</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5765,28 +5765,28 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>62.44</v>
+        <v>59.12</v>
       </c>
       <c r="F80" t="n">
-        <v>908830203</v>
+        <v>859982178</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>7799171</v>
+        <v>8011305</v>
       </c>
       <c r="I80" t="n">
-        <v>65.02</v>
+        <v>62.97</v>
       </c>
       <c r="J80" t="n">
-        <v>62.38</v>
+        <v>59.13</v>
       </c>
       <c r="K80" t="n">
-        <v>-1.883624011551255</v>
+        <v>-3.441180867104492</v>
       </c>
       <c r="L80" t="n">
-        <v>-2.8827</v>
+        <v>-5.39741</v>
       </c>
       <c r="M80" t="n">
         <v>14544176.16408117</v>
@@ -5801,86 +5801,86 @@
         <v>44450.05208333334</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S80" t="n">
-        <v>0.000214464429305791</v>
+        <v>0.0002087561974660459</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>algorand</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>algo</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Algorand</t>
+          <t>Spiko EU T-Bills Money Market Fund</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.095805</v>
+        <v>1.22</v>
       </c>
       <c r="F81" t="n">
-        <v>867128014</v>
+        <v>797086512</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>38797892</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0.098229</v>
+        <v>1.22</v>
       </c>
       <c r="J81" t="n">
-        <v>0.09395299999999999</v>
+        <v>1.22</v>
       </c>
       <c r="K81" t="n">
-        <v>0.00082591</v>
+        <v>-0.001653273013533907</v>
       </c>
       <c r="L81" t="n">
-        <v>0.85286</v>
+        <v>-0.13521</v>
       </c>
       <c r="M81" t="n">
-        <v>9041440361.74052</v>
+        <v>652741858.0353301</v>
       </c>
       <c r="N81" t="n">
-        <v>9041449215.81741</v>
+        <v>652741858.0353301</v>
       </c>
       <c r="O81" t="n">
-        <v>3.56</v>
+        <v>1.26</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>43636.28563657407</v>
+        <v>46049.54175925926</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R81" t="b">
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0001872725331905293</v>
+        <v>0.0001672797206480362</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5899,34 +5899,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="F82" t="n">
-        <v>828847171</v>
+        <v>794058682</v>
       </c>
       <c r="G82" t="n">
         <v>81</v>
       </c>
       <c r="H82" t="n">
-        <v>50034794</v>
+        <v>40018692</v>
       </c>
       <c r="I82" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="J82" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="K82" t="n">
-        <v>0.01176572</v>
+        <v>-0.06371213836752765</v>
       </c>
       <c r="L82" t="n">
-        <v>0.75398</v>
+        <v>-4.00223</v>
       </c>
       <c r="M82" t="n">
-        <v>530840914.851673</v>
+        <v>531026230.140559</v>
       </c>
       <c r="N82" t="n">
-        <v>530857108.180759</v>
+        <v>531040943.180444</v>
       </c>
       <c r="O82" t="n">
         <v>43.84</v>
@@ -5935,19 +5935,19 @@
         <v>44458.66666666666</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0001623115244036609</v>
+        <v>0.0001652830215304233</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5966,28 +5966,28 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.803162</v>
+        <v>0.787241</v>
       </c>
       <c r="F83" t="n">
-        <v>803120563</v>
+        <v>786768061</v>
       </c>
       <c r="G83" t="n">
         <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>4922595</v>
+        <v>4032116</v>
       </c>
       <c r="I83" t="n">
-        <v>0.838348</v>
+        <v>0.804343</v>
       </c>
       <c r="J83" t="n">
-        <v>0.800049</v>
+        <v>0.784022</v>
       </c>
       <c r="K83" t="n">
-        <v>-0.03110939307527849</v>
+        <v>-0.01602228614867518</v>
       </c>
       <c r="L83" t="n">
-        <v>-3.69456</v>
+        <v>-1.98418</v>
       </c>
       <c r="M83" t="n">
         <v>1000000000</v>
@@ -6002,175 +6002,175 @@
         <v>44328.27623842593</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0001455364996649341</v>
+        <v>0.0001604752296406706</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>algorand</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>algo</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Spiko EU T-Bills Money Market Fund</t>
+          <t>Algorand</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1.22</v>
+        <v>0.086422</v>
       </c>
       <c r="F84" t="n">
-        <v>801792779</v>
+        <v>781294191</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>45158936</v>
       </c>
       <c r="I84" t="n">
-        <v>1.22</v>
+        <v>0.093933</v>
       </c>
       <c r="J84" t="n">
-        <v>1.22</v>
+        <v>0.085676</v>
       </c>
       <c r="K84" t="n">
-        <v>0.00220774</v>
+        <v>-0.009173342790273278</v>
       </c>
       <c r="L84" t="n">
-        <v>0.18093</v>
+        <v>-9.572710000000001</v>
       </c>
       <c r="M84" t="n">
-        <v>655893653.31917</v>
+        <v>9041440361.74052</v>
       </c>
       <c r="N84" t="n">
-        <v>655893653.31917</v>
+        <v>9041658401.381454</v>
       </c>
       <c r="O84" t="n">
-        <v>1.26</v>
+        <v>3.56</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>46049.54175925926</v>
+        <v>43636.28563657407</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001446707186242432</v>
+        <v>0.0001568654921722765</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jupiter-exchange-solana</t>
+          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>jup</t>
+          <t>ustb</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Invesco Short Duration US Government Securities Fund</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.230018</v>
+        <v>11.21</v>
       </c>
       <c r="F85" t="n">
-        <v>763485841</v>
+        <v>746133355</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>60014202</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0.246898</v>
+        <v>11.21</v>
       </c>
       <c r="J85" t="n">
-        <v>0.228675</v>
+        <v>11.21</v>
       </c>
       <c r="K85" t="n">
-        <v>-0.007376134673183238</v>
+        <v>0.001077</v>
       </c>
       <c r="L85" t="n">
-        <v>-3.11634</v>
+        <v>0.00961</v>
       </c>
       <c r="M85" t="n">
-        <v>3319369204.37</v>
+        <v>66538460.783645</v>
       </c>
       <c r="N85" t="n">
-        <v>6861487098.486876</v>
+        <v>66405944.731128</v>
       </c>
       <c r="O85" t="n">
-        <v>2</v>
+        <v>11.21</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>45322.29359953704</v>
+        <v>46281.55567129629</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R85" t="b">
         <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001196926946027759</v>
+        <v>0.0001336787180747442</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
+          <t>janus-henderson-anemoy-aaa-clo-fund</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ustb</t>
+          <t>jaaa</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Invesco Short Duration US Government Securities Fund</t>
+          <t>Janus Henderson Anemoy AAA CLO Fund</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>11.21</v>
+        <v>1.05</v>
       </c>
       <c r="F86" t="n">
-        <v>751978768</v>
+        <v>720567789</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
@@ -6179,378 +6179,378 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>11.21</v>
+        <v>1.05</v>
       </c>
       <c r="J86" t="n">
-        <v>11.21</v>
+        <v>1.05</v>
       </c>
       <c r="K86" t="n">
-        <v>0.003239</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>0.0289</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>67066182.610332</v>
+        <v>686482557.075531</v>
       </c>
       <c r="N86" t="n">
-        <v>65222093.392313</v>
+        <v>686482557.075531</v>
       </c>
       <c r="O86" t="n">
-        <v>11.21</v>
+        <v>1.05</v>
       </c>
       <c r="P86" s="1" t="n">
-        <v>46280.55555555555</v>
+        <v>46280.48611111111</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R86" t="b">
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001121895121293874</v>
+        <v>0.00011681953408044</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>pancakeswap-token</t>
+          <t>stable-2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>​​Stable</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2.29</v>
+        <v>0.02672222</v>
       </c>
       <c r="F87" t="n">
-        <v>732574091</v>
+        <v>704385120</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>74051260</v>
+        <v>9080584</v>
       </c>
       <c r="I87" t="n">
-        <v>2.4</v>
+        <v>0.02764996</v>
       </c>
       <c r="J87" t="n">
-        <v>2.27</v>
+        <v>0.02669047</v>
       </c>
       <c r="K87" t="n">
-        <v>-0.06867599323406859</v>
+        <v>-0.000927100387334255</v>
       </c>
       <c r="L87" t="n">
-        <v>-2.92392</v>
+        <v>-3.31507</v>
       </c>
       <c r="M87" t="n">
-        <v>319429131.5073305</v>
+        <v>26372627229</v>
       </c>
       <c r="N87" t="n">
-        <v>331093394.0100838</v>
+        <v>100000000000</v>
       </c>
       <c r="O87" t="n">
-        <v>43.96</v>
+        <v>0.04323745</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>44316.08914351852</v>
+        <v>46156.97986111111</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R87" t="b">
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>9.953670003997387e-05</v>
+        <v>0.0001061478910512999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>stable-2</t>
+          <t>jupiter-exchange-solana</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>jup</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>​​Stable</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.0276833</v>
+        <v>0.211556</v>
       </c>
       <c r="F88" t="n">
-        <v>729228574</v>
+        <v>700563517</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>9345608</v>
+        <v>67620445</v>
       </c>
       <c r="I88" t="n">
-        <v>0.02859739</v>
+        <v>0.2301</v>
       </c>
       <c r="J88" t="n">
-        <v>0.02752428</v>
+        <v>0.209445</v>
       </c>
       <c r="K88" t="n">
-        <v>-0.001107858424843254</v>
+        <v>-0.01853123163518763</v>
       </c>
       <c r="L88" t="n">
-        <v>-3.90902</v>
+        <v>-7.95869</v>
       </c>
       <c r="M88" t="n">
-        <v>26343010631</v>
+        <v>3319369204.37</v>
       </c>
       <c r="N88" t="n">
-        <v>100000000000</v>
+        <v>6861487082.669715</v>
       </c>
       <c r="O88" t="n">
-        <v>0.04323745</v>
+        <v>2</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>46156.97986111111</v>
+        <v>45322.29359953704</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R88" t="b">
         <v>1</v>
       </c>
       <c r="S88" t="n">
-        <v>9.735525698153293e-05</v>
+        <v>0.0001036277392138563</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>filecoin</t>
+          <t>pancakeswap-token</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.877628</v>
+        <v>2.19</v>
       </c>
       <c r="F89" t="n">
-        <v>726414795</v>
+        <v>697776297</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>182542096</v>
+        <v>66568314</v>
       </c>
       <c r="I89" t="n">
-        <v>0.997536</v>
+        <v>2.28</v>
       </c>
       <c r="J89" t="n">
-        <v>0.869956</v>
+        <v>2.16</v>
       </c>
       <c r="K89" t="n">
-        <v>-0.1430934825638447</v>
+        <v>-0.1069725160327675</v>
       </c>
       <c r="L89" t="n">
-        <v>-13.77457</v>
+        <v>-4.64511</v>
       </c>
       <c r="M89" t="n">
-        <v>827813309</v>
+        <v>319432296.7908565</v>
       </c>
       <c r="N89" t="n">
-        <v>1957050532</v>
+        <v>331093394.0049145</v>
       </c>
       <c r="O89" t="n">
-        <v>236.84</v>
+        <v>43.96</v>
       </c>
       <c r="P89" s="1" t="n">
-        <v>44287.22894675926</v>
+        <v>44316.08914351852</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R89" t="b">
         <v>1</v>
       </c>
       <c r="S89" t="n">
-        <v>9.552053347914544e-05</v>
+        <v>0.0001017897100924747</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-aaa-clo-fund</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>jaaa</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy AAA CLO Fund</t>
+          <t>GHO</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1.05</v>
+        <v>0.998568</v>
       </c>
       <c r="F90" t="n">
-        <v>715044711</v>
+        <v>697975152</v>
       </c>
       <c r="G90" t="n">
         <v>89</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>7653280</v>
       </c>
       <c r="I90" t="n">
-        <v>1.05</v>
+        <v>0.998815</v>
       </c>
       <c r="J90" t="n">
-        <v>1.05</v>
+        <v>0.998372</v>
       </c>
       <c r="K90" t="n">
-        <v>8.500000000000001e-05</v>
+        <v>-0.000165807461207645</v>
       </c>
       <c r="L90" t="n">
-        <v>0.0081</v>
+        <v>-0.019</v>
       </c>
       <c r="M90" t="n">
-        <v>681220739.278982</v>
+        <v>699000000</v>
       </c>
       <c r="N90" t="n">
-        <v>681220786.91379</v>
+        <v>699000000</v>
       </c>
       <c r="O90" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="P90" s="1" t="n">
-        <v>46280.48611111111</v>
+        <v>45350.38608796296</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>8.810667462991815e-05</v>
+        <v>0.0001019208448005108</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>render-token</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>render</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>Dash</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1.36</v>
+        <v>54.29</v>
       </c>
       <c r="F91" t="n">
-        <v>704219729</v>
+        <v>696465238</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>36902335</v>
+        <v>126702373</v>
       </c>
       <c r="I91" t="n">
-        <v>1.41</v>
+        <v>55.98</v>
       </c>
       <c r="J91" t="n">
-        <v>1.35</v>
+        <v>49.94</v>
       </c>
       <c r="K91" t="n">
-        <v>-0.02604220787391576</v>
+        <v>1.85</v>
       </c>
       <c r="L91" t="n">
-        <v>-1.90472</v>
+        <v>3.46177</v>
       </c>
       <c r="M91" t="n">
-        <v>518776241.2826915</v>
+        <v>12830909.72488206</v>
       </c>
       <c r="N91" t="n">
-        <v>533536414.5626915</v>
+        <v>12830982.59594397</v>
       </c>
       <c r="O91" t="n">
-        <v>13.53</v>
+        <v>1493.59</v>
       </c>
       <c r="P91" s="1" t="n">
-        <v>45368.35444444444</v>
+        <v>43088.66666666666</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R91" t="b">
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>8.104824932774568e-05</v>
+        <v>0.0001009251336966934</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6572,7 +6572,7 @@
         <v>1.12</v>
       </c>
       <c r="F92" t="n">
-        <v>700262452</v>
+        <v>675176286</v>
       </c>
       <c r="G92" t="n">
         <v>91</v>
@@ -6587,305 +6587,305 @@
         <v>1.12</v>
       </c>
       <c r="K92" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>0.00011</v>
       </c>
       <c r="L92" t="n">
-        <v>0.008070000000000001</v>
+        <v>0.009860000000000001</v>
       </c>
       <c r="M92" t="n">
-        <v>627489934.721184</v>
+        <v>604951138.283703</v>
       </c>
       <c r="N92" t="n">
-        <v>627489934.721184</v>
+        <v>582549198.395</v>
       </c>
       <c r="O92" t="n">
         <v>1.12</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>46280.48958333334</v>
+        <v>46281.33680555555</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R92" t="b">
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>7.846790839927992e-05</v>
+        <v>8.688615803646711e-05</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>render-token</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>render</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>GHO</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9987549999999999</v>
+        <v>1.3</v>
       </c>
       <c r="F93" t="n">
-        <v>698117719</v>
+        <v>674256609</v>
       </c>
       <c r="G93" t="n">
         <v>92</v>
       </c>
       <c r="H93" t="n">
-        <v>7700537</v>
+        <v>41520575</v>
       </c>
       <c r="I93" t="n">
-        <v>0.999081</v>
+        <v>1.36</v>
       </c>
       <c r="J93" t="n">
-        <v>0.998621</v>
+        <v>1.29</v>
       </c>
       <c r="K93" t="n">
-        <v>0.00015295</v>
+        <v>-0.05666880936932883</v>
       </c>
       <c r="L93" t="n">
-        <v>0.01535</v>
+        <v>-4.1354</v>
       </c>
       <c r="M93" t="n">
-        <v>699000000</v>
+        <v>518776241.2826915</v>
       </c>
       <c r="N93" t="n">
-        <v>699000000</v>
+        <v>533536414.5626915</v>
       </c>
       <c r="O93" t="n">
-        <v>1.03</v>
+        <v>13.53</v>
       </c>
       <c r="P93" s="1" t="n">
-        <v>45350.38608796296</v>
+        <v>45368.35444444444</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S93" t="n">
-        <v>7.706943608093294e-05</v>
+        <v>8.627967806421343e-05</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>filecoin</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>fil</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Dash</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>52.5</v>
+        <v>0.78289</v>
       </c>
       <c r="F94" t="n">
-        <v>673584844</v>
+        <v>648099111</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
       </c>
       <c r="H94" t="n">
-        <v>91099510</v>
+        <v>156588845</v>
       </c>
       <c r="I94" t="n">
-        <v>56.34</v>
+        <v>0.869021</v>
       </c>
       <c r="J94" t="n">
-        <v>52.44</v>
+        <v>0.779522</v>
       </c>
       <c r="K94" t="n">
-        <v>-1.576147428098317</v>
+        <v>-0.09343837998466098</v>
       </c>
       <c r="L94" t="n">
-        <v>-3.00894</v>
+        <v>-10.75323</v>
       </c>
       <c r="M94" t="n">
-        <v>12829630.22789848</v>
+        <v>827813309</v>
       </c>
       <c r="N94" t="n">
-        <v>12829743.16411079</v>
+        <v>1957045721</v>
       </c>
       <c r="O94" t="n">
-        <v>1493.59</v>
+        <v>236.84</v>
       </c>
       <c r="P94" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>44287.22894675926</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S94" t="n">
-        <v>6.107278448049294e-05</v>
+        <v>6.903014517248545e-05</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>vechain</t>
+          <t>akedo</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>vet</t>
+          <t>ake</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VeChain</t>
+          <t>Akedo</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.00737211</v>
+        <v>0.02712454</v>
       </c>
       <c r="F95" t="n">
-        <v>634078632</v>
+        <v>617387700</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>11823521</v>
+        <v>51222202</v>
       </c>
       <c r="I95" t="n">
-        <v>0.007920190000000001</v>
+        <v>0.02946829</v>
       </c>
       <c r="J95" t="n">
-        <v>0.00730566</v>
+        <v>0.02453896</v>
       </c>
       <c r="K95" t="n">
-        <v>-0.000340490086909007</v>
+        <v>0.00127937</v>
       </c>
       <c r="L95" t="n">
-        <v>-4.44513</v>
+        <v>4.44773</v>
       </c>
       <c r="M95" t="n">
-        <v>85985041177</v>
+        <v>22796250000</v>
       </c>
       <c r="N95" t="n">
-        <v>85985041177</v>
+        <v>100000000000</v>
       </c>
       <c r="O95" t="n">
-        <v>0.280991</v>
+        <v>0.0363756</v>
       </c>
       <c r="P95" s="1" t="n">
-        <v>44304.71413194444</v>
+        <v>46267.90648148148</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>3.531277431384421e-05</v>
+        <v>4.877753943030488e-05</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>akedo</t>
+          <t>vechain</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ake</t>
+          <t>vet</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Akedo</t>
+          <t>VeChain</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.02610193</v>
+        <v>0.00697751</v>
       </c>
       <c r="F96" t="n">
-        <v>597035420</v>
+        <v>599636325</v>
       </c>
       <c r="G96" t="n">
         <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>61721944</v>
+        <v>12618280</v>
       </c>
       <c r="I96" t="n">
-        <v>0.02741537</v>
+        <v>0.007447</v>
       </c>
       <c r="J96" t="n">
-        <v>0.01516416</v>
+        <v>0.00695035</v>
       </c>
       <c r="K96" t="n">
-        <v>0.01068846</v>
+        <v>-0.000403271147242099</v>
       </c>
       <c r="L96" t="n">
-        <v>69.84222</v>
+        <v>-5.32643</v>
       </c>
       <c r="M96" t="n">
-        <v>22796250000</v>
+        <v>85985041177</v>
       </c>
       <c r="N96" t="n">
-        <v>100000000000</v>
+        <v>85985041177</v>
       </c>
       <c r="O96" t="n">
-        <v>0.0363756</v>
+        <v>0.280991</v>
       </c>
       <c r="P96" s="1" t="n">
-        <v>46267.90648148148</v>
+        <v>44304.71413194444</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R96" t="b">
         <v>1</v>
       </c>
       <c r="S96" t="n">
-        <v>1.115876233908633e-05</v>
+        <v>3.707141497849768e-05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6904,34 +6904,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.075861</v>
+        <v>0.075923</v>
       </c>
       <c r="F97" t="n">
-        <v>596871431</v>
+        <v>597572288</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>10114343</v>
+        <v>8624950</v>
       </c>
       <c r="I97" t="n">
-        <v>0.076349</v>
+        <v>0.07636</v>
       </c>
       <c r="J97" t="n">
-        <v>0.07459200000000001</v>
+        <v>0.07541399999999999</v>
       </c>
       <c r="K97" t="n">
-        <v>-0.00050519058263214</v>
+        <v>-5.8036939795517e-05</v>
       </c>
       <c r="L97" t="n">
-        <v>-0.68989</v>
+        <v>-0.02864</v>
       </c>
       <c r="M97" t="n">
-        <v>7870696881.257065</v>
+        <v>7870705626.343594</v>
       </c>
       <c r="N97" t="n">
-        <v>9939636626.049881</v>
+        <v>9939645626.343594</v>
       </c>
       <c r="O97" t="n">
         <v>0.450785</v>
@@ -6940,19 +6940,19 @@
         <v>43450.66666666666</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>1.105183337542819e-05</v>
+        <v>3.571028808015123e-05</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6971,28 +6971,28 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.611225</v>
+        <v>0.583417</v>
       </c>
       <c r="F98" t="n">
-        <v>590090078</v>
+        <v>562370413</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>38896642</v>
+        <v>36220169</v>
       </c>
       <c r="I98" t="n">
-        <v>0.662154</v>
+        <v>0.610816</v>
       </c>
       <c r="J98" t="n">
-        <v>0.607681</v>
+        <v>0.575364</v>
       </c>
       <c r="K98" t="n">
-        <v>-0.03185111082065628</v>
+        <v>-0.02821208126055863</v>
       </c>
       <c r="L98" t="n">
-        <v>-4.98443</v>
+        <v>-4.57759</v>
       </c>
       <c r="M98" t="n">
         <v>965350000</v>
@@ -7007,86 +7007,86 @@
         <v>45378.63525462963</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R98" t="b">
         <v>1</v>
       </c>
       <c r="S98" t="n">
-        <v>6.630054789730483e-06</v>
+        <v>1.249645085982546e-05</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>injective-protocol</t>
+          <t>usual-usd</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>inj</t>
+          <t>usd0</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Injective</t>
+          <t>Usual USD</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5.89</v>
+        <v>0.999088</v>
       </c>
       <c r="F99" t="n">
-        <v>589329459</v>
+        <v>547070561</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>88259966</v>
+        <v>2174570</v>
       </c>
       <c r="I99" t="n">
-        <v>6.43</v>
+        <v>0.999333</v>
       </c>
       <c r="J99" t="n">
-        <v>5.84</v>
+        <v>0.997592</v>
       </c>
       <c r="K99" t="n">
-        <v>-0.3017526046568832</v>
+        <v>0.00019516</v>
       </c>
       <c r="L99" t="n">
-        <v>-4.91081</v>
+        <v>0.01938</v>
       </c>
       <c r="M99" t="n">
-        <v>100000000</v>
+        <v>547588559.06276</v>
       </c>
       <c r="N99" t="n">
-        <v>100000000</v>
+        <v>547513539.7413483</v>
       </c>
       <c r="O99" t="n">
-        <v>52.62</v>
+        <v>1.33</v>
       </c>
       <c r="P99" s="1" t="n">
-        <v>45365.29608796296</v>
+        <v>45485.02012731481</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>6.134093466661944e-06</v>
+        <v>2.406980517036164e-06</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7105,28 +7105,28 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.02914224</v>
+        <v>0.02738998</v>
       </c>
       <c r="F100" t="n">
-        <v>581431899</v>
+        <v>546193737</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>10513944</v>
+        <v>11023396</v>
       </c>
       <c r="I100" t="n">
-        <v>0.02919974</v>
+        <v>0.02899922</v>
       </c>
       <c r="J100" t="n">
-        <v>0.02784208</v>
+        <v>0.02713273</v>
       </c>
       <c r="K100" t="n">
-        <v>0.00139765</v>
+        <v>-0.001787140154804887</v>
       </c>
       <c r="L100" t="n">
-        <v>5.02064</v>
+        <v>-6.02369</v>
       </c>
       <c r="M100" t="n">
         <v>19946688440</v>
@@ -7141,19 +7141,19 @@
         <v>44428.86097222222</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R100" t="b">
         <v>1</v>
       </c>
       <c r="S100" t="n">
-        <v>9.844925408197425e-07</v>
+        <v>1.828759907853417e-06</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7172,34 +7172,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.00666919</v>
+        <v>0.00624858</v>
       </c>
       <c r="F101" t="n">
-        <v>579922056</v>
+        <v>543420573</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>5808817</v>
+        <v>4229846</v>
       </c>
       <c r="I101" t="n">
-        <v>0.00683709</v>
+        <v>0.00670541</v>
       </c>
       <c r="J101" t="n">
-        <v>0.00649789</v>
+        <v>0.0062435</v>
       </c>
       <c r="K101" t="n">
-        <v>9.24e-05</v>
+        <v>-0.000419855243895558</v>
       </c>
       <c r="L101" t="n">
-        <v>1.39992</v>
+        <v>-6.28322</v>
       </c>
       <c r="M101" t="n">
-        <v>86956577959.42989</v>
+        <v>86970320242.41383</v>
       </c>
       <c r="N101" t="n">
-        <v>106552783687.1503</v>
+        <v>106559883415.9188</v>
       </c>
       <c r="O101" t="n">
         <v>0.150073</v>
@@ -7208,10 +7208,10 @@
         <v>44935.80144675926</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46280.59259259259</v>
+        <v>46281.58692129629</v>
       </c>
       <c r="R101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>

--- a/src/xlsx/cleaned_data.xlsx
+++ b/src/xlsx/cleaned_data.xlsx
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,34 +539,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>75575</v>
+        <v>76644</v>
       </c>
       <c r="F2" t="n">
-        <v>1516961178908</v>
+        <v>1539320607676</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>36368251316</v>
+        <v>30133625120</v>
       </c>
       <c r="I2" t="n">
-        <v>77146</v>
+        <v>77024</v>
       </c>
       <c r="J2" t="n">
-        <v>75038</v>
+        <v>75161</v>
       </c>
       <c r="K2" t="n">
-        <v>-769.8386863019696</v>
+        <v>1202.29</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.95843</v>
+        <v>1.59367</v>
       </c>
       <c r="M2" t="n">
-        <v>20085225</v>
+        <v>20085603</v>
       </c>
       <c r="N2" t="n">
-        <v>20085256</v>
+        <v>20085665</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -575,7 +575,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -587,7 +587,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,34 +606,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2391.27</v>
+        <v>2463.87</v>
       </c>
       <c r="F3" t="n">
-        <v>291683286516</v>
+        <v>300760183438</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>17993150906</v>
+        <v>15874627280</v>
       </c>
       <c r="I3" t="n">
-        <v>2445.14</v>
+        <v>2473.53</v>
       </c>
       <c r="J3" t="n">
-        <v>2361.16</v>
+        <v>2371.36</v>
       </c>
       <c r="K3" t="n">
-        <v>-56.62823994185237</v>
+        <v>79.62</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.27435</v>
+        <v>3.33959</v>
       </c>
       <c r="M3" t="n">
-        <v>122053082.6997495</v>
+        <v>122056009.605603</v>
       </c>
       <c r="N3" t="n">
-        <v>122053082.6997494</v>
+        <v>122056009.605603</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -642,19 +642,19 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1919918599889429</v>
+        <v>0.1950978003442244</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,28 +673,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999375</v>
+        <v>0.99915</v>
       </c>
       <c r="F4" t="n">
-        <v>183321762724</v>
+        <v>183284327911</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>64865798573</v>
+        <v>61718644343</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999575</v>
+        <v>0.999539</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999246</v>
+        <v>0.999112</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000230253735472474</v>
+        <v>-0.000238099616719611</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.02245</v>
+        <v>-0.02382</v>
       </c>
       <c r="M4" t="n">
         <v>183442587855.5799</v>
@@ -709,19 +709,19 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1205329739422779</v>
+        <v>0.1187538669601907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,34 +740,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>709.98</v>
+        <v>726.74</v>
       </c>
       <c r="F5" t="n">
-        <v>94483713743</v>
+        <v>96755073209</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>962279454</v>
+        <v>1032713365</v>
       </c>
       <c r="I5" t="n">
-        <v>723.8200000000001</v>
+        <v>731.53</v>
       </c>
       <c r="J5" t="n">
-        <v>704.22</v>
+        <v>708.73</v>
       </c>
       <c r="K5" t="n">
-        <v>-9.017519857691013</v>
+        <v>17.6</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.23775</v>
+        <v>2.4826</v>
       </c>
       <c r="M5" t="n">
-        <v>133160634.98</v>
+        <v>133160558.5</v>
       </c>
       <c r="N5" t="n">
-        <v>133160630.47</v>
+        <v>133160532.83</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -776,19 +776,19 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0619488215919766</v>
+        <v>0.06252117448815084</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -807,28 +807,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="F6" t="n">
-        <v>79971731012</v>
+        <v>82009347142</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>5372201415</v>
+        <v>3625730823</v>
       </c>
       <c r="I6" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="J6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.135845277811097</v>
+        <v>0.03567597</v>
       </c>
       <c r="L6" t="n">
-        <v>-9.61839</v>
+        <v>2.81145</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -843,19 +843,19 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05237891076019242</v>
+        <v>0.05293838214747688</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,34 +874,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999722</v>
+        <v>0.999571</v>
       </c>
       <c r="F7" t="n">
-        <v>73642078830</v>
+        <v>73555159854</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>19054647817</v>
+        <v>19170526434</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.999802</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999605</v>
+        <v>0.999055</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.6245719710569e-05</v>
+        <v>-0.000145914927842328</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0043</v>
+        <v>-0.0146</v>
       </c>
       <c r="M7" t="n">
-        <v>73664812907.1277</v>
+        <v>73587375656.46214</v>
       </c>
       <c r="N7" t="n">
-        <v>73653551003.2375</v>
+        <v>73590256479.63303</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -910,19 +910,19 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04820482868603507</v>
+        <v>0.04744426671213216</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -941,34 +941,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>97</v>
+        <v>100.77</v>
       </c>
       <c r="F8" t="n">
-        <v>56905505779</v>
+        <v>59152011113</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3795321892</v>
+        <v>3739451532</v>
       </c>
       <c r="I8" t="n">
-        <v>100.54</v>
+        <v>101.24</v>
       </c>
       <c r="J8" t="n">
-        <v>96.06999999999999</v>
+        <v>96.11</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.282241035908527</v>
+        <v>4.05</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.20872</v>
+        <v>4.18322</v>
       </c>
       <c r="M8" t="n">
-        <v>587064549.8169115</v>
+        <v>587212147.1182363</v>
       </c>
       <c r="N8" t="n">
-        <v>634110600.7933525</v>
+        <v>634204567.4934224</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -977,19 +977,19 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03716791424803979</v>
+        <v>0.03808410480421986</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1008,34 +1008,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.334519</v>
+        <v>0.334283</v>
       </c>
       <c r="F9" t="n">
-        <v>31757981216</v>
+        <v>31742370925</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>506942384</v>
+        <v>342292091</v>
       </c>
       <c r="I9" t="n">
-        <v>0.336594</v>
+        <v>0.336124</v>
       </c>
       <c r="J9" t="n">
-        <v>0.331863</v>
+        <v>0.334217</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.002960896167564342</v>
+        <v>-0.000219834965064225</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8641</v>
+        <v>-0.06572</v>
       </c>
       <c r="M9" t="n">
-        <v>94952171628.92049</v>
+        <v>94953504416.74518</v>
       </c>
       <c r="N9" t="n">
-        <v>94952166580.72699</v>
+        <v>94953498011.30618</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1044,153 +1044,153 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02058440721326888</v>
+        <v>0.02027142546508483</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>figure-heloc</t>
+          <t>zcash</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>figr_heloc</t>
+          <t>zec</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Figure Heloc</t>
+          <t>Zcash</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.003</v>
+        <v>1405.63</v>
       </c>
       <c r="F10" t="n">
-        <v>22696694484</v>
+        <v>23797511040</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>786631020</v>
+        <v>2809381550</v>
       </c>
       <c r="I10" t="n">
-        <v>1.047</v>
+        <v>1388.42</v>
       </c>
       <c r="J10" t="n">
-        <v>1.003</v>
+        <v>1235.16</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.02554960894943803</v>
+        <v>157.34</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.48407</v>
+        <v>12.60406</v>
       </c>
       <c r="M10" t="n">
-        <v>22624876494.218</v>
+        <v>16937203.2905448</v>
       </c>
       <c r="N10" t="n">
-        <v>22598468218.548</v>
+        <v>16937454.8530448</v>
       </c>
       <c r="O10" t="n">
-        <v>1.061</v>
+        <v>3191.93</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>46237.59675925926</v>
+        <v>42671.66666666666</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01460895178075724</v>
+        <v>0.01510830619189497</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>zcash</t>
+          <t>figure-heloc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>zec</t>
+          <t>figr_heloc</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Zcash</t>
+          <t>Figure Heloc</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1247.89</v>
+        <v>1.03</v>
       </c>
       <c r="F11" t="n">
-        <v>21100710958</v>
+        <v>23270039358</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1521322408</v>
+        <v>98622645</v>
       </c>
       <c r="I11" t="n">
-        <v>1268.97</v>
+        <v>1.03</v>
       </c>
       <c r="J11" t="n">
-        <v>1088.87</v>
+        <v>1.001</v>
       </c>
       <c r="K11" t="n">
-        <v>114.82</v>
+        <v>0.02657361</v>
       </c>
       <c r="L11" t="n">
-        <v>10.09064</v>
+        <v>2.64907</v>
       </c>
       <c r="M11" t="n">
-        <v>16933759.5405448</v>
+        <v>22598468218.548</v>
       </c>
       <c r="N11" t="n">
-        <v>16935675.1655448</v>
+        <v>22598468218.548</v>
       </c>
       <c r="O11" t="n">
-        <v>3191.93</v>
+        <v>1.061</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>42671.66666666666</v>
+        <v>46237.59675925926</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01355648222398262</v>
+        <v>0.01476551862272237</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1209,28 +1209,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>78.44</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>17440527363</v>
+        <v>18231266029</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>931340877</v>
+        <v>1146341296</v>
       </c>
       <c r="I12" t="n">
-        <v>79.58</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>75.27</v>
+        <v>77.19</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3175158379041818</v>
+        <v>3.78</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.40749</v>
+        <v>4.83726</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1245,19 +1245,19 @@
         <v>46271.5199074074</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01114277823319131</v>
+        <v>0.01149097532494652</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1276,34 +1276,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.07914300000000001</v>
+        <v>0.08157399999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>12328095249</v>
+        <v>12717767225</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>845852778</v>
+        <v>729261588</v>
       </c>
       <c r="I13" t="n">
-        <v>0.082368</v>
+        <v>0.08165500000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.078671</v>
+        <v>0.07836799999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.003420279153313957</v>
+        <v>0.00275889</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.14377</v>
+        <v>3.50047</v>
       </c>
       <c r="M13" t="n">
-        <v>155939426383.7052</v>
+        <v>155951756383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171651883126.579</v>
+        <v>171665603126.5791</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1312,19 +1312,19 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.007771390575733804</v>
+        <v>0.007907922590261105</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1343,34 +1343,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.999362</v>
+        <v>0.999765</v>
       </c>
       <c r="F14" t="n">
-        <v>9577947441</v>
+        <v>9555093003</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>218091969</v>
+        <v>234322913</v>
       </c>
       <c r="I14" t="n">
-        <v>0.999655</v>
+        <v>0.999879</v>
       </c>
       <c r="J14" t="n">
-        <v>0.999215</v>
+        <v>0.999135</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000261162282703786</v>
+        <v>0.00034214</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.02601</v>
+        <v>0.03423</v>
       </c>
       <c r="M14" t="n">
-        <v>9583931558.104593</v>
+        <v>9556951530.004086</v>
       </c>
       <c r="N14" t="n">
-        <v>9577504586.820999</v>
+        <v>9558143909.30253</v>
       </c>
       <c r="O14" t="n">
         <v>1.057</v>
@@ -1379,354 +1379,354 @@
         <v>45593.90336805556</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R14" t="b">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.005957808670032822</v>
+        <v>0.00585259820861168</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.01321058</v>
+        <v>505.06</v>
       </c>
       <c r="F15" t="n">
-        <v>9373518968</v>
+        <v>9497377500</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>26286505</v>
+        <v>117728327</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01451168</v>
+        <v>504.23</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01254013</v>
+        <v>485.12</v>
       </c>
       <c r="K15" t="n">
-        <v>0.00014604</v>
+        <v>9.43</v>
       </c>
       <c r="L15" t="n">
-        <v>1.13872</v>
+        <v>1.90225</v>
       </c>
       <c r="M15" t="n">
-        <v>709233397159.627</v>
+        <v>18805792.94955427</v>
       </c>
       <c r="N15" t="n">
-        <v>1142408526965.963</v>
+        <v>18805870.34941343</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01946402</v>
+        <v>797.73</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>46259.82847222222</v>
+        <v>46036.48202546296</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005822998541441042</v>
+        <v>0.005815090684223016</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>494.91</v>
+        <v>79.05</v>
       </c>
       <c r="F16" t="n">
-        <v>9317262109</v>
+        <v>9318236388</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>110227395</v>
+        <v>156128201</v>
       </c>
       <c r="I16" t="n">
-        <v>517.62</v>
+        <v>79.44</v>
       </c>
       <c r="J16" t="n">
-        <v>494.65</v>
+        <v>77.11</v>
       </c>
       <c r="K16" t="n">
-        <v>-21.99978176566327</v>
+        <v>1.51</v>
       </c>
       <c r="L16" t="n">
-        <v>-4.26237</v>
+        <v>1.94453</v>
       </c>
       <c r="M16" t="n">
-        <v>18805370.55291757</v>
+        <v>117882016</v>
       </c>
       <c r="N16" t="n">
-        <v>18805423.95177342</v>
+        <v>293532015</v>
       </c>
       <c r="O16" t="n">
-        <v>797.73</v>
+        <v>83.22</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>46036.48202546296</v>
+        <v>46276.58553240741</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.005785900018497227</v>
+        <v>0.005698672403551492</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>77.68000000000001</v>
+        <v>0.01306588</v>
       </c>
       <c r="F17" t="n">
-        <v>9153123057</v>
+        <v>9257577125</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>163351294</v>
+        <v>21935510</v>
       </c>
       <c r="I17" t="n">
-        <v>79.44</v>
+        <v>0.01345016</v>
       </c>
       <c r="J17" t="n">
-        <v>77.27</v>
+        <v>0.01191321</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.220355107256495</v>
+        <v>-0.00015046852519901</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.53926</v>
+        <v>-1.1385</v>
       </c>
       <c r="M17" t="n">
-        <v>117882016</v>
+        <v>709233558707.1311</v>
       </c>
       <c r="N17" t="n">
-        <v>293532015</v>
+        <v>1142408526965.963</v>
       </c>
       <c r="O17" t="n">
-        <v>83.22</v>
+        <v>0.01946402</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>46276.58553240741</v>
+        <v>46259.82847222222</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0056776587036631</v>
+        <v>0.005659251820378704</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>leo-token</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LEO Token</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>8.880000000000001</v>
+        <v>11.31</v>
       </c>
       <c r="F18" t="n">
-        <v>8163877232</v>
+        <v>8462869436</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>319807</v>
+        <v>441283863</v>
       </c>
       <c r="I18" t="n">
-        <v>8.91</v>
+        <v>11.32</v>
       </c>
       <c r="J18" t="n">
-        <v>8.73</v>
+        <v>10.62</v>
       </c>
       <c r="K18" t="n">
-        <v>0.11644</v>
+        <v>0.661099</v>
       </c>
       <c r="L18" t="n">
-        <v>1.32755</v>
+        <v>6.20719</v>
       </c>
       <c r="M18" t="n">
-        <v>919857851.9</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N18" t="n">
-        <v>985239504</v>
+        <v>1000000000</v>
       </c>
       <c r="O18" t="n">
-        <v>10.61</v>
+        <v>52.7</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>46146.39930555555</v>
+        <v>44325.67635416667</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005025301647329115</v>
+        <v>0.005142795816746102</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>leo-token</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>LEO Token</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>10.69</v>
+        <v>8.92</v>
       </c>
       <c r="F19" t="n">
-        <v>7986538864</v>
+        <v>8202960071</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>450558976</v>
+        <v>156127</v>
       </c>
       <c r="I19" t="n">
-        <v>11.38</v>
+        <v>9</v>
       </c>
       <c r="J19" t="n">
-        <v>10.68</v>
+        <v>8.83</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6460806364119609</v>
+        <v>0.04280543</v>
       </c>
       <c r="L19" t="n">
-        <v>-5.68476</v>
+        <v>0.48232</v>
       </c>
       <c r="M19" t="n">
-        <v>748099970.424884</v>
+        <v>919857851.9</v>
       </c>
       <c r="N19" t="n">
-        <v>1000000000</v>
+        <v>985239504</v>
       </c>
       <c r="O19" t="n">
-        <v>52.7</v>
+        <v>10.61</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>44325.67635416667</v>
+        <v>46146.39930555555</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004908356058275401</v>
+        <v>0.004973888740833076</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1745,31 +1745,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.191834</v>
+        <v>0.201196</v>
       </c>
       <c r="F20" t="n">
-        <v>7189370215</v>
+        <v>7544303914</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>466275840</v>
+        <v>438569875</v>
       </c>
       <c r="I20" t="n">
-        <v>0.204209</v>
+        <v>0.201745</v>
       </c>
       <c r="J20" t="n">
-        <v>0.191485</v>
+        <v>0.190464</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.01285599910683713</v>
+        <v>0.00979934</v>
       </c>
       <c r="L20" t="n">
-        <v>-6.26884</v>
+        <v>5.1199</v>
       </c>
       <c r="M20" t="n">
-        <v>37516725700.17653</v>
+        <v>37522923322.16203</v>
       </c>
       <c r="N20" t="n">
         <v>45000000000</v>
@@ -1781,19 +1781,19 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R20" t="b">
         <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004382664081497658</v>
+        <v>0.004545848429507704</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1812,31 +1812,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.174197</v>
+        <v>0.184749</v>
       </c>
       <c r="F21" t="n">
-        <v>6061365830</v>
+        <v>6432935996</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>350153192</v>
+        <v>253193320</v>
       </c>
       <c r="I21" t="n">
-        <v>0.193982</v>
+        <v>0.186542</v>
       </c>
       <c r="J21" t="n">
-        <v>0.173614</v>
+        <v>0.172569</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.02132487491538929</v>
+        <v>0.01109385</v>
       </c>
       <c r="L21" t="n">
-        <v>-10.8698</v>
+        <v>6.38843</v>
       </c>
       <c r="M21" t="n">
-        <v>34842263125.93008</v>
+        <v>34845006961.13458</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70148</v>
@@ -1848,19 +1848,19 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R21" t="b">
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.003638802847480899</v>
+        <v>0.003823604714692248</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1879,34 +1879,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.999165</v>
+        <v>0.999393</v>
       </c>
       <c r="F22" t="n">
-        <v>4727220083</v>
+        <v>4730616606</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>93356081</v>
+        <v>39878908</v>
       </c>
       <c r="I22" t="n">
-        <v>0.99937</v>
+        <v>0.999579</v>
       </c>
       <c r="J22" t="n">
-        <v>0.998924</v>
+        <v>0.998964</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.000318845787347533</v>
+        <v>0.00023556</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.02983</v>
+        <v>0.02358</v>
       </c>
       <c r="M22" t="n">
-        <v>4731366617.901646</v>
+        <v>4733546802.134655</v>
       </c>
       <c r="N22" t="n">
-        <v>4730392672.461645</v>
+        <v>4735546801.034656</v>
       </c>
       <c r="O22" t="n">
         <v>1.034</v>
@@ -1915,19 +1915,19 @@
         <v>46000.38208333333</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R22" t="b">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.002759001922131101</v>
+        <v>0.002717319874071196</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1946,34 +1946,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0.999919</v>
       </c>
       <c r="F23" t="n">
-        <v>4582463387</v>
+        <v>4585446425</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>315605485</v>
+        <v>344249986</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0.999623</v>
+        <v>0.999743</v>
       </c>
       <c r="K23" t="n">
-        <v>0.00011636</v>
+        <v>-0.000207849320602471</v>
       </c>
       <c r="L23" t="n">
-        <v>0.00776</v>
+        <v>-0.02078</v>
       </c>
       <c r="M23" t="n">
-        <v>4582364613.50938</v>
+        <v>4586319939.449437</v>
       </c>
       <c r="N23" t="n">
-        <v>4538186664.507218</v>
+        <v>4567710822.886193</v>
       </c>
       <c r="O23" t="n">
         <v>1.22</v>
@@ -1982,19 +1982,19 @@
         <v>43902.79363425926</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R23" t="b">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.002663542280350764</v>
+        <v>0.002622978253166253</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2013,34 +2013,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>217.59</v>
+        <v>227.71</v>
       </c>
       <c r="F24" t="n">
-        <v>4368271459</v>
+        <v>4574710821</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>138736543</v>
+        <v>162583254</v>
       </c>
       <c r="I24" t="n">
-        <v>223.76</v>
+        <v>227.22</v>
       </c>
       <c r="J24" t="n">
-        <v>213.37</v>
+        <v>214.03</v>
       </c>
       <c r="K24" t="n">
-        <v>-6.059388942349528</v>
+        <v>10.97</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.658</v>
+        <v>5.05925</v>
       </c>
       <c r="M24" t="n">
-        <v>20089853.02165077</v>
+        <v>20090593.64665077</v>
       </c>
       <c r="N24" t="n">
-        <v>20089940.52165077</v>
+        <v>20090631.14665077</v>
       </c>
       <c r="O24" t="n">
         <v>3785.82</v>
@@ -2049,622 +2049,622 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002522293652245025</v>
+        <v>0.002616001515410766</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>usd1-wlfi</t>
+          <t>uniswap</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>usd1</t>
+          <t>uni</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>USD1</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.999203</v>
+        <v>7.27</v>
       </c>
       <c r="F25" t="n">
-        <v>4342992938</v>
+        <v>4510962530</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>1107595320</v>
+        <v>1031082317</v>
       </c>
       <c r="I25" t="n">
-        <v>0.99947</v>
+        <v>7.23</v>
       </c>
       <c r="J25" t="n">
-        <v>0.999034</v>
+        <v>6.05</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.000215952711094203</v>
+        <v>1.14</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.02075</v>
+        <v>18.51215</v>
       </c>
       <c r="M25" t="n">
-        <v>4346607627.726874</v>
+        <v>621120422.6104751</v>
       </c>
       <c r="N25" t="n">
-        <v>4346607627.726874</v>
+        <v>888368418.9163101</v>
       </c>
       <c r="O25" t="n">
-        <v>1.048</v>
+        <v>44.92</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>46212.42696759259</v>
+        <v>44318.89240740741</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002505623759755929</v>
+        <v>0.002574573468263397</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>litecoin</t>
+          <t>usd1-wlfi</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ltc</t>
+          <t>usd1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>USD1</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>50.37</v>
+        <v>0.999027</v>
       </c>
       <c r="F26" t="n">
-        <v>3911524891</v>
+        <v>4342369348</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>253209054</v>
+        <v>1095614662</v>
       </c>
       <c r="I26" t="n">
-        <v>52.18</v>
+        <v>0.999374</v>
       </c>
       <c r="J26" t="n">
-        <v>50.37</v>
+        <v>0.998899</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.916235601012829</v>
+        <v>-0.000183543199977265</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.76849</v>
+        <v>-0.01837</v>
       </c>
       <c r="M26" t="n">
-        <v>77612279.40124893</v>
+        <v>4346607629.555521</v>
       </c>
       <c r="N26" t="n">
-        <v>77616385.66292557</v>
+        <v>4346607629.555521</v>
       </c>
       <c r="O26" t="n">
-        <v>410.26</v>
+        <v>1.048</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>44325.80077546297</v>
+        <v>46212.42696759259</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002221092637228226</v>
+        <v>0.002465009961806089</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>uniswap</t>
+          <t>litecoin</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>uni</t>
+          <t>ltc</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6.2</v>
+        <v>52.69</v>
       </c>
       <c r="F27" t="n">
-        <v>3856869904</v>
+        <v>4088774742</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>623546845</v>
+        <v>240686831</v>
       </c>
       <c r="I27" t="n">
-        <v>6.56</v>
+        <v>53.04</v>
       </c>
       <c r="J27" t="n">
-        <v>6.21</v>
+        <v>50.23</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.1916856986930116</v>
+        <v>2.43</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.88367</v>
+        <v>4.8292</v>
       </c>
       <c r="M27" t="n">
-        <v>623212423.7271129</v>
+        <v>77617035.66946276</v>
       </c>
       <c r="N27" t="n">
-        <v>890460420.0329479</v>
+        <v>77619816.92657901</v>
       </c>
       <c r="O27" t="n">
-        <v>44.92</v>
+        <v>410.26</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>44318.89240740741</v>
+        <v>44325.80077546297</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002185050466988799</v>
+        <v>0.002300206652903482</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>the-open-network</t>
+          <t>canton-network</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>gram</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Gram (prev. Toncoin)</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.31</v>
+        <v>0.100303</v>
       </c>
       <c r="F28" t="n">
-        <v>3653450637</v>
+        <v>3974102558</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>27111515</v>
+        <v>21161075</v>
       </c>
       <c r="I28" t="n">
-        <v>1.33</v>
+        <v>0.102749</v>
       </c>
       <c r="J28" t="n">
-        <v>1.31</v>
+        <v>0.08894199999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.03105510902163489</v>
+        <v>0.00987384</v>
       </c>
       <c r="L28" t="n">
-        <v>-2.27751</v>
+        <v>10.91892</v>
       </c>
       <c r="M28" t="n">
-        <v>2794750881.605409</v>
+        <v>39606318586.9813</v>
       </c>
       <c r="N28" t="n">
-        <v>5250123209.163897</v>
+        <v>39607203165.6683</v>
       </c>
       <c r="O28" t="n">
-        <v>8.25</v>
+        <v>0.194152</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>45457.69225694444</v>
+        <v>46056.00148148148</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002050905858168502</v>
+        <v>0.002225684739127884</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>canton-network</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.091306</v>
+        <v>2.87</v>
       </c>
       <c r="F29" t="n">
-        <v>3617437521</v>
+        <v>3744407634</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>8729948</v>
+        <v>884382460</v>
       </c>
       <c r="I29" t="n">
-        <v>0.094012</v>
+        <v>2.89</v>
       </c>
       <c r="J29" t="n">
-        <v>0.09014800000000001</v>
+        <v>2.43</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.002752256873662845</v>
+        <v>0.416577</v>
       </c>
       <c r="L29" t="n">
-        <v>-2.90075</v>
+        <v>16.97419</v>
       </c>
       <c r="M29" t="n">
-        <v>39601011841.82496</v>
+        <v>1306570064</v>
       </c>
       <c r="N29" t="n">
-        <v>39601011841.82496</v>
+        <v>1306570052</v>
       </c>
       <c r="O29" t="n">
-        <v>0.194152</v>
+        <v>20.44</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>46056.00148148148</v>
+        <v>44577.59010416667</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002027157048975222</v>
+        <v>0.002076413096049904</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>global-dollar</t>
+          <t>the-open-network</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>usdg</t>
+          <t>gram</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Global Dollar</t>
+          <t>Gram (prev. Toncoin)</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="F30" t="n">
-        <v>3282838433</v>
+        <v>3723196551</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>1103839469</v>
+        <v>37803025</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>1.34</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9998089999999999</v>
+        <v>1.29</v>
       </c>
       <c r="K30" t="n">
-        <v>5.409e-05</v>
+        <v>0.02461108</v>
       </c>
       <c r="L30" t="n">
-        <v>0.01099</v>
+        <v>1.88162</v>
       </c>
       <c r="M30" t="n">
-        <v>3282758930.547109</v>
+        <v>2795318240.360763</v>
       </c>
       <c r="N30" t="n">
-        <v>3282758930.547109</v>
+        <v>5250683882.598795</v>
       </c>
       <c r="O30" t="n">
-        <v>1.65</v>
+        <v>8.25</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>45686.67436342593</v>
+        <v>45457.69225694444</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.001806506053455766</v>
+        <v>0.002062628667749375</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>avalanche-2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>avax</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2.46</v>
+        <v>7.6</v>
       </c>
       <c r="F31" t="n">
-        <v>3213737490</v>
+        <v>3365564812</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>399257593</v>
+        <v>315743529</v>
       </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>7.62</v>
       </c>
       <c r="J31" t="n">
-        <v>2.3</v>
+        <v>7.18</v>
       </c>
       <c r="K31" t="n">
-        <v>0.088107</v>
+        <v>0.363565</v>
       </c>
       <c r="L31" t="n">
-        <v>3.82432</v>
+        <v>5.02368</v>
       </c>
       <c r="M31" t="n">
-        <v>1306460821</v>
+        <v>442854991.1362558</v>
       </c>
       <c r="N31" t="n">
-        <v>1306488202</v>
+        <v>469523691.2347694</v>
       </c>
       <c r="O31" t="n">
-        <v>20.44</v>
+        <v>144.96</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>44577.59010416667</v>
+        <v>44521.26314814815</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0.001760937513638696</v>
+        <v>0.001830214836534867</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>avalanche-2</t>
+          <t>hedera-hashgraph</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>avax</t>
+          <t>hbar</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Hedera</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>7.26</v>
+        <v>0.074882</v>
       </c>
       <c r="F32" t="n">
-        <v>3212309286</v>
+        <v>3277165955</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>276887586</v>
+        <v>83369773</v>
       </c>
       <c r="I32" t="n">
-        <v>7.53</v>
+        <v>0.075281</v>
       </c>
       <c r="J32" t="n">
-        <v>7.19</v>
+        <v>0.07199800000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.2650792157821398</v>
+        <v>0.0021675</v>
       </c>
       <c r="L32" t="n">
-        <v>-3.60054</v>
+        <v>2.98084</v>
       </c>
       <c r="M32" t="n">
-        <v>442839467.2032731</v>
+        <v>43831556055.85902</v>
       </c>
       <c r="N32" t="n">
-        <v>469508157.910476</v>
+        <v>50000000000</v>
       </c>
       <c r="O32" t="n">
-        <v>144.96</v>
+        <v>0.569229</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>44521.26314814815</v>
+        <v>44454.11143518519</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001759995686103276</v>
+        <v>0.001772767147222388</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>hedera-hashgraph</t>
+          <t>global-dollar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>hbar</t>
+          <t>usdg</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Hedera</t>
+          <t>Global Dollar</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.072974</v>
+        <v>0.999893</v>
       </c>
       <c r="F33" t="n">
-        <v>3196842944</v>
+        <v>3264423128</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>90080835</v>
+        <v>1221877042</v>
       </c>
       <c r="I33" t="n">
-        <v>0.078586</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>0.073006</v>
+        <v>0.999796</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.005635858701912577</v>
+        <v>-0.000157751230601577</v>
       </c>
       <c r="L33" t="n">
-        <v>-7.24699</v>
+        <v>-0.01577</v>
       </c>
       <c r="M33" t="n">
-        <v>43831556056.62752</v>
+        <v>3264764991.306926</v>
       </c>
       <c r="N33" t="n">
-        <v>50000000000</v>
+        <v>3264762512.446477</v>
       </c>
       <c r="O33" t="n">
-        <v>0.569229</v>
+        <v>1.65</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>44454.11143518519</v>
+        <v>45686.67436342593</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001749796424115615</v>
+        <v>0.001764485977178995</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2683,34 +2683,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4.78e-06</v>
+        <v>5.1e-06</v>
       </c>
       <c r="F34" t="n">
-        <v>2819044705</v>
+        <v>2998823174</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>89914815</v>
+        <v>91696970</v>
       </c>
       <c r="I34" t="n">
-        <v>5.16e-06</v>
+        <v>5.08e-06</v>
       </c>
       <c r="J34" t="n">
-        <v>4.79e-06</v>
+        <v>4.75e-06</v>
       </c>
       <c r="K34" t="n">
-        <v>-3.72696589079e-07</v>
+        <v>3.30119e-07</v>
       </c>
       <c r="L34" t="n">
-        <v>-7.17479</v>
+        <v>6.92423</v>
       </c>
       <c r="M34" t="n">
-        <v>589239215066517.9</v>
+        <v>589239162555937.8</v>
       </c>
       <c r="N34" t="n">
-        <v>589496238721205.9</v>
+        <v>589496186210625.8</v>
       </c>
       <c r="O34" t="n">
         <v>8.616e-05</v>
@@ -2719,19 +2719,19 @@
         <v>44496.82980324074</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R34" t="b">
         <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001500657796634217</v>
+        <v>0.001591880763077633</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.688042</v>
+        <v>0.730534</v>
       </c>
       <c r="F35" t="n">
-        <v>2815990283</v>
+        <v>2991065166</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>516267580</v>
+        <v>540010749</v>
       </c>
       <c r="I35" t="n">
-        <v>0.71071</v>
+        <v>0.729483</v>
       </c>
       <c r="J35" t="n">
-        <v>0.675641</v>
+        <v>0.678101</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.02100642298407862</v>
+        <v>0.04594057</v>
       </c>
       <c r="L35" t="n">
-        <v>-2.96068</v>
+        <v>6.71063</v>
       </c>
       <c r="M35" t="n">
         <v>4096537146.540959</v>
@@ -2786,354 +2786,354 @@
         <v>45661.62243055556</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001498643561451853</v>
+        <v>0.001586839073078545</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>paypal-usd</t>
+          <t>crypto-com-chain</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>pyusd</t>
+          <t>cro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PayPal USD</t>
+          <t>Cronos</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.999512</v>
+        <v>0.058095</v>
       </c>
       <c r="F36" t="n">
-        <v>2804921432</v>
+        <v>2888376470</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>100030070</v>
+        <v>9904469</v>
       </c>
       <c r="I36" t="n">
-        <v>0.999706</v>
+        <v>0.058871</v>
       </c>
       <c r="J36" t="n">
-        <v>0.999375</v>
+        <v>0.054783</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.000122881507387151</v>
+        <v>0.00273442</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.01195</v>
+        <v>4.93931</v>
       </c>
       <c r="M36" t="n">
-        <v>2806316064.287177</v>
+        <v>49726994055.42311</v>
       </c>
       <c r="N36" t="n">
-        <v>2806266063.289376</v>
+        <v>98927036947.05304</v>
       </c>
       <c r="O36" t="n">
-        <v>1.021</v>
+        <v>0.891544</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>45222.61454861111</v>
+        <v>44523.66666666666</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001491344220001148</v>
+        <v>0.001520104858362267</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>blackrock-usd-institutional-digital-liquidity-fund</t>
+          <t>paypal-usd</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>buidl</t>
+          <t>pyusd</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund</t>
+          <t>PayPal USD</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0.999484</v>
       </c>
       <c r="F37" t="n">
-        <v>2701488574</v>
+        <v>2812163218</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>126246032</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0.998742</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>-6.6882718195882e-05</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>-0.00669</v>
       </c>
       <c r="M37" t="n">
-        <v>2701488573.550449</v>
+        <v>2813570609.128083</v>
       </c>
       <c r="N37" t="n">
-        <v>2701488573.550449</v>
+        <v>2818512719.760797</v>
       </c>
       <c r="O37" t="n">
-        <v>1</v>
+        <v>1.021</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>45699.87511574074</v>
+        <v>45222.61454861111</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001423135537115788</v>
+        <v>0.00147057621771039</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>crypto-com-chain</t>
+          <t>tether-gold</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>cro</t>
+          <t>xaut</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cronos</t>
+          <t>Tether Gold</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.055498</v>
+        <v>4367.42</v>
       </c>
       <c r="F38" t="n">
-        <v>2694112592</v>
+        <v>2720856987</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
       </c>
       <c r="H38" t="n">
-        <v>8206200</v>
+        <v>366365385</v>
       </c>
       <c r="I38" t="n">
-        <v>0.057362</v>
+        <v>4372.55</v>
       </c>
       <c r="J38" t="n">
-        <v>0.05466</v>
+        <v>4242.72</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.001550860462855075</v>
+        <v>35.76</v>
       </c>
       <c r="L38" t="n">
-        <v>-2.65792</v>
+        <v>0.8255</v>
       </c>
       <c r="M38" t="n">
-        <v>48558313167.31941</v>
+        <v>622823.6595320001</v>
       </c>
       <c r="N38" t="n">
-        <v>98924974447.10681</v>
+        <v>707747.089</v>
       </c>
       <c r="O38" t="n">
-        <v>0.891544</v>
+        <v>5504.62</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>44523.66666666666</v>
+        <v>46050.66666666666</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R38" t="b">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001418271454009759</v>
+        <v>0.00141123911575237</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>tether-gold</t>
+          <t>blackrock-usd-institutional-digital-liquidity-fund</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>xaut</t>
+          <t>buidl</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tether Gold</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4323.31</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>2693520445</v>
+        <v>2651746553</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>167835192</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>4354.07</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>4274.94</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>26.07</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.53286</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>622823.6595320001</v>
+        <v>2651746553.070448</v>
       </c>
       <c r="N39" t="n">
-        <v>707747.089</v>
+        <v>2651746553.070449</v>
       </c>
       <c r="O39" t="n">
-        <v>5504.62</v>
+        <v>1</v>
       </c>
       <c r="P39" s="1" t="n">
-        <v>46050.66666666666</v>
+        <v>45699.87511574074</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001417880963330825</v>
+        <v>0.001366326377336731</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>hashnote-usyc</t>
+          <t>bittensor</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>usyc</t>
+          <t>tao</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Circle USYC</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1.14</v>
+        <v>227.62</v>
       </c>
       <c r="F40" t="n">
-        <v>2606216681</v>
+        <v>2579063424</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>172806682</v>
       </c>
       <c r="I40" t="n">
-        <v>1.14</v>
+        <v>228.93</v>
       </c>
       <c r="J40" t="n">
-        <v>1.14</v>
+        <v>214.05</v>
       </c>
       <c r="K40" t="n">
-        <v>0.00010164</v>
+        <v>12.7</v>
       </c>
       <c r="L40" t="n">
-        <v>0.00894</v>
+        <v>5.90712</v>
       </c>
       <c r="M40" t="n">
-        <v>2291321221.608375</v>
+        <v>11339645.9251</v>
       </c>
       <c r="N40" t="n">
-        <v>2246343166.601824</v>
+        <v>21000000</v>
       </c>
       <c r="O40" t="n">
-        <v>1.14</v>
+        <v>757.6</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>46281.53125</v>
+        <v>45358.44833333333</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001360308593500589</v>
+        <v>0.001319091854688425</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3152,34 +3152,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="F41" t="n">
-        <v>2531426802</v>
+        <v>2563032234</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
       </c>
       <c r="H41" t="n">
-        <v>627998</v>
+        <v>1702992</v>
       </c>
       <c r="I41" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="J41" t="n">
-        <v>1.091</v>
+        <v>1.1</v>
       </c>
       <c r="K41" t="n">
-        <v>0.01102276</v>
+        <v>0.01359534</v>
       </c>
       <c r="L41" t="n">
-        <v>1.04359</v>
+        <v>1.22081</v>
       </c>
       <c r="M41" t="n">
-        <v>2273447446.030578</v>
+        <v>2273802309.23221</v>
       </c>
       <c r="N41" t="n">
-        <v>5414837292.537803</v>
+        <v>5415192155.739435</v>
       </c>
       <c r="O41" t="n">
         <v>5.64</v>
@@ -3188,220 +3188,220 @@
         <v>46205.17638888889</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001310988491181214</v>
+        <v>0.001308673679005121</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>bittensor</t>
+          <t>hashnote-usyc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>tao</t>
+          <t>usyc</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>Circle USYC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>216</v>
+        <v>1.14</v>
       </c>
       <c r="F42" t="n">
-        <v>2447094677</v>
+        <v>2555275633</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
       </c>
       <c r="H42" t="n">
-        <v>183067847</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>226.84</v>
+        <v>1.14</v>
       </c>
       <c r="J42" t="n">
-        <v>213.51</v>
+        <v>1.14</v>
       </c>
       <c r="K42" t="n">
-        <v>-9.15093076012684</v>
+        <v>9.719e-05</v>
       </c>
       <c r="L42" t="n">
-        <v>-4.07487</v>
+        <v>0.008540000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>11339645.9251</v>
+        <v>2246343166.601824</v>
       </c>
       <c r="N42" t="n">
-        <v>21000000</v>
+        <v>2246365281.581388</v>
       </c>
       <c r="O42" t="n">
-        <v>757.6</v>
+        <v>1.14</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>45358.44833333333</v>
+        <v>46282.53148148148</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001255375765376291</v>
+        <v>0.001303632903371915</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ripple-usd</t>
+          <t>okb</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>rlusd</t>
+          <t>okb</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ripple USD</t>
+          <t>OKB</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>112.03</v>
       </c>
       <c r="F43" t="n">
-        <v>2347586666</v>
+        <v>2351966933</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>334483072</v>
+        <v>19050807</v>
       </c>
       <c r="I43" t="n">
-        <v>1.001</v>
+        <v>112.32</v>
       </c>
       <c r="J43" t="n">
-        <v>0.9996429999999999</v>
+        <v>108.66</v>
       </c>
       <c r="K43" t="n">
-        <v>0.00027881</v>
+        <v>2.83</v>
       </c>
       <c r="L43" t="n">
-        <v>0.0092</v>
+        <v>2.58897</v>
       </c>
       <c r="M43" t="n">
-        <v>2347466285.367542</v>
+        <v>21000000</v>
       </c>
       <c r="N43" t="n">
-        <v>2347467285.367542</v>
+        <v>21000000</v>
       </c>
       <c r="O43" t="n">
-        <v>1.073</v>
+        <v>228.74</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>45652.11518518518</v>
+        <v>45934.66666666666</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001189755318469063</v>
+        <v>0.001171508853033527</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>okb</t>
+          <t>ripple-usd</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>okb</t>
+          <t>rlusd</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>OKB</t>
+          <t>Ripple USD</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>109.54</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>2299970668</v>
+        <v>2344924147</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>20138692</v>
+        <v>344223044</v>
       </c>
       <c r="I44" t="n">
-        <v>111.78</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>108.53</v>
+        <v>0.999736</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.603623464937826</v>
+        <v>1.688e-05</v>
       </c>
       <c r="L44" t="n">
-        <v>-2.30475</v>
+        <v>0.00169</v>
       </c>
       <c r="M44" t="n">
-        <v>21000000</v>
+        <v>2344753285.367475</v>
       </c>
       <c r="N44" t="n">
-        <v>21000000</v>
+        <v>2345208787.367478</v>
       </c>
       <c r="O44" t="n">
-        <v>228.74</v>
+        <v>1.073</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>45934.66666666666</v>
+        <v>45652.11518518518</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001158355001677546</v>
+        <v>0.001166931963741596</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3423,13 +3423,13 @@
         <v>1.14</v>
       </c>
       <c r="F45" t="n">
-        <v>2234039229</v>
+        <v>2209305470</v>
       </c>
       <c r="G45" t="n">
         <v>44</v>
       </c>
       <c r="H45" t="n">
-        <v>4117977</v>
+        <v>3179687</v>
       </c>
       <c r="I45" t="n">
         <v>1.15</v>
@@ -3438,16 +3438,16 @@
         <v>1.14</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.001008384954372055</v>
+        <v>-0.002401500943753243</v>
       </c>
       <c r="L45" t="n">
-        <v>0.15997</v>
+        <v>-0.20949</v>
       </c>
       <c r="M45" t="n">
-        <v>1954712699.278615</v>
+        <v>1931966768.507879</v>
       </c>
       <c r="N45" t="n">
-        <v>1954713137.876704</v>
+        <v>1931966768.507879</v>
       </c>
       <c r="O45" t="n">
         <v>1.26</v>
@@ -3456,957 +3456,957 @@
         <v>45377.89175925926</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.00111487658773943</v>
+        <v>0.001078797570541632</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>aster-2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>aster</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.765609</v>
+        <v>0.738395</v>
       </c>
       <c r="F46" t="n">
-        <v>2074964727</v>
+        <v>1996127339</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>15877531</v>
+        <v>127611461</v>
       </c>
       <c r="I46" t="n">
-        <v>0.789172</v>
+        <v>0.74396</v>
       </c>
       <c r="J46" t="n">
-        <v>0.679488</v>
+        <v>0.672885</v>
       </c>
       <c r="K46" t="n">
-        <v>0.061745</v>
+        <v>0.060384</v>
       </c>
       <c r="L46" t="n">
-        <v>8.760260000000001</v>
+        <v>8.906090000000001</v>
       </c>
       <c r="M46" t="n">
-        <v>2708142280.000001</v>
+        <v>2704071066.799731</v>
       </c>
       <c r="N46" t="n">
-        <v>10000000000</v>
+        <v>7799908028.130118</v>
       </c>
       <c r="O46" t="n">
-        <v>0.789172</v>
+        <v>2.41</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>46281.50775462963</v>
+        <v>45924.13766203704</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R46" t="b">
         <v>1</v>
       </c>
       <c r="S46" t="n">
-        <v>0.001009975084756069</v>
+        <v>0.0009402596815516997</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>pax-gold</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>paxg</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>PAX Gold</t>
+          <t>Aave</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4331.13</v>
+        <v>125.7</v>
       </c>
       <c r="F47" t="n">
-        <v>1882287997</v>
+        <v>1939069708</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>167216327</v>
+        <v>303025650</v>
       </c>
       <c r="I47" t="n">
-        <v>4358.82</v>
+        <v>124.97</v>
       </c>
       <c r="J47" t="n">
-        <v>4278.77</v>
+        <v>113.33</v>
       </c>
       <c r="K47" t="n">
-        <v>32.52</v>
+        <v>9.1</v>
       </c>
       <c r="L47" t="n">
-        <v>0.68909</v>
+        <v>7.80158</v>
       </c>
       <c r="M47" t="n">
-        <v>434499.367539</v>
+        <v>15427787.0612566</v>
       </c>
       <c r="N47" t="n">
-        <v>434499.367539</v>
+        <v>16000000</v>
       </c>
       <c r="O47" t="n">
-        <v>5619.09</v>
+        <v>661.6900000000001</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>46050.93814814815</v>
+        <v>44334.55554398148</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0008829146299830021</v>
+        <v>0.0009031796878749257</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>aster-2</t>
+          <t>pax-gold</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>aster</t>
+          <t>paxg</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>PAX Gold</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.679137</v>
+        <v>4369.53</v>
       </c>
       <c r="F48" t="n">
-        <v>1833968107</v>
+        <v>1898790572</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>94782264</v>
+        <v>265197590</v>
       </c>
       <c r="I48" t="n">
-        <v>0.695809</v>
+        <v>4375.21</v>
       </c>
       <c r="J48" t="n">
-        <v>0.6623250000000001</v>
+        <v>4246.28</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.01434930831923498</v>
+        <v>31.42</v>
       </c>
       <c r="L48" t="n">
-        <v>-2.07165</v>
+        <v>0.72435</v>
       </c>
       <c r="M48" t="n">
-        <v>2704071066.799731</v>
+        <v>434499.367539</v>
       </c>
       <c r="N48" t="n">
-        <v>7803968119.651995</v>
+        <v>434499.367539</v>
       </c>
       <c r="O48" t="n">
-        <v>2.41</v>
+        <v>5619.09</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>45924.13766203704</v>
+        <v>46050.93814814815</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0008510501323968921</v>
+        <v>0.0008770035203402813</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>world-liberty-financial</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>wlfi</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>World Liberty Financial</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.056921</v>
+        <v>0.00404275</v>
       </c>
       <c r="F49" t="n">
-        <v>1807603208</v>
+        <v>1892522088</v>
       </c>
       <c r="G49" t="n">
         <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>32654435</v>
+        <v>204354174</v>
       </c>
       <c r="I49" t="n">
-        <v>0.057554</v>
+        <v>0.0040652</v>
       </c>
       <c r="J49" t="n">
-        <v>0.056071</v>
+        <v>0.00357329</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.000205578363537087</v>
+        <v>0.00043942</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.30227</v>
+        <v>12.19483</v>
       </c>
       <c r="M49" t="n">
-        <v>31777370298</v>
+        <v>468029630136.9791</v>
       </c>
       <c r="N49" t="n">
-        <v>100000000000</v>
+        <v>833533630174.015</v>
       </c>
       <c r="O49" t="n">
-        <v>0.331336</v>
+        <v>0.00881908</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>45901.18065972222</v>
+        <v>45914.36296296296</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0008336638291469564</v>
+        <v>0.0008729298260243893</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>mantle</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>mnt</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Aave</t>
+          <t>Mantle</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>117.04</v>
+        <v>0.566157</v>
       </c>
       <c r="F50" t="n">
-        <v>1803872610</v>
+        <v>1869179216</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>258050196</v>
+        <v>30598666</v>
       </c>
       <c r="I50" t="n">
-        <v>127.12</v>
+        <v>0.56815</v>
       </c>
       <c r="J50" t="n">
-        <v>116.96</v>
+        <v>0.539739</v>
       </c>
       <c r="K50" t="n">
-        <v>-10.12713674677889</v>
+        <v>0.02107673</v>
       </c>
       <c r="L50" t="n">
-        <v>-7.94872</v>
+        <v>3.86672</v>
       </c>
       <c r="M50" t="n">
-        <v>15427760.79998905</v>
+        <v>3302294382.53684</v>
       </c>
       <c r="N50" t="n">
-        <v>16000000</v>
+        <v>6219316794.889999</v>
       </c>
       <c r="O50" t="n">
-        <v>661.6900000000001</v>
+        <v>2.86</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>44334.55554398148</v>
+        <v>45938.71164351852</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0008312036904552965</v>
+        <v>0.0008577600138364675</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>mantle</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>mnt</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mantle</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.545925</v>
+        <v>0.680604</v>
       </c>
       <c r="F51" t="n">
-        <v>1802664518</v>
+        <v>1839698066</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>22538349</v>
+        <v>7929620</v>
       </c>
       <c r="I51" t="n">
-        <v>0.552142</v>
+        <v>0.772931</v>
       </c>
       <c r="J51" t="n">
-        <v>0.537594</v>
+        <v>0.6681009999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.006649308129468623</v>
+        <v>-0.08474640409757295</v>
       </c>
       <c r="L51" t="n">
-        <v>-1.13588</v>
+        <v>-11.07289</v>
       </c>
       <c r="M51" t="n">
-        <v>3302294382.53684</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N51" t="n">
-        <v>6219316794.889999</v>
+        <v>10000000000</v>
       </c>
       <c r="O51" t="n">
-        <v>2.86</v>
+        <v>0.789172</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>45938.71164351852</v>
+        <v>46281.50775462963</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0008304070155328619</v>
+        <v>0.0008386011241940983</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>world-liberty-financial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>wlfi</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.0036242</v>
+        <v>0.05792</v>
       </c>
       <c r="F52" t="n">
-        <v>1693844208</v>
+        <v>1840656511</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>149774810</v>
+        <v>32604826</v>
       </c>
       <c r="I52" t="n">
-        <v>0.00367103</v>
+        <v>0.0594</v>
       </c>
       <c r="J52" t="n">
-        <v>0.0034046</v>
+        <v>0.056783</v>
       </c>
       <c r="K52" t="n">
-        <v>3.511e-05</v>
+        <v>0.00108228</v>
       </c>
       <c r="L52" t="n">
-        <v>1.04017</v>
+        <v>1.90417</v>
       </c>
       <c r="M52" t="n">
-        <v>468254258147.3779</v>
+        <v>31777382106</v>
       </c>
       <c r="N52" t="n">
-        <v>833746661504.1492</v>
+        <v>100000000000</v>
       </c>
       <c r="O52" t="n">
-        <v>0.00881908</v>
+        <v>0.331336</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>45914.36296296296</v>
+        <v>45901.18065972222</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R52" t="b">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0007586455834328562</v>
+        <v>0.0008392239880234699</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>polkadot</t>
+          <t>ondo-finance</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>dot</t>
+          <t>ondo</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Ondo</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.974857</v>
+        <v>0.37134</v>
       </c>
       <c r="F53" t="n">
-        <v>1658632157</v>
+        <v>1806733356</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>172781669</v>
+        <v>208226419</v>
       </c>
       <c r="I53" t="n">
-        <v>0.991195</v>
+        <v>0.372151</v>
       </c>
       <c r="J53" t="n">
-        <v>0.937387</v>
+        <v>0.327035</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.01264061151858564</v>
+        <v>0.04377661</v>
       </c>
       <c r="L53" t="n">
-        <v>-1.3444</v>
+        <v>13.36432</v>
       </c>
       <c r="M53" t="n">
-        <v>1703027693.562892</v>
+        <v>4869330647</v>
       </c>
       <c r="N53" t="n">
-        <v>1703041183.197886</v>
+        <v>10000000000</v>
       </c>
       <c r="O53" t="n">
-        <v>54.98</v>
+        <v>2.14</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>44504.25704861111</v>
+        <v>45641.69166666667</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0007354250356606762</v>
+        <v>0.0008171783764049956</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ondo-finance</t>
+          <t>polkadot</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ondo</t>
+          <t>dot</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Ondo</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.328726</v>
+        <v>1.038</v>
       </c>
       <c r="F54" t="n">
-        <v>1600661449</v>
+        <v>1769036897</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>134573756</v>
+        <v>249066985</v>
       </c>
       <c r="I54" t="n">
-        <v>0.346461</v>
+        <v>1.041</v>
       </c>
       <c r="J54" t="n">
-        <v>0.323088</v>
+        <v>0.968247</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.01760857147179312</v>
+        <v>0.070989</v>
       </c>
       <c r="L54" t="n">
-        <v>-5.04144</v>
+        <v>7.33821</v>
       </c>
       <c r="M54" t="n">
-        <v>4869330647</v>
+        <v>1703175769.0622</v>
       </c>
       <c r="N54" t="n">
-        <v>10000000000</v>
+        <v>1703195639.199992</v>
       </c>
       <c r="O54" t="n">
-        <v>2.14</v>
+        <v>54.98</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>45641.69166666667</v>
+        <v>44504.25704861111</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R54" t="b">
         <v>1</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0006971963169046713</v>
+        <v>0.0007926806109552388</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>ethena</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>ena</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>USDD</t>
+          <t>Ethena</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.998667</v>
+        <v>0.152906</v>
       </c>
       <c r="F55" t="n">
-        <v>1510476486</v>
+        <v>1542817824</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>3599737</v>
+        <v>415066681</v>
       </c>
       <c r="I55" t="n">
-        <v>0.999115</v>
+        <v>0.154895</v>
       </c>
       <c r="J55" t="n">
-        <v>0.998204</v>
+        <v>0.140985</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.000243772364906358</v>
+        <v>0.008657750000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>-0.07045</v>
+        <v>6.00198</v>
       </c>
       <c r="M55" t="n">
-        <v>1512683787</v>
+        <v>10095312500</v>
       </c>
       <c r="N55" t="n">
-        <v>1514683059</v>
+        <v>15000000000</v>
       </c>
       <c r="O55" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>46212.39942129629</v>
+        <v>45393.21892361111</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0006377239436062859</v>
+        <v>0.0006456678161827802</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>htx-dao</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>htx</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>HTX DAO</t>
+          <t>USDD</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1.66e-06</v>
+        <v>0.998041</v>
       </c>
       <c r="F56" t="n">
-        <v>1491562831</v>
+        <v>1522673691</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>13864357</v>
+        <v>3812072</v>
       </c>
       <c r="I56" t="n">
-        <v>1.69e-06</v>
+        <v>0.998827</v>
       </c>
       <c r="J56" t="n">
-        <v>1.65e-06</v>
+        <v>0.998</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.7396874213e-08</v>
+        <v>-0.000455181043583108</v>
       </c>
       <c r="L56" t="n">
-        <v>-1.65791</v>
+        <v>-0.04559</v>
       </c>
       <c r="M56" t="n">
-        <v>898232728634017.2</v>
+        <v>1525678971</v>
       </c>
       <c r="N56" t="n">
-        <v>898232728634017.2</v>
+        <v>1532416904</v>
       </c>
       <c r="O56" t="n">
-        <v>3.75e-06</v>
+        <v>1.24</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>45629.67800925926</v>
+        <v>46212.39942129629</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R56" t="b">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0006252513549043658</v>
+        <v>0.0006325767657628268</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ethena</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ena</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Ethena</t>
+          <t>Morpho</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.145504</v>
+        <v>2.18</v>
       </c>
       <c r="F57" t="n">
-        <v>1464719993</v>
+        <v>1519592899</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>357939471</v>
+        <v>28306439</v>
       </c>
       <c r="I57" t="n">
-        <v>0.147265</v>
+        <v>2.18</v>
       </c>
       <c r="J57" t="n">
-        <v>0.135956</v>
+        <v>2.04</v>
       </c>
       <c r="K57" t="n">
-        <v>0.00228853</v>
+        <v>0.088154</v>
       </c>
       <c r="L57" t="n">
-        <v>1.4782</v>
+        <v>4.22391</v>
       </c>
       <c r="M57" t="n">
-        <v>10095312500</v>
+        <v>698762865.4973865</v>
       </c>
       <c r="N57" t="n">
-        <v>15000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="O57" t="n">
-        <v>1.52</v>
+        <v>4.17</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>45393.21892361111</v>
+        <v>45674.19883101852</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R57" t="b">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0006075498753137595</v>
+        <v>0.0006305746541104966</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Morpho</t>
+          <t>Pepe</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2.1</v>
+        <v>3.6e-06</v>
       </c>
       <c r="F58" t="n">
-        <v>1444714709</v>
+        <v>1510642948</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>20211623</v>
+        <v>241445300</v>
       </c>
       <c r="I58" t="n">
-        <v>2.16</v>
+        <v>3.56e-06</v>
       </c>
       <c r="J58" t="n">
-        <v>2.06</v>
+        <v>3.29e-06</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.0329807614339539</v>
+        <v>2.70054e-07</v>
       </c>
       <c r="L58" t="n">
-        <v>-1.55208</v>
+        <v>8.12138</v>
       </c>
       <c r="M58" t="n">
-        <v>689193692.0482025</v>
+        <v>420690000000000</v>
       </c>
       <c r="N58" t="n">
-        <v>1000000000</v>
+        <v>420690000000000</v>
       </c>
       <c r="O58" t="n">
-        <v>4.17</v>
+        <v>2.803e-05</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>45674.19883101852</v>
+        <v>45635.35457175926</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0005943574130849042</v>
+        <v>0.0006247583571372234</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>htx-dao</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>htx</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Pepe</t>
+          <t>HTX DAO</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3.34e-06</v>
+        <v>1.67e-06</v>
       </c>
       <c r="F59" t="n">
-        <v>1403578214</v>
+        <v>1499397010</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>227287742</v>
+        <v>11595933</v>
       </c>
       <c r="I59" t="n">
-        <v>3.45e-06</v>
+        <v>1.68e-06</v>
       </c>
       <c r="J59" t="n">
-        <v>3.28e-06</v>
+        <v>1.65e-06</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.02294976604e-07</v>
+        <v>8.452e-09</v>
       </c>
       <c r="L59" t="n">
-        <v>-2.91505</v>
+        <v>0.50884</v>
       </c>
       <c r="M59" t="n">
-        <v>420690000000000</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="N59" t="n">
-        <v>420690000000000</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="O59" t="n">
-        <v>2.803e-05</v>
+        <v>3.75e-06</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>45635.35457175926</v>
+        <v>45629.67800925926</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R59" t="b">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0005672299973223988</v>
+        <v>0.0006174499690632532</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4425,34 +4425,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="F60" t="n">
-        <v>1382482369</v>
+        <v>1416789101</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>46496852</v>
+        <v>35975123</v>
       </c>
       <c r="I60" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J60" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.07423048861210324</v>
+        <v>0.073019</v>
       </c>
       <c r="L60" t="n">
-        <v>-2.8557</v>
+        <v>2.95352</v>
       </c>
       <c r="M60" t="n">
-        <v>556864813.9605618</v>
+        <v>556876586.3612336</v>
       </c>
       <c r="N60" t="n">
-        <v>556870388.8185315</v>
+        <v>556898366.3095052</v>
       </c>
       <c r="O60" t="n">
         <v>700.65</v>
@@ -4461,86 +4461,86 @@
         <v>44326.33741898148</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0005533183658580173</v>
+        <v>0.0005637656381562879</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>united-stables</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>United Stables</t>
+          <t>Sky</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.99959</v>
+        <v>0.059549</v>
       </c>
       <c r="F61" t="n">
-        <v>1377510242</v>
+        <v>1396218627</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>225841873</v>
+        <v>25029323</v>
       </c>
       <c r="I61" t="n">
-        <v>0.999798</v>
+        <v>0.059461</v>
       </c>
       <c r="J61" t="n">
-        <v>0.999166</v>
+        <v>0.055601</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.000154769200326643</v>
+        <v>0.0023684</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.01442</v>
+        <v>4.14196</v>
       </c>
       <c r="M61" t="n">
-        <v>1378129007.8</v>
+        <v>23422355874.89505</v>
       </c>
       <c r="N61" t="n">
-        <v>1378129007.8</v>
+        <v>23459804203.60596</v>
       </c>
       <c r="O61" t="n">
-        <v>1.008</v>
+        <v>0.100535</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>46058.54591435185</v>
+        <v>45630.09302083333</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0005500395022515535</v>
+        <v>0.0005503975218766574</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4559,34 +4559,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>1.001</v>
       </c>
       <c r="F62" t="n">
-        <v>1376853385</v>
+        <v>1382453846</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>29199129</v>
+        <v>44979784</v>
       </c>
       <c r="I62" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="J62" t="n">
         <v>1</v>
       </c>
-      <c r="J62" t="n">
-        <v>0.99992</v>
-      </c>
       <c r="K62" t="n">
-        <v>-8.0981112964729e-05</v>
+        <v>0.0004182</v>
       </c>
       <c r="L62" t="n">
-        <v>0.009379999999999999</v>
+        <v>0.04182</v>
       </c>
       <c r="M62" t="n">
-        <v>1376792098.16</v>
+        <v>1381786099.16</v>
       </c>
       <c r="N62" t="n">
-        <v>1376792098.16</v>
+        <v>1381786099.16</v>
       </c>
       <c r="O62" t="n">
         <v>1.002</v>
@@ -4595,153 +4595,153 @@
         <v>46092.00303240741</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005496063386352679</v>
+        <v>0.0005414522154645813</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>spiko-amundi-overnight-swap-fund-eur</t>
+          <t>united-stables</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>eursafo</t>
+          <t>u</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Spiko Amundi Overnight Swap Fund (EUR)</t>
+          <t>United Stables</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1.17</v>
+        <v>0.999395</v>
       </c>
       <c r="F63" t="n">
-        <v>1376168930</v>
+        <v>1379395979</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>226543219</v>
       </c>
       <c r="I63" t="n">
-        <v>1.17</v>
+        <v>0.99981</v>
       </c>
       <c r="J63" t="n">
-        <v>1.17</v>
+        <v>0.999273</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.001659150911115903</v>
+        <v>-0.00020392443719397</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.14188</v>
+        <v>-0.0204</v>
       </c>
       <c r="M63" t="n">
-        <v>1178470806.74904</v>
+        <v>1380129007.8</v>
       </c>
       <c r="N63" t="n">
-        <v>1178470806.74904</v>
+        <v>1381129007.8</v>
       </c>
       <c r="O63" t="n">
-        <v>1.18</v>
+        <v>1.008</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>46255.48263888889</v>
+        <v>46058.54591435185</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.000549154975548653</v>
+        <v>0.0005394650020623211</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>spiko-amundi-overnight-swap-fund-eur</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>eursafo</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sky</t>
+          <t>Spiko Amundi Overnight Swap Fund (EUR)</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.057334</v>
+        <v>1.16</v>
       </c>
       <c r="F64" t="n">
-        <v>1342806546</v>
+        <v>1374291233</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>10993284</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>0.06300699999999999</v>
+        <v>1.17</v>
       </c>
       <c r="J64" t="n">
-        <v>0.057434</v>
+        <v>1.16</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.004148728338795607</v>
+        <v>-0.003745298799760377</v>
       </c>
       <c r="L64" t="n">
-        <v>-6.78372</v>
+        <v>-0.32071</v>
       </c>
       <c r="M64" t="n">
-        <v>23424420947.147</v>
+        <v>1180601693.72564</v>
       </c>
       <c r="N64" t="n">
-        <v>23459804203.60596</v>
+        <v>1180601693.72564</v>
       </c>
       <c r="O64" t="n">
-        <v>0.100535</v>
+        <v>1.18</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>45630.09302083333</v>
+        <v>46255.48263888889</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0005271541886173318</v>
+        <v>0.0005361475851614768</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4760,34 +4760,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.9957589999999999</v>
+        <v>0.995373</v>
       </c>
       <c r="F65" t="n">
-        <v>1339091149</v>
+        <v>1370746760</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>460881</v>
+        <v>515735</v>
       </c>
       <c r="I65" t="n">
-        <v>0.996406</v>
+        <v>0.995996</v>
       </c>
       <c r="J65" t="n">
-        <v>0.995601</v>
+        <v>0.994539</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.000431174357211184</v>
+        <v>-0.000409648525748874</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.0372</v>
+        <v>-0.04114</v>
       </c>
       <c r="M65" t="n">
-        <v>1344884513.993609</v>
+        <v>1377036984.967512</v>
       </c>
       <c r="N65" t="n">
-        <v>1344884513.993609</v>
+        <v>1377036984.967512</v>
       </c>
       <c r="O65" t="n">
         <v>1.075</v>
@@ -4796,488 +4796,488 @@
         <v>45785.55951388889</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0005247040742081735</v>
+        <v>0.0005338441415357241</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>bitget-token</t>
+          <t>worldcoin-wld</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>bgb</t>
+          <t>wld</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Bitget Token</t>
+          <t>Worldcoin</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1.9</v>
+        <v>0.379331</v>
       </c>
       <c r="F66" t="n">
-        <v>1332577327</v>
+        <v>1363343419</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
       </c>
       <c r="H66" t="n">
-        <v>13392614</v>
+        <v>244255382</v>
       </c>
       <c r="I66" t="n">
-        <v>1.93</v>
+        <v>0.380943</v>
       </c>
       <c r="J66" t="n">
-        <v>1.86</v>
+        <v>0.356458</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.02025327828207968</v>
+        <v>0.01649123</v>
       </c>
       <c r="L66" t="n">
-        <v>-0.97004</v>
+        <v>4.54505</v>
       </c>
       <c r="M66" t="n">
-        <v>699992029.6481038</v>
+        <v>3597195132.800737</v>
       </c>
       <c r="N66" t="n">
-        <v>910920874.6481038</v>
+        <v>10000000000</v>
       </c>
       <c r="O66" t="n">
-        <v>8.449999999999999</v>
+        <v>11.74</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>45653.15375</v>
+        <v>45360.67409722223</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0005204085415528767</v>
+        <v>0.0005290329386754617</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>bitget-token</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>bgb</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>BFUSD</t>
+          <t>Bitget Token</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9993570000000001</v>
+        <v>1.91</v>
       </c>
       <c r="F67" t="n">
-        <v>1318973778</v>
+        <v>1338041857</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
       </c>
       <c r="H67" t="n">
-        <v>1518246</v>
+        <v>10756738</v>
       </c>
       <c r="I67" t="n">
-        <v>0.999513</v>
+        <v>1.92</v>
       </c>
       <c r="J67" t="n">
-        <v>0.999119</v>
+        <v>1.88</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.000116076332385417</v>
+        <v>0.008219189999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>-0.01124</v>
+        <v>0.43179</v>
       </c>
       <c r="M67" t="n">
-        <v>1320000000</v>
+        <v>699992029.6481038</v>
       </c>
       <c r="N67" t="n">
-        <v>1320000000</v>
+        <v>910920874.6481038</v>
       </c>
       <c r="O67" t="n">
-        <v>1.007</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>45940.56990740741</v>
+        <v>45653.15375</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0005114376963321398</v>
+        <v>0.0005125902342986798</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>worldcoin-wld</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>wld</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Worldcoin</t>
+          <t>BFUSD</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.365299</v>
+        <v>0.9990250000000001</v>
       </c>
       <c r="F68" t="n">
-        <v>1311688082</v>
+        <v>1318696189</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>153619759</v>
+        <v>1777162</v>
       </c>
       <c r="I68" t="n">
-        <v>0.376268</v>
+        <v>0.999493</v>
       </c>
       <c r="J68" t="n">
-        <v>0.356093</v>
+        <v>0.998989</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.01090622315875917</v>
+        <v>-0.000245648644366159</v>
       </c>
       <c r="L68" t="n">
-        <v>-2.86525</v>
+        <v>-0.02458</v>
       </c>
       <c r="M68" t="n">
-        <v>3595707955.148494</v>
+        <v>1320000000</v>
       </c>
       <c r="N68" t="n">
-        <v>10000000000</v>
+        <v>1320000000</v>
       </c>
       <c r="O68" t="n">
-        <v>11.74</v>
+        <v>1.007</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>45360.67409722223</v>
+        <v>45940.56990740741</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.000506633152228146</v>
+        <v>0.0005000180816428331</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ethereum-classic</t>
+          <t>lighter</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>lit</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ethereum Classic</t>
+          <t>Lighter</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>7.18</v>
+        <v>4.89</v>
       </c>
       <c r="F69" t="n">
-        <v>1133907018</v>
+        <v>1221441356</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>46650779</v>
+        <v>111076432</v>
       </c>
       <c r="I69" t="n">
-        <v>7.45</v>
+        <v>5.03</v>
       </c>
       <c r="J69" t="n">
-        <v>7.11</v>
+        <v>4.2</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.20766814353341</v>
+        <v>0.689974</v>
       </c>
       <c r="L69" t="n">
-        <v>-2.87563</v>
+        <v>16.44272</v>
       </c>
       <c r="M69" t="n">
-        <v>158185641.5337251</v>
+        <v>250000000</v>
       </c>
       <c r="N69" t="n">
-        <v>158186024.4073251</v>
+        <v>1000000000</v>
       </c>
       <c r="O69" t="n">
-        <v>167.09</v>
+        <v>7.86</v>
       </c>
       <c r="P69" s="1" t="n">
-        <v>44322.44053240741</v>
+        <v>46021.04538194444</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0003893956277908165</v>
+        <v>0.0004368151668096583</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>venice-token</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>arb</t>
+          <t>vvv</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Arbitrum</t>
+          <t>Venice Token</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.165277</v>
+        <v>25.17</v>
       </c>
       <c r="F70" t="n">
-        <v>1102969954</v>
+        <v>1208891980</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>650336297</v>
+        <v>66657622</v>
       </c>
       <c r="I70" t="n">
-        <v>0.172852</v>
+        <v>25.52</v>
       </c>
       <c r="J70" t="n">
-        <v>0.137254</v>
+        <v>21.91</v>
       </c>
       <c r="K70" t="n">
-        <v>0.02526612</v>
+        <v>2.78</v>
       </c>
       <c r="L70" t="n">
-        <v>18.2524</v>
+        <v>12.40954</v>
       </c>
       <c r="M70" t="n">
-        <v>6678075931</v>
+        <v>48019756.90750279</v>
       </c>
       <c r="N70" t="n">
-        <v>10000000000</v>
+        <v>80994962.03776868</v>
       </c>
       <c r="O70" t="n">
-        <v>2.39</v>
+        <v>29.19</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>45303.18748842592</v>
+        <v>46274.32083333333</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R70" t="b">
         <v>1</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0003689942154293784</v>
+        <v>0.0004286597146015661</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>venice-token</t>
+          <t>ethereum-classic</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>vvv</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Venice Token</t>
+          <t>Ethereum Classic</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>22.61</v>
+        <v>7.39</v>
       </c>
       <c r="F71" t="n">
-        <v>1083491058</v>
+        <v>1167747533</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>43193731</v>
+        <v>53759258</v>
       </c>
       <c r="I71" t="n">
-        <v>23.14</v>
+        <v>7.46</v>
       </c>
       <c r="J71" t="n">
-        <v>21.2</v>
+        <v>7.09</v>
       </c>
       <c r="K71" t="n">
-        <v>0.357533</v>
+        <v>0.252723</v>
       </c>
       <c r="L71" t="n">
-        <v>1.59864</v>
+        <v>3.53998</v>
       </c>
       <c r="M71" t="n">
-        <v>48003455.9200405</v>
+        <v>158196100.6131674</v>
       </c>
       <c r="N71" t="n">
-        <v>81021132.76533473</v>
+        <v>158196503.4035674</v>
       </c>
       <c r="O71" t="n">
-        <v>29.19</v>
+        <v>167.09</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>46274.32083333333</v>
+        <v>44322.44053240741</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R71" t="b">
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0003561488791802253</v>
+        <v>0.0004019212081501791</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>lighter</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>lit</t>
+          <t>arb</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Lighter</t>
+          <t>Arbitrum</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4.23</v>
+        <v>0.163462</v>
       </c>
       <c r="F72" t="n">
-        <v>1055579082</v>
+        <v>1109381474</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>96637961</v>
+        <v>411987225</v>
       </c>
       <c r="I72" t="n">
-        <v>4.34</v>
+        <v>0.173113</v>
       </c>
       <c r="J72" t="n">
-        <v>4.01</v>
+        <v>0.154982</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.07017384741305221</v>
+        <v>-0.000614510887292863</v>
       </c>
       <c r="L72" t="n">
-        <v>-1.61376</v>
+        <v>-0.37453</v>
       </c>
       <c r="M72" t="n">
-        <v>250000000</v>
+        <v>6785574605</v>
       </c>
       <c r="N72" t="n">
-        <v>1000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O72" t="n">
-        <v>7.86</v>
+        <v>2.39</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>46021.04538194444</v>
+        <v>45303.18748842592</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0003377423577275572</v>
+        <v>0.0003639909074922668</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5296,34 +5296,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.09250899999999999</v>
+        <v>0.097736</v>
       </c>
       <c r="F73" t="n">
-        <v>991192671</v>
+        <v>1046007483</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>107112474</v>
+        <v>91697989</v>
       </c>
       <c r="I73" t="n">
-        <v>0.09823900000000001</v>
+        <v>0.09819600000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>0.090587</v>
+        <v>0.09082999999999999</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.004415757777720158</v>
+        <v>0.00574446</v>
       </c>
       <c r="L73" t="n">
-        <v>-4.61361</v>
+        <v>6.24455</v>
       </c>
       <c r="M73" t="n">
-        <v>10715266597.60465</v>
+        <v>10715847841.42047</v>
       </c>
       <c r="N73" t="n">
-        <v>10715266597.60465</v>
+        <v>10715847841.42047</v>
       </c>
       <c r="O73" t="n">
         <v>1.29</v>
@@ -5332,421 +5332,421 @@
         <v>45364.45493055556</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R73" t="b">
         <v>1</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0002952828107814076</v>
+        <v>0.00032280610636458</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>blockchain-capital</t>
+          <t>gatechain-token</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>bcap</t>
+          <t>gt</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Blockchain Capital</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106.54</v>
+        <v>9.35</v>
       </c>
       <c r="F74" t="n">
-        <v>970804306</v>
+        <v>997312993</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>3575734</v>
       </c>
       <c r="I74" t="n">
-        <v>106.54</v>
+        <v>9.41</v>
       </c>
       <c r="J74" t="n">
-        <v>106.54</v>
+        <v>9.01</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>0.330257</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>3.66004</v>
       </c>
       <c r="M74" t="n">
-        <v>9112111</v>
+        <v>106631229.6668511</v>
       </c>
       <c r="N74" t="n">
-        <v>9112111</v>
+        <v>118882512.0959876</v>
       </c>
       <c r="O74" t="n">
-        <v>106.54</v>
+        <v>25.38</v>
       </c>
       <c r="P74" s="1" t="n">
-        <v>46280.14583333334</v>
+        <v>45682.66666666666</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R74" t="b">
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0002818377262142194</v>
+        <v>0.000291161059950127</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>gatechain-token</t>
+          <t>blockchain-capital</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>gt</t>
+          <t>bcap</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Blockchain Capital</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>9.029999999999999</v>
+        <v>106.54</v>
       </c>
       <c r="F75" t="n">
-        <v>964005510</v>
+        <v>970804306</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
       </c>
       <c r="H75" t="n">
-        <v>3857894</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>9.17</v>
+        <v>106.54</v>
       </c>
       <c r="J75" t="n">
-        <v>8.970000000000001</v>
+        <v>106.54</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.1091559648858578</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>-1.13057</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>106630069.9300583</v>
+        <v>9112111</v>
       </c>
       <c r="N75" t="n">
-        <v>118881346.4290974</v>
+        <v>9112111</v>
       </c>
       <c r="O75" t="n">
-        <v>25.38</v>
+        <v>106.54</v>
       </c>
       <c r="P75" s="1" t="n">
-        <v>45682.66666666666</v>
+        <v>46280.14583333334</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R75" t="b">
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0002773542677723551</v>
+        <v>0.0002739338822858531</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>just</t>
+          <t>kucoin-shares</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>jst</t>
+          <t>kcs</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>JUST</t>
+          <t>KuCoin</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.115864</v>
+        <v>7.02</v>
       </c>
       <c r="F76" t="n">
-        <v>947734118</v>
+        <v>963335093</v>
       </c>
       <c r="G76" t="n">
         <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>17124734</v>
+        <v>67520676</v>
       </c>
       <c r="I76" t="n">
-        <v>0.116574</v>
+        <v>7.03</v>
       </c>
       <c r="J76" t="n">
-        <v>0.113158</v>
+        <v>6.71</v>
       </c>
       <c r="K76" t="n">
-        <v>0.00020579</v>
+        <v>0.243767</v>
       </c>
       <c r="L76" t="n">
-        <v>0.19438</v>
+        <v>3.5954</v>
       </c>
       <c r="M76" t="n">
-        <v>8188743036.341737</v>
+        <v>137155021.2773955</v>
       </c>
       <c r="N76" t="n">
-        <v>8188743036.341737</v>
+        <v>142155021.2773955</v>
       </c>
       <c r="O76" t="n">
-        <v>0.193254</v>
+        <v>28.83</v>
       </c>
       <c r="P76" s="1" t="n">
-        <v>44290.85721064815</v>
+        <v>44531.29832175926</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R76" t="b">
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0002666241164597869</v>
+        <v>0.0002690798712454985</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>kucoin-shares</t>
+          <t>just</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>kcs</t>
+          <t>jst</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KuCoin</t>
+          <t>JUST</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6.78</v>
+        <v>0.116583</v>
       </c>
       <c r="F77" t="n">
-        <v>929627401</v>
+        <v>954756417</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>4671099</v>
+        <v>26505719</v>
       </c>
       <c r="I77" t="n">
-        <v>6.84</v>
+        <v>0.117692</v>
       </c>
       <c r="J77" t="n">
-        <v>6.76</v>
+        <v>0.115665</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.1033133770776775</v>
+        <v>0.00059799</v>
       </c>
       <c r="L77" t="n">
-        <v>-1.48355</v>
+        <v>0.51558</v>
       </c>
       <c r="M77" t="n">
-        <v>137155021.2773955</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="N77" t="n">
-        <v>142155021.2773955</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="O77" t="n">
-        <v>28.83</v>
+        <v>0.193254</v>
       </c>
       <c r="P77" s="1" t="n">
-        <v>44531.29832175926</v>
+        <v>44290.85721064815</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R77" t="b">
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002546836621222692</v>
+        <v>0.0002635048544377539</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>pi-network</t>
+          <t>kaspa</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>pi</t>
+          <t>kas</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Pi Network</t>
+          <t>Kaspa</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.082159</v>
+        <v>0.0335759</v>
       </c>
       <c r="F78" t="n">
-        <v>919967696</v>
+        <v>930001042</v>
       </c>
       <c r="G78" t="n">
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>15567692</v>
+        <v>12445308</v>
       </c>
       <c r="I78" t="n">
-        <v>0.09499</v>
+        <v>0.03459489</v>
       </c>
       <c r="J78" t="n">
-        <v>0.081188</v>
+        <v>0.03175054</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.0134566338486979</v>
+        <v>0.00157764</v>
       </c>
       <c r="L78" t="n">
-        <v>-14.04266</v>
+        <v>4.93041</v>
       </c>
       <c r="M78" t="n">
-        <v>11202518627.78052</v>
+        <v>27705335017.92249</v>
       </c>
       <c r="N78" t="n">
-        <v>17234644042.73926</v>
+        <v>27705589343.2654</v>
       </c>
       <c r="O78" t="n">
-        <v>2.99</v>
+        <v>0.207411</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>45714.36184027778</v>
+        <v>45504.69498842592</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.000248313580430133</v>
+        <v>0.0002474171001377871</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>kaspa</t>
+          <t>pi-network</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>kas</t>
+          <t>pi</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Kaspa</t>
+          <t>Pi Network</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.03209132</v>
+        <v>0.082855</v>
       </c>
       <c r="F79" t="n">
-        <v>888927046</v>
+        <v>929483978</v>
       </c>
       <c r="G79" t="n">
         <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>11894660</v>
+        <v>9276245</v>
       </c>
       <c r="I79" t="n">
-        <v>0.03407844</v>
+        <v>0.08591600000000001</v>
       </c>
       <c r="J79" t="n">
-        <v>0.03173331</v>
+        <v>0.08044</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.00185140908267041</v>
+        <v>0.00066717</v>
       </c>
       <c r="L79" t="n">
-        <v>-5.43137</v>
+        <v>0.81177</v>
       </c>
       <c r="M79" t="n">
-        <v>27701989210.63944</v>
+        <v>11218698151.07317</v>
       </c>
       <c r="N79" t="n">
-        <v>27703725584.33658</v>
+        <v>17259535617.03564</v>
       </c>
       <c r="O79" t="n">
-        <v>0.207411</v>
+        <v>2.99</v>
       </c>
       <c r="P79" s="1" t="n">
-        <v>45504.69498842592</v>
+        <v>45714.36184027778</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002278438583964883</v>
+        <v>0.0002470810761999813</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5765,28 +5765,28 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>59.12</v>
+        <v>61.2</v>
       </c>
       <c r="F80" t="n">
-        <v>859982178</v>
+        <v>889954623</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>8011305</v>
+        <v>7408866</v>
       </c>
       <c r="I80" t="n">
-        <v>62.97</v>
+        <v>61.98</v>
       </c>
       <c r="J80" t="n">
-        <v>59.13</v>
+        <v>58.91</v>
       </c>
       <c r="K80" t="n">
-        <v>-3.441180867104492</v>
+        <v>2.07</v>
       </c>
       <c r="L80" t="n">
-        <v>-5.39741</v>
+        <v>3.49961</v>
       </c>
       <c r="M80" t="n">
         <v>14544176.16408117</v>
@@ -5801,309 +5801,309 @@
         <v>44450.05208333334</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002087561974660459</v>
+        <v>0.0002213921682001564</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>algorand</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>algo</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Spiko EU T-Bills Money Market Fund</t>
+          <t>Algorand</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1.22</v>
+        <v>0.09013</v>
       </c>
       <c r="F81" t="n">
-        <v>797086512</v>
+        <v>814602846</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>44122052</v>
       </c>
       <c r="I81" t="n">
-        <v>1.22</v>
+        <v>0.09153699999999999</v>
       </c>
       <c r="J81" t="n">
-        <v>1.22</v>
+        <v>0.08534</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.001653273013533907</v>
+        <v>0.00407963</v>
       </c>
       <c r="L81" t="n">
-        <v>-0.13521</v>
+        <v>4.74096</v>
       </c>
       <c r="M81" t="n">
-        <v>652741858.0353301</v>
+        <v>9041440361.74052</v>
       </c>
       <c r="N81" t="n">
-        <v>652741858.0353301</v>
+        <v>9041867790.797272</v>
       </c>
       <c r="O81" t="n">
-        <v>1.26</v>
+        <v>3.56</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>46049.54175925926</v>
+        <v>43636.28563657407</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R81" t="b">
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0001672797206480362</v>
+        <v>0.0001724233735669954</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>cosmos</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Cosmos Hub</t>
+          <t>NEXO</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1.5</v>
+        <v>0.813817</v>
       </c>
       <c r="F82" t="n">
-        <v>794058682</v>
+        <v>814150815</v>
       </c>
       <c r="G82" t="n">
         <v>81</v>
       </c>
       <c r="H82" t="n">
-        <v>40018692</v>
+        <v>3265526</v>
       </c>
       <c r="I82" t="n">
-        <v>1.57</v>
+        <v>0.810526</v>
       </c>
       <c r="J82" t="n">
-        <v>1.48</v>
+        <v>0.778729</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.06371213836752765</v>
+        <v>0.027226</v>
       </c>
       <c r="L82" t="n">
-        <v>-4.00223</v>
+        <v>3.46127</v>
       </c>
       <c r="M82" t="n">
-        <v>531026230.140559</v>
+        <v>1000000000</v>
       </c>
       <c r="N82" t="n">
-        <v>531040943.180444</v>
+        <v>1000000000</v>
       </c>
       <c r="O82" t="n">
-        <v>43.84</v>
+        <v>4.07</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>44458.66666666666</v>
+        <v>44328.27623842593</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0001652830215304233</v>
+        <v>0.0001721296125690719</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>cosmos</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NEXO</t>
+          <t>Cosmos Hub</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.787241</v>
+        <v>1.53</v>
       </c>
       <c r="F83" t="n">
-        <v>786768061</v>
+        <v>811905140</v>
       </c>
       <c r="G83" t="n">
         <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>4032116</v>
+        <v>39690657</v>
       </c>
       <c r="I83" t="n">
-        <v>0.804343</v>
+        <v>1.55</v>
       </c>
       <c r="J83" t="n">
-        <v>0.784022</v>
+        <v>1.47</v>
       </c>
       <c r="K83" t="n">
-        <v>-0.01602228614867518</v>
+        <v>0.03987303</v>
       </c>
       <c r="L83" t="n">
-        <v>-1.98418</v>
+        <v>2.67726</v>
       </c>
       <c r="M83" t="n">
-        <v>1000000000</v>
+        <v>531209599.807218</v>
       </c>
       <c r="N83" t="n">
-        <v>1000000000</v>
+        <v>531224914.94615</v>
       </c>
       <c r="O83" t="n">
-        <v>4.07</v>
+        <v>43.84</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>44328.27623842593</v>
+        <v>44458.66666666666</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0001604752296406706</v>
+        <v>0.0001706702176846245</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>algorand</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>algo</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Algorand</t>
+          <t>Spiko EU T-Bills Money Market Fund</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.086422</v>
+        <v>1.22</v>
       </c>
       <c r="F84" t="n">
-        <v>781294191</v>
+        <v>794507303</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>45158936</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>0.093933</v>
+        <v>1.22</v>
       </c>
       <c r="J84" t="n">
-        <v>0.085676</v>
+        <v>1.21</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.009173342790273278</v>
+        <v>-0.004000636553897152</v>
       </c>
       <c r="L84" t="n">
-        <v>-9.572710000000001</v>
+        <v>-0.3276</v>
       </c>
       <c r="M84" t="n">
-        <v>9041440361.74052</v>
+        <v>652741858.0353301</v>
       </c>
       <c r="N84" t="n">
-        <v>9041658401.381454</v>
+        <v>652909474.76177</v>
       </c>
       <c r="O84" t="n">
-        <v>3.56</v>
+        <v>1.26</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>43636.28563657407</v>
+        <v>46049.54175925926</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001568654921722765</v>
+        <v>0.0001593639002886298</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
+          <t>janus-henderson-anemoy-aaa-clo-fund</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ustb</t>
+          <t>jaaa</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Invesco Short Duration US Government Securities Fund</t>
+          <t>Janus Henderson Anemoy AAA CLO Fund</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>11.21</v>
+        <v>1.05</v>
       </c>
       <c r="F85" t="n">
-        <v>746133355</v>
+        <v>775002313</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
@@ -6112,713 +6112,713 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>11.21</v>
+        <v>1.05</v>
       </c>
       <c r="J85" t="n">
-        <v>11.21</v>
+        <v>1.05</v>
       </c>
       <c r="K85" t="n">
-        <v>0.001077</v>
+        <v>0.000151</v>
       </c>
       <c r="L85" t="n">
-        <v>0.00961</v>
+        <v>0.01439</v>
       </c>
       <c r="M85" t="n">
-        <v>66538460.783645</v>
+        <v>738235948.461841</v>
       </c>
       <c r="N85" t="n">
-        <v>66405944.731128</v>
+        <v>738235948.461841</v>
       </c>
       <c r="O85" t="n">
-        <v>11.21</v>
+        <v>1.05</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>46281.55567129629</v>
+        <v>46282.42384259259</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R85" t="b">
         <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001336787180747442</v>
+        <v>0.0001466882091814133</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-aaa-clo-fund</t>
+          <t>pancakeswap-token</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>jaaa</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy AAA CLO Fund</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1.05</v>
+        <v>2.38</v>
       </c>
       <c r="F86" t="n">
-        <v>720567789</v>
+        <v>759100711</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>98183689</v>
       </c>
       <c r="I86" t="n">
-        <v>1.05</v>
+        <v>2.43</v>
       </c>
       <c r="J86" t="n">
-        <v>1.05</v>
+        <v>2.17</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>0.196026</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>8.98293</v>
       </c>
       <c r="M86" t="n">
-        <v>686482557.075531</v>
+        <v>319432763.8588443</v>
       </c>
       <c r="N86" t="n">
-        <v>686482557.075531</v>
+        <v>331093394.0049145</v>
       </c>
       <c r="O86" t="n">
-        <v>1.05</v>
+        <v>43.96</v>
       </c>
       <c r="P86" s="1" t="n">
-        <v>46280.48611111111</v>
+        <v>44316.08914351852</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S86" t="n">
-        <v>0.00011681953408044</v>
+        <v>0.0001363542487404238</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>stable-2</t>
+          <t>jupiter-exchange-solana</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>jup</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>​​Stable</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.02672222</v>
+        <v>0.226699</v>
       </c>
       <c r="F87" t="n">
-        <v>704385120</v>
+        <v>751341092</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>9080584</v>
+        <v>85706896</v>
       </c>
       <c r="I87" t="n">
-        <v>0.02764996</v>
+        <v>0.227422</v>
       </c>
       <c r="J87" t="n">
-        <v>0.02669047</v>
+        <v>0.207452</v>
       </c>
       <c r="K87" t="n">
-        <v>-0.000927100387334255</v>
+        <v>0.01625699</v>
       </c>
       <c r="L87" t="n">
-        <v>-3.31507</v>
+        <v>7.72517</v>
       </c>
       <c r="M87" t="n">
-        <v>26372627229</v>
+        <v>3319369204.37</v>
       </c>
       <c r="N87" t="n">
-        <v>100000000000</v>
+        <v>6861487035.852483</v>
       </c>
       <c r="O87" t="n">
-        <v>0.04323745</v>
+        <v>2</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>46156.97986111111</v>
+        <v>45322.29359953704</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001061478910512999</v>
+        <v>0.0001313115118021487</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jupiter-exchange-solana</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>jup</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Dash</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.211556</v>
+        <v>58.3</v>
       </c>
       <c r="F88" t="n">
-        <v>700563517</v>
+        <v>746560452</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>67620445</v>
+        <v>224653157</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2301</v>
+        <v>60.37</v>
       </c>
       <c r="J88" t="n">
-        <v>0.209445</v>
+        <v>52.99</v>
       </c>
       <c r="K88" t="n">
-        <v>-0.01853123163518763</v>
+        <v>4.2</v>
       </c>
       <c r="L88" t="n">
-        <v>-7.95869</v>
+        <v>7.75706</v>
       </c>
       <c r="M88" t="n">
-        <v>3319369204.37</v>
+        <v>12831918.9507522</v>
       </c>
       <c r="N88" t="n">
-        <v>6861487082.669715</v>
+        <v>12832046.56713975</v>
       </c>
       <c r="O88" t="n">
-        <v>2</v>
+        <v>1493.59</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>45322.29359953704</v>
+        <v>43088.66666666666</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R88" t="b">
         <v>1</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001036277392138563</v>
+        <v>0.0001282047213892951</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>pancakeswap-token</t>
+          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>ustb</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>Invesco Short Duration US Government Securities Fund</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2.19</v>
+        <v>11.21</v>
       </c>
       <c r="F89" t="n">
-        <v>697776297</v>
+        <v>732885815</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>66568314</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>2.28</v>
+        <v>11.21</v>
       </c>
       <c r="J89" t="n">
-        <v>2.16</v>
+        <v>11.21</v>
       </c>
       <c r="K89" t="n">
-        <v>-0.1069725160327675</v>
+        <v>0.001081</v>
       </c>
       <c r="L89" t="n">
-        <v>-4.64511</v>
+        <v>0.009639999999999999</v>
       </c>
       <c r="M89" t="n">
-        <v>319432296.7908565</v>
+        <v>65350775.701558</v>
       </c>
       <c r="N89" t="n">
-        <v>331093394.0049145</v>
+        <v>65348949.048738</v>
       </c>
       <c r="O89" t="n">
-        <v>43.96</v>
+        <v>11.21</v>
       </c>
       <c r="P89" s="1" t="n">
-        <v>44316.08914351852</v>
+        <v>46282.55208333334</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001017897100924747</v>
+        <v>0.0001193179967811147</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>render-token</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>render</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>GHO</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.998568</v>
+        <v>1.4</v>
       </c>
       <c r="F90" t="n">
-        <v>697975152</v>
+        <v>726354679</v>
       </c>
       <c r="G90" t="n">
         <v>89</v>
       </c>
       <c r="H90" t="n">
-        <v>7653280</v>
+        <v>43603831</v>
       </c>
       <c r="I90" t="n">
-        <v>0.998815</v>
+        <v>1.4</v>
       </c>
       <c r="J90" t="n">
-        <v>0.998372</v>
+        <v>1.29</v>
       </c>
       <c r="K90" t="n">
-        <v>-0.000165807461207645</v>
+        <v>0.104528</v>
       </c>
       <c r="L90" t="n">
-        <v>-0.019</v>
+        <v>8.059810000000001</v>
       </c>
       <c r="M90" t="n">
-        <v>699000000</v>
+        <v>518776241.2826915</v>
       </c>
       <c r="N90" t="n">
-        <v>699000000</v>
+        <v>533536414.5626915</v>
       </c>
       <c r="O90" t="n">
-        <v>1.03</v>
+        <v>13.53</v>
       </c>
       <c r="P90" s="1" t="n">
-        <v>45350.38608796296</v>
+        <v>45368.35444444444</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S90" t="n">
-        <v>0.0001019208448005108</v>
+        <v>0.0001150736130354567</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Dash</t>
+          <t>GHO</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>54.29</v>
+        <v>0.998519</v>
       </c>
       <c r="F91" t="n">
-        <v>696465238</v>
+        <v>697955648</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>126702373</v>
+        <v>12091739</v>
       </c>
       <c r="I91" t="n">
-        <v>55.98</v>
+        <v>0.998878</v>
       </c>
       <c r="J91" t="n">
-        <v>49.94</v>
+        <v>0.998148</v>
       </c>
       <c r="K91" t="n">
-        <v>1.85</v>
+        <v>-3.0372547706881e-05</v>
       </c>
       <c r="L91" t="n">
-        <v>3.46177</v>
+        <v>-0.00304</v>
       </c>
       <c r="M91" t="n">
-        <v>12830909.72488206</v>
+        <v>699000000</v>
       </c>
       <c r="N91" t="n">
-        <v>12830982.59594397</v>
+        <v>699000000</v>
       </c>
       <c r="O91" t="n">
-        <v>1493.59</v>
+        <v>1.03</v>
       </c>
       <c r="P91" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>45350.38608796296</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R91" t="b">
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>0.0001009251336966934</v>
+        <v>9.661795913867103e-05</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-treasury-fund</t>
+          <t>marscat-token</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>jtrsy</t>
+          <t>mcat</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund</t>
+          <t>Marscat Token</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1.12</v>
+        <v>0.6707419999999999</v>
       </c>
       <c r="F92" t="n">
-        <v>675176286</v>
+        <v>671748418</v>
       </c>
       <c r="G92" t="n">
         <v>91</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>16628728</v>
       </c>
       <c r="I92" t="n">
-        <v>1.12</v>
+        <v>0.819144</v>
       </c>
       <c r="J92" t="n">
-        <v>1.12</v>
+        <v>0.217044</v>
       </c>
       <c r="K92" t="n">
-        <v>0.00011</v>
+        <v>0.439347</v>
       </c>
       <c r="L92" t="n">
-        <v>0.009860000000000001</v>
+        <v>189.86889</v>
       </c>
       <c r="M92" t="n">
-        <v>604951138.283703</v>
+        <v>1000000000</v>
       </c>
       <c r="N92" t="n">
-        <v>582549198.395</v>
+        <v>1000000000</v>
       </c>
       <c r="O92" t="n">
-        <v>1.12</v>
+        <v>0.819144</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>46281.33680555555</v>
+        <v>46282.41516203704</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S92" t="n">
-        <v>8.688615803646711e-05</v>
+        <v>7.9586689076201e-05</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>render-token</t>
+          <t>filecoin</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>render</t>
+          <t>fil</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1.3</v>
+        <v>0.819213</v>
       </c>
       <c r="F93" t="n">
-        <v>674256609</v>
+        <v>677259265</v>
       </c>
       <c r="G93" t="n">
         <v>92</v>
       </c>
       <c r="H93" t="n">
-        <v>41520575</v>
+        <v>125078551</v>
       </c>
       <c r="I93" t="n">
-        <v>1.36</v>
+        <v>0.817635</v>
       </c>
       <c r="J93" t="n">
-        <v>1.29</v>
+        <v>0.768896</v>
       </c>
       <c r="K93" t="n">
-        <v>-0.05666880936932883</v>
+        <v>0.04083346</v>
       </c>
       <c r="L93" t="n">
-        <v>-4.1354</v>
+        <v>5.24596</v>
       </c>
       <c r="M93" t="n">
-        <v>518776241.2826915</v>
+        <v>827813309</v>
       </c>
       <c r="N93" t="n">
-        <v>533536414.5626915</v>
+        <v>1957043843</v>
       </c>
       <c r="O93" t="n">
-        <v>13.53</v>
+        <v>236.84</v>
       </c>
       <c r="P93" s="1" t="n">
-        <v>45368.35444444444</v>
+        <v>44287.22894675926</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R93" t="b">
         <v>1</v>
       </c>
       <c r="S93" t="n">
-        <v>8.627967806421343e-05</v>
+        <v>8.316801848529737e-05</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>filecoin</t>
+          <t>janus-henderson-anemoy-treasury-fund</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>jtrsy</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>Janus Henderson Anemoy Treasury Fund</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.78289</v>
+        <v>1.12</v>
       </c>
       <c r="F94" t="n">
-        <v>648099111</v>
+        <v>650205297</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
       </c>
       <c r="H94" t="n">
-        <v>156588845</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0.869021</v>
+        <v>1.12</v>
       </c>
       <c r="J94" t="n">
-        <v>0.779522</v>
+        <v>1.12</v>
       </c>
       <c r="K94" t="n">
-        <v>-0.09343837998466098</v>
+        <v>5.4e-05</v>
       </c>
       <c r="L94" t="n">
-        <v>-10.75323</v>
+        <v>0.00484</v>
       </c>
       <c r="M94" t="n">
-        <v>827813309</v>
+        <v>582549198.395</v>
       </c>
       <c r="N94" t="n">
-        <v>1957045721</v>
+        <v>537749706.0290329</v>
       </c>
       <c r="O94" t="n">
-        <v>236.84</v>
+        <v>1.12</v>
       </c>
       <c r="P94" s="1" t="n">
-        <v>44287.22894675926</v>
+        <v>46282.42384259259</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>6.903014517248545e-05</v>
+        <v>6.558647952565065e-05</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>akedo</t>
+          <t>stable-2</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ake</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Akedo</t>
+          <t>​​Stable</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.02712454</v>
+        <v>0.02337075</v>
       </c>
       <c r="F95" t="n">
-        <v>617387700</v>
+        <v>617208310</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>51222202</v>
+        <v>11681429</v>
       </c>
       <c r="I95" t="n">
-        <v>0.02946829</v>
+        <v>0.02669918</v>
       </c>
       <c r="J95" t="n">
-        <v>0.02453896</v>
+        <v>0.0233546</v>
       </c>
       <c r="K95" t="n">
-        <v>0.00127937</v>
+        <v>-0.00332136202994586</v>
       </c>
       <c r="L95" t="n">
-        <v>4.44773</v>
+        <v>-12.44324</v>
       </c>
       <c r="M95" t="n">
-        <v>22796250000</v>
+        <v>26401971536</v>
       </c>
       <c r="N95" t="n">
         <v>100000000000</v>
       </c>
       <c r="O95" t="n">
-        <v>0.0363756</v>
+        <v>0.04323745</v>
       </c>
       <c r="P95" s="1" t="n">
-        <v>46267.90648148148</v>
+        <v>46156.97986111111</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S95" t="n">
-        <v>4.877753943030488e-05</v>
+        <v>4.414275591026617e-05</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6837,28 +6837,28 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.00697751</v>
+        <v>0.00716083</v>
       </c>
       <c r="F96" t="n">
-        <v>599636325</v>
+        <v>615409250</v>
       </c>
       <c r="G96" t="n">
         <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>12618280</v>
+        <v>10609511</v>
       </c>
       <c r="I96" t="n">
-        <v>0.007447</v>
+        <v>0.00726114</v>
       </c>
       <c r="J96" t="n">
-        <v>0.00695035</v>
+        <v>0.00681043</v>
       </c>
       <c r="K96" t="n">
-        <v>-0.000403271147242099</v>
+        <v>0.00019794</v>
       </c>
       <c r="L96" t="n">
-        <v>-5.32643</v>
+        <v>2.84273</v>
       </c>
       <c r="M96" t="n">
         <v>85985041177</v>
@@ -6873,287 +6873,287 @@
         <v>44304.71413194444</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>3.707141497849768e-05</v>
+        <v>4.297360233247151e-05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>beldex</t>
+          <t>ether-fi</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>bdx</t>
+          <t>ethfi</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Beldex</t>
+          <t>Ether.fi</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.075923</v>
+        <v>0.6242490000000001</v>
       </c>
       <c r="F97" t="n">
-        <v>597572288</v>
+        <v>603124403</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>8624950</v>
+        <v>51379350</v>
       </c>
       <c r="I97" t="n">
-        <v>0.07636</v>
+        <v>0.62782</v>
       </c>
       <c r="J97" t="n">
-        <v>0.07541399999999999</v>
+        <v>0.575779</v>
       </c>
       <c r="K97" t="n">
-        <v>-5.8036939795517e-05</v>
+        <v>0.04198894</v>
       </c>
       <c r="L97" t="n">
-        <v>-0.02864</v>
+        <v>7.21137</v>
       </c>
       <c r="M97" t="n">
-        <v>7870705626.343594</v>
+        <v>965350000</v>
       </c>
       <c r="N97" t="n">
-        <v>9939645626.343594</v>
+        <v>965350000</v>
       </c>
       <c r="O97" t="n">
-        <v>0.450785</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="P97" s="1" t="n">
-        <v>43450.66666666666</v>
+        <v>45378.63525462963</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S97" t="n">
-        <v>3.571028808015123e-05</v>
+        <v>3.499005935852407e-05</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ether-fi</t>
+          <t>beldex</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ethfi</t>
+          <t>bdx</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Ether.fi</t>
+          <t>Beldex</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.583417</v>
+        <v>0.07616100000000001</v>
       </c>
       <c r="F98" t="n">
-        <v>562370413</v>
+        <v>599440658</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>36220169</v>
+        <v>7836802</v>
       </c>
       <c r="I98" t="n">
-        <v>0.610816</v>
+        <v>0.076672</v>
       </c>
       <c r="J98" t="n">
-        <v>0.575364</v>
+        <v>0.075295</v>
       </c>
       <c r="K98" t="n">
-        <v>-0.02821208126055863</v>
+        <v>0.00104262</v>
       </c>
       <c r="L98" t="n">
-        <v>-4.57759</v>
+        <v>1.38796</v>
       </c>
       <c r="M98" t="n">
-        <v>965350000</v>
+        <v>7870732376.983206</v>
       </c>
       <c r="N98" t="n">
-        <v>965350000</v>
+        <v>9939671749.706188</v>
       </c>
       <c r="O98" t="n">
-        <v>8.529999999999999</v>
+        <v>0.450785</v>
       </c>
       <c r="P98" s="1" t="n">
-        <v>45378.63525462963</v>
+        <v>43450.66666666666</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>1.249645085982546e-05</v>
+        <v>3.259610715768965e-05</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>usual-usd</t>
+          <t>aerodrome-finance</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>usd0</t>
+          <t>aero</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Usual USD</t>
+          <t>Aerodrome Finance</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.999088</v>
+        <v>0.596889</v>
       </c>
       <c r="F99" t="n">
-        <v>547070561</v>
+        <v>592814115</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>2174570</v>
+        <v>52101612</v>
       </c>
       <c r="I99" t="n">
-        <v>0.999333</v>
+        <v>0.594585</v>
       </c>
       <c r="J99" t="n">
-        <v>0.997592</v>
+        <v>0.518055</v>
       </c>
       <c r="K99" t="n">
-        <v>0.00019516</v>
+        <v>0.076251</v>
       </c>
       <c r="L99" t="n">
-        <v>0.01938</v>
+        <v>14.64574</v>
       </c>
       <c r="M99" t="n">
-        <v>547588559.06276</v>
+        <v>993277331.60516</v>
       </c>
       <c r="N99" t="n">
-        <v>547513539.7413483</v>
+        <v>1983240735.576791</v>
       </c>
       <c r="O99" t="n">
-        <v>1.33</v>
+        <v>2.32</v>
       </c>
       <c r="P99" s="1" t="n">
-        <v>45485.02012731481</v>
+        <v>45633.25043981482</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S99" t="n">
-        <v>2.406980517036164e-06</v>
+        <v>2.828972134684393e-05</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>xdce-crowd-sale</t>
+          <t>injective-protocol</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>xdc</t>
+          <t>inj</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>XDC Network</t>
+          <t>Injective</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.02738998</v>
+        <v>5.69</v>
       </c>
       <c r="F100" t="n">
-        <v>546193737</v>
+        <v>568474370</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>11023396</v>
+        <v>94931431</v>
       </c>
       <c r="I100" t="n">
-        <v>0.02899922</v>
+        <v>5.67</v>
       </c>
       <c r="J100" t="n">
-        <v>0.02713273</v>
+        <v>5.16</v>
       </c>
       <c r="K100" t="n">
-        <v>-0.001787140154804887</v>
+        <v>0.286238</v>
       </c>
       <c r="L100" t="n">
-        <v>-6.02369</v>
+        <v>5.29727</v>
       </c>
       <c r="M100" t="n">
-        <v>19946688440</v>
+        <v>100000000</v>
       </c>
       <c r="N100" t="n">
-        <v>38065686425.1</v>
+        <v>100000000</v>
       </c>
       <c r="O100" t="n">
-        <v>0.192754</v>
+        <v>52.62</v>
       </c>
       <c r="P100" s="1" t="n">
-        <v>44428.86097222222</v>
+        <v>45365.29608796296</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R100" t="b">
         <v>1</v>
       </c>
       <c r="S100" t="n">
-        <v>1.828759907853417e-06</v>
+        <v>1.247207215817902e-05</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7172,34 +7172,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.00624858</v>
+        <v>0.00631737</v>
       </c>
       <c r="F101" t="n">
-        <v>543420573</v>
+        <v>549282703</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>4229846</v>
+        <v>2343719</v>
       </c>
       <c r="I101" t="n">
-        <v>0.00670541</v>
+        <v>0.00635515</v>
       </c>
       <c r="J101" t="n">
-        <v>0.0062435</v>
+        <v>0.00622597</v>
       </c>
       <c r="K101" t="n">
-        <v>-0.000419855243895558</v>
+        <v>7.227e-05</v>
       </c>
       <c r="L101" t="n">
-        <v>-6.28322</v>
+        <v>1.1572</v>
       </c>
       <c r="M101" t="n">
-        <v>86970320242.41383</v>
+        <v>86974846982.67435</v>
       </c>
       <c r="N101" t="n">
-        <v>106559883415.9188</v>
+        <v>106567132005.1747</v>
       </c>
       <c r="O101" t="n">
         <v>0.150073</v>
@@ -7208,10 +7208,10 @@
         <v>44935.80144675926</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46281.58692129629</v>
+        <v>46282.59108796297</v>
       </c>
       <c r="R101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>

--- a/src/xlsx/cleaned_data.xlsx
+++ b/src/xlsx/cleaned_data.xlsx
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,34 +539,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>76644</v>
+        <v>78107</v>
       </c>
       <c r="F2" t="n">
-        <v>1539320607676</v>
+        <v>1568598802085</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>30133625120</v>
+        <v>29746226629</v>
       </c>
       <c r="I2" t="n">
-        <v>77024</v>
+        <v>78372</v>
       </c>
       <c r="J2" t="n">
-        <v>75161</v>
+        <v>76205</v>
       </c>
       <c r="K2" t="n">
-        <v>1202.29</v>
+        <v>1623.81</v>
       </c>
       <c r="L2" t="n">
-        <v>1.59367</v>
+        <v>2.12309</v>
       </c>
       <c r="M2" t="n">
-        <v>20085603</v>
+        <v>20086075</v>
       </c>
       <c r="N2" t="n">
-        <v>20085665</v>
+        <v>20086075</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -575,7 +575,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -587,7 +587,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,34 +606,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2463.87</v>
+        <v>2504.2</v>
       </c>
       <c r="F3" t="n">
-        <v>300760183438</v>
+        <v>305590691965</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>15874627280</v>
+        <v>15043114849</v>
       </c>
       <c r="I3" t="n">
-        <v>2473.53</v>
+        <v>2518</v>
       </c>
       <c r="J3" t="n">
-        <v>2371.36</v>
+        <v>2435.96</v>
       </c>
       <c r="K3" t="n">
-        <v>79.62</v>
+        <v>52.04</v>
       </c>
       <c r="L3" t="n">
-        <v>3.33959</v>
+        <v>2.12207</v>
       </c>
       <c r="M3" t="n">
-        <v>122056009.605603</v>
+        <v>122058930.7915531</v>
       </c>
       <c r="N3" t="n">
-        <v>122056009.605603</v>
+        <v>122058930.7915531</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -642,19 +642,19 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1950978003442244</v>
+        <v>0.1945279805147563</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,28 +673,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.99915</v>
+        <v>0.9991640000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>183284327911</v>
+        <v>183289006638</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>61718644343</v>
+        <v>61371983187</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999539</v>
+        <v>0.9993610000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999112</v>
+        <v>0.999089</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000238099616719611</v>
+        <v>-2.8548222514524e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.02382</v>
+        <v>-0.00286</v>
       </c>
       <c r="M4" t="n">
         <v>183442587855.5799</v>
@@ -709,19 +709,19 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1187538669601907</v>
+        <v>0.1165311848667633</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,34 +740,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>726.74</v>
+        <v>750.21</v>
       </c>
       <c r="F5" t="n">
-        <v>96755073209</v>
+        <v>99874497337</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1032713365</v>
+        <v>1327798862</v>
       </c>
       <c r="I5" t="n">
-        <v>731.53</v>
+        <v>758.16</v>
       </c>
       <c r="J5" t="n">
-        <v>708.73</v>
+        <v>724.1900000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>17.6</v>
+        <v>23.05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4826</v>
+        <v>3.1697</v>
       </c>
       <c r="M5" t="n">
-        <v>133160558.5</v>
+        <v>133160438.17</v>
       </c>
       <c r="N5" t="n">
-        <v>133160532.83</v>
+        <v>133160429.28</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -776,19 +776,19 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06252117448815084</v>
+        <v>0.06333433464648759</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -807,28 +807,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="F6" t="n">
-        <v>82009347142</v>
+        <v>83325852293</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>3625730823</v>
+        <v>2693394422</v>
       </c>
       <c r="I6" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="J6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03567597</v>
+        <v>0.02428641</v>
       </c>
       <c r="L6" t="n">
-        <v>2.81145</v>
+        <v>1.8667</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -843,19 +843,19 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05293838214747688</v>
+        <v>0.05278058567486089</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,34 +874,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999571</v>
+        <v>0.999514</v>
       </c>
       <c r="F7" t="n">
-        <v>73555159854</v>
+        <v>73773705191</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>19170526434</v>
+        <v>16804878019</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999802</v>
+        <v>0.999703</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999055</v>
+        <v>0.999464</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.000145914927842328</v>
+        <v>-7.1772637548539e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0146</v>
+        <v>-0.00718</v>
       </c>
       <c r="M7" t="n">
-        <v>73587375656.46214</v>
+        <v>73809548950.31921</v>
       </c>
       <c r="N7" t="n">
-        <v>73590256479.63303</v>
+        <v>73809465033.80299</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -910,19 +910,19 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04744426671213216</v>
+        <v>0.046688790099663</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -941,34 +941,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100.77</v>
+        <v>105.87</v>
       </c>
       <c r="F8" t="n">
-        <v>59152011113</v>
+        <v>62173407445</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3739451532</v>
+        <v>4336330927</v>
       </c>
       <c r="I8" t="n">
-        <v>101.24</v>
+        <v>106.53</v>
       </c>
       <c r="J8" t="n">
-        <v>96.11</v>
+        <v>100.11</v>
       </c>
       <c r="K8" t="n">
-        <v>4.05</v>
+        <v>5.5</v>
       </c>
       <c r="L8" t="n">
-        <v>4.18322</v>
+        <v>5.47797</v>
       </c>
       <c r="M8" t="n">
-        <v>587212147.1182363</v>
+        <v>587297218.9841995</v>
       </c>
       <c r="N8" t="n">
-        <v>634204567.4934224</v>
+        <v>634298467.6716927</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -977,19 +977,19 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03808410480421986</v>
+        <v>0.03929080494245527</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1008,34 +1008,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.334283</v>
+        <v>0.338083</v>
       </c>
       <c r="F9" t="n">
-        <v>31742370925</v>
+        <v>32101739690</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>342292091</v>
+        <v>387644195</v>
       </c>
       <c r="I9" t="n">
-        <v>0.336124</v>
+        <v>0.337939</v>
       </c>
       <c r="J9" t="n">
-        <v>0.334217</v>
+        <v>0.333425</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.000219834965064225</v>
+        <v>0.00335145</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.06572</v>
+        <v>1.00124</v>
       </c>
       <c r="M9" t="n">
-        <v>94953504416.74518</v>
+        <v>94954902669.86409</v>
       </c>
       <c r="N9" t="n">
-        <v>94953498011.30618</v>
+        <v>94954901666.17758</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1044,19 +1044,19 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02027142546508483</v>
+        <v>0.02011287032601977</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1075,34 +1075,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1405.63</v>
+        <v>1467.74</v>
       </c>
       <c r="F10" t="n">
-        <v>23797511040</v>
+        <v>24865345606</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>2809381550</v>
+        <v>2178796951</v>
       </c>
       <c r="I10" t="n">
-        <v>1388.42</v>
+        <v>1526.56</v>
       </c>
       <c r="J10" t="n">
-        <v>1235.16</v>
+        <v>1370.29</v>
       </c>
       <c r="K10" t="n">
-        <v>157.34</v>
+        <v>105.04</v>
       </c>
       <c r="L10" t="n">
-        <v>12.60406</v>
+        <v>7.70855</v>
       </c>
       <c r="M10" t="n">
-        <v>16937203.2905448</v>
+        <v>16938925.1655448</v>
       </c>
       <c r="N10" t="n">
-        <v>16937454.8530448</v>
+        <v>16939175.1655448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1111,19 +1111,19 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01510830619189497</v>
+        <v>0.01549792533087104</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1142,34 +1142,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.03</v>
+        <v>1.028</v>
       </c>
       <c r="F11" t="n">
-        <v>23270039358</v>
+        <v>23301466219</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>98622645</v>
+        <v>209412055</v>
       </c>
       <c r="I11" t="n">
-        <v>1.03</v>
+        <v>1.035</v>
       </c>
       <c r="J11" t="n">
-        <v>1.001</v>
+        <v>1.004</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02657361</v>
+        <v>-0.001618662688462669</v>
       </c>
       <c r="L11" t="n">
-        <v>2.64907</v>
+        <v>-0.1572</v>
       </c>
       <c r="M11" t="n">
-        <v>22598468218.548</v>
+        <v>22665434312.548</v>
       </c>
       <c r="N11" t="n">
-        <v>22598468218.548</v>
+        <v>22665434312.548</v>
       </c>
       <c r="O11" t="n">
         <v>1.061</v>
@@ -1178,19 +1178,19 @@
         <v>46237.59675925926</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01476551862272237</v>
+        <v>0.01450057537089449</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1209,28 +1209,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>81.98999999999999</v>
+        <v>91.27</v>
       </c>
       <c r="F12" t="n">
-        <v>18231266029</v>
+        <v>20297028307</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1146341296</v>
+        <v>1618650214</v>
       </c>
       <c r="I12" t="n">
-        <v>82.70999999999999</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>77.19</v>
+        <v>81.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.78</v>
+        <v>9.19</v>
       </c>
       <c r="L12" t="n">
-        <v>4.83726</v>
+        <v>11.19346</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1239,25 +1239,25 @@
         <v>955307079.4341414</v>
       </c>
       <c r="O12" t="n">
-        <v>89.59999999999999</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>46271.5199074074</v>
+        <v>46283.5275462963</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01149097532494652</v>
+        <v>0.01258452221731123</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1276,34 +1276,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.08157399999999999</v>
+        <v>0.085364</v>
       </c>
       <c r="F13" t="n">
-        <v>12717767225</v>
+        <v>13314001045</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>729261588</v>
+        <v>877130041</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08165500000000001</v>
+        <v>0.08678</v>
       </c>
       <c r="J13" t="n">
-        <v>0.07836799999999999</v>
+        <v>0.081105</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00275889</v>
+        <v>0.00417871</v>
       </c>
       <c r="L13" t="n">
-        <v>3.50047</v>
+        <v>5.14712</v>
       </c>
       <c r="M13" t="n">
-        <v>155951756383.7052</v>
+        <v>155966856383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171665603126.5791</v>
+        <v>155966926383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1312,153 +1312,153 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.007907922590261105</v>
+        <v>0.008131159625435827</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.999765</v>
+        <v>531.61</v>
       </c>
       <c r="F14" t="n">
-        <v>9555093003</v>
+        <v>9993028627</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>234322913</v>
+        <v>138577997</v>
       </c>
       <c r="I14" t="n">
-        <v>0.999879</v>
+        <v>544.41</v>
       </c>
       <c r="J14" t="n">
-        <v>0.999135</v>
+        <v>502.16</v>
       </c>
       <c r="K14" t="n">
-        <v>0.00034214</v>
+        <v>29.06</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03423</v>
+        <v>5.78332</v>
       </c>
       <c r="M14" t="n">
-        <v>9556951530.004086</v>
+        <v>18806245.33931784</v>
       </c>
       <c r="N14" t="n">
-        <v>9558143909.30253</v>
+        <v>18806257.93928528</v>
       </c>
       <c r="O14" t="n">
-        <v>1.057</v>
+        <v>797.73</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>45593.90336805556</v>
+        <v>46036.48202546296</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.00585259820861168</v>
+        <v>0.006013239448401412</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>505.06</v>
+        <v>0.999767</v>
       </c>
       <c r="F15" t="n">
-        <v>9497377500</v>
+        <v>9562217003</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>117728327</v>
+        <v>141420739</v>
       </c>
       <c r="I15" t="n">
-        <v>504.23</v>
+        <v>0.999965</v>
       </c>
       <c r="J15" t="n">
-        <v>485.12</v>
+        <v>0.999596</v>
       </c>
       <c r="K15" t="n">
-        <v>9.43</v>
+        <v>9.39e-06</v>
       </c>
       <c r="L15" t="n">
-        <v>1.90225</v>
+        <v>0.00094</v>
       </c>
       <c r="M15" t="n">
-        <v>18805792.94955427</v>
+        <v>9564389019.369761</v>
       </c>
       <c r="N15" t="n">
-        <v>18805870.34941343</v>
+        <v>9565459355.707329</v>
       </c>
       <c r="O15" t="n">
-        <v>797.73</v>
+        <v>1.057</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>46036.48202546296</v>
+        <v>45593.90336805556</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005815090684223016</v>
+        <v>0.005738493224667324</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1477,28 +1477,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>79.05</v>
+        <v>80.44</v>
       </c>
       <c r="F16" t="n">
-        <v>9318236388</v>
+        <v>9482447599</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>156128201</v>
+        <v>112012858</v>
       </c>
       <c r="I16" t="n">
-        <v>79.44</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>77.11</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="L16" t="n">
-        <v>1.94453</v>
+        <v>1.97292</v>
       </c>
       <c r="M16" t="n">
         <v>117882016</v>
@@ -1513,19 +1513,19 @@
         <v>46276.58553240741</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.005698672403551492</v>
+        <v>0.005687621007443865</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1544,31 +1544,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.01306588</v>
+        <v>0.01278862</v>
       </c>
       <c r="F17" t="n">
-        <v>9257577125</v>
+        <v>9073126084</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>21935510</v>
+        <v>27820992</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01345016</v>
+        <v>0.01310816</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01191321</v>
+        <v>0.01260467</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.00015046852519901</v>
+        <v>-0.000263625237508211</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1385</v>
+        <v>-2.01977</v>
       </c>
       <c r="M17" t="n">
-        <v>709233558707.1311</v>
+        <v>709234074452.8706</v>
       </c>
       <c r="N17" t="n">
         <v>1142408526965.963</v>
@@ -1580,19 +1580,19 @@
         <v>46259.82847222222</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005659251820378704</v>
+        <v>0.005426579906706606</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1611,28 +1611,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.31</v>
+        <v>11.82</v>
       </c>
       <c r="F18" t="n">
-        <v>8462869436</v>
+        <v>8843197796</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>441283863</v>
+        <v>465095252</v>
       </c>
       <c r="I18" t="n">
-        <v>11.32</v>
+        <v>11.95</v>
       </c>
       <c r="J18" t="n">
-        <v>10.62</v>
+        <v>11.22</v>
       </c>
       <c r="K18" t="n">
-        <v>0.661099</v>
+        <v>0.575928</v>
       </c>
       <c r="L18" t="n">
-        <v>6.20719</v>
+        <v>5.12126</v>
       </c>
       <c r="M18" t="n">
         <v>748099970.424884</v>
@@ -1647,19 +1647,19 @@
         <v>44325.67635416667</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005142795816746102</v>
+        <v>0.005279945216883001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1678,28 +1678,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.92</v>
+        <v>8.9</v>
       </c>
       <c r="F19" t="n">
-        <v>8202960071</v>
+        <v>8184667580</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>156127</v>
+        <v>76720</v>
       </c>
       <c r="I19" t="n">
-        <v>9</v>
+        <v>8.93</v>
       </c>
       <c r="J19" t="n">
-        <v>8.83</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.04280543</v>
+        <v>-0.01999754405595056</v>
       </c>
       <c r="L19" t="n">
-        <v>0.48232</v>
+        <v>-0.22424</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1714,19 +1714,19 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004973888740833076</v>
+        <v>0.004859973516999635</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1745,28 +1745,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.201196</v>
+        <v>0.21587</v>
       </c>
       <c r="F20" t="n">
-        <v>7544303914</v>
+        <v>8101095616</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>438569875</v>
+        <v>552742767</v>
       </c>
       <c r="I20" t="n">
-        <v>0.201745</v>
+        <v>0.216996</v>
       </c>
       <c r="J20" t="n">
-        <v>0.190464</v>
+        <v>0.199529</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00979934</v>
+        <v>0.01551854</v>
       </c>
       <c r="L20" t="n">
-        <v>5.1199</v>
+        <v>7.74566</v>
       </c>
       <c r="M20" t="n">
         <v>37522923322.16203</v>
@@ -1781,19 +1781,19 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R20" t="b">
         <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004545848429507704</v>
+        <v>0.004806676251466612</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1812,31 +1812,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.184749</v>
+        <v>0.186694</v>
       </c>
       <c r="F21" t="n">
-        <v>6432935996</v>
+        <v>6499674331</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>253193320</v>
+        <v>190708288</v>
       </c>
       <c r="I21" t="n">
-        <v>0.186542</v>
+        <v>0.18919</v>
       </c>
       <c r="J21" t="n">
-        <v>0.172569</v>
+        <v>0.182408</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01109385</v>
+        <v>0.00268673</v>
       </c>
       <c r="L21" t="n">
-        <v>6.38843</v>
+        <v>1.46012</v>
       </c>
       <c r="M21" t="n">
-        <v>34845006961.13458</v>
+        <v>34845172352.88166</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70148</v>
@@ -1848,421 +1848,421 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.003823604714692248</v>
+        <v>0.003785384284977933</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ethena-usde</t>
+          <t>uniswap</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>usde</t>
+          <t>uni</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ethena USDe</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.999393</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>4730616606</v>
+        <v>5460492757</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>39878908</v>
+        <v>2254307216</v>
       </c>
       <c r="I22" t="n">
-        <v>0.999579</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.998964</v>
+        <v>7.03</v>
       </c>
       <c r="K22" t="n">
-        <v>0.00023556</v>
+        <v>1.75</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02358</v>
+        <v>24.79101</v>
       </c>
       <c r="M22" t="n">
-        <v>4733546802.134655</v>
+        <v>621108422.6104751</v>
       </c>
       <c r="N22" t="n">
-        <v>4735546801.034656</v>
+        <v>888250418.9163101</v>
       </c>
       <c r="O22" t="n">
-        <v>1.034</v>
+        <v>44.92</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>46000.38208333333</v>
+        <v>44318.89240740741</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.002717319874071196</v>
+        <v>0.003122655618142922</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>bitcoin-cash</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>bch</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Dai</t>
+          <t>Bitcoin Cash</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.999919</v>
+        <v>249.65</v>
       </c>
       <c r="F23" t="n">
-        <v>4585446425</v>
+        <v>5016474464</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>344249986</v>
+        <v>244794593</v>
       </c>
       <c r="I23" t="n">
+        <v>250.55</v>
+      </c>
+      <c r="J23" t="n">
+        <v>226.76</v>
+      </c>
+      <c r="K23" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>10.83102</v>
+      </c>
+      <c r="M23" t="n">
+        <v>20090740.52165077</v>
+      </c>
+      <c r="N23" t="n">
+        <v>20090768.64665077</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3785.82</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <v>43088.66666666666</v>
+      </c>
+      <c r="Q23" s="1" t="n">
+        <v>46283.56203703704</v>
+      </c>
+      <c r="R23" t="b">
         <v>1</v>
       </c>
-      <c r="J23" t="n">
-        <v>0.999743</v>
-      </c>
-      <c r="K23" t="n">
-        <v>-0.000207849320602471</v>
-      </c>
-      <c r="L23" t="n">
-        <v>-0.02078</v>
-      </c>
-      <c r="M23" t="n">
-        <v>4586319939.449437</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4567710822.886193</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P23" s="1" t="n">
-        <v>43902.79363425926</v>
-      </c>
-      <c r="Q23" s="1" t="n">
-        <v>46282.59108796297</v>
-      </c>
-      <c r="R23" t="b">
-        <v>0</v>
-      </c>
       <c r="S23" t="n">
-        <v>0.002622978253166253</v>
+        <v>0.002839486960487097</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>bitcoin-cash</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>bch</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Bitcoin Cash</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>227.71</v>
+        <v>3.65</v>
       </c>
       <c r="F24" t="n">
-        <v>4574710821</v>
+        <v>4768990338</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>162583254</v>
+        <v>2076188545</v>
       </c>
       <c r="I24" t="n">
-        <v>227.22</v>
+        <v>3.61</v>
       </c>
       <c r="J24" t="n">
-        <v>214.03</v>
+        <v>2.81</v>
       </c>
       <c r="K24" t="n">
-        <v>10.97</v>
+        <v>0.793762</v>
       </c>
       <c r="L24" t="n">
-        <v>5.05925</v>
+        <v>27.77192</v>
       </c>
       <c r="M24" t="n">
-        <v>20090593.64665077</v>
+        <v>1306651055</v>
       </c>
       <c r="N24" t="n">
-        <v>20090631.14665077</v>
+        <v>1306651049</v>
       </c>
       <c r="O24" t="n">
-        <v>3785.82</v>
+        <v>20.44</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>44577.59010416667</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R24" t="b">
         <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002616001515410766</v>
+        <v>0.002681656193477358</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>uniswap</t>
+          <t>ethena-usde</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>uni</t>
+          <t>usde</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Ethena USDe</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7.27</v>
+        <v>0.999391</v>
       </c>
       <c r="F25" t="n">
-        <v>4510962530</v>
+        <v>4772921019</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>1031082317</v>
+        <v>31566827</v>
       </c>
       <c r="I25" t="n">
-        <v>7.23</v>
+        <v>0.99955</v>
       </c>
       <c r="J25" t="n">
-        <v>6.05</v>
+        <v>0.9990830000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>1.14</v>
+        <v>-6.692927984952599e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>18.51215</v>
+        <v>-0.0067</v>
       </c>
       <c r="M25" t="n">
-        <v>621120422.6104751</v>
+        <v>4775827775.692125</v>
       </c>
       <c r="N25" t="n">
-        <v>888368418.9163101</v>
+        <v>4798657893.686825</v>
       </c>
       <c r="O25" t="n">
-        <v>44.92</v>
+        <v>1.034</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>44318.89240740741</v>
+        <v>46000.38208333333</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002574573468263397</v>
+        <v>0.002684162949797966</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>usd1-wlfi</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>usd1</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>USD1</t>
+          <t>Dai</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.999027</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>4342369348</v>
+        <v>4578867048</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>1095614662</v>
+        <v>257162840</v>
       </c>
       <c r="I26" t="n">
-        <v>0.999374</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>0.998899</v>
+        <v>0.999726</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.000183543199977265</v>
+        <v>0.00019033</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.01837</v>
+        <v>0.01904</v>
       </c>
       <c r="M26" t="n">
-        <v>4346607629.555521</v>
+        <v>4578574950.264173</v>
       </c>
       <c r="N26" t="n">
-        <v>4346607629.555521</v>
+        <v>4575207021.076258</v>
       </c>
       <c r="O26" t="n">
-        <v>1.048</v>
+        <v>1.22</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>46212.42696759259</v>
+        <v>43902.79363425926</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002465009961806089</v>
+        <v>0.002560406781759069</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>litecoin</t>
+          <t>usd1-wlfi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ltc</t>
+          <t>usd1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>USD1</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>52.69</v>
+        <v>0.999174</v>
       </c>
       <c r="F27" t="n">
-        <v>4088774742</v>
+        <v>4343272623</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>240686831</v>
+        <v>950429360</v>
       </c>
       <c r="I27" t="n">
-        <v>53.04</v>
+        <v>0.999248</v>
       </c>
       <c r="J27" t="n">
-        <v>50.23</v>
+        <v>0.998936</v>
       </c>
       <c r="K27" t="n">
-        <v>2.43</v>
+        <v>5.078e-05</v>
       </c>
       <c r="L27" t="n">
-        <v>4.8292</v>
+        <v>0.00508</v>
       </c>
       <c r="M27" t="n">
-        <v>77617035.66946276</v>
+        <v>4346798749.096848</v>
       </c>
       <c r="N27" t="n">
-        <v>77619816.92657901</v>
+        <v>4346798749.096848</v>
       </c>
       <c r="O27" t="n">
-        <v>410.26</v>
+        <v>1.048</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>44325.80077546297</v>
+        <v>46212.42696759259</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002300206652903482</v>
+        <v>0.002410158564218973</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2281,34 +2281,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.100303</v>
+        <v>0.108678</v>
       </c>
       <c r="F28" t="n">
-        <v>3974102558</v>
+        <v>4305137059</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>21161075</v>
+        <v>20082534</v>
       </c>
       <c r="I28" t="n">
-        <v>0.102749</v>
+        <v>0.112495</v>
       </c>
       <c r="J28" t="n">
-        <v>0.08894199999999999</v>
+        <v>0.098889</v>
       </c>
       <c r="K28" t="n">
-        <v>0.00987384</v>
+        <v>0.00801662</v>
       </c>
       <c r="L28" t="n">
-        <v>10.91892</v>
+        <v>7.96391</v>
       </c>
       <c r="M28" t="n">
-        <v>39606318586.9813</v>
+        <v>39627697476.64375</v>
       </c>
       <c r="N28" t="n">
-        <v>39607203165.6683</v>
+        <v>39628294476.72729</v>
       </c>
       <c r="O28" t="n">
         <v>0.194152</v>
@@ -2317,86 +2317,86 @@
         <v>46056.00148148148</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R28" t="b">
         <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002225684739127884</v>
+        <v>0.002385837952575101</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>litecoin</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>ltc</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2.87</v>
+        <v>55.17</v>
       </c>
       <c r="F29" t="n">
-        <v>3744407634</v>
+        <v>4282135782</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>884382460</v>
+        <v>278606277</v>
       </c>
       <c r="I29" t="n">
-        <v>2.89</v>
+        <v>55.96</v>
       </c>
       <c r="J29" t="n">
-        <v>2.43</v>
+        <v>52.64</v>
       </c>
       <c r="K29" t="n">
-        <v>0.416577</v>
+        <v>2.38</v>
       </c>
       <c r="L29" t="n">
-        <v>16.97419</v>
+        <v>4.50704</v>
       </c>
       <c r="M29" t="n">
-        <v>1306570064</v>
+        <v>77620798.18076394</v>
       </c>
       <c r="N29" t="n">
-        <v>1306570052</v>
+        <v>77620816.93088555</v>
       </c>
       <c r="O29" t="n">
-        <v>20.44</v>
+        <v>410.26</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>44577.59010416667</v>
+        <v>44325.80077546297</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002076413096049904</v>
+        <v>0.002371169095829464</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2415,34 +2415,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="F30" t="n">
-        <v>3723196551</v>
+        <v>3824472057</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>37803025</v>
+        <v>36381124</v>
       </c>
       <c r="I30" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="J30" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="K30" t="n">
-        <v>0.02461108</v>
+        <v>0.03610414</v>
       </c>
       <c r="L30" t="n">
-        <v>1.88162</v>
+        <v>2.71316</v>
       </c>
       <c r="M30" t="n">
-        <v>2795318240.360763</v>
+        <v>2797860400.195174</v>
       </c>
       <c r="N30" t="n">
-        <v>5250683882.598795</v>
+        <v>5251239978.193309</v>
       </c>
       <c r="O30" t="n">
         <v>8.25</v>
@@ -2451,19 +2451,19 @@
         <v>45457.69225694444</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.002062628667749375</v>
+        <v>0.002079298187109911</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2482,34 +2482,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>7.6</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>3365564812</v>
+        <v>3564409188</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>315743529</v>
+        <v>341203798</v>
       </c>
       <c r="I31" t="n">
-        <v>7.62</v>
+        <v>8.02</v>
       </c>
       <c r="J31" t="n">
-        <v>7.18</v>
+        <v>7.53</v>
       </c>
       <c r="K31" t="n">
-        <v>0.363565</v>
+        <v>0.460474</v>
       </c>
       <c r="L31" t="n">
-        <v>5.02368</v>
+        <v>6.06813</v>
       </c>
       <c r="M31" t="n">
-        <v>442854991.1362558</v>
+        <v>442859844.5502368</v>
       </c>
       <c r="N31" t="n">
-        <v>469523691.2347694</v>
+        <v>469528544.5502368</v>
       </c>
       <c r="O31" t="n">
         <v>144.96</v>
@@ -2518,19 +2518,19 @@
         <v>44521.26314814815</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R31" t="b">
         <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0.001830214836534867</v>
+        <v>0.001913445440315867</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2549,31 +2549,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.074882</v>
+        <v>0.077292</v>
       </c>
       <c r="F32" t="n">
-        <v>3277165955</v>
+        <v>3386438008</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>83369773</v>
+        <v>84016076</v>
       </c>
       <c r="I32" t="n">
-        <v>0.075281</v>
+        <v>0.078053</v>
       </c>
       <c r="J32" t="n">
-        <v>0.07199800000000001</v>
+        <v>0.073949</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0021675</v>
+        <v>0.00272201</v>
       </c>
       <c r="L32" t="n">
-        <v>2.98084</v>
+        <v>3.65028</v>
       </c>
       <c r="M32" t="n">
-        <v>43831556055.85902</v>
+        <v>43831556054.63917</v>
       </c>
       <c r="N32" t="n">
         <v>50000000000</v>
@@ -2585,19 +2585,19 @@
         <v>44454.11143518519</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001772767147222388</v>
+        <v>0.001799945927037878</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2616,34 +2616,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.999893</v>
+        <v>0.999974</v>
       </c>
       <c r="F33" t="n">
-        <v>3264423128</v>
+        <v>3277171964</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>1221877042</v>
+        <v>987110058</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>0.999796</v>
+        <v>0.999846</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.000157751230601577</v>
+        <v>4.477e-05</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.01577</v>
+        <v>0.00448</v>
       </c>
       <c r="M33" t="n">
-        <v>3264764991.306926</v>
+        <v>3277253193.314953</v>
       </c>
       <c r="N33" t="n">
-        <v>3264762512.446477</v>
+        <v>3277764991.302639</v>
       </c>
       <c r="O33" t="n">
         <v>1.65</v>
@@ -2652,153 +2652,153 @@
         <v>45686.67436342593</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R33" t="b">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001764485977178995</v>
+        <v>0.001730262493957246</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>shiba-inu</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>shib</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Shiba Inu</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5.1e-06</v>
+        <v>0.799369</v>
       </c>
       <c r="F34" t="n">
-        <v>2998823174</v>
+        <v>3275696110</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>91696970</v>
+        <v>609142705</v>
       </c>
       <c r="I34" t="n">
-        <v>5.08e-06</v>
+        <v>0.800675</v>
       </c>
       <c r="J34" t="n">
-        <v>4.75e-06</v>
+        <v>0.722626</v>
       </c>
       <c r="K34" t="n">
-        <v>3.30119e-07</v>
+        <v>0.07224700000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>6.92423</v>
+        <v>9.936070000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>589239162555937.8</v>
+        <v>4096537146.540959</v>
       </c>
       <c r="N34" t="n">
-        <v>589496186210625.8</v>
+        <v>10000000000</v>
       </c>
       <c r="O34" t="n">
-        <v>8.616e-05</v>
+        <v>5.35</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>44496.82980324074</v>
+        <v>45661.62243055556</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R34" t="b">
         <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001591880763077633</v>
+        <v>0.001729321281393114</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>shiba-inu</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>shib</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>Shiba Inu</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.730534</v>
+        <v>5.37e-06</v>
       </c>
       <c r="F35" t="n">
-        <v>2991065166</v>
+        <v>3163842188</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>540010749</v>
+        <v>107036297</v>
       </c>
       <c r="I35" t="n">
-        <v>0.729483</v>
+        <v>5.44e-06</v>
       </c>
       <c r="J35" t="n">
-        <v>0.678101</v>
+        <v>5.06e-06</v>
       </c>
       <c r="K35" t="n">
-        <v>0.04594057</v>
+        <v>3.03228e-07</v>
       </c>
       <c r="L35" t="n">
-        <v>6.71063</v>
+        <v>5.98639</v>
       </c>
       <c r="M35" t="n">
-        <v>4096537146.540959</v>
+        <v>589239049876142.6</v>
       </c>
       <c r="N35" t="n">
-        <v>10000000000</v>
+        <v>589496073530830.6</v>
       </c>
       <c r="O35" t="n">
-        <v>5.35</v>
+        <v>8.616e-05</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>45661.62243055556</v>
+        <v>44496.82980324074</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R35" t="b">
         <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001586839073078545</v>
+        <v>0.001657987452481972</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2817,34 +2817,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.058095</v>
+        <v>0.059222</v>
       </c>
       <c r="F36" t="n">
-        <v>2888376470</v>
+        <v>2944707211</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>9904469</v>
+        <v>8117944</v>
       </c>
       <c r="I36" t="n">
-        <v>0.058871</v>
+        <v>0.059787</v>
       </c>
       <c r="J36" t="n">
-        <v>0.054783</v>
+        <v>0.057196</v>
       </c>
       <c r="K36" t="n">
-        <v>0.00273442</v>
+        <v>0.00141129</v>
       </c>
       <c r="L36" t="n">
-        <v>4.93931</v>
+        <v>2.44125</v>
       </c>
       <c r="M36" t="n">
-        <v>49726994055.42311</v>
+        <v>49728972620.92609</v>
       </c>
       <c r="N36" t="n">
-        <v>98927036947.05304</v>
+        <v>98928969658.44186</v>
       </c>
       <c r="O36" t="n">
         <v>0.891544</v>
@@ -2853,376 +2853,376 @@
         <v>44523.66666666666</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001520104858362267</v>
+        <v>0.001518236099303984</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>paypal-usd</t>
+          <t>memecore</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>pyusd</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PayPal USD</t>
+          <t>MemeCore</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.999484</v>
+        <v>1.29</v>
       </c>
       <c r="F37" t="n">
-        <v>2812163218</v>
+        <v>2931281436</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>126246032</v>
+        <v>1724362</v>
       </c>
       <c r="I37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.16002</v>
+      </c>
+      <c r="L37" t="n">
+        <v>14.17474</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2274172592.558846</v>
+      </c>
+      <c r="N37" t="n">
+        <v>5415562438.891223</v>
+      </c>
+      <c r="O37" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="P37" s="1" t="n">
+        <v>46205.17638888889</v>
+      </c>
+      <c r="Q37" s="1" t="n">
+        <v>46283.56203703704</v>
+      </c>
+      <c r="R37" t="b">
         <v>1</v>
       </c>
-      <c r="J37" t="n">
-        <v>0.998742</v>
-      </c>
-      <c r="K37" t="n">
-        <v>-6.6882718195882e-05</v>
-      </c>
-      <c r="L37" t="n">
-        <v>-0.00669</v>
-      </c>
-      <c r="M37" t="n">
-        <v>2813570609.128083</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2818512719.760797</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.021</v>
-      </c>
-      <c r="P37" s="1" t="n">
-        <v>45222.61454861111</v>
-      </c>
-      <c r="Q37" s="1" t="n">
-        <v>46282.59108796297</v>
-      </c>
-      <c r="R37" t="b">
-        <v>0</v>
-      </c>
       <c r="S37" t="n">
-        <v>0.00147057621771039</v>
+        <v>0.00150967393250889</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>tether-gold</t>
+          <t>bittensor</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>xaut</t>
+          <t>tao</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tether Gold</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4367.42</v>
+        <v>247.27</v>
       </c>
       <c r="F38" t="n">
-        <v>2720856987</v>
+        <v>2804711067</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
       </c>
       <c r="H38" t="n">
-        <v>366365385</v>
+        <v>235965657</v>
       </c>
       <c r="I38" t="n">
-        <v>4372.55</v>
+        <v>251.24</v>
       </c>
       <c r="J38" t="n">
-        <v>4242.72</v>
+        <v>225.84</v>
       </c>
       <c r="K38" t="n">
-        <v>35.76</v>
+        <v>20.55</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8255</v>
+        <v>9.063789999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>622823.6595320001</v>
+        <v>11339645.9251</v>
       </c>
       <c r="N38" t="n">
-        <v>707747.089</v>
+        <v>21000000</v>
       </c>
       <c r="O38" t="n">
-        <v>5504.62</v>
+        <v>757.6</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>46050.66666666666</v>
+        <v>45358.44833333333</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.00141123911575237</v>
+        <v>0.001428954822387153</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>blackrock-usd-institutional-digital-liquidity-fund</t>
+          <t>paypal-usd</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>buidl</t>
+          <t>pyusd</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund</t>
+          <t>PayPal USD</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0.999743</v>
       </c>
       <c r="F39" t="n">
-        <v>2651746553</v>
+        <v>2788292790</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>84854717</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0.998889</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>0.00039146</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>0.03917</v>
       </c>
       <c r="M39" t="n">
-        <v>2651746553.070448</v>
+        <v>2789009291.248121</v>
       </c>
       <c r="N39" t="n">
-        <v>2651746553.070449</v>
+        <v>2789009291.248121</v>
       </c>
       <c r="O39" t="n">
-        <v>1</v>
+        <v>1.021</v>
       </c>
       <c r="P39" s="1" t="n">
-        <v>45699.87511574074</v>
+        <v>45222.61454861111</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001366326377336731</v>
+        <v>0.001418484214458593</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>bittensor</t>
+          <t>tether-gold</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>tao</t>
+          <t>xaut</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>Tether Gold</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>227.62</v>
+        <v>4362.11</v>
       </c>
       <c r="F40" t="n">
-        <v>2579063424</v>
+        <v>2716798606</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>172806682</v>
+        <v>186499015</v>
       </c>
       <c r="I40" t="n">
-        <v>228.93</v>
+        <v>4392.46</v>
       </c>
       <c r="J40" t="n">
-        <v>214.05</v>
+        <v>4333.61</v>
       </c>
       <c r="K40" t="n">
-        <v>12.7</v>
+        <v>0.821041</v>
       </c>
       <c r="L40" t="n">
-        <v>5.90712</v>
+        <v>0.01883</v>
       </c>
       <c r="M40" t="n">
-        <v>11339645.9251</v>
+        <v>622823.6595320001</v>
       </c>
       <c r="N40" t="n">
-        <v>21000000</v>
+        <v>707747.089</v>
       </c>
       <c r="O40" t="n">
-        <v>757.6</v>
+        <v>5504.62</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>45358.44833333333</v>
+        <v>46050.66666666666</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001319091854688425</v>
+        <v>0.00137288944407944</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>memecore</t>
+          <t>hashnote-usyc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>usyc</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MemeCore</t>
+          <t>Circle USYC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="F41" t="n">
-        <v>2563032234</v>
+        <v>2556077986</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
       </c>
       <c r="H41" t="n">
-        <v>1702992</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="J41" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="K41" t="n">
-        <v>0.01359534</v>
+        <v>0.00034598</v>
       </c>
       <c r="L41" t="n">
-        <v>1.22081</v>
+        <v>0.03042</v>
       </c>
       <c r="M41" t="n">
-        <v>2273802309.23221</v>
+        <v>2246365281.581388</v>
       </c>
       <c r="N41" t="n">
-        <v>5415192155.739435</v>
+        <v>2246365281.581388</v>
       </c>
       <c r="O41" t="n">
-        <v>5.64</v>
+        <v>1.14</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>46205.17638888889</v>
+        <v>46283.52430555555</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001308673679005121</v>
+        <v>0.001270391319699209</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>hashnote-usyc</t>
+          <t>blackrock-usd-institutional-digital-liquidity-fund</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>usyc</t>
+          <t>buidl</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Circle USYC</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>2555275633</v>
+        <v>2401998374</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
@@ -3231,43 +3231,43 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>9.719e-05</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0.008540000000000001</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2246343166.601824</v>
+        <v>2401998374.270448</v>
       </c>
       <c r="N42" t="n">
-        <v>2246365281.581388</v>
+        <v>2401998374.270449</v>
       </c>
       <c r="O42" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>46282.53148148148</v>
+        <v>45699.87511574074</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001303632903371915</v>
+        <v>0.001172128438214346</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3286,28 +3286,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>112.03</v>
+        <v>113.96</v>
       </c>
       <c r="F43" t="n">
-        <v>2351966933</v>
+        <v>2393106804</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>19050807</v>
+        <v>24147277</v>
       </c>
       <c r="I43" t="n">
-        <v>112.32</v>
+        <v>114.94</v>
       </c>
       <c r="J43" t="n">
-        <v>108.66</v>
+        <v>111.58</v>
       </c>
       <c r="K43" t="n">
-        <v>2.83</v>
+        <v>1.86</v>
       </c>
       <c r="L43" t="n">
-        <v>2.58897</v>
+        <v>1.65929</v>
       </c>
       <c r="M43" t="n">
         <v>21000000</v>
@@ -3322,19 +3322,19 @@
         <v>45934.66666666666</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001171508853033527</v>
+        <v>0.001166457919722098</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3356,31 +3356,31 @@
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>2344924147</v>
+        <v>2348698435</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>344223044</v>
+        <v>167724819</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>0.999736</v>
+        <v>0.999686</v>
       </c>
       <c r="K44" t="n">
-        <v>1.688e-05</v>
+        <v>4.037e-05</v>
       </c>
       <c r="L44" t="n">
-        <v>0.00169</v>
+        <v>0.00404</v>
       </c>
       <c r="M44" t="n">
-        <v>2344753285.367475</v>
+        <v>2348574551.087477</v>
       </c>
       <c r="N44" t="n">
-        <v>2345208787.367478</v>
+        <v>2348674551.087477</v>
       </c>
       <c r="O44" t="n">
         <v>1.073</v>
@@ -3389,19 +3389,19 @@
         <v>45652.11518518518</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001166931963741596</v>
+        <v>0.001138136883321883</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3423,13 +3423,13 @@
         <v>1.14</v>
       </c>
       <c r="F45" t="n">
-        <v>2209305470</v>
+        <v>2240578177</v>
       </c>
       <c r="G45" t="n">
         <v>44</v>
       </c>
       <c r="H45" t="n">
-        <v>3179687</v>
+        <v>2302257</v>
       </c>
       <c r="I45" t="n">
         <v>1.15</v>
@@ -3438,16 +3438,16 @@
         <v>1.14</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.002401500943753243</v>
+        <v>0.00095087</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.20949</v>
+        <v>0.08312</v>
       </c>
       <c r="M45" t="n">
-        <v>1931966768.507879</v>
+        <v>1955826437.104192</v>
       </c>
       <c r="N45" t="n">
-        <v>1931966768.507879</v>
+        <v>1955826437.104191</v>
       </c>
       <c r="O45" t="n">
         <v>1.26</v>
@@ -3456,287 +3456,287 @@
         <v>45377.89175925926</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.001078797570541632</v>
+        <v>0.001069184164918315</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>aster-2</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>aster</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Aave</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.738395</v>
+        <v>138.14</v>
       </c>
       <c r="F46" t="n">
-        <v>1996127339</v>
+        <v>2131202453</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>127611461</v>
+        <v>337041822</v>
       </c>
       <c r="I46" t="n">
-        <v>0.74396</v>
+        <v>137.77</v>
       </c>
       <c r="J46" t="n">
-        <v>0.672885</v>
+        <v>124.21</v>
       </c>
       <c r="K46" t="n">
-        <v>0.060384</v>
+        <v>13.85</v>
       </c>
       <c r="L46" t="n">
-        <v>8.906090000000001</v>
+        <v>11.14285</v>
       </c>
       <c r="M46" t="n">
-        <v>2704071066.799731</v>
+        <v>15427945.63274938</v>
       </c>
       <c r="N46" t="n">
-        <v>7799908028.130118</v>
+        <v>16000000</v>
       </c>
       <c r="O46" t="n">
-        <v>2.41</v>
+        <v>661.6900000000001</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>45924.13766203704</v>
+        <v>44334.55554398148</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R46" t="b">
         <v>1</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0009402596815516997</v>
+        <v>0.0009994307844079005</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>aster-2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>aster</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Aave</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>125.7</v>
+        <v>0.750459</v>
       </c>
       <c r="F47" t="n">
-        <v>1939069708</v>
+        <v>2029711486</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>303025650</v>
+        <v>105439785</v>
       </c>
       <c r="I47" t="n">
-        <v>124.97</v>
+        <v>0.7589</v>
       </c>
       <c r="J47" t="n">
-        <v>113.33</v>
+        <v>0.735137</v>
       </c>
       <c r="K47" t="n">
-        <v>9.1</v>
+        <v>0.01330934</v>
       </c>
       <c r="L47" t="n">
-        <v>7.80158</v>
+        <v>1.80551</v>
       </c>
       <c r="M47" t="n">
-        <v>15427787.0612566</v>
+        <v>2704071066.799731</v>
       </c>
       <c r="N47" t="n">
-        <v>16000000</v>
+        <v>7799908028.130118</v>
       </c>
       <c r="O47" t="n">
-        <v>661.6900000000001</v>
+        <v>2.41</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>44334.55554398148</v>
+        <v>45924.13766203704</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0009031796878749257</v>
+        <v>0.0009347058364887352</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>pax-gold</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>paxg</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>PAX Gold</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4369.53</v>
+        <v>0.00421794</v>
       </c>
       <c r="F48" t="n">
-        <v>1898790572</v>
+        <v>1974322461</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>265197590</v>
+        <v>178993049</v>
       </c>
       <c r="I48" t="n">
-        <v>4375.21</v>
+        <v>0.00432743</v>
       </c>
       <c r="J48" t="n">
-        <v>4246.28</v>
+        <v>0.00390878</v>
       </c>
       <c r="K48" t="n">
-        <v>31.42</v>
+        <v>0.00024496</v>
       </c>
       <c r="L48" t="n">
-        <v>0.72435</v>
+        <v>6.16552</v>
       </c>
       <c r="M48" t="n">
-        <v>434499.367539</v>
+        <v>467830826317.6539</v>
       </c>
       <c r="N48" t="n">
-        <v>434499.367539</v>
+        <v>833342646572.925</v>
       </c>
       <c r="O48" t="n">
-        <v>5619.09</v>
+        <v>0.00881908</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>46050.93814814815</v>
+        <v>45914.36296296296</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0008770035203402813</v>
+        <v>0.0008993819858605475</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>polkadot</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>dot</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.00404275</v>
+        <v>1.15</v>
       </c>
       <c r="F49" t="n">
-        <v>1892522088</v>
+        <v>1967870820</v>
       </c>
       <c r="G49" t="n">
         <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>204354174</v>
+        <v>281422394</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0040652</v>
+        <v>1.17</v>
       </c>
       <c r="J49" t="n">
-        <v>0.00357329</v>
+        <v>1.028</v>
       </c>
       <c r="K49" t="n">
-        <v>0.00043942</v>
+        <v>0.119869</v>
       </c>
       <c r="L49" t="n">
-        <v>12.19483</v>
+        <v>11.58255</v>
       </c>
       <c r="M49" t="n">
-        <v>468029630136.9791</v>
+        <v>1703333666.274981</v>
       </c>
       <c r="N49" t="n">
-        <v>833533630174.015</v>
+        <v>1703340562.729311</v>
       </c>
       <c r="O49" t="n">
-        <v>0.00881908</v>
+        <v>54.98</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>45914.36296296296</v>
+        <v>44504.25704861111</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R49" t="b">
         <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0008729298260243893</v>
+        <v>0.0008952675100597784</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3755,28 +3755,28 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.566157</v>
+        <v>0.589264</v>
       </c>
       <c r="F50" t="n">
-        <v>1869179216</v>
+        <v>1946784134</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>30598666</v>
+        <v>38160355</v>
       </c>
       <c r="I50" t="n">
-        <v>0.56815</v>
+        <v>0.597494</v>
       </c>
       <c r="J50" t="n">
-        <v>0.539739</v>
+        <v>0.56402</v>
       </c>
       <c r="K50" t="n">
-        <v>0.02107673</v>
+        <v>0.02248901</v>
       </c>
       <c r="L50" t="n">
-        <v>3.86672</v>
+        <v>3.96789</v>
       </c>
       <c r="M50" t="n">
         <v>3302294382.53684</v>
@@ -3791,1091 +3791,1091 @@
         <v>45938.71164351852</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R50" t="b">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0008577600138364675</v>
+        <v>0.000881819666438998</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>ondo-finance</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>ondo</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>Ondo</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.680604</v>
+        <v>0.395727</v>
       </c>
       <c r="F51" t="n">
-        <v>1839698066</v>
+        <v>1927543245</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>7929620</v>
+        <v>285266113</v>
       </c>
       <c r="I51" t="n">
-        <v>0.772931</v>
+        <v>0.39866</v>
       </c>
       <c r="J51" t="n">
-        <v>0.6681009999999999</v>
+        <v>0.36607</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.08474640409757295</v>
+        <v>0.02897538</v>
       </c>
       <c r="L51" t="n">
-        <v>-11.07289</v>
+        <v>7.90055</v>
       </c>
       <c r="M51" t="n">
-        <v>2708142280.000001</v>
+        <v>4869330647</v>
       </c>
       <c r="N51" t="n">
         <v>10000000000</v>
       </c>
       <c r="O51" t="n">
-        <v>0.789172</v>
+        <v>2.14</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>46281.50775462963</v>
+        <v>45641.69166666667</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R51" t="b">
         <v>1</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0008386011241940983</v>
+        <v>0.0008695489631906642</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>world-liberty-financial</t>
+          <t>pax-gold</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>wlfi</t>
+          <t>paxg</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>World Liberty Financial</t>
+          <t>PAX Gold</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.05792</v>
+        <v>4359.77</v>
       </c>
       <c r="F52" t="n">
-        <v>1840656511</v>
+        <v>1894268516</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>32604826</v>
+        <v>160238224</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0594</v>
+        <v>4390.95</v>
       </c>
       <c r="J52" t="n">
-        <v>0.056783</v>
+        <v>4332.04</v>
       </c>
       <c r="K52" t="n">
-        <v>0.00108228</v>
+        <v>-3.186490241558204</v>
       </c>
       <c r="L52" t="n">
-        <v>1.90417</v>
+        <v>-0.07303999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>31777382106</v>
+        <v>434499.367539</v>
       </c>
       <c r="N52" t="n">
-        <v>100000000000</v>
+        <v>434499.367539</v>
       </c>
       <c r="O52" t="n">
-        <v>0.331336</v>
+        <v>5619.09</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>45901.18065972222</v>
+        <v>46050.93814814815</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R52" t="b">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0008392239880234699</v>
+        <v>0.0008483283051832443</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ondo-finance</t>
+          <t>world-liberty-financial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ondo</t>
+          <t>wlfi</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ondo</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.37134</v>
+        <v>0.057868</v>
       </c>
       <c r="F53" t="n">
-        <v>1806733356</v>
+        <v>1838746916</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>208226419</v>
+        <v>35661533</v>
       </c>
       <c r="I53" t="n">
-        <v>0.372151</v>
+        <v>0.058888</v>
       </c>
       <c r="J53" t="n">
-        <v>0.327035</v>
+        <v>0.05651</v>
       </c>
       <c r="K53" t="n">
-        <v>0.04377661</v>
+        <v>-0.000128102341798934</v>
       </c>
       <c r="L53" t="n">
-        <v>13.36432</v>
+        <v>-0.22088</v>
       </c>
       <c r="M53" t="n">
-        <v>4869330647</v>
+        <v>31777383848</v>
       </c>
       <c r="N53" t="n">
-        <v>10000000000</v>
+        <v>100000000000</v>
       </c>
       <c r="O53" t="n">
-        <v>2.14</v>
+        <v>0.331336</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>45641.69166666667</v>
+        <v>45901.18065972222</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0008171783764049956</v>
+        <v>0.0008129199060457258</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>polkadot</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>dot</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1.038</v>
+        <v>0.67672</v>
       </c>
       <c r="F54" t="n">
-        <v>1769036897</v>
+        <v>1831877381</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>249066985</v>
+        <v>7119621</v>
       </c>
       <c r="I54" t="n">
-        <v>1.041</v>
+        <v>0.748717</v>
       </c>
       <c r="J54" t="n">
-        <v>0.968247</v>
+        <v>0.662755</v>
       </c>
       <c r="K54" t="n">
-        <v>0.070989</v>
+        <v>-0.01025005210828844</v>
       </c>
       <c r="L54" t="n">
-        <v>7.33821</v>
+        <v>-1.49207</v>
       </c>
       <c r="M54" t="n">
-        <v>1703175769.0622</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N54" t="n">
-        <v>1703195639.199992</v>
+        <v>10000000000</v>
       </c>
       <c r="O54" t="n">
-        <v>54.98</v>
+        <v>0.789172</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>44504.25704861111</v>
+        <v>46281.50775462963</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0007926806109552388</v>
+        <v>0.0008085389221193052</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ethena</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ena</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ethena</t>
+          <t>Morpho</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.152906</v>
+        <v>2.43</v>
       </c>
       <c r="F55" t="n">
-        <v>1542817824</v>
+        <v>1697634147</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>415066681</v>
+        <v>39225576</v>
       </c>
       <c r="I55" t="n">
-        <v>0.154895</v>
+        <v>2.44</v>
       </c>
       <c r="J55" t="n">
-        <v>0.140985</v>
+        <v>2.16</v>
       </c>
       <c r="K55" t="n">
-        <v>0.008657750000000001</v>
+        <v>0.28278</v>
       </c>
       <c r="L55" t="n">
-        <v>6.00198</v>
+        <v>13.17526</v>
       </c>
       <c r="M55" t="n">
-        <v>10095312500</v>
+        <v>698811224.6305897</v>
       </c>
       <c r="N55" t="n">
-        <v>15000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="O55" t="n">
-        <v>1.52</v>
+        <v>4.17</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>45393.21892361111</v>
+        <v>45674.19883101852</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R55" t="b">
         <v>1</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0006456678161827802</v>
+        <v>0.0007229265116163064</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>ethena</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>ena</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>USDD</t>
+          <t>Ethena</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.998041</v>
+        <v>0.162882</v>
       </c>
       <c r="F56" t="n">
-        <v>1522673691</v>
+        <v>1643691501</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>3812072</v>
+        <v>395914204</v>
       </c>
       <c r="I56" t="n">
-        <v>0.998827</v>
+        <v>0.171363</v>
       </c>
       <c r="J56" t="n">
-        <v>0.998</v>
+        <v>0.150158</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.000455181043583108</v>
+        <v>0.01117441</v>
       </c>
       <c r="L56" t="n">
-        <v>-0.04559</v>
+        <v>7.36578</v>
       </c>
       <c r="M56" t="n">
-        <v>1525678971</v>
+        <v>10095312500</v>
       </c>
       <c r="N56" t="n">
-        <v>1532416904</v>
+        <v>15000000000</v>
       </c>
       <c r="O56" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>46212.39942129629</v>
+        <v>45393.21892361111</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0006325767657628268</v>
+        <v>0.000688525076137108</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>worldcoin-wld</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>wld</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Morpho</t>
+          <t>Worldcoin</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2.18</v>
+        <v>0.436069</v>
       </c>
       <c r="F57" t="n">
-        <v>1519592899</v>
+        <v>1569712430</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>28306439</v>
+        <v>338897392</v>
       </c>
       <c r="I57" t="n">
-        <v>2.18</v>
+        <v>0.444948</v>
       </c>
       <c r="J57" t="n">
-        <v>2.04</v>
+        <v>0.371902</v>
       </c>
       <c r="K57" t="n">
-        <v>0.088154</v>
+        <v>0.060714</v>
       </c>
       <c r="L57" t="n">
-        <v>4.22391</v>
+        <v>16.17523</v>
       </c>
       <c r="M57" t="n">
-        <v>698762865.4973865</v>
+        <v>3598634710.039344</v>
       </c>
       <c r="N57" t="n">
-        <v>1000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O57" t="n">
-        <v>4.17</v>
+        <v>11.74</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>45674.19883101852</v>
+        <v>45360.67409722223</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0006305746541104966</v>
+        <v>0.0006413455915078677</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>internet-computer</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>icp</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Pepe</t>
+          <t>Internet Computer</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3.6e-06</v>
+        <v>2.82</v>
       </c>
       <c r="F58" t="n">
-        <v>1510642948</v>
+        <v>1567418634</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>241445300</v>
+        <v>51776621</v>
       </c>
       <c r="I58" t="n">
-        <v>3.56e-06</v>
+        <v>2.83</v>
       </c>
       <c r="J58" t="n">
-        <v>3.29e-06</v>
+        <v>2.54</v>
       </c>
       <c r="K58" t="n">
-        <v>2.70054e-07</v>
+        <v>0.267689</v>
       </c>
       <c r="L58" t="n">
-        <v>8.12138</v>
+        <v>10.50747</v>
       </c>
       <c r="M58" t="n">
-        <v>420690000000000</v>
+        <v>556900340.8723615</v>
       </c>
       <c r="N58" t="n">
-        <v>420690000000000</v>
+        <v>556900340.8723615</v>
       </c>
       <c r="O58" t="n">
-        <v>2.803e-05</v>
+        <v>700.65</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>45635.35457175926</v>
+        <v>44326.33741898148</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R58" t="b">
         <v>1</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0006247583571372234</v>
+        <v>0.0006398827438178148</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>htx-dao</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>htx</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HTX DAO</t>
+          <t>Pepe</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1.67e-06</v>
+        <v>3.71e-06</v>
       </c>
       <c r="F59" t="n">
-        <v>1499397010</v>
+        <v>1559649045</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>11595933</v>
+        <v>258560399</v>
       </c>
       <c r="I59" t="n">
-        <v>1.68e-06</v>
+        <v>3.76e-06</v>
       </c>
       <c r="J59" t="n">
-        <v>1.65e-06</v>
+        <v>3.55e-06</v>
       </c>
       <c r="K59" t="n">
-        <v>8.452e-09</v>
+        <v>1.6912e-07</v>
       </c>
       <c r="L59" t="n">
-        <v>0.50884</v>
+        <v>4.7828</v>
       </c>
       <c r="M59" t="n">
-        <v>898232728634017.2</v>
+        <v>420690000000000</v>
       </c>
       <c r="N59" t="n">
-        <v>898232728634017.2</v>
+        <v>420690000000000</v>
       </c>
       <c r="O59" t="n">
-        <v>3.75e-06</v>
+        <v>2.803e-05</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>45629.67800925926</v>
+        <v>45635.35457175926</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R59" t="b">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0006174499690632532</v>
+        <v>0.0006349277585788002</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>internet-computer</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>icp</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Internet Computer</t>
+          <t>Sky</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2.55</v>
+        <v>0.065134</v>
       </c>
       <c r="F60" t="n">
-        <v>1416789101</v>
+        <v>1525648633</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>35975123</v>
+        <v>29729413</v>
       </c>
       <c r="I60" t="n">
-        <v>2.58</v>
+        <v>0.06775200000000001</v>
       </c>
       <c r="J60" t="n">
-        <v>2.44</v>
+        <v>0.058324</v>
       </c>
       <c r="K60" t="n">
-        <v>0.073019</v>
+        <v>0.00648944</v>
       </c>
       <c r="L60" t="n">
-        <v>2.95352</v>
+        <v>11.06578</v>
       </c>
       <c r="M60" t="n">
-        <v>556876586.3612336</v>
+        <v>23420675080.81244</v>
       </c>
       <c r="N60" t="n">
-        <v>556898366.3095052</v>
+        <v>23459804203.60596</v>
       </c>
       <c r="O60" t="n">
-        <v>700.65</v>
+        <v>0.100535</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>44326.33741898148</v>
+        <v>45630.09302083333</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0005637656381562879</v>
+        <v>0.0006132443027897726</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sky</t>
+          <t>USDD</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.059549</v>
+        <v>0.998357</v>
       </c>
       <c r="F61" t="n">
-        <v>1396218627</v>
+        <v>1514047083</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>25029323</v>
+        <v>3654614</v>
       </c>
       <c r="I61" t="n">
-        <v>0.059461</v>
+        <v>0.998753</v>
       </c>
       <c r="J61" t="n">
-        <v>0.055601</v>
+        <v>0.997866</v>
       </c>
       <c r="K61" t="n">
-        <v>0.0023684</v>
+        <v>-0.000135585887886203</v>
       </c>
       <c r="L61" t="n">
-        <v>4.14196</v>
+        <v>-0.01358</v>
       </c>
       <c r="M61" t="n">
-        <v>23422355874.89505</v>
+        <v>1516354806</v>
       </c>
       <c r="N61" t="n">
-        <v>23459804203.60596</v>
+        <v>1516354806</v>
       </c>
       <c r="O61" t="n">
-        <v>0.100535</v>
+        <v>1.24</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>45630.09302083333</v>
+        <v>46212.39942129629</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0005503975218766574</v>
+        <v>0.0006058455190188821</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>usdgo</t>
+          <t>htx-dao</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>usdgo</t>
+          <t>htx</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>USDGO</t>
+          <t>HTX DAO</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1.001</v>
+        <v>1.68e-06</v>
       </c>
       <c r="F62" t="n">
-        <v>1382453846</v>
+        <v>1509737418</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>44979784</v>
+        <v>10066164</v>
       </c>
       <c r="I62" t="n">
-        <v>1.001</v>
+        <v>1.68e-06</v>
       </c>
       <c r="J62" t="n">
-        <v>1</v>
+        <v>1.66e-06</v>
       </c>
       <c r="K62" t="n">
-        <v>0.0004182</v>
+        <v>1.165e-08</v>
       </c>
       <c r="L62" t="n">
-        <v>0.04182</v>
+        <v>0.69768</v>
       </c>
       <c r="M62" t="n">
-        <v>1381786099.16</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="N62" t="n">
-        <v>1381786099.16</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="O62" t="n">
-        <v>1.002</v>
+        <v>3.75e-06</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>46092.00303240741</v>
+        <v>45629.67800925926</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005414522154645813</v>
+        <v>0.0006030970690738337</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>united-stables</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>arb</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>United Stables</t>
+          <t>Arbitrum</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.999395</v>
+        <v>0.212126</v>
       </c>
       <c r="F63" t="n">
-        <v>1379395979</v>
+        <v>1439191946</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>226543219</v>
+        <v>716908068</v>
       </c>
       <c r="I63" t="n">
-        <v>0.99981</v>
+        <v>0.228573</v>
       </c>
       <c r="J63" t="n">
-        <v>0.999273</v>
+        <v>0.161914</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.00020392443719397</v>
+        <v>0.04953603</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.0204</v>
+        <v>30.46682</v>
       </c>
       <c r="M63" t="n">
-        <v>1380129007.8</v>
+        <v>6785574605</v>
       </c>
       <c r="N63" t="n">
-        <v>1381129007.8</v>
+        <v>10000000000</v>
       </c>
       <c r="O63" t="n">
-        <v>1.008</v>
+        <v>2.39</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>46058.54591435185</v>
+        <v>45303.18748842592</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0005394650020623211</v>
+        <v>0.0005581073312074784</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>spiko-amundi-overnight-swap-fund-eur</t>
+          <t>united-stables</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>eursafo</t>
+          <t>u</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Spiko Amundi Overnight Swap Fund (EUR)</t>
+          <t>United Stables</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1.16</v>
+        <v>0.999455</v>
       </c>
       <c r="F64" t="n">
-        <v>1374291233</v>
+        <v>1392401237</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>161853344</v>
       </c>
       <c r="I64" t="n">
-        <v>1.17</v>
+        <v>0.9997200000000001</v>
       </c>
       <c r="J64" t="n">
-        <v>1.16</v>
+        <v>0.999331</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.003745298799760377</v>
+        <v>-7.083445307221e-05</v>
       </c>
       <c r="L64" t="n">
-        <v>-0.32071</v>
+        <v>-0.00709</v>
       </c>
       <c r="M64" t="n">
-        <v>1180601693.72564</v>
+        <v>1393129007.8</v>
       </c>
       <c r="N64" t="n">
-        <v>1180601693.72564</v>
+        <v>1393129007.8</v>
       </c>
       <c r="O64" t="n">
-        <v>1.18</v>
+        <v>1.008</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>46255.48263888889</v>
+        <v>46058.54591435185</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R64" t="b">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0005361475851614768</v>
+        <v>0.0005282669789806067</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>falcon-finance</t>
+          <t>spiko-amundi-overnight-swap-fund-eur</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>usdf</t>
+          <t>eursafo</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Falcon USD</t>
+          <t>Spiko Amundi Overnight Swap Fund (EUR)</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.995373</v>
+        <v>1.16</v>
       </c>
       <c r="F65" t="n">
-        <v>1370746760</v>
+        <v>1389846512</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>515735</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>0.995996</v>
+        <v>1.16</v>
       </c>
       <c r="J65" t="n">
-        <v>0.994539</v>
+        <v>1.16</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.000409648525748874</v>
+        <v>-0.002379406934365225</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.04114</v>
+        <v>-0.20452</v>
       </c>
       <c r="M65" t="n">
-        <v>1377036984.967512</v>
+        <v>1197060629.42477</v>
       </c>
       <c r="N65" t="n">
-        <v>1377036984.967512</v>
+        <v>1197060629.42477</v>
       </c>
       <c r="O65" t="n">
-        <v>1.075</v>
+        <v>1.18</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>45785.55951388889</v>
+        <v>46255.48263888889</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0005338441415357241</v>
+        <v>0.0005266377261765341</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>worldcoin-wld</t>
+          <t>usdgo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>wld</t>
+          <t>usdgo</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Worldcoin</t>
+          <t>USDGO</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.379331</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>1363343419</v>
+        <v>1382196392</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
       </c>
       <c r="H66" t="n">
-        <v>244255382</v>
+        <v>23323261</v>
       </c>
       <c r="I66" t="n">
-        <v>0.380943</v>
+        <v>1.001</v>
       </c>
       <c r="J66" t="n">
-        <v>0.356458</v>
+        <v>1</v>
       </c>
       <c r="K66" t="n">
-        <v>0.01649123</v>
+        <v>-0.000122698445858882</v>
       </c>
       <c r="L66" t="n">
-        <v>4.54505</v>
+        <v>-0.01226</v>
       </c>
       <c r="M66" t="n">
-        <v>3597195132.800737</v>
+        <v>1381786100.28</v>
       </c>
       <c r="N66" t="n">
-        <v>10000000000</v>
+        <v>1381786100.28</v>
       </c>
       <c r="O66" t="n">
-        <v>11.74</v>
+        <v>1.002</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>45360.67409722223</v>
+        <v>46092.00303240741</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0005290329386754617</v>
+        <v>0.0005217589312136743</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4894,28 +4894,28 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="F67" t="n">
-        <v>1338041857</v>
+        <v>1379592305</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
       </c>
       <c r="H67" t="n">
-        <v>10756738</v>
+        <v>11709342</v>
       </c>
       <c r="I67" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="J67" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="K67" t="n">
-        <v>0.008219189999999999</v>
+        <v>0.062015</v>
       </c>
       <c r="L67" t="n">
-        <v>0.43179</v>
+        <v>3.24884</v>
       </c>
       <c r="M67" t="n">
         <v>699992029.6481038</v>
@@ -4930,354 +4930,354 @@
         <v>45653.15375</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0005125902342986798</v>
+        <v>0.0005200981982397538</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>falcon-finance</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>usdf</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>BFUSD</t>
+          <t>Falcon USD</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9990250000000001</v>
+        <v>0.995544</v>
       </c>
       <c r="F68" t="n">
-        <v>1318696189</v>
+        <v>1370895100</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>1777162</v>
+        <v>869400</v>
       </c>
       <c r="I68" t="n">
-        <v>0.999493</v>
+        <v>0.996159</v>
       </c>
       <c r="J68" t="n">
-        <v>0.998989</v>
+        <v>0.994829</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.000245648644366159</v>
+        <v>3.772e-05</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.02458</v>
+        <v>0.00379</v>
       </c>
       <c r="M68" t="n">
-        <v>1320000000</v>
+        <v>1377031690.833898</v>
       </c>
       <c r="N68" t="n">
-        <v>1320000000</v>
+        <v>1377031690.833898</v>
       </c>
       <c r="O68" t="n">
-        <v>1.007</v>
+        <v>1.075</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>45940.56990740741</v>
+        <v>45785.55951388889</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0005000180816428331</v>
+        <v>0.0005145516342714816</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>lighter</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>lit</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Lighter</t>
+          <t>BFUSD</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4.89</v>
+        <v>0.99866</v>
       </c>
       <c r="F69" t="n">
-        <v>1221441356</v>
+        <v>1318230786</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>111076432</v>
+        <v>4686827</v>
       </c>
       <c r="I69" t="n">
-        <v>5.03</v>
+        <v>0.999302</v>
       </c>
       <c r="J69" t="n">
-        <v>4.2</v>
+        <v>0.998594</v>
       </c>
       <c r="K69" t="n">
-        <v>0.689974</v>
+        <v>-0.00041621193149266</v>
       </c>
       <c r="L69" t="n">
-        <v>16.44272</v>
+        <v>-0.04166</v>
       </c>
       <c r="M69" t="n">
-        <v>250000000</v>
+        <v>1320000000</v>
       </c>
       <c r="N69" t="n">
-        <v>1000000000</v>
+        <v>1320000000</v>
       </c>
       <c r="O69" t="n">
-        <v>7.86</v>
+        <v>1.007</v>
       </c>
       <c r="P69" s="1" t="n">
-        <v>46021.04538194444</v>
+        <v>45940.56990740741</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0004368151668096583</v>
+        <v>0.0004809654434841916</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>venice-token</t>
+          <t>ethereum-classic</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>vvv</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Venice Token</t>
+          <t>Ethereum Classic</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>25.17</v>
+        <v>7.95</v>
       </c>
       <c r="F70" t="n">
-        <v>1208891980</v>
+        <v>1258354981</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>66657622</v>
+        <v>57470292</v>
       </c>
       <c r="I70" t="n">
-        <v>25.52</v>
+        <v>7.98</v>
       </c>
       <c r="J70" t="n">
-        <v>21.91</v>
+        <v>7.35</v>
       </c>
       <c r="K70" t="n">
-        <v>2.78</v>
+        <v>0.586362</v>
       </c>
       <c r="L70" t="n">
-        <v>12.40954</v>
+        <v>7.95987</v>
       </c>
       <c r="M70" t="n">
-        <v>48019756.90750279</v>
+        <v>158206077.5915582</v>
       </c>
       <c r="N70" t="n">
-        <v>80994962.03776868</v>
+        <v>158206497.9435582</v>
       </c>
       <c r="O70" t="n">
-        <v>29.19</v>
+        <v>167.09</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>46274.32083333333</v>
+        <v>44322.44053240741</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R70" t="b">
         <v>1</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0004286597146015661</v>
+        <v>0.0004427801894187427</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ethereum-classic</t>
+          <t>venice-token</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>vvv</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Ethereum Classic</t>
+          <t>Venice Token</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>7.39</v>
+        <v>26.11</v>
       </c>
       <c r="F71" t="n">
-        <v>1167747533</v>
+        <v>1254484722</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>53759258</v>
+        <v>79852560</v>
       </c>
       <c r="I71" t="n">
-        <v>7.46</v>
+        <v>27.61</v>
       </c>
       <c r="J71" t="n">
-        <v>7.09</v>
+        <v>24.21</v>
       </c>
       <c r="K71" t="n">
-        <v>0.252723</v>
+        <v>1.5</v>
       </c>
       <c r="L71" t="n">
-        <v>3.53998</v>
+        <v>6.10161</v>
       </c>
       <c r="M71" t="n">
-        <v>158196100.6131674</v>
+        <v>48035223.66929011</v>
       </c>
       <c r="N71" t="n">
-        <v>158196503.4035674</v>
+        <v>81000641.2993075</v>
       </c>
       <c r="O71" t="n">
-        <v>167.09</v>
+        <v>29.19</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>44322.44053240741</v>
+        <v>46274.32083333333</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0004019212081501791</v>
+        <v>0.0004403119666831303</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>lighter</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>arb</t>
+          <t>lit</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Arbitrum</t>
+          <t>Lighter</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.163462</v>
+        <v>4.89</v>
       </c>
       <c r="F72" t="n">
-        <v>1109381474</v>
+        <v>1221178530</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>411987225</v>
+        <v>96098968</v>
       </c>
       <c r="I72" t="n">
-        <v>0.173113</v>
+        <v>5.15</v>
       </c>
       <c r="J72" t="n">
-        <v>0.154982</v>
+        <v>4.63</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.000614510887292863</v>
+        <v>-0.04900761539183396</v>
       </c>
       <c r="L72" t="n">
-        <v>-0.37453</v>
+        <v>-0.99324</v>
       </c>
       <c r="M72" t="n">
-        <v>6785574605</v>
+        <v>250000000</v>
       </c>
       <c r="N72" t="n">
-        <v>10000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="O72" t="n">
-        <v>2.39</v>
+        <v>7.86</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>45303.18748842592</v>
+        <v>46021.04538194444</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0003639909074922668</v>
+        <v>0.0004190712434315161</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5296,34 +5296,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.097736</v>
+        <v>0.09998799999999999</v>
       </c>
       <c r="F73" t="n">
-        <v>1046007483</v>
+        <v>1071688769</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>91697989</v>
+        <v>127176677</v>
       </c>
       <c r="I73" t="n">
-        <v>0.09819600000000001</v>
+        <v>0.101543</v>
       </c>
       <c r="J73" t="n">
-        <v>0.09082999999999999</v>
+        <v>0.096651</v>
       </c>
       <c r="K73" t="n">
-        <v>0.00574446</v>
+        <v>0.00212377</v>
       </c>
       <c r="L73" t="n">
-        <v>6.24455</v>
+        <v>2.17012</v>
       </c>
       <c r="M73" t="n">
-        <v>10715847841.42047</v>
+        <v>10716429232.27866</v>
       </c>
       <c r="N73" t="n">
-        <v>10715847841.42047</v>
+        <v>10716429232.27866</v>
       </c>
       <c r="O73" t="n">
         <v>1.29</v>
@@ -5332,19 +5332,19 @@
         <v>45364.45493055556</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.00032280610636458</v>
+        <v>0.0003237354979836138</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5363,34 +5363,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>9.35</v>
+        <v>9.81</v>
       </c>
       <c r="F74" t="n">
-        <v>997312993</v>
+        <v>1046669885</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>3575734</v>
+        <v>3582913</v>
       </c>
       <c r="I74" t="n">
-        <v>9.41</v>
+        <v>9.9</v>
       </c>
       <c r="J74" t="n">
-        <v>9.01</v>
+        <v>9.31</v>
       </c>
       <c r="K74" t="n">
-        <v>0.330257</v>
+        <v>0.468169</v>
       </c>
       <c r="L74" t="n">
-        <v>3.66004</v>
+        <v>5.00911</v>
       </c>
       <c r="M74" t="n">
-        <v>106631229.6668511</v>
+        <v>106632325.8526192</v>
       </c>
       <c r="N74" t="n">
-        <v>118882512.0959876</v>
+        <v>118883590.353713</v>
       </c>
       <c r="O74" t="n">
         <v>25.38</v>
@@ -5399,86 +5399,86 @@
         <v>45682.66666666666</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R74" t="b">
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.000291161059950127</v>
+        <v>0.0003077799305891714</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>blockchain-capital</t>
+          <t>kaspa</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>bcap</t>
+          <t>kas</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Blockchain Capital</t>
+          <t>Kaspa</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106.54</v>
+        <v>0.03556016</v>
       </c>
       <c r="F75" t="n">
-        <v>970804306</v>
+        <v>985350397</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>14199670</v>
       </c>
       <c r="I75" t="n">
-        <v>106.54</v>
+        <v>0.03674564</v>
       </c>
       <c r="J75" t="n">
-        <v>106.54</v>
+        <v>0.03318585</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>0.00183327</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>5.43564</v>
       </c>
       <c r="M75" t="n">
-        <v>9112111</v>
+        <v>27705890801.55766</v>
       </c>
       <c r="N75" t="n">
-        <v>9112111</v>
+        <v>27707400028.46774</v>
       </c>
       <c r="O75" t="n">
-        <v>106.54</v>
+        <v>0.207411</v>
       </c>
       <c r="P75" s="1" t="n">
-        <v>46280.14583333334</v>
+        <v>45504.69498842592</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0002739338822858531</v>
+        <v>0.0002686739807243931</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5497,28 +5497,28 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>7.02</v>
+        <v>7.17</v>
       </c>
       <c r="F76" t="n">
-        <v>963335093</v>
+        <v>983203500</v>
       </c>
       <c r="G76" t="n">
         <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>67520676</v>
+        <v>5417571</v>
       </c>
       <c r="I76" t="n">
-        <v>7.03</v>
+        <v>7.2</v>
       </c>
       <c r="J76" t="n">
-        <v>6.71</v>
+        <v>6.97</v>
       </c>
       <c r="K76" t="n">
-        <v>0.243767</v>
+        <v>0.18184</v>
       </c>
       <c r="L76" t="n">
-        <v>3.5954</v>
+        <v>2.60243</v>
       </c>
       <c r="M76" t="n">
         <v>137155021.2773955</v>
@@ -5533,19 +5533,19 @@
         <v>44531.29832175926</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R76" t="b">
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0002690798712454985</v>
+        <v>0.0002673048165453503</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5564,28 +5564,28 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.116583</v>
+        <v>0.118528</v>
       </c>
       <c r="F77" t="n">
-        <v>954756417</v>
+        <v>971455906</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>26505719</v>
+        <v>32560510</v>
       </c>
       <c r="I77" t="n">
-        <v>0.117692</v>
+        <v>0.118293</v>
       </c>
       <c r="J77" t="n">
-        <v>0.115665</v>
+        <v>0.113817</v>
       </c>
       <c r="K77" t="n">
-        <v>0.00059799</v>
+        <v>0.00215167</v>
       </c>
       <c r="L77" t="n">
-        <v>0.51558</v>
+        <v>1.84888</v>
       </c>
       <c r="M77" t="n">
         <v>8188743036.341737</v>
@@ -5600,86 +5600,86 @@
         <v>44290.85721064815</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R77" t="b">
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002635048544377539</v>
+        <v>0.0002598128945319804</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>kaspa</t>
+          <t>blockchain-capital</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>kas</t>
+          <t>bcap</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Kaspa</t>
+          <t>Blockchain Capital</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.0335759</v>
+        <v>106.54</v>
       </c>
       <c r="F78" t="n">
-        <v>930001042</v>
+        <v>970804306</v>
       </c>
       <c r="G78" t="n">
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>12445308</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0.03459489</v>
+        <v>106.54</v>
       </c>
       <c r="J78" t="n">
-        <v>0.03175054</v>
+        <v>106.54</v>
       </c>
       <c r="K78" t="n">
-        <v>0.00157764</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>4.93041</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>27705335017.92249</v>
+        <v>9112111</v>
       </c>
       <c r="N78" t="n">
-        <v>27705589343.2654</v>
+        <v>9112111</v>
       </c>
       <c r="O78" t="n">
-        <v>0.207411</v>
+        <v>106.54</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>45504.69498842592</v>
+        <v>46280.14583333334</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R78" t="b">
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002474171001377871</v>
+        <v>0.0002593973425147833</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5698,34 +5698,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.082855</v>
+        <v>0.083913</v>
       </c>
       <c r="F79" t="n">
-        <v>929483978</v>
+        <v>942708036</v>
       </c>
       <c r="G79" t="n">
         <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>9276245</v>
+        <v>8620899</v>
       </c>
       <c r="I79" t="n">
-        <v>0.08591600000000001</v>
+        <v>0.08415</v>
       </c>
       <c r="J79" t="n">
-        <v>0.08044</v>
+        <v>0.08086699999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>0.00066717</v>
+        <v>0.00115749</v>
       </c>
       <c r="L79" t="n">
-        <v>0.81177</v>
+        <v>1.39868</v>
       </c>
       <c r="M79" t="n">
-        <v>11218698151.07317</v>
+        <v>11239267182.72403</v>
       </c>
       <c r="N79" t="n">
-        <v>17259535617.03564</v>
+        <v>17291180281.11388</v>
       </c>
       <c r="O79" t="n">
         <v>2.99</v>
@@ -5734,19 +5734,19 @@
         <v>45714.36184027778</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R79" t="b">
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002470810761999813</v>
+        <v>0.0002414791999822287</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5765,28 +5765,28 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>61.2</v>
+        <v>63.34</v>
       </c>
       <c r="F80" t="n">
-        <v>889954623</v>
+        <v>921129189</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>7408866</v>
+        <v>8715173</v>
       </c>
       <c r="I80" t="n">
-        <v>61.98</v>
+        <v>63.35</v>
       </c>
       <c r="J80" t="n">
-        <v>58.91</v>
+        <v>60.72</v>
       </c>
       <c r="K80" t="n">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="L80" t="n">
-        <v>3.49961</v>
+        <v>3.27333</v>
       </c>
       <c r="M80" t="n">
         <v>14544176.16408117</v>
@@ -5801,1024 +5801,1024 @@
         <v>44450.05208333334</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R80" t="b">
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002213921682001564</v>
+        <v>0.0002277174851270472</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>algorand</t>
+          <t>cosmos</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>algo</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Algorand</t>
+          <t>Cosmos Hub</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.09013</v>
+        <v>1.67</v>
       </c>
       <c r="F81" t="n">
-        <v>814602846</v>
+        <v>887148662</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>44122052</v>
+        <v>59111575</v>
       </c>
       <c r="I81" t="n">
-        <v>0.09153699999999999</v>
+        <v>1.67</v>
       </c>
       <c r="J81" t="n">
-        <v>0.08534</v>
+        <v>1.52</v>
       </c>
       <c r="K81" t="n">
-        <v>0.00407963</v>
+        <v>0.140951</v>
       </c>
       <c r="L81" t="n">
-        <v>4.74096</v>
+        <v>9.22336</v>
       </c>
       <c r="M81" t="n">
-        <v>9041440361.74052</v>
+        <v>531398115.177704</v>
       </c>
       <c r="N81" t="n">
-        <v>9041867790.797272</v>
+        <v>531405147.717275</v>
       </c>
       <c r="O81" t="n">
-        <v>3.56</v>
+        <v>43.84</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>43636.28563657407</v>
+        <v>44458.66666666666</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0001724233735669954</v>
+        <v>0.000206046710817243</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>algorand</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>algo</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NEXO</t>
+          <t>Algorand</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.813817</v>
+        <v>0.096716</v>
       </c>
       <c r="F82" t="n">
-        <v>814150815</v>
+        <v>874520830</v>
       </c>
       <c r="G82" t="n">
         <v>81</v>
       </c>
       <c r="H82" t="n">
-        <v>3265526</v>
+        <v>45382156</v>
       </c>
       <c r="I82" t="n">
-        <v>0.810526</v>
+        <v>0.09686400000000001</v>
       </c>
       <c r="J82" t="n">
-        <v>0.778729</v>
+        <v>0.089339</v>
       </c>
       <c r="K82" t="n">
-        <v>0.027226</v>
+        <v>0.00716556</v>
       </c>
       <c r="L82" t="n">
-        <v>3.46127</v>
+        <v>8.00169</v>
       </c>
       <c r="M82" t="n">
-        <v>1000000000</v>
+        <v>9042038142.191359</v>
       </c>
       <c r="N82" t="n">
-        <v>1000000000</v>
+        <v>9042065635.209162</v>
       </c>
       <c r="O82" t="n">
-        <v>4.07</v>
+        <v>3.56</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>44328.27623842593</v>
+        <v>43636.28563657407</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0001721296125690719</v>
+        <v>0.0001979934249663754</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>cosmos</t>
+          <t>pancakeswap-token</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cosmos Hub</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1.53</v>
+        <v>2.49</v>
       </c>
       <c r="F83" t="n">
-        <v>811905140</v>
+        <v>866497842</v>
       </c>
       <c r="G83" t="n">
         <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>39690657</v>
+        <v>115480970</v>
       </c>
       <c r="I83" t="n">
-        <v>1.55</v>
+        <v>2.55</v>
       </c>
       <c r="J83" t="n">
-        <v>1.47</v>
+        <v>2.37</v>
       </c>
       <c r="K83" t="n">
-        <v>0.03987303</v>
+        <v>0.096279</v>
       </c>
       <c r="L83" t="n">
-        <v>2.67726</v>
+        <v>4.02796</v>
       </c>
       <c r="M83" t="n">
-        <v>531209599.807218</v>
+        <v>348474256.3337419</v>
       </c>
       <c r="N83" t="n">
-        <v>531224914.94615</v>
+        <v>360130842.00171</v>
       </c>
       <c r="O83" t="n">
-        <v>43.84</v>
+        <v>43.96</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>44458.66666666666</v>
+        <v>44316.08914351852</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0001706702176846245</v>
+        <v>0.0001928768368028585</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>jupiter-exchange-solana</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>jup</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Spiko EU T-Bills Money Market Fund</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1.22</v>
+        <v>0.261142</v>
       </c>
       <c r="F84" t="n">
-        <v>794507303</v>
+        <v>866378292</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>114685025</v>
       </c>
       <c r="I84" t="n">
-        <v>1.22</v>
+        <v>0.259521</v>
       </c>
       <c r="J84" t="n">
-        <v>1.21</v>
+        <v>0.223636</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.004000636553897152</v>
+        <v>0.0366646</v>
       </c>
       <c r="L84" t="n">
-        <v>-0.3276</v>
+        <v>16.33335</v>
       </c>
       <c r="M84" t="n">
-        <v>652741858.0353301</v>
+        <v>3319369204.37</v>
       </c>
       <c r="N84" t="n">
-        <v>652909474.76177</v>
+        <v>6861486931.569773</v>
       </c>
       <c r="O84" t="n">
-        <v>1.26</v>
+        <v>2</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>46049.54175925926</v>
+        <v>45322.29359953704</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001593639002886298</v>
+        <v>0.0001928005948696849</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-aaa-clo-fund</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>jaaa</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy AAA CLO Fund</t>
+          <t>NEXO</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1.05</v>
+        <v>0.825546</v>
       </c>
       <c r="F85" t="n">
-        <v>775002313</v>
+        <v>825568397</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>2585723</v>
       </c>
       <c r="I85" t="n">
-        <v>1.05</v>
+        <v>0.828891</v>
       </c>
       <c r="J85" t="n">
-        <v>1.05</v>
+        <v>0.805134</v>
       </c>
       <c r="K85" t="n">
-        <v>0.000151</v>
+        <v>0.02332409</v>
       </c>
       <c r="L85" t="n">
-        <v>0.01439</v>
+        <v>2.90744</v>
       </c>
       <c r="M85" t="n">
-        <v>738235948.461841</v>
+        <v>1000000000</v>
       </c>
       <c r="N85" t="n">
-        <v>738235948.461841</v>
+        <v>1000000000</v>
       </c>
       <c r="O85" t="n">
-        <v>1.05</v>
+        <v>4.07</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>46282.42384259259</v>
+        <v>44328.27623842593</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R85" t="b">
         <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001466882091814133</v>
+        <v>0.0001667744527750727</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>pancakeswap-token</t>
+          <t>render-token</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>render</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="F86" t="n">
-        <v>759100711</v>
+        <v>795709144</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
       </c>
       <c r="H86" t="n">
-        <v>98183689</v>
+        <v>69435580</v>
       </c>
       <c r="I86" t="n">
-        <v>2.43</v>
+        <v>1.54</v>
       </c>
       <c r="J86" t="n">
-        <v>2.17</v>
+        <v>1.39</v>
       </c>
       <c r="K86" t="n">
-        <v>0.196026</v>
+        <v>0.140904</v>
       </c>
       <c r="L86" t="n">
-        <v>8.98293</v>
+        <v>10.12291</v>
       </c>
       <c r="M86" t="n">
-        <v>319432763.8588443</v>
+        <v>518776241.2826915</v>
       </c>
       <c r="N86" t="n">
-        <v>331093394.0049145</v>
+        <v>533536414.5626915</v>
       </c>
       <c r="O86" t="n">
-        <v>43.96</v>
+        <v>13.53</v>
       </c>
       <c r="P86" s="1" t="n">
-        <v>44316.08914351852</v>
+        <v>45368.35444444444</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R86" t="b">
         <v>1</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001363542487404238</v>
+        <v>0.0001477319837509065</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jupiter-exchange-solana</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>jup</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Spiko EU T-Bills Money Market Fund</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.226699</v>
+        <v>1.21</v>
       </c>
       <c r="F87" t="n">
-        <v>751341092</v>
+        <v>790361818</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>85706896</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0.227422</v>
+        <v>1.22</v>
       </c>
       <c r="J87" t="n">
-        <v>0.207452</v>
+        <v>1.21</v>
       </c>
       <c r="K87" t="n">
-        <v>0.01625699</v>
+        <v>-0.002520738062147032</v>
       </c>
       <c r="L87" t="n">
-        <v>7.72517</v>
+        <v>-0.20721</v>
       </c>
       <c r="M87" t="n">
-        <v>3319369204.37</v>
+        <v>651037363.70003</v>
       </c>
       <c r="N87" t="n">
-        <v>6861487035.852483</v>
+        <v>651037363.70003</v>
       </c>
       <c r="O87" t="n">
-        <v>2</v>
+        <v>1.26</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>45322.29359953704</v>
+        <v>46049.54175925926</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001313115118021487</v>
+        <v>0.0001443217748713635</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>janus-henderson-anemoy-aaa-clo-fund</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>jaaa</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Dash</t>
+          <t>Janus Henderson Anemoy AAA CLO Fund</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>58.3</v>
+        <v>1.05</v>
       </c>
       <c r="F88" t="n">
-        <v>746560452</v>
+        <v>776469917</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>224653157</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>60.37</v>
+        <v>1.05</v>
       </c>
       <c r="J88" t="n">
-        <v>52.99</v>
+        <v>1.05</v>
       </c>
       <c r="K88" t="n">
-        <v>4.2</v>
+        <v>9.1e-05</v>
       </c>
       <c r="L88" t="n">
-        <v>7.75706</v>
+        <v>0.008670000000000001</v>
       </c>
       <c r="M88" t="n">
-        <v>12831918.9507522</v>
+        <v>739569820.670837</v>
       </c>
       <c r="N88" t="n">
-        <v>12832046.56713975</v>
+        <v>739569820.670837</v>
       </c>
       <c r="O88" t="n">
-        <v>1493.59</v>
+        <v>1.05</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>46283.36122685186</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001282047213892951</v>
+        <v>0.0001354623404280677</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ustb</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Invesco Short Duration US Government Securities Fund</t>
+          <t>Dash</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>11.21</v>
+        <v>58.77</v>
       </c>
       <c r="F89" t="n">
-        <v>732885815</v>
+        <v>754086368</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>188486590</v>
       </c>
       <c r="I89" t="n">
-        <v>11.21</v>
+        <v>62.48</v>
       </c>
       <c r="J89" t="n">
-        <v>11.21</v>
+        <v>57.02</v>
       </c>
       <c r="K89" t="n">
-        <v>0.001081</v>
+        <v>1.21</v>
       </c>
       <c r="L89" t="n">
-        <v>0.009639999999999999</v>
+        <v>2.10693</v>
       </c>
       <c r="M89" t="n">
-        <v>65350775.701558</v>
+        <v>12832779.61981004</v>
       </c>
       <c r="N89" t="n">
-        <v>65348949.048738</v>
+        <v>12832868.22864153</v>
       </c>
       <c r="O89" t="n">
-        <v>11.21</v>
+        <v>1493.59</v>
       </c>
       <c r="P89" s="1" t="n">
-        <v>46282.55208333334</v>
+        <v>43088.66666666666</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R89" t="b">
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001193179967811147</v>
+        <v>0.0001211874341374312</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>render-token</t>
+          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>render</t>
+          <t>ustb</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>Invesco Short Duration US Government Securities Fund</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1.4</v>
+        <v>11.22</v>
       </c>
       <c r="F90" t="n">
-        <v>726354679</v>
+        <v>729506977</v>
       </c>
       <c r="G90" t="n">
         <v>89</v>
       </c>
       <c r="H90" t="n">
-        <v>43603831</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>1.4</v>
+        <v>11.21</v>
       </c>
       <c r="J90" t="n">
-        <v>1.29</v>
+        <v>11.21</v>
       </c>
       <c r="K90" t="n">
-        <v>0.104528</v>
+        <v>0.001068</v>
       </c>
       <c r="L90" t="n">
-        <v>8.059810000000001</v>
+        <v>0.009520000000000001</v>
       </c>
       <c r="M90" t="n">
-        <v>518776241.2826915</v>
+        <v>65043293.460603</v>
       </c>
       <c r="N90" t="n">
-        <v>533536414.5626915</v>
+        <v>64962641.508854</v>
       </c>
       <c r="O90" t="n">
-        <v>13.53</v>
+        <v>11.22</v>
       </c>
       <c r="P90" s="1" t="n">
-        <v>45368.35444444444</v>
+        <v>46283.55902777778</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>0.0001150736130354567</v>
+        <v>0.0001055121494358893</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>filecoin</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>fil</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>GHO</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.998519</v>
+        <v>0.874042</v>
       </c>
       <c r="F91" t="n">
-        <v>697955648</v>
+        <v>722662480</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>12091739</v>
+        <v>136321802</v>
       </c>
       <c r="I91" t="n">
-        <v>0.998878</v>
+        <v>0.879723</v>
       </c>
       <c r="J91" t="n">
-        <v>0.998148</v>
+        <v>0.810361</v>
       </c>
       <c r="K91" t="n">
-        <v>-3.0372547706881e-05</v>
+        <v>0.062831</v>
       </c>
       <c r="L91" t="n">
-        <v>-0.00304</v>
+        <v>7.74531</v>
       </c>
       <c r="M91" t="n">
-        <v>699000000</v>
+        <v>827813309</v>
       </c>
       <c r="N91" t="n">
-        <v>699000000</v>
+        <v>1957042330</v>
       </c>
       <c r="O91" t="n">
-        <v>1.03</v>
+        <v>236.84</v>
       </c>
       <c r="P91" s="1" t="n">
-        <v>45350.38608796296</v>
+        <v>44287.22894675926</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S91" t="n">
-        <v>9.661795913867103e-05</v>
+        <v>0.0001011471332679196</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>marscat-token</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>mcat</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Marscat Token</t>
+          <t>GHO</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.6707419999999999</v>
+        <v>0.998333</v>
       </c>
       <c r="F92" t="n">
-        <v>671748418</v>
+        <v>697834500</v>
       </c>
       <c r="G92" t="n">
         <v>91</v>
       </c>
       <c r="H92" t="n">
-        <v>16628728</v>
+        <v>13580607</v>
       </c>
       <c r="I92" t="n">
-        <v>0.819144</v>
+        <v>0.998651</v>
       </c>
       <c r="J92" t="n">
-        <v>0.217044</v>
+        <v>0.998274</v>
       </c>
       <c r="K92" t="n">
-        <v>0.439347</v>
+        <v>-0.000139759986692467</v>
       </c>
       <c r="L92" t="n">
-        <v>189.86889</v>
+        <v>-0.014</v>
       </c>
       <c r="M92" t="n">
-        <v>1000000000</v>
+        <v>699000000</v>
       </c>
       <c r="N92" t="n">
-        <v>1000000000</v>
+        <v>699000000</v>
       </c>
       <c r="O92" t="n">
-        <v>0.819144</v>
+        <v>1.03</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>46282.41516203704</v>
+        <v>45350.38608796296</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>7.9586689076201e-05</v>
+        <v>8.531331317594948e-05</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>filecoin</t>
+          <t>ether-fi</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>ethfi</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>Ether.fi</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.819213</v>
+        <v>0.712028</v>
       </c>
       <c r="F93" t="n">
-        <v>677259265</v>
+        <v>685510629</v>
       </c>
       <c r="G93" t="n">
         <v>92</v>
       </c>
       <c r="H93" t="n">
-        <v>125078551</v>
+        <v>66519364</v>
       </c>
       <c r="I93" t="n">
-        <v>0.817635</v>
+        <v>0.699136</v>
       </c>
       <c r="J93" t="n">
-        <v>0.768896</v>
+        <v>0.610697</v>
       </c>
       <c r="K93" t="n">
-        <v>0.04083346</v>
+        <v>0.09155000000000001</v>
       </c>
       <c r="L93" t="n">
-        <v>5.24596</v>
+        <v>14.75484</v>
       </c>
       <c r="M93" t="n">
-        <v>827813309</v>
+        <v>965350000</v>
       </c>
       <c r="N93" t="n">
-        <v>1957043843</v>
+        <v>965350000</v>
       </c>
       <c r="O93" t="n">
-        <v>236.84</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="P93" s="1" t="n">
-        <v>44287.22894675926</v>
+        <v>45378.63525462963</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R93" t="b">
         <v>1</v>
       </c>
       <c r="S93" t="n">
-        <v>8.316801848529737e-05</v>
+        <v>7.745387570859822e-05</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-treasury-fund</t>
+          <t>stable-2</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>jtrsy</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund</t>
+          <t>​​Stable</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1.12</v>
+        <v>0.0250295</v>
       </c>
       <c r="F94" t="n">
-        <v>650205297</v>
+        <v>661455263</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>10849867</v>
       </c>
       <c r="I94" t="n">
-        <v>1.12</v>
+        <v>0.02510017</v>
       </c>
       <c r="J94" t="n">
-        <v>1.12</v>
+        <v>0.02296381</v>
       </c>
       <c r="K94" t="n">
-        <v>5.4e-05</v>
+        <v>0.00145235</v>
       </c>
       <c r="L94" t="n">
-        <v>0.00484</v>
+        <v>6.15998</v>
       </c>
       <c r="M94" t="n">
-        <v>582549198.395</v>
+        <v>26430929012</v>
       </c>
       <c r="N94" t="n">
-        <v>537749706.0290329</v>
+        <v>100000000000</v>
       </c>
       <c r="O94" t="n">
-        <v>1.12</v>
+        <v>0.04323745</v>
       </c>
       <c r="P94" s="1" t="n">
-        <v>46282.42384259259</v>
+        <v>46156.97986111111</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S94" t="n">
-        <v>6.558647952565065e-05</v>
+        <v>6.211278321978139e-05</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>stable-2</t>
+          <t>injective-protocol</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>inj</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>​​Stable</t>
+          <t>Injective</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.02337075</v>
+        <v>6.59</v>
       </c>
       <c r="F95" t="n">
-        <v>617208310</v>
+        <v>658192252</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>11681429</v>
+        <v>181255434</v>
       </c>
       <c r="I95" t="n">
-        <v>0.02669918</v>
+        <v>6.94</v>
       </c>
       <c r="J95" t="n">
-        <v>0.0233546</v>
+        <v>5.53</v>
       </c>
       <c r="K95" t="n">
-        <v>-0.00332136202994586</v>
+        <v>0.969625</v>
       </c>
       <c r="L95" t="n">
-        <v>-12.44324</v>
+        <v>17.24359</v>
       </c>
       <c r="M95" t="n">
-        <v>26401971536</v>
+        <v>100000000</v>
       </c>
       <c r="N95" t="n">
-        <v>100000000000</v>
+        <v>100000000</v>
       </c>
       <c r="O95" t="n">
-        <v>0.04323745</v>
+        <v>52.62</v>
       </c>
       <c r="P95" s="1" t="n">
-        <v>46156.97986111111</v>
+        <v>45365.29608796296</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R95" t="b">
         <v>1</v>
       </c>
       <c r="S95" t="n">
-        <v>4.414275591026617e-05</v>
+        <v>6.003182741378673e-05</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6837,28 +6837,28 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.00716083</v>
+        <v>0.00757389</v>
       </c>
       <c r="F96" t="n">
-        <v>615409250</v>
+        <v>651227129</v>
       </c>
       <c r="G96" t="n">
         <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>10609511</v>
+        <v>11025377</v>
       </c>
       <c r="I96" t="n">
-        <v>0.00726114</v>
+        <v>0.00759125</v>
       </c>
       <c r="J96" t="n">
-        <v>0.00681043</v>
+        <v>0.00712051</v>
       </c>
       <c r="K96" t="n">
-        <v>0.00019794</v>
+        <v>0.00041545</v>
       </c>
       <c r="L96" t="n">
-        <v>2.84273</v>
+        <v>5.80369</v>
       </c>
       <c r="M96" t="n">
         <v>85985041177</v>
@@ -6873,345 +6873,345 @@
         <v>44304.71413194444</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S96" t="n">
-        <v>4.297360233247151e-05</v>
+        <v>5.558988310335781e-05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ether-fi</t>
+          <t>aerodrome-finance</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ethfi</t>
+          <t>aero</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Ether.fi</t>
+          <t>Aerodrome Finance</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.6242490000000001</v>
+        <v>0.625135</v>
       </c>
       <c r="F97" t="n">
-        <v>603124403</v>
+        <v>621011216</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>51379350</v>
+        <v>57074561</v>
       </c>
       <c r="I97" t="n">
-        <v>0.62782</v>
+        <v>0.649736</v>
       </c>
       <c r="J97" t="n">
-        <v>0.575779</v>
+        <v>0.578275</v>
       </c>
       <c r="K97" t="n">
-        <v>0.04198894</v>
+        <v>0.0400783</v>
       </c>
       <c r="L97" t="n">
-        <v>7.21137</v>
+        <v>6.85033</v>
       </c>
       <c r="M97" t="n">
-        <v>965350000</v>
+        <v>993231546.6010708</v>
       </c>
       <c r="N97" t="n">
-        <v>965350000</v>
+        <v>1983240735.576791</v>
       </c>
       <c r="O97" t="n">
-        <v>8.529999999999999</v>
+        <v>2.32</v>
       </c>
       <c r="P97" s="1" t="n">
-        <v>45378.63525462963</v>
+        <v>45633.25043981482</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R97" t="b">
         <v>1</v>
       </c>
       <c r="S97" t="n">
-        <v>3.499005935852407e-05</v>
+        <v>3.631995738420464e-05</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>beldex</t>
+          <t>aptos</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>bdx</t>
+          <t>apt</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Beldex</t>
+          <t>Aptos</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.07616100000000001</v>
+        <v>0.686259</v>
       </c>
       <c r="F98" t="n">
-        <v>599440658</v>
+        <v>598121508</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>7836802</v>
+        <v>200509884</v>
       </c>
       <c r="I98" t="n">
-        <v>0.076672</v>
+        <v>0.707517</v>
       </c>
       <c r="J98" t="n">
-        <v>0.075295</v>
+        <v>0.5719610000000001</v>
       </c>
       <c r="K98" t="n">
-        <v>0.00104262</v>
+        <v>0.113278</v>
       </c>
       <c r="L98" t="n">
-        <v>1.38796</v>
+        <v>19.76985</v>
       </c>
       <c r="M98" t="n">
-        <v>7870732376.983206</v>
+        <v>870437430.8473938</v>
       </c>
       <c r="N98" t="n">
-        <v>9939671749.706188</v>
+        <v>1208877694.477877</v>
       </c>
       <c r="O98" t="n">
-        <v>0.450785</v>
+        <v>19.92</v>
       </c>
       <c r="P98" s="1" t="n">
-        <v>43450.66666666666</v>
+        <v>44952.26755787037</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S98" t="n">
-        <v>3.259610715768965e-05</v>
+        <v>2.172225276104445e-05</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>aerodrome-finance</t>
+          <t>akedo</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>aero</t>
+          <t>ake</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Aerodrome Finance</t>
+          <t>Akedo</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.596889</v>
+        <v>0.02618744</v>
       </c>
       <c r="F99" t="n">
-        <v>592814115</v>
+        <v>597563482</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>52101612</v>
+        <v>19874412</v>
       </c>
       <c r="I99" t="n">
-        <v>0.594585</v>
+        <v>0.02640787</v>
       </c>
       <c r="J99" t="n">
-        <v>0.518055</v>
+        <v>0.02073256</v>
       </c>
       <c r="K99" t="n">
-        <v>0.076251</v>
+        <v>0.00468007</v>
       </c>
       <c r="L99" t="n">
-        <v>14.64574</v>
+        <v>21.76031</v>
       </c>
       <c r="M99" t="n">
-        <v>993277331.60516</v>
+        <v>22796250000</v>
       </c>
       <c r="N99" t="n">
-        <v>1983240735.576791</v>
+        <v>100000000000</v>
       </c>
       <c r="O99" t="n">
-        <v>2.32</v>
+        <v>0.0363756</v>
       </c>
       <c r="P99" s="1" t="n">
-        <v>45633.25043981482</v>
+        <v>46267.90648148148</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R99" t="b">
         <v>1</v>
       </c>
       <c r="S99" t="n">
-        <v>2.828972134684393e-05</v>
+        <v>2.136637671753863e-05</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>injective-protocol</t>
+          <t>beldex</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>inj</t>
+          <t>bdx</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Injective</t>
+          <t>Beldex</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5.69</v>
+        <v>0.075929</v>
       </c>
       <c r="F100" t="n">
-        <v>568474370</v>
+        <v>597701598</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>94931431</v>
+        <v>1582692</v>
       </c>
       <c r="I100" t="n">
-        <v>5.67</v>
+        <v>0.076638</v>
       </c>
       <c r="J100" t="n">
-        <v>5.16</v>
+        <v>0.075601</v>
       </c>
       <c r="K100" t="n">
-        <v>0.286238</v>
+        <v>-0.000318594938063965</v>
       </c>
       <c r="L100" t="n">
-        <v>5.29727</v>
+        <v>-0.41784</v>
       </c>
       <c r="M100" t="n">
-        <v>100000000</v>
+        <v>7870743834.936207</v>
       </c>
       <c r="N100" t="n">
-        <v>100000000</v>
+        <v>9939683660.568291</v>
       </c>
       <c r="O100" t="n">
-        <v>52.62</v>
+        <v>0.450785</v>
       </c>
       <c r="P100" s="1" t="n">
-        <v>45365.29608796296</v>
+        <v>43450.66666666666</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>1.247207215817902e-05</v>
+        <v>2.145445894959385e-05</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>flare-networks</t>
+          <t>official-trump</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>flr</t>
+          <t>trump</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Flare</t>
+          <t>Official Trump</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.00631737</v>
+        <v>2.06</v>
       </c>
       <c r="F101" t="n">
-        <v>549282703</v>
+        <v>564060261</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>2343719</v>
+        <v>181529355</v>
       </c>
       <c r="I101" t="n">
-        <v>0.00635515</v>
+        <v>2.07</v>
       </c>
       <c r="J101" t="n">
-        <v>0.00622597</v>
+        <v>1.93</v>
       </c>
       <c r="K101" t="n">
-        <v>7.227e-05</v>
+        <v>0.122432</v>
       </c>
       <c r="L101" t="n">
-        <v>1.1572</v>
+        <v>6.30502</v>
       </c>
       <c r="M101" t="n">
-        <v>86974846982.67435</v>
+        <v>273137120.287634</v>
       </c>
       <c r="N101" t="n">
-        <v>106567132005.1747</v>
+        <v>1000000000</v>
       </c>
       <c r="O101" t="n">
-        <v>0.150073</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="P101" s="1" t="n">
-        <v>44935.80144675926</v>
+        <v>45676.16011574074</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46282.59108796297</v>
+        <v>46283.56203703704</v>
       </c>
       <c r="R101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>

--- a/src/xlsx/cleaned_data.xlsx
+++ b/src/xlsx/cleaned_data.xlsx
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,34 +539,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>78107</v>
+        <v>81303</v>
       </c>
       <c r="F2" t="n">
-        <v>1568598802085</v>
+        <v>1633087433036</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>29746226629</v>
+        <v>39046726177</v>
       </c>
       <c r="I2" t="n">
-        <v>78372</v>
+        <v>81675</v>
       </c>
       <c r="J2" t="n">
-        <v>76205</v>
+        <v>80014</v>
       </c>
       <c r="K2" t="n">
-        <v>1623.81</v>
+        <v>3308.3</v>
       </c>
       <c r="L2" t="n">
-        <v>2.12309</v>
+        <v>4.27011</v>
       </c>
       <c r="M2" t="n">
-        <v>20086075</v>
+        <v>20086521</v>
       </c>
       <c r="N2" t="n">
-        <v>20086075</v>
+        <v>20086553</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -575,7 +575,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -587,7 +587,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,34 +606,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2504.2</v>
+        <v>2640.53</v>
       </c>
       <c r="F3" t="n">
-        <v>305590691965</v>
+        <v>322307862116</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>15043114849</v>
+        <v>20959346820</v>
       </c>
       <c r="I3" t="n">
-        <v>2518</v>
+        <v>2655.71</v>
       </c>
       <c r="J3" t="n">
-        <v>2435.96</v>
+        <v>2552.3</v>
       </c>
       <c r="K3" t="n">
-        <v>52.04</v>
+        <v>140.11</v>
       </c>
       <c r="L3" t="n">
-        <v>2.12207</v>
+        <v>5.64929</v>
       </c>
       <c r="M3" t="n">
-        <v>122058930.7915531</v>
+        <v>122061836.5153193</v>
       </c>
       <c r="N3" t="n">
-        <v>122058930.7915531</v>
+        <v>122061836.5153193</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -642,19 +642,19 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1945279805147563</v>
+        <v>0.1970734177712673</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,34 +673,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9991640000000001</v>
+        <v>0.999655</v>
       </c>
       <c r="F4" t="n">
-        <v>183289006638</v>
+        <v>183321470793</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>61371983187</v>
+        <v>73806318083</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9993610000000001</v>
+        <v>0.999786</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999089</v>
+        <v>0.999212</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.8548222514524e-05</v>
+        <v>0.00048018</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00286</v>
+        <v>0.04844</v>
       </c>
       <c r="M4" t="n">
-        <v>183442587855.5799</v>
+        <v>183384649794.4283</v>
       </c>
       <c r="N4" t="n">
-        <v>188909533773.7262</v>
+        <v>188851595759.0362</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -709,19 +709,19 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1165311848667633</v>
+        <v>0.1119363965382041</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,34 +740,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>750.21</v>
+        <v>771.92</v>
       </c>
       <c r="F5" t="n">
-        <v>99874497337</v>
+        <v>102788869489</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1327798862</v>
+        <v>1257822052</v>
       </c>
       <c r="I5" t="n">
-        <v>758.16</v>
+        <v>769.3200000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>724.1900000000001</v>
+        <v>754.7</v>
       </c>
       <c r="K5" t="n">
-        <v>23.05</v>
+        <v>25.56</v>
       </c>
       <c r="L5" t="n">
-        <v>3.1697</v>
+        <v>3.48143</v>
       </c>
       <c r="M5" t="n">
-        <v>133160438.17</v>
+        <v>133160340.96</v>
       </c>
       <c r="N5" t="n">
-        <v>133160429.28</v>
+        <v>133160340.96</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -776,19 +776,19 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06333433464648759</v>
+        <v>0.0626056259360764</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -807,28 +807,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="F6" t="n">
-        <v>83325852293</v>
+        <v>89964077796</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2693394422</v>
+        <v>4324462181</v>
       </c>
       <c r="I6" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="J6" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02428641</v>
+        <v>0.108094</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8667</v>
+        <v>8.24385</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -843,19 +843,19 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05278058567486089</v>
+        <v>0.05474971607120988</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,34 +874,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999514</v>
+        <v>0.99977</v>
       </c>
       <c r="F7" t="n">
-        <v>73773705191</v>
+        <v>74243970808</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>16804878019</v>
+        <v>19667075261</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999703</v>
+        <v>0.999862</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999464</v>
+        <v>0.999515</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.1772637548539e-05</v>
+        <v>0.00024919</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00718</v>
+        <v>0.02565</v>
       </c>
       <c r="M7" t="n">
-        <v>73809548950.31921</v>
+        <v>74260936982.90303</v>
       </c>
       <c r="N7" t="n">
-        <v>73809465033.80299</v>
+        <v>74261085155.35321</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -910,19 +910,19 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.046688790099663</v>
+        <v>0.04512026192333529</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -941,34 +941,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105.87</v>
+        <v>111.73</v>
       </c>
       <c r="F8" t="n">
-        <v>62173407445</v>
+        <v>65619505724</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4336330927</v>
+        <v>5307023206</v>
       </c>
       <c r="I8" t="n">
-        <v>106.53</v>
+        <v>114.14</v>
       </c>
       <c r="J8" t="n">
-        <v>100.11</v>
+        <v>108.45</v>
       </c>
       <c r="K8" t="n">
-        <v>5.5</v>
+        <v>6.04</v>
       </c>
       <c r="L8" t="n">
-        <v>5.47797</v>
+        <v>5.75077</v>
       </c>
       <c r="M8" t="n">
-        <v>587297218.9841995</v>
+        <v>587296224.8630985</v>
       </c>
       <c r="N8" t="n">
-        <v>634298467.6716927</v>
+        <v>634297490.1327897</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -977,19 +977,19 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03929080494245527</v>
+        <v>0.03983728954027715</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1008,34 +1008,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.338083</v>
+        <v>0.338162</v>
       </c>
       <c r="F9" t="n">
-        <v>32101739690</v>
+        <v>32110527640</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>387644195</v>
+        <v>444297894</v>
       </c>
       <c r="I9" t="n">
-        <v>0.337939</v>
+        <v>0.339776</v>
       </c>
       <c r="J9" t="n">
-        <v>0.333425</v>
+        <v>0.337075</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00335145</v>
+        <v>0.00045238</v>
       </c>
       <c r="L9" t="n">
-        <v>1.00124</v>
+        <v>0.13803</v>
       </c>
       <c r="M9" t="n">
-        <v>94954902669.86409</v>
+        <v>94955991096.57959</v>
       </c>
       <c r="N9" t="n">
-        <v>94954901666.17758</v>
+        <v>94956666619.81319</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1044,19 +1044,19 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02011287032601977</v>
+        <v>0.01931114628639689</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1075,34 +1075,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1467.74</v>
+        <v>1534.88</v>
       </c>
       <c r="F10" t="n">
-        <v>24865345606</v>
+        <v>26001228471</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>2178796951</v>
+        <v>1664369969</v>
       </c>
       <c r="I10" t="n">
-        <v>1526.56</v>
+        <v>1590.8</v>
       </c>
       <c r="J10" t="n">
-        <v>1370.29</v>
+        <v>1437.73</v>
       </c>
       <c r="K10" t="n">
-        <v>105.04</v>
+        <v>74.98</v>
       </c>
       <c r="L10" t="n">
-        <v>7.70855</v>
+        <v>5.09457</v>
       </c>
       <c r="M10" t="n">
-        <v>16938925.1655448</v>
+        <v>16940251.7280448</v>
       </c>
       <c r="N10" t="n">
-        <v>16939175.1655448</v>
+        <v>16940898.6030448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1111,19 +1111,19 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01549792533087104</v>
+        <v>0.0155688552022178</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1142,34 +1142,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.028</v>
+        <v>1.03</v>
       </c>
       <c r="F11" t="n">
-        <v>23301466219</v>
+        <v>23389434218</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>209412055</v>
+        <v>52721291</v>
       </c>
       <c r="I11" t="n">
-        <v>1.035</v>
+        <v>1.034</v>
       </c>
       <c r="J11" t="n">
-        <v>1.004</v>
+        <v>1.027</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.001618662688462669</v>
+        <v>0.00207246</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1572</v>
+        <v>0.20108</v>
       </c>
       <c r="M11" t="n">
-        <v>22665434312.548</v>
+        <v>22705389532.338</v>
       </c>
       <c r="N11" t="n">
-        <v>22665434312.548</v>
+        <v>22705389532.338</v>
       </c>
       <c r="O11" t="n">
         <v>1.061</v>
@@ -1178,19 +1178,19 @@
         <v>46237.59675925926</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01450057537089449</v>
+        <v>0.0139689835841592</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1209,28 +1209,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>91.27</v>
+        <v>92.44</v>
       </c>
       <c r="F12" t="n">
-        <v>20297028307</v>
+        <v>20562860000</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1618650214</v>
+        <v>1445408936</v>
       </c>
       <c r="I12" t="n">
-        <v>91.79000000000001</v>
+        <v>94.48</v>
       </c>
       <c r="J12" t="n">
-        <v>81.5</v>
+        <v>90.36</v>
       </c>
       <c r="K12" t="n">
-        <v>9.19</v>
+        <v>1.25</v>
       </c>
       <c r="L12" t="n">
-        <v>11.19346</v>
+        <v>1.50458</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1239,25 +1239,25 @@
         <v>955307079.4341414</v>
       </c>
       <c r="O12" t="n">
-        <v>91.79000000000001</v>
+        <v>94.48</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>46283.5275462963</v>
+        <v>46284.12847222222</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01258452221731123</v>
+        <v>0.01223754709657214</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1276,34 +1276,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.085364</v>
+        <v>0.088697</v>
       </c>
       <c r="F13" t="n">
-        <v>13314001045</v>
+        <v>13834995349</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>877130041</v>
+        <v>1053761028</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08678</v>
+        <v>0.08876100000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.081105</v>
+        <v>0.08651</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00417871</v>
+        <v>0.00331129</v>
       </c>
       <c r="L13" t="n">
-        <v>5.14712</v>
+        <v>3.91707</v>
       </c>
       <c r="M13" t="n">
-        <v>155966856383.7052</v>
+        <v>155979846383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>155966926383.7052</v>
+        <v>171691843126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1312,19 +1312,19 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.008131159625435827</v>
+        <v>0.008116349688732294</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1343,34 +1343,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>531.61</v>
+        <v>582.04</v>
       </c>
       <c r="F14" t="n">
-        <v>9993028627</v>
+        <v>10946267634</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>138577997</v>
+        <v>213999830</v>
       </c>
       <c r="I14" t="n">
-        <v>544.41</v>
+        <v>605</v>
       </c>
       <c r="J14" t="n">
-        <v>502.16</v>
+        <v>537.42</v>
       </c>
       <c r="K14" t="n">
-        <v>29.06</v>
+        <v>47.71</v>
       </c>
       <c r="L14" t="n">
-        <v>5.78332</v>
+        <v>8.926119999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>18806245.33931784</v>
+        <v>18806665.92890474</v>
       </c>
       <c r="N14" t="n">
-        <v>18806257.93928528</v>
+        <v>18806692.32885915</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1379,220 +1379,220 @@
         <v>46036.48202546296</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R14" t="b">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.006013239448401412</v>
+        <v>0.0063468406708534</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.999767</v>
+        <v>83.14</v>
       </c>
       <c r="F15" t="n">
-        <v>9562217003</v>
+        <v>9884929159</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>141420739</v>
+        <v>129651249</v>
       </c>
       <c r="I15" t="n">
-        <v>0.999965</v>
+        <v>83.64</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999596</v>
+        <v>82.25</v>
       </c>
       <c r="K15" t="n">
-        <v>9.39e-06</v>
+        <v>2.81</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00094</v>
+        <v>3.54404</v>
       </c>
       <c r="M15" t="n">
-        <v>9564389019.369761</v>
+        <v>118887984</v>
       </c>
       <c r="N15" t="n">
-        <v>9565459355.707329</v>
+        <v>293457483</v>
       </c>
       <c r="O15" t="n">
-        <v>1.057</v>
+        <v>83.64</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>45593.90336805556</v>
+        <v>46283.82569444444</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005738493224667324</v>
+        <v>0.005696710860147328</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>80.44</v>
+        <v>0.01392643</v>
       </c>
       <c r="F16" t="n">
-        <v>9482447599</v>
+        <v>9877121902</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>112012858</v>
+        <v>24502476</v>
       </c>
       <c r="I16" t="n">
-        <v>80.70999999999999</v>
+        <v>0.01403534</v>
       </c>
       <c r="J16" t="n">
-        <v>78.51000000000001</v>
+        <v>0.01258685</v>
       </c>
       <c r="K16" t="n">
-        <v>1.56</v>
+        <v>0.00113075</v>
       </c>
       <c r="L16" t="n">
-        <v>1.97292</v>
+        <v>8.83832</v>
       </c>
       <c r="M16" t="n">
-        <v>117882016</v>
+        <v>709234380366.2201</v>
       </c>
       <c r="N16" t="n">
-        <v>293532015</v>
+        <v>1142408526965.963</v>
       </c>
       <c r="O16" t="n">
-        <v>83.22</v>
+        <v>0.01946402</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>46276.58553240741</v>
+        <v>46259.82847222222</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>0.005687621007443865</v>
+        <v>0.005691928473910418</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.01278862</v>
+        <v>0.999902</v>
       </c>
       <c r="F17" t="n">
-        <v>9073126084</v>
+        <v>9594602900</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>27820992</v>
+        <v>135400991</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01310816</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01260467</v>
+        <v>0.9997779999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.000263625237508211</v>
+        <v>0.00012737</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.01977</v>
+        <v>0.01791</v>
       </c>
       <c r="M17" t="n">
-        <v>709234074452.8706</v>
+        <v>9595541701.9596</v>
       </c>
       <c r="N17" t="n">
-        <v>1142408526965.963</v>
+        <v>9593827178.349619</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01946402</v>
+        <v>1.057</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>46259.82847222222</v>
+        <v>45593.90336805556</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005426579906706606</v>
+        <v>0.005518869615103732</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1611,28 +1611,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.82</v>
+        <v>12.52</v>
       </c>
       <c r="F18" t="n">
-        <v>8843197796</v>
+        <v>9366762678</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>465095252</v>
+        <v>519635409</v>
       </c>
       <c r="I18" t="n">
-        <v>11.95</v>
+        <v>12.6</v>
       </c>
       <c r="J18" t="n">
-        <v>11.22</v>
+        <v>11.99</v>
       </c>
       <c r="K18" t="n">
-        <v>0.575928</v>
+        <v>0.708727</v>
       </c>
       <c r="L18" t="n">
-        <v>5.12126</v>
+        <v>6.05539</v>
       </c>
       <c r="M18" t="n">
         <v>748099970.424884</v>
@@ -1647,153 +1647,153 @@
         <v>44325.67635416667</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005279945216883001</v>
+        <v>0.005379304599899615</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>leo-token</t>
+          <t>cardano</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>ada</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LEO Token</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.9</v>
+        <v>0.226696</v>
       </c>
       <c r="F19" t="n">
-        <v>8184667580</v>
+        <v>8506282135</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>76720</v>
+        <v>663518519</v>
       </c>
       <c r="I19" t="n">
-        <v>8.93</v>
+        <v>0.234678</v>
       </c>
       <c r="J19" t="n">
-        <v>8.890000000000001</v>
+        <v>0.216904</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.01999754405595056</v>
+        <v>0.01201744</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.22424</v>
+        <v>5.67518</v>
       </c>
       <c r="M19" t="n">
-        <v>919857851.9</v>
+        <v>37522923322.16203</v>
       </c>
       <c r="N19" t="n">
-        <v>985239504</v>
+        <v>45000000000</v>
       </c>
       <c r="O19" t="n">
-        <v>10.61</v>
+        <v>3.09</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>46146.39930555555</v>
+        <v>44440.91678240741</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004859973516999635</v>
+        <v>0.004852211626532332</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>cardano</t>
+          <t>leo-token</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ada</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>LEO Token</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.21587</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>8101095616</v>
+        <v>8172462611</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>552742767</v>
+        <v>53547</v>
       </c>
       <c r="I20" t="n">
-        <v>0.216996</v>
+        <v>8.92</v>
       </c>
       <c r="J20" t="n">
-        <v>0.199529</v>
+        <v>8.81</v>
       </c>
       <c r="K20" t="n">
-        <v>0.01551854</v>
+        <v>-0.01326123114329647</v>
       </c>
       <c r="L20" t="n">
-        <v>7.74566</v>
+        <v>-0.14903</v>
       </c>
       <c r="M20" t="n">
-        <v>37522923322.16203</v>
+        <v>919857851.9</v>
       </c>
       <c r="N20" t="n">
-        <v>45000000000</v>
+        <v>985239504</v>
       </c>
       <c r="O20" t="n">
-        <v>3.09</v>
+        <v>10.61</v>
       </c>
       <c r="P20" s="1" t="n">
-        <v>44440.91678240741</v>
+        <v>46146.39930555555</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004806676251466612</v>
+        <v>0.004647728298112422</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1812,31 +1812,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.186694</v>
+        <v>0.199434</v>
       </c>
       <c r="F21" t="n">
-        <v>6499674331</v>
+        <v>6953702577</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>190708288</v>
+        <v>273347233</v>
       </c>
       <c r="I21" t="n">
-        <v>0.18919</v>
+        <v>0.196206</v>
       </c>
       <c r="J21" t="n">
-        <v>0.182408</v>
+        <v>0.189492</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00268673</v>
+        <v>0.01351744</v>
       </c>
       <c r="L21" t="n">
-        <v>1.46012</v>
+        <v>7.31125</v>
       </c>
       <c r="M21" t="n">
-        <v>34845172352.88166</v>
+        <v>34867269295.95199</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70148</v>
@@ -1848,19 +1848,19 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.003785384284977933</v>
+        <v>0.003901168883877915</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1879,34 +1879,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>8.789999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="F22" t="n">
-        <v>5460492757</v>
+        <v>5631064554</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>2254307216</v>
+        <v>1435766007</v>
       </c>
       <c r="I22" t="n">
-        <v>9.390000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="J22" t="n">
-        <v>7.03</v>
+        <v>8.6</v>
       </c>
       <c r="K22" t="n">
-        <v>1.75</v>
+        <v>0.422102</v>
       </c>
       <c r="L22" t="n">
-        <v>24.79101</v>
+        <v>5.0829</v>
       </c>
       <c r="M22" t="n">
-        <v>621108422.6104751</v>
+        <v>620990422.6104751</v>
       </c>
       <c r="N22" t="n">
-        <v>888250418.9163101</v>
+        <v>888238418.9163101</v>
       </c>
       <c r="O22" t="n">
         <v>44.92</v>
@@ -1915,19 +1915,19 @@
         <v>44318.89240740741</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.003122655618142922</v>
+        <v>0.003090978329422003</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1946,34 +1946,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>249.65</v>
+        <v>251.99</v>
       </c>
       <c r="F23" t="n">
-        <v>5016474464</v>
+        <v>5062765144</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>244794593</v>
+        <v>295039948</v>
       </c>
       <c r="I23" t="n">
-        <v>250.55</v>
+        <v>264.9</v>
       </c>
       <c r="J23" t="n">
-        <v>226.76</v>
+        <v>245.38</v>
       </c>
       <c r="K23" t="n">
-        <v>24.4</v>
+        <v>2.27</v>
       </c>
       <c r="L23" t="n">
-        <v>10.83102</v>
+        <v>0.92301</v>
       </c>
       <c r="M23" t="n">
-        <v>20090740.52165077</v>
+        <v>20091159.27165077</v>
       </c>
       <c r="N23" t="n">
-        <v>20090768.64665077</v>
+        <v>20091462.39665077</v>
       </c>
       <c r="O23" t="n">
         <v>3785.82</v>
@@ -1982,153 +1982,153 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.002839486960487097</v>
+        <v>0.002742862816274633</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>ethena-usde</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>usde</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Ethena USDe</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.65</v>
+        <v>0.999699</v>
       </c>
       <c r="F24" t="n">
-        <v>4768990338</v>
+        <v>4806809632</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>2076188545</v>
+        <v>32606200</v>
       </c>
       <c r="I24" t="n">
-        <v>3.61</v>
+        <v>0.999931</v>
       </c>
       <c r="J24" t="n">
-        <v>2.81</v>
+        <v>0.999394</v>
       </c>
       <c r="K24" t="n">
-        <v>0.793762</v>
+        <v>0.00028496</v>
       </c>
       <c r="L24" t="n">
-        <v>27.77192</v>
+        <v>0.02919</v>
       </c>
       <c r="M24" t="n">
-        <v>1306651055</v>
+        <v>4808257984.85422</v>
       </c>
       <c r="N24" t="n">
-        <v>1306651049</v>
+        <v>4832281815.490858</v>
       </c>
       <c r="O24" t="n">
-        <v>20.44</v>
+        <v>1.034</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>44577.59010416667</v>
+        <v>46000.38208333333</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002681656193477358</v>
+        <v>0.002586075596659575</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ethena-usde</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>usde</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ethena USDe</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.999391</v>
+        <v>3.63</v>
       </c>
       <c r="F25" t="n">
-        <v>4772921019</v>
+        <v>4739515967</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>31566827</v>
+        <v>1304547274</v>
       </c>
       <c r="I25" t="n">
-        <v>0.99955</v>
+        <v>3.91</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9990830000000001</v>
+        <v>3.57</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.692927984952599e-05</v>
+        <v>0.02360836</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.0067</v>
+        <v>0.62856</v>
       </c>
       <c r="M25" t="n">
-        <v>4775827775.692125</v>
+        <v>1306731469</v>
       </c>
       <c r="N25" t="n">
-        <v>4798657893.686825</v>
+        <v>1306731496</v>
       </c>
       <c r="O25" t="n">
-        <v>1.034</v>
+        <v>20.44</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>46000.38208333333</v>
+        <v>44577.59010416667</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002684162949797966</v>
+        <v>0.002544854422907094</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2147,34 +2147,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0.999908</v>
       </c>
       <c r="F26" t="n">
-        <v>4578867048</v>
+        <v>4597242919</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>257162840</v>
+        <v>248389251</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>0.999726</v>
+        <v>0.999708</v>
       </c>
       <c r="K26" t="n">
-        <v>0.00019033</v>
+        <v>-6.7611320880401e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01904</v>
+        <v>0.01342</v>
       </c>
       <c r="M26" t="n">
-        <v>4578574950.264173</v>
+        <v>4597666728.880691</v>
       </c>
       <c r="N26" t="n">
-        <v>4575207021.076258</v>
+        <v>4588681220.277516</v>
       </c>
       <c r="O26" t="n">
         <v>1.22</v>
@@ -2183,86 +2183,86 @@
         <v>43902.79363425926</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002560406781759069</v>
+        <v>0.002457704138673013</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>usd1-wlfi</t>
+          <t>litecoin</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>usd1</t>
+          <t>ltc</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>USD1</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.999174</v>
+        <v>58.01</v>
       </c>
       <c r="F27" t="n">
-        <v>4343272623</v>
+        <v>4503368511</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>950429360</v>
+        <v>431386158</v>
       </c>
       <c r="I27" t="n">
-        <v>0.999248</v>
+        <v>59.16</v>
       </c>
       <c r="J27" t="n">
-        <v>0.998936</v>
+        <v>55.4</v>
       </c>
       <c r="K27" t="n">
-        <v>5.078e-05</v>
+        <v>2.84</v>
       </c>
       <c r="L27" t="n">
-        <v>0.00508</v>
+        <v>5.21912</v>
       </c>
       <c r="M27" t="n">
-        <v>4346798749.096848</v>
+        <v>77624504.44021429</v>
       </c>
       <c r="N27" t="n">
-        <v>4346798749.096848</v>
+        <v>77627366.94755507</v>
       </c>
       <c r="O27" t="n">
-        <v>1.048</v>
+        <v>410.26</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>46212.42696759259</v>
+        <v>44325.80077546297</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002410158564218973</v>
+        <v>0.002400200757291137</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2281,34 +2281,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.108678</v>
+        <v>0.111067</v>
       </c>
       <c r="F28" t="n">
-        <v>4305137059</v>
+        <v>4402165335</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>20082534</v>
+        <v>10920109</v>
       </c>
       <c r="I28" t="n">
-        <v>0.112495</v>
+        <v>0.113569</v>
       </c>
       <c r="J28" t="n">
-        <v>0.098889</v>
+        <v>0.107754</v>
       </c>
       <c r="K28" t="n">
-        <v>0.00801662</v>
+        <v>0.00329884</v>
       </c>
       <c r="L28" t="n">
-        <v>7.96391</v>
+        <v>3.10572</v>
       </c>
       <c r="M28" t="n">
-        <v>39627697476.64375</v>
+        <v>39635347931.85809</v>
       </c>
       <c r="N28" t="n">
-        <v>39628294476.72729</v>
+        <v>39635347931.85809</v>
       </c>
       <c r="O28" t="n">
         <v>0.194152</v>
@@ -2317,220 +2317,220 @@
         <v>46056.00148148148</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002385837952575101</v>
+        <v>0.002338208091232617</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>litecoin</t>
+          <t>usd1-wlfi</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ltc</t>
+          <t>usd1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>USD1</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>55.17</v>
+        <v>0.9996429999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>4282135782</v>
+        <v>4355242509</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>278606277</v>
+        <v>1209396989</v>
       </c>
       <c r="I29" t="n">
-        <v>55.96</v>
+        <v>0.999766</v>
       </c>
       <c r="J29" t="n">
-        <v>52.64</v>
+        <v>0.999263</v>
       </c>
       <c r="K29" t="n">
-        <v>2.38</v>
+        <v>0.00046674</v>
       </c>
       <c r="L29" t="n">
-        <v>4.50704</v>
+        <v>0.04476</v>
       </c>
       <c r="M29" t="n">
-        <v>77620798.18076394</v>
+        <v>4356798749.096847</v>
       </c>
       <c r="N29" t="n">
-        <v>77620816.93088555</v>
+        <v>4356798749.096847</v>
       </c>
       <c r="O29" t="n">
-        <v>410.26</v>
+        <v>1.048</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>44325.80077546297</v>
+        <v>46212.42696759259</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002371169095829464</v>
+        <v>0.002309465207879431</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>the-open-network</t>
+          <t>avalanche-2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>gram</t>
+          <t>avax</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Gram (prev. Toncoin)</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.37</v>
+        <v>9.33</v>
       </c>
       <c r="F30" t="n">
-        <v>3824472057</v>
+        <v>4132083352</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>36381124</v>
+        <v>736451226</v>
       </c>
       <c r="I30" t="n">
-        <v>1.37</v>
+        <v>9.35</v>
       </c>
       <c r="J30" t="n">
-        <v>1.33</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.03610414</v>
+        <v>1.34</v>
       </c>
       <c r="L30" t="n">
-        <v>2.71316</v>
+        <v>16.80374</v>
       </c>
       <c r="M30" t="n">
-        <v>2797860400.195174</v>
+        <v>442873736.1288731</v>
       </c>
       <c r="N30" t="n">
-        <v>5251239978.193309</v>
+        <v>469542447.6310036</v>
       </c>
       <c r="O30" t="n">
-        <v>8.25</v>
+        <v>144.96</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>45457.69225694444</v>
+        <v>44521.26314814815</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>0.002079298187109911</v>
+        <v>0.00217276760959653</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>avalanche-2</t>
+          <t>the-open-network</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>avax</t>
+          <t>gram</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Gram (prev. Toncoin)</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>8.050000000000001</v>
+        <v>1.39</v>
       </c>
       <c r="F31" t="n">
-        <v>3564409188</v>
+        <v>3881514914</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>341203798</v>
+        <v>37331609</v>
       </c>
       <c r="I31" t="n">
-        <v>8.02</v>
+        <v>1.39</v>
       </c>
       <c r="J31" t="n">
-        <v>7.53</v>
+        <v>1.35</v>
       </c>
       <c r="K31" t="n">
-        <v>0.460474</v>
+        <v>0.02007921</v>
       </c>
       <c r="L31" t="n">
-        <v>6.06813</v>
+        <v>1.49008</v>
       </c>
       <c r="M31" t="n">
-        <v>442859844.5502368</v>
+        <v>2798418312.826097</v>
       </c>
       <c r="N31" t="n">
-        <v>469528544.5502368</v>
+        <v>5251809962.746284</v>
       </c>
       <c r="O31" t="n">
-        <v>144.96</v>
+        <v>8.25</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>44521.26314814815</v>
+        <v>45457.69225694444</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.001913445440315867</v>
+        <v>0.002019280277324084</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2549,31 +2549,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.077292</v>
+        <v>0.08067199999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>3386438008</v>
+        <v>3535989216</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>84016076</v>
+        <v>98941677</v>
       </c>
       <c r="I32" t="n">
-        <v>0.078053</v>
+        <v>0.080799</v>
       </c>
       <c r="J32" t="n">
-        <v>0.073949</v>
+        <v>0.077612</v>
       </c>
       <c r="K32" t="n">
-        <v>0.00272201</v>
+        <v>0.00359811</v>
       </c>
       <c r="L32" t="n">
-        <v>3.65028</v>
+        <v>4.76082</v>
       </c>
       <c r="M32" t="n">
-        <v>43831556054.63917</v>
+        <v>43831706402.06228</v>
       </c>
       <c r="N32" t="n">
         <v>50000000000</v>
@@ -2585,153 +2585,153 @@
         <v>44454.11143518519</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001799945927037878</v>
+        <v>0.001807626255608888</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>global-dollar</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>usdg</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Global Dollar</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.999974</v>
+        <v>0.850953</v>
       </c>
       <c r="F33" t="n">
-        <v>3277171964</v>
+        <v>3485961697</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>987110058</v>
+        <v>885201033</v>
       </c>
       <c r="I33" t="n">
+        <v>0.868613</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.796157</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.052166</v>
+      </c>
+      <c r="L33" t="n">
+        <v>6.6382</v>
+      </c>
+      <c r="M33" t="n">
+        <v>4096537146.540959</v>
+      </c>
+      <c r="N33" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="O33" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="P33" s="1" t="n">
+        <v>45661.62243055556</v>
+      </c>
+      <c r="Q33" s="1" t="n">
+        <v>46284.54108796296</v>
+      </c>
+      <c r="R33" t="b">
         <v>1</v>
       </c>
-      <c r="J33" t="n">
-        <v>0.999846</v>
-      </c>
-      <c r="K33" t="n">
-        <v>4.477e-05</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0.00448</v>
-      </c>
-      <c r="M33" t="n">
-        <v>3277253193.314953</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3277764991.302639</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P33" s="1" t="n">
-        <v>45686.67436342593</v>
-      </c>
-      <c r="Q33" s="1" t="n">
-        <v>46283.56203703704</v>
-      </c>
-      <c r="R33" t="b">
-        <v>0</v>
-      </c>
       <c r="S33" t="n">
-        <v>0.001730262493957246</v>
+        <v>0.001776981572292791</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>global-dollar</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>usdg</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>Global Dollar</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.799369</v>
+        <v>0.999862</v>
       </c>
       <c r="F34" t="n">
-        <v>3275696110</v>
+        <v>3259123737</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>609142705</v>
+        <v>914713989</v>
       </c>
       <c r="I34" t="n">
-        <v>0.800675</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>0.722626</v>
+        <v>0.999776</v>
       </c>
       <c r="K34" t="n">
-        <v>0.07224700000000001</v>
+        <v>-0.000110598148557184</v>
       </c>
       <c r="L34" t="n">
-        <v>9.936070000000001</v>
+        <v>-0.00652</v>
       </c>
       <c r="M34" t="n">
-        <v>4096537146.540959</v>
+        <v>3259575067.166086</v>
       </c>
       <c r="N34" t="n">
-        <v>10000000000</v>
+        <v>3259575067.166086</v>
       </c>
       <c r="O34" t="n">
-        <v>5.35</v>
+        <v>1.65</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>45661.62243055556</v>
+        <v>45686.67436342593</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001729321281393114</v>
+        <v>0.001638030499218999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2750,34 +2750,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5.37e-06</v>
+        <v>5.48e-06</v>
       </c>
       <c r="F35" t="n">
-        <v>3163842188</v>
+        <v>3227703703</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>107036297</v>
+        <v>89625103</v>
       </c>
       <c r="I35" t="n">
-        <v>5.44e-06</v>
+        <v>5.51e-06</v>
       </c>
       <c r="J35" t="n">
-        <v>5.06e-06</v>
+        <v>5.37e-06</v>
       </c>
       <c r="K35" t="n">
-        <v>3.03228e-07</v>
+        <v>9.948e-08</v>
       </c>
       <c r="L35" t="n">
-        <v>5.98639</v>
+        <v>1.85543</v>
       </c>
       <c r="M35" t="n">
-        <v>589239049876142.6</v>
+        <v>589239049649142.6</v>
       </c>
       <c r="N35" t="n">
-        <v>589496073530830.6</v>
+        <v>589496073303830.6</v>
       </c>
       <c r="O35" t="n">
         <v>8.616e-05</v>
@@ -2786,220 +2786,220 @@
         <v>44496.82980324074</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001657987452481972</v>
+        <v>0.001618783952299273</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>crypto-com-chain</t>
+          <t>bittensor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>cro</t>
+          <t>tao</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cronos</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.059222</v>
+        <v>265.37</v>
       </c>
       <c r="F36" t="n">
-        <v>2944707211</v>
+        <v>3009165450</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>8117944</v>
+        <v>333417078</v>
       </c>
       <c r="I36" t="n">
-        <v>0.059787</v>
+        <v>271.96</v>
       </c>
       <c r="J36" t="n">
-        <v>0.057196</v>
+        <v>246.72</v>
       </c>
       <c r="K36" t="n">
-        <v>0.00141129</v>
+        <v>18.77</v>
       </c>
       <c r="L36" t="n">
-        <v>2.44125</v>
+        <v>7.67099</v>
       </c>
       <c r="M36" t="n">
-        <v>49728972620.92609</v>
+        <v>11339645.9251</v>
       </c>
       <c r="N36" t="n">
-        <v>98928969658.44186</v>
+        <v>21000000</v>
       </c>
       <c r="O36" t="n">
-        <v>0.891544</v>
+        <v>757.6</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>44523.66666666666</v>
+        <v>45358.44833333333</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001518236099303984</v>
+        <v>0.00148491691892434</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>memecore</t>
+          <t>crypto-com-chain</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>cro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MemeCore</t>
+          <t>Cronos</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1.29</v>
+        <v>0.059987</v>
       </c>
       <c r="F37" t="n">
-        <v>2931281436</v>
+        <v>2983222544</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>1724362</v>
+        <v>10539800</v>
       </c>
       <c r="I37" t="n">
-        <v>1.33</v>
+        <v>0.060428</v>
       </c>
       <c r="J37" t="n">
-        <v>1.13</v>
+        <v>0.058546</v>
       </c>
       <c r="K37" t="n">
-        <v>0.16002</v>
+        <v>0.00087021</v>
       </c>
       <c r="L37" t="n">
-        <v>14.17474</v>
+        <v>1.47573</v>
       </c>
       <c r="M37" t="n">
-        <v>2274172592.558846</v>
+        <v>49730956672.65237</v>
       </c>
       <c r="N37" t="n">
-        <v>5415562438.891223</v>
+        <v>98930992992.14902</v>
       </c>
       <c r="O37" t="n">
-        <v>5.64</v>
+        <v>0.891544</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>46205.17638888889</v>
+        <v>44523.66666666666</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.00150967393250889</v>
+        <v>0.001469025422512749</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>bittensor</t>
+          <t>memecore</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>tao</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>MemeCore</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>247.27</v>
+        <v>1.29</v>
       </c>
       <c r="F38" t="n">
-        <v>2804711067</v>
+        <v>2937160197</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
       </c>
       <c r="H38" t="n">
-        <v>235965657</v>
+        <v>1933129</v>
       </c>
       <c r="I38" t="n">
-        <v>251.24</v>
+        <v>1.38</v>
       </c>
       <c r="J38" t="n">
-        <v>225.84</v>
+        <v>1.27</v>
       </c>
       <c r="K38" t="n">
-        <v>20.55</v>
+        <v>0.00587505</v>
       </c>
       <c r="L38" t="n">
-        <v>9.063789999999999</v>
+        <v>0.42336</v>
       </c>
       <c r="M38" t="n">
-        <v>11339645.9251</v>
+        <v>2274542875.649129</v>
       </c>
       <c r="N38" t="n">
-        <v>21000000</v>
+        <v>5415932722.156354</v>
       </c>
       <c r="O38" t="n">
-        <v>757.6</v>
+        <v>5.64</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>45358.44833333333</v>
+        <v>46205.17638888889</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001428954822387153</v>
+        <v>0.001440809631187755</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3018,34 +3018,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.999743</v>
+        <v>0.999916</v>
       </c>
       <c r="F39" t="n">
-        <v>2788292790</v>
+        <v>2802423965</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>84854717</v>
+        <v>74089421</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0.998889</v>
+        <v>0.999807</v>
       </c>
       <c r="K39" t="n">
-        <v>0.00039146</v>
+        <v>0.0001641</v>
       </c>
       <c r="L39" t="n">
-        <v>0.03917</v>
+        <v>0.02013</v>
       </c>
       <c r="M39" t="n">
-        <v>2789009291.248121</v>
+        <v>2802658207.994529</v>
       </c>
       <c r="N39" t="n">
-        <v>2789009291.248121</v>
+        <v>2802658207.994529</v>
       </c>
       <c r="O39" t="n">
         <v>1.021</v>
@@ -3054,19 +3054,19 @@
         <v>45222.61454861111</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001418484214458593</v>
+        <v>0.001358276072790742</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3085,28 +3085,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4362.11</v>
+        <v>4373.64</v>
       </c>
       <c r="F40" t="n">
-        <v>2716798606</v>
+        <v>2724008200</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>186499015</v>
+        <v>129160606</v>
       </c>
       <c r="I40" t="n">
-        <v>4392.46</v>
+        <v>4392.89</v>
       </c>
       <c r="J40" t="n">
-        <v>4333.61</v>
+        <v>4345.82</v>
       </c>
       <c r="K40" t="n">
-        <v>0.821041</v>
+        <v>6.84</v>
       </c>
       <c r="L40" t="n">
-        <v>0.01883</v>
+        <v>0.19182</v>
       </c>
       <c r="M40" t="n">
         <v>622823.6595320001</v>
@@ -3121,108 +3121,108 @@
         <v>46050.66666666666</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.00137288944407944</v>
+        <v>0.001310241984084195</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>hashnote-usyc</t>
+          <t>okb</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>usyc</t>
+          <t>okb</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Circle USYC</t>
+          <t>OKB</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1.14</v>
+        <v>121.74</v>
       </c>
       <c r="F41" t="n">
-        <v>2556077986</v>
+        <v>2556533363</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>53843878</v>
       </c>
       <c r="I41" t="n">
-        <v>1.14</v>
+        <v>122.95</v>
       </c>
       <c r="J41" t="n">
-        <v>1.14</v>
+        <v>115.02</v>
       </c>
       <c r="K41" t="n">
-        <v>0.00034598</v>
+        <v>7.64</v>
       </c>
       <c r="L41" t="n">
-        <v>0.03042</v>
+        <v>6.70177</v>
       </c>
       <c r="M41" t="n">
-        <v>2246365281.581388</v>
+        <v>21000000</v>
       </c>
       <c r="N41" t="n">
-        <v>2246365281.581388</v>
+        <v>21000000</v>
       </c>
       <c r="O41" t="n">
-        <v>1.14</v>
+        <v>228.74</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>46283.52430555555</v>
+        <v>45934.66666666666</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001270391319699209</v>
+        <v>0.001207654179494486</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>blackrock-usd-institutional-digital-liquidity-fund</t>
+          <t>hashnote-usyc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>buidl</t>
+          <t>usyc</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund</t>
+          <t>Circle USYC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="F42" t="n">
-        <v>2401998374</v>
+        <v>2508311923</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
@@ -3231,10 +3231,10 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3243,165 +3243,165 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2401998374.270448</v>
+        <v>2204386896.824222</v>
       </c>
       <c r="N42" t="n">
-        <v>2401998374.270449</v>
+        <v>2204386896.824222</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>45699.87511574074</v>
+        <v>46283.52430555555</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001172128438214346</v>
+        <v>0.001178115821658947</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>okb</t>
+          <t>ripple-usd</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>okb</t>
+          <t>rlusd</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>OKB</t>
+          <t>Ripple USD</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>113.96</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>2393106804</v>
+        <v>2379074812</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>24147277</v>
+        <v>115946978</v>
       </c>
       <c r="I43" t="n">
-        <v>114.94</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>111.58</v>
+        <v>0.999839</v>
       </c>
       <c r="K43" t="n">
-        <v>1.86</v>
+        <v>9.816e-05</v>
       </c>
       <c r="L43" t="n">
-        <v>1.65929</v>
+        <v>0.01142</v>
       </c>
       <c r="M43" t="n">
-        <v>21000000</v>
+        <v>2378997051.087129</v>
       </c>
       <c r="N43" t="n">
-        <v>21000000</v>
+        <v>2378997051.087127</v>
       </c>
       <c r="O43" t="n">
-        <v>228.74</v>
+        <v>1.073</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>45934.66666666666</v>
+        <v>45652.11518518518</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001166457919722098</v>
+        <v>0.001098950785725779</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ripple-usd</t>
+          <t>blackrock-usd-institutional-digital-liquidity-fund</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>rlusd</t>
+          <t>buidl</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ripple USD</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund</t>
         </is>
       </c>
       <c r="E44" t="n">
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>2348698435</v>
+        <v>2329036631</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>167724819</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>0.999686</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>4.037e-05</v>
+        <v>1.11e-16</v>
       </c>
       <c r="L44" t="n">
-        <v>0.00404</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2348574551.087477</v>
+        <v>2329036630.620448</v>
       </c>
       <c r="N44" t="n">
-        <v>2348674551.087477</v>
+        <v>2329036630.620449</v>
       </c>
       <c r="O44" t="n">
-        <v>1.073</v>
+        <v>1</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>45652.11518518518</v>
+        <v>45699.87511574074</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001138136883321883</v>
+        <v>0.001068299571331986</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3420,16 +3420,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="F45" t="n">
-        <v>2240578177</v>
+        <v>2250644223</v>
       </c>
       <c r="G45" t="n">
         <v>44</v>
       </c>
       <c r="H45" t="n">
-        <v>2302257</v>
+        <v>1401621</v>
       </c>
       <c r="I45" t="n">
         <v>1.15</v>
@@ -3438,16 +3438,16 @@
         <v>1.14</v>
       </c>
       <c r="K45" t="n">
-        <v>0.00095087</v>
+        <v>0.00257079</v>
       </c>
       <c r="L45" t="n">
-        <v>0.08312</v>
+        <v>0.28132</v>
       </c>
       <c r="M45" t="n">
-        <v>1955826437.104192</v>
+        <v>1963196048.466981</v>
       </c>
       <c r="N45" t="n">
-        <v>1955826437.104191</v>
+        <v>1963196048.46698</v>
       </c>
       <c r="O45" t="n">
         <v>1.26</v>
@@ -3456,19 +3456,19 @@
         <v>45377.89175925926</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.001069184164918315</v>
+        <v>0.00102027979010825</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3487,31 +3487,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>138.14</v>
+        <v>142.5</v>
       </c>
       <c r="F46" t="n">
-        <v>2131202453</v>
+        <v>2198543761</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>337041822</v>
+        <v>357964281</v>
       </c>
       <c r="I46" t="n">
-        <v>137.77</v>
+        <v>146.6</v>
       </c>
       <c r="J46" t="n">
-        <v>124.21</v>
+        <v>136.91</v>
       </c>
       <c r="K46" t="n">
-        <v>13.85</v>
+        <v>5.1</v>
       </c>
       <c r="L46" t="n">
-        <v>11.14285</v>
+        <v>3.66088</v>
       </c>
       <c r="M46" t="n">
-        <v>15427945.63274938</v>
+        <v>15428034.66896128</v>
       </c>
       <c r="N46" t="n">
         <v>16000000</v>
@@ -3523,19 +3523,19 @@
         <v>44334.55554398148</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0009994307844079005</v>
+        <v>0.00098836531202645</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3554,28 +3554,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.750459</v>
+        <v>0.768416</v>
       </c>
       <c r="F47" t="n">
-        <v>2029711486</v>
+        <v>2077850549</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>105439785</v>
+        <v>144253256</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7589</v>
+        <v>0.790454</v>
       </c>
       <c r="J47" t="n">
-        <v>0.735137</v>
+        <v>0.743399</v>
       </c>
       <c r="K47" t="n">
-        <v>0.01330934</v>
+        <v>0.01797252</v>
       </c>
       <c r="L47" t="n">
-        <v>1.80551</v>
+        <v>2.42583</v>
       </c>
       <c r="M47" t="n">
         <v>2704071066.799731</v>
@@ -3590,1024 +3590,1024 @@
         <v>45924.13766203704</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0009347058364887352</v>
+        <v>0.0009144338971956932</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>ondo-finance</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>ondo</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>Ondo</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.00421794</v>
+        <v>0.425945</v>
       </c>
       <c r="F48" t="n">
-        <v>1974322461</v>
+        <v>2074065760</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>178993049</v>
+        <v>233956955</v>
       </c>
       <c r="I48" t="n">
-        <v>0.00432743</v>
+        <v>0.41497</v>
       </c>
       <c r="J48" t="n">
-        <v>0.00390878</v>
+        <v>0.392623</v>
       </c>
       <c r="K48" t="n">
-        <v>0.00024496</v>
+        <v>0.03092754</v>
       </c>
       <c r="L48" t="n">
-        <v>6.16552</v>
+        <v>7.91917</v>
       </c>
       <c r="M48" t="n">
-        <v>467830826317.6539</v>
+        <v>4869330647</v>
       </c>
       <c r="N48" t="n">
-        <v>833342646572.925</v>
+        <v>10000000000</v>
       </c>
       <c r="O48" t="n">
-        <v>0.00881908</v>
+        <v>2.14</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>45914.36296296296</v>
+        <v>45641.69166666667</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R48" t="b">
         <v>1</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0008993819858605475</v>
+        <v>0.0009121154999886831</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>polkadot</t>
+          <t>mantle</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>dot</t>
+          <t>mnt</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Mantle</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1.15</v>
+        <v>0.623375</v>
       </c>
       <c r="F49" t="n">
-        <v>1967870820</v>
+        <v>2058567278</v>
       </c>
       <c r="G49" t="n">
         <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>281422394</v>
+        <v>36418018</v>
       </c>
       <c r="I49" t="n">
-        <v>1.17</v>
+        <v>0.630436</v>
       </c>
       <c r="J49" t="n">
-        <v>1.028</v>
+        <v>0.593005</v>
       </c>
       <c r="K49" t="n">
-        <v>0.119869</v>
+        <v>0.03647781</v>
       </c>
       <c r="L49" t="n">
-        <v>11.58255</v>
+        <v>6.24446</v>
       </c>
       <c r="M49" t="n">
-        <v>1703333666.274981</v>
+        <v>3302294382.53684</v>
       </c>
       <c r="N49" t="n">
-        <v>1703340562.729311</v>
+        <v>6219316794.889999</v>
       </c>
       <c r="O49" t="n">
-        <v>54.98</v>
+        <v>2.86</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>44504.25704861111</v>
+        <v>45938.71164351852</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R49" t="b">
         <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0008952675100597784</v>
+        <v>0.0009026218036738561</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>mantle</t>
+          <t>ethena</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>mnt</t>
+          <t>ena</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mantle</t>
+          <t>Ethena</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.589264</v>
+        <v>0.196643</v>
       </c>
       <c r="F50" t="n">
-        <v>1946784134</v>
+        <v>1985168612</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>38160355</v>
+        <v>722630593</v>
       </c>
       <c r="I50" t="n">
-        <v>0.597494</v>
+        <v>0.195173</v>
       </c>
       <c r="J50" t="n">
-        <v>0.56402</v>
+        <v>0.162775</v>
       </c>
       <c r="K50" t="n">
-        <v>0.02248901</v>
+        <v>0.03399471</v>
       </c>
       <c r="L50" t="n">
-        <v>3.96789</v>
+        <v>21.00862</v>
       </c>
       <c r="M50" t="n">
-        <v>3302294382.53684</v>
+        <v>10095312500</v>
       </c>
       <c r="N50" t="n">
-        <v>6219316794.889999</v>
+        <v>15000000000</v>
       </c>
       <c r="O50" t="n">
-        <v>2.86</v>
+        <v>1.52</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>45938.71164351852</v>
+        <v>45393.21892361111</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" t="n">
-        <v>0.000881819666438998</v>
+        <v>0.0008576609717086736</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ondo-finance</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ondo</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Ondo</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.395727</v>
+        <v>0.00414921</v>
       </c>
       <c r="F51" t="n">
-        <v>1927543245</v>
+        <v>1940424994</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>285266113</v>
+        <v>148386496</v>
       </c>
       <c r="I51" t="n">
-        <v>0.39866</v>
+        <v>0.00444095</v>
       </c>
       <c r="J51" t="n">
-        <v>0.36607</v>
+        <v>0.00405448</v>
       </c>
       <c r="K51" t="n">
-        <v>0.02897538</v>
+        <v>-6.7927667411628e-05</v>
       </c>
       <c r="L51" t="n">
-        <v>7.90055</v>
+        <v>-1.57295</v>
       </c>
       <c r="M51" t="n">
-        <v>4869330647</v>
+        <v>467661147593.8102</v>
       </c>
       <c r="N51" t="n">
-        <v>10000000000</v>
+        <v>833163604241.7463</v>
       </c>
       <c r="O51" t="n">
-        <v>2.14</v>
+        <v>0.00881908</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>45641.69166666667</v>
+        <v>45914.36296296296</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0008695489631906642</v>
+        <v>0.0008302529764405808</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>pax-gold</t>
+          <t>polkadot</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>paxg</t>
+          <t>dot</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PAX Gold</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4359.77</v>
+        <v>1.13</v>
       </c>
       <c r="F52" t="n">
-        <v>1894268516</v>
+        <v>1929873645</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>160238224</v>
+        <v>204374902</v>
       </c>
       <c r="I52" t="n">
-        <v>4390.95</v>
+        <v>1.16</v>
       </c>
       <c r="J52" t="n">
-        <v>4332.04</v>
+        <v>1.1</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.186490241558204</v>
+        <v>-0.008683841196597264</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.07303999999999999</v>
+        <v>-0.75322</v>
       </c>
       <c r="M52" t="n">
-        <v>434499.367539</v>
+        <v>1703483485.668379</v>
       </c>
       <c r="N52" t="n">
-        <v>434499.367539</v>
+        <v>1703489020.963728</v>
       </c>
       <c r="O52" t="n">
-        <v>5619.09</v>
+        <v>54.98</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>46050.93814814815</v>
+        <v>44504.25704861111</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R52" t="b">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0008483283051832443</v>
+        <v>0.0008237896787371185</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>world-liberty-financial</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>wlfi</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>World Liberty Financial</t>
+          <t>Morpho</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.057868</v>
+        <v>2.73</v>
       </c>
       <c r="F53" t="n">
-        <v>1838746916</v>
+        <v>1906683134</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>35661533</v>
+        <v>68936984</v>
       </c>
       <c r="I53" t="n">
-        <v>0.058888</v>
+        <v>2.81</v>
       </c>
       <c r="J53" t="n">
-        <v>0.05651</v>
+        <v>2.38</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.000128102341798934</v>
+        <v>0.297117</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.22088</v>
+        <v>12.06161</v>
       </c>
       <c r="M53" t="n">
-        <v>31777383848</v>
+        <v>698862182.2199675</v>
       </c>
       <c r="N53" t="n">
-        <v>100000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="O53" t="n">
-        <v>0.331336</v>
+        <v>4.17</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>45901.18065972222</v>
+        <v>45674.19883101852</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0008129199060457258</v>
+        <v>0.0008095841798489273</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>pax-gold</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>paxg</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>PAX Gold</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.67672</v>
+        <v>4366.16</v>
       </c>
       <c r="F54" t="n">
-        <v>1831877381</v>
+        <v>1897094993</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>7119621</v>
+        <v>111719882</v>
       </c>
       <c r="I54" t="n">
-        <v>0.748717</v>
+        <v>4388.3</v>
       </c>
       <c r="J54" t="n">
-        <v>0.662755</v>
+        <v>4341.8</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.01025005210828844</v>
+        <v>2.26</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.49207</v>
+        <v>0.08689</v>
       </c>
       <c r="M54" t="n">
-        <v>2708142280.000001</v>
+        <v>434499.367539</v>
       </c>
       <c r="N54" t="n">
-        <v>10000000000</v>
+        <v>434499.367539</v>
       </c>
       <c r="O54" t="n">
-        <v>0.789172</v>
+        <v>5619.09</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>46281.50775462963</v>
+        <v>46050.93814814815</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R54" t="b">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0008085389221193052</v>
+        <v>0.000803710901493167</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>world-liberty-financial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>wlfi</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Morpho</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2.43</v>
+        <v>0.058953</v>
       </c>
       <c r="F55" t="n">
-        <v>1697634147</v>
+        <v>1873382921</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>39225576</v>
+        <v>33080034</v>
       </c>
       <c r="I55" t="n">
-        <v>2.44</v>
+        <v>0.059313</v>
       </c>
       <c r="J55" t="n">
-        <v>2.16</v>
+        <v>0.058131</v>
       </c>
       <c r="K55" t="n">
-        <v>0.28278</v>
+        <v>0.00114767</v>
       </c>
       <c r="L55" t="n">
-        <v>13.17526</v>
+        <v>1.97488</v>
       </c>
       <c r="M55" t="n">
-        <v>698811224.6305897</v>
+        <v>31777393281</v>
       </c>
       <c r="N55" t="n">
-        <v>1000000000</v>
+        <v>100000000000</v>
       </c>
       <c r="O55" t="n">
-        <v>4.17</v>
+        <v>0.331336</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>45674.19883101852</v>
+        <v>45901.18065972222</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0007229265116163064</v>
+        <v>0.000789185917009957</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ethena</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ena</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Ethena</t>
+          <t>Sky</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.162882</v>
+        <v>0.069615</v>
       </c>
       <c r="F56" t="n">
-        <v>1643691501</v>
+        <v>1630341007</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>395914204</v>
+        <v>38229096</v>
       </c>
       <c r="I56" t="n">
-        <v>0.171363</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>0.150158</v>
+        <v>0.066331</v>
       </c>
       <c r="K56" t="n">
-        <v>0.01117441</v>
+        <v>0.00438045</v>
       </c>
       <c r="L56" t="n">
-        <v>7.36578</v>
+        <v>6.7081</v>
       </c>
       <c r="M56" t="n">
-        <v>10095312500</v>
+        <v>23419267381.19225</v>
       </c>
       <c r="N56" t="n">
-        <v>15000000000</v>
+        <v>23459804203.60596</v>
       </c>
       <c r="O56" t="n">
-        <v>1.52</v>
+        <v>0.100535</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>45393.21892361111</v>
+        <v>45630.09302083333</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R56" t="b">
         <v>1</v>
       </c>
       <c r="S56" t="n">
-        <v>0.000688525076137108</v>
+        <v>0.0006403090061427982</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>worldcoin-wld</t>
+          <t>internet-computer</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>wld</t>
+          <t>icp</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Worldcoin</t>
+          <t>Internet Computer</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.436069</v>
+        <v>2.9</v>
       </c>
       <c r="F57" t="n">
-        <v>1569712430</v>
+        <v>1614934309</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>338897392</v>
+        <v>55661757</v>
       </c>
       <c r="I57" t="n">
-        <v>0.444948</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
-        <v>0.371902</v>
+        <v>2.8</v>
       </c>
       <c r="K57" t="n">
-        <v>0.060714</v>
+        <v>0.085447</v>
       </c>
       <c r="L57" t="n">
-        <v>16.17523</v>
+        <v>3.01852</v>
       </c>
       <c r="M57" t="n">
-        <v>3598634710.039344</v>
+        <v>556901197.5075812</v>
       </c>
       <c r="N57" t="n">
-        <v>10000000000</v>
+        <v>556904308.555163</v>
       </c>
       <c r="O57" t="n">
-        <v>11.74</v>
+        <v>700.65</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>45360.67409722223</v>
+        <v>44326.33741898148</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0006413455915078677</v>
+        <v>0.0006308715327162877</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>internet-computer</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>icp</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Internet Computer</t>
+          <t>Pepe</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2.82</v>
+        <v>3.82e-06</v>
       </c>
       <c r="F58" t="n">
-        <v>1567418634</v>
+        <v>1605881714</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>51776621</v>
+        <v>312140947</v>
       </c>
       <c r="I58" t="n">
-        <v>2.83</v>
+        <v>3.89e-06</v>
       </c>
       <c r="J58" t="n">
-        <v>2.54</v>
+        <v>3.72e-06</v>
       </c>
       <c r="K58" t="n">
-        <v>0.267689</v>
+        <v>1.22452e-07</v>
       </c>
       <c r="L58" t="n">
-        <v>10.50747</v>
+        <v>3.36713</v>
       </c>
       <c r="M58" t="n">
-        <v>556900340.8723615</v>
+        <v>420690000000000</v>
       </c>
       <c r="N58" t="n">
-        <v>556900340.8723615</v>
+        <v>420690000000000</v>
       </c>
       <c r="O58" t="n">
-        <v>700.65</v>
+        <v>2.803e-05</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>44326.33741898148</v>
+        <v>45635.35457175926</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0006398827438178148</v>
+        <v>0.0006253263065585827</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Pepe</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3.71e-06</v>
+        <v>0.5788450000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>1559649045</v>
+        <v>1567594246</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>258560399</v>
+        <v>8439074</v>
       </c>
       <c r="I59" t="n">
-        <v>3.76e-06</v>
+        <v>0.690213</v>
       </c>
       <c r="J59" t="n">
-        <v>3.55e-06</v>
+        <v>0.585388</v>
       </c>
       <c r="K59" t="n">
-        <v>1.6912e-07</v>
+        <v>-0.09388214689214247</v>
       </c>
       <c r="L59" t="n">
-        <v>4.7828</v>
+        <v>-13.96584</v>
       </c>
       <c r="M59" t="n">
-        <v>420690000000000</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N59" t="n">
-        <v>420690000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O59" t="n">
-        <v>2.803e-05</v>
+        <v>0.789172</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>45635.35457175926</v>
+        <v>46281.50775462963</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0006349277585788002</v>
+        <v>0.0006018730681152532</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>worldcoin-wld</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>wld</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sky</t>
+          <t>Worldcoin</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.065134</v>
+        <v>0.432174</v>
       </c>
       <c r="F60" t="n">
-        <v>1525648633</v>
+        <v>1555853308</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>29729413</v>
+        <v>228977249</v>
       </c>
       <c r="I60" t="n">
-        <v>0.06775200000000001</v>
+        <v>0.43735</v>
       </c>
       <c r="J60" t="n">
-        <v>0.058324</v>
+        <v>0.413067</v>
       </c>
       <c r="K60" t="n">
-        <v>0.00648944</v>
+        <v>-0.007900419231261557</v>
       </c>
       <c r="L60" t="n">
-        <v>11.06578</v>
+        <v>-1.67455</v>
       </c>
       <c r="M60" t="n">
-        <v>23420675080.81244</v>
+        <v>3600061882.051912</v>
       </c>
       <c r="N60" t="n">
-        <v>23459804203.60596</v>
+        <v>10000000000</v>
       </c>
       <c r="O60" t="n">
-        <v>0.100535</v>
+        <v>11.74</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>45630.09302083333</v>
+        <v>45360.67409722223</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0006132443027897726</v>
+        <v>0.0005946810799048459</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>htx-dao</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>htx</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>USDD</t>
+          <t>HTX DAO</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.998357</v>
+        <v>1.7e-06</v>
       </c>
       <c r="F61" t="n">
-        <v>1514047083</v>
+        <v>1530245421</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>3654614</v>
+        <v>3198616</v>
       </c>
       <c r="I61" t="n">
-        <v>0.998753</v>
+        <v>1.71e-06</v>
       </c>
       <c r="J61" t="n">
-        <v>0.997866</v>
+        <v>1.68e-06</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.000135585887886203</v>
+        <v>2.4968e-08</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.01358</v>
+        <v>1.47629</v>
       </c>
       <c r="M61" t="n">
-        <v>1516354806</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="N61" t="n">
-        <v>1516354806</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="O61" t="n">
-        <v>1.24</v>
+        <v>3.75e-06</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>46212.39942129629</v>
+        <v>45629.67800925926</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0006058455190188821</v>
+        <v>0.0005789948015685286</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>htx-dao</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>htx</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>HTX DAO</t>
+          <t>USDD</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1.68e-06</v>
+        <v>0.99799</v>
       </c>
       <c r="F62" t="n">
-        <v>1509737418</v>
+        <v>1526947830</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>10066164</v>
+        <v>3657552</v>
       </c>
       <c r="I62" t="n">
-        <v>1.68e-06</v>
+        <v>0.999088</v>
       </c>
       <c r="J62" t="n">
-        <v>1.66e-06</v>
+        <v>0.997081</v>
       </c>
       <c r="K62" t="n">
-        <v>1.165e-08</v>
+        <v>-0.00045256413609529</v>
       </c>
       <c r="L62" t="n">
-        <v>0.69768</v>
+        <v>-0.04467</v>
       </c>
       <c r="M62" t="n">
-        <v>898232728634017.2</v>
+        <v>1530023428</v>
       </c>
       <c r="N62" t="n">
-        <v>898232728634017.2</v>
+        <v>1531219537</v>
       </c>
       <c r="O62" t="n">
-        <v>3.75e-06</v>
+        <v>1.24</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>45629.67800925926</v>
+        <v>46212.39942129629</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0006030970690738337</v>
+        <v>0.0005769748406765841</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4626,28 +4626,28 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.212126</v>
+        <v>0.21076</v>
       </c>
       <c r="F63" t="n">
-        <v>1439191946</v>
+        <v>1430127833</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>716908068</v>
+        <v>481398830</v>
       </c>
       <c r="I63" t="n">
-        <v>0.228573</v>
+        <v>0.227783</v>
       </c>
       <c r="J63" t="n">
-        <v>0.161914</v>
+        <v>0.205551</v>
       </c>
       <c r="K63" t="n">
-        <v>0.04953603</v>
+        <v>-0.000670181396933006</v>
       </c>
       <c r="L63" t="n">
-        <v>30.46682</v>
+        <v>-0.48827</v>
       </c>
       <c r="M63" t="n">
         <v>6785574605</v>
@@ -4662,86 +4662,86 @@
         <v>45303.18748842592</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0005581073312074784</v>
+        <v>0.0005176671195255418</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>united-stables</t>
+          <t>bitget-token</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>bgb</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>United Stables</t>
+          <t>Bitget Token</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.999455</v>
+        <v>2.03</v>
       </c>
       <c r="F64" t="n">
-        <v>1392401237</v>
+        <v>1420581991</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>161853344</v>
+        <v>15072621</v>
       </c>
       <c r="I64" t="n">
-        <v>0.9997200000000001</v>
+        <v>2.03</v>
       </c>
       <c r="J64" t="n">
-        <v>0.999331</v>
+        <v>1.96</v>
       </c>
       <c r="K64" t="n">
-        <v>-7.083445307221e-05</v>
+        <v>0.057695</v>
       </c>
       <c r="L64" t="n">
-        <v>-0.00709</v>
+        <v>2.94211</v>
       </c>
       <c r="M64" t="n">
-        <v>1393129007.8</v>
+        <v>699992029.6481038</v>
       </c>
       <c r="N64" t="n">
-        <v>1393129007.8</v>
+        <v>910920874.6481038</v>
       </c>
       <c r="O64" t="n">
-        <v>1.008</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>46058.54591435185</v>
+        <v>45653.15375</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R64" t="b">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0005282669789806067</v>
+        <v>0.0005118197516983366</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4763,7 +4763,7 @@
         <v>1.16</v>
       </c>
       <c r="F65" t="n">
-        <v>1389846512</v>
+        <v>1407771011</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
@@ -4778,16 +4778,16 @@
         <v>1.16</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.002379406934365225</v>
+        <v>0.0015034</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.20452</v>
+        <v>0.12946</v>
       </c>
       <c r="M65" t="n">
-        <v>1197060629.42477</v>
+        <v>1210660472.36437</v>
       </c>
       <c r="N65" t="n">
-        <v>1197060629.42477</v>
+        <v>1210660472.36437</v>
       </c>
       <c r="O65" t="n">
         <v>1.18</v>
@@ -4796,287 +4796,287 @@
         <v>46255.48263888889</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0005266377261765341</v>
+        <v>0.0005039723022761725</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>usdgo</t>
+          <t>akedo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>usdgo</t>
+          <t>ake</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>USDGO</t>
+          <t>Akedo</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>0.061588</v>
       </c>
       <c r="F66" t="n">
-        <v>1382196392</v>
+        <v>1403973963</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
       </c>
       <c r="H66" t="n">
-        <v>23323261</v>
+        <v>221768120</v>
       </c>
       <c r="I66" t="n">
-        <v>1.001</v>
+        <v>0.06482300000000001</v>
       </c>
       <c r="J66" t="n">
+        <v>0.02575841</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.03530292</v>
+      </c>
+      <c r="L66" t="n">
+        <v>134.28414</v>
+      </c>
+      <c r="M66" t="n">
+        <v>22796250000</v>
+      </c>
+      <c r="N66" t="n">
+        <v>100000000000</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.06482300000000001</v>
+      </c>
+      <c r="P66" s="1" t="n">
+        <v>46284.43101851852</v>
+      </c>
+      <c r="Q66" s="1" t="n">
+        <v>46284.54108796296</v>
+      </c>
+      <c r="R66" t="b">
         <v>1</v>
       </c>
-      <c r="K66" t="n">
-        <v>-0.000122698445858882</v>
-      </c>
-      <c r="L66" t="n">
-        <v>-0.01226</v>
-      </c>
-      <c r="M66" t="n">
-        <v>1381786100.28</v>
-      </c>
-      <c r="N66" t="n">
-        <v>1381786100.28</v>
-      </c>
-      <c r="O66" t="n">
-        <v>1.002</v>
-      </c>
-      <c r="P66" s="1" t="n">
-        <v>46092.00303240741</v>
-      </c>
-      <c r="Q66" s="1" t="n">
-        <v>46283.56203703704</v>
-      </c>
-      <c r="R66" t="b">
-        <v>0</v>
-      </c>
       <c r="S66" t="n">
-        <v>0.0005217589312136743</v>
+        <v>0.0005016463957386922</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>bitget-token</t>
+          <t>united-stables</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>bgb</t>
+          <t>u</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Bitget Token</t>
+          <t>United Stables</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1.97</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>1379592305</v>
+        <v>1393129534</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
       </c>
       <c r="H67" t="n">
-        <v>11709342</v>
+        <v>157171689</v>
       </c>
       <c r="I67" t="n">
-        <v>1.97</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>1.91</v>
+        <v>0.999493</v>
       </c>
       <c r="K67" t="n">
-        <v>0.062015</v>
+        <v>0.00055459</v>
       </c>
       <c r="L67" t="n">
-        <v>3.24884</v>
+        <v>0.04974</v>
       </c>
       <c r="M67" t="n">
-        <v>699992029.6481038</v>
+        <v>1393129007.8</v>
       </c>
       <c r="N67" t="n">
-        <v>910920874.6481038</v>
+        <v>1393129007.8</v>
       </c>
       <c r="O67" t="n">
-        <v>8.449999999999999</v>
+        <v>1.008</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>45653.15375</v>
+        <v>46058.54591435185</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0005200981982397538</v>
+        <v>0.0004950035699681618</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>falcon-finance</t>
+          <t>usdgo</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>usdf</t>
+          <t>usdgo</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Falcon USD</t>
+          <t>USDGO</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.995544</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>1370895100</v>
+        <v>1383948752</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>869400</v>
+        <v>33059541</v>
       </c>
       <c r="I68" t="n">
-        <v>0.996159</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
-        <v>0.994829</v>
+        <v>0.999566</v>
       </c>
       <c r="K68" t="n">
-        <v>3.772e-05</v>
+        <v>-0.000179455571939435</v>
       </c>
       <c r="L68" t="n">
-        <v>0.00379</v>
+        <v>-0.02022</v>
       </c>
       <c r="M68" t="n">
-        <v>1377031690.833898</v>
+        <v>1383787304.97</v>
       </c>
       <c r="N68" t="n">
-        <v>1377031690.833898</v>
+        <v>1383787304.97</v>
       </c>
       <c r="O68" t="n">
-        <v>1.075</v>
+        <v>1.002</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>45785.55951388889</v>
+        <v>46092.00303240741</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0005145516342714816</v>
+        <v>0.0004893798220268712</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>falcon-finance</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>usdf</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BFUSD</t>
+          <t>Falcon USD</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.99866</v>
+        <v>0.995613</v>
       </c>
       <c r="F69" t="n">
-        <v>1318230786</v>
+        <v>1371004229</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>4686827</v>
+        <v>515832</v>
       </c>
       <c r="I69" t="n">
-        <v>0.999302</v>
+        <v>0.996291</v>
       </c>
       <c r="J69" t="n">
-        <v>0.998594</v>
+        <v>0.995053</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.00041621193149266</v>
+        <v>2.866e-05</v>
       </c>
       <c r="L69" t="n">
-        <v>-0.04166</v>
+        <v>0.0034</v>
       </c>
       <c r="M69" t="n">
-        <v>1320000000</v>
+        <v>1377045504.45504</v>
       </c>
       <c r="N69" t="n">
-        <v>1320000000</v>
+        <v>1377045504.45504</v>
       </c>
       <c r="O69" t="n">
-        <v>1.007</v>
+        <v>1.075</v>
       </c>
       <c r="P69" s="1" t="n">
-        <v>45940.56990740741</v>
+        <v>45785.55951388889</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0004809654434841916</v>
+        <v>0.0004814505699683605</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5095,34 +5095,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>7.95</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>1258354981</v>
+        <v>1340644126</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>57470292</v>
+        <v>79617319</v>
       </c>
       <c r="I70" t="n">
-        <v>7.98</v>
+        <v>8.59</v>
       </c>
       <c r="J70" t="n">
-        <v>7.35</v>
+        <v>7.97</v>
       </c>
       <c r="K70" t="n">
-        <v>0.586362</v>
+        <v>0.503223</v>
       </c>
       <c r="L70" t="n">
-        <v>7.95987</v>
+        <v>6.49692</v>
       </c>
       <c r="M70" t="n">
-        <v>158206077.5915582</v>
+        <v>158215665.2670572</v>
       </c>
       <c r="N70" t="n">
-        <v>158206497.9435582</v>
+        <v>158216963.8921894</v>
       </c>
       <c r="O70" t="n">
         <v>167.09</v>
@@ -5131,19 +5131,19 @@
         <v>44322.44053240741</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R70" t="b">
         <v>1</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0004427801894187427</v>
+        <v>0.0004628532907013417</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5162,457 +5162,457 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>26.11</v>
+        <v>27.88</v>
       </c>
       <c r="F71" t="n">
-        <v>1254484722</v>
+        <v>1339871374</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>79852560</v>
+        <v>96922668</v>
       </c>
       <c r="I71" t="n">
-        <v>27.61</v>
+        <v>29.44</v>
       </c>
       <c r="J71" t="n">
-        <v>24.21</v>
+        <v>25.99</v>
       </c>
       <c r="K71" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="L71" t="n">
-        <v>6.10161</v>
+        <v>7.14008</v>
       </c>
       <c r="M71" t="n">
-        <v>48035223.66929011</v>
+        <v>48053201.36919299</v>
       </c>
       <c r="N71" t="n">
-        <v>81000641.2993075</v>
+        <v>81007609.62721066</v>
       </c>
       <c r="O71" t="n">
-        <v>29.19</v>
+        <v>29.44</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>46274.32083333333</v>
+        <v>46284.10787037037</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R71" t="b">
         <v>1</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0004403119666831303</v>
+        <v>0.0004623799364196337</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>lighter</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>lit</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Lighter</t>
+          <t>BFUSD</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4.89</v>
+        <v>0.9996</v>
       </c>
       <c r="F72" t="n">
-        <v>1221178530</v>
+        <v>1319471561</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>96098968</v>
+        <v>1804515</v>
       </c>
       <c r="I72" t="n">
-        <v>5.15</v>
+        <v>0.999725</v>
       </c>
       <c r="J72" t="n">
-        <v>4.63</v>
+        <v>0.998817</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.04900761539183396</v>
+        <v>0.00093291</v>
       </c>
       <c r="L72" t="n">
-        <v>-0.99324</v>
+        <v>0.09393</v>
       </c>
       <c r="M72" t="n">
-        <v>250000000</v>
+        <v>1320000000</v>
       </c>
       <c r="N72" t="n">
-        <v>1000000000</v>
+        <v>1320000000</v>
       </c>
       <c r="O72" t="n">
-        <v>7.86</v>
+        <v>1.007</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>46021.04538194444</v>
+        <v>45940.56990740741</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0004190712434315161</v>
+        <v>0.0004498838978075131</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>polygon-ecosystem-token</t>
+          <t>lighter</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>pol</t>
+          <t>lit</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>POL (ex-MATIC)</t>
+          <t>Lighter</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.09998799999999999</v>
+        <v>5.08</v>
       </c>
       <c r="F73" t="n">
-        <v>1071688769</v>
+        <v>1270773372</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>127176677</v>
+        <v>113532386</v>
       </c>
       <c r="I73" t="n">
-        <v>0.101543</v>
+        <v>5.27</v>
       </c>
       <c r="J73" t="n">
-        <v>0.096651</v>
+        <v>4.67</v>
       </c>
       <c r="K73" t="n">
-        <v>0.00212377</v>
+        <v>0.1814</v>
       </c>
       <c r="L73" t="n">
-        <v>2.17012</v>
+        <v>3.74222</v>
       </c>
       <c r="M73" t="n">
-        <v>10716429232.27866</v>
+        <v>250000000</v>
       </c>
       <c r="N73" t="n">
-        <v>10716429232.27866</v>
+        <v>1000000000</v>
       </c>
       <c r="O73" t="n">
-        <v>1.29</v>
+        <v>7.86</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>45364.45493055556</v>
+        <v>46021.04538194444</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R73" t="b">
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003237354979836138</v>
+        <v>0.0004200535042600648</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>gatechain-token</t>
+          <t>polygon-ecosystem-token</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>gt</t>
+          <t>pol</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>POL (ex-MATIC)</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>9.81</v>
+        <v>0.104722</v>
       </c>
       <c r="F74" t="n">
-        <v>1046669885</v>
+        <v>1122307480</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>3582913</v>
+        <v>127939160</v>
       </c>
       <c r="I74" t="n">
-        <v>9.9</v>
+        <v>0.109444</v>
       </c>
       <c r="J74" t="n">
-        <v>9.31</v>
+        <v>0.100445</v>
       </c>
       <c r="K74" t="n">
-        <v>0.468169</v>
+        <v>0.00457585</v>
       </c>
       <c r="L74" t="n">
-        <v>5.00911</v>
+        <v>4.60869</v>
       </c>
       <c r="M74" t="n">
-        <v>106632325.8526192</v>
+        <v>10717010654.78035</v>
       </c>
       <c r="N74" t="n">
-        <v>118883590.353713</v>
+        <v>10717010654.78035</v>
       </c>
       <c r="O74" t="n">
-        <v>25.38</v>
+        <v>1.29</v>
       </c>
       <c r="P74" s="1" t="n">
-        <v>45682.66666666666</v>
+        <v>45364.45493055556</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R74" t="b">
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0003077799305891714</v>
+        <v>0.0003291097530102404</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>kaspa</t>
+          <t>gatechain-token</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>kas</t>
+          <t>gt</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Kaspa</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.03556016</v>
+        <v>10.01</v>
       </c>
       <c r="F75" t="n">
-        <v>985350397</v>
+        <v>1067690542</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
       </c>
       <c r="H75" t="n">
-        <v>14199670</v>
+        <v>3804156</v>
       </c>
       <c r="I75" t="n">
-        <v>0.03674564</v>
+        <v>10.21</v>
       </c>
       <c r="J75" t="n">
-        <v>0.03318585</v>
+        <v>9.85</v>
       </c>
       <c r="K75" t="n">
-        <v>0.00183327</v>
+        <v>0.136528</v>
       </c>
       <c r="L75" t="n">
-        <v>5.43564</v>
+        <v>1.31699</v>
       </c>
       <c r="M75" t="n">
-        <v>27705890801.55766</v>
+        <v>106633446.0521377</v>
       </c>
       <c r="N75" t="n">
-        <v>27707400028.46774</v>
+        <v>118884734.5494255</v>
       </c>
       <c r="O75" t="n">
-        <v>0.207411</v>
+        <v>25.38</v>
       </c>
       <c r="P75" s="1" t="n">
-        <v>45504.69498842592</v>
+        <v>45682.66666666666</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0002686739807243931</v>
+        <v>0.0002956537911284428</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>kucoin-shares</t>
+          <t>kaspa</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>kcs</t>
+          <t>kas</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>KuCoin</t>
+          <t>Kaspa</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>7.17</v>
+        <v>0.03816901</v>
       </c>
       <c r="F76" t="n">
-        <v>983203500</v>
+        <v>1057608938</v>
       </c>
       <c r="G76" t="n">
         <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>5417571</v>
+        <v>20064411</v>
       </c>
       <c r="I76" t="n">
-        <v>7.2</v>
+        <v>0.03895499</v>
       </c>
       <c r="J76" t="n">
-        <v>6.97</v>
+        <v>0.03581762</v>
       </c>
       <c r="K76" t="n">
-        <v>0.18184</v>
+        <v>0.00235444</v>
       </c>
       <c r="L76" t="n">
-        <v>2.60243</v>
+        <v>6.5786</v>
       </c>
       <c r="M76" t="n">
-        <v>137155021.2773955</v>
+        <v>27708574135.96641</v>
       </c>
       <c r="N76" t="n">
-        <v>142155021.2773955</v>
+        <v>27709298793.27851</v>
       </c>
       <c r="O76" t="n">
-        <v>28.83</v>
+        <v>0.207411</v>
       </c>
       <c r="P76" s="1" t="n">
-        <v>44531.29832175926</v>
+        <v>45504.69498842592</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0002673048165453503</v>
+        <v>0.0002894782387909723</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>just</t>
+          <t>kucoin-shares</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>jst</t>
+          <t>kcs</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>JUST</t>
+          <t>KuCoin</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.118528</v>
+        <v>7.28</v>
       </c>
       <c r="F77" t="n">
-        <v>971455906</v>
+        <v>998107368</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>32560510</v>
+        <v>10265485</v>
       </c>
       <c r="I77" t="n">
-        <v>0.118293</v>
+        <v>7.32</v>
       </c>
       <c r="J77" t="n">
-        <v>0.113817</v>
+        <v>7.12</v>
       </c>
       <c r="K77" t="n">
-        <v>0.00215167</v>
+        <v>0.091711</v>
       </c>
       <c r="L77" t="n">
-        <v>1.84888</v>
+        <v>1.27165</v>
       </c>
       <c r="M77" t="n">
-        <v>8188743036.341737</v>
+        <v>137155021.2773955</v>
       </c>
       <c r="N77" t="n">
-        <v>8188743036.341737</v>
+        <v>142155021.2773955</v>
       </c>
       <c r="O77" t="n">
-        <v>0.193254</v>
+        <v>28.83</v>
       </c>
       <c r="P77" s="1" t="n">
-        <v>44290.85721064815</v>
+        <v>44531.29832175926</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R77" t="b">
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002598128945319804</v>
+        <v>0.0002530301636933329</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5649,7 +5649,7 @@
         <v>106.54</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>1.4211e-14</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -5667,19 +5667,19 @@
         <v>46280.14583333334</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R78" t="b">
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002593973425147833</v>
+        <v>0.0002363054948455781</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5698,34 +5698,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.083913</v>
+        <v>0.085049</v>
       </c>
       <c r="F79" t="n">
-        <v>942708036</v>
+        <v>956203211</v>
       </c>
       <c r="G79" t="n">
         <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>8620899</v>
+        <v>7267165</v>
       </c>
       <c r="I79" t="n">
-        <v>0.08415</v>
+        <v>0.0868</v>
       </c>
       <c r="J79" t="n">
-        <v>0.08086699999999999</v>
+        <v>0.08384800000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>0.00115749</v>
+        <v>0.00175985</v>
       </c>
       <c r="L79" t="n">
-        <v>1.39868</v>
+        <v>2.13146</v>
       </c>
       <c r="M79" t="n">
-        <v>11239267182.72403</v>
+        <v>11243018943.001</v>
       </c>
       <c r="N79" t="n">
-        <v>17291180281.11388</v>
+        <v>17296952220.00153</v>
       </c>
       <c r="O79" t="n">
         <v>2.99</v>
@@ -5734,354 +5734,354 @@
         <v>45714.36184027778</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R79" t="b">
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002414791999822287</v>
+        <v>0.0002273614987952593</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>quant-network</t>
+          <t>just</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>qnt</t>
+          <t>jst</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>JUST</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>63.34</v>
+        <v>0.116103</v>
       </c>
       <c r="F80" t="n">
-        <v>921129189</v>
+        <v>950736359</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>8715173</v>
+        <v>24202971</v>
       </c>
       <c r="I80" t="n">
-        <v>63.35</v>
+        <v>0.118694</v>
       </c>
       <c r="J80" t="n">
-        <v>60.72</v>
+        <v>0.112293</v>
       </c>
       <c r="K80" t="n">
-        <v>2.01</v>
+        <v>-0.002184845546124511</v>
       </c>
       <c r="L80" t="n">
-        <v>3.27333</v>
+        <v>-1.8513</v>
       </c>
       <c r="M80" t="n">
-        <v>14544176.16408117</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="N80" t="n">
-        <v>14612493</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="O80" t="n">
-        <v>427.42</v>
+        <v>0.193254</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>44450.05208333334</v>
+        <v>44290.85721064815</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R80" t="b">
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002277174851270472</v>
+        <v>0.0002240127429179995</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>cosmos</t>
+          <t>quant-network</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>qnt</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Cosmos Hub</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1.67</v>
+        <v>65.23</v>
       </c>
       <c r="F81" t="n">
-        <v>887148662</v>
+        <v>948734831</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>59111575</v>
+        <v>9168942</v>
       </c>
       <c r="I81" t="n">
-        <v>1.67</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="J81" t="n">
-        <v>1.52</v>
+        <v>63.03</v>
       </c>
       <c r="K81" t="n">
-        <v>0.140951</v>
+        <v>2.5</v>
       </c>
       <c r="L81" t="n">
-        <v>9.22336</v>
+        <v>4.00621</v>
       </c>
       <c r="M81" t="n">
-        <v>531398115.177704</v>
+        <v>14544176.16408117</v>
       </c>
       <c r="N81" t="n">
-        <v>531405147.717275</v>
+        <v>14612493</v>
       </c>
       <c r="O81" t="n">
-        <v>43.84</v>
+        <v>427.42</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>44458.66666666666</v>
+        <v>44450.05208333334</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.000206046710817243</v>
+        <v>0.0002227866938767049</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>algorand</t>
+          <t>cosmos</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>algo</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Algorand</t>
+          <t>Cosmos Hub</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.096716</v>
+        <v>1.75</v>
       </c>
       <c r="F82" t="n">
-        <v>874520830</v>
+        <v>928518127</v>
       </c>
       <c r="G82" t="n">
         <v>81</v>
       </c>
       <c r="H82" t="n">
-        <v>45382156</v>
+        <v>69176887</v>
       </c>
       <c r="I82" t="n">
-        <v>0.09686400000000001</v>
+        <v>1.78</v>
       </c>
       <c r="J82" t="n">
-        <v>0.089339</v>
+        <v>1.66</v>
       </c>
       <c r="K82" t="n">
-        <v>0.00716556</v>
+        <v>0.09384000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>8.00169</v>
+        <v>5.62372</v>
       </c>
       <c r="M82" t="n">
-        <v>9042038142.191359</v>
+        <v>531564934.540691</v>
       </c>
       <c r="N82" t="n">
-        <v>9042065635.209162</v>
+        <v>531591001.367196</v>
       </c>
       <c r="O82" t="n">
-        <v>3.56</v>
+        <v>43.84</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>43636.28563657407</v>
+        <v>44458.66666666666</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R82" t="b">
         <v>1</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0001979934249663754</v>
+        <v>0.0002104028198777709</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>pancakeswap-token</t>
+          <t>jupiter-exchange-solana</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>jup</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2.49</v>
+        <v>0.277427</v>
       </c>
       <c r="F83" t="n">
-        <v>866497842</v>
+        <v>920883420</v>
       </c>
       <c r="G83" t="n">
         <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>115480970</v>
+        <v>112476681</v>
       </c>
       <c r="I83" t="n">
-        <v>2.55</v>
+        <v>0.286745</v>
       </c>
       <c r="J83" t="n">
-        <v>2.37</v>
+        <v>0.25763</v>
       </c>
       <c r="K83" t="n">
-        <v>0.096279</v>
+        <v>0.0197335</v>
       </c>
       <c r="L83" t="n">
-        <v>4.02796</v>
+        <v>7.73468</v>
       </c>
       <c r="M83" t="n">
-        <v>348474256.3337419</v>
+        <v>3319369204.37</v>
       </c>
       <c r="N83" t="n">
-        <v>360130842.00171</v>
+        <v>6861486900.297955</v>
       </c>
       <c r="O83" t="n">
-        <v>43.96</v>
+        <v>2</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>44316.08914351852</v>
+        <v>45322.29359953704</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0001928768368028585</v>
+        <v>0.0002057261302696737</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jupiter-exchange-solana</t>
+          <t>algorand</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>jup</t>
+          <t>algo</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Algorand</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.261142</v>
+        <v>0.099742</v>
       </c>
       <c r="F84" t="n">
-        <v>866378292</v>
+        <v>901883555</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>114685025</v>
+        <v>45194216</v>
       </c>
       <c r="I84" t="n">
-        <v>0.259521</v>
+        <v>0.099658</v>
       </c>
       <c r="J84" t="n">
-        <v>0.223636</v>
+        <v>0.095639</v>
       </c>
       <c r="K84" t="n">
-        <v>0.0366646</v>
+        <v>0.0031548</v>
       </c>
       <c r="L84" t="n">
-        <v>16.33335</v>
+        <v>3.25392</v>
       </c>
       <c r="M84" t="n">
-        <v>3319369204.37</v>
+        <v>9042193573.716511</v>
       </c>
       <c r="N84" t="n">
-        <v>6861486931.569773</v>
+        <v>9042264038.746319</v>
       </c>
       <c r="O84" t="n">
-        <v>2</v>
+        <v>3.56</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>45322.29359953704</v>
+        <v>43636.28563657407</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001928005948696849</v>
+        <v>0.0001940876389430581</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6100,28 +6100,28 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.825546</v>
+        <v>0.853658</v>
       </c>
       <c r="F85" t="n">
-        <v>825568397</v>
+        <v>853658122</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>2585723</v>
+        <v>3372089</v>
       </c>
       <c r="I85" t="n">
-        <v>0.828891</v>
+        <v>0.849484</v>
       </c>
       <c r="J85" t="n">
-        <v>0.805134</v>
+        <v>0.826249</v>
       </c>
       <c r="K85" t="n">
-        <v>0.02332409</v>
+        <v>0.03323759</v>
       </c>
       <c r="L85" t="n">
-        <v>2.90744</v>
+        <v>4.07791</v>
       </c>
       <c r="M85" t="n">
         <v>1000000000</v>
@@ -6136,309 +6136,309 @@
         <v>44328.27623842593</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R85" t="b">
         <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001667744527750727</v>
+        <v>0.000164546835169306</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>render-token</t>
+          <t>pancakeswap-token</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>render</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1.53</v>
+        <v>2.44</v>
       </c>
       <c r="F86" t="n">
-        <v>795709144</v>
+        <v>851553351</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
       </c>
       <c r="H86" t="n">
-        <v>69435580</v>
+        <v>93158522</v>
       </c>
       <c r="I86" t="n">
-        <v>1.54</v>
+        <v>2.51</v>
       </c>
       <c r="J86" t="n">
-        <v>1.39</v>
+        <v>2.39</v>
       </c>
       <c r="K86" t="n">
-        <v>0.140904</v>
+        <v>-0.0218518113947046</v>
       </c>
       <c r="L86" t="n">
-        <v>10.12291</v>
+        <v>-0.81335</v>
       </c>
       <c r="M86" t="n">
-        <v>518776241.2826915</v>
+        <v>348474895.6233068</v>
       </c>
       <c r="N86" t="n">
-        <v>533536414.5626915</v>
+        <v>360130841.8225635</v>
       </c>
       <c r="O86" t="n">
-        <v>13.53</v>
+        <v>43.96</v>
       </c>
       <c r="P86" s="1" t="n">
-        <v>45368.35444444444</v>
+        <v>44316.08914351852</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001477319837509065</v>
+        <v>0.0001632575439544467</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>render-token</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>render</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Spiko EU T-Bills Money Market Fund</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1.21</v>
+        <v>1.63</v>
       </c>
       <c r="F87" t="n">
-        <v>790361818</v>
+        <v>843339790</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>70401750</v>
       </c>
       <c r="I87" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
-        <v>1.21</v>
+        <v>1.51</v>
       </c>
       <c r="K87" t="n">
-        <v>-0.002520738062147032</v>
+        <v>0.089157</v>
       </c>
       <c r="L87" t="n">
-        <v>-0.20721</v>
+        <v>5.75997</v>
       </c>
       <c r="M87" t="n">
-        <v>651037363.70003</v>
+        <v>518776241.2826915</v>
       </c>
       <c r="N87" t="n">
-        <v>651037363.70003</v>
+        <v>533536414.5626915</v>
       </c>
       <c r="O87" t="n">
-        <v>1.26</v>
+        <v>13.53</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>46049.54175925926</v>
+        <v>45368.35444444444</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001443217748713635</v>
+        <v>0.0001582262735502029</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-aaa-clo-fund</t>
+          <t>filecoin</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>jaaa</t>
+          <t>fil</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy AAA CLO Fund</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1.05</v>
+        <v>0.987888</v>
       </c>
       <c r="F88" t="n">
-        <v>776469917</v>
+        <v>817787018</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>223542577</v>
       </c>
       <c r="I88" t="n">
-        <v>1.05</v>
+        <v>0.997</v>
       </c>
       <c r="J88" t="n">
-        <v>1.05</v>
+        <v>0.8783570000000001</v>
       </c>
       <c r="K88" t="n">
-        <v>9.1e-05</v>
+        <v>0.124844</v>
       </c>
       <c r="L88" t="n">
-        <v>0.008670000000000001</v>
+        <v>14.47929</v>
       </c>
       <c r="M88" t="n">
-        <v>739569820.670837</v>
+        <v>827813309</v>
       </c>
       <c r="N88" t="n">
-        <v>739569820.670837</v>
+        <v>1957040788</v>
       </c>
       <c r="O88" t="n">
-        <v>1.05</v>
+        <v>236.84</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>46283.36122685186</v>
+        <v>44287.22894675926</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001354623404280677</v>
+        <v>0.0001425737562668966</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Dash</t>
+          <t>Spiko EU T-Bills Money Market Fund</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>58.77</v>
+        <v>1.22</v>
       </c>
       <c r="F89" t="n">
-        <v>754086368</v>
+        <v>791533121</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>188486590</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>62.48</v>
+        <v>1.22</v>
       </c>
       <c r="J89" t="n">
-        <v>57.02</v>
+        <v>1.21</v>
       </c>
       <c r="K89" t="n">
-        <v>1.21</v>
+        <v>0.00152768</v>
       </c>
       <c r="L89" t="n">
-        <v>2.10693</v>
+        <v>0.12581</v>
       </c>
       <c r="M89" t="n">
-        <v>12832779.61981004</v>
+        <v>651037363.70003</v>
       </c>
       <c r="N89" t="n">
-        <v>12832868.22864153</v>
+        <v>651037363.70003</v>
       </c>
       <c r="O89" t="n">
-        <v>1493.59</v>
+        <v>1.26</v>
       </c>
       <c r="P89" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>46049.54175925926</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R89" t="b">
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001211874341374312</v>
+        <v>0.0001264917602882747</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
+          <t>janus-henderson-anemoy-aaa-clo-fund</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ustb</t>
+          <t>jaaa</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Invesco Short Duration US Government Securities Fund</t>
+          <t>Janus Henderson Anemoy AAA CLO Fund</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>11.22</v>
+        <v>1.05</v>
       </c>
       <c r="F90" t="n">
-        <v>729506977</v>
+        <v>776469917</v>
       </c>
       <c r="G90" t="n">
         <v>89</v>
@@ -6447,646 +6447,646 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>11.21</v>
+        <v>1.05</v>
       </c>
       <c r="J90" t="n">
-        <v>11.21</v>
+        <v>1.05</v>
       </c>
       <c r="K90" t="n">
-        <v>0.001068</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>0.009520000000000001</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>65043293.460603</v>
+        <v>739569820.670837</v>
       </c>
       <c r="N90" t="n">
-        <v>64962641.508854</v>
+        <v>739569820.670837</v>
       </c>
       <c r="O90" t="n">
-        <v>11.22</v>
+        <v>1.05</v>
       </c>
       <c r="P90" s="1" t="n">
-        <v>46283.55902777778</v>
+        <v>46283.36122685186</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>0.0001055121494358893</v>
+        <v>0.0001172646963536077</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>filecoin</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>Dash</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.874042</v>
+        <v>60.36</v>
       </c>
       <c r="F91" t="n">
-        <v>722662480</v>
+        <v>774579585</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>136321802</v>
+        <v>183651947</v>
       </c>
       <c r="I91" t="n">
-        <v>0.879723</v>
+        <v>64.87</v>
       </c>
       <c r="J91" t="n">
-        <v>0.810361</v>
+        <v>57.53</v>
       </c>
       <c r="K91" t="n">
-        <v>0.062831</v>
+        <v>1.73</v>
       </c>
       <c r="L91" t="n">
-        <v>7.74531</v>
+        <v>2.96131</v>
       </c>
       <c r="M91" t="n">
-        <v>827813309</v>
+        <v>12833705.99189731</v>
       </c>
       <c r="N91" t="n">
-        <v>1957042330</v>
+        <v>12833828.23743384</v>
       </c>
       <c r="O91" t="n">
-        <v>236.84</v>
+        <v>1493.59</v>
       </c>
       <c r="P91" s="1" t="n">
-        <v>44287.22894675926</v>
+        <v>43088.66666666666</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>0.0001011471332679196</v>
+        <v>0.0001161067611479405</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>injective-protocol</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>inj</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>GHO</t>
+          <t>Injective</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.998333</v>
+        <v>7.55</v>
       </c>
       <c r="F92" t="n">
-        <v>697834500</v>
+        <v>755206082</v>
       </c>
       <c r="G92" t="n">
         <v>91</v>
       </c>
       <c r="H92" t="n">
-        <v>13580607</v>
+        <v>278755754</v>
       </c>
       <c r="I92" t="n">
-        <v>0.998651</v>
+        <v>7.77</v>
       </c>
       <c r="J92" t="n">
-        <v>0.998274</v>
+        <v>6.43</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.000139759986692467</v>
+        <v>1.06</v>
       </c>
       <c r="L92" t="n">
-        <v>-0.014</v>
+        <v>16.37045</v>
       </c>
       <c r="M92" t="n">
-        <v>699000000</v>
+        <v>100000000</v>
       </c>
       <c r="N92" t="n">
-        <v>699000000</v>
+        <v>100000000</v>
       </c>
       <c r="O92" t="n">
-        <v>1.03</v>
+        <v>52.62</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>45350.38608796296</v>
+        <v>45365.29608796296</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S92" t="n">
-        <v>8.531331317594948e-05</v>
+        <v>0.0001042393954255177</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ether-fi</t>
+          <t>vechain</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ethfi</t>
+          <t>vet</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Ether.fi</t>
+          <t>VeChain</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.712028</v>
+        <v>0.008651839999999999</v>
       </c>
       <c r="F93" t="n">
-        <v>685510629</v>
+        <v>743928678</v>
       </c>
       <c r="G93" t="n">
         <v>92</v>
       </c>
       <c r="H93" t="n">
-        <v>66519364</v>
+        <v>30200498</v>
       </c>
       <c r="I93" t="n">
-        <v>0.699136</v>
+        <v>0.00871715</v>
       </c>
       <c r="J93" t="n">
-        <v>0.610697</v>
+        <v>0.00765455</v>
       </c>
       <c r="K93" t="n">
-        <v>0.09155000000000001</v>
+        <v>0.00109549</v>
       </c>
       <c r="L93" t="n">
-        <v>14.75484</v>
+        <v>14.53099</v>
       </c>
       <c r="M93" t="n">
-        <v>965350000</v>
+        <v>85985041177</v>
       </c>
       <c r="N93" t="n">
-        <v>965350000</v>
+        <v>85985041177</v>
       </c>
       <c r="O93" t="n">
-        <v>8.529999999999999</v>
+        <v>0.280991</v>
       </c>
       <c r="P93" s="1" t="n">
-        <v>45378.63525462963</v>
+        <v>44304.71413194444</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R93" t="b">
         <v>1</v>
       </c>
       <c r="S93" t="n">
-        <v>7.745387570859822e-05</v>
+        <v>9.733134799251018e-05</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>stable-2</t>
+          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>ustb</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>​​Stable</t>
+          <t>Invesco Short Duration US Government Securities Fund</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.0250295</v>
+        <v>11.22</v>
       </c>
       <c r="F94" t="n">
-        <v>661455263</v>
+        <v>742999390</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
       </c>
       <c r="H94" t="n">
-        <v>10849867</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0.02510017</v>
+        <v>11.22</v>
       </c>
       <c r="J94" t="n">
-        <v>0.02296381</v>
+        <v>11.22</v>
       </c>
       <c r="K94" t="n">
-        <v>0.00145235</v>
+        <v>0.001068</v>
       </c>
       <c r="L94" t="n">
-        <v>6.15998</v>
+        <v>0.009520000000000001</v>
       </c>
       <c r="M94" t="n">
-        <v>26430929012</v>
+        <v>66246285.313571</v>
       </c>
       <c r="N94" t="n">
-        <v>100000000000</v>
+        <v>66264112.081849</v>
       </c>
       <c r="O94" t="n">
-        <v>0.04323745</v>
+        <v>11.22</v>
       </c>
       <c r="P94" s="1" t="n">
-        <v>46156.97986111111</v>
+        <v>46283.55902777778</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>6.211278321978139e-05</v>
+        <v>9.676210656221961e-05</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>injective-protocol</t>
+          <t>ether-fi</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>inj</t>
+          <t>ethfi</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Injective</t>
+          <t>Ether.fi</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6.59</v>
+        <v>0.7330179999999999</v>
       </c>
       <c r="F95" t="n">
-        <v>658192252</v>
+        <v>707619011</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>181255434</v>
+        <v>71413854</v>
       </c>
       <c r="I95" t="n">
-        <v>6.94</v>
+        <v>0.756706</v>
       </c>
       <c r="J95" t="n">
-        <v>5.53</v>
+        <v>0.707048</v>
       </c>
       <c r="K95" t="n">
-        <v>0.969625</v>
+        <v>0.03397617</v>
       </c>
       <c r="L95" t="n">
-        <v>17.24359</v>
+        <v>4.97038</v>
       </c>
       <c r="M95" t="n">
-        <v>100000000</v>
+        <v>965350000</v>
       </c>
       <c r="N95" t="n">
-        <v>100000000</v>
+        <v>965350000</v>
       </c>
       <c r="O95" t="n">
-        <v>52.62</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="P95" s="1" t="n">
-        <v>45365.29608796296</v>
+        <v>45378.63525462963</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>6.003182741378673e-05</v>
+        <v>7.508962446174825e-05</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>vechain</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>vet</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VeChain</t>
+          <t>GHO</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.00757389</v>
+        <v>0.999158</v>
       </c>
       <c r="F96" t="n">
-        <v>651227129</v>
+        <v>698411721</v>
       </c>
       <c r="G96" t="n">
         <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>11025377</v>
+        <v>8352207</v>
       </c>
       <c r="I96" t="n">
-        <v>0.00759125</v>
+        <v>0.999203</v>
       </c>
       <c r="J96" t="n">
-        <v>0.00712051</v>
+        <v>0.998354</v>
       </c>
       <c r="K96" t="n">
-        <v>0.00041545</v>
+        <v>0.00082107</v>
       </c>
       <c r="L96" t="n">
-        <v>5.80369</v>
+        <v>0.08276</v>
       </c>
       <c r="M96" t="n">
-        <v>85985041177</v>
+        <v>699000000</v>
       </c>
       <c r="N96" t="n">
-        <v>85985041177</v>
+        <v>699000000</v>
       </c>
       <c r="O96" t="n">
-        <v>0.280991</v>
+        <v>1.03</v>
       </c>
       <c r="P96" s="1" t="n">
-        <v>44304.71413194444</v>
+        <v>45350.38608796296</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>5.558988310335781e-05</v>
+        <v>6.944963887202777e-05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>aerodrome-finance</t>
+          <t>stable-2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>aero</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Aerodrome Finance</t>
+          <t>​​Stable</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.625135</v>
+        <v>0.02552026</v>
       </c>
       <c r="F97" t="n">
-        <v>621011216</v>
+        <v>675267312</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>57074561</v>
+        <v>9735529</v>
       </c>
       <c r="I97" t="n">
-        <v>0.649736</v>
+        <v>0.02577869</v>
       </c>
       <c r="J97" t="n">
-        <v>0.578275</v>
+        <v>0.02471799</v>
       </c>
       <c r="K97" t="n">
-        <v>0.0400783</v>
+        <v>0.00061767</v>
       </c>
       <c r="L97" t="n">
-        <v>6.85033</v>
+        <v>2.49109</v>
       </c>
       <c r="M97" t="n">
-        <v>993231546.6010708</v>
+        <v>26460045953</v>
       </c>
       <c r="N97" t="n">
-        <v>1983240735.576791</v>
+        <v>100000000000</v>
       </c>
       <c r="O97" t="n">
-        <v>2.32</v>
+        <v>0.04323745</v>
       </c>
       <c r="P97" s="1" t="n">
-        <v>45633.25043981482</v>
+        <v>46156.97986111111</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>3.631995738420464e-05</v>
+        <v>5.527238006486553e-05</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>aptos</t>
+          <t>aerodrome-finance</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>apt</t>
+          <t>aero</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Aptos</t>
+          <t>Aerodrome Finance</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.686259</v>
+        <v>0.676086</v>
       </c>
       <c r="F98" t="n">
-        <v>598121508</v>
+        <v>671136888</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>200509884</v>
+        <v>87495268</v>
       </c>
       <c r="I98" t="n">
-        <v>0.707517</v>
+        <v>0.691195</v>
       </c>
       <c r="J98" t="n">
-        <v>0.5719610000000001</v>
+        <v>0.629119</v>
       </c>
       <c r="K98" t="n">
-        <v>0.113278</v>
+        <v>0.058827</v>
       </c>
       <c r="L98" t="n">
-        <v>19.76985</v>
+        <v>9.57982</v>
       </c>
       <c r="M98" t="n">
-        <v>870437430.8473938</v>
+        <v>992679168.7721908</v>
       </c>
       <c r="N98" t="n">
-        <v>1208877694.477877</v>
+        <v>1983240735.576791</v>
       </c>
       <c r="O98" t="n">
-        <v>19.92</v>
+        <v>2.32</v>
       </c>
       <c r="P98" s="1" t="n">
-        <v>44952.26755787037</v>
+        <v>45633.25043981482</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R98" t="b">
         <v>1</v>
       </c>
       <c r="S98" t="n">
-        <v>2.172225276104445e-05</v>
+        <v>5.274226188248661e-05</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>akedo</t>
+          <t>aptos</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ake</t>
+          <t>apt</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Akedo</t>
+          <t>Aptos</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.02618744</v>
+        <v>0.739513</v>
       </c>
       <c r="F99" t="n">
-        <v>597563482</v>
+        <v>643735939</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>19874412</v>
+        <v>294915580</v>
       </c>
       <c r="I99" t="n">
-        <v>0.02640787</v>
+        <v>0.780166</v>
       </c>
       <c r="J99" t="n">
-        <v>0.02073256</v>
+        <v>0.668581</v>
       </c>
       <c r="K99" t="n">
-        <v>0.00468007</v>
+        <v>0.04581178</v>
       </c>
       <c r="L99" t="n">
-        <v>21.76031</v>
+        <v>6.97469</v>
       </c>
       <c r="M99" t="n">
-        <v>22796250000</v>
+        <v>870485718.1680963</v>
       </c>
       <c r="N99" t="n">
-        <v>100000000000</v>
+        <v>1208925887.093529</v>
       </c>
       <c r="O99" t="n">
-        <v>0.0363756</v>
+        <v>19.92</v>
       </c>
       <c r="P99" s="1" t="n">
-        <v>46267.90648148148</v>
+        <v>44952.26755787037</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R99" t="b">
         <v>1</v>
       </c>
       <c r="S99" t="n">
-        <v>2.136637671753863e-05</v>
+        <v>3.595763171392825e-05</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7105,34 +7105,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.075929</v>
+        <v>0.075616</v>
       </c>
       <c r="F100" t="n">
-        <v>597701598</v>
+        <v>595153733</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>1582692</v>
+        <v>3430787</v>
       </c>
       <c r="I100" t="n">
-        <v>0.076638</v>
+        <v>0.076763</v>
       </c>
       <c r="J100" t="n">
-        <v>0.075601</v>
+        <v>0.075255</v>
       </c>
       <c r="K100" t="n">
-        <v>-0.000318594938063965</v>
+        <v>-0.000268082142819329</v>
       </c>
       <c r="L100" t="n">
-        <v>-0.41784</v>
+        <v>-0.37544</v>
       </c>
       <c r="M100" t="n">
-        <v>7870743834.936207</v>
+        <v>7870755165.810848</v>
       </c>
       <c r="N100" t="n">
-        <v>9939683660.568291</v>
+        <v>9939695277.199703</v>
       </c>
       <c r="O100" t="n">
         <v>0.450785</v>
@@ -7141,74 +7141,74 @@
         <v>43450.66666666666</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R100" t="b">
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>2.145445894959385e-05</v>
+        <v>6.198284310204505e-06</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>official-trump</t>
+          <t>blockstack</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>trump</t>
+          <t>stx</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Official Trump</t>
+          <t>Stacks</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2.06</v>
+        <v>0.313238</v>
       </c>
       <c r="F101" t="n">
-        <v>564060261</v>
+        <v>585035019</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>181529355</v>
+        <v>41366435</v>
       </c>
       <c r="I101" t="n">
-        <v>2.07</v>
+        <v>0.321993</v>
       </c>
       <c r="J101" t="n">
-        <v>1.93</v>
+        <v>0.271596</v>
       </c>
       <c r="K101" t="n">
-        <v>0.122432</v>
+        <v>0.04080722</v>
       </c>
       <c r="L101" t="n">
-        <v>6.30502</v>
+        <v>14.95778</v>
       </c>
       <c r="M101" t="n">
-        <v>273137120.287634</v>
+        <v>1867702388.984369</v>
       </c>
       <c r="N101" t="n">
-        <v>1000000000</v>
+        <v>1867702388.984369</v>
       </c>
       <c r="O101" t="n">
-        <v>73.43000000000001</v>
+        <v>3.86</v>
       </c>
       <c r="P101" s="1" t="n">
-        <v>45676.16011574074</v>
+        <v>45383.19094907407</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46283.56203703704</v>
+        <v>46284.54108796296</v>
       </c>
       <c r="R101" t="b">
         <v>1</v>

--- a/src/xlsx/cleaned_data.xlsx
+++ b/src/xlsx/cleaned_data.xlsx
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,34 +539,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>81303</v>
+        <v>80495</v>
       </c>
       <c r="F2" t="n">
-        <v>1633087433036</v>
+        <v>1616935563111</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>39046726177</v>
+        <v>23866467100</v>
       </c>
       <c r="I2" t="n">
-        <v>81675</v>
+        <v>81864</v>
       </c>
       <c r="J2" t="n">
-        <v>80014</v>
+        <v>80155</v>
       </c>
       <c r="K2" t="n">
-        <v>3308.3</v>
+        <v>-716.1132064880803</v>
       </c>
       <c r="L2" t="n">
-        <v>4.27011</v>
+        <v>-0.88179</v>
       </c>
       <c r="M2" t="n">
-        <v>20086521</v>
+        <v>20086925</v>
       </c>
       <c r="N2" t="n">
-        <v>20086553</v>
+        <v>20086940</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -575,7 +575,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -587,7 +587,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,34 +606,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2640.53</v>
+        <v>2580.2</v>
       </c>
       <c r="F3" t="n">
-        <v>322307862116</v>
+        <v>314968305243</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>20959346820</v>
+        <v>9962778525</v>
       </c>
       <c r="I3" t="n">
-        <v>2655.71</v>
+        <v>2655.64</v>
       </c>
       <c r="J3" t="n">
-        <v>2552.3</v>
+        <v>2568.1</v>
       </c>
       <c r="K3" t="n">
-        <v>140.11</v>
+        <v>-52.42004059185319</v>
       </c>
       <c r="L3" t="n">
-        <v>5.64929</v>
+        <v>-1.99117</v>
       </c>
       <c r="M3" t="n">
-        <v>122061836.5153193</v>
+        <v>122064744.0690741</v>
       </c>
       <c r="N3" t="n">
-        <v>122061836.5153193</v>
+        <v>122064744.0690741</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -642,19 +642,19 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1970734177712673</v>
+        <v>0.1945062923950015</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,31 +673,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999655</v>
+        <v>0.999618</v>
       </c>
       <c r="F4" t="n">
-        <v>183321470793</v>
+        <v>183316154408</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>73806318083</v>
+        <v>47434232181</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999786</v>
+        <v>0.999725</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999212</v>
+        <v>0.9993649999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00048018</v>
+        <v>-5.0405962333966e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04844</v>
+        <v>-0.00504</v>
       </c>
       <c r="M4" t="n">
-        <v>183384649794.4283</v>
+        <v>183384649789.2811</v>
       </c>
       <c r="N4" t="n">
         <v>188851595759.0362</v>
@@ -709,19 +709,19 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1119363965382041</v>
+        <v>0.1130564875328519</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,34 +740,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>771.92</v>
+        <v>751.14</v>
       </c>
       <c r="F5" t="n">
-        <v>102788869489</v>
+        <v>100013527800</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1257822052</v>
+        <v>925413271</v>
       </c>
       <c r="I5" t="n">
-        <v>769.3200000000001</v>
+        <v>772.55</v>
       </c>
       <c r="J5" t="n">
-        <v>754.7</v>
+        <v>746.64</v>
       </c>
       <c r="K5" t="n">
-        <v>25.56</v>
+        <v>-17.74319357724983</v>
       </c>
       <c r="L5" t="n">
-        <v>3.48143</v>
+        <v>-2.30766</v>
       </c>
       <c r="M5" t="n">
-        <v>133160340.96</v>
+        <v>133160261.42</v>
       </c>
       <c r="N5" t="n">
-        <v>133160340.96</v>
+        <v>133160255.08</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -776,19 +776,19 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0626056259360764</v>
+        <v>0.06151929168232792</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -807,28 +807,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="F6" t="n">
-        <v>89964077796</v>
+        <v>86599821752</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>4324462181</v>
+        <v>2615052383</v>
       </c>
       <c r="I6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="J6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="K6" t="n">
-        <v>0.108094</v>
+        <v>-0.05751144693811527</v>
       </c>
       <c r="L6" t="n">
-        <v>8.24385</v>
+        <v>-4.00873</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -843,19 +843,19 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05474971607120988</v>
+        <v>0.05322057621768561</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,34 +874,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.99977</v>
+        <v>0.999739</v>
       </c>
       <c r="F7" t="n">
-        <v>74243970808</v>
+        <v>74195791330</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>19667075261</v>
+        <v>11424902046</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999862</v>
+        <v>1.002</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999515</v>
+        <v>0.9994690000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00024919</v>
+        <v>-1.7217957993698e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02565</v>
+        <v>-0.00172</v>
       </c>
       <c r="M7" t="n">
-        <v>74260936982.90303</v>
+        <v>74214798719.86125</v>
       </c>
       <c r="N7" t="n">
-        <v>74261085155.35321</v>
+        <v>74213440603.05618</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -910,19 +910,19 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04512026192333529</v>
+        <v>0.04554652113413224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -941,34 +941,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>111.73</v>
+        <v>108.19</v>
       </c>
       <c r="F8" t="n">
-        <v>65619505724</v>
+        <v>63553214540</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>5307023206</v>
+        <v>2831986860</v>
       </c>
       <c r="I8" t="n">
-        <v>114.14</v>
+        <v>112.21</v>
       </c>
       <c r="J8" t="n">
-        <v>108.45</v>
+        <v>107.5</v>
       </c>
       <c r="K8" t="n">
-        <v>6.04</v>
+        <v>-3.282472112539367</v>
       </c>
       <c r="L8" t="n">
-        <v>5.75077</v>
+        <v>-2.94473</v>
       </c>
       <c r="M8" t="n">
-        <v>587296224.8630985</v>
+        <v>587366825.3628587</v>
       </c>
       <c r="N8" t="n">
-        <v>634297490.1327897</v>
+        <v>634375499.6096436</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -977,19 +977,19 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03983728954027715</v>
+        <v>0.03896223217813675</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1008,34 +1008,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.338162</v>
+        <v>0.342134</v>
       </c>
       <c r="F9" t="n">
-        <v>32110527640</v>
+        <v>32482355042</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>444297894</v>
+        <v>373296960</v>
       </c>
       <c r="I9" t="n">
-        <v>0.339776</v>
+        <v>0.342855</v>
       </c>
       <c r="J9" t="n">
-        <v>0.337075</v>
+        <v>0.337711</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00045238</v>
+        <v>0.0043126</v>
       </c>
       <c r="L9" t="n">
-        <v>0.13803</v>
+        <v>1.27659</v>
       </c>
       <c r="M9" t="n">
         <v>94955991096.57959</v>
       </c>
       <c r="N9" t="n">
-        <v>94956666619.81319</v>
+        <v>94958776822.35458</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1044,19 +1044,19 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01931114628639689</v>
+        <v>0.01973948931400291</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1075,34 +1075,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1534.88</v>
+        <v>1449.06</v>
       </c>
       <c r="F10" t="n">
-        <v>26001228471</v>
+        <v>24547629301</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1664369969</v>
+        <v>1070998386</v>
       </c>
       <c r="I10" t="n">
-        <v>1590.8</v>
+        <v>1532.34</v>
       </c>
       <c r="J10" t="n">
-        <v>1437.73</v>
+        <v>1429.69</v>
       </c>
       <c r="K10" t="n">
-        <v>74.98</v>
+        <v>-86.56531411476908</v>
       </c>
       <c r="L10" t="n">
-        <v>5.09457</v>
+        <v>-5.63715</v>
       </c>
       <c r="M10" t="n">
-        <v>16940251.7280448</v>
+        <v>16942351.7280448</v>
       </c>
       <c r="N10" t="n">
-        <v>16940898.6030448</v>
+        <v>16942756.4155448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1111,19 +1111,19 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0155688552022178</v>
+        <v>0.01483047826374584</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1142,34 +1142,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.03</v>
+        <v>1.017</v>
       </c>
       <c r="F11" t="n">
-        <v>23389434218</v>
+        <v>23140466333</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>52721291</v>
+        <v>345014</v>
       </c>
       <c r="I11" t="n">
-        <v>1.034</v>
+        <v>1.044</v>
       </c>
       <c r="J11" t="n">
-        <v>1.027</v>
+        <v>1.001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.00207246</v>
+        <v>-0.01372322010803706</v>
       </c>
       <c r="L11" t="n">
-        <v>0.20108</v>
+        <v>-1.3316</v>
       </c>
       <c r="M11" t="n">
-        <v>22705389532.338</v>
+        <v>22756817018.848</v>
       </c>
       <c r="N11" t="n">
-        <v>22705389532.338</v>
+        <v>22756817018.848</v>
       </c>
       <c r="O11" t="n">
         <v>1.061</v>
@@ -1178,19 +1178,19 @@
         <v>46237.59675925926</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46284.89166666667</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0139689835841592</v>
+        <v>0.01395990267173376</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1209,28 +1209,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>92.44</v>
+        <v>91.02</v>
       </c>
       <c r="F12" t="n">
-        <v>20562860000</v>
+        <v>20248590427</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1445408936</v>
+        <v>816678542</v>
       </c>
       <c r="I12" t="n">
-        <v>94.48</v>
+        <v>93.34</v>
       </c>
       <c r="J12" t="n">
-        <v>90.36</v>
+        <v>89.91</v>
       </c>
       <c r="K12" t="n">
-        <v>1.25</v>
+        <v>-1.201150679321842</v>
       </c>
       <c r="L12" t="n">
-        <v>1.50458</v>
+        <v>-1.30245</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1245,19 +1245,19 @@
         <v>46284.12847222222</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01223754709657214</v>
+        <v>0.01217077331277282</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1276,34 +1276,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.088697</v>
+        <v>0.084982</v>
       </c>
       <c r="F13" t="n">
-        <v>13834995349</v>
+        <v>13258401671</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1053761028</v>
+        <v>957418339</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08876100000000001</v>
+        <v>0.09105199999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08651</v>
+        <v>0.084508</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00331129</v>
+        <v>-0.003840532751950301</v>
       </c>
       <c r="L13" t="n">
-        <v>3.91707</v>
+        <v>-4.32382</v>
       </c>
       <c r="M13" t="n">
-        <v>155979846383.7052</v>
+        <v>155990666383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171691843126.579</v>
+        <v>155993876383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1312,19 +1312,19 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>0.008116349688732294</v>
+        <v>0.007846123039194233</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1343,34 +1343,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>582.04</v>
+        <v>535.58</v>
       </c>
       <c r="F14" t="n">
-        <v>10946267634</v>
+        <v>10061624614</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>213999830</v>
+        <v>131885688</v>
       </c>
       <c r="I14" t="n">
-        <v>605</v>
+        <v>579.76</v>
       </c>
       <c r="J14" t="n">
-        <v>537.42</v>
+        <v>518.29</v>
       </c>
       <c r="K14" t="n">
-        <v>47.71</v>
+        <v>-42.40255239524106</v>
       </c>
       <c r="L14" t="n">
-        <v>8.926119999999999</v>
+        <v>-7.33635</v>
       </c>
       <c r="M14" t="n">
-        <v>18806665.92890474</v>
+        <v>18807107.52726052</v>
       </c>
       <c r="N14" t="n">
-        <v>18806692.32885915</v>
+        <v>18807145.32714538</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1379,19 +1379,19 @@
         <v>46036.48202546296</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R14" t="b">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0063468406708534</v>
+        <v>0.0058683591680458</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1410,28 +1410,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>83.14</v>
+        <v>81.87</v>
       </c>
       <c r="F15" t="n">
-        <v>9884929159</v>
+        <v>9729647899</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>129651249</v>
+        <v>66922631</v>
       </c>
       <c r="I15" t="n">
-        <v>83.64</v>
+        <v>83.58</v>
       </c>
       <c r="J15" t="n">
-        <v>82.25</v>
+        <v>81.56</v>
       </c>
       <c r="K15" t="n">
-        <v>2.81</v>
+        <v>-1.16256627545016</v>
       </c>
       <c r="L15" t="n">
-        <v>3.54404</v>
+        <v>-1.4002</v>
       </c>
       <c r="M15" t="n">
         <v>118887984</v>
@@ -1446,153 +1446,153 @@
         <v>46283.82569444444</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005696710860147328</v>
+        <v>0.005662973699718616</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.01392643</v>
+        <v>0.999799</v>
       </c>
       <c r="F16" t="n">
-        <v>9877121902</v>
+        <v>9594177187</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>24502476</v>
+        <v>73095244</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01403534</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01258685</v>
+        <v>0.999555</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00113075</v>
+        <v>-0.000212149564497666</v>
       </c>
       <c r="L16" t="n">
-        <v>8.83832</v>
+        <v>-0.02121</v>
       </c>
       <c r="M16" t="n">
-        <v>709234380366.2201</v>
+        <v>9596506299.314947</v>
       </c>
       <c r="N16" t="n">
-        <v>1142408526965.963</v>
+        <v>9615952659.618965</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01946402</v>
+        <v>1.057</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>46259.82847222222</v>
+        <v>45593.90336805556</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.005691928473910418</v>
+        <v>0.005579161449125267</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.999902</v>
+        <v>0.01319963</v>
       </c>
       <c r="F17" t="n">
-        <v>9594602900</v>
+        <v>9360305215</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>135400991</v>
+        <v>22251262</v>
       </c>
       <c r="I17" t="n">
+        <v>0.01400625</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.01315802</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.000716285644190382</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-5.14724</v>
+      </c>
+      <c r="M17" t="n">
+        <v>709239215179.4515</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1142408526965.963</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.01946402</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>46259.82847222222</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>46285.56273148148</v>
+      </c>
+      <c r="R17" t="b">
         <v>1</v>
       </c>
-      <c r="J17" t="n">
-        <v>0.9997779999999999</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.00012737</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.01791</v>
-      </c>
-      <c r="M17" t="n">
-        <v>9595541701.9596</v>
-      </c>
-      <c r="N17" t="n">
-        <v>9593827178.349619</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.057</v>
-      </c>
-      <c r="P17" s="1" t="n">
-        <v>45593.90336805556</v>
-      </c>
-      <c r="Q17" s="1" t="n">
-        <v>46284.54108796296</v>
-      </c>
-      <c r="R17" t="b">
-        <v>0</v>
-      </c>
       <c r="S17" t="n">
-        <v>0.005518869615103732</v>
+        <v>0.005434470865938365</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1611,28 +1611,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>12.52</v>
+        <v>12.1</v>
       </c>
       <c r="F18" t="n">
-        <v>9366762678</v>
+        <v>9051969224</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>519635409</v>
+        <v>444890857</v>
       </c>
       <c r="I18" t="n">
-        <v>12.6</v>
+        <v>12.67</v>
       </c>
       <c r="J18" t="n">
-        <v>11.99</v>
+        <v>11.92</v>
       </c>
       <c r="K18" t="n">
-        <v>0.708727</v>
+        <v>-0.3614832084632802</v>
       </c>
       <c r="L18" t="n">
-        <v>6.05539</v>
+        <v>-2.90074</v>
       </c>
       <c r="M18" t="n">
         <v>748099970.424884</v>
@@ -1647,19 +1647,19 @@
         <v>44325.67635416667</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005379304599899615</v>
+        <v>0.005243711306450401</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1678,28 +1678,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.226696</v>
+        <v>0.221201</v>
       </c>
       <c r="F19" t="n">
-        <v>8506282135</v>
+        <v>8300217493</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>663518519</v>
+        <v>422086912</v>
       </c>
       <c r="I19" t="n">
-        <v>0.234678</v>
+        <v>0.231163</v>
       </c>
       <c r="J19" t="n">
-        <v>0.216904</v>
+        <v>0.218425</v>
       </c>
       <c r="K19" t="n">
-        <v>0.01201744</v>
+        <v>-0.005928161879755561</v>
       </c>
       <c r="L19" t="n">
-        <v>5.67518</v>
+        <v>-2.61004</v>
       </c>
       <c r="M19" t="n">
         <v>37522923322.16203</v>
@@ -1714,19 +1714,19 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004852211626532332</v>
+        <v>0.004778621815649199</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1745,28 +1745,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.880000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="F20" t="n">
-        <v>8172462611</v>
+        <v>8218224663</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>53547</v>
+        <v>163463</v>
       </c>
       <c r="I20" t="n">
-        <v>8.92</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>8.81</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.01326123114329647</v>
+        <v>0.04202022</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.14903</v>
+        <v>0.47255</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -1781,19 +1781,19 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004647728298112422</v>
+        <v>0.004727894957324148</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1812,31 +1812,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.199434</v>
+        <v>0.190217</v>
       </c>
       <c r="F21" t="n">
-        <v>6953702577</v>
+        <v>6633745483</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>273347233</v>
+        <v>209188054</v>
       </c>
       <c r="I21" t="n">
-        <v>0.196206</v>
+        <v>0.202311</v>
       </c>
       <c r="J21" t="n">
-        <v>0.189492</v>
+        <v>0.188682</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01351744</v>
+        <v>-0.01022295789780794</v>
       </c>
       <c r="L21" t="n">
-        <v>7.31125</v>
+        <v>-5.10025</v>
       </c>
       <c r="M21" t="n">
-        <v>34867269295.95199</v>
+        <v>34867261640.33779</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70148</v>
@@ -1848,19 +1848,19 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R21" t="b">
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.003901168883877915</v>
+        <v>0.003747618378471406</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1879,34 +1879,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>9.07</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>5631064554</v>
+        <v>5355976540</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>1435766007</v>
+        <v>806083310</v>
       </c>
       <c r="I22" t="n">
-        <v>9.41</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>8.6</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.422102</v>
+        <v>-0.3641764250946125</v>
       </c>
       <c r="L22" t="n">
-        <v>5.0829</v>
+        <v>-4.04975</v>
       </c>
       <c r="M22" t="n">
-        <v>620990422.6104751</v>
+        <v>620926422.6104751</v>
       </c>
       <c r="N22" t="n">
-        <v>888238418.9163101</v>
+        <v>888126418.9163101</v>
       </c>
       <c r="O22" t="n">
         <v>44.92</v>
@@ -1915,19 +1915,19 @@
         <v>44318.89240740741</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R22" t="b">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.003090978329422003</v>
+        <v>0.002957095546856589</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1946,34 +1946,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>251.99</v>
+        <v>246.11</v>
       </c>
       <c r="F23" t="n">
-        <v>5062765144</v>
+        <v>4945351588</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>295039948</v>
+        <v>145678419</v>
       </c>
       <c r="I23" t="n">
-        <v>264.9</v>
+        <v>256.71</v>
       </c>
       <c r="J23" t="n">
-        <v>245.38</v>
+        <v>243.4</v>
       </c>
       <c r="K23" t="n">
-        <v>2.27</v>
+        <v>-5.721021554373493</v>
       </c>
       <c r="L23" t="n">
-        <v>0.92301</v>
+        <v>-2.27178</v>
       </c>
       <c r="M23" t="n">
-        <v>20091159.27165077</v>
+        <v>20091637.39665077</v>
       </c>
       <c r="N23" t="n">
-        <v>20091462.39665077</v>
+        <v>20091940.52165077</v>
       </c>
       <c r="O23" t="n">
         <v>3785.82</v>
@@ -1982,19 +1982,19 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R23" t="b">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.002742862816274633</v>
+        <v>0.002703052434003487</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2013,34 +2013,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.999699</v>
+        <v>0.999728</v>
       </c>
       <c r="F24" t="n">
-        <v>4806809632</v>
+        <v>4844853212</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>32606200</v>
+        <v>33630793</v>
       </c>
       <c r="I24" t="n">
-        <v>0.999931</v>
+        <v>0.9998010000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.999394</v>
+        <v>0.999471</v>
       </c>
       <c r="K24" t="n">
-        <v>0.00028496</v>
+        <v>4.12e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.02919</v>
+        <v>0.00412</v>
       </c>
       <c r="M24" t="n">
-        <v>4808257984.85422</v>
+        <v>4846068728.449359</v>
       </c>
       <c r="N24" t="n">
-        <v>4832281815.490858</v>
+        <v>4846803023.178389</v>
       </c>
       <c r="O24" t="n">
         <v>1.034</v>
@@ -2049,19 +2049,19 @@
         <v>46000.38208333333</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002586075596659575</v>
+        <v>0.002640876669595186</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2080,34 +2080,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3.63</v>
+        <v>3.69</v>
       </c>
       <c r="F25" t="n">
-        <v>4739515967</v>
+        <v>4814880203</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>1304547274</v>
+        <v>1242982579</v>
       </c>
       <c r="I25" t="n">
-        <v>3.91</v>
+        <v>3.74</v>
       </c>
       <c r="J25" t="n">
-        <v>3.57</v>
+        <v>3.43</v>
       </c>
       <c r="K25" t="n">
-        <v>0.02360836</v>
+        <v>0.120604</v>
       </c>
       <c r="L25" t="n">
-        <v>0.62856</v>
+        <v>3.37953</v>
       </c>
       <c r="M25" t="n">
-        <v>1306731469</v>
+        <v>1306811794</v>
       </c>
       <c r="N25" t="n">
-        <v>1306731496</v>
+        <v>1306811791</v>
       </c>
       <c r="O25" t="n">
         <v>20.44</v>
@@ -2116,220 +2116,220 @@
         <v>44577.59010416667</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002544854422907094</v>
+        <v>0.002622333138641096</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>avalanche-2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>avax</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Dai</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.999908</v>
+        <v>10.62</v>
       </c>
       <c r="F26" t="n">
-        <v>4597242919</v>
+        <v>4711603532</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>248389251</v>
+        <v>1342152577</v>
       </c>
       <c r="I26" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="J26" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L26" t="n">
+        <v>14.82973</v>
+      </c>
+      <c r="M26" t="n">
+        <v>442879289.6632363</v>
+      </c>
+      <c r="N26" t="n">
+        <v>469547976.0745428</v>
+      </c>
+      <c r="O26" t="n">
+        <v>144.96</v>
+      </c>
+      <c r="P26" s="1" t="n">
+        <v>44521.26314814815</v>
+      </c>
+      <c r="Q26" s="1" t="n">
+        <v>46285.56273148148</v>
+      </c>
+      <c r="R26" t="b">
         <v>1</v>
       </c>
-      <c r="J26" t="n">
-        <v>0.999708</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-6.7611320880401e-05</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.01342</v>
-      </c>
-      <c r="M26" t="n">
-        <v>4597666728.880691</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4588681220.277516</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P26" s="1" t="n">
-        <v>43902.79363425926</v>
-      </c>
-      <c r="Q26" s="1" t="n">
-        <v>46284.54108796296</v>
-      </c>
-      <c r="R26" t="b">
-        <v>0</v>
-      </c>
       <c r="S26" t="n">
-        <v>0.002457704138673013</v>
+        <v>0.002558438514463592</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>litecoin</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ltc</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Dai</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>58.01</v>
+        <v>0.999841</v>
       </c>
       <c r="F27" t="n">
-        <v>4503368511</v>
+        <v>4605413603</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>431386158</v>
+        <v>172647200</v>
       </c>
       <c r="I27" t="n">
-        <v>59.16</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>55.4</v>
+        <v>0.999503</v>
       </c>
       <c r="K27" t="n">
-        <v>2.84</v>
+        <v>-3.219872398819e-06</v>
       </c>
       <c r="L27" t="n">
-        <v>5.21912</v>
+        <v>-0.00032</v>
       </c>
       <c r="M27" t="n">
-        <v>77624504.44021429</v>
+        <v>4605655963.213758</v>
       </c>
       <c r="N27" t="n">
-        <v>77627366.94755507</v>
+        <v>4606200673.079864</v>
       </c>
       <c r="O27" t="n">
-        <v>410.26</v>
+        <v>1.22</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>44325.80077546297</v>
+        <v>43902.79363425926</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002400200757291137</v>
+        <v>0.002492741532374666</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>canton-network</t>
+          <t>litecoin</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>ltc</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.111067</v>
+        <v>56.92</v>
       </c>
       <c r="F28" t="n">
-        <v>4402165335</v>
+        <v>4418176889</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>10920109</v>
+        <v>277072921</v>
       </c>
       <c r="I28" t="n">
-        <v>0.113569</v>
+        <v>58.41</v>
       </c>
       <c r="J28" t="n">
-        <v>0.107754</v>
+        <v>56.59</v>
       </c>
       <c r="K28" t="n">
-        <v>0.00329884</v>
+        <v>-0.9526302316288451</v>
       </c>
       <c r="L28" t="n">
-        <v>3.10572</v>
+        <v>-1.64611</v>
       </c>
       <c r="M28" t="n">
-        <v>39635347931.85809</v>
+        <v>77628260.69940798</v>
       </c>
       <c r="N28" t="n">
-        <v>39635347931.85809</v>
+        <v>77631210.7072867</v>
       </c>
       <c r="O28" t="n">
-        <v>0.194152</v>
+        <v>410.26</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>46056.00148148148</v>
+        <v>44325.80077546297</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002338208091232617</v>
+        <v>0.002376902985707521</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2348,34 +2348,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9996429999999999</v>
+        <v>0.999407</v>
       </c>
       <c r="F29" t="n">
-        <v>4355242509</v>
+        <v>4354328121</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>1209396989</v>
+        <v>801746341</v>
       </c>
       <c r="I29" t="n">
-        <v>0.999766</v>
+        <v>0.999739</v>
       </c>
       <c r="J29" t="n">
-        <v>0.999263</v>
+        <v>0.999196</v>
       </c>
       <c r="K29" t="n">
-        <v>0.00046674</v>
+        <v>-0.00025750416125081</v>
       </c>
       <c r="L29" t="n">
-        <v>0.04476</v>
+        <v>-0.02576</v>
       </c>
       <c r="M29" t="n">
-        <v>4356798749.096847</v>
+        <v>4356798749.070584</v>
       </c>
       <c r="N29" t="n">
-        <v>4356798749.096847</v>
+        <v>4356798749.070584</v>
       </c>
       <c r="O29" t="n">
         <v>1.048</v>
@@ -2384,86 +2384,86 @@
         <v>46212.42696759259</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002309465207879431</v>
+        <v>0.002337401392597915</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>avalanche-2</t>
+          <t>canton-network</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>avax</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>9.33</v>
+        <v>0.104589</v>
       </c>
       <c r="F30" t="n">
-        <v>4132083352</v>
+        <v>4146281070</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>736451226</v>
+        <v>8159457</v>
       </c>
       <c r="I30" t="n">
-        <v>9.35</v>
+        <v>0.113632</v>
       </c>
       <c r="J30" t="n">
-        <v>8.050000000000001</v>
+        <v>0.102843</v>
       </c>
       <c r="K30" t="n">
-        <v>1.34</v>
+        <v>-0.006877583372992727</v>
       </c>
       <c r="L30" t="n">
-        <v>16.80374</v>
+        <v>-6.17011</v>
       </c>
       <c r="M30" t="n">
-        <v>442873736.1288731</v>
+        <v>39642019727.36819</v>
       </c>
       <c r="N30" t="n">
-        <v>469542447.6310036</v>
+        <v>39643068193.79603</v>
       </c>
       <c r="O30" t="n">
-        <v>144.96</v>
+        <v>0.194152</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>44521.26314814815</v>
+        <v>46056.00148148148</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R30" t="b">
         <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>0.00217276760959653</v>
+        <v>0.002208688024843419</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2482,34 +2482,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="F31" t="n">
-        <v>3881514914</v>
+        <v>3837702612</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>37331609</v>
+        <v>39656864</v>
       </c>
       <c r="I31" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="K31" t="n">
-        <v>0.02007921</v>
+        <v>-0.02118006897896074</v>
       </c>
       <c r="L31" t="n">
-        <v>1.49008</v>
+        <v>-1.52103</v>
       </c>
       <c r="M31" t="n">
-        <v>2798418312.826097</v>
+        <v>2799003081.352252</v>
       </c>
       <c r="N31" t="n">
-        <v>5251809962.746284</v>
+        <v>5252388289.862276</v>
       </c>
       <c r="O31" t="n">
         <v>8.25</v>
@@ -2518,19 +2518,19 @@
         <v>45457.69225694444</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.002019280277324084</v>
+        <v>0.002017778457249168</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2549,31 +2549,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.08067199999999999</v>
+        <v>0.08301799999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>3535989216</v>
+        <v>3635864245</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>98941677</v>
+        <v>144444996</v>
       </c>
       <c r="I32" t="n">
-        <v>0.080799</v>
+        <v>0.083749</v>
       </c>
       <c r="J32" t="n">
-        <v>0.077612</v>
+        <v>0.079527</v>
       </c>
       <c r="K32" t="n">
-        <v>0.00359811</v>
+        <v>0.00182624</v>
       </c>
       <c r="L32" t="n">
-        <v>4.76082</v>
+        <v>2.2493</v>
       </c>
       <c r="M32" t="n">
-        <v>43831706402.06228</v>
+        <v>43831706401.51488</v>
       </c>
       <c r="N32" t="n">
         <v>50000000000</v>
@@ -2585,287 +2585,287 @@
         <v>44454.11143518519</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001807626255608888</v>
+        <v>0.001892906242844947</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>memecore</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>MemeCore</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.850953</v>
+        <v>1.52</v>
       </c>
       <c r="F33" t="n">
-        <v>3485961697</v>
+        <v>3452848597</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>885201033</v>
+        <v>4391838</v>
       </c>
       <c r="I33" t="n">
-        <v>0.868613</v>
+        <v>1.78</v>
       </c>
       <c r="J33" t="n">
-        <v>0.796157</v>
+        <v>1.27</v>
       </c>
       <c r="K33" t="n">
-        <v>0.052166</v>
+        <v>0.225627</v>
       </c>
       <c r="L33" t="n">
-        <v>6.6382</v>
+        <v>17.43532</v>
       </c>
       <c r="M33" t="n">
-        <v>4096537146.540959</v>
+        <v>2275413158.37504</v>
       </c>
       <c r="N33" t="n">
-        <v>10000000000</v>
+        <v>5416287555.165793</v>
       </c>
       <c r="O33" t="n">
-        <v>5.35</v>
+        <v>5.64</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>45661.62243055556</v>
+        <v>46205.17638888889</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R33" t="b">
         <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001776981572292791</v>
+        <v>0.001779679161313994</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>global-dollar</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>usdg</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Global Dollar</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.999862</v>
+        <v>0.818716</v>
       </c>
       <c r="F34" t="n">
-        <v>3259123737</v>
+        <v>3355103041</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>914713989</v>
+        <v>801060446</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0.885594</v>
       </c>
       <c r="J34" t="n">
-        <v>0.999776</v>
+        <v>0.809067</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.000110598148557184</v>
+        <v>-0.02899743878369299</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.00652</v>
+        <v>-3.42067</v>
       </c>
       <c r="M34" t="n">
-        <v>3259575067.166086</v>
+        <v>4096537146.540959</v>
       </c>
       <c r="N34" t="n">
-        <v>3259575067.166086</v>
+        <v>10000000000</v>
       </c>
       <c r="O34" t="n">
-        <v>1.65</v>
+        <v>5.35</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>45686.67436342593</v>
+        <v>45661.62243055556</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R34" t="b">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001638030499218999</v>
+        <v>0.001719206495946603</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>shiba-inu</t>
+          <t>global-dollar</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>shib</t>
+          <t>usdg</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Shiba Inu</t>
+          <t>Global Dollar</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5.48e-06</v>
+        <v>0.999937</v>
       </c>
       <c r="F35" t="n">
-        <v>3227703703</v>
+        <v>3259397697</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>89625103</v>
+        <v>593925412</v>
       </c>
       <c r="I35" t="n">
-        <v>5.51e-06</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>5.37e-06</v>
+        <v>0.999688</v>
       </c>
       <c r="K35" t="n">
-        <v>9.948e-08</v>
+        <v>2.836e-05</v>
       </c>
       <c r="L35" t="n">
-        <v>1.85543</v>
+        <v>0.00284</v>
       </c>
       <c r="M35" t="n">
-        <v>589239049649142.6</v>
+        <v>3259575067.132162</v>
       </c>
       <c r="N35" t="n">
-        <v>589496073303830.6</v>
+        <v>3259575067.132162</v>
       </c>
       <c r="O35" t="n">
-        <v>8.616e-05</v>
+        <v>1.65</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>44496.82980324074</v>
+        <v>45686.67436342593</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001618783952299273</v>
+        <v>0.001659996057350467</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>bittensor</t>
+          <t>shiba-inu</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>tao</t>
+          <t>shib</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>Shiba Inu</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>265.37</v>
+        <v>5.36e-06</v>
       </c>
       <c r="F36" t="n">
-        <v>3009165450</v>
+        <v>3159278566</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>333417078</v>
+        <v>94491922</v>
       </c>
       <c r="I36" t="n">
-        <v>271.96</v>
+        <v>5.68e-06</v>
       </c>
       <c r="J36" t="n">
-        <v>246.72</v>
+        <v>5.32e-06</v>
       </c>
       <c r="K36" t="n">
-        <v>18.77</v>
+        <v>-1.0395809831e-07</v>
       </c>
       <c r="L36" t="n">
-        <v>7.67099</v>
+        <v>-1.90239</v>
       </c>
       <c r="M36" t="n">
-        <v>11339645.9251</v>
+        <v>589238979414596.2</v>
       </c>
       <c r="N36" t="n">
-        <v>21000000</v>
+        <v>589496072572615.9</v>
       </c>
       <c r="O36" t="n">
-        <v>757.6</v>
+        <v>8.616e-05</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>45358.44833333333</v>
+        <v>44496.82980324074</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.00148491691892434</v>
+        <v>0.001598054922084563</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2884,34 +2884,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.059987</v>
+        <v>0.058421</v>
       </c>
       <c r="F37" t="n">
-        <v>2983222544</v>
+        <v>2905781385</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>10539800</v>
+        <v>5958031</v>
       </c>
       <c r="I37" t="n">
-        <v>0.060428</v>
+        <v>0.060372</v>
       </c>
       <c r="J37" t="n">
-        <v>0.058546</v>
+        <v>0.057552</v>
       </c>
       <c r="K37" t="n">
-        <v>0.00087021</v>
+        <v>-0.00136383075890182</v>
       </c>
       <c r="L37" t="n">
-        <v>1.47573</v>
+        <v>-2.28125</v>
       </c>
       <c r="M37" t="n">
-        <v>49730956672.65237</v>
+        <v>49733008409.9673</v>
       </c>
       <c r="N37" t="n">
-        <v>98930992992.14902</v>
+        <v>98933025248.62096</v>
       </c>
       <c r="O37" t="n">
         <v>0.891544</v>
@@ -2920,86 +2920,86 @@
         <v>44523.66666666666</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001469025422512749</v>
+        <v>0.001441222726069533</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>memecore</t>
+          <t>bittensor</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>tao</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MemeCore</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.29</v>
+        <v>251.86</v>
       </c>
       <c r="F38" t="n">
-        <v>2937160197</v>
+        <v>2855709416</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
       </c>
       <c r="H38" t="n">
-        <v>1933129</v>
+        <v>243526788</v>
       </c>
       <c r="I38" t="n">
-        <v>1.38</v>
+        <v>273.18</v>
       </c>
       <c r="J38" t="n">
-        <v>1.27</v>
+        <v>248.91</v>
       </c>
       <c r="K38" t="n">
-        <v>0.00587505</v>
+        <v>-13.04437088448014</v>
       </c>
       <c r="L38" t="n">
-        <v>0.42336</v>
+        <v>-4.92422</v>
       </c>
       <c r="M38" t="n">
-        <v>2274542875.649129</v>
+        <v>11339645.9251</v>
       </c>
       <c r="N38" t="n">
-        <v>5415932722.156354</v>
+        <v>21000000</v>
       </c>
       <c r="O38" t="n">
-        <v>5.64</v>
+        <v>757.6</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>46205.17638888889</v>
+        <v>45358.44833333333</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001440809631187755</v>
+        <v>0.001410244484709655</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3018,34 +3018,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.999916</v>
+        <v>0.999825</v>
       </c>
       <c r="F39" t="n">
-        <v>2802423965</v>
+        <v>2801865407</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>74089421</v>
+        <v>41046849</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0.999807</v>
+        <v>0.999559</v>
       </c>
       <c r="K39" t="n">
-        <v>0.0001641</v>
+        <v>-0.000162931911100284</v>
       </c>
       <c r="L39" t="n">
-        <v>0.02013</v>
+        <v>-0.01629</v>
       </c>
       <c r="M39" t="n">
-        <v>2802658207.994529</v>
+        <v>2802363980.256867</v>
       </c>
       <c r="N39" t="n">
-        <v>2802658207.994529</v>
+        <v>2802363980.256867</v>
       </c>
       <c r="O39" t="n">
         <v>1.021</v>
@@ -3054,19 +3054,19 @@
         <v>45222.61454861111</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001358276072790742</v>
+        <v>0.001376932579068689</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3085,28 +3085,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4373.64</v>
+        <v>4368.6</v>
       </c>
       <c r="F40" t="n">
-        <v>2724008200</v>
+        <v>2720877354</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>129160606</v>
+        <v>66174544</v>
       </c>
       <c r="I40" t="n">
-        <v>4392.89</v>
+        <v>4376.12</v>
       </c>
       <c r="J40" t="n">
-        <v>4345.82</v>
+        <v>4365.59</v>
       </c>
       <c r="K40" t="n">
-        <v>6.84</v>
+        <v>-4.785671587365869</v>
       </c>
       <c r="L40" t="n">
-        <v>0.19182</v>
+        <v>-0.10943</v>
       </c>
       <c r="M40" t="n">
         <v>622823.6595320001</v>
@@ -3121,153 +3121,153 @@
         <v>46050.66666666666</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001310241984084195</v>
+        <v>0.001326827350470617</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>okb</t>
+          <t>hashnote-usyc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>okb</t>
+          <t>usyc</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>OKB</t>
+          <t>Circle USYC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>121.74</v>
+        <v>1.14</v>
       </c>
       <c r="F41" t="n">
-        <v>2556533363</v>
+        <v>2508311923</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
       </c>
       <c r="H41" t="n">
-        <v>53843878</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>122.95</v>
+        <v>1.14</v>
       </c>
       <c r="J41" t="n">
-        <v>115.02</v>
+        <v>1.14</v>
       </c>
       <c r="K41" t="n">
-        <v>7.64</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>6.70177</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>21000000</v>
+        <v>2204386896.824222</v>
       </c>
       <c r="N41" t="n">
-        <v>21000000</v>
+        <v>2204386896.824222</v>
       </c>
       <c r="O41" t="n">
-        <v>228.74</v>
+        <v>1.14</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>45934.66666666666</v>
+        <v>46283.52430555555</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001207654179494486</v>
+        <v>0.001195318577043226</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>hashnote-usyc</t>
+          <t>okb</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>usyc</t>
+          <t>okb</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Circle USYC</t>
+          <t>OKB</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1.14</v>
+        <v>116.02</v>
       </c>
       <c r="F42" t="n">
-        <v>2508311923</v>
+        <v>2435395117</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>33071122</v>
       </c>
       <c r="I42" t="n">
-        <v>1.14</v>
+        <v>121.32</v>
       </c>
       <c r="J42" t="n">
-        <v>1.14</v>
+        <v>114.58</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>-4.302428166146768</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>-3.57589</v>
       </c>
       <c r="M42" t="n">
-        <v>2204386896.824222</v>
+        <v>21000000</v>
       </c>
       <c r="N42" t="n">
-        <v>2204386896.824222</v>
+        <v>21000000</v>
       </c>
       <c r="O42" t="n">
-        <v>1.14</v>
+        <v>228.74</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>46283.52430555555</v>
+        <v>45934.66666666666</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001178115821658947</v>
+        <v>0.001150206821692456</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3286,34 +3286,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0.999946</v>
       </c>
       <c r="F43" t="n">
-        <v>2379074812</v>
+        <v>2378965485</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>115946978</v>
+        <v>194923335</v>
       </c>
       <c r="I43" t="n">
         <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>0.999839</v>
+        <v>0.999656</v>
       </c>
       <c r="K43" t="n">
-        <v>9.816e-05</v>
+        <v>-5.4896245646363e-05</v>
       </c>
       <c r="L43" t="n">
-        <v>0.01142</v>
+        <v>-0.00549</v>
       </c>
       <c r="M43" t="n">
-        <v>2378997051.087129</v>
+        <v>2378997051.087201</v>
       </c>
       <c r="N43" t="n">
-        <v>2378997051.087127</v>
+        <v>2378997051.0872</v>
       </c>
       <c r="O43" t="n">
         <v>1.073</v>
@@ -3322,19 +3322,19 @@
         <v>45652.11518518518</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001098950785725779</v>
+        <v>0.001115295257500821</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3371,7 +3371,7 @@
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>1.11e-16</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -3380,7 +3380,7 @@
         <v>2329036630.620448</v>
       </c>
       <c r="N44" t="n">
-        <v>2329036630.620449</v>
+        <v>2329036630.620448</v>
       </c>
       <c r="O44" t="n">
         <v>1</v>
@@ -3389,19 +3389,19 @@
         <v>45699.87511574074</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001068299571331986</v>
+        <v>0.001084405557716216</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3420,34 +3420,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="F45" t="n">
-        <v>2250644223</v>
+        <v>2250160386</v>
       </c>
       <c r="G45" t="n">
         <v>44</v>
       </c>
       <c r="H45" t="n">
-        <v>1401621</v>
+        <v>3272478</v>
       </c>
       <c r="I45" t="n">
         <v>1.15</v>
       </c>
       <c r="J45" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="K45" t="n">
-        <v>0.00257079</v>
+        <v>-0.006108838413215967</v>
       </c>
       <c r="L45" t="n">
-        <v>0.28132</v>
+        <v>-0.53277</v>
       </c>
       <c r="M45" t="n">
-        <v>1963196048.466981</v>
+        <v>1963184587.959249</v>
       </c>
       <c r="N45" t="n">
-        <v>1963196048.46698</v>
+        <v>1963184587.959249</v>
       </c>
       <c r="O45" t="n">
         <v>1.26</v>
@@ -3456,19 +3456,19 @@
         <v>45377.89175925926</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.00102027979010825</v>
+        <v>0.001035606850495998</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3487,31 +3487,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>142.5</v>
+        <v>133.96</v>
       </c>
       <c r="F46" t="n">
-        <v>2198543761</v>
+        <v>2066513911</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>357964281</v>
+        <v>213181350</v>
       </c>
       <c r="I46" t="n">
-        <v>146.6</v>
+        <v>143.81</v>
       </c>
       <c r="J46" t="n">
-        <v>136.91</v>
+        <v>134.25</v>
       </c>
       <c r="K46" t="n">
-        <v>5.1</v>
+        <v>-8.328760258624357</v>
       </c>
       <c r="L46" t="n">
-        <v>3.66088</v>
+        <v>-5.85334</v>
       </c>
       <c r="M46" t="n">
-        <v>15428034.66896128</v>
+        <v>15428127.9033128</v>
       </c>
       <c r="N46" t="n">
         <v>16000000</v>
@@ -3523,86 +3523,86 @@
         <v>44334.55554398148</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
-        <v>0.00098836531202645</v>
+        <v>0.0009219894924999367</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>aster-2</t>
+          <t>ethena</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>aster</t>
+          <t>ena</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Ethena</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.768416</v>
+        <v>0.20318</v>
       </c>
       <c r="F47" t="n">
-        <v>2077850549</v>
+        <v>2052220482</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>144253256</v>
+        <v>802946485</v>
       </c>
       <c r="I47" t="n">
-        <v>0.790454</v>
+        <v>0.219782</v>
       </c>
       <c r="J47" t="n">
-        <v>0.743399</v>
+        <v>0.190993</v>
       </c>
       <c r="K47" t="n">
-        <v>0.01797252</v>
+        <v>0.00551982</v>
       </c>
       <c r="L47" t="n">
-        <v>2.42583</v>
+        <v>2.79258</v>
       </c>
       <c r="M47" t="n">
-        <v>2704071066.799731</v>
+        <v>10095312500</v>
       </c>
       <c r="N47" t="n">
-        <v>7799908028.130118</v>
+        <v>15000000000</v>
       </c>
       <c r="O47" t="n">
-        <v>2.41</v>
+        <v>1.52</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>45924.13766203704</v>
+        <v>45393.21892361111</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0009144338971956932</v>
+        <v>0.0009131465150363928</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3621,28 +3621,28 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.425945</v>
+        <v>0.409013</v>
       </c>
       <c r="F48" t="n">
-        <v>2074065760</v>
+        <v>1991023913</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>233956955</v>
+        <v>214027943</v>
       </c>
       <c r="I48" t="n">
-        <v>0.41497</v>
+        <v>0.441448</v>
       </c>
       <c r="J48" t="n">
-        <v>0.392623</v>
+        <v>0.401798</v>
       </c>
       <c r="K48" t="n">
-        <v>0.03092754</v>
+        <v>-0.01473807119701176</v>
       </c>
       <c r="L48" t="n">
-        <v>7.91917</v>
+        <v>-3.478</v>
       </c>
       <c r="M48" t="n">
         <v>4869330647</v>
@@ -3657,957 +3657,957 @@
         <v>45641.69166666667</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0009121154999886831</v>
+        <v>0.0008752857693389669</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>mantle</t>
+          <t>aster-2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>mnt</t>
+          <t>aster</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mantle</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.623375</v>
+        <v>0.728447</v>
       </c>
       <c r="F49" t="n">
-        <v>2058567278</v>
+        <v>1969587215</v>
       </c>
       <c r="G49" t="n">
         <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>36418018</v>
+        <v>143403554</v>
       </c>
       <c r="I49" t="n">
-        <v>0.630436</v>
+        <v>0.770739</v>
       </c>
       <c r="J49" t="n">
-        <v>0.593005</v>
+        <v>0.72988</v>
       </c>
       <c r="K49" t="n">
-        <v>0.03647781</v>
+        <v>-0.03539861755666773</v>
       </c>
       <c r="L49" t="n">
-        <v>6.24446</v>
+        <v>-4.63427</v>
       </c>
       <c r="M49" t="n">
-        <v>3302294382.53684</v>
+        <v>2704071066.799731</v>
       </c>
       <c r="N49" t="n">
-        <v>6219316794.889999</v>
+        <v>7799908028.129959</v>
       </c>
       <c r="O49" t="n">
-        <v>2.86</v>
+        <v>2.41</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>45938.71164351852</v>
+        <v>45924.13766203704</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R49" t="b">
         <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0009026218036738561</v>
+        <v>0.0008620234347860199</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ethena</t>
+          <t>mantle</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ena</t>
+          <t>mnt</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ethena</t>
+          <t>Mantle</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.196643</v>
+        <v>0.594839</v>
       </c>
       <c r="F50" t="n">
-        <v>1985168612</v>
+        <v>1964424504</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>722630593</v>
+        <v>34962814</v>
       </c>
       <c r="I50" t="n">
-        <v>0.195173</v>
+        <v>0.644878</v>
       </c>
       <c r="J50" t="n">
-        <v>0.162775</v>
+        <v>0.585395</v>
       </c>
       <c r="K50" t="n">
-        <v>0.03399471</v>
+        <v>-0.03131049210115233</v>
       </c>
       <c r="L50" t="n">
-        <v>21.00862</v>
+        <v>-5.00048</v>
       </c>
       <c r="M50" t="n">
-        <v>10095312500</v>
+        <v>3302294382.53684</v>
       </c>
       <c r="N50" t="n">
-        <v>15000000000</v>
+        <v>6219316794.889999</v>
       </c>
       <c r="O50" t="n">
-        <v>1.52</v>
+        <v>2.86</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>45393.21892361111</v>
+        <v>45938.71164351852</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R50" t="b">
         <v>1</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0008576609717086736</v>
+        <v>0.0008588293980700023</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>pax-gold</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>paxg</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>PAX Gold</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.00414921</v>
+        <v>4359.57</v>
       </c>
       <c r="F51" t="n">
-        <v>1940424994</v>
+        <v>1894234710</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>148386496</v>
+        <v>58008894</v>
       </c>
       <c r="I51" t="n">
-        <v>0.00444095</v>
+        <v>4367.08</v>
       </c>
       <c r="J51" t="n">
-        <v>0.00405448</v>
+        <v>4358.71</v>
       </c>
       <c r="K51" t="n">
-        <v>-6.7927667411628e-05</v>
+        <v>-6.34483767065467</v>
       </c>
       <c r="L51" t="n">
-        <v>-1.57295</v>
+        <v>-0.14533</v>
       </c>
       <c r="M51" t="n">
-        <v>467661147593.8102</v>
+        <v>434499.367539</v>
       </c>
       <c r="N51" t="n">
-        <v>833163604241.7463</v>
+        <v>434499.367539</v>
       </c>
       <c r="O51" t="n">
-        <v>0.00881908</v>
+        <v>5619.09</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>45914.36296296296</v>
+        <v>46050.93814814815</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R51" t="b">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0008302529764405808</v>
+        <v>0.0008154047750132962</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>polkadot</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>dot</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1.13</v>
+        <v>0.00404864</v>
       </c>
       <c r="F52" t="n">
-        <v>1929873645</v>
+        <v>1893132177</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>204374902</v>
+        <v>127290135</v>
       </c>
       <c r="I52" t="n">
-        <v>1.16</v>
+        <v>0.00426634</v>
       </c>
       <c r="J52" t="n">
-        <v>1.1</v>
+        <v>0.00391748</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.008683841196597264</v>
+        <v>-9.0381777523358e-05</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.75322</v>
+        <v>-2.18365</v>
       </c>
       <c r="M52" t="n">
-        <v>1703483485.668379</v>
+        <v>467477309368.556</v>
       </c>
       <c r="N52" t="n">
-        <v>1703489020.963728</v>
+        <v>832984570267.5187</v>
       </c>
       <c r="O52" t="n">
-        <v>54.98</v>
+        <v>0.00881908</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>44504.25704861111</v>
+        <v>45914.36296296296</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R52" t="b">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0008237896787371185</v>
+        <v>0.0008147226661595135</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>polkadot</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>dot</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Morpho</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2.73</v>
+        <v>1.095</v>
       </c>
       <c r="F53" t="n">
-        <v>1906683134</v>
+        <v>1865994513</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>68936984</v>
+        <v>176284533</v>
       </c>
       <c r="I53" t="n">
-        <v>2.81</v>
+        <v>1.14</v>
       </c>
       <c r="J53" t="n">
-        <v>2.38</v>
+        <v>1.073</v>
       </c>
       <c r="K53" t="n">
-        <v>0.297117</v>
+        <v>-0.03251862337215128</v>
       </c>
       <c r="L53" t="n">
-        <v>12.06161</v>
+        <v>-2.88381</v>
       </c>
       <c r="M53" t="n">
-        <v>698862182.2199675</v>
+        <v>1703621352.353134</v>
       </c>
       <c r="N53" t="n">
-        <v>1000000000</v>
+        <v>1703649304.443802</v>
       </c>
       <c r="O53" t="n">
-        <v>4.17</v>
+        <v>54.98</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>45674.19883101852</v>
+        <v>44504.25704861111</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0008095841798489273</v>
+        <v>0.000797933290344569</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>pax-gold</t>
+          <t>world-liberty-financial</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>paxg</t>
+          <t>wlfi</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>PAX Gold</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4366.16</v>
+        <v>0.058161</v>
       </c>
       <c r="F54" t="n">
-        <v>1897094993</v>
+        <v>1848511633</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>111719882</v>
+        <v>28571333</v>
       </c>
       <c r="I54" t="n">
-        <v>4388.3</v>
+        <v>0.059403</v>
       </c>
       <c r="J54" t="n">
-        <v>4341.8</v>
+        <v>0.05732</v>
       </c>
       <c r="K54" t="n">
-        <v>2.26</v>
+        <v>-0.00089482964559788</v>
       </c>
       <c r="L54" t="n">
-        <v>0.08689</v>
+        <v>-1.51522</v>
       </c>
       <c r="M54" t="n">
-        <v>434499.367539</v>
+        <v>31777404701</v>
       </c>
       <c r="N54" t="n">
-        <v>434499.367539</v>
+        <v>100000000000</v>
       </c>
       <c r="O54" t="n">
-        <v>5619.09</v>
+        <v>0.331336</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>46050.93814814815</v>
+        <v>45901.18065972222</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R54" t="b">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.000803710901493167</v>
+        <v>0.0007871170814532076</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>world-liberty-financial</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>wlfi</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>World Liberty Financial</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.058953</v>
+        <v>0.664219</v>
       </c>
       <c r="F55" t="n">
-        <v>1873382921</v>
+        <v>1778401615</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>33080034</v>
+        <v>15397948</v>
       </c>
       <c r="I55" t="n">
-        <v>0.059313</v>
+        <v>0.830167</v>
       </c>
       <c r="J55" t="n">
-        <v>0.058131</v>
+        <v>0.5676020000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>0.00114767</v>
+        <v>0.088199</v>
       </c>
       <c r="L55" t="n">
-        <v>1.97488</v>
+        <v>15.31172</v>
       </c>
       <c r="M55" t="n">
-        <v>31777393281</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N55" t="n">
-        <v>100000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O55" t="n">
-        <v>0.331336</v>
+        <v>0.830167</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>45901.18065972222</v>
+        <v>46285.43854166667</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S55" t="n">
-        <v>0.000789185917009957</v>
+        <v>0.0007437418137590344</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sky</t>
+          <t>Morpho</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.069615</v>
+        <v>2.49</v>
       </c>
       <c r="F56" t="n">
-        <v>1630341007</v>
+        <v>1742127600</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>38229096</v>
+        <v>27816998</v>
       </c>
       <c r="I56" t="n">
-        <v>0.07199999999999999</v>
+        <v>2.74</v>
       </c>
       <c r="J56" t="n">
-        <v>0.066331</v>
+        <v>2.48</v>
       </c>
       <c r="K56" t="n">
-        <v>0.00438045</v>
+        <v>-0.2377347840652968</v>
       </c>
       <c r="L56" t="n">
-        <v>6.7081</v>
+        <v>-8.70748</v>
       </c>
       <c r="M56" t="n">
-        <v>23419267381.19225</v>
+        <v>698911943.4172602</v>
       </c>
       <c r="N56" t="n">
-        <v>23459804203.60596</v>
+        <v>1000000000</v>
       </c>
       <c r="O56" t="n">
-        <v>0.100535</v>
+        <v>4.17</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>45630.09302083333</v>
+        <v>45674.19883101852</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R56" t="b">
         <v>1</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0006403090061427982</v>
+        <v>0.0007213000122041203</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>internet-computer</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>icp</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Internet Computer</t>
+          <t>Pepe</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2.9</v>
+        <v>3.96e-06</v>
       </c>
       <c r="F57" t="n">
-        <v>1614934309</v>
+        <v>1667708170</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>55661757</v>
+        <v>530426959</v>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>4.31e-06</v>
       </c>
       <c r="J57" t="n">
-        <v>2.8</v>
+        <v>3.8e-06</v>
       </c>
       <c r="K57" t="n">
-        <v>0.085447</v>
+        <v>1.55684e-07</v>
       </c>
       <c r="L57" t="n">
-        <v>3.01852</v>
+        <v>4.08743</v>
       </c>
       <c r="M57" t="n">
-        <v>556901197.5075812</v>
+        <v>420690000000000</v>
       </c>
       <c r="N57" t="n">
-        <v>556904308.555163</v>
+        <v>420690000000000</v>
       </c>
       <c r="O57" t="n">
-        <v>700.65</v>
+        <v>2.803e-05</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>44326.33741898148</v>
+        <v>45635.35457175926</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R57" t="b">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0006308715327162877</v>
+        <v>0.0006752586219723022</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Pepe</t>
+          <t>Sky</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3.82e-06</v>
+        <v>0.068407</v>
       </c>
       <c r="F58" t="n">
-        <v>1605881714</v>
+        <v>1602711159</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>312140947</v>
+        <v>11164701</v>
       </c>
       <c r="I58" t="n">
-        <v>3.89e-06</v>
+        <v>0.070019</v>
       </c>
       <c r="J58" t="n">
-        <v>3.72e-06</v>
+        <v>0.067327</v>
       </c>
       <c r="K58" t="n">
-        <v>1.22452e-07</v>
+        <v>-0.000703844532935427</v>
       </c>
       <c r="L58" t="n">
-        <v>3.36713</v>
+        <v>-1.01843</v>
       </c>
       <c r="M58" t="n">
-        <v>420690000000000</v>
+        <v>23428622590.8406</v>
       </c>
       <c r="N58" t="n">
-        <v>420690000000000</v>
+        <v>23459804203.60596</v>
       </c>
       <c r="O58" t="n">
-        <v>2.803e-05</v>
+        <v>0.100535</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>45635.35457175926</v>
+        <v>45630.09302083333</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0006253263065585827</v>
+        <v>0.0006350466404057575</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>htx-dao</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>htx</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>HTX DAO</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.5788450000000001</v>
+        <v>1.71e-06</v>
       </c>
       <c r="F59" t="n">
-        <v>1567594246</v>
+        <v>1539312839</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>8439074</v>
+        <v>5564147</v>
       </c>
       <c r="I59" t="n">
-        <v>0.690213</v>
+        <v>1.72e-06</v>
       </c>
       <c r="J59" t="n">
-        <v>0.585388</v>
+        <v>1.7e-06</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.09388214689214247</v>
+        <v>9.069999999999999e-09</v>
       </c>
       <c r="L59" t="n">
-        <v>-13.96584</v>
+        <v>0.53218</v>
       </c>
       <c r="M59" t="n">
-        <v>2708142280.000001</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="N59" t="n">
-        <v>10000000000</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="O59" t="n">
-        <v>0.789172</v>
+        <v>3.75e-06</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>46281.50775462963</v>
+        <v>45629.67800925926</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0006018730681152532</v>
+        <v>0.0005958237279061364</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>worldcoin-wld</t>
+          <t>internet-computer</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>wld</t>
+          <t>icp</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Worldcoin</t>
+          <t>Internet Computer</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.432174</v>
+        <v>2.76</v>
       </c>
       <c r="F60" t="n">
-        <v>1555853308</v>
+        <v>1535872586</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>228977249</v>
+        <v>55899817</v>
       </c>
       <c r="I60" t="n">
-        <v>0.43735</v>
+        <v>2.97</v>
       </c>
       <c r="J60" t="n">
-        <v>0.413067</v>
+        <v>2.74</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.007900419231261557</v>
+        <v>-0.1079435132927644</v>
       </c>
       <c r="L60" t="n">
-        <v>-1.67455</v>
+        <v>-3.76626</v>
       </c>
       <c r="M60" t="n">
-        <v>3600061882.051912</v>
+        <v>556905075.050398</v>
       </c>
       <c r="N60" t="n">
-        <v>10000000000</v>
+        <v>556905520.6385173</v>
       </c>
       <c r="O60" t="n">
-        <v>11.74</v>
+        <v>700.65</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>45360.67409722223</v>
+        <v>44326.33741898148</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0005946810799048459</v>
+        <v>0.0005936953317215757</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>htx-dao</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>htx</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>HTX DAO</t>
+          <t>USDD</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1.7e-06</v>
+        <v>0.998409</v>
       </c>
       <c r="F61" t="n">
-        <v>1530245421</v>
+        <v>1530501563</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>3198616</v>
+        <v>1710078</v>
       </c>
       <c r="I61" t="n">
-        <v>1.71e-06</v>
+        <v>0.999278</v>
       </c>
       <c r="J61" t="n">
-        <v>1.68e-06</v>
+        <v>0.997703</v>
       </c>
       <c r="K61" t="n">
-        <v>2.4968e-08</v>
+        <v>0.0003523</v>
       </c>
       <c r="L61" t="n">
-        <v>1.47629</v>
+        <v>0.0353</v>
       </c>
       <c r="M61" t="n">
-        <v>898232728634017.2</v>
+        <v>1532863245</v>
       </c>
       <c r="N61" t="n">
-        <v>898232728634017.2</v>
+        <v>1534240769</v>
       </c>
       <c r="O61" t="n">
-        <v>3.75e-06</v>
+        <v>1.24</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>45629.67800925926</v>
+        <v>46212.39942129629</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0005789948015685286</v>
+        <v>0.0005903724177206613</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>worldcoin-wld</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>wld</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>USDD</t>
+          <t>Worldcoin</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.99799</v>
+        <v>0.418505</v>
       </c>
       <c r="F62" t="n">
-        <v>1526947830</v>
+        <v>1506775772</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>3657552</v>
+        <v>179127352</v>
       </c>
       <c r="I62" t="n">
-        <v>0.999088</v>
+        <v>0.440425</v>
       </c>
       <c r="J62" t="n">
-        <v>0.997081</v>
+        <v>0.417599</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.00045256413609529</v>
+        <v>-0.009340951957156951</v>
       </c>
       <c r="L62" t="n">
-        <v>-0.04467</v>
+        <v>-2.18325</v>
       </c>
       <c r="M62" t="n">
-        <v>1530023428</v>
+        <v>3601490383.124579</v>
       </c>
       <c r="N62" t="n">
-        <v>1531219537</v>
+        <v>10000000000</v>
       </c>
       <c r="O62" t="n">
-        <v>1.24</v>
+        <v>11.74</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>46212.39942129629</v>
+        <v>45360.67409722223</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005769748406765841</v>
+        <v>0.0005756938801130827</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4626,28 +4626,28 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.21076</v>
+        <v>0.208887</v>
       </c>
       <c r="F63" t="n">
-        <v>1430127833</v>
+        <v>1417030807</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>481398830</v>
+        <v>333916946</v>
       </c>
       <c r="I63" t="n">
-        <v>0.227783</v>
+        <v>0.218059</v>
       </c>
       <c r="J63" t="n">
-        <v>0.205551</v>
+        <v>0.20086</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.000670181396933006</v>
+        <v>0.00031019</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.48827</v>
+        <v>0.14872</v>
       </c>
       <c r="M63" t="n">
         <v>6785574605</v>
@@ -4662,287 +4662,287 @@
         <v>45303.18748842592</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0005176671195255418</v>
+        <v>0.0005201709749402556</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>bitget-token</t>
+          <t>spiko-amundi-overnight-swap-fund-eur</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>bgb</t>
+          <t>eursafo</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Bitget Token</t>
+          <t>Spiko Amundi Overnight Swap Fund (EUR)</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2.03</v>
+        <v>1.16</v>
       </c>
       <c r="F64" t="n">
-        <v>1420581991</v>
+        <v>1407771011</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>15072621</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>2.03</v>
+        <v>1.16</v>
       </c>
       <c r="J64" t="n">
-        <v>1.96</v>
+        <v>1.16</v>
       </c>
       <c r="K64" t="n">
-        <v>0.057695</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>2.94211</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>699992029.6481038</v>
+        <v>1210660472.36437</v>
       </c>
       <c r="N64" t="n">
-        <v>910920874.6481038</v>
+        <v>1210660472.36437</v>
       </c>
       <c r="O64" t="n">
-        <v>8.449999999999999</v>
+        <v>1.18</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>45653.15375</v>
+        <v>46255.48263888889</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R64" t="b">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0005118197516983366</v>
+        <v>0.0005144421769488839</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>spiko-amundi-overnight-swap-fund-eur</t>
+          <t>bitget-token</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>eursafo</t>
+          <t>bgb</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Spiko Amundi Overnight Swap Fund (EUR)</t>
+          <t>Bitget Token</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1.16</v>
+        <v>1.99</v>
       </c>
       <c r="F65" t="n">
-        <v>1407771011</v>
+        <v>1393178318</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>10302086</v>
       </c>
       <c r="I65" t="n">
-        <v>1.16</v>
+        <v>2.06</v>
       </c>
       <c r="J65" t="n">
-        <v>1.16</v>
+        <v>1.97</v>
       </c>
       <c r="K65" t="n">
-        <v>0.0015034</v>
+        <v>-0.04851798921705774</v>
       </c>
       <c r="L65" t="n">
-        <v>0.12946</v>
+        <v>-2.37987</v>
       </c>
       <c r="M65" t="n">
-        <v>1210660472.36437</v>
+        <v>699992029.6481038</v>
       </c>
       <c r="N65" t="n">
-        <v>1210660472.36437</v>
+        <v>910920874.6481038</v>
       </c>
       <c r="O65" t="n">
-        <v>1.18</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>46255.48263888889</v>
+        <v>45653.15375</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0005039723022761725</v>
+        <v>0.0005054140525337128</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>akedo</t>
+          <t>united-stables</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ake</t>
+          <t>u</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Akedo</t>
+          <t>United Stables</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.061588</v>
+        <v>0.999777</v>
       </c>
       <c r="F66" t="n">
-        <v>1403973963</v>
+        <v>1392856034</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
       </c>
       <c r="H66" t="n">
-        <v>221768120</v>
+        <v>99747718</v>
       </c>
       <c r="I66" t="n">
-        <v>0.06482300000000001</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
-        <v>0.02575841</v>
+        <v>0.999536</v>
       </c>
       <c r="K66" t="n">
-        <v>0.03530292</v>
+        <v>-0.000133328224996121</v>
       </c>
       <c r="L66" t="n">
-        <v>134.28414</v>
+        <v>-0.01333</v>
       </c>
       <c r="M66" t="n">
-        <v>22796250000</v>
+        <v>1393129007.8</v>
       </c>
       <c r="N66" t="n">
-        <v>100000000000</v>
+        <v>1393129007.8</v>
       </c>
       <c r="O66" t="n">
-        <v>0.06482300000000001</v>
+        <v>1.008</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>46284.43101851852</v>
+        <v>46058.54591435185</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0005016463957386922</v>
+        <v>0.0005052146636992448</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>united-stables</t>
+          <t>venice-token</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>vvv</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>United Stables</t>
+          <t>Venice Token</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>28.99</v>
       </c>
       <c r="F67" t="n">
-        <v>1393129534</v>
+        <v>1390249492</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
       </c>
       <c r="H67" t="n">
-        <v>157171689</v>
+        <v>78077222</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>29.87</v>
       </c>
       <c r="J67" t="n">
-        <v>0.999493</v>
+        <v>25.03</v>
       </c>
       <c r="K67" t="n">
-        <v>0.00055459</v>
+        <v>0.981791</v>
       </c>
       <c r="L67" t="n">
-        <v>0.04974</v>
+        <v>3.50519</v>
       </c>
       <c r="M67" t="n">
-        <v>1393129007.8</v>
+        <v>48066966.41405931</v>
       </c>
       <c r="N67" t="n">
-        <v>1393129007.8</v>
+        <v>81013661.93979919</v>
       </c>
       <c r="O67" t="n">
-        <v>1.008</v>
+        <v>29.87</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>46058.54591435185</v>
+        <v>46285.54143518519</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0004950035699681618</v>
+        <v>0.0005036020631004815</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4961,28 +4961,28 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>0.999987</v>
       </c>
       <c r="F68" t="n">
-        <v>1383948752</v>
+        <v>1383803613</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>33059541</v>
+        <v>54160877</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>1.001</v>
       </c>
       <c r="J68" t="n">
-        <v>0.999566</v>
+        <v>0.999735</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.000179455571939435</v>
+        <v>-0.000121582571536494</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.02022</v>
+        <v>-0.01216</v>
       </c>
       <c r="M68" t="n">
         <v>1383787304.97</v>
@@ -4997,19 +4997,19 @@
         <v>46092.00303240741</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0004893798220268712</v>
+        <v>0.0004996141632949323</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5028,34 +5028,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.995613</v>
+        <v>0.995828</v>
       </c>
       <c r="F69" t="n">
-        <v>1371004229</v>
+        <v>1371297189</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>515832</v>
+        <v>539321</v>
       </c>
       <c r="I69" t="n">
-        <v>0.996291</v>
+        <v>0.996548</v>
       </c>
       <c r="J69" t="n">
-        <v>0.995053</v>
+        <v>0.994584</v>
       </c>
       <c r="K69" t="n">
-        <v>2.866e-05</v>
+        <v>0.00021359</v>
       </c>
       <c r="L69" t="n">
-        <v>0.0034</v>
+        <v>0.02145</v>
       </c>
       <c r="M69" t="n">
-        <v>1377045504.45504</v>
+        <v>1377031442.049245</v>
       </c>
       <c r="N69" t="n">
-        <v>1377045504.45504</v>
+        <v>1377031442.049245</v>
       </c>
       <c r="O69" t="n">
         <v>1.075</v>
@@ -5064,220 +5064,220 @@
         <v>45785.55951388889</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0004814505699683605</v>
+        <v>0.0004918767599341624</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ethereum-classic</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Ethereum Classic</t>
+          <t>BFUSD</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>8.470000000000001</v>
+        <v>0.999651</v>
       </c>
       <c r="F70" t="n">
-        <v>1340644126</v>
+        <v>1319550427</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>79617319</v>
+        <v>7639533</v>
       </c>
       <c r="I70" t="n">
-        <v>8.59</v>
+        <v>0.999769</v>
       </c>
       <c r="J70" t="n">
-        <v>7.97</v>
+        <v>0.999301</v>
       </c>
       <c r="K70" t="n">
-        <v>0.503223</v>
+        <v>-5.9185672644402e-05</v>
       </c>
       <c r="L70" t="n">
-        <v>6.49692</v>
+        <v>-0.00592</v>
       </c>
       <c r="M70" t="n">
-        <v>158215665.2670572</v>
+        <v>1320000000</v>
       </c>
       <c r="N70" t="n">
-        <v>158216963.8921894</v>
+        <v>1320000000</v>
       </c>
       <c r="O70" t="n">
-        <v>167.09</v>
+        <v>1.007</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>44322.44053240741</v>
+        <v>45940.56990740741</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0004628532907013417</v>
+        <v>0.0004598623671542794</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>venice-token</t>
+          <t>ethereum-classic</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>vvv</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Venice Token</t>
+          <t>Ethereum Classic</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>27.88</v>
+        <v>8.25</v>
       </c>
       <c r="F71" t="n">
-        <v>1339871374</v>
+        <v>1305311435</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>96922668</v>
+        <v>75227585</v>
       </c>
       <c r="I71" t="n">
-        <v>29.44</v>
+        <v>8.77</v>
       </c>
       <c r="J71" t="n">
-        <v>25.99</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>1.86</v>
+        <v>-0.1553929350739427</v>
       </c>
       <c r="L71" t="n">
-        <v>7.14008</v>
+        <v>-1.84917</v>
       </c>
       <c r="M71" t="n">
-        <v>48053201.36919299</v>
+        <v>158226588.0989012</v>
       </c>
       <c r="N71" t="n">
-        <v>81007609.62721066</v>
+        <v>158227480.9245012</v>
       </c>
       <c r="O71" t="n">
-        <v>29.44</v>
+        <v>167.09</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>46284.10787037037</v>
+        <v>44322.44053240741</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0004623799364196337</v>
+        <v>0.00045105306846468</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>akedo</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>ake</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>BFUSD</t>
+          <t>Akedo</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9996</v>
+        <v>0.051878</v>
       </c>
       <c r="F72" t="n">
-        <v>1319471561</v>
+        <v>1181652254</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>1804515</v>
+        <v>138375486</v>
       </c>
       <c r="I72" t="n">
-        <v>0.999725</v>
+        <v>0.146656</v>
       </c>
       <c r="J72" t="n">
-        <v>0.998817</v>
+        <v>0.04596138</v>
       </c>
       <c r="K72" t="n">
-        <v>0.00093291</v>
+        <v>-0.01045600252542676</v>
       </c>
       <c r="L72" t="n">
-        <v>0.09393</v>
+        <v>-16.77405</v>
       </c>
       <c r="M72" t="n">
-        <v>1320000000</v>
+        <v>22796250000</v>
       </c>
       <c r="N72" t="n">
-        <v>1320000000</v>
+        <v>100000000000</v>
       </c>
       <c r="O72" t="n">
-        <v>1.007</v>
+        <v>0.146656</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>45940.56990740741</v>
+        <v>46285.43993055556</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0004498838978075131</v>
+        <v>0.0003745483087780226</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5296,28 +5296,28 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5.08</v>
+        <v>4.72</v>
       </c>
       <c r="F73" t="n">
-        <v>1270773372</v>
+        <v>1180283855</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>113532386</v>
+        <v>65144763</v>
       </c>
       <c r="I73" t="n">
-        <v>5.27</v>
+        <v>5.21</v>
       </c>
       <c r="J73" t="n">
-        <v>4.67</v>
+        <v>4.58</v>
       </c>
       <c r="K73" t="n">
-        <v>0.1814</v>
+        <v>-0.4150986854558916</v>
       </c>
       <c r="L73" t="n">
-        <v>3.74222</v>
+        <v>-8.082179999999999</v>
       </c>
       <c r="M73" t="n">
         <v>250000000</v>
@@ -5332,19 +5332,19 @@
         <v>46021.04538194444</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0004200535042600648</v>
+        <v>0.000373701715457544</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5363,34 +5363,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.104722</v>
+        <v>0.103521</v>
       </c>
       <c r="F74" t="n">
-        <v>1122307480</v>
+        <v>1109401167</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>127939160</v>
+        <v>67553877</v>
       </c>
       <c r="I74" t="n">
-        <v>0.109444</v>
+        <v>0.106841</v>
       </c>
       <c r="J74" t="n">
-        <v>0.100445</v>
+        <v>0.10307</v>
       </c>
       <c r="K74" t="n">
-        <v>0.00457585</v>
+        <v>-0.001922091538787959</v>
       </c>
       <c r="L74" t="n">
-        <v>4.60869</v>
+        <v>-1.82286</v>
       </c>
       <c r="M74" t="n">
-        <v>10717010654.78035</v>
+        <v>10717592108.82727</v>
       </c>
       <c r="N74" t="n">
-        <v>10717010654.78035</v>
+        <v>10717592108.82727</v>
       </c>
       <c r="O74" t="n">
         <v>1.29</v>
@@ -5399,19 +5399,19 @@
         <v>45364.45493055556</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R74" t="b">
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0003291097530102404</v>
+        <v>0.0003298484166767254</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5430,34 +5430,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>10.01</v>
+        <v>10.2</v>
       </c>
       <c r="F75" t="n">
-        <v>1067690542</v>
+        <v>1088646020</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
       </c>
       <c r="H75" t="n">
-        <v>3804156</v>
+        <v>3809198</v>
       </c>
       <c r="I75" t="n">
-        <v>10.21</v>
+        <v>10.64</v>
       </c>
       <c r="J75" t="n">
-        <v>9.85</v>
+        <v>10.06</v>
       </c>
       <c r="K75" t="n">
-        <v>0.136528</v>
+        <v>0.090124</v>
       </c>
       <c r="L75" t="n">
-        <v>1.31699</v>
+        <v>0.89158</v>
       </c>
       <c r="M75" t="n">
-        <v>106633446.0521377</v>
+        <v>106634608.2701089</v>
       </c>
       <c r="N75" t="n">
-        <v>118884734.5494255</v>
+        <v>118885881.9758941</v>
       </c>
       <c r="O75" t="n">
         <v>25.38</v>
@@ -5466,19 +5466,19 @@
         <v>45682.66666666666</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R75" t="b">
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0002956537911284428</v>
+        <v>0.0003170077402250818</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5497,34 +5497,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.03816901</v>
+        <v>0.03828229</v>
       </c>
       <c r="F76" t="n">
-        <v>1057608938</v>
+        <v>1060695698</v>
       </c>
       <c r="G76" t="n">
         <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>20064411</v>
+        <v>24304294</v>
       </c>
       <c r="I76" t="n">
-        <v>0.03895499</v>
+        <v>0.04084235</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03581762</v>
+        <v>0.0376825</v>
       </c>
       <c r="K76" t="n">
-        <v>0.00235444</v>
+        <v>-1.2627467712453e-05</v>
       </c>
       <c r="L76" t="n">
-        <v>6.5786</v>
+        <v>-0.03297</v>
       </c>
       <c r="M76" t="n">
-        <v>27708574135.96641</v>
+        <v>27710766029.85906</v>
       </c>
       <c r="N76" t="n">
-        <v>27709298793.27851</v>
+        <v>27711234792.36683</v>
       </c>
       <c r="O76" t="n">
         <v>0.207411</v>
@@ -5533,19 +5533,19 @@
         <v>45504.69498842592</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0002894782387909723</v>
+        <v>0.0002997155937747936</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5564,28 +5564,28 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>7.28</v>
+        <v>7.12</v>
       </c>
       <c r="F77" t="n">
-        <v>998107368</v>
+        <v>977040628</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>10265485</v>
+        <v>22842987</v>
       </c>
       <c r="I77" t="n">
-        <v>7.32</v>
+        <v>7.28</v>
       </c>
       <c r="J77" t="n">
-        <v>7.12</v>
+        <v>7.1</v>
       </c>
       <c r="K77" t="n">
-        <v>0.091711</v>
+        <v>-0.145397866042674</v>
       </c>
       <c r="L77" t="n">
-        <v>1.27165</v>
+        <v>-2.00022</v>
       </c>
       <c r="M77" t="n">
         <v>137155021.2773955</v>
@@ -5600,19 +5600,19 @@
         <v>44531.29832175926</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R77" t="b">
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002530301636933329</v>
+        <v>0.0002479603502484719</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5649,7 +5649,7 @@
         <v>106.54</v>
       </c>
       <c r="K78" t="n">
-        <v>1.4211e-14</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -5667,19 +5667,19 @@
         <v>46280.14583333334</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R78" t="b">
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002363054948455781</v>
+        <v>0.0002441020979773476</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5698,34 +5698,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.085049</v>
+        <v>0.084915</v>
       </c>
       <c r="F79" t="n">
-        <v>956203211</v>
+        <v>954699581</v>
       </c>
       <c r="G79" t="n">
         <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>7267165</v>
+        <v>4483170</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0868</v>
+        <v>0.08533300000000001</v>
       </c>
       <c r="J79" t="n">
-        <v>0.08384800000000001</v>
+        <v>0.083199</v>
       </c>
       <c r="K79" t="n">
-        <v>0.00175985</v>
+        <v>-1.5620016221421e-05</v>
       </c>
       <c r="L79" t="n">
-        <v>2.13146</v>
+        <v>-0.01839</v>
       </c>
       <c r="M79" t="n">
-        <v>11243018943.001</v>
+        <v>11243020014.141</v>
       </c>
       <c r="N79" t="n">
-        <v>17296952220.00153</v>
+        <v>17296953741.26307</v>
       </c>
       <c r="O79" t="n">
         <v>2.99</v>
@@ -5734,488 +5734,488 @@
         <v>45714.36184027778</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R79" t="b">
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002273614987952593</v>
+        <v>0.0002341385181931284</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>just</t>
+          <t>algorand</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>jst</t>
+          <t>algo</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>JUST</t>
+          <t>Algorand</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.116103</v>
+        <v>0.1055</v>
       </c>
       <c r="F80" t="n">
-        <v>950736359</v>
+        <v>954315578</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>24202971</v>
+        <v>78112732</v>
       </c>
       <c r="I80" t="n">
-        <v>0.118694</v>
+        <v>0.110094</v>
       </c>
       <c r="J80" t="n">
-        <v>0.112293</v>
+        <v>0.09980700000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>-0.002184845546124511</v>
+        <v>0.00589527</v>
       </c>
       <c r="L80" t="n">
-        <v>-1.8513</v>
+        <v>5.91868</v>
       </c>
       <c r="M80" t="n">
-        <v>8188743036.341737</v>
+        <v>9042435038.282944</v>
       </c>
       <c r="N80" t="n">
-        <v>8188743036.341737</v>
+        <v>9042480349.856657</v>
       </c>
       <c r="O80" t="n">
-        <v>0.193254</v>
+        <v>3.56</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>44290.85721064815</v>
+        <v>43636.28563657407</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002240127429179995</v>
+        <v>0.0002339009453983194</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>quant-network</t>
+          <t>just</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>qnt</t>
+          <t>jst</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>JUST</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>65.23</v>
+        <v>0.114254</v>
       </c>
       <c r="F81" t="n">
-        <v>948734831</v>
+        <v>935643444</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>9168942</v>
+        <v>29647707</v>
       </c>
       <c r="I81" t="n">
-        <v>65.29000000000001</v>
+        <v>0.118997</v>
       </c>
       <c r="J81" t="n">
-        <v>63.03</v>
+        <v>0.11362</v>
       </c>
       <c r="K81" t="n">
-        <v>2.5</v>
+        <v>-0.002244477417203586</v>
       </c>
       <c r="L81" t="n">
-        <v>4.00621</v>
+        <v>-1.92662</v>
       </c>
       <c r="M81" t="n">
-        <v>14544176.16408117</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="N81" t="n">
-        <v>14612493</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="O81" t="n">
-        <v>427.42</v>
+        <v>0.193254</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>44450.05208333334</v>
+        <v>44290.85721064815</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R81" t="b">
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0002227866938767049</v>
+        <v>0.0002223489755974919</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>cosmos</t>
+          <t>quant-network</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>qnt</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Cosmos Hub</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1.75</v>
+        <v>63.8</v>
       </c>
       <c r="F82" t="n">
-        <v>928518127</v>
+        <v>928151271</v>
       </c>
       <c r="G82" t="n">
         <v>81</v>
       </c>
       <c r="H82" t="n">
-        <v>69176887</v>
+        <v>7900603</v>
       </c>
       <c r="I82" t="n">
-        <v>1.78</v>
+        <v>66.45</v>
       </c>
       <c r="J82" t="n">
-        <v>1.66</v>
+        <v>63.37</v>
       </c>
       <c r="K82" t="n">
-        <v>0.09384000000000001</v>
+        <v>-1.646758330233091</v>
       </c>
       <c r="L82" t="n">
-        <v>5.62372</v>
+        <v>-2.5161</v>
       </c>
       <c r="M82" t="n">
-        <v>531564934.540691</v>
+        <v>14544176.16408117</v>
       </c>
       <c r="N82" t="n">
-        <v>531591001.367196</v>
+        <v>14612493</v>
       </c>
       <c r="O82" t="n">
-        <v>43.84</v>
+        <v>427.42</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>44458.66666666666</v>
+        <v>44450.05208333334</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0002104028198777709</v>
+        <v>0.0002177137605632288</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jupiter-exchange-solana</t>
+          <t>pancakeswap-token</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>jup</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.277427</v>
+        <v>2.51</v>
       </c>
       <c r="F83" t="n">
-        <v>920883420</v>
+        <v>918844835</v>
       </c>
       <c r="G83" t="n">
         <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>112476681</v>
+        <v>134840819</v>
       </c>
       <c r="I83" t="n">
-        <v>0.286745</v>
+        <v>2.5</v>
       </c>
       <c r="J83" t="n">
-        <v>0.25763</v>
+        <v>2.3</v>
       </c>
       <c r="K83" t="n">
-        <v>0.0197335</v>
+        <v>0.083675</v>
       </c>
       <c r="L83" t="n">
-        <v>7.73468</v>
+        <v>3.45209</v>
       </c>
       <c r="M83" t="n">
-        <v>3319369204.37</v>
+        <v>366600236.5776587</v>
       </c>
       <c r="N83" t="n">
-        <v>6861486900.297955</v>
+        <v>378248721.8225635</v>
       </c>
       <c r="O83" t="n">
-        <v>2</v>
+        <v>43.96</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>45322.29359953704</v>
+        <v>44316.08914351852</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0002057261302696737</v>
+        <v>0.0002119561076015837</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>algorand</t>
+          <t>jupiter-exchange-solana</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>algo</t>
+          <t>jup</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Algorand</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.099742</v>
+        <v>0.269469</v>
       </c>
       <c r="F84" t="n">
-        <v>901883555</v>
+        <v>894616196</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>45194216</v>
+        <v>79315136</v>
       </c>
       <c r="I84" t="n">
-        <v>0.099658</v>
+        <v>0.286863</v>
       </c>
       <c r="J84" t="n">
-        <v>0.095639</v>
+        <v>0.266477</v>
       </c>
       <c r="K84" t="n">
-        <v>0.0031548</v>
+        <v>-0.00602656052099293</v>
       </c>
       <c r="L84" t="n">
-        <v>3.25392</v>
+        <v>-2.18753</v>
       </c>
       <c r="M84" t="n">
-        <v>9042193573.716511</v>
+        <v>3319369204.37</v>
       </c>
       <c r="N84" t="n">
-        <v>9042264038.746319</v>
+        <v>6861486880.683001</v>
       </c>
       <c r="O84" t="n">
-        <v>3.56</v>
+        <v>2</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>43636.28563657407</v>
+        <v>45322.29359953704</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R84" t="b">
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001940876389430581</v>
+        <v>0.000196966470849665</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>cosmos</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NEXO</t>
+          <t>Cosmos Hub</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.853658</v>
+        <v>1.68</v>
       </c>
       <c r="F85" t="n">
-        <v>853658122</v>
+        <v>894351921</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>3372089</v>
+        <v>48009775</v>
       </c>
       <c r="I85" t="n">
-        <v>0.849484</v>
+        <v>1.76</v>
       </c>
       <c r="J85" t="n">
-        <v>0.826249</v>
+        <v>1.67</v>
       </c>
       <c r="K85" t="n">
-        <v>0.03323759</v>
+        <v>-0.0521794658494894</v>
       </c>
       <c r="L85" t="n">
-        <v>4.07791</v>
+        <v>-3.00901</v>
       </c>
       <c r="M85" t="n">
-        <v>1000000000</v>
+        <v>531759588.764152</v>
       </c>
       <c r="N85" t="n">
-        <v>1000000000</v>
+        <v>531776444.345809</v>
       </c>
       <c r="O85" t="n">
-        <v>4.07</v>
+        <v>43.84</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>44328.27623842593</v>
+        <v>44458.66666666666</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R85" t="b">
         <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.000164546835169306</v>
+        <v>0.0001968029706938117</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>pancakeswap-token</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>NEXO</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2.44</v>
+        <v>0.819611</v>
       </c>
       <c r="F86" t="n">
-        <v>851553351</v>
+        <v>819967082</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
       </c>
       <c r="H86" t="n">
-        <v>93158522</v>
+        <v>3746975</v>
       </c>
       <c r="I86" t="n">
-        <v>2.51</v>
+        <v>0.849463</v>
       </c>
       <c r="J86" t="n">
-        <v>2.39</v>
+        <v>0.817512</v>
       </c>
       <c r="K86" t="n">
-        <v>-0.0218518113947046</v>
+        <v>-0.02646533128100348</v>
       </c>
       <c r="L86" t="n">
-        <v>-0.81335</v>
+        <v>-3.12801</v>
       </c>
       <c r="M86" t="n">
-        <v>348474895.6233068</v>
+        <v>1000000000</v>
       </c>
       <c r="N86" t="n">
-        <v>360130841.8225635</v>
+        <v>1000000000</v>
       </c>
       <c r="O86" t="n">
-        <v>43.96</v>
+        <v>4.07</v>
       </c>
       <c r="P86" s="1" t="n">
-        <v>44316.08914351852</v>
+        <v>44328.27623842593</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R86" t="b">
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001632575439544467</v>
+        <v>0.0001507829810253883</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6234,28 +6234,28 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="F87" t="n">
-        <v>843339790</v>
+        <v>793606737</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>70401750</v>
+        <v>52882448</v>
       </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="J87" t="n">
         <v>1.51</v>
       </c>
       <c r="K87" t="n">
-        <v>0.089157</v>
+        <v>-0.07782713717880529</v>
       </c>
       <c r="L87" t="n">
-        <v>5.75997</v>
+        <v>-4.84117</v>
       </c>
       <c r="M87" t="n">
         <v>518776241.2826915</v>
@@ -6270,153 +6270,153 @@
         <v>45368.35444444444</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R87" t="b">
         <v>1</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001582262735502029</v>
+        <v>0.0001344745125140015</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>filecoin</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>Spiko EU T-Bills Money Market Fund</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.987888</v>
+        <v>1.22</v>
       </c>
       <c r="F88" t="n">
-        <v>817787018</v>
+        <v>791533121</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>223542577</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0.997</v>
+        <v>1.22</v>
       </c>
       <c r="J88" t="n">
-        <v>0.8783570000000001</v>
+        <v>1.22</v>
       </c>
       <c r="K88" t="n">
-        <v>0.124844</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>14.47929</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>827813309</v>
+        <v>651037363.70003</v>
       </c>
       <c r="N88" t="n">
-        <v>1957040788</v>
+        <v>651037363.70003</v>
       </c>
       <c r="O88" t="n">
-        <v>236.84</v>
+        <v>1.26</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>44287.22894675926</v>
+        <v>46049.54175925926</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001425737562668966</v>
+        <v>0.000133191619545768</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>injective-protocol</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>inj</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Spiko EU T-Bills Money Market Fund</t>
+          <t>Injective</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1.22</v>
+        <v>7.84</v>
       </c>
       <c r="F89" t="n">
-        <v>791533121</v>
+        <v>784086286</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>229517357</v>
       </c>
       <c r="I89" t="n">
-        <v>1.22</v>
+        <v>8.32</v>
       </c>
       <c r="J89" t="n">
-        <v>1.21</v>
+        <v>7.36</v>
       </c>
       <c r="K89" t="n">
-        <v>0.00152768</v>
+        <v>0.182582</v>
       </c>
       <c r="L89" t="n">
-        <v>0.12581</v>
+        <v>2.38357</v>
       </c>
       <c r="M89" t="n">
-        <v>651037363.70003</v>
+        <v>100000000</v>
       </c>
       <c r="N89" t="n">
-        <v>651037363.70003</v>
+        <v>100000000</v>
       </c>
       <c r="O89" t="n">
-        <v>1.26</v>
+        <v>52.62</v>
       </c>
       <c r="P89" s="1" t="n">
-        <v>46049.54175925926</v>
+        <v>45365.29608796296</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R89" t="b">
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001264917602882747</v>
+        <v>0.000128584453967814</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6471,421 +6471,421 @@
         <v>46283.36122685186</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>0.0001172646963536077</v>
+        <v>0.0001238724020577346</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>filecoin</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>fil</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Dash</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>60.36</v>
+        <v>0.926125</v>
       </c>
       <c r="F91" t="n">
-        <v>774579585</v>
+        <v>769342018</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>183651947</v>
+        <v>257140423</v>
       </c>
       <c r="I91" t="n">
-        <v>64.87</v>
+        <v>1.13</v>
       </c>
       <c r="J91" t="n">
-        <v>57.53</v>
+        <v>0.9441659999999999</v>
       </c>
       <c r="K91" t="n">
-        <v>1.73</v>
+        <v>-0.06729471258352648</v>
       </c>
       <c r="L91" t="n">
-        <v>2.96131</v>
+        <v>-6.77405</v>
       </c>
       <c r="M91" t="n">
-        <v>12833705.99189731</v>
+        <v>830607045</v>
       </c>
       <c r="N91" t="n">
-        <v>12833828.23743384</v>
+        <v>1957039188</v>
       </c>
       <c r="O91" t="n">
-        <v>1493.59</v>
+        <v>236.84</v>
       </c>
       <c r="P91" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>44287.22894675926</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S91" t="n">
-        <v>0.0001161067611479405</v>
+        <v>0.000119462553992626</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>injective-protocol</t>
+          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>inj</t>
+          <t>ustb</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Injective</t>
+          <t>Invesco Short Duration US Government Securities Fund</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>7.55</v>
+        <v>11.22</v>
       </c>
       <c r="F92" t="n">
-        <v>755206082</v>
+        <v>747343793</v>
       </c>
       <c r="G92" t="n">
         <v>91</v>
       </c>
       <c r="H92" t="n">
-        <v>278755754</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>7.77</v>
+        <v>11.22</v>
       </c>
       <c r="J92" t="n">
-        <v>6.43</v>
+        <v>11.22</v>
       </c>
       <c r="K92" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>16.37045</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>100000000</v>
+        <v>66633634.978314</v>
       </c>
       <c r="N92" t="n">
-        <v>100000000</v>
+        <v>66633634.978314</v>
       </c>
       <c r="O92" t="n">
-        <v>52.62</v>
+        <v>11.22</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>45365.29608796296</v>
+        <v>46283.55902777778</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>0.0001042393954255177</v>
+        <v>0.0001058528171049296</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>vechain</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>vet</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VeChain</t>
+          <t>Dash</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.008651839999999999</v>
+        <v>55.1</v>
       </c>
       <c r="F93" t="n">
-        <v>743928678</v>
+        <v>706900026</v>
       </c>
       <c r="G93" t="n">
         <v>92</v>
       </c>
       <c r="H93" t="n">
-        <v>30200498</v>
+        <v>104129492</v>
       </c>
       <c r="I93" t="n">
-        <v>0.00871715</v>
+        <v>59.98</v>
       </c>
       <c r="J93" t="n">
-        <v>0.00765455</v>
+        <v>55.36</v>
       </c>
       <c r="K93" t="n">
-        <v>0.00109549</v>
+        <v>-4.725648139787666</v>
       </c>
       <c r="L93" t="n">
-        <v>14.53099</v>
+        <v>-7.89882</v>
       </c>
       <c r="M93" t="n">
-        <v>85985041177</v>
+        <v>12834288.94306016</v>
       </c>
       <c r="N93" t="n">
-        <v>85985041177</v>
+        <v>12834444.02060831</v>
       </c>
       <c r="O93" t="n">
-        <v>0.280991</v>
+        <v>1493.59</v>
       </c>
       <c r="P93" s="1" t="n">
-        <v>44304.71413194444</v>
+        <v>43088.66666666666</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R93" t="b">
         <v>1</v>
       </c>
       <c r="S93" t="n">
-        <v>9.733134799251018e-05</v>
+        <v>8.083129706786773e-05</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ustb</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Invesco Short Duration US Government Securities Fund</t>
+          <t>GHO</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>11.22</v>
+        <v>0.998873</v>
       </c>
       <c r="F94" t="n">
-        <v>742999390</v>
+        <v>698217912</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>4130425</v>
       </c>
       <c r="I94" t="n">
-        <v>11.22</v>
+        <v>0.9992220000000001</v>
       </c>
       <c r="J94" t="n">
-        <v>11.22</v>
+        <v>0.998735</v>
       </c>
       <c r="K94" t="n">
-        <v>0.001068</v>
+        <v>-0.000329611745378156</v>
       </c>
       <c r="L94" t="n">
-        <v>0.009520000000000001</v>
+        <v>-0.03299</v>
       </c>
       <c r="M94" t="n">
-        <v>66246285.313571</v>
+        <v>699000000</v>
       </c>
       <c r="N94" t="n">
-        <v>66264112.081849</v>
+        <v>699000000</v>
       </c>
       <c r="O94" t="n">
-        <v>11.22</v>
+        <v>1.03</v>
       </c>
       <c r="P94" s="1" t="n">
-        <v>46283.55902777778</v>
+        <v>45350.38608796296</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R94" t="b">
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>9.676210656221961e-05</v>
+        <v>7.545989609488083e-05</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ether-fi</t>
+          <t>vechain</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ethfi</t>
+          <t>vet</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Ether.fi</t>
+          <t>VeChain</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.7330179999999999</v>
+        <v>0.00811577</v>
       </c>
       <c r="F95" t="n">
-        <v>707619011</v>
+        <v>697935434</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>71413854</v>
+        <v>18346791</v>
       </c>
       <c r="I95" t="n">
-        <v>0.756706</v>
+        <v>0.00883454</v>
       </c>
       <c r="J95" t="n">
-        <v>0.707048</v>
+        <v>0.008146469999999999</v>
       </c>
       <c r="K95" t="n">
-        <v>0.03397617</v>
+        <v>-0.000445351937834066</v>
       </c>
       <c r="L95" t="n">
-        <v>4.97038</v>
+        <v>-5.20203</v>
       </c>
       <c r="M95" t="n">
-        <v>965350000</v>
+        <v>85985041177</v>
       </c>
       <c r="N95" t="n">
-        <v>965350000</v>
+        <v>85985041177</v>
       </c>
       <c r="O95" t="n">
-        <v>8.529999999999999</v>
+        <v>0.280991</v>
       </c>
       <c r="P95" s="1" t="n">
-        <v>45378.63525462963</v>
+        <v>44304.71413194444</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S95" t="n">
-        <v>7.508962446174825e-05</v>
+        <v>7.528513421038503e-05</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>ether-fi</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>ethfi</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>GHO</t>
+          <t>Ether.fi</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.999158</v>
+        <v>0.690631</v>
       </c>
       <c r="F96" t="n">
-        <v>698411721</v>
+        <v>667093213</v>
       </c>
       <c r="G96" t="n">
         <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>8352207</v>
+        <v>43497357</v>
       </c>
       <c r="I96" t="n">
-        <v>0.999203</v>
+        <v>0.757291</v>
       </c>
       <c r="J96" t="n">
-        <v>0.998354</v>
+        <v>0.690352</v>
       </c>
       <c r="K96" t="n">
-        <v>0.00082107</v>
+        <v>-0.04496680518341711</v>
       </c>
       <c r="L96" t="n">
-        <v>0.08276</v>
+        <v>-6.11296</v>
       </c>
       <c r="M96" t="n">
-        <v>699000000</v>
+        <v>965350000</v>
       </c>
       <c r="N96" t="n">
-        <v>699000000</v>
+        <v>965350000</v>
       </c>
       <c r="O96" t="n">
-        <v>1.03</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="P96" s="1" t="n">
-        <v>45350.38608796296</v>
+        <v>45378.63525462963</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S96" t="n">
-        <v>6.944963887202777e-05</v>
+        <v>5.620384411347118e-05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6904,31 +6904,31 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.02552026</v>
+        <v>0.02466683</v>
       </c>
       <c r="F97" t="n">
-        <v>675267312</v>
+        <v>653449197</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>9735529</v>
+        <v>12599558</v>
       </c>
       <c r="I97" t="n">
-        <v>0.02577869</v>
+        <v>0.02570266</v>
       </c>
       <c r="J97" t="n">
-        <v>0.02471799</v>
+        <v>0.02316713</v>
       </c>
       <c r="K97" t="n">
-        <v>0.00061767</v>
+        <v>-0.0009946546413089721</v>
       </c>
       <c r="L97" t="n">
-        <v>2.49109</v>
+        <v>-3.87606</v>
       </c>
       <c r="M97" t="n">
-        <v>26460045953</v>
+        <v>26490157407</v>
       </c>
       <c r="N97" t="n">
         <v>100000000000</v>
@@ -6940,19 +6940,19 @@
         <v>46156.97986111111</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>5.527238006486553e-05</v>
+        <v>4.776264179594242e-05</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6971,31 +6971,31 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.676086</v>
+        <v>0.651114</v>
       </c>
       <c r="F98" t="n">
-        <v>671136888</v>
+        <v>646446304</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>87495268</v>
+        <v>39978894</v>
       </c>
       <c r="I98" t="n">
-        <v>0.691195</v>
+        <v>0.675009</v>
       </c>
       <c r="J98" t="n">
-        <v>0.629119</v>
+        <v>0.638014</v>
       </c>
       <c r="K98" t="n">
-        <v>0.058827</v>
+        <v>-0.02330602382306102</v>
       </c>
       <c r="L98" t="n">
-        <v>9.57982</v>
+        <v>-3.45571</v>
       </c>
       <c r="M98" t="n">
-        <v>992679168.7721908</v>
+        <v>992679535.5672693</v>
       </c>
       <c r="N98" t="n">
         <v>1983240735.576791</v>
@@ -7007,19 +7007,19 @@
         <v>45633.25043981482</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>5.274226188248661e-05</v>
+        <v>4.343013173284913e-05</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7038,34 +7038,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.739513</v>
+        <v>0.721151</v>
       </c>
       <c r="F99" t="n">
-        <v>643735939</v>
+        <v>627500848</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>294915580</v>
+        <v>120774558</v>
       </c>
       <c r="I99" t="n">
-        <v>0.780166</v>
+        <v>0.748103</v>
       </c>
       <c r="J99" t="n">
-        <v>0.668581</v>
+        <v>0.7104549999999999</v>
       </c>
       <c r="K99" t="n">
-        <v>0.04581178</v>
+        <v>-0.01582235679890542</v>
       </c>
       <c r="L99" t="n">
-        <v>6.97469</v>
+        <v>-2.14694</v>
       </c>
       <c r="M99" t="n">
-        <v>870485718.1680963</v>
+        <v>870534155.5712929</v>
       </c>
       <c r="N99" t="n">
-        <v>1208925887.093529</v>
+        <v>1208974392.707352</v>
       </c>
       <c r="O99" t="n">
         <v>19.92</v>
@@ -7074,19 +7074,19 @@
         <v>44952.26755787037</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>3.595763171392825e-05</v>
+        <v>3.170906462959749e-05</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7105,34 +7105,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.075616</v>
+        <v>0.075895</v>
       </c>
       <c r="F100" t="n">
-        <v>595153733</v>
+        <v>597644598</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>3430787</v>
+        <v>3842711</v>
       </c>
       <c r="I100" t="n">
-        <v>0.076763</v>
+        <v>0.076097</v>
       </c>
       <c r="J100" t="n">
-        <v>0.075255</v>
+        <v>0.075479</v>
       </c>
       <c r="K100" t="n">
-        <v>-0.000268082142819329</v>
+        <v>0.00023246</v>
       </c>
       <c r="L100" t="n">
-        <v>-0.37544</v>
+        <v>0.30724</v>
       </c>
       <c r="M100" t="n">
-        <v>7870755165.810848</v>
+        <v>7870780683.443047</v>
       </c>
       <c r="N100" t="n">
-        <v>9939695277.199703</v>
+        <v>9939720596.243883</v>
       </c>
       <c r="O100" t="n">
         <v>0.450785</v>
@@ -7141,19 +7141,19 @@
         <v>43450.66666666666</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R100" t="b">
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>6.198284310204505e-06</v>
+        <v>1.323776947040697e-05</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7172,34 +7172,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.313238</v>
+        <v>0.308622</v>
       </c>
       <c r="F101" t="n">
-        <v>585035019</v>
+        <v>576247606</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>41366435</v>
+        <v>44500577</v>
       </c>
       <c r="I101" t="n">
-        <v>0.321993</v>
+        <v>0.331991</v>
       </c>
       <c r="J101" t="n">
-        <v>0.271596</v>
+        <v>0.300479</v>
       </c>
       <c r="K101" t="n">
-        <v>0.04080722</v>
+        <v>-0.000836197743021072</v>
       </c>
       <c r="L101" t="n">
-        <v>14.95778</v>
+        <v>-0.27021</v>
       </c>
       <c r="M101" t="n">
-        <v>1867702388.984369</v>
+        <v>1867933631.498019</v>
       </c>
       <c r="N101" t="n">
-        <v>1867702388.984369</v>
+        <v>1867933631.498019</v>
       </c>
       <c r="O101" t="n">
         <v>3.86</v>
@@ -7208,10 +7208,10 @@
         <v>45383.19094907407</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46284.54108796296</v>
+        <v>46285.56273148148</v>
       </c>
       <c r="R101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>

--- a/src/xlsx/cleaned_data.xlsx
+++ b/src/xlsx/cleaned_data.xlsx
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,34 +539,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>80495</v>
+        <v>86124</v>
       </c>
       <c r="F2" t="n">
-        <v>1616935563111</v>
+        <v>1728665546532</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>23866467100</v>
+        <v>53399664432</v>
       </c>
       <c r="I2" t="n">
-        <v>81864</v>
+        <v>86048</v>
       </c>
       <c r="J2" t="n">
-        <v>80155</v>
+        <v>80631</v>
       </c>
       <c r="K2" t="n">
-        <v>-716.1132064880803</v>
+        <v>5263.94</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.88179</v>
+        <v>6.50996</v>
       </c>
       <c r="M2" t="n">
-        <v>20086925</v>
+        <v>20087478</v>
       </c>
       <c r="N2" t="n">
-        <v>20086940</v>
+        <v>20087478</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -575,10 +575,10 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -587,7 +587,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,34 +606,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2580.2</v>
+        <v>2750.02</v>
       </c>
       <c r="F3" t="n">
-        <v>314968305243</v>
+        <v>335133212622</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>9962778525</v>
+        <v>24352107151</v>
       </c>
       <c r="I3" t="n">
-        <v>2655.64</v>
+        <v>2751.07</v>
       </c>
       <c r="J3" t="n">
-        <v>2568.1</v>
+        <v>2607</v>
       </c>
       <c r="K3" t="n">
-        <v>-52.42004059185319</v>
+        <v>144.87</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.99117</v>
+        <v>5.56097</v>
       </c>
       <c r="M3" t="n">
-        <v>122064744.0690741</v>
+        <v>122067645.9189046</v>
       </c>
       <c r="N3" t="n">
-        <v>122064744.0690741</v>
+        <v>122067645.9189046</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -642,19 +642,19 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1945062923950015</v>
+        <v>0.1935827213788247</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,31 +673,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999618</v>
+        <v>0.999874</v>
       </c>
       <c r="F4" t="n">
-        <v>183316154408</v>
+        <v>183365978384</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>47434232181</v>
+        <v>93897835021</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999725</v>
+        <v>0.999816</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9993649999999999</v>
+        <v>0.999577</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.0405962333966e-05</v>
+        <v>0.00023771</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00504</v>
+        <v>0.02378</v>
       </c>
       <c r="M4" t="n">
-        <v>183384649789.2811</v>
+        <v>183384649781.6938</v>
       </c>
       <c r="N4" t="n">
         <v>188851595759.0362</v>
@@ -709,19 +709,19 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1130564875328519</v>
+        <v>0.1057571883503426</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,34 +740,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>751.14</v>
+        <v>805.13</v>
       </c>
       <c r="F5" t="n">
-        <v>100013527800</v>
+        <v>107128051029</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>925413271</v>
+        <v>1861840599</v>
       </c>
       <c r="I5" t="n">
-        <v>772.55</v>
+        <v>798.53</v>
       </c>
       <c r="J5" t="n">
-        <v>746.64</v>
+        <v>756.27</v>
       </c>
       <c r="K5" t="n">
-        <v>-17.74319357724983</v>
+        <v>48.91</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.30766</v>
+        <v>6.46797</v>
       </c>
       <c r="M5" t="n">
-        <v>133160261.42</v>
+        <v>133160157.48</v>
       </c>
       <c r="N5" t="n">
-        <v>133160255.08</v>
+        <v>133160152.56</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -776,19 +776,19 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06151929168232792</v>
+        <v>0.06163938755785053</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -807,28 +807,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="F6" t="n">
-        <v>86599821752</v>
+        <v>94051358788</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2615052383</v>
+        <v>4723578943</v>
       </c>
       <c r="I6" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="J6" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.05751144693811527</v>
+        <v>0.112485</v>
       </c>
       <c r="L6" t="n">
-        <v>-4.00873</v>
+        <v>8.11206</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -843,19 +843,19 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05322057621768561</v>
+        <v>0.05407209233710331</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,34 +874,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999739</v>
+        <v>0.9999169999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>74195791330</v>
+        <v>74231800122</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>11424902046</v>
+        <v>24254647063</v>
       </c>
       <c r="I7" t="n">
-        <v>1.002</v>
+        <v>0.9998629999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9994690000000001</v>
+        <v>0.999598</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.7217957993698e-05</v>
+        <v>0.00021933</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00172</v>
+        <v>0.02194</v>
       </c>
       <c r="M7" t="n">
-        <v>74214798719.86125</v>
+        <v>74237004006.76027</v>
       </c>
       <c r="N7" t="n">
-        <v>74213440603.05618</v>
+        <v>74254811731.89992</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -910,19 +910,19 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04554652113413224</v>
+        <v>0.04260279652387772</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -941,34 +941,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>108.19</v>
+        <v>118.05</v>
       </c>
       <c r="F8" t="n">
-        <v>63553214540</v>
+        <v>69255259901</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2831986860</v>
+        <v>6440764344</v>
       </c>
       <c r="I8" t="n">
-        <v>112.21</v>
+        <v>118.69</v>
       </c>
       <c r="J8" t="n">
-        <v>107.5</v>
+        <v>108.51</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.282472112539367</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.94473</v>
+        <v>8.87163</v>
       </c>
       <c r="M8" t="n">
-        <v>587366825.3628587</v>
+        <v>587437261.0683235</v>
       </c>
       <c r="N8" t="n">
-        <v>634375499.6096436</v>
+        <v>634453375.546979</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -977,19 +977,19 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03896223217813675</v>
+        <v>0.03972294370359374</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1008,34 +1008,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.342134</v>
+        <v>0.345544</v>
       </c>
       <c r="F9" t="n">
-        <v>32482355042</v>
+        <v>32816706862</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>373296960</v>
+        <v>440937993</v>
       </c>
       <c r="I9" t="n">
-        <v>0.342855</v>
+        <v>0.345088</v>
       </c>
       <c r="J9" t="n">
-        <v>0.337711</v>
+        <v>0.342488</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0043126</v>
+        <v>0.00109724</v>
       </c>
       <c r="L9" t="n">
-        <v>1.27659</v>
+        <v>0.31855</v>
       </c>
       <c r="M9" t="n">
-        <v>94955991096.57959</v>
+        <v>94960364758.90469</v>
       </c>
       <c r="N9" t="n">
-        <v>94958776822.35458</v>
+        <v>94960365761.90469</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1044,19 +1044,19 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01973948931400291</v>
+        <v>0.01863647296763626</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1075,34 +1075,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1449.06</v>
+        <v>1495.75</v>
       </c>
       <c r="F10" t="n">
-        <v>24547629301</v>
+        <v>25309984948</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1070998386</v>
+        <v>1431547468</v>
       </c>
       <c r="I10" t="n">
-        <v>1532.34</v>
+        <v>1568.53</v>
       </c>
       <c r="J10" t="n">
-        <v>1429.69</v>
+        <v>1439.75</v>
       </c>
       <c r="K10" t="n">
-        <v>-86.56531411476908</v>
+        <v>53.35</v>
       </c>
       <c r="L10" t="n">
-        <v>-5.63715</v>
+        <v>3.69892</v>
       </c>
       <c r="M10" t="n">
         <v>16942351.7280448</v>
       </c>
       <c r="N10" t="n">
-        <v>16942756.4155448</v>
+        <v>16944709.5405448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1111,19 +1111,19 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01483047826374584</v>
+        <v>0.01429244010241479</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1142,34 +1142,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.017</v>
+        <v>1.04</v>
       </c>
       <c r="F11" t="n">
-        <v>23140466333</v>
+        <v>23664863580</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>345014</v>
+        <v>16837398</v>
       </c>
       <c r="I11" t="n">
-        <v>1.044</v>
+        <v>1.021</v>
       </c>
       <c r="J11" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.01372322010803706</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3316</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>22756817018.848</v>
+        <v>22764228455.528</v>
       </c>
       <c r="N11" t="n">
-        <v>22756817018.848</v>
+        <v>22764228455.528</v>
       </c>
       <c r="O11" t="n">
         <v>1.061</v>
@@ -1178,19 +1178,19 @@
         <v>46237.59675925926</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46284.89166666667</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01395990267173376</v>
+        <v>0.01334043183945489</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1209,28 +1209,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>91.02</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>20248590427</v>
+        <v>20757345051</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>816678542</v>
+        <v>1256686450</v>
       </c>
       <c r="I12" t="n">
-        <v>93.34</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>89.91</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.201150679321842</v>
+        <v>1.53</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.30245</v>
+        <v>1.66271</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1239,25 +1239,25 @@
         <v>955307079.4341414</v>
       </c>
       <c r="O12" t="n">
-        <v>94.48</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>46284.12847222222</v>
+        <v>46286.47291666667</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01217077331277282</v>
+        <v>0.01165789235139143</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1276,34 +1276,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.084982</v>
+        <v>0.097469</v>
       </c>
       <c r="F13" t="n">
-        <v>13258401671</v>
+        <v>15181065525</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>957418339</v>
+        <v>1882978328</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09105199999999999</v>
+        <v>0.095163</v>
       </c>
       <c r="J13" t="n">
-        <v>0.084508</v>
+        <v>0.085616</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.003840532751950301</v>
+        <v>0.01187787</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.32382</v>
+        <v>13.87742</v>
       </c>
       <c r="M13" t="n">
-        <v>155990666383.7052</v>
+        <v>156008016383.7053</v>
       </c>
       <c r="N13" t="n">
-        <v>155993876383.7052</v>
+        <v>156008916383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1312,19 +1312,19 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R13" t="b">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>0.007846123039194233</v>
+        <v>0.008430978952424452</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1343,34 +1343,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>535.58</v>
+        <v>572.01</v>
       </c>
       <c r="F14" t="n">
-        <v>10061624614</v>
+        <v>10738217262</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>131885688</v>
+        <v>235272967</v>
       </c>
       <c r="I14" t="n">
-        <v>579.76</v>
+        <v>630.51</v>
       </c>
       <c r="J14" t="n">
-        <v>518.29</v>
+        <v>540.97</v>
       </c>
       <c r="K14" t="n">
-        <v>-42.40255239524106</v>
+        <v>29.3</v>
       </c>
       <c r="L14" t="n">
-        <v>-7.33635</v>
+        <v>5.39931</v>
       </c>
       <c r="M14" t="n">
-        <v>18807107.52726052</v>
+        <v>18807603.12217533</v>
       </c>
       <c r="N14" t="n">
-        <v>18807145.32714538</v>
+        <v>18807625.32201612</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1379,19 +1379,19 @@
         <v>46036.48202546296</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0058683591680458</v>
+        <v>0.005859966053482513</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1410,28 +1410,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>81.87</v>
+        <v>86.64</v>
       </c>
       <c r="F15" t="n">
-        <v>9729647899</v>
+        <v>10291846518</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>66922631</v>
+        <v>215315698</v>
       </c>
       <c r="I15" t="n">
-        <v>83.58</v>
+        <v>86.64</v>
       </c>
       <c r="J15" t="n">
-        <v>81.56</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.16256627545016</v>
+        <v>4.33</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.4002</v>
+        <v>5.26004</v>
       </c>
       <c r="M15" t="n">
         <v>118887984</v>
@@ -1440,226 +1440,226 @@
         <v>293457483</v>
       </c>
       <c r="O15" t="n">
-        <v>83.64</v>
+        <v>86.8</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>46283.82569444444</v>
+        <v>46286.63425925926</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005662973699718616</v>
+        <v>0.005601657672777343</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.999799</v>
+        <v>0.01414863</v>
       </c>
       <c r="F16" t="n">
-        <v>9594177187</v>
+        <v>10032920141</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>73095244</v>
+        <v>29041461</v>
       </c>
       <c r="I16" t="n">
+        <v>0.01427443</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.01325824</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.00097359</v>
+      </c>
+      <c r="L16" t="n">
+        <v>7.38968</v>
+      </c>
+      <c r="M16" t="n">
+        <v>709239296767.5244</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1142408526965.963</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.01946402</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>46259.82847222222</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>46286.65775462963</v>
+      </c>
+      <c r="R16" t="b">
         <v>1</v>
       </c>
-      <c r="J16" t="n">
-        <v>0.999555</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-0.000212149564497666</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-0.02121</v>
-      </c>
-      <c r="M16" t="n">
-        <v>9596506299.314947</v>
-      </c>
-      <c r="N16" t="n">
-        <v>9615952659.618965</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.057</v>
-      </c>
-      <c r="P16" s="1" t="n">
-        <v>45593.90336805556</v>
-      </c>
-      <c r="Q16" s="1" t="n">
-        <v>46285.56273148148</v>
-      </c>
-      <c r="R16" t="b">
-        <v>0</v>
-      </c>
       <c r="S16" t="n">
-        <v>0.005579161449125267</v>
+        <v>0.005451820672786307</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.01319963</v>
+        <v>13.03</v>
       </c>
       <c r="F17" t="n">
-        <v>9360305215</v>
+        <v>9741654136</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>22251262</v>
+        <v>695570017</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01400625</v>
+        <v>13.16</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01315802</v>
+        <v>12.32</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.000716285644190382</v>
+        <v>0.717199</v>
       </c>
       <c r="L17" t="n">
-        <v>-5.14724</v>
+        <v>5.82362</v>
       </c>
       <c r="M17" t="n">
-        <v>709239215179.4515</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N17" t="n">
-        <v>1142408526965.963</v>
+        <v>1000000000</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01946402</v>
+        <v>52.7</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>46259.82847222222</v>
+        <v>44325.67635416667</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005434470865938365</v>
+        <v>0.005283269191495647</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>12.1</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>9051969224</v>
+        <v>9595586523</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>444890857</v>
+        <v>196078899</v>
       </c>
       <c r="I18" t="n">
-        <v>12.67</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>11.92</v>
+        <v>0.999754</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3614832084632802</v>
+        <v>0.00015973</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.90074</v>
+        <v>0.01598</v>
       </c>
       <c r="M18" t="n">
-        <v>748099970.424884</v>
+        <v>9594149705.433596</v>
       </c>
       <c r="N18" t="n">
-        <v>1000000000</v>
+        <v>9594892921.253408</v>
       </c>
       <c r="O18" t="n">
-        <v>52.7</v>
+        <v>1.057</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>44325.67635416667</v>
+        <v>45593.90336805556</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005243711306450401</v>
+        <v>0.005198741947955018</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1678,28 +1678,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.221201</v>
+        <v>0.245391</v>
       </c>
       <c r="F19" t="n">
-        <v>8300217493</v>
+        <v>9197046672</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>422086912</v>
+        <v>826630614</v>
       </c>
       <c r="I19" t="n">
-        <v>0.231163</v>
+        <v>0.248479</v>
       </c>
       <c r="J19" t="n">
-        <v>0.218425</v>
+        <v>0.22404</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.005928161879755561</v>
+        <v>0.02123083</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.61004</v>
+        <v>9.471270000000001</v>
       </c>
       <c r="M19" t="n">
         <v>37522923322.16203</v>
@@ -1714,19 +1714,19 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004778621815649199</v>
+        <v>0.004968112622574567</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1745,28 +1745,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.93</v>
+        <v>8.92</v>
       </c>
       <c r="F20" t="n">
-        <v>8218224663</v>
+        <v>8205789399</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>163463</v>
+        <v>45234</v>
       </c>
       <c r="I20" t="n">
-        <v>8.970000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="J20" t="n">
         <v>8.880000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.04202022</v>
+        <v>-0.01354870721141488</v>
       </c>
       <c r="L20" t="n">
-        <v>0.47255</v>
+        <v>-0.15166</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -1781,19 +1781,19 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004727894957324148</v>
+        <v>0.004394486182014535</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1812,31 +1812,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.190217</v>
+        <v>0.210781</v>
       </c>
       <c r="F21" t="n">
-        <v>6633745483</v>
+        <v>7340660289</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>209188054</v>
+        <v>385358090</v>
       </c>
       <c r="I21" t="n">
-        <v>0.202311</v>
+        <v>0.212907</v>
       </c>
       <c r="J21" t="n">
-        <v>0.188682</v>
+        <v>0.193655</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.01022295789780794</v>
+        <v>0.01715873</v>
       </c>
       <c r="L21" t="n">
-        <v>-5.10025</v>
+        <v>8.861940000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>34867261640.33779</v>
+        <v>34882253227.52757</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70148</v>
@@ -1848,19 +1848,19 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R21" t="b">
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.003747618378471406</v>
+        <v>0.003893848309777537</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1879,34 +1879,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>8.630000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>5355976540</v>
+        <v>5515671145</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>806083310</v>
+        <v>1170568252</v>
       </c>
       <c r="I22" t="n">
-        <v>9.050000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="J22" t="n">
-        <v>8.460000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3641764250946125</v>
+        <v>0.21966</v>
       </c>
       <c r="L22" t="n">
-        <v>-4.04975</v>
+        <v>2.53223</v>
       </c>
       <c r="M22" t="n">
-        <v>620926422.6104751</v>
+        <v>620798422.6104751</v>
       </c>
       <c r="N22" t="n">
-        <v>888126418.9163101</v>
+        <v>888046418.9163101</v>
       </c>
       <c r="O22" t="n">
         <v>44.92</v>
@@ -1915,19 +1915,19 @@
         <v>44318.89240740741</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R22" t="b">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.002957095546856589</v>
+        <v>0.002837753131211902</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1946,34 +1946,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>246.11</v>
+        <v>264.35</v>
       </c>
       <c r="F23" t="n">
-        <v>4945351588</v>
+        <v>5307183344</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>145678419</v>
+        <v>296383774</v>
       </c>
       <c r="I23" t="n">
-        <v>256.71</v>
+        <v>271.86</v>
       </c>
       <c r="J23" t="n">
-        <v>243.4</v>
+        <v>247.88</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.721021554373493</v>
+        <v>16.82</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.27178</v>
+        <v>6.79536</v>
       </c>
       <c r="M23" t="n">
-        <v>20091637.39665077</v>
+        <v>20092153.02165077</v>
       </c>
       <c r="N23" t="n">
-        <v>20091940.52165077</v>
+        <v>20092453.02165077</v>
       </c>
       <c r="O23" t="n">
         <v>3785.82</v>
@@ -1982,1024 +1982,1024 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.002703052434003487</v>
+        <v>0.002717104215491091</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ethena-usde</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>usde</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ethena USDe</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.999728</v>
+        <v>4.04</v>
       </c>
       <c r="F24" t="n">
-        <v>4844853212</v>
+        <v>5280599037</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>33630793</v>
+        <v>1859521787</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9998010000000001</v>
+        <v>4.44</v>
       </c>
       <c r="J24" t="n">
-        <v>0.999471</v>
+        <v>3.87</v>
       </c>
       <c r="K24" t="n">
-        <v>4.12e-05</v>
+        <v>0.255399</v>
       </c>
       <c r="L24" t="n">
-        <v>0.00412</v>
+        <v>6.74642</v>
       </c>
       <c r="M24" t="n">
-        <v>4846068728.449359</v>
+        <v>1306919679</v>
       </c>
       <c r="N24" t="n">
-        <v>4846803023.178389</v>
+        <v>1306919694</v>
       </c>
       <c r="O24" t="n">
-        <v>1.034</v>
+        <v>20.44</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>46000.38208333333</v>
+        <v>44577.59010416667</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002640876669595186</v>
+        <v>0.002701720256336861</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>avalanche-2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>avax</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3.69</v>
+        <v>11.2</v>
       </c>
       <c r="F25" t="n">
-        <v>4814880203</v>
+        <v>4956319449</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>1242982579</v>
+        <v>1232465817</v>
       </c>
       <c r="I25" t="n">
-        <v>3.74</v>
+        <v>11.78</v>
       </c>
       <c r="J25" t="n">
-        <v>3.43</v>
+        <v>10.92</v>
       </c>
       <c r="K25" t="n">
-        <v>0.120604</v>
+        <v>-0.05499586640539</v>
       </c>
       <c r="L25" t="n">
-        <v>3.37953</v>
+        <v>-0.4887</v>
       </c>
       <c r="M25" t="n">
-        <v>1306811794</v>
+        <v>442892841.602698</v>
       </c>
       <c r="N25" t="n">
-        <v>1306811791</v>
+        <v>469561413.4440742</v>
       </c>
       <c r="O25" t="n">
-        <v>20.44</v>
+        <v>144.96</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>44577.59010416667</v>
+        <v>44521.26314814815</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002622333138641096</v>
+        <v>0.002514064285604111</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>avalanche-2</t>
+          <t>ethena-usde</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>avax</t>
+          <t>usde</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Ethena USDe</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>10.62</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>4711603532</v>
+        <v>4883273448</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>1342152577</v>
+        <v>43152985</v>
       </c>
       <c r="I26" t="n">
-        <v>10.79</v>
+        <v>0.999964</v>
       </c>
       <c r="J26" t="n">
-        <v>9.279999999999999</v>
+        <v>0.999695</v>
       </c>
       <c r="K26" t="n">
-        <v>1.37</v>
+        <v>0.00034911</v>
       </c>
       <c r="L26" t="n">
-        <v>14.82973</v>
+        <v>0.03492</v>
       </c>
       <c r="M26" t="n">
-        <v>442879289.6632363</v>
+        <v>4882671688.190312</v>
       </c>
       <c r="N26" t="n">
-        <v>469547976.0745428</v>
+        <v>4883552134.801312</v>
       </c>
       <c r="O26" t="n">
-        <v>144.96</v>
+        <v>1.034</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>44521.26314814815</v>
+        <v>46000.38208333333</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002558438514463592</v>
+        <v>0.002471793607050638</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>litecoin</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>ltc</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Dai</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.999841</v>
+        <v>62.5</v>
       </c>
       <c r="F27" t="n">
-        <v>4605413603</v>
+        <v>4854766688</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>172647200</v>
+        <v>555253226</v>
       </c>
       <c r="I27" t="n">
+        <v>63.74</v>
+      </c>
+      <c r="J27" t="n">
+        <v>57.44</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="L27" t="n">
+        <v>8.866899999999999</v>
+      </c>
+      <c r="M27" t="n">
+        <v>77632004.46059512</v>
+      </c>
+      <c r="N27" t="n">
+        <v>77635191.97028677</v>
+      </c>
+      <c r="O27" t="n">
+        <v>410.26</v>
+      </c>
+      <c r="P27" s="1" t="n">
+        <v>44325.80077546297</v>
+      </c>
+      <c r="Q27" s="1" t="n">
+        <v>46286.65775462963</v>
+      </c>
+      <c r="R27" t="b">
         <v>1</v>
       </c>
-      <c r="J27" t="n">
-        <v>0.999503</v>
-      </c>
-      <c r="K27" t="n">
-        <v>-3.219872398819e-06</v>
-      </c>
-      <c r="L27" t="n">
-        <v>-0.00032</v>
-      </c>
-      <c r="M27" t="n">
-        <v>4605655963.213758</v>
-      </c>
-      <c r="N27" t="n">
-        <v>4606200673.079864</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P27" s="1" t="n">
-        <v>43902.79363425926</v>
-      </c>
-      <c r="Q27" s="1" t="n">
-        <v>46285.56273148148</v>
-      </c>
-      <c r="R27" t="b">
-        <v>0</v>
-      </c>
       <c r="S27" t="n">
-        <v>0.002492741532374666</v>
+        <v>0.002455297151774997</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>litecoin</t>
+          <t>canton-network</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ltc</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>56.92</v>
+        <v>0.116617</v>
       </c>
       <c r="F28" t="n">
-        <v>4418176889</v>
+        <v>4621327246</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>277072921</v>
+        <v>17034306</v>
       </c>
       <c r="I28" t="n">
-        <v>58.41</v>
+        <v>0.118847</v>
       </c>
       <c r="J28" t="n">
-        <v>56.59</v>
+        <v>0.106795</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.9526302316288451</v>
+        <v>0.009704809999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>-1.64611</v>
+        <v>9.077400000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>77628260.69940798</v>
+        <v>39650914855.51295</v>
       </c>
       <c r="N28" t="n">
-        <v>77631210.7072867</v>
+        <v>39650914855.51295</v>
       </c>
       <c r="O28" t="n">
-        <v>410.26</v>
+        <v>0.194152</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>44325.80077546297</v>
+        <v>46056.00148148148</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002376902985707521</v>
+        <v>0.002320209077419168</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>usd1-wlfi</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>usd1</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>USD1</t>
+          <t>Dai</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.999407</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>4354328121</v>
+        <v>4587287767</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>801746341</v>
+        <v>332234991</v>
       </c>
       <c r="I29" t="n">
-        <v>0.999739</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.999196</v>
+        <v>0.999663</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.00025750416125081</v>
+        <v>4.657e-05</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.02576</v>
+        <v>0.00466</v>
       </c>
       <c r="M29" t="n">
-        <v>4356798749.070584</v>
+        <v>4587555760.165159</v>
       </c>
       <c r="N29" t="n">
-        <v>4356798749.070584</v>
+        <v>4589397370.72186</v>
       </c>
       <c r="O29" t="n">
-        <v>1.048</v>
+        <v>1.22</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>46212.42696759259</v>
+        <v>43902.79363425926</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002337401392597915</v>
+        <v>0.002300510916599431</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>canton-network</t>
+          <t>usd1-wlfi</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>usd1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>USD1</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.104589</v>
+        <v>0.999808</v>
       </c>
       <c r="F30" t="n">
-        <v>4146281070</v>
+        <v>4356161972</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>8159457</v>
+        <v>1388534334</v>
       </c>
       <c r="I30" t="n">
-        <v>0.113632</v>
+        <v>0.999771</v>
       </c>
       <c r="J30" t="n">
-        <v>0.102843</v>
+        <v>0.99937</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.006877583372992727</v>
+        <v>0.00033205</v>
       </c>
       <c r="L30" t="n">
-        <v>-6.17011</v>
+        <v>0.03322</v>
       </c>
       <c r="M30" t="n">
-        <v>39642019727.36819</v>
+        <v>4356796476.280436</v>
       </c>
       <c r="N30" t="n">
-        <v>39643068193.79603</v>
+        <v>4356796476.280436</v>
       </c>
       <c r="O30" t="n">
-        <v>0.194152</v>
+        <v>1.048</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>46056.00148148148</v>
+        <v>46212.42696759259</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.002208688024843419</v>
+        <v>0.002166761716751232</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>the-open-network</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>gram</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Gram (prev. Toncoin)</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.37</v>
+        <v>1.022</v>
       </c>
       <c r="F31" t="n">
-        <v>3837702612</v>
+        <v>4178422617</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>39656864</v>
+        <v>2166507655</v>
       </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>1.054</v>
       </c>
       <c r="J31" t="n">
-        <v>1.37</v>
+        <v>0.843444</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.02118006897896074</v>
+        <v>0.181534</v>
       </c>
       <c r="L31" t="n">
-        <v>-1.52103</v>
+        <v>21.60945</v>
       </c>
       <c r="M31" t="n">
-        <v>2799003081.352252</v>
+        <v>4096537146.540959</v>
       </c>
       <c r="N31" t="n">
-        <v>5252388289.862276</v>
+        <v>10000000000</v>
       </c>
       <c r="O31" t="n">
-        <v>8.25</v>
+        <v>5.35</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>45457.69225694444</v>
+        <v>45661.62243055556</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0.002017778457249168</v>
+        <v>0.002063906488009737</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>hedera-hashgraph</t>
+          <t>the-open-network</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>hbar</t>
+          <t>gram</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Hedera</t>
+          <t>Gram (prev. Toncoin)</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.08301799999999999</v>
+        <v>1.43</v>
       </c>
       <c r="F32" t="n">
-        <v>3635864245</v>
+        <v>4028994265</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>144444996</v>
+        <v>60620535</v>
       </c>
       <c r="I32" t="n">
-        <v>0.083749</v>
+        <v>1.44</v>
       </c>
       <c r="J32" t="n">
-        <v>0.079527</v>
+        <v>1.37</v>
       </c>
       <c r="K32" t="n">
-        <v>0.00182624</v>
+        <v>0.061308</v>
       </c>
       <c r="L32" t="n">
-        <v>2.2493</v>
+        <v>4.46488</v>
       </c>
       <c r="M32" t="n">
-        <v>43831706401.51488</v>
+        <v>2810474514.130084</v>
       </c>
       <c r="N32" t="n">
-        <v>50000000000</v>
+        <v>5253006691.507872</v>
       </c>
       <c r="O32" t="n">
-        <v>0.569229</v>
+        <v>8.25</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>44454.11143518519</v>
+        <v>45457.69225694444</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001892906242844947</v>
+        <v>0.001977434432761057</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>memecore</t>
+          <t>hedera-hashgraph</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>hbar</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MemeCore</t>
+          <t>Hedera</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.52</v>
+        <v>0.091629</v>
       </c>
       <c r="F33" t="n">
-        <v>3452848597</v>
+        <v>4010077306</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>4391838</v>
+        <v>222101860</v>
       </c>
       <c r="I33" t="n">
-        <v>1.78</v>
+        <v>0.092859</v>
       </c>
       <c r="J33" t="n">
-        <v>1.27</v>
+        <v>0.084797</v>
       </c>
       <c r="K33" t="n">
-        <v>0.225627</v>
+        <v>0.00531559</v>
       </c>
       <c r="L33" t="n">
-        <v>17.43532</v>
+        <v>6.15846</v>
       </c>
       <c r="M33" t="n">
-        <v>2275413158.37504</v>
+        <v>43831706400.74403</v>
       </c>
       <c r="N33" t="n">
-        <v>5416287555.165793</v>
+        <v>50000000000</v>
       </c>
       <c r="O33" t="n">
-        <v>5.64</v>
+        <v>0.569229</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>46205.17638888889</v>
+        <v>44454.11143518519</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R33" t="b">
         <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001779679161313994</v>
+        <v>0.001966487458496193</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>shiba-inu</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>shib</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>Shiba Inu</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.818716</v>
+        <v>5.97e-06</v>
       </c>
       <c r="F34" t="n">
-        <v>3355103041</v>
+        <v>3499895427</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>801060446</v>
+        <v>133814849</v>
       </c>
       <c r="I34" t="n">
-        <v>0.885594</v>
+        <v>5.87e-06</v>
       </c>
       <c r="J34" t="n">
-        <v>0.809067</v>
+        <v>5.4e-06</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.02899743878369299</v>
+        <v>5.74284e-07</v>
       </c>
       <c r="L34" t="n">
-        <v>-3.42067</v>
+        <v>10.6398</v>
       </c>
       <c r="M34" t="n">
-        <v>4096537146.540959</v>
+        <v>589238972680230.1</v>
       </c>
       <c r="N34" t="n">
-        <v>10000000000</v>
+        <v>589496072572615.9</v>
       </c>
       <c r="O34" t="n">
-        <v>5.35</v>
+        <v>8.616e-05</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>45661.62243055556</v>
+        <v>44496.82980324074</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001719206495946603</v>
+        <v>0.001671252484428065</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>global-dollar</t>
+          <t>memecore</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>usdg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Global Dollar</t>
+          <t>MemeCore</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.999937</v>
+        <v>1.49</v>
       </c>
       <c r="F35" t="n">
-        <v>3259397697</v>
+        <v>3393781990</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>593925412</v>
+        <v>2344197</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>1.61</v>
       </c>
       <c r="J35" t="n">
-        <v>0.999688</v>
+        <v>1.45</v>
       </c>
       <c r="K35" t="n">
-        <v>2.836e-05</v>
+        <v>-0.04122143441758852</v>
       </c>
       <c r="L35" t="n">
-        <v>0.00284</v>
+        <v>-2.69026</v>
       </c>
       <c r="M35" t="n">
-        <v>3259575067.132162</v>
+        <v>2276129700.761904</v>
       </c>
       <c r="N35" t="n">
-        <v>3259575067.132162</v>
+        <v>5416704127.604535</v>
       </c>
       <c r="O35" t="n">
-        <v>1.65</v>
+        <v>5.64</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>45686.67436342593</v>
+        <v>46205.17638888889</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001659996057350467</v>
+        <v>0.001609846152469781</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>shiba-inu</t>
+          <t>bittensor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>shib</t>
+          <t>tao</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Shiba Inu</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5.36e-06</v>
+        <v>289.07</v>
       </c>
       <c r="F36" t="n">
-        <v>3159278566</v>
+        <v>3267924960</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>94491922</v>
+        <v>470609612</v>
       </c>
       <c r="I36" t="n">
-        <v>5.68e-06</v>
+        <v>288.6</v>
       </c>
       <c r="J36" t="n">
-        <v>5.32e-06</v>
+        <v>254.14</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.0395809831e-07</v>
+        <v>35.18</v>
       </c>
       <c r="L36" t="n">
-        <v>-1.90239</v>
+        <v>13.85522</v>
       </c>
       <c r="M36" t="n">
-        <v>589238979414596.2</v>
+        <v>11339645.9251</v>
       </c>
       <c r="N36" t="n">
-        <v>589496072572615.9</v>
+        <v>21000000</v>
       </c>
       <c r="O36" t="n">
-        <v>8.616e-05</v>
+        <v>757.6</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>44496.82980324074</v>
+        <v>45358.44833333333</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001598054922084563</v>
+        <v>0.001537014484945302</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>crypto-com-chain</t>
+          <t>global-dollar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>cro</t>
+          <t>usdg</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cronos</t>
+          <t>Global Dollar</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.058421</v>
+        <v>0.9999479999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>2905781385</v>
+        <v>3244051484</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>5958031</v>
+        <v>1028610394</v>
       </c>
       <c r="I37" t="n">
-        <v>0.060372</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>0.057552</v>
+        <v>0.99979</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.00136383075890182</v>
+        <v>-7.465353777646999e-05</v>
       </c>
       <c r="L37" t="n">
-        <v>-2.28125</v>
+        <v>-0.00747</v>
       </c>
       <c r="M37" t="n">
-        <v>49733008409.9673</v>
+        <v>3244126367.123568</v>
       </c>
       <c r="N37" t="n">
-        <v>98933025248.62096</v>
+        <v>3247147890.103568</v>
       </c>
       <c r="O37" t="n">
-        <v>0.891544</v>
+        <v>1.65</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>44523.66666666666</v>
+        <v>45686.67436342593</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001441222726069533</v>
+        <v>0.001523199245012454</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>bittensor</t>
+          <t>crypto-com-chain</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>tao</t>
+          <t>cro</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>Cronos</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>251.86</v>
+        <v>0.0636</v>
       </c>
       <c r="F38" t="n">
-        <v>2855709416</v>
+        <v>3161313953</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
       </c>
       <c r="H38" t="n">
-        <v>243526788</v>
+        <v>13759695</v>
       </c>
       <c r="I38" t="n">
-        <v>273.18</v>
+        <v>0.06450500000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>248.91</v>
+        <v>0.058538</v>
       </c>
       <c r="K38" t="n">
-        <v>-13.04437088448014</v>
+        <v>0.00494188</v>
       </c>
       <c r="L38" t="n">
-        <v>-4.92422</v>
+        <v>8.42489</v>
       </c>
       <c r="M38" t="n">
-        <v>11339645.9251</v>
+        <v>49735222151.92632</v>
       </c>
       <c r="N38" t="n">
-        <v>21000000</v>
+        <v>98935195279.49802</v>
       </c>
       <c r="O38" t="n">
-        <v>757.6</v>
+        <v>0.891544</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>45358.44833333333</v>
+        <v>44523.66666666666</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R38" t="b">
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001410244484709655</v>
+        <v>0.00147532021632738</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3018,34 +3018,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.999825</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>2801865407</v>
+        <v>2780507392</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>41046849</v>
+        <v>80675032</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0.999559</v>
+        <v>0.99975</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.000162931911100284</v>
+        <v>0.00024728</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.01629</v>
+        <v>0.02473</v>
       </c>
       <c r="M39" t="n">
-        <v>2802363980.256867</v>
+        <v>2780174063.099801</v>
       </c>
       <c r="N39" t="n">
-        <v>2802363980.256867</v>
+        <v>2780171733.0998</v>
       </c>
       <c r="O39" t="n">
         <v>1.021</v>
@@ -3054,19 +3054,19 @@
         <v>45222.61454861111</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001376932579068689</v>
+        <v>0.001254952892850162</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3085,28 +3085,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4368.6</v>
+        <v>4351.16</v>
       </c>
       <c r="F40" t="n">
-        <v>2720877354</v>
+        <v>2709821109</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>66174544</v>
+        <v>178966320</v>
       </c>
       <c r="I40" t="n">
-        <v>4376.12</v>
+        <v>4381.92</v>
       </c>
       <c r="J40" t="n">
-        <v>4365.59</v>
+        <v>4328.37</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.785671587365869</v>
+        <v>-17.7913020598844</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.10943</v>
+        <v>-0.40722</v>
       </c>
       <c r="M40" t="n">
         <v>622823.6595320001</v>
@@ -3121,622 +3121,622 @@
         <v>46050.66666666666</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001326827350470617</v>
+        <v>0.001214047749434675</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>hashnote-usyc</t>
+          <t>okb</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>usyc</t>
+          <t>okb</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Circle USYC</t>
+          <t>OKB</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1.14</v>
+        <v>123.32</v>
       </c>
       <c r="F41" t="n">
-        <v>2508311923</v>
+        <v>2591259374</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>48633818</v>
       </c>
       <c r="I41" t="n">
-        <v>1.14</v>
+        <v>124.08</v>
       </c>
       <c r="J41" t="n">
-        <v>1.14</v>
+        <v>116.9</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>6.83</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>5.86617</v>
       </c>
       <c r="M41" t="n">
-        <v>2204386896.824222</v>
+        <v>21000000</v>
       </c>
       <c r="N41" t="n">
-        <v>2204386896.824222</v>
+        <v>21000000</v>
       </c>
       <c r="O41" t="n">
-        <v>1.14</v>
+        <v>228.74</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>46283.52430555555</v>
+        <v>45934.66666666666</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001195318577043226</v>
+        <v>0.00114543776503694</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>okb</t>
+          <t>hashnote-usyc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>okb</t>
+          <t>usyc</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>OKB</t>
+          <t>Circle USYC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>116.02</v>
+        <v>1.14</v>
       </c>
       <c r="F42" t="n">
-        <v>2435395117</v>
+        <v>2508517113</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
       </c>
       <c r="H42" t="n">
-        <v>33071122</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>121.32</v>
+        <v>1.14</v>
       </c>
       <c r="J42" t="n">
-        <v>114.58</v>
+        <v>1.14</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.302428166146768</v>
+        <v>8.125e-05</v>
       </c>
       <c r="L42" t="n">
-        <v>-3.57589</v>
+        <v>0.00714</v>
       </c>
       <c r="M42" t="n">
-        <v>21000000</v>
+        <v>2204409826.472634</v>
       </c>
       <c r="N42" t="n">
-        <v>21000000</v>
+        <v>2204409826.472634</v>
       </c>
       <c r="O42" t="n">
-        <v>228.74</v>
+        <v>1.14</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>45934.66666666666</v>
+        <v>46286.54189814815</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001150206821692456</v>
+        <v>0.001097555999168354</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ripple-usd</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>rlusd</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ripple USD</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.999946</v>
+        <v>0.908653</v>
       </c>
       <c r="F43" t="n">
-        <v>2378965485</v>
+        <v>2455127227</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>194923335</v>
+        <v>29155304</v>
       </c>
       <c r="I43" t="n">
+        <v>0.922215</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.692906</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.198456</v>
+      </c>
+      <c r="L43" t="n">
+        <v>27.94389</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2708142280.000001</v>
+      </c>
+      <c r="N43" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.922215</v>
+      </c>
+      <c r="P43" s="1" t="n">
+        <v>46286.57083333333</v>
+      </c>
+      <c r="Q43" s="1" t="n">
+        <v>46286.65775462963</v>
+      </c>
+      <c r="R43" t="b">
         <v>1</v>
       </c>
-      <c r="J43" t="n">
-        <v>0.999656</v>
-      </c>
-      <c r="K43" t="n">
-        <v>-5.4896245646363e-05</v>
-      </c>
-      <c r="L43" t="n">
-        <v>-0.00549</v>
-      </c>
-      <c r="M43" t="n">
-        <v>2378997051.087201</v>
-      </c>
-      <c r="N43" t="n">
-        <v>2378997051.0872</v>
-      </c>
-      <c r="O43" t="n">
-        <v>1.073</v>
-      </c>
-      <c r="P43" s="1" t="n">
-        <v>45652.11518518518</v>
-      </c>
-      <c r="Q43" s="1" t="n">
-        <v>46285.56273148148</v>
-      </c>
-      <c r="R43" t="b">
-        <v>0</v>
-      </c>
       <c r="S43" t="n">
-        <v>0.001115295257500821</v>
+        <v>0.001066660033910618</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>blackrock-usd-institutional-digital-liquidity-fund</t>
+          <t>ripple-usd</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>buidl</t>
+          <t>rlusd</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund</t>
+          <t>Ripple USD</t>
         </is>
       </c>
       <c r="E44" t="n">
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>2329036631</v>
+        <v>2368658098</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>386949611</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0.999826</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>0.00019016</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>0.01902</v>
       </c>
       <c r="M44" t="n">
-        <v>2329036630.620448</v>
+        <v>2368466183.08722</v>
       </c>
       <c r="N44" t="n">
-        <v>2329036630.620448</v>
+        <v>2373816183.087221</v>
       </c>
       <c r="O44" t="n">
-        <v>1</v>
+        <v>1.073</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>45699.87511574074</v>
+        <v>45652.11518518518</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001084405557716216</v>
+        <v>0.001016621582705633</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ondo-us-dollar-yield</t>
+          <t>blackrock-usd-institutional-digital-liquidity-fund</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>usdy</t>
+          <t>buidl</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ondo US Dollar Yield</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>2250160386</v>
+        <v>2329036631</v>
       </c>
       <c r="G45" t="n">
         <v>44</v>
       </c>
       <c r="H45" t="n">
-        <v>3272478</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.006108838413215967</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.53277</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1963184587.959249</v>
+        <v>2329036630.620449</v>
       </c>
       <c r="N45" t="n">
-        <v>1963184587.959249</v>
+        <v>2329735522.270449</v>
       </c>
       <c r="O45" t="n">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>45377.89175925926</v>
+        <v>45699.87511574074</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.001035606850495998</v>
+        <v>0.0009936932050744745</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>ondo-us-dollar-yield</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>usdy</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Aave</t>
+          <t>Ondo US Dollar Yield</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>133.96</v>
+        <v>1.15</v>
       </c>
       <c r="F46" t="n">
-        <v>2066513911</v>
+        <v>2246038869</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>213181350</v>
+        <v>1173758</v>
       </c>
       <c r="I46" t="n">
-        <v>143.81</v>
+        <v>1.15</v>
       </c>
       <c r="J46" t="n">
-        <v>134.25</v>
+        <v>1.13</v>
       </c>
       <c r="K46" t="n">
-        <v>-8.328760258624357</v>
+        <v>0.0005346800000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>-5.85334</v>
+        <v>0.04665</v>
       </c>
       <c r="M46" t="n">
-        <v>15428127.9033128</v>
+        <v>1969763856.975529</v>
       </c>
       <c r="N46" t="n">
-        <v>16000000</v>
+        <v>1969996524.04932</v>
       </c>
       <c r="O46" t="n">
-        <v>661.6900000000001</v>
+        <v>1.26</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>44334.55554398148</v>
+        <v>45377.89175925926</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0009219894924999367</v>
+        <v>0.0009456635844226938</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ethena</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ena</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ethena</t>
+          <t>Aave</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.20318</v>
+        <v>143.63</v>
       </c>
       <c r="F47" t="n">
-        <v>2052220482</v>
+        <v>2214275421</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>802946485</v>
+        <v>363017691</v>
       </c>
       <c r="I47" t="n">
-        <v>0.219782</v>
+        <v>148.98</v>
       </c>
       <c r="J47" t="n">
-        <v>0.190993</v>
+        <v>135.04</v>
       </c>
       <c r="K47" t="n">
-        <v>0.00551982</v>
+        <v>8.01</v>
       </c>
       <c r="L47" t="n">
-        <v>2.79258</v>
+        <v>5.90774</v>
       </c>
       <c r="M47" t="n">
-        <v>10095312500</v>
+        <v>15428777.33265995</v>
       </c>
       <c r="N47" t="n">
-        <v>15000000000</v>
+        <v>16000000</v>
       </c>
       <c r="O47" t="n">
-        <v>1.52</v>
+        <v>661.6900000000001</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>45393.21892361111</v>
+        <v>44334.55554398148</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0009131465150363928</v>
+        <v>0.0009272825302680943</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ondo-finance</t>
+          <t>ethena</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ondo</t>
+          <t>ena</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ondo</t>
+          <t>Ethena</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.409013</v>
+        <v>0.216225</v>
       </c>
       <c r="F48" t="n">
-        <v>1991023913</v>
+        <v>2181612757</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>214027943</v>
+        <v>720364026</v>
       </c>
       <c r="I48" t="n">
-        <v>0.441448</v>
+        <v>0.230131</v>
       </c>
       <c r="J48" t="n">
-        <v>0.401798</v>
+        <v>0.203336</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.01473807119701176</v>
+        <v>0.01567105</v>
       </c>
       <c r="L48" t="n">
-        <v>-3.478</v>
+        <v>7.81387</v>
       </c>
       <c r="M48" t="n">
-        <v>4869330647</v>
+        <v>10095312500</v>
       </c>
       <c r="N48" t="n">
-        <v>10000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="O48" t="n">
-        <v>2.14</v>
+        <v>1.52</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>45641.69166666667</v>
+        <v>45393.21892361111</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0008752857693389669</v>
+        <v>0.0009083811126443688</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>aster-2</t>
+          <t>ondo-finance</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>aster</t>
+          <t>ondo</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Ondo</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.728447</v>
+        <v>0.444165</v>
       </c>
       <c r="F49" t="n">
-        <v>1969587215</v>
+        <v>2161052269</v>
       </c>
       <c r="G49" t="n">
         <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>143403554</v>
+        <v>291126477</v>
       </c>
       <c r="I49" t="n">
-        <v>0.770739</v>
+        <v>0.458235</v>
       </c>
       <c r="J49" t="n">
-        <v>0.72988</v>
+        <v>0.415353</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.03539861755666773</v>
+        <v>0.03020456</v>
       </c>
       <c r="L49" t="n">
-        <v>-4.63427</v>
+        <v>7.29649</v>
       </c>
       <c r="M49" t="n">
-        <v>2704071066.799731</v>
+        <v>4869330647</v>
       </c>
       <c r="N49" t="n">
-        <v>7799908028.129959</v>
+        <v>10000000000</v>
       </c>
       <c r="O49" t="n">
-        <v>2.41</v>
+        <v>2.14</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>45924.13766203704</v>
+        <v>45641.69166666667</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R49" t="b">
         <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0008620234347860199</v>
+        <v>0.0008964830515971866</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3755,28 +3755,28 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.594839</v>
+        <v>0.642248</v>
       </c>
       <c r="F50" t="n">
-        <v>1964424504</v>
+        <v>2119720789</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>34962814</v>
+        <v>46036318</v>
       </c>
       <c r="I50" t="n">
-        <v>0.644878</v>
+        <v>0.638996</v>
       </c>
       <c r="J50" t="n">
-        <v>0.585395</v>
+        <v>0.600169</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.03131049210115233</v>
+        <v>0.04491815</v>
       </c>
       <c r="L50" t="n">
-        <v>-5.00048</v>
+        <v>7.51982</v>
       </c>
       <c r="M50" t="n">
         <v>3302294382.53684</v>
@@ -3791,488 +3791,488 @@
         <v>45938.71164351852</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R50" t="b">
         <v>1</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0008588293980700023</v>
+        <v>0.0008725651138415076</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>pax-gold</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>paxg</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PAX Gold</t>
+          <t>Pepe</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4359.57</v>
+        <v>5.03e-06</v>
       </c>
       <c r="F51" t="n">
-        <v>1894234710</v>
+        <v>2102717236</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>58008894</v>
+        <v>813645807</v>
       </c>
       <c r="I51" t="n">
-        <v>4367.08</v>
+        <v>4.87e-06</v>
       </c>
       <c r="J51" t="n">
-        <v>4358.71</v>
+        <v>3.92e-06</v>
       </c>
       <c r="K51" t="n">
-        <v>-6.34483767065467</v>
+        <v>1.07e-06</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.14533</v>
+        <v>27.03744</v>
       </c>
       <c r="M51" t="n">
-        <v>434499.367539</v>
+        <v>420690000000000</v>
       </c>
       <c r="N51" t="n">
-        <v>434499.367539</v>
+        <v>420690000000000</v>
       </c>
       <c r="O51" t="n">
-        <v>5619.09</v>
+        <v>2.803e-05</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>46050.93814814815</v>
+        <v>45635.35457175926</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0008154047750132962</v>
+        <v>0.000862725400328239</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>aster-2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>aster</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.00404864</v>
+        <v>0.7507239999999999</v>
       </c>
       <c r="F52" t="n">
-        <v>1893132177</v>
+        <v>2035419904</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>127290135</v>
+        <v>176946024</v>
       </c>
       <c r="I52" t="n">
-        <v>0.00426634</v>
+        <v>0.766236</v>
       </c>
       <c r="J52" t="n">
-        <v>0.00391748</v>
+        <v>0.732133</v>
       </c>
       <c r="K52" t="n">
-        <v>-9.0381777523358e-05</v>
+        <v>0.02004207</v>
       </c>
       <c r="L52" t="n">
-        <v>-2.18365</v>
+        <v>2.74293</v>
       </c>
       <c r="M52" t="n">
-        <v>467477309368.556</v>
+        <v>2710487455.649731</v>
       </c>
       <c r="N52" t="n">
-        <v>832984570267.5187</v>
+        <v>7795741639.279952</v>
       </c>
       <c r="O52" t="n">
-        <v>0.00881908</v>
+        <v>2.41</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>45914.36296296296</v>
+        <v>45924.13766203704</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R52" t="b">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0008147226661595135</v>
+        <v>0.0008237813945026729</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>polkadot</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>dot</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1.095</v>
+        <v>0.00435338</v>
       </c>
       <c r="F53" t="n">
-        <v>1865994513</v>
+        <v>2030520104</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>176284533</v>
+        <v>184922999</v>
       </c>
       <c r="I53" t="n">
-        <v>1.14</v>
+        <v>0.00451054</v>
       </c>
       <c r="J53" t="n">
-        <v>1.073</v>
+        <v>0.00407465</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.03251862337215128</v>
+        <v>0.00027591</v>
       </c>
       <c r="L53" t="n">
-        <v>-2.88381</v>
+        <v>6.7666</v>
       </c>
       <c r="M53" t="n">
-        <v>1703621352.353134</v>
+        <v>467279734243.4806</v>
       </c>
       <c r="N53" t="n">
-        <v>1703649304.443802</v>
+        <v>832769967768.4836</v>
       </c>
       <c r="O53" t="n">
-        <v>54.98</v>
+        <v>0.00881908</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>44504.25704861111</v>
+        <v>45914.36296296296</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" t="n">
-        <v>0.000797933290344569</v>
+        <v>0.0008209459501533471</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>world-liberty-financial</t>
+          <t>polkadot</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>wlfi</t>
+          <t>dot</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>World Liberty Financial</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.058161</v>
+        <v>1.18</v>
       </c>
       <c r="F54" t="n">
-        <v>1848511633</v>
+        <v>2017115893</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>28571333</v>
+        <v>266894098</v>
       </c>
       <c r="I54" t="n">
-        <v>0.059403</v>
+        <v>1.2</v>
       </c>
       <c r="J54" t="n">
-        <v>0.05732</v>
+        <v>1.11</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.00089482964559788</v>
+        <v>0.076651</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.51522</v>
+        <v>6.92083</v>
       </c>
       <c r="M54" t="n">
-        <v>31777404701</v>
+        <v>1703808907.243623</v>
       </c>
       <c r="N54" t="n">
-        <v>100000000000</v>
+        <v>1703819243.637835</v>
       </c>
       <c r="O54" t="n">
-        <v>0.331336</v>
+        <v>54.98</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>45901.18065972222</v>
+        <v>44504.25704861111</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0007871170814532076</v>
+        <v>0.0008131891244998261</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>Morpho</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.664219</v>
+        <v>2.75</v>
       </c>
       <c r="F55" t="n">
-        <v>1778401615</v>
+        <v>1919720910</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>15397948</v>
+        <v>52265765</v>
       </c>
       <c r="I55" t="n">
-        <v>0.830167</v>
+        <v>2.84</v>
       </c>
       <c r="J55" t="n">
-        <v>0.5676020000000001</v>
+        <v>2.52</v>
       </c>
       <c r="K55" t="n">
-        <v>0.088199</v>
+        <v>0.227306</v>
       </c>
       <c r="L55" t="n">
-        <v>15.31172</v>
+        <v>9.02125</v>
       </c>
       <c r="M55" t="n">
-        <v>2708142280.000001</v>
+        <v>699207451.3256872</v>
       </c>
       <c r="N55" t="n">
-        <v>10000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="O55" t="n">
-        <v>0.830167</v>
+        <v>4.17</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>46285.43854166667</v>
+        <v>45674.19883101852</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R55" t="b">
         <v>1</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0007437418137590344</v>
+        <v>0.0007568280374758575</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>pax-gold</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>paxg</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Morpho</t>
+          <t>PAX Gold</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2.49</v>
+        <v>4347.76</v>
       </c>
       <c r="F56" t="n">
-        <v>1742127600</v>
+        <v>1889049810</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>27816998</v>
+        <v>160372105</v>
       </c>
       <c r="I56" t="n">
-        <v>2.74</v>
+        <v>4372.34</v>
       </c>
       <c r="J56" t="n">
-        <v>2.48</v>
+        <v>4326.12</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.2377347840652968</v>
+        <v>-11.95432789098686</v>
       </c>
       <c r="L56" t="n">
-        <v>-8.70748</v>
+        <v>-0.2742</v>
       </c>
       <c r="M56" t="n">
-        <v>698911943.4172602</v>
+        <v>434499.367539</v>
       </c>
       <c r="N56" t="n">
-        <v>1000000000</v>
+        <v>434499.367539</v>
       </c>
       <c r="O56" t="n">
-        <v>4.17</v>
+        <v>5619.09</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>45674.19883101852</v>
+        <v>46050.93814814815</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0007213000122041203</v>
+        <v>0.0007390791095231636</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>world-liberty-financial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>wlfi</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Pepe</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3.96e-06</v>
+        <v>0.05751</v>
       </c>
       <c r="F57" t="n">
-        <v>1667708170</v>
+        <v>1827430362</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>530426959</v>
+        <v>50977157</v>
       </c>
       <c r="I57" t="n">
-        <v>4.31e-06</v>
+        <v>0.05868</v>
       </c>
       <c r="J57" t="n">
-        <v>3.8e-06</v>
+        <v>0.057433</v>
       </c>
       <c r="K57" t="n">
-        <v>1.55684e-07</v>
+        <v>-0.000690303918718715</v>
       </c>
       <c r="L57" t="n">
-        <v>4.08743</v>
+        <v>-1.18608</v>
       </c>
       <c r="M57" t="n">
-        <v>420690000000000</v>
+        <v>31777471043</v>
       </c>
       <c r="N57" t="n">
-        <v>420690000000000</v>
+        <v>100000000000</v>
       </c>
       <c r="O57" t="n">
-        <v>2.803e-05</v>
+        <v>0.331336</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>45635.35457175926</v>
+        <v>45901.18065972222</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R57" t="b">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0006752586219723022</v>
+        <v>0.0007034208141559688</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4291,31 +4291,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.068407</v>
+        <v>0.072577</v>
       </c>
       <c r="F58" t="n">
-        <v>1602711159</v>
+        <v>1699069436</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>11164701</v>
+        <v>17930234</v>
       </c>
       <c r="I58" t="n">
-        <v>0.070019</v>
+        <v>0.07318</v>
       </c>
       <c r="J58" t="n">
-        <v>0.067327</v>
+        <v>0.068775</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.000703844532935427</v>
+        <v>0.00370732</v>
       </c>
       <c r="L58" t="n">
-        <v>-1.01843</v>
+        <v>5.38306</v>
       </c>
       <c r="M58" t="n">
-        <v>23428622590.8406</v>
+        <v>23426953149.00353</v>
       </c>
       <c r="N58" t="n">
         <v>23459804203.60596</v>
@@ -4327,421 +4327,421 @@
         <v>45630.09302083333</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0006350466404057575</v>
+        <v>0.0006291401777420459</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>htx-dao</t>
+          <t>internet-computer</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>htx</t>
+          <t>icp</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HTX DAO</t>
+          <t>Internet Computer</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1.71e-06</v>
+        <v>2.95</v>
       </c>
       <c r="F59" t="n">
-        <v>1539312839</v>
+        <v>1643500300</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>5564147</v>
+        <v>89056182</v>
       </c>
       <c r="I59" t="n">
-        <v>1.72e-06</v>
+        <v>3.04</v>
       </c>
       <c r="J59" t="n">
-        <v>1.7e-06</v>
+        <v>2.81</v>
       </c>
       <c r="K59" t="n">
-        <v>9.069999999999999e-09</v>
+        <v>0.15801</v>
       </c>
       <c r="L59" t="n">
-        <v>0.53218</v>
+        <v>5.65301</v>
       </c>
       <c r="M59" t="n">
-        <v>898232728634017.2</v>
+        <v>556899589.1864374</v>
       </c>
       <c r="N59" t="n">
-        <v>898232728634017.2</v>
+        <v>556899589.1864374</v>
       </c>
       <c r="O59" t="n">
-        <v>3.75e-06</v>
+        <v>700.65</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>45629.67800925926</v>
+        <v>44326.33741898148</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R59" t="b">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0005958237279061364</v>
+        <v>0.0005969831116029949</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>internet-computer</t>
+          <t>worldcoin-wld</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>icp</t>
+          <t>wld</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Internet Computer</t>
+          <t>Worldcoin</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2.76</v>
+        <v>0.440412</v>
       </c>
       <c r="F60" t="n">
-        <v>1535872586</v>
+        <v>1602016980</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>55899817</v>
+        <v>267402589</v>
       </c>
       <c r="I60" t="n">
-        <v>2.97</v>
+        <v>0.457331</v>
       </c>
       <c r="J60" t="n">
-        <v>2.74</v>
+        <v>0.429347</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.1079435132927644</v>
+        <v>0.01056067</v>
       </c>
       <c r="L60" t="n">
-        <v>-3.76626</v>
+        <v>2.45682</v>
       </c>
       <c r="M60" t="n">
-        <v>556905075.050398</v>
+        <v>3645494676.034653</v>
       </c>
       <c r="N60" t="n">
-        <v>556905520.6385173</v>
+        <v>10000000000</v>
       </c>
       <c r="O60" t="n">
-        <v>700.65</v>
+        <v>11.74</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>44326.33741898148</v>
+        <v>45360.67409722223</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0005936953317215757</v>
+        <v>0.0005729773062057792</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>arb</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>USDD</t>
+          <t>Arbitrum</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.998409</v>
+        <v>0.230271</v>
       </c>
       <c r="F61" t="n">
-        <v>1530501563</v>
+        <v>1559573761</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>1710078</v>
+        <v>553235680</v>
       </c>
       <c r="I61" t="n">
-        <v>0.999278</v>
+        <v>0.247068</v>
       </c>
       <c r="J61" t="n">
-        <v>0.997703</v>
+        <v>0.203259</v>
       </c>
       <c r="K61" t="n">
-        <v>0.0003523</v>
+        <v>0.02840191</v>
       </c>
       <c r="L61" t="n">
-        <v>0.0353</v>
+        <v>14.0695</v>
       </c>
       <c r="M61" t="n">
-        <v>1532863245</v>
+        <v>6785574605</v>
       </c>
       <c r="N61" t="n">
-        <v>1534240769</v>
+        <v>10000000000</v>
       </c>
       <c r="O61" t="n">
-        <v>1.24</v>
+        <v>2.39</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>46212.39942129629</v>
+        <v>45303.18748842592</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0005903724177206613</v>
+        <v>0.0005484160209531665</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>worldcoin-wld</t>
+          <t>htx-dao</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>wld</t>
+          <t>htx</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Worldcoin</t>
+          <t>HTX DAO</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.418505</v>
+        <v>1.72e-06</v>
       </c>
       <c r="F62" t="n">
-        <v>1506775772</v>
+        <v>1546353942</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>179127352</v>
+        <v>9478676</v>
       </c>
       <c r="I62" t="n">
-        <v>0.440425</v>
+        <v>1.72e-06</v>
       </c>
       <c r="J62" t="n">
-        <v>0.417599</v>
+        <v>1.7e-06</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.009340951957156951</v>
+        <v>2.336e-09</v>
       </c>
       <c r="L62" t="n">
-        <v>-2.18325</v>
+        <v>0.13596</v>
       </c>
       <c r="M62" t="n">
-        <v>3601490383.124579</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="N62" t="n">
-        <v>10000000000</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="O62" t="n">
-        <v>11.74</v>
+        <v>3.75e-06</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>45360.67409722223</v>
+        <v>45629.67800925926</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005756938801130827</v>
+        <v>0.0005407659003191282</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>arb</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Arbitrum</t>
+          <t>USDD</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.208887</v>
+        <v>0.998678</v>
       </c>
       <c r="F63" t="n">
-        <v>1417030807</v>
+        <v>1509307672</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>333916946</v>
+        <v>13809872</v>
       </c>
       <c r="I63" t="n">
-        <v>0.218059</v>
+        <v>0.999596</v>
       </c>
       <c r="J63" t="n">
-        <v>0.20086</v>
+        <v>0.99781</v>
       </c>
       <c r="K63" t="n">
-        <v>0.00031019</v>
+        <v>0.00053826</v>
       </c>
       <c r="L63" t="n">
-        <v>0.14872</v>
+        <v>0.05393</v>
       </c>
       <c r="M63" t="n">
-        <v>6785574605</v>
+        <v>1511273305</v>
       </c>
       <c r="N63" t="n">
-        <v>10000000000</v>
+        <v>1511042343</v>
       </c>
       <c r="O63" t="n">
-        <v>2.39</v>
+        <v>1.24</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>45303.18748842592</v>
+        <v>46212.39942129629</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0005201709749402556</v>
+        <v>0.0005193277524487862</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>spiko-amundi-overnight-swap-fund-eur</t>
+          <t>venice-token</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>eursafo</t>
+          <t>vvv</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Spiko Amundi Overnight Swap Fund (EUR)</t>
+          <t>Venice Token</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1.16</v>
+        <v>31.31</v>
       </c>
       <c r="F64" t="n">
-        <v>1407771011</v>
+        <v>1505283839</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>137801425</v>
       </c>
       <c r="I64" t="n">
-        <v>1.16</v>
+        <v>34.53</v>
       </c>
       <c r="J64" t="n">
-        <v>1.16</v>
+        <v>27.73</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>8.005699999999999</v>
       </c>
       <c r="M64" t="n">
-        <v>1210660472.36437</v>
+        <v>48098269.92982138</v>
       </c>
       <c r="N64" t="n">
-        <v>1210660472.36437</v>
+        <v>81020526.78963831</v>
       </c>
       <c r="O64" t="n">
-        <v>1.18</v>
+        <v>34.53</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>46255.48263888889</v>
+        <v>46286.34548611111</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0005144421769488839</v>
+        <v>0.0005169992177040046</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4760,28 +4760,28 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="F65" t="n">
-        <v>1393178318</v>
+        <v>1484368859</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>10302086</v>
+        <v>21371401</v>
       </c>
       <c r="I65" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="J65" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.04851798921705774</v>
+        <v>0.105322</v>
       </c>
       <c r="L65" t="n">
-        <v>-2.37987</v>
+        <v>5.22639</v>
       </c>
       <c r="M65" t="n">
         <v>699992029.6481038</v>
@@ -4796,19 +4796,19 @@
         <v>45653.15375</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0005054140525337128</v>
+        <v>0.0005048960171943381</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4827,34 +4827,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.999777</v>
+        <v>0.999817</v>
       </c>
       <c r="F66" t="n">
-        <v>1392856034</v>
+        <v>1412321040</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
       </c>
       <c r="H66" t="n">
-        <v>99747718</v>
+        <v>232093814</v>
       </c>
       <c r="I66" t="n">
         <v>1</v>
       </c>
       <c r="J66" t="n">
-        <v>0.999536</v>
+        <v>0.999466</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.000133328224996121</v>
+        <v>6.242e-05</v>
       </c>
       <c r="L66" t="n">
-        <v>-0.01333</v>
+        <v>0.00624</v>
       </c>
       <c r="M66" t="n">
-        <v>1393129007.8</v>
+        <v>1412429007.8</v>
       </c>
       <c r="N66" t="n">
-        <v>1393129007.8</v>
+        <v>1412429007.8</v>
       </c>
       <c r="O66" t="n">
         <v>1.008</v>
@@ -4863,86 +4863,86 @@
         <v>46058.54591435185</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0005052146636992448</v>
+        <v>0.0004632029723221382</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>venice-token</t>
+          <t>spiko-amundi-overnight-swap-fund-eur</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>vvv</t>
+          <t>eursafo</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Venice Token</t>
+          <t>Spiko Amundi Overnight Swap Fund (EUR)</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>28.99</v>
+        <v>1.16</v>
       </c>
       <c r="F67" t="n">
-        <v>1390249492</v>
+        <v>1406563294</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
       </c>
       <c r="H67" t="n">
-        <v>78077222</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>29.87</v>
+        <v>1.16</v>
       </c>
       <c r="J67" t="n">
-        <v>25.03</v>
+        <v>1.16</v>
       </c>
       <c r="K67" t="n">
-        <v>0.981791</v>
+        <v>-0.000997568167990126</v>
       </c>
       <c r="L67" t="n">
-        <v>3.50519</v>
+        <v>-0.08579000000000001</v>
       </c>
       <c r="M67" t="n">
-        <v>48066966.41405931</v>
+        <v>1210660472.36437</v>
       </c>
       <c r="N67" t="n">
-        <v>81013661.93979919</v>
+        <v>1210660472.36437</v>
       </c>
       <c r="O67" t="n">
-        <v>29.87</v>
+        <v>1.18</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>46285.54143518519</v>
+        <v>46255.48263888889</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0005036020631004815</v>
+        <v>0.0004598710468638433</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4961,34 +4961,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.999987</v>
+        <v>0.9997509999999999</v>
       </c>
       <c r="F68" t="n">
-        <v>1383803613</v>
+        <v>1404123443</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>54160877</v>
+        <v>42030632</v>
       </c>
       <c r="I68" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
-        <v>0.999735</v>
+        <v>0.999719</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.000121582571536494</v>
+        <v>-0.000266318963444978</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.01216</v>
+        <v>-0.02663</v>
       </c>
       <c r="M68" t="n">
-        <v>1383787304.97</v>
+        <v>1403784804.97</v>
       </c>
       <c r="N68" t="n">
-        <v>1383787304.97</v>
+        <v>1403784804.97</v>
       </c>
       <c r="O68" t="n">
         <v>1.002</v>
@@ -4997,689 +4997,689 @@
         <v>46092.00303240741</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0004996141632949323</v>
+        <v>0.0004584591399021005</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>falcon-finance</t>
+          <t>ethereum-classic</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>usdf</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Falcon USD</t>
+          <t>Ethereum Classic</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.995828</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="F69" t="n">
-        <v>1371297189</v>
+        <v>1387516750</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>539321</v>
+        <v>73190996</v>
       </c>
       <c r="I69" t="n">
-        <v>0.996548</v>
+        <v>8.85</v>
       </c>
       <c r="J69" t="n">
-        <v>0.994584</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>0.00021359</v>
+        <v>0.351076</v>
       </c>
       <c r="L69" t="n">
-        <v>0.02145</v>
+        <v>4.16573</v>
       </c>
       <c r="M69" t="n">
-        <v>1377031442.049245</v>
+        <v>158238312.7479364</v>
       </c>
       <c r="N69" t="n">
-        <v>1377031442.049245</v>
+        <v>158238719.9927364</v>
       </c>
       <c r="O69" t="n">
-        <v>1.075</v>
+        <v>167.09</v>
       </c>
       <c r="P69" s="1" t="n">
-        <v>45785.55951388889</v>
+        <v>44322.44053240741</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0004918767599341624</v>
+        <v>0.0004488490836084069</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>falcon-finance</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>usdf</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>BFUSD</t>
+          <t>Falcon USD</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.999651</v>
+        <v>0.996047</v>
       </c>
       <c r="F70" t="n">
-        <v>1319550427</v>
+        <v>1371628457</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>7639533</v>
+        <v>899679</v>
       </c>
       <c r="I70" t="n">
-        <v>0.999769</v>
+        <v>0.996566</v>
       </c>
       <c r="J70" t="n">
-        <v>0.999301</v>
+        <v>0.995507</v>
       </c>
       <c r="K70" t="n">
-        <v>-5.9185672644402e-05</v>
+        <v>0.00023299</v>
       </c>
       <c r="L70" t="n">
-        <v>-0.00592</v>
+        <v>0.0234</v>
       </c>
       <c r="M70" t="n">
-        <v>1320000000</v>
+        <v>1377035569.737884</v>
       </c>
       <c r="N70" t="n">
-        <v>1320000000</v>
+        <v>1377035569.737884</v>
       </c>
       <c r="O70" t="n">
-        <v>1.007</v>
+        <v>1.075</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>45940.56990740741</v>
+        <v>45785.55951388889</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R70" t="b">
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0004598623671542794</v>
+        <v>0.0004396547551445341</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ethereum-classic</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Ethereum Classic</t>
+          <t>BFUSD</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>8.25</v>
+        <v>0.999924</v>
       </c>
       <c r="F71" t="n">
-        <v>1305311435</v>
+        <v>1319931512</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>75227585</v>
+        <v>4921075</v>
       </c>
       <c r="I71" t="n">
-        <v>8.77</v>
+        <v>0.999837</v>
       </c>
       <c r="J71" t="n">
-        <v>8.220000000000001</v>
+        <v>0.99952</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.1553929350739427</v>
+        <v>0.00035509</v>
       </c>
       <c r="L71" t="n">
-        <v>-1.84917</v>
+        <v>0.03552</v>
       </c>
       <c r="M71" t="n">
-        <v>158226588.0989012</v>
+        <v>1320000000</v>
       </c>
       <c r="N71" t="n">
-        <v>158227480.9245012</v>
+        <v>1320000000</v>
       </c>
       <c r="O71" t="n">
-        <v>167.09</v>
+        <v>1.007</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>44322.44053240741</v>
+        <v>45940.56990740741</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R71" t="b">
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0.00045105306846468</v>
+        <v>0.0004097384706885029</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>akedo</t>
+          <t>lighter</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ake</t>
+          <t>lit</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Akedo</t>
+          <t>Lighter</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.051878</v>
+        <v>4.98</v>
       </c>
       <c r="F72" t="n">
-        <v>1181652254</v>
+        <v>1243289462</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>138375486</v>
+        <v>96086565</v>
       </c>
       <c r="I72" t="n">
-        <v>0.146656</v>
+        <v>5.14</v>
       </c>
       <c r="J72" t="n">
-        <v>0.04596138</v>
+        <v>4.65</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.01045600252542676</v>
+        <v>0.29391</v>
       </c>
       <c r="L72" t="n">
-        <v>-16.77405</v>
+        <v>6.2781</v>
       </c>
       <c r="M72" t="n">
-        <v>22796250000</v>
+        <v>250000000</v>
       </c>
       <c r="N72" t="n">
-        <v>100000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="O72" t="n">
-        <v>0.146656</v>
+        <v>7.86</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>46285.43993055556</v>
+        <v>46021.04538194444</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R72" t="b">
         <v>1</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0003745483087780226</v>
+        <v>0.0003653868098873982</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>lighter</t>
+          <t>polygon-ecosystem-token</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>lit</t>
+          <t>pol</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Lighter</t>
+          <t>POL (ex-MATIC)</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4.72</v>
+        <v>0.113591</v>
       </c>
       <c r="F73" t="n">
-        <v>1180283855</v>
+        <v>1215803428</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>65144763</v>
+        <v>183440017</v>
       </c>
       <c r="I73" t="n">
-        <v>5.21</v>
+        <v>0.114508</v>
       </c>
       <c r="J73" t="n">
-        <v>4.58</v>
+        <v>0.104</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.4150986854558916</v>
+        <v>0.0096837</v>
       </c>
       <c r="L73" t="n">
-        <v>-8.082179999999999</v>
+        <v>9.319520000000001</v>
       </c>
       <c r="M73" t="n">
-        <v>250000000</v>
+        <v>10718173594.42111</v>
       </c>
       <c r="N73" t="n">
-        <v>1000000000</v>
+        <v>10718173594.42111</v>
       </c>
       <c r="O73" t="n">
-        <v>7.86</v>
+        <v>1.29</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>46021.04538194444</v>
+        <v>45364.45493055556</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R73" t="b">
         <v>1</v>
       </c>
       <c r="S73" t="n">
-        <v>0.000373701715457544</v>
+        <v>0.0003494810341841697</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>polygon-ecosystem-token</t>
+          <t>akedo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>pol</t>
+          <t>ake</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>POL (ex-MATIC)</t>
+          <t>Akedo</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.103521</v>
+        <v>0.052968</v>
       </c>
       <c r="F74" t="n">
-        <v>1109401167</v>
+        <v>1210389596</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>67553877</v>
+        <v>117071699</v>
       </c>
       <c r="I74" t="n">
-        <v>0.106841</v>
+        <v>0.06970899999999999</v>
       </c>
       <c r="J74" t="n">
-        <v>0.10307</v>
+        <v>0.03148813</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.001922091538787959</v>
+        <v>-0.000541111920599274</v>
       </c>
       <c r="L74" t="n">
-        <v>-1.82286</v>
+        <v>-1.01126</v>
       </c>
       <c r="M74" t="n">
-        <v>10717592108.82727</v>
+        <v>22796250000</v>
       </c>
       <c r="N74" t="n">
-        <v>10717592108.82727</v>
+        <v>100000000000</v>
       </c>
       <c r="O74" t="n">
-        <v>1.29</v>
+        <v>0.146656</v>
       </c>
       <c r="P74" s="1" t="n">
-        <v>45364.45493055556</v>
+        <v>46285.43993055556</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R74" t="b">
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0003298484166767254</v>
+        <v>0.0003463481268506867</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>gatechain-token</t>
+          <t>kaspa</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>gt</t>
+          <t>kas</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Kaspa</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>10.2</v>
+        <v>0.04256497</v>
       </c>
       <c r="F75" t="n">
-        <v>1088646020</v>
+        <v>1181593079</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
       </c>
       <c r="H75" t="n">
-        <v>3809198</v>
+        <v>22251594</v>
       </c>
       <c r="I75" t="n">
-        <v>10.64</v>
+        <v>0.04197595</v>
       </c>
       <c r="J75" t="n">
-        <v>10.06</v>
+        <v>0.0386518</v>
       </c>
       <c r="K75" t="n">
-        <v>0.090124</v>
+        <v>0.00356807</v>
       </c>
       <c r="L75" t="n">
-        <v>0.89158</v>
+        <v>9.149609999999999</v>
       </c>
       <c r="M75" t="n">
-        <v>106634608.2701089</v>
+        <v>27710766029.85906</v>
       </c>
       <c r="N75" t="n">
-        <v>118885881.9758941</v>
+        <v>27713280689.21</v>
       </c>
       <c r="O75" t="n">
-        <v>25.38</v>
+        <v>0.207411</v>
       </c>
       <c r="P75" s="1" t="n">
-        <v>45682.66666666666</v>
+        <v>45504.69498842592</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0003170077402250818</v>
+        <v>0.0003296839933334172</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>kaspa</t>
+          <t>gatechain-token</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>kas</t>
+          <t>gt</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Kaspa</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.03828229</v>
+        <v>11.04</v>
       </c>
       <c r="F76" t="n">
-        <v>1060695698</v>
+        <v>1177930690</v>
       </c>
       <c r="G76" t="n">
         <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>24304294</v>
+        <v>6827786</v>
       </c>
       <c r="I76" t="n">
-        <v>0.04084235</v>
+        <v>11.4</v>
       </c>
       <c r="J76" t="n">
-        <v>0.0376825</v>
+        <v>10.34</v>
       </c>
       <c r="K76" t="n">
-        <v>-1.2627467712453e-05</v>
+        <v>0.713846</v>
       </c>
       <c r="L76" t="n">
-        <v>-0.03297</v>
+        <v>6.91129</v>
       </c>
       <c r="M76" t="n">
-        <v>27710766029.85906</v>
+        <v>106635883.2020504</v>
       </c>
       <c r="N76" t="n">
-        <v>27711234792.36683</v>
+        <v>118887115.3090956</v>
       </c>
       <c r="O76" t="n">
-        <v>0.207411</v>
+        <v>25.38</v>
       </c>
       <c r="P76" s="1" t="n">
-        <v>45504.69498842592</v>
+        <v>45682.66666666666</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0002997155937747936</v>
+        <v>0.0003275646210743284</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>kucoin-shares</t>
+          <t>algorand</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>kcs</t>
+          <t>algo</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KuCoin</t>
+          <t>Algorand</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>7.12</v>
+        <v>0.112858</v>
       </c>
       <c r="F77" t="n">
-        <v>977040628</v>
+        <v>1018245871</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>22842987</v>
+        <v>91425780</v>
       </c>
       <c r="I77" t="n">
-        <v>7.28</v>
+        <v>0.117367</v>
       </c>
       <c r="J77" t="n">
-        <v>7.1</v>
+        <v>0.107695</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.145397866042674</v>
+        <v>-0.000398156635310759</v>
       </c>
       <c r="L77" t="n">
-        <v>-2.00022</v>
+        <v>-0.35155</v>
       </c>
       <c r="M77" t="n">
-        <v>137155021.2773955</v>
+        <v>9042435038.282944</v>
       </c>
       <c r="N77" t="n">
-        <v>142155021.2773955</v>
+        <v>9042705520.702909</v>
       </c>
       <c r="O77" t="n">
-        <v>28.83</v>
+        <v>3.56</v>
       </c>
       <c r="P77" s="1" t="n">
-        <v>44531.29832175926</v>
+        <v>43636.28563657407</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R77" t="b">
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002479603502484719</v>
+        <v>0.0002351572947127058</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>blockchain-capital</t>
+          <t>jupiter-exchange-solana</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>bcap</t>
+          <t>jup</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Blockchain Capital</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106.54</v>
+        <v>0.306944</v>
       </c>
       <c r="F78" t="n">
-        <v>970804306</v>
+        <v>1016626399</v>
       </c>
       <c r="G78" t="n">
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>126703075</v>
       </c>
       <c r="I78" t="n">
-        <v>106.54</v>
+        <v>0.317727</v>
       </c>
       <c r="J78" t="n">
-        <v>106.54</v>
+        <v>0.271277</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>0.03662334</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>13.5481</v>
       </c>
       <c r="M78" t="n">
-        <v>9112111</v>
+        <v>3319369204.37</v>
       </c>
       <c r="N78" t="n">
-        <v>9112111</v>
+        <v>6861486876.193287</v>
       </c>
       <c r="O78" t="n">
-        <v>106.54</v>
+        <v>2</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>46280.14583333334</v>
+        <v>45322.29359953704</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002441020979773476</v>
+        <v>0.0002342201293730407</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5698,34 +5698,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.084915</v>
+        <v>0.089172</v>
       </c>
       <c r="F79" t="n">
-        <v>954699581</v>
+        <v>1000832394</v>
       </c>
       <c r="G79" t="n">
         <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>4483170</v>
+        <v>8282429</v>
       </c>
       <c r="I79" t="n">
-        <v>0.08533300000000001</v>
+        <v>0.090407</v>
       </c>
       <c r="J79" t="n">
-        <v>0.083199</v>
+        <v>0.08477800000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>-1.5620016221421e-05</v>
+        <v>0.00432623</v>
       </c>
       <c r="L79" t="n">
-        <v>-0.01839</v>
+        <v>5.09892</v>
       </c>
       <c r="M79" t="n">
-        <v>11243020014.141</v>
+        <v>11243021168.581</v>
       </c>
       <c r="N79" t="n">
-        <v>17296953741.26307</v>
+        <v>17296955494.70923</v>
       </c>
       <c r="O79" t="n">
         <v>2.99</v>
@@ -5734,421 +5734,421 @@
         <v>45714.36184027778</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R79" t="b">
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002341385181931284</v>
+        <v>0.0002250803640294603</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>algorand</t>
+          <t>kucoin-shares</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>algo</t>
+          <t>kcs</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Algorand</t>
+          <t>KuCoin</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.1055</v>
+        <v>7.24</v>
       </c>
       <c r="F80" t="n">
-        <v>954315578</v>
+        <v>991808381</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>78112732</v>
+        <v>42457066</v>
       </c>
       <c r="I80" t="n">
-        <v>0.110094</v>
+        <v>7.34</v>
       </c>
       <c r="J80" t="n">
-        <v>0.09980700000000001</v>
+        <v>7.08</v>
       </c>
       <c r="K80" t="n">
-        <v>0.00589527</v>
+        <v>0.123972</v>
       </c>
       <c r="L80" t="n">
-        <v>5.91868</v>
+        <v>1.74107</v>
       </c>
       <c r="M80" t="n">
-        <v>9042435038.282944</v>
+        <v>137155021.2773955</v>
       </c>
       <c r="N80" t="n">
-        <v>9042480349.856657</v>
+        <v>142155021.2773955</v>
       </c>
       <c r="O80" t="n">
-        <v>3.56</v>
+        <v>28.83</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>43636.28563657407</v>
+        <v>44531.29832175926</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002339009453983194</v>
+        <v>0.0002198582964615814</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>just</t>
+          <t>quant-network</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>jst</t>
+          <t>qnt</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>JUST</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.114254</v>
+        <v>67.02</v>
       </c>
       <c r="F81" t="n">
-        <v>935643444</v>
+        <v>974120723</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>29647707</v>
+        <v>11479032</v>
       </c>
       <c r="I81" t="n">
-        <v>0.118997</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="J81" t="n">
-        <v>0.11362</v>
+        <v>63.8</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.002244477417203586</v>
+        <v>2.88</v>
       </c>
       <c r="L81" t="n">
-        <v>-1.92662</v>
+        <v>4.48507</v>
       </c>
       <c r="M81" t="n">
-        <v>8188743036.341737</v>
+        <v>14544176.16408117</v>
       </c>
       <c r="N81" t="n">
-        <v>8188743036.341737</v>
+        <v>14612493</v>
       </c>
       <c r="O81" t="n">
-        <v>0.193254</v>
+        <v>427.42</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>44290.85721064815</v>
+        <v>44450.05208333334</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R81" t="b">
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0002223489755974919</v>
+        <v>0.0002096227011456687</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>quant-network</t>
+          <t>blockchain-capital</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>qnt</t>
+          <t>bcap</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Blockchain Capital</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>63.8</v>
+        <v>106.54</v>
       </c>
       <c r="F82" t="n">
-        <v>928151271</v>
+        <v>970804306</v>
       </c>
       <c r="G82" t="n">
         <v>81</v>
       </c>
       <c r="H82" t="n">
-        <v>7900603</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>66.45</v>
+        <v>106.54</v>
       </c>
       <c r="J82" t="n">
-        <v>63.37</v>
+        <v>106.54</v>
       </c>
       <c r="K82" t="n">
-        <v>-1.646758330233091</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>-2.5161</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>14544176.16408117</v>
+        <v>9112111</v>
       </c>
       <c r="N82" t="n">
-        <v>14612493</v>
+        <v>9112111</v>
       </c>
       <c r="O82" t="n">
-        <v>427.42</v>
+        <v>106.54</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>44450.05208333334</v>
+        <v>46280.14583333334</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R82" t="b">
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0002177137605632288</v>
+        <v>0.0002077035379466282</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>pancakeswap-token</t>
+          <t>cosmos</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>Cosmos Hub</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2.51</v>
+        <v>1.8</v>
       </c>
       <c r="F83" t="n">
-        <v>918844835</v>
+        <v>957099766</v>
       </c>
       <c r="G83" t="n">
         <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>134840819</v>
+        <v>77080955</v>
       </c>
       <c r="I83" t="n">
-        <v>2.5</v>
+        <v>1.82</v>
       </c>
       <c r="J83" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="K83" t="n">
-        <v>0.083675</v>
+        <v>0.06481000000000001</v>
       </c>
       <c r="L83" t="n">
-        <v>3.45209</v>
+        <v>3.73722</v>
       </c>
       <c r="M83" t="n">
-        <v>366600236.5776587</v>
+        <v>531968735.793199</v>
       </c>
       <c r="N83" t="n">
-        <v>378248721.8225635</v>
+        <v>531981425.106379</v>
       </c>
       <c r="O83" t="n">
-        <v>43.96</v>
+        <v>43.84</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>44316.08914351852</v>
+        <v>44458.66666666666</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0002119561076015837</v>
+        <v>0.0001997729161859215</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jupiter-exchange-solana</t>
+          <t>just</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>jup</t>
+          <t>jst</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>JUST</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.269469</v>
+        <v>0.113382</v>
       </c>
       <c r="F84" t="n">
-        <v>894616196</v>
+        <v>928875168</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>79315136</v>
+        <v>41477573</v>
       </c>
       <c r="I84" t="n">
-        <v>0.286863</v>
+        <v>0.116713</v>
       </c>
       <c r="J84" t="n">
-        <v>0.266477</v>
+        <v>0.111332</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.00602656052099293</v>
+        <v>-0.002727350903736575</v>
       </c>
       <c r="L84" t="n">
-        <v>-2.18753</v>
+        <v>-2.34894</v>
       </c>
       <c r="M84" t="n">
-        <v>3319369204.37</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="N84" t="n">
-        <v>6861486880.683001</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="O84" t="n">
-        <v>2</v>
+        <v>0.193254</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>45322.29359953704</v>
+        <v>44290.85721064815</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R84" t="b">
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.000196966470849665</v>
+        <v>0.0001834397440337735</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>cosmos</t>
+          <t>render-token</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>render</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Cosmos Hub</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="F85" t="n">
-        <v>894351921</v>
+        <v>919580013</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>48009775</v>
+        <v>170326835</v>
       </c>
       <c r="I85" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="J85" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="K85" t="n">
-        <v>-0.0521794658494894</v>
+        <v>0.216485</v>
       </c>
       <c r="L85" t="n">
-        <v>-3.00901</v>
+        <v>13.88918</v>
       </c>
       <c r="M85" t="n">
-        <v>531759588.764152</v>
+        <v>518776241.2826915</v>
       </c>
       <c r="N85" t="n">
-        <v>531776444.345809</v>
+        <v>533536414.5626915</v>
       </c>
       <c r="O85" t="n">
-        <v>43.84</v>
+        <v>13.53</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>44458.66666666666</v>
+        <v>45368.35444444444</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001968029706938117</v>
+        <v>0.0001780607704591667</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6167,28 +6167,28 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.819611</v>
+        <v>0.8806079999999999</v>
       </c>
       <c r="F86" t="n">
-        <v>819967082</v>
+        <v>879827644</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
       </c>
       <c r="H86" t="n">
-        <v>3746975</v>
+        <v>7817219</v>
       </c>
       <c r="I86" t="n">
-        <v>0.849463</v>
+        <v>0.87577</v>
       </c>
       <c r="J86" t="n">
-        <v>0.817512</v>
+        <v>0.819816</v>
       </c>
       <c r="K86" t="n">
-        <v>-0.02646533128100348</v>
+        <v>0.060156</v>
       </c>
       <c r="L86" t="n">
-        <v>-3.12801</v>
+        <v>7.33199</v>
       </c>
       <c r="M86" t="n">
         <v>1000000000</v>
@@ -6203,220 +6203,220 @@
         <v>44328.27623842593</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001507829810253883</v>
+        <v>0.0001550566417083263</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>render-token</t>
+          <t>pancakeswap-token</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>render</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1.53</v>
+        <v>2.61</v>
       </c>
       <c r="F87" t="n">
-        <v>793606737</v>
+        <v>832854645</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>52882448</v>
+        <v>136695825</v>
       </c>
       <c r="I87" t="n">
-        <v>1.61</v>
+        <v>2.62</v>
       </c>
       <c r="J87" t="n">
-        <v>1.51</v>
+        <v>2.45</v>
       </c>
       <c r="K87" t="n">
-        <v>-0.07782713717880529</v>
+        <v>0.151086</v>
       </c>
       <c r="L87" t="n">
-        <v>-4.84117</v>
+        <v>6.13663</v>
       </c>
       <c r="M87" t="n">
-        <v>518776241.2826915</v>
+        <v>318981673.778035</v>
       </c>
       <c r="N87" t="n">
-        <v>533536414.5626915</v>
+        <v>330627631.6127986</v>
       </c>
       <c r="O87" t="n">
-        <v>13.53</v>
+        <v>43.96</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>45368.35444444444</v>
+        <v>44316.08914351852</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R87" t="b">
         <v>1</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001344745125140015</v>
+        <v>0.0001278740374009177</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>filecoin</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>fil</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Spiko EU T-Bills Money Market Fund</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1.22</v>
+        <v>0.968076</v>
       </c>
       <c r="F88" t="n">
-        <v>791533121</v>
+        <v>803262272</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>201765623</v>
       </c>
       <c r="I88" t="n">
-        <v>1.22</v>
+        <v>1.015</v>
       </c>
       <c r="J88" t="n">
-        <v>1.22</v>
+        <v>0.926796</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>0.04226669</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>4.56538</v>
       </c>
       <c r="M88" t="n">
-        <v>651037363.70003</v>
+        <v>830669925</v>
       </c>
       <c r="N88" t="n">
-        <v>651037363.70003</v>
+        <v>1957036618</v>
       </c>
       <c r="O88" t="n">
-        <v>1.26</v>
+        <v>236.84</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>46049.54175925926</v>
+        <v>44287.22894675926</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R88" t="b">
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>0.000133191619545768</v>
+        <v>0.0001107493533717748</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>injective-protocol</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>inj</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Injective</t>
+          <t>Spiko EU T-Bills Money Market Fund</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>7.84</v>
+        <v>1.21</v>
       </c>
       <c r="F89" t="n">
-        <v>784086286</v>
+        <v>784718961</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>229517357</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>8.32</v>
+        <v>1.22</v>
       </c>
       <c r="J89" t="n">
-        <v>7.36</v>
+        <v>1.21</v>
       </c>
       <c r="K89" t="n">
-        <v>0.182582</v>
+        <v>-0.000973066503648035</v>
       </c>
       <c r="L89" t="n">
-        <v>2.38357</v>
+        <v>-0.08003</v>
       </c>
       <c r="M89" t="n">
-        <v>100000000</v>
+        <v>645949689.8613</v>
       </c>
       <c r="N89" t="n">
-        <v>100000000</v>
+        <v>645949689.8613</v>
       </c>
       <c r="O89" t="n">
-        <v>52.62</v>
+        <v>1.26</v>
       </c>
       <c r="P89" s="1" t="n">
-        <v>45365.29608796296</v>
+        <v>46049.54175925926</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R89" t="b">
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.000128584453967814</v>
+        <v>0.0001000186038732764</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6438,7 +6438,7 @@
         <v>1.05</v>
       </c>
       <c r="F90" t="n">
-        <v>776469917</v>
+        <v>776845619</v>
       </c>
       <c r="G90" t="n">
         <v>89</v>
@@ -6453,10 +6453,10 @@
         <v>1.05</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>0.000508</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>0.04839</v>
       </c>
       <c r="M90" t="n">
         <v>739569820.670837</v>
@@ -6468,558 +6468,558 @@
         <v>1.05</v>
       </c>
       <c r="P90" s="1" t="n">
-        <v>46283.36122685186</v>
+        <v>46286.30578703704</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>0.0001238724020577346</v>
+        <v>9.546241319524659e-05</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>filecoin</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>Dash</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.926125</v>
+        <v>60.37</v>
       </c>
       <c r="F91" t="n">
-        <v>769342018</v>
+        <v>774060503</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>257140423</v>
+        <v>161994185</v>
       </c>
       <c r="I91" t="n">
-        <v>1.13</v>
+        <v>61.42</v>
       </c>
       <c r="J91" t="n">
-        <v>0.9441659999999999</v>
+        <v>54.89</v>
       </c>
       <c r="K91" t="n">
-        <v>-0.06729471258352648</v>
+        <v>5.44</v>
       </c>
       <c r="L91" t="n">
-        <v>-6.77405</v>
+        <v>9.900130000000001</v>
       </c>
       <c r="M91" t="n">
-        <v>830607045</v>
+        <v>12841975.17033605</v>
       </c>
       <c r="N91" t="n">
-        <v>1957039188</v>
+        <v>12841989.85954539</v>
       </c>
       <c r="O91" t="n">
-        <v>236.84</v>
+        <v>1493.59</v>
       </c>
       <c r="P91" s="1" t="n">
-        <v>44287.22894675926</v>
+        <v>43088.66666666666</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R91" t="b">
         <v>1</v>
       </c>
       <c r="S91" t="n">
-        <v>0.000119462553992626</v>
+        <v>9.385070630426795e-05</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
+          <t>injective-protocol</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ustb</t>
+          <t>inj</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Invesco Short Duration US Government Securities Fund</t>
+          <t>Injective</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>11.22</v>
+        <v>7.71</v>
       </c>
       <c r="F92" t="n">
-        <v>747343793</v>
+        <v>769674354</v>
       </c>
       <c r="G92" t="n">
         <v>91</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>187091879</v>
       </c>
       <c r="I92" t="n">
-        <v>11.22</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J92" t="n">
-        <v>11.22</v>
+        <v>7.58</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>-0.2849914879713022</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>-3.56668</v>
       </c>
       <c r="M92" t="n">
-        <v>66633634.978314</v>
+        <v>100000000</v>
       </c>
       <c r="N92" t="n">
-        <v>66633634.978314</v>
+        <v>100000000</v>
       </c>
       <c r="O92" t="n">
-        <v>11.22</v>
+        <v>52.62</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>46283.55902777778</v>
+        <v>45365.29608796296</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R92" t="b">
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>0.0001058528171049296</v>
+        <v>9.131250445983524e-05</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>vechain</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>vet</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Dash</t>
+          <t>VeChain</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>55.1</v>
+        <v>0.00893233</v>
       </c>
       <c r="F93" t="n">
-        <v>706900026</v>
+        <v>767070561</v>
       </c>
       <c r="G93" t="n">
         <v>92</v>
       </c>
       <c r="H93" t="n">
-        <v>104129492</v>
+        <v>18904924</v>
       </c>
       <c r="I93" t="n">
-        <v>59.98</v>
+        <v>0.00909602</v>
       </c>
       <c r="J93" t="n">
-        <v>55.36</v>
+        <v>0.008248190000000001</v>
       </c>
       <c r="K93" t="n">
-        <v>-4.725648139787666</v>
+        <v>0.00070602</v>
       </c>
       <c r="L93" t="n">
-        <v>-7.89882</v>
+        <v>8.58253</v>
       </c>
       <c r="M93" t="n">
-        <v>12834288.94306016</v>
+        <v>85985041177</v>
       </c>
       <c r="N93" t="n">
-        <v>12834444.02060831</v>
+        <v>85985041177</v>
       </c>
       <c r="O93" t="n">
-        <v>1493.59</v>
+        <v>0.280991</v>
       </c>
       <c r="P93" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>44304.71413194444</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R93" t="b">
         <v>1</v>
       </c>
       <c r="S93" t="n">
-        <v>8.083129706786773e-05</v>
+        <v>8.980572660182791e-05</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>ustb</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>GHO</t>
+          <t>Invesco Short Duration US Government Securities Fund</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.998873</v>
+        <v>11.22</v>
       </c>
       <c r="F94" t="n">
-        <v>698217912</v>
+        <v>720195294</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
       </c>
       <c r="H94" t="n">
-        <v>4130425</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0.9992220000000001</v>
+        <v>11.22</v>
       </c>
       <c r="J94" t="n">
-        <v>0.998735</v>
+        <v>11.22</v>
       </c>
       <c r="K94" t="n">
-        <v>-0.000329611745378156</v>
+        <v>0.001094</v>
       </c>
       <c r="L94" t="n">
-        <v>-0.03299</v>
+        <v>0.00975</v>
       </c>
       <c r="M94" t="n">
-        <v>699000000</v>
+        <v>64206795.204266</v>
       </c>
       <c r="N94" t="n">
-        <v>699000000</v>
+        <v>64206795.204266</v>
       </c>
       <c r="O94" t="n">
-        <v>1.03</v>
+        <v>11.22</v>
       </c>
       <c r="P94" s="1" t="n">
-        <v>45350.38608796296</v>
+        <v>46286.55219907407</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R94" t="b">
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>7.545989609488083e-05</v>
+        <v>6.267967840837254e-05</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>vechain</t>
+          <t>ether-fi</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>vet</t>
+          <t>ethfi</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VeChain</t>
+          <t>Ether.fi</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.00811577</v>
+        <v>0.724214</v>
       </c>
       <c r="F95" t="n">
-        <v>697935434</v>
+        <v>698709596</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>18346791</v>
+        <v>55805811</v>
       </c>
       <c r="I95" t="n">
-        <v>0.00883454</v>
+        <v>0.769383</v>
       </c>
       <c r="J95" t="n">
-        <v>0.008146469999999999</v>
+        <v>0.704524</v>
       </c>
       <c r="K95" t="n">
-        <v>-0.000445351937834066</v>
+        <v>0.0248904</v>
       </c>
       <c r="L95" t="n">
-        <v>-5.20203</v>
+        <v>3.55921</v>
       </c>
       <c r="M95" t="n">
-        <v>85985041177</v>
+        <v>965350000</v>
       </c>
       <c r="N95" t="n">
-        <v>85985041177</v>
+        <v>965350000</v>
       </c>
       <c r="O95" t="n">
-        <v>0.280991</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="P95" s="1" t="n">
-        <v>44304.71413194444</v>
+        <v>45378.63525462963</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>7.528513421038503e-05</v>
+        <v>5.024621153514861e-05</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ether-fi</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ethfi</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Ether.fi</t>
+          <t>GHO</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.690631</v>
+        <v>0.999173</v>
       </c>
       <c r="F96" t="n">
-        <v>667093213</v>
+        <v>698438859</v>
       </c>
       <c r="G96" t="n">
         <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>43497357</v>
+        <v>5302269</v>
       </c>
       <c r="I96" t="n">
-        <v>0.757291</v>
+        <v>0.999187</v>
       </c>
       <c r="J96" t="n">
-        <v>0.690352</v>
+        <v>0.9988320000000001</v>
       </c>
       <c r="K96" t="n">
-        <v>-0.04496680518341711</v>
+        <v>0.00023127</v>
       </c>
       <c r="L96" t="n">
-        <v>-6.11296</v>
+        <v>0.02315</v>
       </c>
       <c r="M96" t="n">
-        <v>965350000</v>
+        <v>699000000</v>
       </c>
       <c r="N96" t="n">
-        <v>965350000</v>
+        <v>699000000</v>
       </c>
       <c r="O96" t="n">
-        <v>8.529999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="P96" s="1" t="n">
-        <v>45378.63525462963</v>
+        <v>45350.38608796296</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>5.620384411347118e-05</v>
+        <v>5.008953989614223e-05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>stable-2</t>
+          <t>aerodrome-finance</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>aero</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>​​Stable</t>
+          <t>Aerodrome Finance</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.02466683</v>
+        <v>0.686856</v>
       </c>
       <c r="F97" t="n">
-        <v>653449197</v>
+        <v>681820872</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>12599558</v>
+        <v>56831776</v>
       </c>
       <c r="I97" t="n">
-        <v>0.02570266</v>
+        <v>0.6991810000000001</v>
       </c>
       <c r="J97" t="n">
-        <v>0.02316713</v>
+        <v>0.648524</v>
       </c>
       <c r="K97" t="n">
-        <v>-0.0009946546413089721</v>
+        <v>0.02865724</v>
       </c>
       <c r="L97" t="n">
-        <v>-3.87606</v>
+        <v>4.35389</v>
       </c>
       <c r="M97" t="n">
-        <v>26490157407</v>
+        <v>992665694.3208704</v>
       </c>
       <c r="N97" t="n">
-        <v>100000000000</v>
+        <v>1983240735.576791</v>
       </c>
       <c r="O97" t="n">
-        <v>0.04323745</v>
+        <v>2.32</v>
       </c>
       <c r="P97" s="1" t="n">
-        <v>46156.97986111111</v>
+        <v>45633.25043981482</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>4.776264179594242e-05</v>
+        <v>4.047294792579218e-05</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>aerodrome-finance</t>
+          <t>stable-2</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>aero</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Aerodrome Finance</t>
+          <t>​​Stable</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.651114</v>
+        <v>0.02539244</v>
       </c>
       <c r="F98" t="n">
-        <v>646446304</v>
+        <v>673849676</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>39978894</v>
+        <v>10507115</v>
       </c>
       <c r="I98" t="n">
-        <v>0.675009</v>
+        <v>0.02655115</v>
       </c>
       <c r="J98" t="n">
-        <v>0.638014</v>
+        <v>0.02444799</v>
       </c>
       <c r="K98" t="n">
-        <v>-0.02330602382306102</v>
+        <v>0.0009418299999999999</v>
       </c>
       <c r="L98" t="n">
-        <v>-3.45571</v>
+        <v>3.85196</v>
       </c>
       <c r="M98" t="n">
-        <v>992679535.5672693</v>
+        <v>26522995541</v>
       </c>
       <c r="N98" t="n">
-        <v>1983240735.576791</v>
+        <v>100000000000</v>
       </c>
       <c r="O98" t="n">
-        <v>2.32</v>
+        <v>0.04323745</v>
       </c>
       <c r="P98" s="1" t="n">
-        <v>45633.25043981482</v>
+        <v>46156.97986111111</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R98" t="b">
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>4.343013173284913e-05</v>
+        <v>3.586013053414983e-05</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7038,34 +7038,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.721151</v>
+        <v>0.771625</v>
       </c>
       <c r="F99" t="n">
-        <v>627500848</v>
+        <v>671274865</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>120774558</v>
+        <v>181966908</v>
       </c>
       <c r="I99" t="n">
-        <v>0.748103</v>
+        <v>0.790511</v>
       </c>
       <c r="J99" t="n">
-        <v>0.7104549999999999</v>
+        <v>0.721949</v>
       </c>
       <c r="K99" t="n">
-        <v>-0.01582235679890542</v>
+        <v>0.050075</v>
       </c>
       <c r="L99" t="n">
-        <v>-2.14694</v>
+        <v>6.93996</v>
       </c>
       <c r="M99" t="n">
-        <v>870534155.5712929</v>
+        <v>870586041.4259734</v>
       </c>
       <c r="N99" t="n">
-        <v>1208974392.707352</v>
+        <v>1209026324.181685</v>
       </c>
       <c r="O99" t="n">
         <v>19.92</v>
@@ -7074,144 +7074,144 @@
         <v>44952.26755787037</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S99" t="n">
-        <v>3.170906462959749e-05</v>
+        <v>3.437012414602539e-05</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>beldex</t>
+          <t>blockstack</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>bdx</t>
+          <t>stx</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Beldex</t>
+          <t>Stacks</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.075895</v>
+        <v>0.330374</v>
       </c>
       <c r="F100" t="n">
-        <v>597644598</v>
+        <v>618216922</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>3842711</v>
+        <v>35672699</v>
       </c>
       <c r="I100" t="n">
-        <v>0.076097</v>
+        <v>0.34015</v>
       </c>
       <c r="J100" t="n">
-        <v>0.075479</v>
+        <v>0.30827</v>
       </c>
       <c r="K100" t="n">
-        <v>0.00023246</v>
+        <v>0.01942084</v>
       </c>
       <c r="L100" t="n">
-        <v>0.30724</v>
+        <v>6.24558</v>
       </c>
       <c r="M100" t="n">
-        <v>7870780683.443047</v>
+        <v>1868230389.165669</v>
       </c>
       <c r="N100" t="n">
-        <v>9939720596.243883</v>
+        <v>1868230389.165669</v>
       </c>
       <c r="O100" t="n">
-        <v>0.450785</v>
+        <v>3.86</v>
       </c>
       <c r="P100" s="1" t="n">
-        <v>43450.66666666666</v>
+        <v>45383.19094907407</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S100" t="n">
-        <v>1.323776947040697e-05</v>
+        <v>3.666249566204706e-06</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>blockstack</t>
+          <t>official-trump</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>stx</t>
+          <t>trump</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Stacks</t>
+          <t>Official Trump</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.308622</v>
+        <v>2.18</v>
       </c>
       <c r="F101" t="n">
-        <v>576247606</v>
+        <v>611881446</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>44500577</v>
+        <v>311874452</v>
       </c>
       <c r="I101" t="n">
-        <v>0.331991</v>
+        <v>2.19</v>
       </c>
       <c r="J101" t="n">
-        <v>0.300479</v>
+        <v>2.03</v>
       </c>
       <c r="K101" t="n">
-        <v>-0.000836197743021072</v>
+        <v>0.14939</v>
       </c>
       <c r="L101" t="n">
-        <v>-0.27021</v>
+        <v>7.37318</v>
       </c>
       <c r="M101" t="n">
-        <v>1867933631.498019</v>
+        <v>281867936.287634</v>
       </c>
       <c r="N101" t="n">
-        <v>1867933631.498019</v>
+        <v>1000000000</v>
       </c>
       <c r="O101" t="n">
-        <v>3.86</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="P101" s="1" t="n">
-        <v>45383.19094907407</v>
+        <v>45676.16011574074</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46285.56273148148</v>
+        <v>46286.65775462963</v>
       </c>
       <c r="R101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>

--- a/src/xlsx/cleaned_data.xlsx
+++ b/src/xlsx/cleaned_data.xlsx
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,34 +539,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86124</v>
+        <v>86132</v>
       </c>
       <c r="F2" t="n">
-        <v>1728665546532</v>
+        <v>1730358233094</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>53399664432</v>
+        <v>49306386707</v>
       </c>
       <c r="I2" t="n">
-        <v>86048</v>
+        <v>87330</v>
       </c>
       <c r="J2" t="n">
-        <v>80631</v>
+        <v>85098</v>
       </c>
       <c r="K2" t="n">
-        <v>5263.94</v>
+        <v>592.03</v>
       </c>
       <c r="L2" t="n">
-        <v>6.50996</v>
+        <v>0.69211</v>
       </c>
       <c r="M2" t="n">
-        <v>20087478</v>
+        <v>20087871</v>
       </c>
       <c r="N2" t="n">
-        <v>20087478</v>
+        <v>20087940</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -575,10 +575,10 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -587,7 +587,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,34 +606,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2750.02</v>
+        <v>2754.3</v>
       </c>
       <c r="F3" t="n">
-        <v>335133212622</v>
+        <v>336292649409</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>24352107151</v>
+        <v>19972791098</v>
       </c>
       <c r="I3" t="n">
-        <v>2751.07</v>
+        <v>2804.42</v>
       </c>
       <c r="J3" t="n">
-        <v>2607</v>
+        <v>2714.5</v>
       </c>
       <c r="K3" t="n">
-        <v>144.87</v>
+        <v>19.06</v>
       </c>
       <c r="L3" t="n">
-        <v>5.56097</v>
+        <v>0.6967</v>
       </c>
       <c r="M3" t="n">
-        <v>122067645.9189046</v>
+        <v>122070499.1930826</v>
       </c>
       <c r="N3" t="n">
-        <v>122067645.9189046</v>
+        <v>122070499.1930825</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -642,19 +642,19 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1935827213788247</v>
+        <v>0.1940587384332607</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,28 +673,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999874</v>
+        <v>0.999735</v>
       </c>
       <c r="F4" t="n">
-        <v>183365978384</v>
+        <v>183336508352</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>93897835021</v>
+        <v>87755318333</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999816</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999577</v>
+        <v>0.9996080000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00023771</v>
+        <v>9.564999999999999e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02378</v>
+        <v>0.00957</v>
       </c>
       <c r="M4" t="n">
         <v>183384649781.6938</v>
@@ -709,19 +709,19 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1057571883503426</v>
+        <v>0.1056312880101583</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,34 +740,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>805.13</v>
+        <v>789.84</v>
       </c>
       <c r="F5" t="n">
-        <v>107128051029</v>
+        <v>105180447721</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1861840599</v>
+        <v>1606078435</v>
       </c>
       <c r="I5" t="n">
-        <v>798.53</v>
+        <v>806.75</v>
       </c>
       <c r="J5" t="n">
-        <v>756.27</v>
+        <v>783.38</v>
       </c>
       <c r="K5" t="n">
-        <v>48.91</v>
+        <v>-4.924875956322353</v>
       </c>
       <c r="L5" t="n">
-        <v>6.46797</v>
+        <v>-0.61966</v>
       </c>
       <c r="M5" t="n">
-        <v>133160157.48</v>
+        <v>133160075.87</v>
       </c>
       <c r="N5" t="n">
-        <v>133160152.56</v>
+        <v>133160072.53</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -776,19 +776,19 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06163938755785053</v>
+        <v>0.06044747826604828</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -807,28 +807,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="F6" t="n">
-        <v>94051358788</v>
+        <v>99065321389</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>4723578943</v>
+        <v>6307464848</v>
       </c>
       <c r="I6" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="J6" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="K6" t="n">
-        <v>0.112485</v>
+        <v>0.089047</v>
       </c>
       <c r="L6" t="n">
-        <v>8.11206</v>
+        <v>5.97063</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -843,19 +843,19 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05407209233710331</v>
+        <v>0.05691218359388192</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,34 +874,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9999169999999999</v>
+        <v>0.99983</v>
       </c>
       <c r="F7" t="n">
-        <v>74231800122</v>
+        <v>74582091668</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>24254647063</v>
+        <v>23229656383</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9998629999999999</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999598</v>
+        <v>0.999694</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00021933</v>
+        <v>0.00012216</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02194</v>
+        <v>0.01222</v>
       </c>
       <c r="M7" t="n">
-        <v>74237004006.76027</v>
+        <v>74594529696.15031</v>
       </c>
       <c r="N7" t="n">
-        <v>74254811731.89992</v>
+        <v>74599622744.57069</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -910,19 +910,19 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04260279652387772</v>
+        <v>0.04275786741285092</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -941,34 +941,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>118.05</v>
+        <v>117.61</v>
       </c>
       <c r="F8" t="n">
-        <v>69255259901</v>
+        <v>69106453195</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>6440764344</v>
+        <v>5533889889</v>
       </c>
       <c r="I8" t="n">
-        <v>118.69</v>
+        <v>119.9</v>
       </c>
       <c r="J8" t="n">
-        <v>108.51</v>
+        <v>115.58</v>
       </c>
       <c r="K8" t="n">
-        <v>9.619999999999999</v>
+        <v>-0.5882841268877286</v>
       </c>
       <c r="L8" t="n">
-        <v>8.87163</v>
+        <v>-0.49769</v>
       </c>
       <c r="M8" t="n">
-        <v>587437261.0683235</v>
+        <v>587507739.1137596</v>
       </c>
       <c r="N8" t="n">
-        <v>634453375.546979</v>
+        <v>634531389.3135934</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -977,19 +977,19 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03972294370359374</v>
+        <v>0.03959227532704116</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1008,34 +1008,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.345544</v>
+        <v>0.342896</v>
       </c>
       <c r="F9" t="n">
-        <v>32816706862</v>
+        <v>32558762440</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>440937993</v>
+        <v>611135640</v>
       </c>
       <c r="I9" t="n">
-        <v>0.345088</v>
+        <v>0.349178</v>
       </c>
       <c r="J9" t="n">
-        <v>0.342488</v>
+        <v>0.343759</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00109724</v>
+        <v>-0.001853093714661691</v>
       </c>
       <c r="L9" t="n">
-        <v>0.31855</v>
+        <v>-0.53752</v>
       </c>
       <c r="M9" t="n">
-        <v>94960364758.90469</v>
+        <v>94961752942.69308</v>
       </c>
       <c r="N9" t="n">
-        <v>94960365761.90469</v>
+        <v>94961735259.42459</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1044,19 +1044,19 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01863647296763626</v>
+        <v>0.0184632177424079</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1075,34 +1075,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1495.75</v>
+        <v>1515.29</v>
       </c>
       <c r="F10" t="n">
-        <v>25309984948</v>
+        <v>25679897777</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1431547468</v>
+        <v>1439199278</v>
       </c>
       <c r="I10" t="n">
-        <v>1568.53</v>
+        <v>1540.34</v>
       </c>
       <c r="J10" t="n">
-        <v>1439.75</v>
+        <v>1444.17</v>
       </c>
       <c r="K10" t="n">
-        <v>53.35</v>
+        <v>-22.07724586670861</v>
       </c>
       <c r="L10" t="n">
-        <v>3.69892</v>
+        <v>-1.43604</v>
       </c>
       <c r="M10" t="n">
-        <v>16942351.7280448</v>
+        <v>16945106.4155448</v>
       </c>
       <c r="N10" t="n">
-        <v>16944709.5405448</v>
+        <v>16946415.7905448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1111,19 +1111,19 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01429244010241479</v>
+        <v>0.01448638843858815</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1142,34 +1142,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.04</v>
+        <v>1.013</v>
       </c>
       <c r="F11" t="n">
-        <v>23664863580</v>
+        <v>23062335218</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>16837398</v>
+        <v>55232417</v>
       </c>
       <c r="I11" t="n">
-        <v>1.021</v>
+        <v>1.04</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>1.012</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-0.006103827815765017</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.59888</v>
       </c>
       <c r="M11" t="n">
         <v>22764228455.528</v>
       </c>
       <c r="N11" t="n">
-        <v>22764228455.528</v>
+        <v>22966221270.418</v>
       </c>
       <c r="O11" t="n">
         <v>1.061</v>
@@ -1178,19 +1178,19 @@
         <v>46237.59675925926</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01334043183945489</v>
+        <v>0.01297311553685428</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1209,28 +1209,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>93.40000000000001</v>
+        <v>95.36</v>
       </c>
       <c r="F12" t="n">
-        <v>20757345051</v>
+        <v>21211241880</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1256686450</v>
+        <v>1293604135</v>
       </c>
       <c r="I12" t="n">
-        <v>95.98999999999999</v>
+        <v>95.88</v>
       </c>
       <c r="J12" t="n">
-        <v>91.90000000000001</v>
+        <v>92.06</v>
       </c>
       <c r="K12" t="n">
-        <v>1.53</v>
+        <v>0.44987</v>
       </c>
       <c r="L12" t="n">
-        <v>1.66271</v>
+        <v>0.47398</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1245,19 +1245,19 @@
         <v>46286.47291666667</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01165789235139143</v>
+        <v>0.01190295605686628</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1276,34 +1276,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.097469</v>
+        <v>0.100752</v>
       </c>
       <c r="F13" t="n">
-        <v>15181065525</v>
+        <v>15718592446</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1882978328</v>
+        <v>3160716957</v>
       </c>
       <c r="I13" t="n">
-        <v>0.095163</v>
+        <v>0.105575</v>
       </c>
       <c r="J13" t="n">
-        <v>0.085616</v>
+        <v>0.09251</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01187787</v>
+        <v>0.00726657</v>
       </c>
       <c r="L13" t="n">
-        <v>13.87742</v>
+        <v>7.77292</v>
       </c>
       <c r="M13" t="n">
-        <v>156008016383.7053</v>
+        <v>156021246383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>156008916383.7052</v>
+        <v>171733843126.5791</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1312,19 +1312,19 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R13" t="b">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>0.008430978952424452</v>
+        <v>0.008727529544664216</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1343,34 +1343,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>572.01</v>
+        <v>572.97</v>
       </c>
       <c r="F14" t="n">
-        <v>10738217262</v>
+        <v>10785142460</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>235272967</v>
+        <v>183437802</v>
       </c>
       <c r="I14" t="n">
-        <v>630.51</v>
+        <v>601.01</v>
       </c>
       <c r="J14" t="n">
-        <v>540.97</v>
+        <v>552.66</v>
       </c>
       <c r="K14" t="n">
-        <v>29.3</v>
+        <v>-2.374429859507018</v>
       </c>
       <c r="L14" t="n">
-        <v>5.39931</v>
+        <v>-0.4127</v>
       </c>
       <c r="M14" t="n">
-        <v>18807603.12217533</v>
+        <v>18808007.51155922</v>
       </c>
       <c r="N14" t="n">
-        <v>18807625.32201612</v>
+        <v>18808040.5111969</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1379,19 +1379,19 @@
         <v>46036.48202546296</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R14" t="b">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.005859966053482513</v>
+        <v>0.0058753890484595</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1410,256 +1410,256 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>86.64</v>
+        <v>86.66</v>
       </c>
       <c r="F15" t="n">
-        <v>10291846518</v>
+        <v>10299673248</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>215315698</v>
+        <v>176791671</v>
       </c>
       <c r="I15" t="n">
-        <v>86.64</v>
+        <v>87.91</v>
       </c>
       <c r="J15" t="n">
-        <v>82.23999999999999</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>4.33</v>
+        <v>0.492012</v>
       </c>
       <c r="L15" t="n">
-        <v>5.26004</v>
+        <v>0.57098</v>
       </c>
       <c r="M15" t="n">
-        <v>118887984</v>
+        <v>118852171</v>
       </c>
       <c r="N15" t="n">
-        <v>293457483</v>
+        <v>293421670</v>
       </c>
       <c r="O15" t="n">
-        <v>86.8</v>
+        <v>87.91</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>46286.63425925926</v>
+        <v>46286.85358796296</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005601657672777343</v>
+        <v>0.005594728171560972</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.01414863</v>
+        <v>13.06</v>
       </c>
       <c r="F16" t="n">
-        <v>10032920141</v>
+        <v>9773544357</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>29041461</v>
+        <v>684922983</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01427443</v>
+        <v>13.26</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01325824</v>
+        <v>12.76</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00097359</v>
+        <v>0.009376229999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>7.38968</v>
+        <v>0.07183</v>
       </c>
       <c r="M16" t="n">
-        <v>709239296767.5244</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N16" t="n">
-        <v>1142408526965.963</v>
+        <v>1000000000</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01946402</v>
+        <v>52.7</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>46259.82847222222</v>
+        <v>44325.67635416667</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.005451820672786307</v>
+        <v>0.005290561002439421</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>13.03</v>
+        <v>0.9998939999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>9741654136</v>
+        <v>9583360912</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>695570017</v>
+        <v>238853572</v>
       </c>
       <c r="I17" t="n">
-        <v>13.16</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>12.32</v>
+        <v>0.999729</v>
       </c>
       <c r="K17" t="n">
-        <v>0.717199</v>
+        <v>7.478999999999999e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>5.82362</v>
+        <v>0.00748</v>
       </c>
       <c r="M17" t="n">
-        <v>748099970.424884</v>
+        <v>9583873777.059114</v>
       </c>
       <c r="N17" t="n">
-        <v>1000000000</v>
+        <v>9576750341.247417</v>
       </c>
       <c r="O17" t="n">
-        <v>52.7</v>
+        <v>1.057</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>44325.67635416667</v>
+        <v>45593.90336805556</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005283269191495647</v>
+        <v>0.005180611594473086</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0.01348809</v>
       </c>
       <c r="F18" t="n">
-        <v>9595586523</v>
+        <v>9559476072</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>196078899</v>
+        <v>17859980</v>
       </c>
       <c r="I18" t="n">
+        <v>0.01420135</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.01343954</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.000638838496365042</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-4.52213</v>
+      </c>
+      <c r="M18" t="n">
+        <v>709239700254.0453</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1142408526965.963</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.01946402</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>46259.82847222222</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>46287.58067129629</v>
+      </c>
+      <c r="R18" t="b">
         <v>1</v>
       </c>
-      <c r="J18" t="n">
-        <v>0.999754</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.00015973</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.01598</v>
-      </c>
-      <c r="M18" t="n">
-        <v>9594149705.433596</v>
-      </c>
-      <c r="N18" t="n">
-        <v>9594892921.253408</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.057</v>
-      </c>
-      <c r="P18" s="1" t="n">
-        <v>45593.90336805556</v>
-      </c>
-      <c r="Q18" s="1" t="n">
-        <v>46286.65775462963</v>
-      </c>
-      <c r="R18" t="b">
-        <v>0</v>
-      </c>
       <c r="S18" t="n">
-        <v>0.005198741947955018</v>
+        <v>0.005166803221102993</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1678,31 +1678,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.245391</v>
+        <v>0.252441</v>
       </c>
       <c r="F19" t="n">
-        <v>9197046672</v>
+        <v>9470964968</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>826630614</v>
+        <v>838000406</v>
       </c>
       <c r="I19" t="n">
-        <v>0.248479</v>
+        <v>0.251521</v>
       </c>
       <c r="J19" t="n">
-        <v>0.22404</v>
+        <v>0.240416</v>
       </c>
       <c r="K19" t="n">
-        <v>0.02123083</v>
+        <v>0.007827020000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>9.471270000000001</v>
+        <v>3.19974</v>
       </c>
       <c r="M19" t="n">
-        <v>37522923322.16203</v>
+        <v>37529061988.53558</v>
       </c>
       <c r="N19" t="n">
         <v>45000000000</v>
@@ -1714,19 +1714,19 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004968112622574567</v>
+        <v>0.005115632923481942</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1745,28 +1745,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.92</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>8205789399</v>
+        <v>8251314793</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>45234</v>
+        <v>157365</v>
       </c>
       <c r="I20" t="n">
-        <v>8.99</v>
+        <v>9</v>
       </c>
       <c r="J20" t="n">
-        <v>8.880000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.01354870721141488</v>
+        <v>-0.01618964306871185</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.15166</v>
+        <v>-0.18016</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -1781,19 +1781,19 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004394486182014535</v>
+        <v>0.004410525206733586</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1812,31 +1812,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.210781</v>
+        <v>0.214975</v>
       </c>
       <c r="F21" t="n">
-        <v>7340660289</v>
+        <v>7505565898</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>385358090</v>
+        <v>450679611</v>
       </c>
       <c r="I21" t="n">
-        <v>0.212907</v>
+        <v>0.219762</v>
       </c>
       <c r="J21" t="n">
-        <v>0.193655</v>
+        <v>0.206236</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01715873</v>
+        <v>0.00500717</v>
       </c>
       <c r="L21" t="n">
-        <v>8.861940000000001</v>
+        <v>2.38473</v>
       </c>
       <c r="M21" t="n">
-        <v>34882253227.52757</v>
+        <v>34931879410.76893</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70148</v>
@@ -1848,354 +1848,354 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.003893848309777537</v>
+        <v>0.00397939068029361</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>uniswap</t>
+          <t>bitcoin-cash</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>uni</t>
+          <t>bch</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Bitcoin Cash</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>8.890000000000001</v>
+        <v>325.71</v>
       </c>
       <c r="F22" t="n">
-        <v>5515671145</v>
+        <v>6541052358</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>1170568252</v>
+        <v>691846249</v>
       </c>
       <c r="I22" t="n">
-        <v>9.25</v>
+        <v>311.05</v>
       </c>
       <c r="J22" t="n">
-        <v>8.529999999999999</v>
+        <v>261.8</v>
       </c>
       <c r="K22" t="n">
-        <v>0.21966</v>
+        <v>56.43</v>
       </c>
       <c r="L22" t="n">
-        <v>2.53223</v>
+        <v>20.95482</v>
       </c>
       <c r="M22" t="n">
-        <v>620798422.6104751</v>
+        <v>20092515.52165077</v>
       </c>
       <c r="N22" t="n">
-        <v>888046418.9163101</v>
+        <v>20092887.39665077</v>
       </c>
       <c r="O22" t="n">
-        <v>44.92</v>
+        <v>3785.82</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>44318.89240740741</v>
+        <v>43088.66666666666</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.002837753131211902</v>
+        <v>0.003421783299175271</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>bitcoin-cash</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>bch</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Bitcoin Cash</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>264.35</v>
+        <v>4.47</v>
       </c>
       <c r="F23" t="n">
-        <v>5307183344</v>
+        <v>5849869047</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>296383774</v>
+        <v>1786719210</v>
       </c>
       <c r="I23" t="n">
-        <v>271.86</v>
+        <v>4.65</v>
       </c>
       <c r="J23" t="n">
-        <v>247.88</v>
+        <v>3.92</v>
       </c>
       <c r="K23" t="n">
-        <v>16.82</v>
+        <v>0.334539</v>
       </c>
       <c r="L23" t="n">
-        <v>6.79536</v>
+        <v>8.08442</v>
       </c>
       <c r="M23" t="n">
-        <v>20092153.02165077</v>
+        <v>1306999800</v>
       </c>
       <c r="N23" t="n">
-        <v>20092453.02165077</v>
+        <v>1306999785</v>
       </c>
       <c r="O23" t="n">
-        <v>3785.82</v>
+        <v>20.44</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>44577.59010416667</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R23" t="b">
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.002717104215491091</v>
+        <v>0.003022194387318821</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>uniswap</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>uni</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4.04</v>
+        <v>9.07</v>
       </c>
       <c r="F24" t="n">
-        <v>5280599037</v>
+        <v>5631538867</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>1859521787</v>
+        <v>1394948640</v>
       </c>
       <c r="I24" t="n">
-        <v>4.44</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>3.87</v>
+        <v>8.68</v>
       </c>
       <c r="K24" t="n">
-        <v>0.255399</v>
+        <v>0.157641</v>
       </c>
       <c r="L24" t="n">
-        <v>6.74642</v>
+        <v>1.76836</v>
       </c>
       <c r="M24" t="n">
-        <v>1306919679</v>
+        <v>620716422.6104751</v>
       </c>
       <c r="N24" t="n">
-        <v>1306919694</v>
+        <v>887964418.9163101</v>
       </c>
       <c r="O24" t="n">
-        <v>20.44</v>
+        <v>44.92</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>44577.59010416667</v>
+        <v>44318.89240740741</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002701720256336861</v>
+        <v>0.002895972706813542</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>avalanche-2</t>
+          <t>ethena-usde</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>avax</t>
+          <t>usde</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Ethena USDe</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>11.2</v>
+        <v>0.999597</v>
       </c>
       <c r="F25" t="n">
-        <v>4956319449</v>
+        <v>4900074139</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>1232465817</v>
+        <v>191810978</v>
       </c>
       <c r="I25" t="n">
-        <v>11.78</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>10.92</v>
+        <v>0.998631</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.05499586640539</v>
+        <v>-0.000232050524545446</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.4887</v>
+        <v>-0.02321</v>
       </c>
       <c r="M25" t="n">
-        <v>442892841.602698</v>
+        <v>4902029610.641097</v>
       </c>
       <c r="N25" t="n">
-        <v>469561413.4440742</v>
+        <v>4901729538.308097</v>
       </c>
       <c r="O25" t="n">
-        <v>144.96</v>
+        <v>1.034</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>44521.26314814815</v>
+        <v>46000.38208333333</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002514064285604111</v>
+        <v>0.002473096184664855</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ethena-usde</t>
+          <t>avalanche-2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>usde</t>
+          <t>avax</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ethena USDe</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F26" t="n">
-        <v>4883273448</v>
+        <v>4869633946</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>43152985</v>
+        <v>796744596</v>
       </c>
       <c r="I26" t="n">
-        <v>0.999964</v>
+        <v>11.36</v>
       </c>
       <c r="J26" t="n">
-        <v>0.999695</v>
+        <v>10.53</v>
       </c>
       <c r="K26" t="n">
-        <v>0.00034911</v>
+        <v>-0.2780236806402367</v>
       </c>
       <c r="L26" t="n">
-        <v>0.03492</v>
+        <v>-2.46536</v>
       </c>
       <c r="M26" t="n">
-        <v>4882671688.190312</v>
+        <v>442925920.1218815</v>
       </c>
       <c r="N26" t="n">
-        <v>4883552134.801312</v>
+        <v>469594897.9267309</v>
       </c>
       <c r="O26" t="n">
-        <v>1.034</v>
+        <v>144.96</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>46000.38208333333</v>
+        <v>44521.26314814815</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002471793607050638</v>
+        <v>0.002455498011497202</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2214,34 +2214,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>62.5</v>
+        <v>61.92</v>
       </c>
       <c r="F27" t="n">
-        <v>4854766688</v>
+        <v>4811453542</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>555253226</v>
+        <v>468229492</v>
       </c>
       <c r="I27" t="n">
-        <v>63.74</v>
+        <v>63.49</v>
       </c>
       <c r="J27" t="n">
-        <v>57.44</v>
+        <v>59.82</v>
       </c>
       <c r="K27" t="n">
-        <v>5.09</v>
+        <v>-0.6188402034689062</v>
       </c>
       <c r="L27" t="n">
-        <v>8.866899999999999</v>
+        <v>-0.9895699999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>77632004.46059512</v>
+        <v>77635616.97446169</v>
       </c>
       <c r="N27" t="n">
-        <v>77635191.97028677</v>
+        <v>77638460.73181786</v>
       </c>
       <c r="O27" t="n">
         <v>410.26</v>
@@ -2250,19 +2250,19 @@
         <v>44325.80077546297</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002455297151774997</v>
+        <v>0.002421862586631266</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2281,34 +2281,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.116617</v>
+        <v>0.117048</v>
       </c>
       <c r="F28" t="n">
-        <v>4621327246</v>
+        <v>4641383435</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>17034306</v>
+        <v>20927321</v>
       </c>
       <c r="I28" t="n">
-        <v>0.118847</v>
+        <v>0.119967</v>
       </c>
       <c r="J28" t="n">
-        <v>0.106795</v>
+        <v>0.114334</v>
       </c>
       <c r="K28" t="n">
-        <v>0.009704809999999999</v>
+        <v>0.00189519</v>
       </c>
       <c r="L28" t="n">
-        <v>9.077400000000001</v>
+        <v>1.6458</v>
       </c>
       <c r="M28" t="n">
-        <v>39650914855.51295</v>
+        <v>39659258394.41443</v>
       </c>
       <c r="N28" t="n">
-        <v>39650914855.51295</v>
+        <v>39660284776.00477</v>
       </c>
       <c r="O28" t="n">
         <v>0.194152</v>
@@ -2317,19 +2317,19 @@
         <v>46056.00148148148</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002320209077419168</v>
+        <v>0.002323541160297754</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2351,31 +2351,31 @@
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>4587287767</v>
+        <v>4589482014</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>332234991</v>
+        <v>158461722</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.999663</v>
+        <v>0.999707</v>
       </c>
       <c r="K29" t="n">
-        <v>4.657e-05</v>
+        <v>0.00015651</v>
       </c>
       <c r="L29" t="n">
-        <v>0.00466</v>
+        <v>0.01565</v>
       </c>
       <c r="M29" t="n">
-        <v>4587555760.165159</v>
+        <v>4589123571.017243</v>
       </c>
       <c r="N29" t="n">
-        <v>4589397370.72186</v>
+        <v>4594670335.870287</v>
       </c>
       <c r="O29" t="n">
         <v>1.22</v>
@@ -2384,19 +2384,19 @@
         <v>43902.79363425926</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002300510916599431</v>
+        <v>0.00229353575939884</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2415,34 +2415,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.999808</v>
+        <v>0.9993069999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>4356161972</v>
+        <v>4373808153</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>1388534334</v>
+        <v>1394890022</v>
       </c>
       <c r="I30" t="n">
-        <v>0.999771</v>
+        <v>0.999969</v>
       </c>
       <c r="J30" t="n">
-        <v>0.99937</v>
+        <v>0.999131</v>
       </c>
       <c r="K30" t="n">
-        <v>0.00033205</v>
+        <v>-0.000327838376545708</v>
       </c>
       <c r="L30" t="n">
-        <v>0.03322</v>
+        <v>-0.0328</v>
       </c>
       <c r="M30" t="n">
-        <v>4356796476.280436</v>
+        <v>4376796475.112089</v>
       </c>
       <c r="N30" t="n">
-        <v>4356796476.280436</v>
+        <v>4376796475.112089</v>
       </c>
       <c r="O30" t="n">
         <v>1.048</v>
@@ -2451,421 +2451,421 @@
         <v>46212.42696759259</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.002166761716751232</v>
+        <v>0.002168849757782014</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>hedera-hashgraph</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>hbar</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>Hedera</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.022</v>
+        <v>0.09669700000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>4178422617</v>
+        <v>4237742715</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>2166507655</v>
+        <v>207390429</v>
       </c>
       <c r="I31" t="n">
-        <v>1.054</v>
+        <v>0.097631</v>
       </c>
       <c r="J31" t="n">
-        <v>0.843444</v>
+        <v>0.089865</v>
       </c>
       <c r="K31" t="n">
-        <v>0.181534</v>
+        <v>0.0055354</v>
       </c>
       <c r="L31" t="n">
-        <v>21.60945</v>
+        <v>6.07206</v>
       </c>
       <c r="M31" t="n">
-        <v>4096537146.540959</v>
+        <v>43831706400.0613</v>
       </c>
       <c r="N31" t="n">
-        <v>10000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="O31" t="n">
-        <v>5.35</v>
+        <v>0.569229</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>45661.62243055556</v>
+        <v>44454.11143518519</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R31" t="b">
         <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0.002063906488009737</v>
+        <v>0.002090187209878436</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>the-open-network</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>gram</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Gram (prev. Toncoin)</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.43</v>
+        <v>1.015</v>
       </c>
       <c r="F32" t="n">
-        <v>4028994265</v>
+        <v>4158290738</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>60620535</v>
+        <v>1393806744</v>
       </c>
       <c r="I32" t="n">
-        <v>1.44</v>
+        <v>1.079</v>
       </c>
       <c r="J32" t="n">
-        <v>1.37</v>
+        <v>0.992193</v>
       </c>
       <c r="K32" t="n">
-        <v>0.061308</v>
+        <v>-0.02509713341816555</v>
       </c>
       <c r="L32" t="n">
-        <v>4.46488</v>
+        <v>-2.4135</v>
       </c>
       <c r="M32" t="n">
-        <v>2810474514.130084</v>
+        <v>4096537146.540959</v>
       </c>
       <c r="N32" t="n">
-        <v>5253006691.507872</v>
+        <v>10000000000</v>
       </c>
       <c r="O32" t="n">
-        <v>8.25</v>
+        <v>5.35</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>45457.69225694444</v>
+        <v>45661.62243055556</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001977434432761057</v>
+        <v>0.002044254201183043</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>hedera-hashgraph</t>
+          <t>the-open-network</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>hbar</t>
+          <t>gram</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Hedera</t>
+          <t>Gram (prev. Toncoin)</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.091629</v>
+        <v>1.43</v>
       </c>
       <c r="F33" t="n">
-        <v>4010077306</v>
+        <v>4021661629</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>222101860</v>
+        <v>64995447</v>
       </c>
       <c r="I33" t="n">
-        <v>0.092859</v>
+        <v>1.48</v>
       </c>
       <c r="J33" t="n">
-        <v>0.084797</v>
+        <v>1.41</v>
       </c>
       <c r="K33" t="n">
-        <v>0.00531559</v>
+        <v>0.00260019</v>
       </c>
       <c r="L33" t="n">
-        <v>6.15846</v>
+        <v>0.18202</v>
       </c>
       <c r="M33" t="n">
-        <v>43831706400.74403</v>
+        <v>2810942525.236758</v>
       </c>
       <c r="N33" t="n">
-        <v>50000000000</v>
+        <v>5253533230.459864</v>
       </c>
       <c r="O33" t="n">
-        <v>0.569229</v>
+        <v>8.25</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>44454.11143518519</v>
+        <v>45457.69225694444</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001966487458496193</v>
+        <v>0.001965265782156782</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>shiba-inu</t>
+          <t>bittensor</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>shib</t>
+          <t>tao</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Shiba Inu</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5.97e-06</v>
+        <v>320.39</v>
       </c>
       <c r="F34" t="n">
-        <v>3499895427</v>
+        <v>3631258347</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>133814849</v>
+        <v>688860057</v>
       </c>
       <c r="I34" t="n">
-        <v>5.87e-06</v>
+        <v>325.76</v>
       </c>
       <c r="J34" t="n">
-        <v>5.4e-06</v>
+        <v>278.1</v>
       </c>
       <c r="K34" t="n">
-        <v>5.74284e-07</v>
+        <v>33.25</v>
       </c>
       <c r="L34" t="n">
-        <v>10.6398</v>
+        <v>11.5799</v>
       </c>
       <c r="M34" t="n">
-        <v>589238972680230.1</v>
+        <v>11339645.9251</v>
       </c>
       <c r="N34" t="n">
-        <v>589496072572615.9</v>
+        <v>21000000</v>
       </c>
       <c r="O34" t="n">
-        <v>8.616e-05</v>
+        <v>757.6</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>44496.82980324074</v>
+        <v>45358.44833333333</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R34" t="b">
         <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001671252484428065</v>
+        <v>0.001739564698006087</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>memecore</t>
+          <t>shiba-inu</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>shib</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MemeCore</t>
+          <t>Shiba Inu</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1.49</v>
+        <v>6.02e-06</v>
       </c>
       <c r="F35" t="n">
-        <v>3393781990</v>
+        <v>3547301637</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>2344197</v>
+        <v>258673537</v>
       </c>
       <c r="I35" t="n">
-        <v>1.61</v>
+        <v>6.25e-06</v>
       </c>
       <c r="J35" t="n">
-        <v>1.45</v>
+        <v>5.67e-06</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.04122143441758852</v>
+        <v>2.9052e-07</v>
       </c>
       <c r="L35" t="n">
-        <v>-2.69026</v>
+        <v>5.07012</v>
       </c>
       <c r="M35" t="n">
-        <v>2276129700.761904</v>
+        <v>589238968628246.4</v>
       </c>
       <c r="N35" t="n">
-        <v>5416704127.604535</v>
+        <v>589496070402766.1</v>
       </c>
       <c r="O35" t="n">
-        <v>5.64</v>
+        <v>8.616e-05</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>46205.17638888889</v>
+        <v>44496.82980324074</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001609846152469781</v>
+        <v>0.001691027399928953</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>bittensor</t>
+          <t>crypto-com-chain</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>tao</t>
+          <t>cro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>Cronos</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>289.07</v>
+        <v>0.066841</v>
       </c>
       <c r="F36" t="n">
-        <v>3267924960</v>
+        <v>3324735280</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>470609612</v>
+        <v>20512650</v>
       </c>
       <c r="I36" t="n">
-        <v>288.6</v>
+        <v>0.068842</v>
       </c>
       <c r="J36" t="n">
-        <v>254.14</v>
+        <v>0.062969</v>
       </c>
       <c r="K36" t="n">
-        <v>35.18</v>
+        <v>0.00316426</v>
       </c>
       <c r="L36" t="n">
-        <v>13.85522</v>
+        <v>4.96927</v>
       </c>
       <c r="M36" t="n">
-        <v>11339645.9251</v>
+        <v>49737083041.94866</v>
       </c>
       <c r="N36" t="n">
-        <v>21000000</v>
+        <v>98937083097.9492</v>
       </c>
       <c r="O36" t="n">
-        <v>757.6</v>
+        <v>0.891544</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>45358.44833333333</v>
+        <v>44523.66666666666</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001537014484945302</v>
+        <v>0.00156235668842</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2884,34 +2884,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9999479999999999</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>3244051484</v>
+        <v>3268121116</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>1028610394</v>
+        <v>942747771</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>0.99979</v>
+        <v>0.999787</v>
       </c>
       <c r="K37" t="n">
-        <v>-7.465353777646999e-05</v>
+        <v>0.00014023</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.00747</v>
+        <v>0.01402</v>
       </c>
       <c r="M37" t="n">
-        <v>3244126367.123568</v>
+        <v>3268047900.209824</v>
       </c>
       <c r="N37" t="n">
-        <v>3247147890.103568</v>
+        <v>3268085897.433343</v>
       </c>
       <c r="O37" t="n">
         <v>1.65</v>
@@ -2920,86 +2920,86 @@
         <v>45686.67436342593</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001523199245012454</v>
+        <v>0.001529626742791404</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>crypto-com-chain</t>
+          <t>memecore</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>cro</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cronos</t>
+          <t>MemeCore</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.0636</v>
+        <v>1.32</v>
       </c>
       <c r="F38" t="n">
-        <v>3161313953</v>
+        <v>3008797579</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
       </c>
       <c r="H38" t="n">
-        <v>13759695</v>
+        <v>1496229</v>
       </c>
       <c r="I38" t="n">
-        <v>0.06450500000000001</v>
+        <v>1.51</v>
       </c>
       <c r="J38" t="n">
-        <v>0.058538</v>
+        <v>1.32</v>
       </c>
       <c r="K38" t="n">
-        <v>0.00494188</v>
+        <v>-0.1607115628173845</v>
       </c>
       <c r="L38" t="n">
-        <v>8.42489</v>
+        <v>-10.84507</v>
       </c>
       <c r="M38" t="n">
-        <v>49735222151.92632</v>
+        <v>2277453794.135731</v>
       </c>
       <c r="N38" t="n">
-        <v>98935195279.49802</v>
+        <v>5417058990.578639</v>
       </c>
       <c r="O38" t="n">
-        <v>0.891544</v>
+        <v>5.64</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>44523.66666666666</v>
+        <v>46205.17638888889</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R38" t="b">
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.00147532021632738</v>
+        <v>0.001379705863164442</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3018,34 +3018,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0.999911</v>
       </c>
       <c r="F39" t="n">
-        <v>2780507392</v>
+        <v>2821974132</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>80675032</v>
+        <v>125350757</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0.99975</v>
+        <v>0.99978</v>
       </c>
       <c r="K39" t="n">
-        <v>0.00024728</v>
+        <v>4.469e-05</v>
       </c>
       <c r="L39" t="n">
-        <v>0.02473</v>
+        <v>0.00447</v>
       </c>
       <c r="M39" t="n">
-        <v>2780174063.099801</v>
+        <v>2822151262.564369</v>
       </c>
       <c r="N39" t="n">
-        <v>2780171733.0998</v>
+        <v>2822151262.564368</v>
       </c>
       <c r="O39" t="n">
         <v>1.021</v>
@@ -3054,19 +3054,19 @@
         <v>45222.61454861111</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001254952892850162</v>
+        <v>0.00127169894704259</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3085,28 +3085,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4351.16</v>
+        <v>4333.56</v>
       </c>
       <c r="F40" t="n">
-        <v>2709821109</v>
+        <v>2698988013</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>178966320</v>
+        <v>222621939</v>
       </c>
       <c r="I40" t="n">
-        <v>4381.92</v>
+        <v>4372.67</v>
       </c>
       <c r="J40" t="n">
-        <v>4328.37</v>
+        <v>4295.64</v>
       </c>
       <c r="K40" t="n">
-        <v>-17.7913020598844</v>
+        <v>-17.04005644263361</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.40722</v>
+        <v>-0.39167</v>
       </c>
       <c r="M40" t="n">
         <v>622823.6595320001</v>
@@ -3121,19 +3121,19 @@
         <v>46050.66666666666</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001214047749434675</v>
+        <v>0.00120059785319014</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3152,28 +3152,28 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>123.32</v>
+        <v>122.29</v>
       </c>
       <c r="F41" t="n">
-        <v>2591259374</v>
+        <v>2567889954</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
       </c>
       <c r="H41" t="n">
-        <v>48633818</v>
+        <v>49631893</v>
       </c>
       <c r="I41" t="n">
-        <v>124.08</v>
+        <v>126.4</v>
       </c>
       <c r="J41" t="n">
-        <v>116.9</v>
+        <v>120.48</v>
       </c>
       <c r="K41" t="n">
-        <v>6.83</v>
+        <v>-0.2250340682920182</v>
       </c>
       <c r="L41" t="n">
-        <v>5.86617</v>
+        <v>-0.18368</v>
       </c>
       <c r="M41" t="n">
         <v>21000000</v>
@@ -3188,19 +3188,19 @@
         <v>45934.66666666666</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.00114543776503694</v>
+        <v>0.001124807060923308</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3222,7 +3222,7 @@
         <v>1.14</v>
       </c>
       <c r="F42" t="n">
-        <v>2508517113</v>
+        <v>2508748748</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
@@ -3237,171 +3237,171 @@
         <v>1.14</v>
       </c>
       <c r="K42" t="n">
-        <v>8.125e-05</v>
+        <v>0.00010508</v>
       </c>
       <c r="L42" t="n">
-        <v>0.00714</v>
+        <v>0.00923</v>
       </c>
       <c r="M42" t="n">
         <v>2204409826.472634</v>
       </c>
       <c r="N42" t="n">
-        <v>2204409826.472634</v>
+        <v>2204477317.470919</v>
       </c>
       <c r="O42" t="n">
         <v>1.14</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>46286.54189814815</v>
+        <v>46287.53819444445</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001097555999168354</v>
+        <v>0.001090616174402585</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>ripple-usd</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>rlusd</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>Ripple USD</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.908653</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>2455127227</v>
+        <v>2444037824</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>29155304</v>
+        <v>194679324</v>
       </c>
       <c r="I43" t="n">
-        <v>0.922215</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>0.692906</v>
+        <v>0.9997740000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>0.198456</v>
+        <v>0.00013348</v>
       </c>
       <c r="L43" t="n">
-        <v>27.94389</v>
+        <v>0.01335</v>
       </c>
       <c r="M43" t="n">
-        <v>2708142280.000001</v>
+        <v>2443757344.087235</v>
       </c>
       <c r="N43" t="n">
-        <v>10000000000</v>
+        <v>2446757344.087215</v>
       </c>
       <c r="O43" t="n">
-        <v>0.922215</v>
+        <v>1.073</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>46286.57083333333</v>
+        <v>45652.11518518518</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001066660033910618</v>
+        <v>0.001053205306265485</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ripple-usd</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>rlusd</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ripple USD</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0.867826</v>
       </c>
       <c r="F44" t="n">
-        <v>2368658098</v>
+        <v>2353876933</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>386949611</v>
+        <v>25229215</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0.972034</v>
       </c>
       <c r="J44" t="n">
-        <v>0.999826</v>
+        <v>0.674004</v>
       </c>
       <c r="K44" t="n">
-        <v>0.00019016</v>
+        <v>0.0273677</v>
       </c>
       <c r="L44" t="n">
-        <v>0.01902</v>
+        <v>3.25628</v>
       </c>
       <c r="M44" t="n">
-        <v>2368466183.08722</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N44" t="n">
-        <v>2373816183.087221</v>
+        <v>10000000000</v>
       </c>
       <c r="O44" t="n">
-        <v>1.073</v>
+        <v>0.972034</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>45652.11518518518</v>
+        <v>46286.79398148148</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001016621582705633</v>
+        <v>0.001001081228971758</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3423,7 +3423,7 @@
         <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>2329036631</v>
+        <v>2311661429</v>
       </c>
       <c r="G45" t="n">
         <v>44</v>
@@ -3438,16 +3438,16 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>-1.11e-16</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2329036630.620449</v>
+        <v>2311661429.407649</v>
       </c>
       <c r="N45" t="n">
-        <v>2329735522.270449</v>
+        <v>2311661429.407649</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
@@ -3456,19 +3456,19 @@
         <v>45699.87511574074</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.0009936932050744745</v>
+        <v>0.0009766754786615752</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3490,13 +3490,13 @@
         <v>1.15</v>
       </c>
       <c r="F46" t="n">
-        <v>2246038869</v>
+        <v>2261756116</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>1173758</v>
+        <v>2551236</v>
       </c>
       <c r="I46" t="n">
         <v>1.15</v>
@@ -3505,16 +3505,16 @@
         <v>1.13</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0005346800000000001</v>
+        <v>0.00666978</v>
       </c>
       <c r="L46" t="n">
-        <v>0.04665</v>
+        <v>0.58504</v>
       </c>
       <c r="M46" t="n">
-        <v>1969763856.975529</v>
+        <v>1972357100.681555</v>
       </c>
       <c r="N46" t="n">
-        <v>1969996524.04932</v>
+        <v>1972357112.080956</v>
       </c>
       <c r="O46" t="n">
         <v>1.26</v>
@@ -3523,19 +3523,19 @@
         <v>45377.89175925926</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0009456635844226938</v>
+        <v>0.0009478240735420358</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3554,31 +3554,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>143.63</v>
+        <v>144.17</v>
       </c>
       <c r="F47" t="n">
-        <v>2214275421</v>
+        <v>2224776584</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>363017691</v>
+        <v>309053020</v>
       </c>
       <c r="I47" t="n">
-        <v>148.98</v>
+        <v>148.31</v>
       </c>
       <c r="J47" t="n">
-        <v>135.04</v>
+        <v>140.18</v>
       </c>
       <c r="K47" t="n">
-        <v>8.01</v>
+        <v>-1.944895074505439</v>
       </c>
       <c r="L47" t="n">
-        <v>5.90774</v>
+        <v>-1.33105</v>
       </c>
       <c r="M47" t="n">
-        <v>15428777.33265995</v>
+        <v>15428841.48679896</v>
       </c>
       <c r="N47" t="n">
         <v>16000000</v>
@@ -3590,756 +3590,756 @@
         <v>44334.55554398148</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0009272825302680943</v>
+        <v>0.0009264453586372126</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ethena</t>
+          <t>mantle</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ena</t>
+          <t>mnt</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ethena</t>
+          <t>Mantle</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.216225</v>
+        <v>0.663218</v>
       </c>
       <c r="F48" t="n">
-        <v>2181612757</v>
+        <v>2190798183</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>720364026</v>
+        <v>60061876</v>
       </c>
       <c r="I48" t="n">
-        <v>0.230131</v>
+        <v>0.663806</v>
       </c>
       <c r="J48" t="n">
-        <v>0.203336</v>
+        <v>0.628171</v>
       </c>
       <c r="K48" t="n">
-        <v>0.01567105</v>
+        <v>0.02828344</v>
       </c>
       <c r="L48" t="n">
-        <v>7.81387</v>
+        <v>4.45454</v>
       </c>
       <c r="M48" t="n">
-        <v>10095312500</v>
+        <v>3302294382.53684</v>
       </c>
       <c r="N48" t="n">
-        <v>15000000000</v>
+        <v>6219316794.889999</v>
       </c>
       <c r="O48" t="n">
-        <v>1.52</v>
+        <v>2.86</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>45393.21892361111</v>
+        <v>45938.71164351852</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0009083811126443688</v>
+        <v>0.0009068016663400586</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ondo-finance</t>
+          <t>ethena</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ondo</t>
+          <t>ena</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ondo</t>
+          <t>Ethena</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.444165</v>
+        <v>0.210673</v>
       </c>
       <c r="F49" t="n">
-        <v>2161052269</v>
+        <v>2127163402</v>
       </c>
       <c r="G49" t="n">
         <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>291126477</v>
+        <v>576923127</v>
       </c>
       <c r="I49" t="n">
-        <v>0.458235</v>
+        <v>0.224915</v>
       </c>
       <c r="J49" t="n">
-        <v>0.415353</v>
+        <v>0.205259</v>
       </c>
       <c r="K49" t="n">
-        <v>0.03020456</v>
+        <v>-0.0139200602721101</v>
       </c>
       <c r="L49" t="n">
-        <v>7.29649</v>
+        <v>-6.19789</v>
       </c>
       <c r="M49" t="n">
-        <v>4869330647</v>
+        <v>10095312500</v>
       </c>
       <c r="N49" t="n">
-        <v>10000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="O49" t="n">
-        <v>2.14</v>
+        <v>1.52</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>45641.69166666667</v>
+        <v>45393.21892361111</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R49" t="b">
         <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0008964830515971866</v>
+        <v>0.0008700129411331019</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>mantle</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>mnt</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mantle</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.642248</v>
+        <v>0.00451865</v>
       </c>
       <c r="F50" t="n">
-        <v>2119720789</v>
+        <v>2110988113</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>46036318</v>
+        <v>237169986</v>
       </c>
       <c r="I50" t="n">
-        <v>0.638996</v>
+        <v>0.00469623</v>
       </c>
       <c r="J50" t="n">
-        <v>0.600169</v>
+        <v>0.00418118</v>
       </c>
       <c r="K50" t="n">
-        <v>0.04491815</v>
+        <v>0.00013365</v>
       </c>
       <c r="L50" t="n">
-        <v>7.51982</v>
+        <v>3.04787</v>
       </c>
       <c r="M50" t="n">
-        <v>3302294382.53684</v>
+        <v>467093607804.5021</v>
       </c>
       <c r="N50" t="n">
-        <v>6219316794.889999</v>
+        <v>832605428059.7732</v>
       </c>
       <c r="O50" t="n">
-        <v>2.86</v>
+        <v>0.00881908</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>45938.71164351852</v>
+        <v>45914.36296296296</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0008725651138415076</v>
+        <v>0.0008606616358749898</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>ondo-finance</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>ondo</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Pepe</t>
+          <t>Ondo</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5.03e-06</v>
+        <v>0.433253</v>
       </c>
       <c r="F51" t="n">
-        <v>2102717236</v>
+        <v>2108618675</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>813645807</v>
+        <v>327655256</v>
       </c>
       <c r="I51" t="n">
-        <v>4.87e-06</v>
+        <v>0.463533</v>
       </c>
       <c r="J51" t="n">
-        <v>3.92e-06</v>
+        <v>0.426035</v>
       </c>
       <c r="K51" t="n">
-        <v>1.07e-06</v>
+        <v>-0.01966368954010023</v>
       </c>
       <c r="L51" t="n">
-        <v>27.03744</v>
+        <v>-4.34157</v>
       </c>
       <c r="M51" t="n">
-        <v>420690000000000</v>
+        <v>4869330647</v>
       </c>
       <c r="N51" t="n">
-        <v>420690000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O51" t="n">
-        <v>2.803e-05</v>
+        <v>2.14</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>45635.35457175926</v>
+        <v>45641.69166666667</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.000862725400328239</v>
+        <v>0.0008592918094670554</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>aster-2</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>aster</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Pepe</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.7507239999999999</v>
+        <v>4.93e-06</v>
       </c>
       <c r="F52" t="n">
-        <v>2035419904</v>
+        <v>2075965729</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>176946024</v>
+        <v>1450366993</v>
       </c>
       <c r="I52" t="n">
-        <v>0.766236</v>
+        <v>5.34e-06</v>
       </c>
       <c r="J52" t="n">
-        <v>0.732133</v>
+        <v>4.3e-06</v>
       </c>
       <c r="K52" t="n">
-        <v>0.02004207</v>
+        <v>6.21765e-07</v>
       </c>
       <c r="L52" t="n">
-        <v>2.74293</v>
+        <v>14.417</v>
       </c>
       <c r="M52" t="n">
-        <v>2710487455.649731</v>
+        <v>420690000000000</v>
       </c>
       <c r="N52" t="n">
-        <v>7795741639.279952</v>
+        <v>420690000000000</v>
       </c>
       <c r="O52" t="n">
-        <v>2.41</v>
+        <v>2.803e-05</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>45924.13766203704</v>
+        <v>45635.35457175926</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0008237813945026729</v>
+        <v>0.0008404143930806991</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>polkadot</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>dot</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.00435338</v>
+        <v>1.18</v>
       </c>
       <c r="F53" t="n">
-        <v>2030520104</v>
+        <v>2008948588</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>184922999</v>
+        <v>197239330</v>
       </c>
       <c r="I53" t="n">
-        <v>0.00451054</v>
+        <v>1.22</v>
       </c>
       <c r="J53" t="n">
-        <v>0.00407465</v>
+        <v>1.16</v>
       </c>
       <c r="K53" t="n">
-        <v>0.00027591</v>
+        <v>-0.004677001194783426</v>
       </c>
       <c r="L53" t="n">
-        <v>6.7666</v>
+        <v>-0.39504</v>
       </c>
       <c r="M53" t="n">
-        <v>467279734243.4806</v>
+        <v>1703948257.127239</v>
       </c>
       <c r="N53" t="n">
-        <v>832769967768.4836</v>
+        <v>1703961108.757197</v>
       </c>
       <c r="O53" t="n">
-        <v>0.00881908</v>
+        <v>54.98</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>45914.36296296296</v>
+        <v>44504.25704861111</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0008209459501533471</v>
+        <v>0.0008016702480445927</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>polkadot</t>
+          <t>aster-2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>dot</t>
+          <t>aster</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1.18</v>
+        <v>0.72357</v>
       </c>
       <c r="F54" t="n">
-        <v>2017115893</v>
+        <v>1962436611</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>266894098</v>
+        <v>193979356</v>
       </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>0.763915</v>
       </c>
       <c r="J54" t="n">
-        <v>1.11</v>
+        <v>0.71743</v>
       </c>
       <c r="K54" t="n">
-        <v>0.076651</v>
+        <v>-0.03372300192623556</v>
       </c>
       <c r="L54" t="n">
-        <v>6.92083</v>
+        <v>-4.4531</v>
       </c>
       <c r="M54" t="n">
-        <v>1703808907.243623</v>
+        <v>2710487455.649731</v>
       </c>
       <c r="N54" t="n">
-        <v>1703819243.637835</v>
+        <v>7795741639.279952</v>
       </c>
       <c r="O54" t="n">
-        <v>54.98</v>
+        <v>2.41</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>44504.25704861111</v>
+        <v>45924.13766203704</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R54" t="b">
         <v>1</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0008131891244998261</v>
+        <v>0.0007747806082313388</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>pax-gold</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>paxg</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Morpho</t>
+          <t>PAX Gold</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2.75</v>
+        <v>4332.88</v>
       </c>
       <c r="F55" t="n">
-        <v>1919720910</v>
+        <v>1882396854</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>52265765</v>
+        <v>186709924</v>
       </c>
       <c r="I55" t="n">
-        <v>2.84</v>
+        <v>4369.08</v>
       </c>
       <c r="J55" t="n">
-        <v>2.52</v>
+        <v>4295.5</v>
       </c>
       <c r="K55" t="n">
-        <v>0.227306</v>
+        <v>-13.77313524242709</v>
       </c>
       <c r="L55" t="n">
-        <v>9.02125</v>
+        <v>-0.31687</v>
       </c>
       <c r="M55" t="n">
-        <v>699207451.3256872</v>
+        <v>434499.367539</v>
       </c>
       <c r="N55" t="n">
-        <v>1000000000</v>
+        <v>434499.367539</v>
       </c>
       <c r="O55" t="n">
-        <v>4.17</v>
+        <v>5619.09</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>45674.19883101852</v>
+        <v>46050.93814814815</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0007568280374758575</v>
+        <v>0.0007285077904478598</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>pax-gold</t>
+          <t>world-liberty-financial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>paxg</t>
+          <t>wlfi</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>PAX Gold</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4347.76</v>
+        <v>0.057917</v>
       </c>
       <c r="F56" t="n">
-        <v>1889049810</v>
+        <v>1839020856</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>160372105</v>
+        <v>71724577</v>
       </c>
       <c r="I56" t="n">
-        <v>4372.34</v>
+        <v>0.058305</v>
       </c>
       <c r="J56" t="n">
-        <v>4326.12</v>
+        <v>0.056587</v>
       </c>
       <c r="K56" t="n">
-        <v>-11.95432789098686</v>
+        <v>-3.1592783279993e-05</v>
       </c>
       <c r="L56" t="n">
-        <v>-0.2742</v>
+        <v>-0.05452</v>
       </c>
       <c r="M56" t="n">
-        <v>434499.367539</v>
+        <v>31777764435</v>
       </c>
       <c r="N56" t="n">
-        <v>434499.367539</v>
+        <v>100000000000</v>
       </c>
       <c r="O56" t="n">
-        <v>5619.09</v>
+        <v>0.331336</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>46050.93814814815</v>
+        <v>45901.18065972222</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R56" t="b">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0007390791095231636</v>
+        <v>0.000703431131961371</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>world-liberty-financial</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>wlfi</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>World Liberty Financial</t>
+          <t>Morpho</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.05751</v>
+        <v>2.61</v>
       </c>
       <c r="F57" t="n">
-        <v>1827430362</v>
+        <v>1826303769</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>50977157</v>
+        <v>33524527</v>
       </c>
       <c r="I57" t="n">
-        <v>0.05868</v>
+        <v>2.77</v>
       </c>
       <c r="J57" t="n">
-        <v>0.057433</v>
+        <v>2.56</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.000690303918718715</v>
+        <v>-0.1578461121207484</v>
       </c>
       <c r="L57" t="n">
-        <v>-1.18608</v>
+        <v>-5.7008</v>
       </c>
       <c r="M57" t="n">
-        <v>31777471043</v>
+        <v>699252762.2754086</v>
       </c>
       <c r="N57" t="n">
-        <v>100000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="O57" t="n">
-        <v>0.331336</v>
+        <v>4.17</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>45901.18065972222</v>
+        <v>45674.19883101852</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0007034208141559688</v>
+        <v>0.000696079092530671</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>worldcoin-wld</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>wld</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sky</t>
+          <t>Worldcoin</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.072577</v>
+        <v>0.45889</v>
       </c>
       <c r="F58" t="n">
-        <v>1699069436</v>
+        <v>1671424695</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>17930234</v>
+        <v>292053266</v>
       </c>
       <c r="I58" t="n">
-        <v>0.07318</v>
+        <v>0.476706</v>
       </c>
       <c r="J58" t="n">
-        <v>0.068775</v>
+        <v>0.429799</v>
       </c>
       <c r="K58" t="n">
-        <v>0.00370732</v>
+        <v>0.01019296</v>
       </c>
       <c r="L58" t="n">
-        <v>5.38306</v>
+        <v>2.27168</v>
       </c>
       <c r="M58" t="n">
-        <v>23426953149.00353</v>
+        <v>3646919863.262543</v>
       </c>
       <c r="N58" t="n">
-        <v>23459804203.60596</v>
+        <v>10000000000</v>
       </c>
       <c r="O58" t="n">
-        <v>0.100535</v>
+        <v>11.74</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>45630.09302083333</v>
+        <v>45360.67409722223</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0006291401777420459</v>
+        <v>0.0006065399505055902</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4358,34 +4358,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="F59" t="n">
-        <v>1643500300</v>
+        <v>1645830453</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>89056182</v>
+        <v>82486242</v>
       </c>
       <c r="I59" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="J59" t="n">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="K59" t="n">
-        <v>0.15801</v>
+        <v>-0.006557359252108874</v>
       </c>
       <c r="L59" t="n">
-        <v>5.65301</v>
+        <v>-0.2214</v>
       </c>
       <c r="M59" t="n">
-        <v>556899589.1864374</v>
+        <v>556904465.200667</v>
       </c>
       <c r="N59" t="n">
-        <v>556899589.1864374</v>
+        <v>556904695.8959877</v>
       </c>
       <c r="O59" t="n">
         <v>700.65</v>
@@ -4394,220 +4394,220 @@
         <v>44326.33741898148</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R59" t="b">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0005969831116029949</v>
+        <v>0.0005917433326651304</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>worldcoin-wld</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>wld</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Worldcoin</t>
+          <t>Sky</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.440412</v>
+        <v>0.06808400000000001</v>
       </c>
       <c r="F60" t="n">
-        <v>1602016980</v>
+        <v>1594747765</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>267402589</v>
+        <v>16921091</v>
       </c>
       <c r="I60" t="n">
-        <v>0.457331</v>
+        <v>0.072945</v>
       </c>
       <c r="J60" t="n">
-        <v>0.429347</v>
+        <v>0.066889</v>
       </c>
       <c r="K60" t="n">
-        <v>0.01056067</v>
+        <v>-0.004632569679609663</v>
       </c>
       <c r="L60" t="n">
-        <v>2.45682</v>
+        <v>-6.37071</v>
       </c>
       <c r="M60" t="n">
-        <v>3645494676.034653</v>
+        <v>23425541252.71795</v>
       </c>
       <c r="N60" t="n">
-        <v>10000000000</v>
+        <v>23459804203.60596</v>
       </c>
       <c r="O60" t="n">
-        <v>11.74</v>
+        <v>0.100535</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>45360.67409722223</v>
+        <v>45630.09302083333</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0005729773062057792</v>
+        <v>0.0005622112600763256</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>htx-dao</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>arb</t>
+          <t>htx</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Arbitrum</t>
+          <t>HTX DAO</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.230271</v>
+        <v>1.73e-06</v>
       </c>
       <c r="F61" t="n">
-        <v>1559573761</v>
+        <v>1555271183</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>553235680</v>
+        <v>5232003</v>
       </c>
       <c r="I61" t="n">
-        <v>0.247068</v>
+        <v>1.75e-06</v>
       </c>
       <c r="J61" t="n">
-        <v>0.203259</v>
+        <v>1.72e-06</v>
       </c>
       <c r="K61" t="n">
-        <v>0.02840191</v>
+        <v>1.0883e-08</v>
       </c>
       <c r="L61" t="n">
-        <v>14.0695</v>
+        <v>0.63264</v>
       </c>
       <c r="M61" t="n">
-        <v>6785574605</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="N61" t="n">
-        <v>10000000000</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="O61" t="n">
-        <v>2.39</v>
+        <v>3.75e-06</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>45303.18748842592</v>
+        <v>45629.67800925926</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0005484160209531665</v>
+        <v>0.0005393889433418985</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>htx-dao</t>
+          <t>venice-token</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>htx</t>
+          <t>vvv</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>HTX DAO</t>
+          <t>Venice Token</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1.72e-06</v>
+        <v>31.62</v>
       </c>
       <c r="F62" t="n">
-        <v>1546353942</v>
+        <v>1521169493</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>9478676</v>
+        <v>100418149</v>
       </c>
       <c r="I62" t="n">
-        <v>1.72e-06</v>
+        <v>32.8</v>
       </c>
       <c r="J62" t="n">
-        <v>1.7e-06</v>
+        <v>30.28</v>
       </c>
       <c r="K62" t="n">
-        <v>2.336e-09</v>
+        <v>-0.8492954790975276</v>
       </c>
       <c r="L62" t="n">
-        <v>0.13596</v>
+        <v>-2.61538</v>
       </c>
       <c r="M62" t="n">
-        <v>898232728634017.2</v>
+        <v>48108760.38154763</v>
       </c>
       <c r="N62" t="n">
-        <v>898232728634017.2</v>
+        <v>81026395.65784027</v>
       </c>
       <c r="O62" t="n">
-        <v>3.75e-06</v>
+        <v>34.53</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>45629.67800925926</v>
+        <v>46286.34548611111</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005407659003191282</v>
+        <v>0.0005196739748484449</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4626,34 +4626,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.998678</v>
+        <v>0.998822</v>
       </c>
       <c r="F63" t="n">
-        <v>1509307672</v>
+        <v>1515482265</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>13809872</v>
+        <v>3465055</v>
       </c>
       <c r="I63" t="n">
-        <v>0.999596</v>
+        <v>0.999067</v>
       </c>
       <c r="J63" t="n">
-        <v>0.99781</v>
+        <v>0.9980869999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>0.00053826</v>
+        <v>0.00033376</v>
       </c>
       <c r="L63" t="n">
-        <v>0.05393</v>
+        <v>0.03343</v>
       </c>
       <c r="M63" t="n">
-        <v>1511273305</v>
+        <v>1517262805</v>
       </c>
       <c r="N63" t="n">
-        <v>1511042343</v>
+        <v>1518156193</v>
       </c>
       <c r="O63" t="n">
         <v>1.24</v>
@@ -4662,86 +4662,86 @@
         <v>46212.39942129629</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0005193277524487862</v>
+        <v>0.0005163860580081039</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>venice-token</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>vvv</t>
+          <t>arb</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Venice Token</t>
+          <t>Arbitrum</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>31.31</v>
+        <v>0.217899</v>
       </c>
       <c r="F64" t="n">
-        <v>1505283839</v>
+        <v>1478091105</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>137801425</v>
+        <v>380079918</v>
       </c>
       <c r="I64" t="n">
-        <v>34.53</v>
+        <v>0.239004</v>
       </c>
       <c r="J64" t="n">
-        <v>27.73</v>
+        <v>0.215682</v>
       </c>
       <c r="K64" t="n">
-        <v>2.32</v>
+        <v>-0.02152506723095796</v>
       </c>
       <c r="L64" t="n">
-        <v>8.005699999999999</v>
+        <v>-8.99037</v>
       </c>
       <c r="M64" t="n">
-        <v>48098269.92982138</v>
+        <v>6785574605</v>
       </c>
       <c r="N64" t="n">
-        <v>81020526.78963831</v>
+        <v>10000000000</v>
       </c>
       <c r="O64" t="n">
-        <v>34.53</v>
+        <v>2.39</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>46286.34548611111</v>
+        <v>45303.18748842592</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R64" t="b">
         <v>1</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0005169992177040046</v>
+        <v>0.0004947693715232498</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4760,28 +4760,28 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="F65" t="n">
-        <v>1484368859</v>
+        <v>1477853649</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>21371401</v>
+        <v>21410734</v>
       </c>
       <c r="I65" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="K65" t="n">
-        <v>0.105322</v>
+        <v>0.01659584</v>
       </c>
       <c r="L65" t="n">
-        <v>5.22639</v>
+        <v>0.79187</v>
       </c>
       <c r="M65" t="n">
         <v>699992029.6481038</v>
@@ -4796,86 +4796,86 @@
         <v>45653.15375</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0005048960171943381</v>
+        <v>0.0004946320927678983</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>united-stables</t>
+          <t>ethereum-classic</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>United Stables</t>
+          <t>Ethereum Classic</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.999817</v>
+        <v>9.08</v>
       </c>
       <c r="F66" t="n">
-        <v>1412321040</v>
+        <v>1438971590</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
       </c>
       <c r="H66" t="n">
-        <v>232093814</v>
+        <v>100830875</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>9.01</v>
       </c>
       <c r="J66" t="n">
-        <v>0.999466</v>
+        <v>8.56</v>
       </c>
       <c r="K66" t="n">
-        <v>6.242e-05</v>
+        <v>0.31211</v>
       </c>
       <c r="L66" t="n">
-        <v>0.00624</v>
+        <v>3.55963</v>
       </c>
       <c r="M66" t="n">
-        <v>1412429007.8</v>
+        <v>158248154.4119364</v>
       </c>
       <c r="N66" t="n">
-        <v>1412429007.8</v>
+        <v>158248154.4119364</v>
       </c>
       <c r="O66" t="n">
-        <v>1.008</v>
+        <v>167.09</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>46058.54591435185</v>
+        <v>44322.44053240741</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0004632029723221382</v>
+        <v>0.0004721534834043857</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4897,7 +4897,7 @@
         <v>1.16</v>
       </c>
       <c r="F67" t="n">
-        <v>1406563294</v>
+        <v>1425892570</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
@@ -4912,16 +4912,16 @@
         <v>1.16</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.000997568167990126</v>
+        <v>-0.001697994121032886</v>
       </c>
       <c r="L67" t="n">
-        <v>-0.08579000000000001</v>
+        <v>-0.14607</v>
       </c>
       <c r="M67" t="n">
-        <v>1210660472.36437</v>
+        <v>1228441715.9192</v>
       </c>
       <c r="N67" t="n">
-        <v>1210660472.36437</v>
+        <v>1228441715.9192</v>
       </c>
       <c r="O67" t="n">
         <v>1.18</v>
@@ -4930,153 +4930,153 @@
         <v>46255.48263888889</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0004598710468638433</v>
+        <v>0.0004645922022120093</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>usdgo</t>
+          <t>united-stables</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>usdgo</t>
+          <t>u</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>USDGO</t>
+          <t>United Stables</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9997509999999999</v>
+        <v>0.999498</v>
       </c>
       <c r="F68" t="n">
-        <v>1404123443</v>
+        <v>1418714402</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>42030632</v>
+        <v>187654515</v>
       </c>
       <c r="I68" t="n">
         <v>1</v>
       </c>
       <c r="J68" t="n">
-        <v>0.999719</v>
+        <v>0.999347</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.000266318963444978</v>
+        <v>-0.000145093162767673</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.02663</v>
+        <v>-0.01451</v>
       </c>
       <c r="M68" t="n">
-        <v>1403784804.97</v>
+        <v>1419429007.8</v>
       </c>
       <c r="N68" t="n">
-        <v>1403784804.97</v>
+        <v>1419429007.8</v>
       </c>
       <c r="O68" t="n">
-        <v>1.002</v>
+        <v>1.008</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>46092.00303240741</v>
+        <v>46058.54591435185</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0004584591399021005</v>
+        <v>0.0004604423387899702</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ethereum-classic</t>
+          <t>usdgo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>usdgo</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ethereum Classic</t>
+          <t>USDGO</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>8.779999999999999</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>1387516750</v>
+        <v>1404486256</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>73190996</v>
+        <v>80565461</v>
       </c>
       <c r="I69" t="n">
-        <v>8.85</v>
+        <v>1.001</v>
       </c>
       <c r="J69" t="n">
-        <v>8.369999999999999</v>
+        <v>0.999579</v>
       </c>
       <c r="K69" t="n">
-        <v>0.351076</v>
+        <v>5.143e-05</v>
       </c>
       <c r="L69" t="n">
-        <v>4.16573</v>
+        <v>0.00514</v>
       </c>
       <c r="M69" t="n">
-        <v>158238312.7479364</v>
+        <v>1403784804.97</v>
       </c>
       <c r="N69" t="n">
-        <v>158238719.9927364</v>
+        <v>1403784804.97</v>
       </c>
       <c r="O69" t="n">
-        <v>167.09</v>
+        <v>1.002</v>
       </c>
       <c r="P69" s="1" t="n">
-        <v>44322.44053240741</v>
+        <v>46092.00303240741</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0004488490836084069</v>
+        <v>0.0004522167215226072</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5095,28 +5095,28 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.996047</v>
+        <v>0.995534</v>
       </c>
       <c r="F70" t="n">
-        <v>1371628457</v>
+        <v>1370891045</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>899679</v>
+        <v>411852</v>
       </c>
       <c r="I70" t="n">
-        <v>0.996566</v>
+        <v>0.996795</v>
       </c>
       <c r="J70" t="n">
-        <v>0.995507</v>
+        <v>0.995154</v>
       </c>
       <c r="K70" t="n">
-        <v>0.00023299</v>
+        <v>-0.000253253266134124</v>
       </c>
       <c r="L70" t="n">
-        <v>0.0234</v>
+        <v>-0.02543</v>
       </c>
       <c r="M70" t="n">
         <v>1377035569.737884</v>
@@ -5131,19 +5131,19 @@
         <v>45785.55951388889</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R70" t="b">
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0004396547551445341</v>
+        <v>0.0004327945601459738</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5162,28 +5162,28 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.999924</v>
+        <v>0.999744</v>
       </c>
       <c r="F71" t="n">
-        <v>1319931512</v>
+        <v>1319667230</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>4921075</v>
+        <v>9828086</v>
       </c>
       <c r="I71" t="n">
-        <v>0.999837</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
-        <v>0.99952</v>
+        <v>0.999545</v>
       </c>
       <c r="K71" t="n">
-        <v>0.00035509</v>
+        <v>6.561e-05</v>
       </c>
       <c r="L71" t="n">
-        <v>0.03552</v>
+        <v>0.00656</v>
       </c>
       <c r="M71" t="n">
         <v>1320000000</v>
@@ -5198,823 +5198,823 @@
         <v>45940.56990740741</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R71" t="b">
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0004097384706885029</v>
+        <v>0.0004031808988042778</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>lighter</t>
+          <t>akedo</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>lit</t>
+          <t>ake</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Lighter</t>
+          <t>Akedo</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4.98</v>
+        <v>0.05307</v>
       </c>
       <c r="F72" t="n">
-        <v>1243289462</v>
+        <v>1211456515</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>96086565</v>
+        <v>67812608</v>
       </c>
       <c r="I72" t="n">
-        <v>5.14</v>
+        <v>0.06265900000000001</v>
       </c>
       <c r="J72" t="n">
-        <v>4.65</v>
+        <v>0.04984009</v>
       </c>
       <c r="K72" t="n">
-        <v>0.29391</v>
+        <v>0.00211539</v>
       </c>
       <c r="L72" t="n">
-        <v>6.2781</v>
+        <v>4.15155</v>
       </c>
       <c r="M72" t="n">
-        <v>250000000</v>
+        <v>22796250000</v>
       </c>
       <c r="N72" t="n">
-        <v>1000000000</v>
+        <v>100000000000</v>
       </c>
       <c r="O72" t="n">
-        <v>7.86</v>
+        <v>0.146656</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>46021.04538194444</v>
+        <v>46285.43993055556</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0003653868098873982</v>
+        <v>0.000340621804610439</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>polygon-ecosystem-token</t>
+          <t>lighter</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>pol</t>
+          <t>lit</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>POL (ex-MATIC)</t>
+          <t>Lighter</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.113591</v>
+        <v>4.73</v>
       </c>
       <c r="F73" t="n">
-        <v>1215803428</v>
+        <v>1181549357</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>183440017</v>
+        <v>72495629</v>
       </c>
       <c r="I73" t="n">
-        <v>0.114508</v>
+        <v>5.06</v>
       </c>
       <c r="J73" t="n">
-        <v>0.104</v>
+        <v>4.66</v>
       </c>
       <c r="K73" t="n">
-        <v>0.0096837</v>
+        <v>-0.2659201923028451</v>
       </c>
       <c r="L73" t="n">
-        <v>9.319520000000001</v>
+        <v>-5.32724</v>
       </c>
       <c r="M73" t="n">
-        <v>10718173594.42111</v>
+        <v>250000000</v>
       </c>
       <c r="N73" t="n">
-        <v>10718173594.42111</v>
+        <v>1000000000</v>
       </c>
       <c r="O73" t="n">
-        <v>1.29</v>
+        <v>7.86</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>45364.45493055556</v>
+        <v>46021.04538194444</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R73" t="b">
         <v>1</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003494810341841697</v>
+        <v>0.0003233317911917861</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>akedo</t>
+          <t>gatechain-token</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ake</t>
+          <t>gt</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Akedo</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.052968</v>
+        <v>10.95</v>
       </c>
       <c r="F74" t="n">
-        <v>1210389596</v>
+        <v>1169349939</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>117071699</v>
+        <v>2661408</v>
       </c>
       <c r="I74" t="n">
-        <v>0.06970899999999999</v>
+        <v>11.4</v>
       </c>
       <c r="J74" t="n">
-        <v>0.03148813</v>
+        <v>10.77</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.000541111920599274</v>
+        <v>-0.1406477564008917</v>
       </c>
       <c r="L74" t="n">
-        <v>-1.01126</v>
+        <v>-1.2679</v>
       </c>
       <c r="M74" t="n">
-        <v>22796250000</v>
+        <v>106636935.4621455</v>
       </c>
       <c r="N74" t="n">
-        <v>100000000000</v>
+        <v>118888167.5691907</v>
       </c>
       <c r="O74" t="n">
-        <v>0.146656</v>
+        <v>25.38</v>
       </c>
       <c r="P74" s="1" t="n">
-        <v>46285.43993055556</v>
+        <v>45682.66666666666</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R74" t="b">
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0003463481268506867</v>
+        <v>0.0003162790280733462</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>kaspa</t>
+          <t>polygon-ecosystem-token</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>kas</t>
+          <t>pol</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Kaspa</t>
+          <t>POL (ex-MATIC)</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.04256497</v>
+        <v>0.108627</v>
       </c>
       <c r="F75" t="n">
-        <v>1181593079</v>
+        <v>1164559209</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
       </c>
       <c r="H75" t="n">
-        <v>22251594</v>
+        <v>85839540</v>
       </c>
       <c r="I75" t="n">
-        <v>0.04197595</v>
+        <v>0.113856</v>
       </c>
       <c r="J75" t="n">
-        <v>0.0386518</v>
+        <v>0.107094</v>
       </c>
       <c r="K75" t="n">
-        <v>0.00356807</v>
+        <v>-0.004522956731351641</v>
       </c>
       <c r="L75" t="n">
-        <v>9.149609999999999</v>
+        <v>-3.99731</v>
       </c>
       <c r="M75" t="n">
-        <v>27710766029.85906</v>
+        <v>10718755191.33206</v>
       </c>
       <c r="N75" t="n">
-        <v>27713280689.21</v>
+        <v>10718755191.33206</v>
       </c>
       <c r="O75" t="n">
-        <v>0.207411</v>
+        <v>1.29</v>
       </c>
       <c r="P75" s="1" t="n">
-        <v>45504.69498842592</v>
+        <v>45364.45493055556</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0003296839933334172</v>
+        <v>0.0003135093972717453</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>gatechain-token</t>
+          <t>kaspa</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>gt</t>
+          <t>kas</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Kaspa</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>11.04</v>
+        <v>0.04192681</v>
       </c>
       <c r="F76" t="n">
-        <v>1177930690</v>
+        <v>1160236232</v>
       </c>
       <c r="G76" t="n">
         <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>6827786</v>
+        <v>33267835</v>
       </c>
       <c r="I76" t="n">
-        <v>11.4</v>
+        <v>0.04506876</v>
       </c>
       <c r="J76" t="n">
-        <v>10.34</v>
+        <v>0.04113569</v>
       </c>
       <c r="K76" t="n">
-        <v>0.713846</v>
+        <v>0.00016146</v>
       </c>
       <c r="L76" t="n">
-        <v>6.91129</v>
+        <v>0.38659</v>
       </c>
       <c r="M76" t="n">
-        <v>106635883.2020504</v>
+        <v>27714964311.97035</v>
       </c>
       <c r="N76" t="n">
-        <v>118887115.3090956</v>
+        <v>27715035504.33063</v>
       </c>
       <c r="O76" t="n">
-        <v>25.38</v>
+        <v>0.207411</v>
       </c>
       <c r="P76" s="1" t="n">
-        <v>45682.66666666666</v>
+        <v>45504.69498842592</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0003275646210743284</v>
+        <v>0.0003110101851988854</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>algorand</t>
+          <t>quant-network</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>algo</t>
+          <t>qnt</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Algorand</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.112858</v>
+        <v>72.55</v>
       </c>
       <c r="F77" t="n">
-        <v>1018245871</v>
+        <v>1054175329</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>91425780</v>
+        <v>22596204</v>
       </c>
       <c r="I77" t="n">
-        <v>0.117367</v>
+        <v>74.06</v>
       </c>
       <c r="J77" t="n">
-        <v>0.107695</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.000398156635310759</v>
+        <v>4.91</v>
       </c>
       <c r="L77" t="n">
-        <v>-0.35155</v>
+        <v>7.25948</v>
       </c>
       <c r="M77" t="n">
-        <v>9042435038.282944</v>
+        <v>14544176.16408117</v>
       </c>
       <c r="N77" t="n">
-        <v>9042705520.702909</v>
+        <v>14612493</v>
       </c>
       <c r="O77" t="n">
-        <v>3.56</v>
+        <v>427.42</v>
       </c>
       <c r="P77" s="1" t="n">
-        <v>43636.28563657407</v>
+        <v>44450.05208333334</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002351572947127058</v>
+        <v>0.0002496939465892375</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jupiter-exchange-solana</t>
+          <t>pi-network</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>jup</t>
+          <t>pi</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Pi Network</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.306944</v>
+        <v>0.08996</v>
       </c>
       <c r="F78" t="n">
-        <v>1016626399</v>
+        <v>1011705804</v>
       </c>
       <c r="G78" t="n">
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>126703075</v>
+        <v>12020749</v>
       </c>
       <c r="I78" t="n">
-        <v>0.317727</v>
+        <v>0.094476</v>
       </c>
       <c r="J78" t="n">
-        <v>0.271277</v>
+        <v>0.087199</v>
       </c>
       <c r="K78" t="n">
-        <v>0.03662334</v>
+        <v>0.00152747</v>
       </c>
       <c r="L78" t="n">
-        <v>13.5481</v>
+        <v>1.72728</v>
       </c>
       <c r="M78" t="n">
-        <v>3319369204.37</v>
+        <v>11243022007.461</v>
       </c>
       <c r="N78" t="n">
-        <v>6861486876.193287</v>
+        <v>17296956934.55538</v>
       </c>
       <c r="O78" t="n">
-        <v>2</v>
+        <v>2.99</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>45322.29359953704</v>
+        <v>45714.36184027778</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002342201293730407</v>
+        <v>0.0002251413409175848</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>pi-network</t>
+          <t>kucoin-shares</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>pi</t>
+          <t>kcs</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Pi Network</t>
+          <t>KuCoin</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.089172</v>
+        <v>7.39</v>
       </c>
       <c r="F79" t="n">
-        <v>1000832394</v>
+        <v>1012925378</v>
       </c>
       <c r="G79" t="n">
         <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>8282429</v>
+        <v>37024362</v>
       </c>
       <c r="I79" t="n">
-        <v>0.090407</v>
+        <v>7.47</v>
       </c>
       <c r="J79" t="n">
-        <v>0.08477800000000001</v>
+        <v>7.2</v>
       </c>
       <c r="K79" t="n">
-        <v>0.00432623</v>
+        <v>0.108718</v>
       </c>
       <c r="L79" t="n">
-        <v>5.09892</v>
+        <v>1.49409</v>
       </c>
       <c r="M79" t="n">
-        <v>11243021168.581</v>
+        <v>137155021.2773955</v>
       </c>
       <c r="N79" t="n">
-        <v>17296955494.70923</v>
+        <v>142155021.2773955</v>
       </c>
       <c r="O79" t="n">
-        <v>2.99</v>
+        <v>28.83</v>
       </c>
       <c r="P79" s="1" t="n">
-        <v>45714.36184027778</v>
+        <v>44531.29832175926</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R79" t="b">
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002250803640294603</v>
+        <v>0.00022584640459582</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>kucoin-shares</t>
+          <t>algorand</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>kcs</t>
+          <t>algo</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>KuCoin</t>
+          <t>Algorand</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>7.24</v>
+        <v>0.110723</v>
       </c>
       <c r="F80" t="n">
-        <v>991808381</v>
+        <v>1001249240</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>42457066</v>
+        <v>68701276</v>
       </c>
       <c r="I80" t="n">
-        <v>7.34</v>
+        <v>0.115246</v>
       </c>
       <c r="J80" t="n">
-        <v>7.08</v>
+        <v>0.108049</v>
       </c>
       <c r="K80" t="n">
-        <v>0.123972</v>
+        <v>-0.004461068946511465</v>
       </c>
       <c r="L80" t="n">
-        <v>1.74107</v>
+        <v>-3.87299</v>
       </c>
       <c r="M80" t="n">
-        <v>137155021.2773955</v>
+        <v>9042752944.706263</v>
       </c>
       <c r="N80" t="n">
-        <v>142155021.2773955</v>
+        <v>9042892862.500069</v>
       </c>
       <c r="O80" t="n">
-        <v>28.83</v>
+        <v>3.56</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>44531.29832175926</v>
+        <v>43636.28563657407</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R80" t="b">
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002198582964615814</v>
+        <v>0.0002190961616373268</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>quant-network</t>
+          <t>blockchain-capital</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>qnt</t>
+          <t>bcap</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Blockchain Capital</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>67.02</v>
+        <v>107.53</v>
       </c>
       <c r="F81" t="n">
-        <v>974120723</v>
+        <v>979825296</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>11479032</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>67.93000000000001</v>
+        <v>107.53</v>
       </c>
       <c r="J81" t="n">
-        <v>63.8</v>
+        <v>106.54</v>
       </c>
       <c r="K81" t="n">
-        <v>2.88</v>
+        <v>0.99</v>
       </c>
       <c r="L81" t="n">
-        <v>4.48507</v>
+        <v>0.92923</v>
       </c>
       <c r="M81" t="n">
-        <v>14544176.16408117</v>
+        <v>9112111</v>
       </c>
       <c r="N81" t="n">
-        <v>14612493</v>
+        <v>9112111</v>
       </c>
       <c r="O81" t="n">
-        <v>427.42</v>
+        <v>107.53</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>44450.05208333334</v>
+        <v>46287.17361111111</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R81" t="b">
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0002096227011456687</v>
+        <v>0.0002067104886409001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>blockchain-capital</t>
+          <t>jupiter-exchange-solana</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>bcap</t>
+          <t>jup</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Blockchain Capital</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106.54</v>
+        <v>0.294238</v>
       </c>
       <c r="F82" t="n">
-        <v>970804306</v>
+        <v>976366984</v>
       </c>
       <c r="G82" t="n">
         <v>81</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>95339920</v>
       </c>
       <c r="I82" t="n">
-        <v>106.54</v>
+        <v>0.308343</v>
       </c>
       <c r="J82" t="n">
-        <v>106.54</v>
+        <v>0.288854</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>-0.009972872788550136</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>-3.27827</v>
       </c>
       <c r="M82" t="n">
-        <v>9112111</v>
+        <v>3319369204.37</v>
       </c>
       <c r="N82" t="n">
-        <v>9112111</v>
+        <v>6861486766.286829</v>
       </c>
       <c r="O82" t="n">
-        <v>106.54</v>
+        <v>2</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>46280.14583333334</v>
+        <v>45322.29359953704</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R82" t="b">
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0002077035379466282</v>
+        <v>0.0002047111592199672</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>cosmos</t>
+          <t>render-token</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>render</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cosmos Hub</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="F83" t="n">
-        <v>957099766</v>
+        <v>958862229</v>
       </c>
       <c r="G83" t="n">
         <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>77080955</v>
+        <v>109902421</v>
       </c>
       <c r="I83" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="J83" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="K83" t="n">
-        <v>0.06481000000000001</v>
+        <v>0.0304896</v>
       </c>
       <c r="L83" t="n">
-        <v>3.73722</v>
+        <v>1.67729</v>
       </c>
       <c r="M83" t="n">
-        <v>531968735.793199</v>
+        <v>518776241.2826915</v>
       </c>
       <c r="N83" t="n">
-        <v>531981425.106379</v>
+        <v>533536414.5626915</v>
       </c>
       <c r="O83" t="n">
-        <v>43.84</v>
+        <v>13.53</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>44458.66666666666</v>
+        <v>45368.35444444444</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0001997729161859215</v>
+        <v>0.0001945912592000378</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6033,28 +6033,28 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.113382</v>
+        <v>0.11566</v>
       </c>
       <c r="F84" t="n">
-        <v>928875168</v>
+        <v>946987396</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>41477573</v>
+        <v>42687627</v>
       </c>
       <c r="I84" t="n">
-        <v>0.116713</v>
+        <v>0.117046</v>
       </c>
       <c r="J84" t="n">
-        <v>0.111332</v>
+        <v>0.111786</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.002727350903736575</v>
+        <v>0.00320481</v>
       </c>
       <c r="L84" t="n">
-        <v>-2.34894</v>
+        <v>2.84987</v>
       </c>
       <c r="M84" t="n">
         <v>8188743036.341737</v>
@@ -6069,86 +6069,86 @@
         <v>44290.85721064815</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R84" t="b">
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001834397440337735</v>
+        <v>0.0001877261461085745</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>render-token</t>
+          <t>cosmos</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>render</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>Cosmos Hub</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="F85" t="n">
-        <v>919580013</v>
+        <v>939677401</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>170326835</v>
+        <v>68387794</v>
       </c>
       <c r="I85" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="J85" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="K85" t="n">
-        <v>0.216485</v>
+        <v>-0.03375685693328645</v>
       </c>
       <c r="L85" t="n">
-        <v>13.88918</v>
+        <v>-1.87549</v>
       </c>
       <c r="M85" t="n">
-        <v>518776241.2826915</v>
+        <v>532132124.756035</v>
       </c>
       <c r="N85" t="n">
-        <v>533536414.5626915</v>
+        <v>532132124.756035</v>
       </c>
       <c r="O85" t="n">
-        <v>13.53</v>
+        <v>43.84</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>45368.35444444444</v>
+        <v>44458.66666666666</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001780607704591667</v>
+        <v>0.0001835000704767714</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6167,28 +6167,28 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.8806079999999999</v>
+        <v>0.883286</v>
       </c>
       <c r="F86" t="n">
-        <v>879827644</v>
+        <v>883120631</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
       </c>
       <c r="H86" t="n">
-        <v>7817219</v>
+        <v>5434240</v>
       </c>
       <c r="I86" t="n">
-        <v>0.87577</v>
+        <v>0.895352</v>
       </c>
       <c r="J86" t="n">
-        <v>0.819816</v>
+        <v>0.857331</v>
       </c>
       <c r="K86" t="n">
-        <v>0.060156</v>
+        <v>0.01110932</v>
       </c>
       <c r="L86" t="n">
-        <v>7.33199</v>
+        <v>1.27375</v>
       </c>
       <c r="M86" t="n">
         <v>1000000000</v>
@@ -6203,488 +6203,488 @@
         <v>44328.27623842593</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001550566417083263</v>
+        <v>0.0001508033056348675</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>pancakeswap-token</t>
+          <t>filecoin</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>fil</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2.61</v>
+        <v>1.017</v>
       </c>
       <c r="F87" t="n">
-        <v>832854645</v>
+        <v>845663649</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>136695825</v>
+        <v>219600040</v>
       </c>
       <c r="I87" t="n">
-        <v>2.62</v>
+        <v>1.018</v>
       </c>
       <c r="J87" t="n">
-        <v>2.45</v>
+        <v>0.953556</v>
       </c>
       <c r="K87" t="n">
-        <v>0.151086</v>
+        <v>0.03429483</v>
       </c>
       <c r="L87" t="n">
-        <v>6.13663</v>
+        <v>3.48977</v>
       </c>
       <c r="M87" t="n">
-        <v>318981673.778035</v>
+        <v>830734725</v>
       </c>
       <c r="N87" t="n">
-        <v>330627631.6127986</v>
+        <v>1957034903</v>
       </c>
       <c r="O87" t="n">
-        <v>43.96</v>
+        <v>236.84</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>44316.08914351852</v>
+        <v>44287.22894675926</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001278740374009177</v>
+        <v>0.0001291485659433783</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>filecoin</t>
+          <t>pancakeswap-token</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.968076</v>
+        <v>2.53</v>
       </c>
       <c r="F88" t="n">
-        <v>803262272</v>
+        <v>807655840</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>201765623</v>
+        <v>100050581</v>
       </c>
       <c r="I88" t="n">
-        <v>1.015</v>
+        <v>2.62</v>
       </c>
       <c r="J88" t="n">
-        <v>0.926796</v>
+        <v>2.46</v>
       </c>
       <c r="K88" t="n">
-        <v>0.04226669</v>
+        <v>-0.01384237113231146</v>
       </c>
       <c r="L88" t="n">
-        <v>4.56538</v>
+        <v>-0.54375</v>
       </c>
       <c r="M88" t="n">
-        <v>830669925</v>
+        <v>318995522.7365205</v>
       </c>
       <c r="N88" t="n">
-        <v>1957036618</v>
+        <v>330627631.6090779</v>
       </c>
       <c r="O88" t="n">
-        <v>236.84</v>
+        <v>43.96</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>44287.22894675926</v>
+        <v>44316.08914351852</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R88" t="b">
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001107493533717748</v>
+        <v>0.000107175380539951</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>vechain</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>vet</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Spiko EU T-Bills Money Market Fund</t>
+          <t>VeChain</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1.21</v>
+        <v>0.009173819999999999</v>
       </c>
       <c r="F89" t="n">
-        <v>784718961</v>
+        <v>788851032</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>19849153</v>
       </c>
       <c r="I89" t="n">
-        <v>1.22</v>
+        <v>0.00934508</v>
       </c>
       <c r="J89" t="n">
-        <v>1.21</v>
+        <v>0.00863981</v>
       </c>
       <c r="K89" t="n">
-        <v>-0.000973066503648035</v>
+        <v>0.00039157</v>
       </c>
       <c r="L89" t="n">
-        <v>-0.08003</v>
+        <v>4.45867</v>
       </c>
       <c r="M89" t="n">
-        <v>645949689.8613</v>
+        <v>85985041177</v>
       </c>
       <c r="N89" t="n">
-        <v>645949689.8613</v>
+        <v>85985041177</v>
       </c>
       <c r="O89" t="n">
-        <v>1.26</v>
+        <v>0.280991</v>
       </c>
       <c r="P89" s="1" t="n">
-        <v>46049.54175925926</v>
+        <v>44304.71413194444</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R89" t="b">
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001000186038732764</v>
+        <v>9.630389008755857e-05</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-aaa-clo-fund</t>
+          <t>injective-protocol</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>jaaa</t>
+          <t>inj</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy AAA CLO Fund</t>
+          <t>Injective</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1.05</v>
+        <v>7.81</v>
       </c>
       <c r="F90" t="n">
-        <v>776845619</v>
+        <v>780760725</v>
       </c>
       <c r="G90" t="n">
         <v>89</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>177768409</v>
       </c>
       <c r="I90" t="n">
-        <v>1.05</v>
+        <v>8.02</v>
       </c>
       <c r="J90" t="n">
-        <v>1.05</v>
+        <v>7.5</v>
       </c>
       <c r="K90" t="n">
-        <v>0.000508</v>
+        <v>-0.1394066408438617</v>
       </c>
       <c r="L90" t="n">
-        <v>0.04839</v>
+        <v>-1.75449</v>
       </c>
       <c r="M90" t="n">
-        <v>739569820.670837</v>
+        <v>100000000</v>
       </c>
       <c r="N90" t="n">
-        <v>739569820.670837</v>
+        <v>100000000</v>
       </c>
       <c r="O90" t="n">
-        <v>1.05</v>
+        <v>52.62</v>
       </c>
       <c r="P90" s="1" t="n">
-        <v>46286.30578703704</v>
+        <v>45365.29608796296</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>9.546241319524659e-05</v>
+        <v>9.162669820623634e-05</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Dash</t>
+          <t>Spiko EU T-Bills Money Market Fund</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>60.37</v>
+        <v>1.21</v>
       </c>
       <c r="F91" t="n">
-        <v>774060503</v>
+        <v>780346488</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>161994185</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>61.42</v>
+        <v>1.22</v>
       </c>
       <c r="J91" t="n">
-        <v>54.89</v>
+        <v>1.21</v>
       </c>
       <c r="K91" t="n">
-        <v>5.44</v>
+        <v>-0.001798923932436081</v>
       </c>
       <c r="L91" t="n">
-        <v>9.900130000000001</v>
+        <v>-0.14801</v>
       </c>
       <c r="M91" t="n">
-        <v>12841975.17033605</v>
+        <v>642998758.0930901</v>
       </c>
       <c r="N91" t="n">
-        <v>12841989.85954539</v>
+        <v>642998758.0930901</v>
       </c>
       <c r="O91" t="n">
-        <v>1493.59</v>
+        <v>1.26</v>
       </c>
       <c r="P91" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>46049.54175925926</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>9.385070630426795e-05</v>
+        <v>9.13872183035153e-05</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>injective-protocol</t>
+          <t>janus-henderson-anemoy-aaa-clo-fund</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>inj</t>
+          <t>jaaa</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Injective</t>
+          <t>Janus Henderson Anemoy AAA CLO Fund</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>7.71</v>
+        <v>1.05</v>
       </c>
       <c r="F92" t="n">
-        <v>769674354</v>
+        <v>776900347</v>
       </c>
       <c r="G92" t="n">
         <v>91</v>
       </c>
       <c r="H92" t="n">
-        <v>187091879</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>8.199999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="J92" t="n">
-        <v>7.58</v>
+        <v>1.05</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.2849914879713022</v>
+        <v>7.4e-05</v>
       </c>
       <c r="L92" t="n">
-        <v>-3.56668</v>
+        <v>0.00704</v>
       </c>
       <c r="M92" t="n">
-        <v>100000000</v>
+        <v>739569820.670837</v>
       </c>
       <c r="N92" t="n">
-        <v>100000000</v>
+        <v>739569820.670837</v>
       </c>
       <c r="O92" t="n">
-        <v>52.62</v>
+        <v>1.05</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>45365.29608796296</v>
+        <v>46287.38530092593</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R92" t="b">
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>9.131250445983524e-05</v>
+        <v>8.93949252166038e-05</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>vechain</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>vet</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VeChain</t>
+          <t>Dash</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.00893233</v>
+        <v>59.63</v>
       </c>
       <c r="F93" t="n">
-        <v>767070561</v>
+        <v>765570243</v>
       </c>
       <c r="G93" t="n">
         <v>92</v>
       </c>
       <c r="H93" t="n">
-        <v>18904924</v>
+        <v>155850865</v>
       </c>
       <c r="I93" t="n">
-        <v>0.00909602</v>
+        <v>61.58</v>
       </c>
       <c r="J93" t="n">
-        <v>0.008248190000000001</v>
+        <v>58.53</v>
       </c>
       <c r="K93" t="n">
-        <v>0.00070602</v>
+        <v>0.237943</v>
       </c>
       <c r="L93" t="n">
-        <v>8.58253</v>
+        <v>0.40065</v>
       </c>
       <c r="M93" t="n">
-        <v>85985041177</v>
+        <v>12842152.9611448</v>
       </c>
       <c r="N93" t="n">
-        <v>85985041177</v>
+        <v>12842634.46163034</v>
       </c>
       <c r="O93" t="n">
-        <v>0.280991</v>
+        <v>1493.59</v>
       </c>
       <c r="P93" s="1" t="n">
-        <v>44304.71413194444</v>
+        <v>43088.66666666666</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>8.980572660182791e-05</v>
+        <v>8.284473244353147e-05</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6706,7 +6706,7 @@
         <v>11.22</v>
       </c>
       <c r="F94" t="n">
-        <v>720195294</v>
+        <v>733020371</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
@@ -6721,372 +6721,372 @@
         <v>11.22</v>
       </c>
       <c r="K94" t="n">
-        <v>0.001094</v>
+        <v>0.003219</v>
       </c>
       <c r="L94" t="n">
-        <v>0.00975</v>
+        <v>0.0287</v>
       </c>
       <c r="M94" t="n">
-        <v>64206795.204266</v>
+        <v>65331426.661091</v>
       </c>
       <c r="N94" t="n">
-        <v>64206795.204266</v>
+        <v>64875097.983642</v>
       </c>
       <c r="O94" t="n">
         <v>11.22</v>
       </c>
       <c r="P94" s="1" t="n">
-        <v>46286.55219907407</v>
+        <v>46287.57291666666</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R94" t="b">
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>6.267967840837254e-05</v>
+        <v>6.402690549870999e-05</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ether-fi</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ethfi</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Ether.fi</t>
+          <t>GHO</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.724214</v>
+        <v>0.999034</v>
       </c>
       <c r="F95" t="n">
-        <v>698709596</v>
+        <v>698327318</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>55805811</v>
+        <v>6496403</v>
       </c>
       <c r="I95" t="n">
-        <v>0.769383</v>
+        <v>0.99935</v>
       </c>
       <c r="J95" t="n">
-        <v>0.704524</v>
+        <v>0.998814</v>
       </c>
       <c r="K95" t="n">
-        <v>0.0248904</v>
+        <v>4.738e-05</v>
       </c>
       <c r="L95" t="n">
-        <v>3.55921</v>
+        <v>0.00474</v>
       </c>
       <c r="M95" t="n">
-        <v>965350000</v>
+        <v>699000000</v>
       </c>
       <c r="N95" t="n">
-        <v>965350000</v>
+        <v>699000000</v>
       </c>
       <c r="O95" t="n">
-        <v>8.529999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="P95" s="1" t="n">
-        <v>45378.63525462963</v>
+        <v>45350.38608796296</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R95" t="b">
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>5.024621153514861e-05</v>
+        <v>4.397005650275941e-05</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>aerodrome-finance</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>aero</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>GHO</t>
+          <t>Aerodrome Finance</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.999173</v>
+        <v>0.694096</v>
       </c>
       <c r="F96" t="n">
-        <v>698438859</v>
+        <v>688916355</v>
       </c>
       <c r="G96" t="n">
         <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>5302269</v>
+        <v>57794387</v>
       </c>
       <c r="I96" t="n">
-        <v>0.999187</v>
+        <v>0.717605</v>
       </c>
       <c r="J96" t="n">
-        <v>0.9988320000000001</v>
+        <v>0.672966</v>
       </c>
       <c r="K96" t="n">
-        <v>0.00023127</v>
+        <v>0.00343653</v>
       </c>
       <c r="L96" t="n">
-        <v>0.02315</v>
+        <v>0.49757</v>
       </c>
       <c r="M96" t="n">
-        <v>699000000</v>
+        <v>992644455.4991199</v>
       </c>
       <c r="N96" t="n">
-        <v>699000000</v>
+        <v>1983240735.576791</v>
       </c>
       <c r="O96" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="P96" s="1" t="n">
-        <v>45350.38608796296</v>
+        <v>45633.25043981482</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R96" t="b">
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>5.008953989614223e-05</v>
+        <v>3.852936312251761e-05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>aerodrome-finance</t>
+          <t>ether-fi</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>aero</t>
+          <t>ethfi</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Aerodrome Finance</t>
+          <t>Ether.fi</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.686856</v>
+        <v>0.707735</v>
       </c>
       <c r="F97" t="n">
-        <v>681820872</v>
+        <v>683010352</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>56831776</v>
+        <v>51078925</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6991810000000001</v>
+        <v>0.743762</v>
       </c>
       <c r="J97" t="n">
-        <v>0.648524</v>
+        <v>0.689801</v>
       </c>
       <c r="K97" t="n">
-        <v>0.02865724</v>
+        <v>-0.03235381505688095</v>
       </c>
       <c r="L97" t="n">
-        <v>4.35389</v>
+        <v>-4.37161</v>
       </c>
       <c r="M97" t="n">
-        <v>992665694.3208704</v>
+        <v>965350000</v>
       </c>
       <c r="N97" t="n">
-        <v>1983240735.576791</v>
+        <v>965350000</v>
       </c>
       <c r="O97" t="n">
-        <v>2.32</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="P97" s="1" t="n">
-        <v>45633.25043981482</v>
+        <v>45378.63525462963</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>4.047294792579218e-05</v>
+        <v>3.511496744103546e-05</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>stable-2</t>
+          <t>aptos</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>apt</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>​​Stable</t>
+          <t>Aptos</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.02539244</v>
+        <v>0.770608</v>
       </c>
       <c r="F98" t="n">
-        <v>673849676</v>
+        <v>670861343</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>10507115</v>
+        <v>154727269</v>
       </c>
       <c r="I98" t="n">
-        <v>0.02655115</v>
+        <v>0.807476</v>
       </c>
       <c r="J98" t="n">
-        <v>0.02444799</v>
+        <v>0.747235</v>
       </c>
       <c r="K98" t="n">
-        <v>0.0009418299999999999</v>
+        <v>-0.01773359354090975</v>
       </c>
       <c r="L98" t="n">
-        <v>3.85196</v>
+        <v>-2.24948</v>
       </c>
       <c r="M98" t="n">
-        <v>26522995541</v>
+        <v>870630015.3156223</v>
       </c>
       <c r="N98" t="n">
-        <v>100000000000</v>
+        <v>1209070249.947673</v>
       </c>
       <c r="O98" t="n">
-        <v>0.04323745</v>
+        <v>19.92</v>
       </c>
       <c r="P98" s="1" t="n">
-        <v>46156.97986111111</v>
+        <v>44952.26755787037</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R98" t="b">
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>3.586013053414983e-05</v>
+        <v>2.809134692071272e-05</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>aptos</t>
+          <t>stable-2</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>apt</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Aptos</t>
+          <t>​​Stable</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.771625</v>
+        <v>0.02442355</v>
       </c>
       <c r="F99" t="n">
-        <v>671274865</v>
+        <v>648646669</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>181966908</v>
+        <v>9002785</v>
       </c>
       <c r="I99" t="n">
-        <v>0.790511</v>
+        <v>0.02568186</v>
       </c>
       <c r="J99" t="n">
-        <v>0.721949</v>
+        <v>0.02423901</v>
       </c>
       <c r="K99" t="n">
-        <v>0.050075</v>
+        <v>-0.001296095724457359</v>
       </c>
       <c r="L99" t="n">
-        <v>6.93996</v>
+        <v>-5.03932</v>
       </c>
       <c r="M99" t="n">
-        <v>870586041.4259734</v>
+        <v>26550036008</v>
       </c>
       <c r="N99" t="n">
-        <v>1209026324.181685</v>
+        <v>100000000000</v>
       </c>
       <c r="O99" t="n">
-        <v>19.92</v>
+        <v>0.04323745</v>
       </c>
       <c r="P99" s="1" t="n">
-        <v>44952.26755787037</v>
+        <v>46156.97986111111</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R99" t="b">
         <v>1</v>
       </c>
       <c r="S99" t="n">
-        <v>3.437012414602539e-05</v>
+        <v>1.524853479021877e-05</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7105,34 +7105,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.330374</v>
+        <v>0.344865</v>
       </c>
       <c r="F100" t="n">
-        <v>618216922</v>
+        <v>644499539</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>35672699</v>
+        <v>44824397</v>
       </c>
       <c r="I100" t="n">
-        <v>0.34015</v>
+        <v>0.353654</v>
       </c>
       <c r="J100" t="n">
-        <v>0.30827</v>
+        <v>0.32632</v>
       </c>
       <c r="K100" t="n">
-        <v>0.01942084</v>
+        <v>0.01264259</v>
       </c>
       <c r="L100" t="n">
-        <v>6.24558</v>
+        <v>3.80546</v>
       </c>
       <c r="M100" t="n">
-        <v>1868230389.165669</v>
+        <v>1868492277.481499</v>
       </c>
       <c r="N100" t="n">
-        <v>1868230389.165669</v>
+        <v>1868492277.481499</v>
       </c>
       <c r="O100" t="n">
         <v>3.86</v>
@@ -7141,19 +7141,19 @@
         <v>45383.19094907407</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>3.666249566204706e-06</v>
+        <v>1.285098389792409e-05</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7172,28 +7172,28 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="F101" t="n">
-        <v>611881446</v>
+        <v>622270730</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>311874452</v>
+        <v>385093664</v>
       </c>
       <c r="I101" t="n">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="J101" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="K101" t="n">
-        <v>0.14939</v>
+        <v>0.059857</v>
       </c>
       <c r="L101" t="n">
-        <v>7.37318</v>
+        <v>2.7831</v>
       </c>
       <c r="M101" t="n">
         <v>281867936.287634</v>
@@ -7208,10 +7208,10 @@
         <v>45676.16011574074</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46286.65775462963</v>
+        <v>46287.58067129629</v>
       </c>
       <c r="R101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>

--- a/src/xlsx/cleaned_data.xlsx
+++ b/src/xlsx/cleaned_data.xlsx
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,34 +539,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86132</v>
+        <v>86238</v>
       </c>
       <c r="F2" t="n">
-        <v>1730358233094</v>
+        <v>1732793991467</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>49306386707</v>
+        <v>43485131868</v>
       </c>
       <c r="I2" t="n">
-        <v>87330</v>
+        <v>86722</v>
       </c>
       <c r="J2" t="n">
-        <v>85098</v>
+        <v>85107</v>
       </c>
       <c r="K2" t="n">
-        <v>592.03</v>
+        <v>-377.4880582667683</v>
       </c>
       <c r="L2" t="n">
-        <v>0.69211</v>
+        <v>-0.42991</v>
       </c>
       <c r="M2" t="n">
-        <v>20087871</v>
+        <v>20088034</v>
       </c>
       <c r="N2" t="n">
-        <v>20087940</v>
+        <v>20088056</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -575,7 +575,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -587,7 +587,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,28 +606,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2754.3</v>
+        <v>2748.95</v>
       </c>
       <c r="F3" t="n">
-        <v>336292649409</v>
+        <v>335700394407</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>19972791098</v>
+        <v>16208315503</v>
       </c>
       <c r="I3" t="n">
-        <v>2804.42</v>
+        <v>2786.01</v>
       </c>
       <c r="J3" t="n">
-        <v>2714.5</v>
+        <v>2716.11</v>
       </c>
       <c r="K3" t="n">
-        <v>19.06</v>
+        <v>-21.36690103358978</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6967</v>
+        <v>-0.75097</v>
       </c>
       <c r="M3" t="n">
         <v>122070499.1930826</v>
@@ -642,19 +642,19 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1940587384332607</v>
+        <v>0.1934418838473869</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,28 +673,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999735</v>
+        <v>0.999898</v>
       </c>
       <c r="F4" t="n">
-        <v>183336508352</v>
+        <v>183363689877</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>87755318333</v>
+        <v>78958984976</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9996080000000001</v>
+        <v>0.999627</v>
       </c>
       <c r="K4" t="n">
-        <v>9.564999999999999e-05</v>
+        <v>6.751e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00957</v>
+        <v>0.00721</v>
       </c>
       <c r="M4" t="n">
         <v>183384649781.6938</v>
@@ -709,19 +709,19 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1056312880101583</v>
+        <v>0.1054961616100404</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,34 +740,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>789.84</v>
+        <v>784.49</v>
       </c>
       <c r="F5" t="n">
-        <v>105180447721</v>
+        <v>104509508003</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1606078435</v>
+        <v>1338733134</v>
       </c>
       <c r="I5" t="n">
         <v>806.75</v>
       </c>
       <c r="J5" t="n">
-        <v>783.38</v>
+        <v>781.83</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.924875956322353</v>
+        <v>-20.06454466473849</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.61966</v>
+        <v>-2.48689</v>
       </c>
       <c r="M5" t="n">
-        <v>133160075.87</v>
+        <v>133160045.24</v>
       </c>
       <c r="N5" t="n">
-        <v>133160072.53</v>
+        <v>133160043.94</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -776,19 +776,19 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06044747826604828</v>
+        <v>0.05997274033254849</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -807,28 +807,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="F6" t="n">
-        <v>99065321389</v>
+        <v>98935861541</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>6307464848</v>
+        <v>6013941970</v>
       </c>
       <c r="I6" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="J6" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="K6" t="n">
-        <v>0.089047</v>
+        <v>0.02050936</v>
       </c>
       <c r="L6" t="n">
-        <v>5.97063</v>
+        <v>1.26594</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -843,19 +843,19 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05691218359388192</v>
+        <v>0.05675501046824196</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,34 +874,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.99983</v>
+        <v>0.999892</v>
       </c>
       <c r="F7" t="n">
-        <v>74582091668</v>
+        <v>75082614224</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>23229656383</v>
+        <v>20211770616</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999694</v>
+        <v>0.999695</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00012216</v>
+        <v>8.51e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01222</v>
+        <v>0.00201</v>
       </c>
       <c r="M7" t="n">
-        <v>74594529696.15031</v>
+        <v>75091582641.99438</v>
       </c>
       <c r="N7" t="n">
-        <v>74599622744.57069</v>
+        <v>75091431783.64163</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -910,19 +910,19 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04275786741285092</v>
+        <v>0.04298425791407672</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -941,34 +941,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>117.61</v>
+        <v>118.13</v>
       </c>
       <c r="F8" t="n">
-        <v>69106453195</v>
+        <v>69442081520</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>5533889889</v>
+        <v>4713073391</v>
       </c>
       <c r="I8" t="n">
-        <v>119.9</v>
+        <v>119.82</v>
       </c>
       <c r="J8" t="n">
         <v>115.58</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5882841268877286</v>
+        <v>-1.022544647266727</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.49769</v>
+        <v>-0.84705</v>
       </c>
       <c r="M8" t="n">
-        <v>587507739.1137596</v>
+        <v>587507395.8954812</v>
       </c>
       <c r="N8" t="n">
-        <v>634531389.3135934</v>
+        <v>634531021.326126</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -977,19 +977,19 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03959227532704116</v>
+        <v>0.03972791385709364</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1008,34 +1008,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.342896</v>
+        <v>0.34165</v>
       </c>
       <c r="F9" t="n">
-        <v>32558762440</v>
+        <v>32442198365</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>611135640</v>
+        <v>605341752</v>
       </c>
       <c r="I9" t="n">
         <v>0.349178</v>
       </c>
       <c r="J9" t="n">
-        <v>0.343759</v>
+        <v>0.34041</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.001853093714661691</v>
+        <v>-0.002637683000221824</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.53752</v>
+        <v>-0.75484</v>
       </c>
       <c r="M9" t="n">
-        <v>94961752942.69308</v>
+        <v>94961729708.24278</v>
       </c>
       <c r="N9" t="n">
-        <v>94961735259.42459</v>
+        <v>94962102587.18929</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1044,19 +1044,19 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0184632177424079</v>
+        <v>0.01836745803783905</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1075,34 +1075,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1515.29</v>
+        <v>1518.81</v>
       </c>
       <c r="F10" t="n">
-        <v>25679897777</v>
+        <v>25756147448</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1439199278</v>
+        <v>1389815932</v>
       </c>
       <c r="I10" t="n">
-        <v>1540.34</v>
+        <v>1562.57</v>
       </c>
       <c r="J10" t="n">
-        <v>1444.17</v>
+        <v>1445.89</v>
       </c>
       <c r="K10" t="n">
-        <v>-22.07724586670861</v>
+        <v>56.04</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.43604</v>
+        <v>3.7356</v>
       </c>
       <c r="M10" t="n">
         <v>16945106.4155448</v>
       </c>
       <c r="N10" t="n">
-        <v>16946415.7905448</v>
+        <v>16946950.1655448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1111,19 +1111,19 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01448638843858815</v>
+        <v>0.01450752435589808</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1142,31 +1142,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.013</v>
+        <v>1.039</v>
       </c>
       <c r="F11" t="n">
-        <v>23062335218</v>
+        <v>23858934286</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>55232417</v>
+        <v>83847558</v>
       </c>
       <c r="I11" t="n">
-        <v>1.04</v>
+        <v>1.043</v>
       </c>
       <c r="J11" t="n">
-        <v>1.012</v>
+        <v>1.006</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.006103827815765017</v>
+        <v>0.0261228</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.59888</v>
+        <v>2.57897</v>
       </c>
       <c r="M11" t="n">
-        <v>22764228455.528</v>
+        <v>22966221270.418</v>
       </c>
       <c r="N11" t="n">
         <v>22966221270.418</v>
@@ -1178,19 +1178,19 @@
         <v>46237.59675925926</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01297311553685428</v>
+        <v>0.01341224149360253</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1209,28 +1209,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>95.36</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>21211241880</v>
+        <v>21655414643</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1293604135</v>
+        <v>1249913907</v>
       </c>
       <c r="I12" t="n">
-        <v>95.88</v>
+        <v>96.87</v>
       </c>
       <c r="J12" t="n">
-        <v>92.06</v>
+        <v>92.19</v>
       </c>
       <c r="K12" t="n">
-        <v>0.44987</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>0.47398</v>
+        <v>4.26103</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1239,25 +1239,25 @@
         <v>955307079.4341414</v>
       </c>
       <c r="O12" t="n">
-        <v>95.98999999999999</v>
+        <v>97.72</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>46286.47291666667</v>
+        <v>46287.91296296296</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01190295605686628</v>
+        <v>0.01214012439571919</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1276,34 +1276,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.100752</v>
+        <v>0.100125</v>
       </c>
       <c r="F13" t="n">
-        <v>15718592446</v>
+        <v>15635492125</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>3160716957</v>
+        <v>2382661626</v>
       </c>
       <c r="I13" t="n">
         <v>0.105575</v>
       </c>
       <c r="J13" t="n">
-        <v>0.09251</v>
+        <v>0.097356</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00726657</v>
+        <v>0.00082386</v>
       </c>
       <c r="L13" t="n">
-        <v>7.77292</v>
+        <v>0.82324</v>
       </c>
       <c r="M13" t="n">
-        <v>156021246383.7052</v>
+        <v>156025536383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171733843126.5791</v>
+        <v>171737883126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1312,19 +1312,19 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.008727529544664216</v>
+        <v>0.008664754258943556</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1343,34 +1343,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>572.97</v>
+        <v>567.3</v>
       </c>
       <c r="F14" t="n">
-        <v>10785142460</v>
+        <v>10671971138</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>183437802</v>
+        <v>163415960</v>
       </c>
       <c r="I14" t="n">
         <v>601.01</v>
       </c>
       <c r="J14" t="n">
-        <v>552.66</v>
+        <v>561.65</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.374429859507018</v>
+        <v>-29.0335298218157</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4127</v>
+        <v>-4.86632</v>
       </c>
       <c r="M14" t="n">
-        <v>18808007.51155922</v>
+        <v>18808120.908502</v>
       </c>
       <c r="N14" t="n">
-        <v>18808040.5111969</v>
+        <v>18808149.70786505</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1379,19 +1379,19 @@
         <v>46036.48202546296</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0058753890484595</v>
+        <v>0.005799256811110969</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1410,28 +1410,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>86.66</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>10299673248</v>
+        <v>10304856260</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>176791671</v>
+        <v>148065627</v>
       </c>
       <c r="I15" t="n">
-        <v>87.91</v>
+        <v>87.28</v>
       </c>
       <c r="J15" t="n">
         <v>85.56999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.492012</v>
+        <v>-0.4387106662780695</v>
       </c>
       <c r="L15" t="n">
-        <v>0.57098</v>
+        <v>-0.49605</v>
       </c>
       <c r="M15" t="n">
         <v>118852171</v>
@@ -1446,19 +1446,19 @@
         <v>46286.85358796296</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005594728171560972</v>
+        <v>0.005587317192294894</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1477,28 +1477,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>13.06</v>
+        <v>12.91</v>
       </c>
       <c r="F16" t="n">
-        <v>9773544357</v>
+        <v>9671530693</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>684922983</v>
+        <v>581165005</v>
       </c>
       <c r="I16" t="n">
         <v>13.26</v>
       </c>
       <c r="J16" t="n">
-        <v>12.76</v>
+        <v>12.78</v>
       </c>
       <c r="K16" t="n">
-        <v>0.009376229999999999</v>
+        <v>-0.2186754109027937</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07183</v>
+        <v>-1.64853</v>
       </c>
       <c r="M16" t="n">
         <v>748099970.424884</v>
@@ -1513,19 +1513,19 @@
         <v>44325.67635416667</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.005290561002439421</v>
+        <v>0.005221691097303301</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9998939999999999</v>
+        <v>0.999922</v>
       </c>
       <c r="F17" t="n">
-        <v>9583360912</v>
+        <v>9592786193</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>238853572</v>
+        <v>247011578</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -1562,16 +1562,16 @@
         <v>0.999729</v>
       </c>
       <c r="K17" t="n">
-        <v>7.478999999999999e-05</v>
+        <v>-5.5729221229095e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>0.00748</v>
+        <v>-0.00507</v>
       </c>
       <c r="M17" t="n">
-        <v>9583873777.059114</v>
+        <v>9593648553.437454</v>
       </c>
       <c r="N17" t="n">
-        <v>9576750341.247417</v>
+        <v>9593648553.437454</v>
       </c>
       <c r="O17" t="n">
         <v>1.057</v>
@@ -1580,153 +1580,153 @@
         <v>45593.90336805556</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005180611594473086</v>
+        <v>0.005176230996626415</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>cardano</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>ada</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.01348809</v>
+        <v>0.251416</v>
       </c>
       <c r="F18" t="n">
-        <v>9559476072</v>
+        <v>9443905073</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>17859980</v>
+        <v>878661987</v>
       </c>
       <c r="I18" t="n">
-        <v>0.01420135</v>
+        <v>0.253817</v>
       </c>
       <c r="J18" t="n">
-        <v>0.01343954</v>
+        <v>0.240769</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.000638838496365042</v>
+        <v>0.00659619</v>
       </c>
       <c r="L18" t="n">
-        <v>-4.52213</v>
+        <v>2.72814</v>
       </c>
       <c r="M18" t="n">
-        <v>709239700254.0453</v>
+        <v>37529061988.53558</v>
       </c>
       <c r="N18" t="n">
-        <v>1142408526965.963</v>
+        <v>45000000000</v>
       </c>
       <c r="O18" t="n">
-        <v>0.01946402</v>
+        <v>3.09</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>46259.82847222222</v>
+        <v>44440.91678240741</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005166803221102993</v>
+        <v>0.005090280222869678</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>cardano</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ada</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.252441</v>
+        <v>0.01309167</v>
       </c>
       <c r="F19" t="n">
-        <v>9470964968</v>
+        <v>9284605249</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>838000406</v>
+        <v>24775479</v>
       </c>
       <c r="I19" t="n">
-        <v>0.251521</v>
+        <v>0.01400767</v>
       </c>
       <c r="J19" t="n">
-        <v>0.240416</v>
+        <v>0.0130726</v>
       </c>
       <c r="K19" t="n">
-        <v>0.007827020000000001</v>
+        <v>-0.000864517740068033</v>
       </c>
       <c r="L19" t="n">
-        <v>3.19974</v>
+        <v>-6.27118</v>
       </c>
       <c r="M19" t="n">
-        <v>37529061988.53558</v>
+        <v>709239749032.6418</v>
       </c>
       <c r="N19" t="n">
-        <v>45000000000</v>
+        <v>1142408526965.963</v>
       </c>
       <c r="O19" t="n">
-        <v>3.09</v>
+        <v>0.01946402</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>44440.91678240741</v>
+        <v>46259.82847222222</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.005115632923481942</v>
+        <v>0.004998314612105115</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1745,28 +1745,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.970000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="F20" t="n">
-        <v>8251314793</v>
+        <v>8260445947</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>157365</v>
+        <v>127098</v>
       </c>
       <c r="I20" t="n">
         <v>9</v>
       </c>
       <c r="J20" t="n">
-        <v>8.779999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.01618964306871185</v>
+        <v>0.02568804</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.18016</v>
+        <v>0.28873</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -1781,19 +1781,19 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004410525206733586</v>
+        <v>0.004407055730810693</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1812,31 +1812,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.214975</v>
+        <v>0.215138</v>
       </c>
       <c r="F21" t="n">
-        <v>7505565898</v>
+        <v>7524022577</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>450679611</v>
+        <v>382146995</v>
       </c>
       <c r="I21" t="n">
         <v>0.219762</v>
       </c>
       <c r="J21" t="n">
-        <v>0.206236</v>
+        <v>0.209091</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00500717</v>
+        <v>-0.001449679238016699</v>
       </c>
       <c r="L21" t="n">
-        <v>2.38473</v>
+        <v>-0.76252</v>
       </c>
       <c r="M21" t="n">
-        <v>34931879410.76893</v>
+        <v>34931895481.5965</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70148</v>
@@ -1848,19 +1848,19 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R21" t="b">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.00397939068029361</v>
+        <v>0.003981910094721682</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1879,34 +1879,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>325.71</v>
+        <v>340.47</v>
       </c>
       <c r="F22" t="n">
-        <v>6541052358</v>
+        <v>6849206386</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>691846249</v>
+        <v>1186844804</v>
       </c>
       <c r="I22" t="n">
-        <v>311.05</v>
+        <v>346.9</v>
       </c>
       <c r="J22" t="n">
         <v>261.8</v>
       </c>
       <c r="K22" t="n">
-        <v>56.43</v>
+        <v>72.33</v>
       </c>
       <c r="L22" t="n">
-        <v>20.95482</v>
+        <v>26.79209</v>
       </c>
       <c r="M22" t="n">
-        <v>20092515.52165077</v>
+        <v>20092971.77165077</v>
       </c>
       <c r="N22" t="n">
-        <v>20092887.39665077</v>
+        <v>20092968.64665077</v>
       </c>
       <c r="O22" t="n">
         <v>3785.82</v>
@@ -1915,287 +1915,287 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R22" t="b">
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.003421783299175271</v>
+        <v>0.003592330987847522</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>uniswap</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>uni</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4.47</v>
+        <v>9.44</v>
       </c>
       <c r="F23" t="n">
-        <v>5849869047</v>
+        <v>5869006543</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>1786719210</v>
+        <v>1593380024</v>
       </c>
       <c r="I23" t="n">
-        <v>4.65</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>3.92</v>
+        <v>8.68</v>
       </c>
       <c r="K23" t="n">
-        <v>0.334539</v>
+        <v>0.672496</v>
       </c>
       <c r="L23" t="n">
-        <v>8.08442</v>
+        <v>7.57425</v>
       </c>
       <c r="M23" t="n">
-        <v>1306999800</v>
+        <v>620708422.6104751</v>
       </c>
       <c r="N23" t="n">
-        <v>1306999785</v>
+        <v>887956418.9163101</v>
       </c>
       <c r="O23" t="n">
-        <v>20.44</v>
+        <v>44.92</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>44577.59010416667</v>
+        <v>44318.89240740741</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R23" t="b">
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.003022194387318821</v>
+        <v>0.00302645040512432</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>uniswap</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>uni</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>9.07</v>
+        <v>4.33</v>
       </c>
       <c r="F24" t="n">
-        <v>5631538867</v>
+        <v>5662458523</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>1394948640</v>
+        <v>1682767802</v>
       </c>
       <c r="I24" t="n">
-        <v>9.699999999999999</v>
+        <v>4.65</v>
       </c>
       <c r="J24" t="n">
-        <v>8.68</v>
+        <v>4.12</v>
       </c>
       <c r="K24" t="n">
-        <v>0.157641</v>
+        <v>0.193685</v>
       </c>
       <c r="L24" t="n">
-        <v>1.76836</v>
+        <v>4.56812</v>
       </c>
       <c r="M24" t="n">
-        <v>620716422.6104751</v>
+        <v>1307027733</v>
       </c>
       <c r="N24" t="n">
-        <v>887964418.9163101</v>
+        <v>1307027728</v>
       </c>
       <c r="O24" t="n">
-        <v>44.92</v>
+        <v>20.44</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>44318.89240740741</v>
+        <v>44577.59010416667</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002895972706813542</v>
+        <v>0.002907207870295712</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ethena-usde</t>
+          <t>avalanche-2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>usde</t>
+          <t>avax</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ethena USDe</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.999597</v>
+        <v>11.08</v>
       </c>
       <c r="F25" t="n">
-        <v>4900074139</v>
+        <v>4909205600</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>191810978</v>
+        <v>633782095</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>11.35</v>
       </c>
       <c r="J25" t="n">
-        <v>0.998631</v>
+        <v>10.53</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.000232050524545446</v>
+        <v>-0.2567119165716321</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.02321</v>
+        <v>-2.2405</v>
       </c>
       <c r="M25" t="n">
-        <v>4902029610.641097</v>
+        <v>442927404.050358</v>
       </c>
       <c r="N25" t="n">
-        <v>4901729538.308097</v>
+        <v>469596104.050358</v>
       </c>
       <c r="O25" t="n">
-        <v>1.034</v>
+        <v>144.96</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>46000.38208333333</v>
+        <v>44521.26314814815</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002473096184664855</v>
+        <v>0.002472346340731893</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>avalanche-2</t>
+          <t>ethena-usde</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>avax</t>
+          <t>usde</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Ethena USDe</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>11</v>
+        <v>0.999824</v>
       </c>
       <c r="F26" t="n">
-        <v>4869633946</v>
+        <v>4898876763</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>796744596</v>
+        <v>175765816</v>
       </c>
       <c r="I26" t="n">
-        <v>11.36</v>
+        <v>0.999931</v>
       </c>
       <c r="J26" t="n">
-        <v>10.53</v>
+        <v>0.998631</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.2780236806402367</v>
+        <v>2.905e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.46536</v>
+        <v>0.00317</v>
       </c>
       <c r="M26" t="n">
-        <v>442925920.1218815</v>
+        <v>4899806603.894896</v>
       </c>
       <c r="N26" t="n">
-        <v>469594897.9267309</v>
+        <v>4897763014.332197</v>
       </c>
       <c r="O26" t="n">
-        <v>144.96</v>
+        <v>1.034</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>44521.26314814815</v>
+        <v>46000.38208333333</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002455498011497202</v>
+        <v>0.002466383384971235</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2214,34 +2214,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>61.92</v>
+        <v>62.62</v>
       </c>
       <c r="F27" t="n">
-        <v>4811453542</v>
+        <v>4864663052</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>468229492</v>
+        <v>500958406</v>
       </c>
       <c r="I27" t="n">
-        <v>63.49</v>
+        <v>63.44</v>
       </c>
       <c r="J27" t="n">
         <v>59.82</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.6188402034689062</v>
+        <v>0.593382</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.9895699999999999</v>
+        <v>0.98769</v>
       </c>
       <c r="M27" t="n">
-        <v>77635616.97446169</v>
+        <v>77636779.47670597</v>
       </c>
       <c r="N27" t="n">
-        <v>77638460.73181786</v>
+        <v>77639516.98369066</v>
       </c>
       <c r="O27" t="n">
         <v>410.26</v>
@@ -2250,153 +2250,153 @@
         <v>44325.80077546297</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002421862586631266</v>
+        <v>0.002446631418210511</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>canton-network</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Dai</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.117048</v>
+        <v>0.999915</v>
       </c>
       <c r="F28" t="n">
-        <v>4641383435</v>
+        <v>4575720883</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>20927321</v>
+        <v>235945685</v>
       </c>
       <c r="I28" t="n">
-        <v>0.119967</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0.114334</v>
+        <v>0.998871</v>
       </c>
       <c r="K28" t="n">
-        <v>0.00189519</v>
+        <v>3.684e-05</v>
       </c>
       <c r="L28" t="n">
-        <v>1.6458</v>
+        <v>0.00452</v>
       </c>
       <c r="M28" t="n">
-        <v>39659258394.41443</v>
+        <v>4575753580.16673</v>
       </c>
       <c r="N28" t="n">
-        <v>39660284776.00477</v>
+        <v>4592088883.495623</v>
       </c>
       <c r="O28" t="n">
-        <v>0.194152</v>
+        <v>1.22</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>46056.00148148148</v>
+        <v>43902.79363425926</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002323541160297754</v>
+        <v>0.002279821798585806</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>canton-network</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Dai</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0.114167</v>
       </c>
       <c r="F29" t="n">
-        <v>4589482014</v>
+        <v>4528241072</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>158461722</v>
+        <v>17809362</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0.119967</v>
       </c>
       <c r="J29" t="n">
-        <v>0.999707</v>
+        <v>0.111864</v>
       </c>
       <c r="K29" t="n">
-        <v>0.00015651</v>
+        <v>-0.001610986985493751</v>
       </c>
       <c r="L29" t="n">
-        <v>0.01565</v>
+        <v>-1.38068</v>
       </c>
       <c r="M29" t="n">
-        <v>4589123571.017243</v>
+        <v>39662232770.86527</v>
       </c>
       <c r="N29" t="n">
-        <v>4594670335.870287</v>
+        <v>39662232770.86527</v>
       </c>
       <c r="O29" t="n">
-        <v>1.22</v>
+        <v>0.194152</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>43902.79363425926</v>
+        <v>46056.00148148148</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.00229353575939884</v>
+        <v>0.002252411160532615</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2415,34 +2415,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9993069999999999</v>
+        <v>0.999344</v>
       </c>
       <c r="F30" t="n">
-        <v>4373808153</v>
+        <v>4392803585</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>1394890022</v>
+        <v>1317635380</v>
       </c>
       <c r="I30" t="n">
-        <v>0.999969</v>
+        <v>0.999651</v>
       </c>
       <c r="J30" t="n">
         <v>0.999131</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.000327838376545708</v>
+        <v>-0.000230891299258684</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.0328</v>
+        <v>-0.0249</v>
       </c>
       <c r="M30" t="n">
-        <v>4376796475.112089</v>
+        <v>4395796475.062263</v>
       </c>
       <c r="N30" t="n">
-        <v>4376796475.112089</v>
+        <v>4395796475.062263</v>
       </c>
       <c r="O30" t="n">
         <v>1.048</v>
@@ -2451,19 +2451,19 @@
         <v>46212.42696759259</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.002168849757782014</v>
+        <v>0.002174221549900198</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2482,31 +2482,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.09669700000000001</v>
+        <v>0.099762</v>
       </c>
       <c r="F31" t="n">
-        <v>4237742715</v>
+        <v>4381497354</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>207390429</v>
+        <v>253199661</v>
       </c>
       <c r="I31" t="n">
-        <v>0.097631</v>
+        <v>0.100667</v>
       </c>
       <c r="J31" t="n">
-        <v>0.089865</v>
+        <v>0.091183</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0055354</v>
+        <v>0.007907839999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>6.07206</v>
+        <v>8.63801</v>
       </c>
       <c r="M31" t="n">
-        <v>43831706400.0613</v>
+        <v>43831706400.35046</v>
       </c>
       <c r="N31" t="n">
         <v>50000000000</v>
@@ -2518,19 +2518,19 @@
         <v>44454.11143518519</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R31" t="b">
         <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0.002090187209878436</v>
+        <v>0.002167694333402079</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2549,28 +2549,28 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.015</v>
+        <v>1.011</v>
       </c>
       <c r="F32" t="n">
-        <v>4158290738</v>
+        <v>4147213010</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>1393806744</v>
+        <v>1118620738</v>
       </c>
       <c r="I32" t="n">
         <v>1.079</v>
       </c>
       <c r="J32" t="n">
-        <v>0.992193</v>
+        <v>0.988259</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.02509713341816555</v>
+        <v>-0.008432258001915161</v>
       </c>
       <c r="L32" t="n">
-        <v>-2.4135</v>
+        <v>-0.78915</v>
       </c>
       <c r="M32" t="n">
         <v>4096537146.540959</v>
@@ -2585,19 +2585,19 @@
         <v>45661.62243055556</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.002044254201183043</v>
+        <v>0.002032439301428316</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2616,34 +2616,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="F33" t="n">
-        <v>4021661629</v>
+        <v>4086969910</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>64995447</v>
+        <v>52837490</v>
       </c>
       <c r="I33" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="J33" t="n">
         <v>1.41</v>
       </c>
       <c r="K33" t="n">
-        <v>0.00260019</v>
+        <v>0.00408983</v>
       </c>
       <c r="L33" t="n">
-        <v>0.18202</v>
+        <v>0.24221</v>
       </c>
       <c r="M33" t="n">
         <v>2810942525.236758</v>
       </c>
       <c r="N33" t="n">
-        <v>5253533230.459864</v>
+        <v>5253728562.764504</v>
       </c>
       <c r="O33" t="n">
         <v>8.25</v>
@@ -2652,153 +2652,153 @@
         <v>45457.69225694444</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R33" t="b">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001965265782156782</v>
+        <v>0.001997660270625051</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>bittensor</t>
+          <t>shiba-inu</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>tao</t>
+          <t>shib</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>Shiba Inu</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>320.39</v>
+        <v>6.05e-06</v>
       </c>
       <c r="F34" t="n">
-        <v>3631258347</v>
+        <v>3567256021</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>688860057</v>
+        <v>213804939</v>
       </c>
       <c r="I34" t="n">
-        <v>325.76</v>
+        <v>6.25e-06</v>
       </c>
       <c r="J34" t="n">
-        <v>278.1</v>
+        <v>5.9e-06</v>
       </c>
       <c r="K34" t="n">
-        <v>33.25</v>
+        <v>8.1711e-08</v>
       </c>
       <c r="L34" t="n">
-        <v>11.5799</v>
+        <v>1.4441</v>
       </c>
       <c r="M34" t="n">
-        <v>11339645.9251</v>
+        <v>589238968628246.4</v>
       </c>
       <c r="N34" t="n">
-        <v>21000000</v>
+        <v>589496070402766.1</v>
       </c>
       <c r="O34" t="n">
-        <v>757.6</v>
+        <v>8.616e-05</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>45358.44833333333</v>
+        <v>44496.82980324074</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001739564698006087</v>
+        <v>0.001697623497045746</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>shiba-inu</t>
+          <t>bittensor</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>shib</t>
+          <t>tao</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Shiba Inu</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6.02e-06</v>
+        <v>309.22</v>
       </c>
       <c r="F35" t="n">
-        <v>3547301637</v>
+        <v>3508186486</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>258673537</v>
+        <v>545675077</v>
       </c>
       <c r="I35" t="n">
-        <v>6.25e-06</v>
+        <v>325.76</v>
       </c>
       <c r="J35" t="n">
-        <v>5.67e-06</v>
+        <v>302.22</v>
       </c>
       <c r="K35" t="n">
-        <v>2.9052e-07</v>
+        <v>1.068</v>
       </c>
       <c r="L35" t="n">
-        <v>5.07012</v>
+        <v>0.49825</v>
       </c>
       <c r="M35" t="n">
-        <v>589238968628246.4</v>
+        <v>11339645.9251</v>
       </c>
       <c r="N35" t="n">
-        <v>589496070402766.1</v>
+        <v>21000000</v>
       </c>
       <c r="O35" t="n">
-        <v>8.616e-05</v>
+        <v>757.6</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>44496.82980324074</v>
+        <v>45358.44833333333</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001691027399928953</v>
+        <v>0.001663521978742413</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2817,34 +2817,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.066841</v>
+        <v>0.06623999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>3324735280</v>
+        <v>3294501272</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>20512650</v>
+        <v>16354864</v>
       </c>
       <c r="I36" t="n">
         <v>0.068842</v>
       </c>
       <c r="J36" t="n">
-        <v>0.062969</v>
+        <v>0.06461500000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>0.00316426</v>
+        <v>0.0008701</v>
       </c>
       <c r="L36" t="n">
-        <v>4.96927</v>
+        <v>1.33228</v>
       </c>
       <c r="M36" t="n">
-        <v>49737083041.94866</v>
+        <v>49737707457.07803</v>
       </c>
       <c r="N36" t="n">
-        <v>98937083097.9492</v>
+        <v>98937691623.08702</v>
       </c>
       <c r="O36" t="n">
         <v>0.891544</v>
@@ -2853,19 +2853,19 @@
         <v>44523.66666666666</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.00156235668842</v>
+        <v>0.001540159060169029</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2887,13 +2887,13 @@
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>3268121116</v>
+        <v>3258615171</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>942747771</v>
+        <v>916316571</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
@@ -2902,16 +2902,16 @@
         <v>0.999787</v>
       </c>
       <c r="K37" t="n">
-        <v>0.00014023</v>
+        <v>-1.5706744024069e-05</v>
       </c>
       <c r="L37" t="n">
-        <v>0.01402</v>
+        <v>-0.00083</v>
       </c>
       <c r="M37" t="n">
-        <v>3268047900.209824</v>
+        <v>3258647890.048256</v>
       </c>
       <c r="N37" t="n">
-        <v>3268085897.433343</v>
+        <v>3258647890.048256</v>
       </c>
       <c r="O37" t="n">
         <v>1.65</v>
@@ -2920,19 +2920,19 @@
         <v>45686.67436342593</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001529626742791404</v>
+        <v>0.00151944160352938</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2951,34 +2951,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="F38" t="n">
-        <v>3008797579</v>
+        <v>2977606566</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
       </c>
       <c r="H38" t="n">
-        <v>1496229</v>
+        <v>1787037</v>
       </c>
       <c r="I38" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="J38" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.1607115628173845</v>
+        <v>-0.1573793546544873</v>
       </c>
       <c r="L38" t="n">
-        <v>-10.84507</v>
+        <v>-10.74441</v>
       </c>
       <c r="M38" t="n">
-        <v>2277453794.135731</v>
+        <v>2277592661.72997</v>
       </c>
       <c r="N38" t="n">
-        <v>5417058990.578639</v>
+        <v>5417166988.519834</v>
       </c>
       <c r="O38" t="n">
         <v>5.64</v>
@@ -2987,19 +2987,19 @@
         <v>46205.17638888889</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R38" t="b">
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001379705863164442</v>
+        <v>0.00135721212116082</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3018,16 +3018,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.999911</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>2821974132</v>
+        <v>2823592224</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>125350757</v>
+        <v>157981743</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
@@ -3036,16 +3036,16 @@
         <v>0.99978</v>
       </c>
       <c r="K39" t="n">
-        <v>4.469e-05</v>
+        <v>6.4e-06</v>
       </c>
       <c r="L39" t="n">
-        <v>0.00447</v>
+        <v>0.00118</v>
       </c>
       <c r="M39" t="n">
-        <v>2822151262.564369</v>
+        <v>2823558770.164367</v>
       </c>
       <c r="N39" t="n">
-        <v>2822151262.564368</v>
+        <v>2823558770.164366</v>
       </c>
       <c r="O39" t="n">
         <v>1.021</v>
@@ -3054,19 +3054,19 @@
         <v>45222.61454861111</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.00127169894704259</v>
+        <v>0.001268297879620087</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4333.56</v>
+        <v>4355.93</v>
       </c>
       <c r="F40" t="n">
-        <v>2698988013</v>
+        <v>2712967630</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>222621939</v>
+        <v>209976775</v>
       </c>
       <c r="I40" t="n">
         <v>4372.67</v>
@@ -3103,10 +3103,10 @@
         <v>4295.64</v>
       </c>
       <c r="K40" t="n">
-        <v>-17.04005644263361</v>
+        <v>15.59</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.39167</v>
+        <v>0.34468</v>
       </c>
       <c r="M40" t="n">
         <v>622823.6595320001</v>
@@ -3121,19 +3121,19 @@
         <v>46050.66666666666</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.00120059785319014</v>
+        <v>0.001204433035972854</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3152,16 +3152,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>122.29</v>
+        <v>123.13</v>
       </c>
       <c r="F41" t="n">
-        <v>2567889954</v>
+        <v>2587013448</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
       </c>
       <c r="H41" t="n">
-        <v>49631893</v>
+        <v>40188551</v>
       </c>
       <c r="I41" t="n">
         <v>126.4</v>
@@ -3170,10 +3170,10 @@
         <v>120.48</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.2250340682920182</v>
+        <v>-0.1176173684437742</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.18368</v>
+        <v>-0.16008</v>
       </c>
       <c r="M41" t="n">
         <v>21000000</v>
@@ -3188,19 +3188,19 @@
         <v>45934.66666666666</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001124807060923308</v>
+        <v>0.001131718245804718</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3222,7 +3222,7 @@
         <v>1.14</v>
       </c>
       <c r="F42" t="n">
-        <v>2508748748</v>
+        <v>2508825557</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
@@ -3243,7 +3243,7 @@
         <v>0.00923</v>
       </c>
       <c r="M42" t="n">
-        <v>2204409826.472634</v>
+        <v>2204477317.470919</v>
       </c>
       <c r="N42" t="n">
         <v>2204477317.470919</v>
@@ -3255,19 +3255,19 @@
         <v>46287.53819444445</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001090616174402585</v>
+        <v>0.001086579481871068</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3289,13 +3289,13 @@
         <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>2444037824</v>
+        <v>2414668604</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>194679324</v>
+        <v>423709547</v>
       </c>
       <c r="I43" t="n">
         <v>1</v>
@@ -3304,16 +3304,16 @@
         <v>0.9997740000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>0.00013348</v>
+        <v>9.699e-05</v>
       </c>
       <c r="L43" t="n">
-        <v>0.01335</v>
+        <v>0.00021</v>
       </c>
       <c r="M43" t="n">
-        <v>2443757344.087235</v>
+        <v>2414682344.087236</v>
       </c>
       <c r="N43" t="n">
-        <v>2446757344.087215</v>
+        <v>2417586212.607235</v>
       </c>
       <c r="O43" t="n">
         <v>1.073</v>
@@ -3322,19 +3322,19 @@
         <v>45652.11518518518</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001053205306265485</v>
+        <v>0.001032221595760816</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3353,28 +3353,28 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.867826</v>
+        <v>0.882043</v>
       </c>
       <c r="F44" t="n">
-        <v>2353876933</v>
+        <v>2386426149</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>25229215</v>
+        <v>13777728</v>
       </c>
       <c r="I44" t="n">
-        <v>0.972034</v>
+        <v>0.885736</v>
       </c>
       <c r="J44" t="n">
-        <v>0.674004</v>
+        <v>0.717963</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0273677</v>
+        <v>0.01416612</v>
       </c>
       <c r="L44" t="n">
-        <v>3.25628</v>
+        <v>1.3311</v>
       </c>
       <c r="M44" t="n">
         <v>2708142280.000001</v>
@@ -3389,19 +3389,19 @@
         <v>46286.79398148148</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001001081228971758</v>
+        <v>0.001015916903399287</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3423,7 +3423,7 @@
         <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>2311661429</v>
+        <v>2280893730</v>
       </c>
       <c r="G45" t="n">
         <v>44</v>
@@ -3438,16 +3438,16 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.11e-16</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2311661429.407649</v>
+        <v>2280893730.007649</v>
       </c>
       <c r="N45" t="n">
-        <v>2311661429.407649</v>
+        <v>2280893730.007649</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
@@ -3456,19 +3456,19 @@
         <v>45699.87511574074</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.0009766754786615752</v>
+        <v>0.0009549918306333762</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3490,13 +3490,13 @@
         <v>1.15</v>
       </c>
       <c r="F46" t="n">
-        <v>2261756116</v>
+        <v>2246400476</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>2551236</v>
+        <v>2779332</v>
       </c>
       <c r="I46" t="n">
         <v>1.15</v>
@@ -3505,16 +3505,16 @@
         <v>1.13</v>
       </c>
       <c r="K46" t="n">
-        <v>0.00666978</v>
+        <v>0.0046907</v>
       </c>
       <c r="L46" t="n">
-        <v>0.58504</v>
+        <v>0.42566</v>
       </c>
       <c r="M46" t="n">
-        <v>1972357100.681555</v>
+        <v>1963554625.495198</v>
       </c>
       <c r="N46" t="n">
-        <v>1972357112.080956</v>
+        <v>1963554625.495198</v>
       </c>
       <c r="O46" t="n">
         <v>1.26</v>
@@ -3523,19 +3523,19 @@
         <v>45377.89175925926</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0009478240735420358</v>
+        <v>0.0009350784805008161</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3554,31 +3554,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>144.17</v>
+        <v>144.82</v>
       </c>
       <c r="F47" t="n">
-        <v>2224776584</v>
+        <v>2236997529</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>309053020</v>
+        <v>267338061</v>
       </c>
       <c r="I47" t="n">
-        <v>148.31</v>
+        <v>146.7</v>
       </c>
       <c r="J47" t="n">
         <v>140.18</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.944895074505439</v>
+        <v>1.28</v>
       </c>
       <c r="L47" t="n">
-        <v>-1.33105</v>
+        <v>0.85148</v>
       </c>
       <c r="M47" t="n">
-        <v>15428841.48679896</v>
+        <v>15428919.91855954</v>
       </c>
       <c r="N47" t="n">
         <v>16000000</v>
@@ -3590,19 +3590,19 @@
         <v>44334.55554398148</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0009264453586372126</v>
+        <v>0.0009296500516292197</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3621,28 +3621,28 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.663218</v>
+        <v>0.668858</v>
       </c>
       <c r="F48" t="n">
-        <v>2190798183</v>
+        <v>2210124703</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>60061876</v>
+        <v>56060834</v>
       </c>
       <c r="I48" t="n">
-        <v>0.663806</v>
+        <v>0.671764</v>
       </c>
       <c r="J48" t="n">
-        <v>0.628171</v>
+        <v>0.636514</v>
       </c>
       <c r="K48" t="n">
-        <v>0.02828344</v>
+        <v>0.02171301</v>
       </c>
       <c r="L48" t="n">
-        <v>4.45454</v>
+        <v>3.34798</v>
       </c>
       <c r="M48" t="n">
         <v>3302294382.53684</v>
@@ -3657,220 +3657,220 @@
         <v>45938.71164351852</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0009068016663400586</v>
+        <v>0.0009141360617577694</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ethena</t>
+          <t>ondo-finance</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ena</t>
+          <t>ondo</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ethena</t>
+          <t>Ondo</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.210673</v>
+        <v>0.435294</v>
       </c>
       <c r="F49" t="n">
-        <v>2127163402</v>
+        <v>2121311587</v>
       </c>
       <c r="G49" t="n">
         <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>576923127</v>
+        <v>252008569</v>
       </c>
       <c r="I49" t="n">
-        <v>0.224915</v>
+        <v>0.463533</v>
       </c>
       <c r="J49" t="n">
-        <v>0.205259</v>
+        <v>0.422514</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.0139200602721101</v>
+        <v>-0.01531617904591515</v>
       </c>
       <c r="L49" t="n">
-        <v>-6.19789</v>
+        <v>-3.43312</v>
       </c>
       <c r="M49" t="n">
-        <v>10095312500</v>
+        <v>4869330647</v>
       </c>
       <c r="N49" t="n">
-        <v>15000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O49" t="n">
-        <v>1.52</v>
+        <v>2.14</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>45393.21892361111</v>
+        <v>45641.69166666667</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0008700129411331019</v>
+        <v>0.0008628632338804206</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>ethena</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>ena</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>Ethena</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.00451865</v>
+        <v>0.208918</v>
       </c>
       <c r="F50" t="n">
-        <v>2110988113</v>
+        <v>2112989817</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>237169986</v>
+        <v>443685103</v>
       </c>
       <c r="I50" t="n">
-        <v>0.00469623</v>
+        <v>0.218605</v>
       </c>
       <c r="J50" t="n">
-        <v>0.00418118</v>
+        <v>0.203656</v>
       </c>
       <c r="K50" t="n">
-        <v>0.00013365</v>
+        <v>0.00058719</v>
       </c>
       <c r="L50" t="n">
-        <v>3.04787</v>
+        <v>0.33878</v>
       </c>
       <c r="M50" t="n">
-        <v>467093607804.5021</v>
+        <v>10095312500</v>
       </c>
       <c r="N50" t="n">
-        <v>832605428059.7732</v>
+        <v>15000000000</v>
       </c>
       <c r="O50" t="n">
-        <v>0.00881908</v>
+        <v>1.52</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>45914.36296296296</v>
+        <v>45393.21892361111</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R50" t="b">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0008606616358749898</v>
+        <v>0.0008580589808594492</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ondo-finance</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ondo</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Ondo</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.433253</v>
+        <v>0.00445687</v>
       </c>
       <c r="F51" t="n">
-        <v>2108618675</v>
+        <v>2083585191</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>327655256</v>
+        <v>226448298</v>
       </c>
       <c r="I51" t="n">
-        <v>0.463533</v>
+        <v>0.00469623</v>
       </c>
       <c r="J51" t="n">
-        <v>0.426035</v>
+        <v>0.00431196</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.01966368954010023</v>
+        <v>0.00013924</v>
       </c>
       <c r="L51" t="n">
-        <v>-4.34157</v>
+        <v>3.18771</v>
       </c>
       <c r="M51" t="n">
-        <v>4869330647</v>
+        <v>467008882120.3215</v>
       </c>
       <c r="N51" t="n">
-        <v>10000000000</v>
+        <v>832520702375.5927</v>
       </c>
       <c r="O51" t="n">
-        <v>2.14</v>
+        <v>0.00881908</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>45641.69166666667</v>
+        <v>45914.36296296296</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R51" t="b">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0008592918094670554</v>
+        <v>0.0008410833538845346</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3889,28 +3889,28 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4.93e-06</v>
+        <v>4.91e-06</v>
       </c>
       <c r="F52" t="n">
-        <v>2075965729</v>
+        <v>2067006553</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>1450366993</v>
+        <v>961220641</v>
       </c>
       <c r="I52" t="n">
         <v>5.34e-06</v>
       </c>
       <c r="J52" t="n">
-        <v>4.3e-06</v>
+        <v>4.71e-06</v>
       </c>
       <c r="K52" t="n">
-        <v>6.21765e-07</v>
+        <v>9.7696e-08</v>
       </c>
       <c r="L52" t="n">
-        <v>14.417</v>
+        <v>1.97647</v>
       </c>
       <c r="M52" t="n">
         <v>420690000000000</v>
@@ -3925,19 +3925,19 @@
         <v>45635.35457175926</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0008404143930806991</v>
+        <v>0.0008315123165096623</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3956,34 +3956,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="F53" t="n">
-        <v>2008948588</v>
+        <v>2039692689</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>197239330</v>
+        <v>176420599</v>
       </c>
       <c r="I53" t="n">
         <v>1.22</v>
       </c>
       <c r="J53" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.004677001194783426</v>
+        <v>0.00602479</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.39504</v>
+        <v>0.45589</v>
       </c>
       <c r="M53" t="n">
-        <v>1703948257.127239</v>
+        <v>1704000796.081443</v>
       </c>
       <c r="N53" t="n">
-        <v>1703961108.757197</v>
+        <v>1704007261.631945</v>
       </c>
       <c r="O53" t="n">
         <v>54.98</v>
@@ -3992,19 +3992,19 @@
         <v>44504.25704861111</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R53" t="b">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0008016702480445927</v>
+        <v>0.0008157437103553943</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4023,28 +4023,28 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.72357</v>
+        <v>0.727623</v>
       </c>
       <c r="F54" t="n">
-        <v>1962436611</v>
+        <v>1974213251</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>193979356</v>
+        <v>165809899</v>
       </c>
       <c r="I54" t="n">
-        <v>0.763915</v>
+        <v>0.748964</v>
       </c>
       <c r="J54" t="n">
-        <v>0.71743</v>
+        <v>0.7117059999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.03372300192623556</v>
+        <v>-0.01163590523736624</v>
       </c>
       <c r="L54" t="n">
-        <v>-4.4531</v>
+        <v>-1.59472</v>
       </c>
       <c r="M54" t="n">
         <v>2710487455.649731</v>
@@ -4059,19 +4059,19 @@
         <v>45924.13766203704</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0007747806082313388</v>
+        <v>0.0007779416817217009</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4332.88</v>
+        <v>4355.91</v>
       </c>
       <c r="F55" t="n">
-        <v>1882396854</v>
+        <v>1894407221</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>186709924</v>
+        <v>199072964</v>
       </c>
       <c r="I55" t="n">
         <v>4369.08</v>
@@ -4108,16 +4108,16 @@
         <v>4295.5</v>
       </c>
       <c r="K55" t="n">
-        <v>-13.77313524242709</v>
+        <v>18.53</v>
       </c>
       <c r="L55" t="n">
-        <v>-0.31687</v>
+        <v>0.41116</v>
       </c>
       <c r="M55" t="n">
-        <v>434499.367539</v>
+        <v>434903.623539</v>
       </c>
       <c r="N55" t="n">
-        <v>434499.367539</v>
+        <v>434903.623539</v>
       </c>
       <c r="O55" t="n">
         <v>5619.09</v>
@@ -4126,19 +4126,19 @@
         <v>46050.93814814815</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R55" t="b">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0007285077904478598</v>
+        <v>0.0007318687476320498</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4157,31 +4157,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.057917</v>
+        <v>0.058378</v>
       </c>
       <c r="F56" t="n">
-        <v>1839020856</v>
+        <v>1855309470</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>71724577</v>
+        <v>57287055</v>
       </c>
       <c r="I56" t="n">
-        <v>0.058305</v>
+        <v>0.058528</v>
       </c>
       <c r="J56" t="n">
-        <v>0.056587</v>
+        <v>0.056703</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.1592783279993e-05</v>
+        <v>0.00125043</v>
       </c>
       <c r="L56" t="n">
-        <v>-0.05452</v>
+        <v>2.19569</v>
       </c>
       <c r="M56" t="n">
-        <v>31777764435</v>
+        <v>31777768006</v>
       </c>
       <c r="N56" t="n">
         <v>100000000000</v>
@@ -4193,19 +4193,19 @@
         <v>45901.18065972222</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R56" t="b">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.000703431131961371</v>
+        <v>0.0007092971687065402</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4224,31 +4224,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="F57" t="n">
-        <v>1826303769</v>
+        <v>1807976374</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>33524527</v>
+        <v>33520122</v>
       </c>
       <c r="I57" t="n">
-        <v>2.77</v>
+        <v>2.67</v>
       </c>
       <c r="J57" t="n">
         <v>2.56</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.1578461121207484</v>
+        <v>-0.0698690106453359</v>
       </c>
       <c r="L57" t="n">
-        <v>-5.7008</v>
+        <v>-2.64098</v>
       </c>
       <c r="M57" t="n">
-        <v>699252762.2754086</v>
+        <v>699288962.8606994</v>
       </c>
       <c r="N57" t="n">
         <v>1000000000</v>
@@ -4260,19 +4260,19 @@
         <v>45674.19883101852</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.000696079092530671</v>
+        <v>0.0006819712309012499</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4291,31 +4291,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.45889</v>
+        <v>0.460206</v>
       </c>
       <c r="F58" t="n">
-        <v>1671424695</v>
+        <v>1680569073</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>292053266</v>
+        <v>249743884</v>
       </c>
       <c r="I58" t="n">
         <v>0.476706</v>
       </c>
       <c r="J58" t="n">
-        <v>0.429799</v>
+        <v>0.441742</v>
       </c>
       <c r="K58" t="n">
-        <v>0.01019296</v>
+        <v>0.00849258</v>
       </c>
       <c r="L58" t="n">
-        <v>2.27168</v>
+        <v>1.89246</v>
       </c>
       <c r="M58" t="n">
-        <v>3646919863.262543</v>
+        <v>3646959224.069938</v>
       </c>
       <c r="N58" t="n">
         <v>10000000000</v>
@@ -4327,19 +4327,19 @@
         <v>45360.67409722223</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0006065399505055902</v>
+        <v>0.0006084175385109214</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4358,16 +4358,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="F59" t="n">
-        <v>1645830453</v>
+        <v>1662258969</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>82486242</v>
+        <v>71912870</v>
       </c>
       <c r="I59" t="n">
         <v>3.07</v>
@@ -4376,16 +4376,16 @@
         <v>2.89</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.006557359252108874</v>
+        <v>0.01167413</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.2214</v>
+        <v>0.40321</v>
       </c>
       <c r="M59" t="n">
-        <v>556904465.200667</v>
+        <v>556905624.1128303</v>
       </c>
       <c r="N59" t="n">
-        <v>556904695.8959877</v>
+        <v>556905641.1775453</v>
       </c>
       <c r="O59" t="n">
         <v>700.65</v>
@@ -4394,19 +4394,19 @@
         <v>44326.33741898148</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R59" t="b">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0005917433326651304</v>
+        <v>0.0005978469060065021</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4425,31 +4425,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.06808400000000001</v>
+        <v>0.069689</v>
       </c>
       <c r="F60" t="n">
-        <v>1594747765</v>
+        <v>1632669937</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>16921091</v>
+        <v>18938739</v>
       </c>
       <c r="I60" t="n">
-        <v>0.072945</v>
+        <v>0.072129</v>
       </c>
       <c r="J60" t="n">
         <v>0.066889</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.004632569679609663</v>
+        <v>-0.002276997225677535</v>
       </c>
       <c r="L60" t="n">
-        <v>-6.37071</v>
+        <v>-3.19928</v>
       </c>
       <c r="M60" t="n">
-        <v>23425541252.71795</v>
+        <v>23425011020.63758</v>
       </c>
       <c r="N60" t="n">
         <v>23459804203.60596</v>
@@ -4461,19 +4461,19 @@
         <v>45630.09302083333</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0005622112600763256</v>
+        <v>0.0005807648193382068</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4495,25 +4495,25 @@
         <v>1.73e-06</v>
       </c>
       <c r="F61" t="n">
-        <v>1555271183</v>
+        <v>1554986701</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>5232003</v>
+        <v>6629811</v>
       </c>
       <c r="I61" t="n">
         <v>1.75e-06</v>
       </c>
       <c r="J61" t="n">
-        <v>1.72e-06</v>
+        <v>1.71e-06</v>
       </c>
       <c r="K61" t="n">
-        <v>1.0883e-08</v>
+        <v>4.177e-09</v>
       </c>
       <c r="L61" t="n">
-        <v>0.63264</v>
+        <v>0.28796</v>
       </c>
       <c r="M61" t="n">
         <v>898232728634017.2</v>
@@ -4528,19 +4528,19 @@
         <v>45629.67800925926</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0005393889433418985</v>
+        <v>0.0005359173985092443</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4559,34 +4559,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>31.62</v>
+        <v>31.94</v>
       </c>
       <c r="F62" t="n">
-        <v>1521169493</v>
+        <v>1538893470</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>100418149</v>
+        <v>78339005</v>
       </c>
       <c r="I62" t="n">
         <v>32.8</v>
       </c>
       <c r="J62" t="n">
-        <v>30.28</v>
+        <v>30.32</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.8492954790975276</v>
+        <v>-0.5217021934352672</v>
       </c>
       <c r="L62" t="n">
-        <v>-2.61538</v>
+        <v>-1.64228</v>
       </c>
       <c r="M62" t="n">
-        <v>48108760.38154763</v>
+        <v>48110483.86115634</v>
       </c>
       <c r="N62" t="n">
-        <v>81026395.65784027</v>
+        <v>81028467.06059173</v>
       </c>
       <c r="O62" t="n">
         <v>34.53</v>
@@ -4595,19 +4595,19 @@
         <v>46286.34548611111</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005196739748484449</v>
+        <v>0.0005266265921484651</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4626,34 +4626,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.998822</v>
+        <v>0.998385</v>
       </c>
       <c r="F63" t="n">
-        <v>1515482265</v>
+        <v>1514650093</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>3465055</v>
+        <v>2022187</v>
       </c>
       <c r="I63" t="n">
-        <v>0.999067</v>
+        <v>0.999239</v>
       </c>
       <c r="J63" t="n">
-        <v>0.9980869999999999</v>
+        <v>0.998009</v>
       </c>
       <c r="K63" t="n">
-        <v>0.00033376</v>
+        <v>-0.000319527799870545</v>
       </c>
       <c r="L63" t="n">
-        <v>0.03343</v>
+        <v>-0.03532</v>
       </c>
       <c r="M63" t="n">
-        <v>1517262805</v>
+        <v>1517125649</v>
       </c>
       <c r="N63" t="n">
-        <v>1518156193</v>
+        <v>1527073089</v>
       </c>
       <c r="O63" t="n">
         <v>1.24</v>
@@ -4662,19 +4662,19 @@
         <v>46212.39942129629</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0005163860580081039</v>
+        <v>0.000512630613265271</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4693,28 +4693,28 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.217899</v>
+        <v>0.217939</v>
       </c>
       <c r="F64" t="n">
-        <v>1478091105</v>
+        <v>1479790029</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>380079918</v>
+        <v>312111878</v>
       </c>
       <c r="I64" t="n">
-        <v>0.239004</v>
+        <v>0.230082</v>
       </c>
       <c r="J64" t="n">
-        <v>0.215682</v>
+        <v>0.211434</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.02152506723095796</v>
+        <v>-0.003795146315592746</v>
       </c>
       <c r="L64" t="n">
-        <v>-8.99037</v>
+        <v>-1.6999</v>
       </c>
       <c r="M64" t="n">
         <v>6785574605</v>
@@ -4729,153 +4729,153 @@
         <v>45303.18748842592</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0004947693715232498</v>
+        <v>0.000492505499523452</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>bitget-token</t>
+          <t>ethereum-classic</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>bgb</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Bitget Token</t>
+          <t>Ethereum Classic</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2.11</v>
+        <v>9.34</v>
       </c>
       <c r="F65" t="n">
-        <v>1477853649</v>
+        <v>1478692181</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>21410734</v>
+        <v>105301995</v>
       </c>
       <c r="I65" t="n">
-        <v>2.18</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="J65" t="n">
-        <v>2.08</v>
+        <v>8.56</v>
       </c>
       <c r="K65" t="n">
-        <v>0.01659584</v>
+        <v>0.556522</v>
       </c>
       <c r="L65" t="n">
-        <v>0.79187</v>
+        <v>6.33342</v>
       </c>
       <c r="M65" t="n">
-        <v>699992029.6481038</v>
+        <v>158251635.651071</v>
       </c>
       <c r="N65" t="n">
-        <v>910920874.6481038</v>
+        <v>158251635.651071</v>
       </c>
       <c r="O65" t="n">
-        <v>8.449999999999999</v>
+        <v>167.09</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>45653.15375</v>
+        <v>44322.44053240741</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0004946320927678983</v>
+        <v>0.000491871699313813</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ethereum-classic</t>
+          <t>bitget-token</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>bgb</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ethereum Classic</t>
+          <t>Bitget Token</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>9.08</v>
+        <v>2.11</v>
       </c>
       <c r="F66" t="n">
-        <v>1438971590</v>
+        <v>1475117403</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
       </c>
       <c r="H66" t="n">
-        <v>100830875</v>
+        <v>16504894</v>
       </c>
       <c r="I66" t="n">
-        <v>9.01</v>
+        <v>2.18</v>
       </c>
       <c r="J66" t="n">
-        <v>8.56</v>
+        <v>2.08</v>
       </c>
       <c r="K66" t="n">
-        <v>0.31211</v>
+        <v>-0.04551146207062784</v>
       </c>
       <c r="L66" t="n">
-        <v>3.55963</v>
+        <v>-2.09981</v>
       </c>
       <c r="M66" t="n">
-        <v>158248154.4119364</v>
+        <v>699992029.6481038</v>
       </c>
       <c r="N66" t="n">
-        <v>158248154.4119364</v>
+        <v>910920874.6481038</v>
       </c>
       <c r="O66" t="n">
-        <v>167.09</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>44322.44053240741</v>
+        <v>45653.15375</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0004721534834043857</v>
+        <v>0.0004898079390794154</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4897,7 +4897,7 @@
         <v>1.16</v>
       </c>
       <c r="F67" t="n">
-        <v>1425892570</v>
+        <v>1449857663</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
@@ -4912,16 +4912,16 @@
         <v>1.16</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.001697994121032886</v>
+        <v>-0.001720484800925348</v>
       </c>
       <c r="L67" t="n">
-        <v>-0.14607</v>
+        <v>-0.14811</v>
       </c>
       <c r="M67" t="n">
-        <v>1228441715.9192</v>
+        <v>1249985019.14243</v>
       </c>
       <c r="N67" t="n">
-        <v>1228441715.9192</v>
+        <v>1249985019.14243</v>
       </c>
       <c r="O67" t="n">
         <v>1.18</v>
@@ -4930,19 +4930,19 @@
         <v>46255.48263888889</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0004645922022120093</v>
+        <v>0.0004752252022092601</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4961,28 +4961,28 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.999498</v>
+        <v>0.999519</v>
       </c>
       <c r="F68" t="n">
-        <v>1418714402</v>
+        <v>1418612169</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>187654515</v>
+        <v>160832716</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0.999923</v>
       </c>
       <c r="J68" t="n">
-        <v>0.999347</v>
+        <v>0.999328</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.000145093162767673</v>
+        <v>-0.000312985174393487</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.01451</v>
+        <v>-0.03296</v>
       </c>
       <c r="M68" t="n">
         <v>1419429007.8</v>
@@ -4997,19 +4997,19 @@
         <v>46058.54591435185</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0004604423387899702</v>
+        <v>0.000457186821078654</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5028,34 +5028,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>0.9997819999999999</v>
       </c>
       <c r="F69" t="n">
-        <v>1404486256</v>
+        <v>1403486151</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>80565461</v>
+        <v>81824505</v>
       </c>
       <c r="I69" t="n">
         <v>1.001</v>
       </c>
       <c r="J69" t="n">
-        <v>0.999579</v>
+        <v>0.999711</v>
       </c>
       <c r="K69" t="n">
-        <v>5.143e-05</v>
+        <v>6.707000000000001e-05</v>
       </c>
       <c r="L69" t="n">
-        <v>0.00514</v>
+        <v>-0.05448</v>
       </c>
       <c r="M69" t="n">
-        <v>1403784804.97</v>
+        <v>1403784805.97</v>
       </c>
       <c r="N69" t="n">
-        <v>1403784804.97</v>
+        <v>1403784805.97</v>
       </c>
       <c r="O69" t="n">
         <v>1.002</v>
@@ -5064,19 +5064,19 @@
         <v>46092.00303240741</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0004522167215226072</v>
+        <v>0.0004484543978475663</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5095,28 +5095,28 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.995534</v>
+        <v>0.995766</v>
       </c>
       <c r="F70" t="n">
-        <v>1370891045</v>
+        <v>1371171784</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>411852</v>
+        <v>346364</v>
       </c>
       <c r="I70" t="n">
-        <v>0.996795</v>
+        <v>0.996614</v>
       </c>
       <c r="J70" t="n">
-        <v>0.995154</v>
+        <v>0.995093</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.000253253266134124</v>
+        <v>-0.000223555758983696</v>
       </c>
       <c r="L70" t="n">
-        <v>-0.02543</v>
+        <v>-0.02179</v>
       </c>
       <c r="M70" t="n">
         <v>1377035569.737884</v>
@@ -5131,19 +5131,19 @@
         <v>45785.55951388889</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R70" t="b">
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0004327945601459738</v>
+        <v>0.0004297989441062914</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5162,28 +5162,28 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.999744</v>
+        <v>0.999819</v>
       </c>
       <c r="F71" t="n">
-        <v>1319667230</v>
+        <v>1319746233</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>9828086</v>
+        <v>9371061</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0.999993</v>
       </c>
       <c r="J71" t="n">
-        <v>0.999545</v>
+        <v>0.999553</v>
       </c>
       <c r="K71" t="n">
-        <v>6.561e-05</v>
+        <v>4.122e-05</v>
       </c>
       <c r="L71" t="n">
-        <v>0.00656</v>
+        <v>0.00457</v>
       </c>
       <c r="M71" t="n">
         <v>1320000000</v>
@@ -5198,220 +5198,220 @@
         <v>45940.56990740741</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R71" t="b">
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0004031808988042778</v>
+        <v>0.0004001103852123458</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>akedo</t>
+          <t>lighter</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ake</t>
+          <t>lit</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Akedo</t>
+          <t>Lighter</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.05307</v>
+        <v>4.94</v>
       </c>
       <c r="F72" t="n">
-        <v>1211456515</v>
+        <v>1235200763</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>67812608</v>
+        <v>78427779</v>
       </c>
       <c r="I72" t="n">
-        <v>0.06265900000000001</v>
+        <v>4.93</v>
       </c>
       <c r="J72" t="n">
-        <v>0.04984009</v>
+        <v>4.64</v>
       </c>
       <c r="K72" t="n">
-        <v>0.00211539</v>
+        <v>0.213891</v>
       </c>
       <c r="L72" t="n">
-        <v>4.15155</v>
+        <v>4.4898</v>
       </c>
       <c r="M72" t="n">
-        <v>22796250000</v>
+        <v>250000000</v>
       </c>
       <c r="N72" t="n">
-        <v>100000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="O72" t="n">
-        <v>0.146656</v>
+        <v>7.86</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>46285.43993055556</v>
+        <v>46021.04538194444</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.000340621804610439</v>
+        <v>0.0003513013181921147</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>lighter</t>
+          <t>gatechain-token</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>lit</t>
+          <t>gt</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Lighter</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4.73</v>
+        <v>11.07</v>
       </c>
       <c r="F73" t="n">
-        <v>1181549357</v>
+        <v>1183284695</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>72495629</v>
+        <v>3660555</v>
       </c>
       <c r="I73" t="n">
-        <v>5.06</v>
+        <v>11.26</v>
       </c>
       <c r="J73" t="n">
-        <v>4.66</v>
+        <v>10.77</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.2659201923028451</v>
+        <v>-0.168040860000696</v>
       </c>
       <c r="L73" t="n">
-        <v>-5.32724</v>
+        <v>-1.49436</v>
       </c>
       <c r="M73" t="n">
-        <v>250000000</v>
+        <v>106637271.2738255</v>
       </c>
       <c r="N73" t="n">
-        <v>1000000000</v>
+        <v>118888593.6983193</v>
       </c>
       <c r="O73" t="n">
-        <v>7.86</v>
+        <v>25.38</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>46021.04538194444</v>
+        <v>45682.66666666666</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003233317911917861</v>
+        <v>0.0003213295782226181</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>gatechain-token</t>
+          <t>akedo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>gt</t>
+          <t>ake</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Akedo</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>10.95</v>
+        <v>0.051642</v>
       </c>
       <c r="F74" t="n">
-        <v>1169349939</v>
+        <v>1177171406</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>2661408</v>
+        <v>43908083</v>
       </c>
       <c r="I74" t="n">
-        <v>11.4</v>
+        <v>0.06265900000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>10.77</v>
+        <v>0.04882322</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.1406477564008917</v>
+        <v>-0.003907926662397344</v>
       </c>
       <c r="L74" t="n">
-        <v>-1.2679</v>
+        <v>-6.42521</v>
       </c>
       <c r="M74" t="n">
-        <v>106636935.4621455</v>
+        <v>22796250000</v>
       </c>
       <c r="N74" t="n">
-        <v>118888167.5691907</v>
+        <v>100000000000</v>
       </c>
       <c r="O74" t="n">
-        <v>25.38</v>
+        <v>0.146656</v>
       </c>
       <c r="P74" s="1" t="n">
-        <v>45682.66666666666</v>
+        <v>46285.43993055556</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0003162790280733462</v>
+        <v>0.0003178003065476835</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5430,28 +5430,28 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.108627</v>
+        <v>0.108775</v>
       </c>
       <c r="F75" t="n">
-        <v>1164559209</v>
+        <v>1166941505</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
       </c>
       <c r="H75" t="n">
-        <v>85839540</v>
+        <v>80978742</v>
       </c>
       <c r="I75" t="n">
-        <v>0.113856</v>
+        <v>0.112923</v>
       </c>
       <c r="J75" t="n">
-        <v>0.107094</v>
+        <v>0.106356</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.004522956731351641</v>
+        <v>-0.003040010552261871</v>
       </c>
       <c r="L75" t="n">
-        <v>-3.99731</v>
+        <v>-2.75053</v>
       </c>
       <c r="M75" t="n">
         <v>10718755191.33206</v>
@@ -5466,19 +5466,19 @@
         <v>45364.45493055556</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R75" t="b">
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0003135093972717453</v>
+        <v>0.0003118944676716404</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5497,34 +5497,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.04192681</v>
+        <v>0.04167618</v>
       </c>
       <c r="F76" t="n">
-        <v>1160236232</v>
+        <v>1155383815</v>
       </c>
       <c r="G76" t="n">
         <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>33267835</v>
+        <v>24976867</v>
       </c>
       <c r="I76" t="n">
-        <v>0.04506876</v>
+        <v>0.04460429</v>
       </c>
       <c r="J76" t="n">
-        <v>0.04113569</v>
+        <v>0.04133447</v>
       </c>
       <c r="K76" t="n">
-        <v>0.00016146</v>
+        <v>-0.001949097888989622</v>
       </c>
       <c r="L76" t="n">
-        <v>0.38659</v>
+        <v>-4.53567</v>
       </c>
       <c r="M76" t="n">
         <v>27714964311.97035</v>
       </c>
       <c r="N76" t="n">
-        <v>27715035504.33063</v>
+        <v>27715665348.36042</v>
       </c>
       <c r="O76" t="n">
         <v>0.207411</v>
@@ -5533,19 +5533,19 @@
         <v>45504.69498842592</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0003110101851988854</v>
+        <v>0.0003052220810161631</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5564,28 +5564,28 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>72.55</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="F77" t="n">
-        <v>1054175329</v>
+        <v>1076099999</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>22596204</v>
+        <v>25158205</v>
       </c>
       <c r="I77" t="n">
-        <v>74.06</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="J77" t="n">
         <v>65.90000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>4.91</v>
+        <v>6.39</v>
       </c>
       <c r="L77" t="n">
-        <v>7.25948</v>
+        <v>9.54158</v>
       </c>
       <c r="M77" t="n">
         <v>14544176.16408117</v>
@@ -5600,19 +5600,19 @@
         <v>44450.05208333334</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R77" t="b">
         <v>1</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002496939465892375</v>
+        <v>0.0002594506270427726</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5631,16 +5631,16 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.08996</v>
+        <v>0.090235</v>
       </c>
       <c r="F78" t="n">
-        <v>1011705804</v>
+        <v>1014603162</v>
       </c>
       <c r="G78" t="n">
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>12020749</v>
+        <v>12821473</v>
       </c>
       <c r="I78" t="n">
         <v>0.094476</v>
@@ -5649,16 +5649,16 @@
         <v>0.087199</v>
       </c>
       <c r="K78" t="n">
-        <v>0.00152747</v>
+        <v>0.00027014</v>
       </c>
       <c r="L78" t="n">
-        <v>1.72728</v>
+        <v>0.28909</v>
       </c>
       <c r="M78" t="n">
-        <v>11243022007.461</v>
+        <v>11243022455.381</v>
       </c>
       <c r="N78" t="n">
-        <v>17296956934.55538</v>
+        <v>17296957623.66307</v>
       </c>
       <c r="O78" t="n">
         <v>2.99</v>
@@ -5667,19 +5667,19 @@
         <v>45714.36184027778</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46287.58067129629</v>
+        <v>46287.91469907408</v>
       </c>
       <c r="R78" t="b">
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002251413409175848</v>
+        <v>0.000223947799526819</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-      